--- a/Excel/Diy优胜/萃儿.xlsx
+++ b/Excel/Diy优胜/萃儿.xlsx
@@ -5,19 +5,19 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Diy优胜\第一届\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Diy优胜\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98339DC4-8C53-49B6-8514-D327173860F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C29B2047-322F-4980-90F9-EC7F060C190B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
     <sheet name="UnitData" sheetId="1" r:id="rId2"/>
     <sheet name="SkillData" sheetId="2" r:id="rId3"/>
-    <sheet name="ModifyData" sheetId="8" r:id="rId4"/>
-    <sheet name="BuffData" sheetId="6" r:id="rId5"/>
+    <sheet name="BuffData" sheetId="6" r:id="rId4"/>
+    <sheet name="ModifyData" sheetId="8" r:id="rId5"/>
     <sheet name="BulletData" sheetId="4" r:id="rId6"/>
     <sheet name="EffectData" sheetId="9" r:id="rId7"/>
     <sheet name="ContractData" sheetId="11" r:id="rId8"/>
@@ -299,7 +299,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="499">
   <si>
     <t>Id</t>
   </si>
@@ -689,12 +689,6 @@
   </si>
   <si>
     <t>211,81,1500,1500</t>
-  </si>
-  <si>
-    <t>近战位</t>
-  </si>
-  <si>
-    <t>费用回复</t>
   </si>
   <si>
     <t>Default</t>
@@ -1619,10 +1613,6 @@
     <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
-    <t>干员</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
     <t>Muzzle</t>
   </si>
   <si>
@@ -1691,13 +1681,6 @@
     <t>跟随攻击</t>
   </si>
   <si>
-    <t>翠儿普攻</t>
-  </si>
-  <si>
-    <t>翠儿普攻</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
     <t>夜莺普攻击中</t>
   </si>
   <si>
@@ -1727,6 +1710,148 @@
   </si>
   <si>
     <t>萃儿链奶弹道</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>中立单位</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>萃蔓0</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>萃儿天赋标记,萃蔓伤害分摊</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>萃儿普攻</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>萃儿天赋标记</t>
+  </si>
+  <si>
+    <t>普通Buff</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>萃蔓伤害分摊</t>
+  </si>
+  <si>
+    <t>伤害分摊</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"'ShareRate":0.2,"Group":"萃儿天赋","OrderCode":-2000}</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>部署装置</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>被动</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>生成萃蔓0</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>生成萃蔓1</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>ew3类部署装置</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>萃蔓效果</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通技能</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,0</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>萃儿天赋标记</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>萃蔓伤害分摊</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>自己入场</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>萃蔓1</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,-1#-1,0#1,0#0,1</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"召唤物ID":"萃蔓0","召唤位置":"使用本技能索敌位置","部署模式":"追加","召唤物方向":"固定方向"}</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"召唤物ID":"萃蔓1","召唤位置":"使用自身位置","数量":4}</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>萃儿普攻,生成萃蔓0</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>治疗</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"Color":"#96C24E","Alpha":0.25}</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"Color":"#96C24E","Alpha":0.5}</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>萃蔓去重</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>自己以外</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>即死</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>萃蔓无敌</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>仅自己</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>无敌2,绝食2</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>萃蔓效果,萃蔓无敌</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>萃蔓去重,生成萃蔓1,萃蔓效果,萃蔓无敌</t>
     <phoneticPr fontId="15" type="noConversion"/>
   </si>
 </sst>
@@ -2278,10 +2403,10 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="18" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
     </row>
   </sheetData>
@@ -2889,14 +3014,14 @@
     </row>
     <row r="5" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A5" s="18" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>125</v>
       </c>
       <c r="E5" s="13"/>
       <c r="F5" s="2" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -2938,13 +3063,13 @@
         <v>1</v>
       </c>
       <c r="AG5" s="2" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="AH5" s="2" t="s">
         <v>126</v>
       </c>
       <c r="AI5" s="2" t="s">
-        <v>457</v>
+        <v>487</v>
       </c>
       <c r="AJ5" s="2"/>
       <c r="AK5">
@@ -2966,10 +3091,10 @@
         <v>0.25</v>
       </c>
       <c r="BB5" s="2" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="BD5" s="2" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="BE5" s="2" t="s">
         <v>127</v>
@@ -2983,27 +3108,23 @@
       <c r="BH5">
         <v>6</v>
       </c>
-      <c r="BI5" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="BJ5" s="2" t="s">
-        <v>131</v>
-      </c>
+      <c r="BI5" s="2"/>
+      <c r="BJ5" s="2"/>
       <c r="BK5" s="15"/>
       <c r="BM5" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="BN5" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="BP5" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="BN5" s="2" t="s">
+      <c r="BQ5" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="BR5" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="BP5" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="BQ5" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="BR5" s="2" t="s">
-        <v>135</v>
       </c>
       <c r="BS5">
         <v>1</v>
@@ -3011,14 +3132,14 @@
     </row>
     <row r="6" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A6" s="18" t="s">
-        <v>441</v>
+        <v>464</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>437</v>
+        <v>463</v>
       </c>
       <c r="E6" s="13"/>
       <c r="F6" s="2" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -3063,16 +3184,21 @@
         <v>0</v>
       </c>
       <c r="AG6" s="18" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="AH6" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="AI6" s="2"/>
+        <v>428</v>
+      </c>
+      <c r="AI6" s="2" t="s">
+        <v>498</v>
+      </c>
       <c r="AJ6" s="2"/>
       <c r="AK6">
         <v>3</v>
       </c>
+      <c r="AM6">
+        <v>1</v>
+      </c>
       <c r="AN6">
         <v>1</v>
       </c>
@@ -3087,9 +3213,12 @@
         <v>0.25</v>
       </c>
       <c r="BB6" s="2" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="BD6" s="2"/>
+      <c r="BL6" s="2" t="s">
+        <v>490</v>
+      </c>
       <c r="BM6" s="2"/>
       <c r="BN6" s="2"/>
       <c r="BP6" s="2"/>
@@ -3097,13 +3226,99 @@
       <c r="BR6" s="2"/>
     </row>
     <row r="7" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
+      <c r="A7" s="18" t="s">
+        <v>483</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>463</v>
+      </c>
       <c r="E7" s="13"/>
-      <c r="F7" s="2"/>
-      <c r="N7" s="2"/>
-      <c r="AG7" s="2"/>
-      <c r="AI7" s="2"/>
-      <c r="BB7" s="2"/>
+      <c r="F7" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>2</v>
+      </c>
+      <c r="J7">
+        <v>90</v>
+      </c>
+      <c r="K7">
+        <v>100</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0.05</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="18" t="s">
+        <v>438</v>
+      </c>
+      <c r="AH7" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="AI7" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="AJ7" s="2"/>
+      <c r="AK7">
+        <v>3</v>
+      </c>
+      <c r="AM7">
+        <v>1</v>
+      </c>
+      <c r="AN7">
+        <v>1</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>0.5</v>
+      </c>
+      <c r="AV7" s="2"/>
+      <c r="AW7">
+        <v>0.25</v>
+      </c>
+      <c r="BB7" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="BD7" s="2"/>
+      <c r="BL7" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="BM7" s="2"/>
+      <c r="BN7" s="2"/>
+      <c r="BP7" s="2"/>
+      <c r="BQ7" s="2"/>
+      <c r="BR7" s="2"/>
     </row>
     <row r="8" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
@@ -5930,7 +6145,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:DJ822"/>
+  <dimension ref="A1:DJ823"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.08203125" customWidth="1"/>
@@ -6017,334 +6232,334 @@
   <sheetData>
     <row r="1" spans="1:113" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
+        <v>134</v>
+      </c>
+      <c r="D1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E1" t="s">
         <v>136</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>137</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>138</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>140</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="J1" t="s">
         <v>141</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="O1" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="P1" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="Q1" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="R1" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="S1" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="T1" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="U1" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="V1" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="W1" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="U1" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="V1" s="5" t="s">
+      <c r="X1" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="W1" s="5" t="s">
+      <c r="Y1" t="s">
         <v>155</v>
       </c>
-      <c r="X1" s="5" t="s">
+      <c r="Z1" t="s">
         <v>156</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AA1" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AB1" t="s">
         <v>158</v>
       </c>
-      <c r="AA1" s="5" t="s">
+      <c r="AC1" t="s">
         <v>159</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AD1" t="s">
         <v>160</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AE1" t="s">
         <v>161</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AF1" t="s">
         <v>162</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AG1" t="s">
         <v>163</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AH1" t="s">
         <v>164</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AI1" t="s">
         <v>165</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AJ1" t="s">
         <v>166</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AK1" t="s">
         <v>167</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AL1" t="s">
         <v>168</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AM1" t="s">
         <v>169</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AN1" t="s">
         <v>170</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AO1" t="s">
         <v>171</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AP1" t="s">
         <v>172</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AQ1" t="s">
         <v>173</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AR1" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="AS1" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="AT1" t="s">
         <v>174</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AU1" t="s">
         <v>175</v>
       </c>
-      <c r="AR1" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="AS1" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="AT1" t="s">
+      <c r="AV1" t="s">
         <v>176</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AW1" t="s">
         <v>177</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AX1" t="s">
         <v>178</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AY1" t="s">
         <v>179</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AZ1" t="s">
         <v>180</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="BA1" t="s">
         <v>181</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BB1" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BC1" t="s">
         <v>183</v>
       </c>
-      <c r="BB1" s="2" t="s">
+      <c r="BD1" t="s">
         <v>184</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BE1" t="s">
         <v>185</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BF1" t="s">
         <v>186</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BG1" t="s">
         <v>187</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BH1" t="s">
         <v>188</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BJ1" t="s">
+        <v>188</v>
+      </c>
+      <c r="BK1" t="s">
         <v>189</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BL1" t="s">
         <v>190</v>
       </c>
-      <c r="BJ1" t="s">
-        <v>190</v>
-      </c>
-      <c r="BK1" t="s">
+      <c r="BM1" t="s">
         <v>191</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BN1" t="s">
         <v>192</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BO1" t="s">
         <v>193</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BP1" t="s">
         <v>194</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BQ1" t="s">
         <v>195</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BR1" t="s">
         <v>196</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BS1" t="s">
         <v>197</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BT1" t="s">
         <v>198</v>
       </c>
-      <c r="BS1" t="s">
+      <c r="BU1" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="BT1" t="s">
+      <c r="BV1" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="BU1" s="2" t="s">
+      <c r="BW1" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="BV1" s="6" t="s">
+      <c r="BX1" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="BW1" s="6" t="s">
+      <c r="BY1" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="BX1" s="6" t="s">
+      <c r="BZ1" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="BY1" s="6" t="s">
+      <c r="CA1" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="BZ1" s="6" t="s">
+      <c r="CB1" t="s">
         <v>206</v>
       </c>
-      <c r="CA1" s="6" t="s">
+      <c r="CC1" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="CB1" t="s">
+      <c r="CD1" t="s">
         <v>208</v>
       </c>
-      <c r="CC1" s="6" t="s">
+      <c r="CE1" t="s">
         <v>209</v>
       </c>
-      <c r="CD1" t="s">
+      <c r="CF1" t="s">
         <v>210</v>
       </c>
-      <c r="CE1" t="s">
+      <c r="CG1" t="s">
         <v>211</v>
       </c>
-      <c r="CF1" t="s">
+      <c r="CH1" t="s">
         <v>212</v>
       </c>
-      <c r="CG1" t="s">
+      <c r="CI1" t="s">
         <v>213</v>
       </c>
-      <c r="CH1" t="s">
+      <c r="CJ1" t="s">
         <v>214</v>
       </c>
-      <c r="CI1" t="s">
+      <c r="CK1" t="s">
         <v>215</v>
       </c>
-      <c r="CJ1" t="s">
+      <c r="CL1" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="CK1" t="s">
+      <c r="CM1" t="s">
         <v>217</v>
       </c>
-      <c r="CL1" s="2" t="s">
+      <c r="CN1" t="s">
         <v>218</v>
       </c>
-      <c r="CM1" t="s">
+      <c r="CO1" t="s">
         <v>219</v>
       </c>
-      <c r="CN1" t="s">
+      <c r="CP1" t="s">
         <v>220</v>
       </c>
-      <c r="CO1" t="s">
+      <c r="CQ1" t="s">
         <v>221</v>
       </c>
-      <c r="CP1" t="s">
+      <c r="CR1" t="s">
+        <v>198</v>
+      </c>
+      <c r="CS1" t="s">
         <v>222</v>
       </c>
-      <c r="CQ1" t="s">
+      <c r="CT1" t="s">
         <v>223</v>
       </c>
-      <c r="CR1" t="s">
-        <v>200</v>
-      </c>
-      <c r="CS1" t="s">
+      <c r="CU1" t="s">
         <v>224</v>
       </c>
-      <c r="CT1" t="s">
+      <c r="CV1" t="s">
         <v>225</v>
       </c>
-      <c r="CU1" t="s">
+      <c r="CW1" t="s">
         <v>226</v>
       </c>
-      <c r="CV1" t="s">
+      <c r="CX1" t="s">
         <v>227</v>
       </c>
-      <c r="CW1" t="s">
+      <c r="CY1" t="s">
         <v>228</v>
       </c>
-      <c r="CX1" t="s">
+      <c r="CZ1" t="s">
+        <v>227</v>
+      </c>
+      <c r="DA1" t="s">
         <v>229</v>
       </c>
-      <c r="CY1" t="s">
+      <c r="DB1" t="s">
         <v>230</v>
       </c>
-      <c r="CZ1" t="s">
-        <v>229</v>
-      </c>
-      <c r="DA1" t="s">
+      <c r="DC1" t="s">
         <v>231</v>
       </c>
-      <c r="DB1" t="s">
+      <c r="DD1" t="s">
         <v>232</v>
       </c>
-      <c r="DC1" t="s">
+      <c r="DE1" t="s">
         <v>233</v>
       </c>
-      <c r="DD1" t="s">
+      <c r="DF1" t="s">
         <v>234</v>
       </c>
-      <c r="DE1" t="s">
+      <c r="DG1" t="s">
         <v>235</v>
       </c>
-      <c r="DF1" t="s">
+      <c r="DH1" t="s">
         <v>236</v>
       </c>
-      <c r="DG1" t="s">
+      <c r="DI1" t="s">
         <v>237</v>
-      </c>
-      <c r="DH1" t="s">
-        <v>238</v>
-      </c>
-      <c r="DI1" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="2" spans="1:113" x14ac:dyDescent="0.25">
@@ -6358,331 +6573,331 @@
         <v>76</v>
       </c>
       <c r="E2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="G2" t="s">
         <v>52</v>
       </c>
       <c r="H2" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="I2" t="s">
+        <v>241</v>
+      </c>
+      <c r="J2" t="s">
         <v>242</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="J2" t="s">
+      <c r="L2" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="M2" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="N2" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="O2" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="P2" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="Q2" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="R2" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="Q2" s="5" t="s">
+      <c r="S2" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="R2" s="5" t="s">
+      <c r="T2" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="S2" s="5" t="s">
+      <c r="U2" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="T2" s="5" t="s">
+      <c r="V2" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="U2" s="5" t="s">
+      <c r="W2" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="V2" s="5" t="s">
+      <c r="X2" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="W2" s="5" t="s">
+      <c r="Y2" t="s">
         <v>257</v>
       </c>
-      <c r="X2" s="5" t="s">
+      <c r="Z2" t="s">
         <v>258</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="AA2" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AB2" t="s">
         <v>260</v>
       </c>
-      <c r="AA2" s="5" t="s">
+      <c r="AC2" t="s">
         <v>261</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AD2" t="s">
         <v>262</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AE2" t="s">
         <v>263</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AF2" t="s">
         <v>264</v>
       </c>
-      <c r="AE2" t="s">
+      <c r="AG2" t="s">
         <v>265</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AH2" t="s">
         <v>266</v>
       </c>
-      <c r="AG2" t="s">
+      <c r="AI2" t="s">
         <v>267</v>
       </c>
-      <c r="AH2" t="s">
+      <c r="AJ2" t="s">
         <v>268</v>
       </c>
-      <c r="AI2" t="s">
+      <c r="AK2" t="s">
         <v>269</v>
       </c>
-      <c r="AJ2" t="s">
+      <c r="AL2" t="s">
         <v>270</v>
       </c>
-      <c r="AK2" t="s">
+      <c r="AM2" t="s">
         <v>271</v>
       </c>
-      <c r="AL2" t="s">
+      <c r="AN2" t="s">
         <v>272</v>
       </c>
-      <c r="AM2" t="s">
+      <c r="AO2" t="s">
         <v>273</v>
       </c>
-      <c r="AN2" t="s">
+      <c r="AP2" t="s">
         <v>274</v>
       </c>
-      <c r="AO2" t="s">
+      <c r="AQ2" t="s">
         <v>275</v>
       </c>
-      <c r="AP2" t="s">
+      <c r="AR2" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="AS2" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="AT2" t="s">
         <v>276</v>
       </c>
-      <c r="AQ2" t="s">
+      <c r="AU2" t="s">
         <v>277</v>
       </c>
-      <c r="AR2" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="AS2" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="AT2" t="s">
+      <c r="AV2" t="s">
         <v>278</v>
       </c>
-      <c r="AU2" t="s">
+      <c r="AW2" t="s">
         <v>279</v>
       </c>
-      <c r="AV2" t="s">
+      <c r="AX2" t="s">
         <v>280</v>
       </c>
-      <c r="AW2" t="s">
+      <c r="AY2" t="s">
         <v>281</v>
       </c>
-      <c r="AX2" t="s">
+      <c r="AZ2" t="s">
         <v>282</v>
       </c>
-      <c r="AY2" t="s">
+      <c r="BA2" t="s">
         <v>283</v>
       </c>
-      <c r="AZ2" t="s">
+      <c r="BB2" t="s">
         <v>284</v>
       </c>
-      <c r="BA2" t="s">
+      <c r="BC2" t="s">
         <v>285</v>
       </c>
-      <c r="BB2" t="s">
+      <c r="BD2" t="s">
         <v>286</v>
       </c>
-      <c r="BC2" t="s">
+      <c r="BE2" t="s">
         <v>287</v>
       </c>
-      <c r="BD2" t="s">
+      <c r="BF2" t="s">
         <v>288</v>
       </c>
-      <c r="BE2" t="s">
+      <c r="BG2" t="s">
         <v>289</v>
       </c>
-      <c r="BF2" t="s">
+      <c r="BH2" t="s">
         <v>290</v>
       </c>
-      <c r="BG2" t="s">
+      <c r="BI2" t="s">
         <v>291</v>
       </c>
-      <c r="BH2" t="s">
+      <c r="BJ2" t="s">
         <v>292</v>
       </c>
-      <c r="BI2" t="s">
+      <c r="BK2" t="s">
         <v>293</v>
       </c>
-      <c r="BJ2" t="s">
+      <c r="BL2" t="s">
         <v>294</v>
       </c>
-      <c r="BK2" t="s">
+      <c r="BM2" t="s">
         <v>295</v>
       </c>
-      <c r="BL2" t="s">
+      <c r="BN2" t="s">
         <v>296</v>
-      </c>
-      <c r="BM2" t="s">
-        <v>297</v>
-      </c>
-      <c r="BN2" t="s">
-        <v>298</v>
       </c>
       <c r="BO2" t="s">
         <v>78</v>
       </c>
       <c r="BP2" t="s">
+        <v>297</v>
+      </c>
+      <c r="BQ2" t="s">
+        <v>298</v>
+      </c>
+      <c r="BR2" t="s">
         <v>299</v>
       </c>
-      <c r="BQ2" t="s">
+      <c r="BS2" t="s">
         <v>300</v>
       </c>
-      <c r="BR2" t="s">
+      <c r="BT2" t="s">
         <v>301</v>
-      </c>
-      <c r="BS2" t="s">
-        <v>302</v>
-      </c>
-      <c r="BT2" t="s">
-        <v>303</v>
       </c>
       <c r="BU2" s="2" t="s">
         <v>94</v>
       </c>
       <c r="BV2" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="BW2" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="BX2" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="BY2" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="BW2" s="6" t="s">
-        <v>439</v>
-      </c>
-      <c r="BX2" s="6" t="s">
+      <c r="BZ2" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="BY2" s="6" t="s">
+      <c r="CA2" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="BZ2" s="6" t="s">
+      <c r="CB2" t="s">
         <v>307</v>
       </c>
-      <c r="CA2" s="6" t="s">
+      <c r="CC2" t="s">
         <v>308</v>
       </c>
-      <c r="CB2" t="s">
+      <c r="CD2" t="s">
         <v>309</v>
       </c>
-      <c r="CC2" t="s">
+      <c r="CE2" t="s">
         <v>310</v>
       </c>
-      <c r="CD2" t="s">
+      <c r="CF2" t="s">
         <v>311</v>
       </c>
-      <c r="CE2" t="s">
+      <c r="CG2" t="s">
         <v>312</v>
       </c>
-      <c r="CF2" t="s">
+      <c r="CH2" t="s">
         <v>313</v>
       </c>
-      <c r="CG2" t="s">
+      <c r="CI2" t="s">
         <v>314</v>
       </c>
-      <c r="CH2" t="s">
+      <c r="CJ2" t="s">
         <v>315</v>
       </c>
-      <c r="CI2" t="s">
+      <c r="CK2" t="s">
         <v>316</v>
       </c>
-      <c r="CJ2" t="s">
+      <c r="CL2" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="CK2" t="s">
+      <c r="CM2" t="s">
         <v>318</v>
       </c>
-      <c r="CL2" s="2" t="s">
+      <c r="CN2" t="s">
         <v>319</v>
       </c>
-      <c r="CM2" t="s">
+      <c r="CO2" t="s">
         <v>320</v>
       </c>
-      <c r="CN2" t="s">
+      <c r="CP2" t="s">
         <v>321</v>
       </c>
-      <c r="CO2" t="s">
+      <c r="CQ2" t="s">
         <v>322</v>
       </c>
-      <c r="CP2" t="s">
+      <c r="CR2" t="s">
         <v>323</v>
       </c>
-      <c r="CQ2" t="s">
+      <c r="CS2" t="s">
         <v>324</v>
       </c>
-      <c r="CR2" t="s">
+      <c r="CT2" t="s">
         <v>325</v>
       </c>
-      <c r="CS2" t="s">
+      <c r="CU2" t="s">
         <v>326</v>
       </c>
-      <c r="CT2" t="s">
+      <c r="CV2" t="s">
         <v>327</v>
       </c>
-      <c r="CU2" t="s">
+      <c r="CW2" t="s">
         <v>328</v>
       </c>
-      <c r="CV2" t="s">
+      <c r="CX2" t="s">
         <v>329</v>
       </c>
-      <c r="CW2" t="s">
+      <c r="CY2" t="s">
         <v>330</v>
       </c>
-      <c r="CX2" t="s">
+      <c r="CZ2" t="s">
         <v>331</v>
       </c>
-      <c r="CY2" t="s">
+      <c r="DA2" t="s">
         <v>332</v>
       </c>
-      <c r="CZ2" t="s">
+      <c r="DB2" t="s">
         <v>333</v>
       </c>
-      <c r="DA2" t="s">
+      <c r="DC2" t="s">
         <v>334</v>
       </c>
-      <c r="DB2" t="s">
+      <c r="DD2" t="s">
         <v>335</v>
       </c>
-      <c r="DC2" t="s">
+      <c r="DE2" t="s">
         <v>336</v>
       </c>
-      <c r="DD2" t="s">
+      <c r="DF2" t="s">
         <v>337</v>
       </c>
-      <c r="DE2" t="s">
+      <c r="DG2" t="s">
         <v>338</v>
       </c>
-      <c r="DF2" t="s">
+      <c r="DH2" t="s">
         <v>339</v>
       </c>
-      <c r="DG2" t="s">
+      <c r="DI2" t="s">
         <v>340</v>
-      </c>
-      <c r="DH2" t="s">
-        <v>341</v>
-      </c>
-      <c r="DI2" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="3" spans="1:113" x14ac:dyDescent="0.25">
@@ -6711,13 +6926,13 @@
         <v>115</v>
       </c>
       <c r="J3" t="s">
+        <v>341</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="L3" s="5" t="s">
         <v>343</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>344</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>345</v>
       </c>
       <c r="M3" s="5" t="s">
         <v>117</v>
@@ -6780,7 +6995,7 @@
         <v>115</v>
       </c>
       <c r="AG3" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="AH3" t="s">
         <v>115</v>
@@ -6804,22 +7019,22 @@
         <v>115</v>
       </c>
       <c r="AO3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="AP3" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="AQ3" t="s">
         <v>2</v>
       </c>
       <c r="AR3" s="2" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="AS3" s="2" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="AT3" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="AU3" t="s">
         <v>115</v>
@@ -6831,7 +7046,7 @@
         <v>115</v>
       </c>
       <c r="AX3" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="AY3" t="s">
         <v>115</v>
@@ -6861,7 +7076,7 @@
         <v>115</v>
       </c>
       <c r="BH3" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="BI3" t="s">
         <v>115</v>
@@ -6888,10 +7103,10 @@
         <v>118</v>
       </c>
       <c r="BQ3" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="BR3" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="BS3" t="s">
         <v>116</v>
@@ -6912,19 +7127,19 @@
         <v>117</v>
       </c>
       <c r="BY3" s="6" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="BZ3" s="6" t="s">
         <v>115</v>
       </c>
       <c r="CA3" s="6" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="CB3" t="s">
         <v>123</v>
       </c>
       <c r="CC3" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="CD3" t="s">
         <v>123</v>
@@ -6936,19 +7151,19 @@
         <v>123</v>
       </c>
       <c r="CG3" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="CH3" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="CI3" t="s">
         <v>2</v>
       </c>
       <c r="CJ3" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="CK3" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="CL3" s="2" t="s">
         <v>124</v>
@@ -6969,7 +7184,7 @@
         <v>122</v>
       </c>
       <c r="CR3" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="CS3" t="s">
         <v>122</v>
@@ -6981,28 +7196,28 @@
         <v>124</v>
       </c>
       <c r="CV3" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="CW3" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="CX3" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="CY3" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="CZ3" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="DA3" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="DB3" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="DC3" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="DD3" t="s">
         <v>115</v>
@@ -7025,7 +7240,7 @@
     </row>
     <row r="4" spans="1:113" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="5" spans="1:113" x14ac:dyDescent="0.25">
@@ -7036,23 +7251,23 @@
     </row>
     <row r="6" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="C6" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="P6" s="3"/>
       <c r="AC6">
         <v>1</v>
       </c>
       <c r="AO6" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="AT6" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="AY6">
         <v>1</v>
@@ -7067,60 +7282,208 @@
         <v>56</v>
       </c>
       <c r="CG6" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="CH6" s="2" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="CI6" t="s">
-        <v>438</v>
+        <v>435</v>
+      </c>
+      <c r="CN6" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="CR6">
+        <v>9999</v>
       </c>
       <c r="CY6" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
     </row>
     <row r="7" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
-      <c r="C7" s="2"/>
+      <c r="A7" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>473</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>488</v>
+      </c>
+      <c r="Q7" s="5" t="s">
+        <v>480</v>
+      </c>
+      <c r="AC7">
+        <v>1</v>
+      </c>
+      <c r="AF7">
+        <v>1</v>
+      </c>
       <c r="AT7" s="2"/>
+      <c r="AV7">
+        <v>20</v>
+      </c>
+      <c r="BD7">
+        <v>1</v>
+      </c>
       <c r="BV7"/>
       <c r="CL7" s="5"/>
-      <c r="CU7" s="2"/>
+      <c r="CU7" s="2" t="s">
+        <v>485</v>
+      </c>
     </row>
     <row r="8" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="J8" s="2"/>
-      <c r="O8"/>
-      <c r="AO8" s="2"/>
-      <c r="CU8" s="2"/>
+      <c r="A8" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>473</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>482</v>
+      </c>
+      <c r="AC8">
+        <v>1</v>
+      </c>
+      <c r="AT8" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="BD8">
+        <v>1</v>
+      </c>
+      <c r="BV8"/>
+      <c r="CL8" s="5"/>
+      <c r="CU8" s="2" t="s">
+        <v>486</v>
+      </c>
     </row>
     <row r="9" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="P9"/>
+      <c r="A9" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>473</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>482</v>
+      </c>
+      <c r="AC9">
+        <v>1</v>
+      </c>
+      <c r="AT9" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="BD9">
+        <v>99</v>
+      </c>
+      <c r="BV9"/>
+      <c r="CL9" s="5"/>
+      <c r="CM9" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="CN9" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="CR9">
+        <v>9999</v>
+      </c>
+      <c r="CU9" s="2"/>
     </row>
     <row r="10" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>473</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>482</v>
+      </c>
+      <c r="AC10">
+        <v>1</v>
+      </c>
+      <c r="AG10" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="AJ10" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="AN10">
+        <v>1</v>
+      </c>
+      <c r="AT10" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="BD10">
+        <v>99</v>
+      </c>
+      <c r="BV10"/>
       <c r="CL10" s="5"/>
+      <c r="CM10" s="2"/>
+      <c r="CN10" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="CR10">
+        <v>1</v>
+      </c>
+      <c r="CU10" s="2"/>
+      <c r="DD10">
+        <v>1</v>
+      </c>
+      <c r="DG10">
+        <v>1</v>
+      </c>
+      <c r="DH10">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
-      <c r="M11"/>
-      <c r="N11"/>
-      <c r="O11" s="7"/>
-      <c r="P11"/>
-      <c r="Q11"/>
-      <c r="R11" s="7"/>
-      <c r="S11" s="7"/>
-      <c r="T11" s="7"/>
-      <c r="U11" s="7"/>
-      <c r="V11" s="7"/>
-      <c r="W11" s="7"/>
-      <c r="X11"/>
-      <c r="BU11" s="8"/>
-      <c r="BV11" s="8"/>
-      <c r="BW11" s="8"/>
-      <c r="BX11" s="8"/>
-      <c r="BY11" s="8"/>
-      <c r="BZ11" s="8"/>
-      <c r="CA11"/>
+      <c r="A11" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>473</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>482</v>
+      </c>
+      <c r="AC11">
+        <v>1</v>
+      </c>
+      <c r="AG11" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="AN11">
+        <v>1</v>
+      </c>
+      <c r="BD11">
+        <v>1</v>
+      </c>
+      <c r="CL11" s="5"/>
+      <c r="CN11" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="CR11">
+        <v>9999</v>
+      </c>
     </row>
     <row r="12" spans="1:113" x14ac:dyDescent="0.25">
       <c r="K12" s="7"/>
@@ -7144,152 +7507,167 @@
       <c r="BY12" s="8"/>
       <c r="BZ12" s="8"/>
       <c r="CA12"/>
-      <c r="CN12" s="3"/>
     </row>
     <row r="13" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="AY13" s="5"/>
-      <c r="BV13"/>
-      <c r="BW13"/>
-      <c r="BX13"/>
-      <c r="BY13"/>
-      <c r="BZ13"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
+      <c r="M13"/>
+      <c r="N13"/>
+      <c r="O13" s="7"/>
+      <c r="P13"/>
+      <c r="Q13"/>
+      <c r="R13" s="7"/>
+      <c r="S13" s="7"/>
+      <c r="T13" s="7"/>
+      <c r="U13" s="7"/>
+      <c r="V13" s="7"/>
+      <c r="W13" s="7"/>
+      <c r="X13"/>
+      <c r="BU13" s="8"/>
+      <c r="BV13" s="8"/>
+      <c r="BW13" s="8"/>
+      <c r="BX13" s="8"/>
+      <c r="BY13" s="8"/>
+      <c r="BZ13" s="8"/>
       <c r="CA13"/>
-      <c r="CB13" s="5"/>
-      <c r="CC13" s="5"/>
-      <c r="CD13" s="5"/>
-      <c r="CE13" s="5"/>
-      <c r="CF13" s="5"/>
-      <c r="CH13" s="5"/>
-      <c r="CI13" s="5"/>
-      <c r="CJ13" s="5"/>
-      <c r="CK13" s="5"/>
-      <c r="CL13" s="5"/>
-      <c r="CM13" s="5"/>
+      <c r="CN13" s="3"/>
     </row>
     <row r="14" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="M14"/>
-      <c r="N14"/>
-      <c r="P14" s="3"/>
-      <c r="R14" s="3"/>
-      <c r="S14"/>
-      <c r="X14"/>
+      <c r="AY14" s="5"/>
       <c r="BV14"/>
-      <c r="CB14" s="6"/>
+      <c r="BW14"/>
+      <c r="BX14"/>
+      <c r="BY14"/>
+      <c r="BZ14"/>
+      <c r="CA14"/>
+      <c r="CB14" s="5"/>
+      <c r="CC14" s="5"/>
+      <c r="CD14" s="5"/>
+      <c r="CE14" s="5"/>
+      <c r="CF14" s="5"/>
+      <c r="CH14" s="5"/>
+      <c r="CI14" s="5"/>
+      <c r="CJ14" s="5"/>
+      <c r="CK14" s="5"/>
+      <c r="CL14" s="5"/>
+      <c r="CM14" s="5"/>
     </row>
     <row r="15" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="M15"/>
+      <c r="N15"/>
+      <c r="P15" s="3"/>
+      <c r="R15" s="3"/>
+      <c r="S15"/>
+      <c r="X15"/>
       <c r="BV15"/>
+      <c r="CB15" s="6"/>
     </row>
     <row r="16" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="M16"/>
-      <c r="O16"/>
-      <c r="BO16" s="2"/>
-      <c r="BP16" s="2"/>
-      <c r="CN16" s="3"/>
+      <c r="BV16"/>
     </row>
     <row r="17" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="J17" s="5"/>
       <c r="M17"/>
-      <c r="O17" s="3"/>
-      <c r="P17"/>
-      <c r="Q17"/>
-      <c r="CN17" s="2"/>
+      <c r="O17"/>
+      <c r="BO17" s="2"/>
+      <c r="BP17" s="2"/>
+      <c r="CN17" s="3"/>
     </row>
     <row r="18" spans="1:92" x14ac:dyDescent="0.25">
+      <c r="J18" s="5"/>
       <c r="M18"/>
-      <c r="CB18" s="9"/>
+      <c r="O18" s="3"/>
+      <c r="P18"/>
+      <c r="Q18"/>
+      <c r="CN18" s="2"/>
     </row>
     <row r="19" spans="1:92" x14ac:dyDescent="0.25">
       <c r="M19"/>
-      <c r="O19" s="3"/>
-      <c r="P19"/>
-      <c r="Q19"/>
+      <c r="CB19" s="9"/>
     </row>
     <row r="20" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="A20" s="2"/>
       <c r="M20"/>
       <c r="O20" s="3"/>
       <c r="P20"/>
       <c r="Q20"/>
-      <c r="CN20" s="3"/>
     </row>
     <row r="21" spans="1:92" x14ac:dyDescent="0.25">
+      <c r="A21" s="2"/>
       <c r="M21"/>
-      <c r="AY21" s="5"/>
-      <c r="BV21"/>
-      <c r="BW21"/>
-      <c r="BX21"/>
-      <c r="BY21"/>
-      <c r="BZ21"/>
-      <c r="CA21"/>
-      <c r="CB21" s="5"/>
-      <c r="CC21" s="5"/>
-      <c r="CD21" s="5"/>
-      <c r="CE21" s="5"/>
-      <c r="CF21" s="5"/>
-      <c r="CH21" s="5"/>
-      <c r="CI21" s="5"/>
-      <c r="CJ21" s="5"/>
-      <c r="CK21" s="5"/>
+      <c r="O21" s="3"/>
+      <c r="P21"/>
+      <c r="Q21"/>
       <c r="CN21" s="3"/>
     </row>
     <row r="22" spans="1:92" x14ac:dyDescent="0.25">
       <c r="M22"/>
-      <c r="O22" s="3"/>
-      <c r="P22" s="3"/>
+      <c r="AY22" s="5"/>
+      <c r="BV22"/>
+      <c r="BW22"/>
+      <c r="BX22"/>
+      <c r="BY22"/>
+      <c r="BZ22"/>
+      <c r="CA22"/>
+      <c r="CB22" s="5"/>
+      <c r="CC22" s="5"/>
+      <c r="CD22" s="5"/>
+      <c r="CE22" s="5"/>
+      <c r="CF22" s="5"/>
+      <c r="CH22" s="5"/>
+      <c r="CI22" s="5"/>
+      <c r="CJ22" s="5"/>
+      <c r="CK22" s="5"/>
+      <c r="CN22" s="3"/>
     </row>
     <row r="23" spans="1:92" x14ac:dyDescent="0.25">
       <c r="M23"/>
-      <c r="N23"/>
-      <c r="BV23"/>
-      <c r="CI23" s="5"/>
-      <c r="CJ23" s="5"/>
+      <c r="O23" s="3"/>
+      <c r="P23" s="3"/>
     </row>
     <row r="24" spans="1:92" x14ac:dyDescent="0.25">
       <c r="M24"/>
       <c r="N24"/>
       <c r="BV24"/>
+      <c r="CI24" s="5"/>
       <c r="CJ24" s="5"/>
     </row>
     <row r="25" spans="1:92" x14ac:dyDescent="0.25">
       <c r="M25"/>
-      <c r="O25" s="3"/>
-      <c r="AG25" s="2"/>
-      <c r="AO25" s="2"/>
-      <c r="BO25" s="2"/>
-      <c r="BP25" s="2"/>
-      <c r="CG25" s="2"/>
-      <c r="CM25" s="2"/>
+      <c r="N25"/>
+      <c r="BV25"/>
+      <c r="CJ25" s="5"/>
     </row>
     <row r="26" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="A26" s="2"/>
       <c r="M26"/>
       <c r="O26" s="3"/>
       <c r="AG26" s="2"/>
       <c r="AO26" s="2"/>
+      <c r="BO26" s="2"/>
+      <c r="BP26" s="2"/>
       <c r="CG26" s="2"/>
+      <c r="CM26" s="2"/>
     </row>
     <row r="27" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="BU27" s="6"/>
-      <c r="CA27"/>
+      <c r="A27" s="2"/>
+      <c r="M27"/>
+      <c r="O27" s="3"/>
+      <c r="AG27" s="2"/>
+      <c r="AO27" s="2"/>
+      <c r="CG27" s="2"/>
     </row>
     <row r="28" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="E28" s="2"/>
-      <c r="O28"/>
-      <c r="W28"/>
-      <c r="X28"/>
-      <c r="BO28" s="2"/>
-      <c r="BP28" s="2"/>
-      <c r="CN28" s="3"/>
+      <c r="BU28" s="6"/>
+      <c r="CA28"/>
     </row>
     <row r="29" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="M29"/>
-      <c r="O29" s="3"/>
-      <c r="P29"/>
-      <c r="Q29"/>
+      <c r="E29" s="2"/>
+      <c r="O29"/>
+      <c r="W29"/>
+      <c r="X29"/>
+      <c r="BO29" s="2"/>
+      <c r="BP29" s="2"/>
       <c r="CN29" s="3"/>
     </row>
     <row r="30" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="A30" s="2"/>
       <c r="M30"/>
       <c r="O30" s="3"/>
       <c r="P30"/>
@@ -7298,84 +7676,89 @@
     </row>
     <row r="31" spans="1:92" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
+      <c r="M31"/>
       <c r="O31" s="3"/>
+      <c r="P31"/>
+      <c r="Q31"/>
+      <c r="CN31" s="3"/>
     </row>
     <row r="32" spans="1:92" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
-      <c r="CL32" s="5"/>
+      <c r="O32" s="3"/>
     </row>
     <row r="33" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="A33" s="2"/>
       <c r="CL33" s="5"/>
     </row>
     <row r="34" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="A34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="J34" s="2"/>
-      <c r="AJ34" s="2"/>
       <c r="CL34" s="5"/>
-      <c r="CU34" s="2"/>
     </row>
     <row r="35" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="A35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="J35" s="2"/>
+      <c r="AJ35" s="2"/>
       <c r="CL35" s="5"/>
+      <c r="CU35" s="2"/>
     </row>
     <row r="36" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="O36"/>
-      <c r="W36"/>
-      <c r="X36"/>
-      <c r="CN36" s="3"/>
+      <c r="CL36" s="5"/>
     </row>
     <row r="37" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="O37" s="3"/>
+      <c r="O37"/>
+      <c r="W37"/>
       <c r="X37"/>
+      <c r="CN37" s="3"/>
     </row>
     <row r="38" spans="1:99" x14ac:dyDescent="0.25">
       <c r="O38" s="3"/>
-      <c r="P38"/>
-      <c r="Q38"/>
       <c r="X38"/>
     </row>
     <row r="39" spans="1:99" x14ac:dyDescent="0.25">
       <c r="O39" s="3"/>
+      <c r="P39"/>
+      <c r="Q39"/>
       <c r="X39"/>
     </row>
-    <row r="42" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="CM42" s="3"/>
-      <c r="CN42" s="3"/>
-    </row>
-    <row r="44" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="M44"/>
-      <c r="N44"/>
-      <c r="BV44"/>
-      <c r="CB44" s="10"/>
-      <c r="CI44" s="5"/>
-      <c r="CJ44" s="5"/>
+    <row r="40" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="O40" s="3"/>
+      <c r="X40"/>
+    </row>
+    <row r="43" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="CM43" s="3"/>
+      <c r="CN43" s="3"/>
     </row>
     <row r="45" spans="1:99" x14ac:dyDescent="0.25">
       <c r="M45"/>
       <c r="N45"/>
       <c r="BV45"/>
       <c r="CB45" s="10"/>
+      <c r="CI45" s="5"/>
       <c r="CJ45" s="5"/>
     </row>
     <row r="46" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="O46"/>
-      <c r="X46"/>
-      <c r="CM46" s="3"/>
-    </row>
-    <row r="49" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL49" s="5"/>
+      <c r="M46"/>
+      <c r="N46"/>
+      <c r="BV46"/>
+      <c r="CB46" s="10"/>
+      <c r="CJ46" s="5"/>
+    </row>
+    <row r="47" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="O47"/>
+      <c r="X47"/>
+      <c r="CM47" s="3"/>
     </row>
     <row r="50" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL50" s="5"/>
     </row>
-    <row r="56" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL56" s="5"/>
+    <row r="51" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL51" s="5"/>
     </row>
     <row r="57" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL57" s="5"/>
     </row>
-    <row r="59" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL59" s="5"/>
+    <row r="58" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL58" s="5"/>
     </row>
     <row r="60" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL60" s="5"/>
@@ -7387,50 +7770,50 @@
       <c r="CL62" s="5"/>
     </row>
     <row r="63" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV63"/>
+      <c r="CL63" s="5"/>
     </row>
     <row r="64" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV64"/>
     </row>
     <row r="65" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV65"/>
-      <c r="CL65" s="5"/>
     </row>
     <row r="66" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV66"/>
       <c r="CL66" s="5"/>
     </row>
     <row r="67" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL67" s="5"/>
     </row>
     <row r="68" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV68"/>
+      <c r="CL68" s="5"/>
     </row>
     <row r="69" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL69" s="5"/>
-    </row>
-    <row r="73" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV73"/>
+      <c r="BV69"/>
+    </row>
+    <row r="70" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL70" s="5"/>
     </row>
     <row r="74" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL74" s="5"/>
-    </row>
-    <row r="82" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL82" s="5"/>
+      <c r="BV74"/>
+    </row>
+    <row r="75" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL75" s="5"/>
     </row>
     <row r="83" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL83" s="5"/>
     </row>
     <row r="84" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV84"/>
-    </row>
-    <row r="89" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV89"/>
+      <c r="CL84" s="5"/>
+    </row>
+    <row r="85" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV85"/>
     </row>
     <row r="90" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV90"/>
-      <c r="CL90" s="5"/>
     </row>
     <row r="91" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV91"/>
       <c r="CL91" s="5"/>
     </row>
     <row r="92" spans="74:90" x14ac:dyDescent="0.25">
@@ -7443,10 +7826,10 @@
       <c r="CL94" s="5"/>
     </row>
     <row r="95" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV95"/>
+      <c r="CL95" s="5"/>
     </row>
     <row r="96" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL96" s="5"/>
+      <c r="BV96"/>
     </row>
     <row r="97" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL97" s="5"/>
@@ -7458,10 +7841,10 @@
       <c r="CL99" s="5"/>
     </row>
     <row r="100" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV100"/>
+      <c r="CL100" s="5"/>
     </row>
     <row r="101" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL101" s="5"/>
+      <c r="BV101"/>
     </row>
     <row r="102" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL102" s="5"/>
@@ -7472,8 +7855,8 @@
     <row r="104" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL104" s="5"/>
     </row>
-    <row r="107" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL107" s="5"/>
+    <row r="105" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL105" s="5"/>
     </row>
     <row r="108" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL108" s="5"/>
@@ -7487,11 +7870,11 @@
     <row r="111" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL111" s="5"/>
     </row>
-    <row r="113" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV113"/>
+    <row r="112" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL112" s="5"/>
     </row>
     <row r="114" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL114" s="5"/>
+      <c r="BV114"/>
     </row>
     <row r="115" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL115" s="5"/>
@@ -7502,17 +7885,17 @@
     <row r="117" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL117" s="5"/>
     </row>
-    <row r="121" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL121" s="5"/>
-    </row>
-    <row r="123" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV123"/>
+    <row r="118" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL118" s="5"/>
+    </row>
+    <row r="122" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL122" s="5"/>
     </row>
     <row r="124" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV124"/>
-      <c r="CL124" s="5"/>
     </row>
     <row r="125" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV125"/>
       <c r="CL125" s="5"/>
     </row>
     <row r="126" spans="74:90" x14ac:dyDescent="0.25">
@@ -7524,50 +7907,50 @@
     <row r="128" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL128" s="5"/>
     </row>
-    <row r="130" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV130"/>
+    <row r="129" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL129" s="5"/>
     </row>
     <row r="131" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL131" s="5"/>
+      <c r="BV131"/>
     </row>
     <row r="132" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL132" s="5"/>
     </row>
-    <row r="134" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL134" s="5"/>
+    <row r="133" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL133" s="5"/>
     </row>
     <row r="135" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL135" s="5"/>
     </row>
-    <row r="137" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV137"/>
+    <row r="136" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL136" s="5"/>
     </row>
     <row r="138" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL138" s="5"/>
-    </row>
-    <row r="141" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL141" s="5"/>
+      <c r="BV138"/>
+    </row>
+    <row r="139" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL139" s="5"/>
     </row>
     <row r="142" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL142" s="5"/>
     </row>
-    <row r="145" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL145" s="5"/>
-    </row>
-    <row r="147" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL147" s="5"/>
-    </row>
-    <row r="149" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV149"/>
+    <row r="143" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL143" s="5"/>
+    </row>
+    <row r="146" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL146" s="5"/>
+    </row>
+    <row r="148" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL148" s="5"/>
     </row>
     <row r="150" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL150" s="5"/>
+      <c r="BV150"/>
     </row>
     <row r="151" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL151" s="5"/>
     </row>
-    <row r="153" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL153" s="5"/>
+    <row r="152" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL152" s="5"/>
     </row>
     <row r="154" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL154" s="5"/>
@@ -7575,187 +7958,186 @@
     <row r="155" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL155" s="5"/>
     </row>
-    <row r="160" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL160" s="5"/>
+    <row r="156" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL156" s="5"/>
     </row>
     <row r="161" spans="90:90" x14ac:dyDescent="0.25">
       <c r="CL161" s="5"/>
     </row>
-    <row r="164" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL164" s="5"/>
+    <row r="162" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL162" s="5"/>
     </row>
     <row r="165" spans="90:90" x14ac:dyDescent="0.25">
       <c r="CL165" s="5"/>
     </row>
-    <row r="169" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL169" s="5"/>
-    </row>
-    <row r="173" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL173" s="5"/>
-    </row>
-    <row r="175" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL175" s="5"/>
+    <row r="166" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL166" s="5"/>
+    </row>
+    <row r="170" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL170" s="5"/>
+    </row>
+    <row r="174" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL174" s="5"/>
     </row>
     <row r="176" spans="90:90" x14ac:dyDescent="0.25">
       <c r="CL176" s="5"/>
     </row>
-    <row r="178" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL178" s="5"/>
+    <row r="177" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL177" s="5"/>
     </row>
     <row r="179" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL179" s="5"/>
     </row>
-    <row r="181" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV181"/>
+    <row r="180" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL180" s="5"/>
     </row>
     <row r="182" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV182"/>
-      <c r="CL182" s="5"/>
     </row>
     <row r="183" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV183"/>
       <c r="CL183" s="5"/>
     </row>
-    <row r="185" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL185" s="5"/>
-    </row>
-    <row r="194" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV194"/>
+    <row r="184" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL184" s="5"/>
+    </row>
+    <row r="186" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL186" s="5"/>
     </row>
     <row r="195" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV195"/>
-      <c r="CL195" s="5"/>
     </row>
     <row r="196" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV196"/>
       <c r="CL196" s="5"/>
     </row>
     <row r="197" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL197" s="5"/>
     </row>
     <row r="198" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV198"/>
+      <c r="CL198" s="5"/>
     </row>
     <row r="199" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV199"/>
-      <c r="CL199" s="5"/>
     </row>
     <row r="200" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV200"/>
       <c r="CL200" s="5"/>
     </row>
-    <row r="202" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV202"/>
+    <row r="201" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL201" s="5"/>
     </row>
     <row r="203" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV203"/>
-      <c r="CL203" s="5"/>
     </row>
     <row r="204" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV204"/>
       <c r="CL204" s="5"/>
     </row>
-    <row r="206" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV206"/>
+    <row r="205" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL205" s="5"/>
     </row>
     <row r="207" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL207" s="5"/>
-    </row>
-    <row r="210" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL210" s="5"/>
-    </row>
-    <row r="214" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL214" s="5"/>
-    </row>
-    <row r="216" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV216"/>
+      <c r="BV207"/>
+    </row>
+    <row r="208" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL208" s="5"/>
+    </row>
+    <row r="211" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL211" s="5"/>
+    </row>
+    <row r="215" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL215" s="5"/>
     </row>
     <row r="217" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL217" s="5"/>
-    </row>
-    <row r="224" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV224"/>
+      <c r="BV217"/>
+    </row>
+    <row r="218" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL218" s="5"/>
     </row>
     <row r="225" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL225" s="5"/>
+      <c r="BV225"/>
     </row>
     <row r="226" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL226" s="5"/>
     </row>
-    <row r="228" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV228"/>
+    <row r="227" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL227" s="5"/>
     </row>
     <row r="229" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV229"/>
-      <c r="CL229" s="5"/>
     </row>
     <row r="230" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV230"/>
       <c r="CL230" s="5"/>
     </row>
-    <row r="236" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV236"/>
+    <row r="231" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL231" s="5"/>
     </row>
     <row r="237" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV237"/>
-      <c r="CL237" s="5"/>
     </row>
     <row r="238" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV238"/>
       <c r="CL238" s="5"/>
     </row>
     <row r="239" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV239"/>
       <c r="CL239" s="5"/>
     </row>
-    <row r="244" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV244"/>
+    <row r="240" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL240" s="5"/>
     </row>
     <row r="245" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV245"/>
     </row>
-    <row r="249" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV249"/>
+    <row r="246" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV246"/>
     </row>
     <row r="250" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL250" s="5"/>
+      <c r="BV250"/>
     </row>
     <row r="251" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV251"/>
+      <c r="CL251" s="5"/>
     </row>
     <row r="252" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL252" s="5"/>
-    </row>
-    <row r="262" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV262"/>
+      <c r="BV252"/>
+    </row>
+    <row r="253" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL253" s="5"/>
     </row>
     <row r="263" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL263" s="5"/>
-    </row>
-    <row r="265" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV265"/>
+      <c r="BV263"/>
+    </row>
+    <row r="264" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL264" s="5"/>
     </row>
     <row r="266" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL266" s="5"/>
-    </row>
-    <row r="274" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV274"/>
+      <c r="BV266"/>
+    </row>
+    <row r="267" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL267" s="5"/>
     </row>
     <row r="275" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL275" s="5"/>
-    </row>
-    <row r="279" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV279"/>
+      <c r="BV275"/>
+    </row>
+    <row r="276" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL276" s="5"/>
     </row>
     <row r="280" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL280" s="5"/>
-    </row>
-    <row r="282" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV282"/>
+      <c r="BV280"/>
+    </row>
+    <row r="281" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL281" s="5"/>
     </row>
     <row r="283" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL283" s="5"/>
-    </row>
-    <row r="299" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV299"/>
+      <c r="BV283"/>
+    </row>
+    <row r="284" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL284" s="5"/>
     </row>
     <row r="300" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV300"/>
-      <c r="CL300" s="5"/>
     </row>
     <row r="301" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV301"/>
@@ -7767,49 +8149,50 @@
     </row>
     <row r="303" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV303"/>
-    </row>
-    <row r="305" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV305"/>
+      <c r="CL303" s="5"/>
+    </row>
+    <row r="304" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV304"/>
     </row>
     <row r="306" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV306"/>
-      <c r="CL306" s="5"/>
     </row>
     <row r="307" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV307"/>
       <c r="CL307" s="5"/>
     </row>
     <row r="308" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV308"/>
       <c r="CL308" s="5"/>
     </row>
-    <row r="312" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV312"/>
+    <row r="309" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL309" s="5"/>
     </row>
     <row r="313" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL313" s="5"/>
-    </row>
-    <row r="315" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV315"/>
+      <c r="BV313"/>
+    </row>
+    <row r="314" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL314" s="5"/>
     </row>
     <row r="316" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV316"/>
-      <c r="CL316" s="5"/>
     </row>
     <row r="317" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV317"/>
       <c r="CL317" s="5"/>
     </row>
     <row r="318" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV318"/>
       <c r="CL318" s="5"/>
     </row>
-    <row r="334" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV334"/>
+    <row r="319" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL319" s="5"/>
     </row>
     <row r="335" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL335" s="5"/>
-    </row>
-    <row r="343" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL343" s="5"/>
+      <c r="BV335"/>
+    </row>
+    <row r="336" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL336" s="5"/>
     </row>
     <row r="344" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL344" s="5"/>
@@ -7823,47 +8206,47 @@
     <row r="347" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL347" s="5"/>
     </row>
-    <row r="349" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV349"/>
+    <row r="348" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL348" s="5"/>
     </row>
     <row r="350" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL350" s="5"/>
+      <c r="BV350"/>
     </row>
     <row r="351" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV351"/>
+      <c r="CL351" s="5"/>
     </row>
     <row r="352" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV352"/>
-      <c r="CL352" s="5"/>
     </row>
     <row r="353" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV353"/>
       <c r="CL353" s="5"/>
     </row>
-    <row r="355" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV355"/>
+    <row r="354" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL354" s="5"/>
     </row>
     <row r="356" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV356"/>
-      <c r="CL356" s="5"/>
     </row>
     <row r="357" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV357"/>
       <c r="CL357" s="5"/>
     </row>
     <row r="358" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV358"/>
       <c r="CL358" s="5"/>
     </row>
-    <row r="360" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL360" s="5"/>
-    </row>
-    <row r="362" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL362" s="5"/>
-    </row>
-    <row r="364" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL364" s="5"/>
-    </row>
-    <row r="367" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL367" s="5"/>
+    <row r="359" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL359" s="5"/>
+    </row>
+    <row r="361" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL361" s="5"/>
+    </row>
+    <row r="363" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL363" s="5"/>
+    </row>
+    <row r="365" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL365" s="5"/>
     </row>
     <row r="368" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL368" s="5"/>
@@ -7881,17 +8264,17 @@
       <c r="CL372" s="5"/>
     </row>
     <row r="373" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV373"/>
+      <c r="CL373" s="5"/>
     </row>
     <row r="374" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV374"/>
-      <c r="CL374" s="5"/>
     </row>
     <row r="375" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV375"/>
       <c r="CL375" s="5"/>
     </row>
     <row r="376" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV376"/>
       <c r="CL376" s="5"/>
     </row>
     <row r="377" spans="74:90" x14ac:dyDescent="0.25">
@@ -7903,37 +8286,36 @@
     <row r="379" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL379" s="5"/>
     </row>
-    <row r="381" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL381" s="5"/>
+    <row r="380" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL380" s="5"/>
     </row>
     <row r="382" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL382" s="5"/>
     </row>
     <row r="383" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV383"/>
+      <c r="CL383" s="5"/>
     </row>
     <row r="384" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV384"/>
-      <c r="CL384" s="5"/>
     </row>
     <row r="385" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV385"/>
       <c r="CL385" s="5"/>
     </row>
     <row r="386" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV386"/>
       <c r="CL386" s="5"/>
     </row>
     <row r="387" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL387" s="5"/>
     </row>
-    <row r="389" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL389" s="5"/>
+    <row r="388" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL388" s="5"/>
     </row>
     <row r="390" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL390" s="5"/>
     </row>
     <row r="391" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV391"/>
       <c r="CL391" s="5"/>
     </row>
     <row r="392" spans="74:90" x14ac:dyDescent="0.25">
@@ -7941,6 +8323,7 @@
       <c r="CL392" s="5"/>
     </row>
     <row r="393" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV393"/>
       <c r="CL393" s="5"/>
     </row>
     <row r="394" spans="74:90" x14ac:dyDescent="0.25">
@@ -7949,70 +8332,70 @@
     <row r="395" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL395" s="5"/>
     </row>
-    <row r="397" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV397"/>
-      <c r="CL397" s="5"/>
+    <row r="396" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL396" s="5"/>
     </row>
     <row r="398" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV398"/>
       <c r="CL398" s="5"/>
     </row>
     <row r="399" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL399" s="5"/>
     </row>
-    <row r="401" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV401"/>
-      <c r="CL401" s="5"/>
+    <row r="400" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL400" s="5"/>
     </row>
     <row r="402" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV402"/>
       <c r="CL402" s="5"/>
     </row>
     <row r="403" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV403"/>
       <c r="CL403" s="5"/>
     </row>
-    <row r="405" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL405" s="5"/>
-    </row>
-    <row r="407" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL407" s="5"/>
-    </row>
-    <row r="410" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL410" s="5"/>
+    <row r="404" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL404" s="5"/>
+    </row>
+    <row r="406" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL406" s="5"/>
+    </row>
+    <row r="408" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL408" s="5"/>
     </row>
     <row r="411" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL411" s="5"/>
     </row>
-    <row r="415" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV415"/>
+    <row r="412" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL412" s="5"/>
     </row>
     <row r="416" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV416"/>
-      <c r="CL416" s="5"/>
     </row>
     <row r="417" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV417"/>
       <c r="CL417" s="5"/>
     </row>
     <row r="418" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV418"/>
       <c r="CL418" s="5"/>
     </row>
     <row r="419" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL419" s="5"/>
     </row>
     <row r="420" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV420"/>
+      <c r="CL420" s="5"/>
     </row>
     <row r="421" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL421" s="5"/>
-    </row>
-    <row r="423" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL423" s="5"/>
+      <c r="BV421"/>
+    </row>
+    <row r="422" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL422" s="5"/>
     </row>
     <row r="424" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL424" s="5"/>
     </row>
-    <row r="426" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL426" s="5"/>
+    <row r="425" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL425" s="5"/>
     </row>
     <row r="427" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL427" s="5"/>
@@ -8032,75 +8415,74 @@
     <row r="432" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL432" s="5"/>
     </row>
-    <row r="434" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV434"/>
+    <row r="433" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL433" s="5"/>
     </row>
     <row r="435" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL435" s="5"/>
+      <c r="BV435"/>
     </row>
     <row r="436" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL436" s="5"/>
     </row>
-    <row r="469" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BU469" s="11"/>
-      <c r="BV469" s="12"/>
+    <row r="437" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL437" s="5"/>
     </row>
     <row r="470" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="H470" s="11"/>
-      <c r="CL470" s="11"/>
-    </row>
-    <row r="476" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BV476"/>
+      <c r="BU470" s="11"/>
+      <c r="BV470" s="12"/>
+    </row>
+    <row r="471" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="H471" s="11"/>
+      <c r="CL471" s="11"/>
     </row>
     <row r="477" spans="8:90" x14ac:dyDescent="0.25">
       <c r="BV477"/>
-      <c r="CL477" s="5"/>
     </row>
     <row r="478" spans="8:90" x14ac:dyDescent="0.25">
       <c r="BV478"/>
       <c r="CL478" s="5"/>
     </row>
     <row r="479" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV479"/>
       <c r="CL479" s="5"/>
     </row>
-    <row r="496" spans="74:74" x14ac:dyDescent="0.25">
-      <c r="BV496"/>
-    </row>
-    <row r="497" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL497" s="5"/>
-    </row>
-    <row r="529" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV529"/>
+    <row r="480" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="CL480" s="5"/>
+    </row>
+    <row r="497" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV497"/>
+    </row>
+    <row r="498" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL498" s="5"/>
     </row>
     <row r="530" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV530"/>
-      <c r="CL530" s="5"/>
     </row>
     <row r="531" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV531"/>
       <c r="CL531" s="5"/>
     </row>
-    <row r="547" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV547"/>
+    <row r="532" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL532" s="5"/>
     </row>
     <row r="548" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL548" s="5"/>
-    </row>
-    <row r="554" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV554"/>
+      <c r="BV548"/>
+    </row>
+    <row r="549" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL549" s="5"/>
     </row>
     <row r="555" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV555"/>
-      <c r="CL555" s="5"/>
     </row>
     <row r="556" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV556"/>
       <c r="CL556" s="5"/>
     </row>
-    <row r="561" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV561"/>
+    <row r="557" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL557" s="5"/>
     </row>
     <row r="562" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV562"/>
-      <c r="CL562" s="5"/>
     </row>
     <row r="563" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV563"/>
@@ -8159,40 +8541,40 @@
       <c r="CL576" s="5"/>
     </row>
     <row r="577" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV577"/>
       <c r="CL577" s="5"/>
     </row>
-    <row r="581" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV581"/>
+    <row r="578" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL578" s="5"/>
     </row>
     <row r="582" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV582"/>
-      <c r="CL582" s="5"/>
     </row>
     <row r="583" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV583"/>
       <c r="CL583" s="5"/>
     </row>
     <row r="584" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV584"/>
+      <c r="CL584" s="5"/>
     </row>
     <row r="585" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL585" s="5"/>
-    </row>
-    <row r="588" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV588"/>
+      <c r="BV585"/>
+    </row>
+    <row r="586" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL586" s="5"/>
     </row>
     <row r="589" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV589"/>
-      <c r="CL589" s="5"/>
     </row>
     <row r="590" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV590"/>
       <c r="CL590" s="5"/>
     </row>
-    <row r="621" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV621"/>
+    <row r="591" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL591" s="5"/>
     </row>
     <row r="622" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV622"/>
-      <c r="CL622" s="5"/>
     </row>
     <row r="623" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV623"/>
@@ -8219,26 +8601,26 @@
       <c r="CL628" s="5"/>
     </row>
     <row r="629" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV629"/>
       <c r="CL629" s="5"/>
     </row>
-    <row r="631" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV631"/>
+    <row r="630" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL630" s="5"/>
     </row>
     <row r="632" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL632" s="5"/>
-    </row>
-    <row r="636" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV636"/>
+      <c r="BV632"/>
+    </row>
+    <row r="633" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL633" s="5"/>
     </row>
     <row r="637" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL637" s="5"/>
-    </row>
-    <row r="640" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV640"/>
+      <c r="BV637"/>
+    </row>
+    <row r="638" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL638" s="5"/>
     </row>
     <row r="641" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV641"/>
-      <c r="CL641" s="5"/>
     </row>
     <row r="642" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV642"/>
@@ -8249,20 +8631,20 @@
       <c r="CL643" s="5"/>
     </row>
     <row r="644" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV644"/>
       <c r="CL644" s="5"/>
     </row>
-    <row r="651" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV651"/>
+    <row r="645" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL645" s="5"/>
     </row>
     <row r="652" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL652" s="5"/>
-    </row>
-    <row r="655" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV655"/>
+      <c r="BV652"/>
+    </row>
+    <row r="653" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL653" s="5"/>
     </row>
     <row r="656" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV656"/>
-      <c r="CL656" s="5"/>
     </row>
     <row r="657" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV657"/>
@@ -8273,74 +8655,74 @@
       <c r="CL658" s="5"/>
     </row>
     <row r="659" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV659"/>
       <c r="CL659" s="5"/>
     </row>
-    <row r="661" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV661"/>
+    <row r="660" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL660" s="5"/>
     </row>
     <row r="662" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV662"/>
-      <c r="CL662" s="5"/>
     </row>
     <row r="663" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV663"/>
       <c r="CL663" s="5"/>
     </row>
     <row r="664" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL664">
+      <c r="CL664" s="5"/>
+    </row>
+    <row r="665" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL665">
         <v>0.15</v>
-      </c>
-    </row>
-    <row r="666" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL666">
-        <v>0.2</v>
       </c>
     </row>
     <row r="667" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL667">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="668" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL668">
         <v>0.1</v>
       </c>
     </row>
-    <row r="669" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL669">
+    <row r="670" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL670">
         <v>0.2</v>
       </c>
     </row>
-    <row r="676" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL676">
+    <row r="677" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL677">
         <v>1</v>
-      </c>
-    </row>
-    <row r="678" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL678">
-        <v>0.4</v>
       </c>
     </row>
     <row r="679" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL679">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="680" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL680">
         <v>0.6</v>
-      </c>
-    </row>
-    <row r="682" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL682">
-        <v>0.5</v>
       </c>
     </row>
     <row r="683" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL683">
-        <v>0.66700000000000004</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="684" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL684">
+        <v>0.66700000000000004</v>
+      </c>
+    </row>
+    <row r="685" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL685">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="687" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV687"/>
     </row>
     <row r="688" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV688"/>
-      <c r="CL688" s="5"/>
     </row>
     <row r="689" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV689"/>
@@ -8371,20 +8753,20 @@
       <c r="CL695" s="5"/>
     </row>
     <row r="696" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV696"/>
       <c r="CL696" s="5"/>
     </row>
     <row r="697" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV697"/>
+      <c r="CL697" s="5"/>
     </row>
     <row r="698" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL698" s="5"/>
-    </row>
-    <row r="707" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV707"/>
+      <c r="BV698"/>
+    </row>
+    <row r="699" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL699" s="5"/>
     </row>
     <row r="708" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV708"/>
-      <c r="CL708" s="5"/>
     </row>
     <row r="709" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV709"/>
@@ -8411,40 +8793,40 @@
       <c r="CL714" s="5"/>
     </row>
     <row r="715" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV715"/>
       <c r="CL715" s="5"/>
     </row>
     <row r="716" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV716"/>
+      <c r="CL716" s="5"/>
     </row>
     <row r="717" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL717" s="5"/>
-    </row>
-    <row r="722" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV722"/>
+      <c r="BV717"/>
+    </row>
+    <row r="718" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL718" s="5"/>
     </row>
     <row r="723" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV723"/>
-      <c r="CL723" s="5"/>
     </row>
     <row r="724" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV724"/>
       <c r="CL724" s="5"/>
     </row>
     <row r="725" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV725"/>
+      <c r="CL725" s="5"/>
     </row>
     <row r="726" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV726"/>
-      <c r="CL726" s="5"/>
     </row>
     <row r="727" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV727"/>
       <c r="CL727" s="5"/>
     </row>
     <row r="728" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV728"/>
+      <c r="CL728" s="5"/>
     </row>
     <row r="729" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV729"/>
-      <c r="CL729" s="5"/>
     </row>
     <row r="730" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV730"/>
@@ -8455,116 +8837,116 @@
       <c r="CL731" s="5"/>
     </row>
     <row r="732" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV732"/>
       <c r="CL732" s="5"/>
     </row>
-    <row r="736" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV736"/>
+    <row r="733" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL733" s="5"/>
     </row>
     <row r="737" spans="8:90" x14ac:dyDescent="0.25">
       <c r="BV737"/>
-      <c r="CL737" s="5"/>
     </row>
     <row r="738" spans="8:90" x14ac:dyDescent="0.25">
       <c r="BV738"/>
       <c r="CL738" s="5"/>
     </row>
     <row r="739" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV739"/>
       <c r="CL739" s="5"/>
     </row>
     <row r="740" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BV740"/>
+      <c r="CL740" s="5"/>
     </row>
     <row r="741" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="CL741" s="5"/>
+      <c r="BV741"/>
     </row>
     <row r="742" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BU742" s="11"/>
-      <c r="BV742" s="12"/>
+      <c r="CL742" s="5"/>
     </row>
     <row r="743" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="H743" s="11"/>
-      <c r="CL743" s="11"/>
-    </row>
-    <row r="760" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BV760"/>
-    </row>
-    <row r="761" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BU743" s="11"/>
+      <c r="BV743" s="12"/>
+    </row>
+    <row r="744" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="H744" s="11"/>
+      <c r="CL744" s="11"/>
+    </row>
+    <row r="761" spans="73:90" x14ac:dyDescent="0.25">
       <c r="BV761"/>
-      <c r="CL761" s="5"/>
-    </row>
-    <row r="762" spans="8:90" x14ac:dyDescent="0.25">
+    </row>
+    <row r="762" spans="73:90" x14ac:dyDescent="0.25">
       <c r="BV762"/>
       <c r="CL762" s="5"/>
     </row>
-    <row r="763" spans="8:90" x14ac:dyDescent="0.25">
+    <row r="763" spans="73:90" x14ac:dyDescent="0.25">
       <c r="BV763"/>
       <c r="CL763" s="5"/>
     </row>
-    <row r="764" spans="8:90" x14ac:dyDescent="0.25">
+    <row r="764" spans="73:90" x14ac:dyDescent="0.25">
+      <c r="BV764"/>
       <c r="CL764" s="5"/>
     </row>
-    <row r="765" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BV765"/>
-    </row>
-    <row r="766" spans="8:90" x14ac:dyDescent="0.25">
+    <row r="765" spans="73:90" x14ac:dyDescent="0.25">
+      <c r="CL765" s="5"/>
+    </row>
+    <row r="766" spans="73:90" x14ac:dyDescent="0.25">
       <c r="BV766"/>
-      <c r="CL766" s="5"/>
-    </row>
-    <row r="767" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BU767" s="11"/>
-      <c r="BV767" s="12"/>
+    </row>
+    <row r="767" spans="73:90" x14ac:dyDescent="0.25">
+      <c r="BV767"/>
       <c r="CL767" s="5"/>
     </row>
-    <row r="768" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="H768" s="11"/>
-      <c r="CL768" s="11"/>
-    </row>
-    <row r="771" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV771"/>
-    </row>
-    <row r="772" spans="74:90" x14ac:dyDescent="0.25">
+    <row r="768" spans="73:90" x14ac:dyDescent="0.25">
+      <c r="BU768" s="11"/>
+      <c r="BV768" s="12"/>
+      <c r="CL768" s="5"/>
+    </row>
+    <row r="769" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="H769" s="11"/>
+      <c r="CL769" s="11"/>
+    </row>
+    <row r="772" spans="8:90" x14ac:dyDescent="0.25">
       <c r="BV772"/>
-      <c r="CL772" s="5"/>
-    </row>
-    <row r="773" spans="74:90" x14ac:dyDescent="0.25">
+    </row>
+    <row r="773" spans="8:90" x14ac:dyDescent="0.25">
       <c r="BV773"/>
       <c r="CL773" s="5"/>
     </row>
-    <row r="774" spans="74:90" x14ac:dyDescent="0.25">
+    <row r="774" spans="8:90" x14ac:dyDescent="0.25">
       <c r="BV774"/>
       <c r="CL774" s="5"/>
     </row>
-    <row r="775" spans="74:90" x14ac:dyDescent="0.25">
+    <row r="775" spans="8:90" x14ac:dyDescent="0.25">
       <c r="BV775"/>
       <c r="CL775" s="5"/>
     </row>
-    <row r="776" spans="74:90" x14ac:dyDescent="0.25">
+    <row r="776" spans="8:90" x14ac:dyDescent="0.25">
       <c r="BV776"/>
       <c r="CL776" s="5"/>
     </row>
-    <row r="777" spans="74:90" x14ac:dyDescent="0.25">
+    <row r="777" spans="8:90" x14ac:dyDescent="0.25">
       <c r="BV777"/>
       <c r="CL777" s="5"/>
     </row>
-    <row r="778" spans="74:90" x14ac:dyDescent="0.25">
+    <row r="778" spans="8:90" x14ac:dyDescent="0.25">
       <c r="BV778"/>
       <c r="CL778" s="5"/>
     </row>
-    <row r="779" spans="74:90" x14ac:dyDescent="0.25">
+    <row r="779" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV779"/>
       <c r="CL779" s="5"/>
     </row>
-    <row r="781" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV781"/>
-    </row>
-    <row r="782" spans="74:90" x14ac:dyDescent="0.25">
+    <row r="780" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="CL780" s="5"/>
+    </row>
+    <row r="782" spans="8:90" x14ac:dyDescent="0.25">
       <c r="BV782"/>
-      <c r="CL782" s="5"/>
-    </row>
-    <row r="783" spans="74:90" x14ac:dyDescent="0.25">
+    </row>
+    <row r="783" spans="8:90" x14ac:dyDescent="0.25">
       <c r="BV783"/>
       <c r="CL783" s="5"/>
     </row>
-    <row r="784" spans="74:90" x14ac:dyDescent="0.25">
+    <row r="784" spans="8:90" x14ac:dyDescent="0.25">
       <c r="BV784"/>
       <c r="CL784" s="5"/>
     </row>
@@ -8577,14 +8959,14 @@
       <c r="CL786" s="5"/>
     </row>
     <row r="787" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV787"/>
       <c r="CL787" s="5"/>
     </row>
     <row r="788" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV788"/>
+      <c r="CL788" s="5"/>
     </row>
     <row r="789" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV789"/>
-      <c r="CL789" s="5"/>
     </row>
     <row r="790" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV790"/>
@@ -8699,21 +9081,25 @@
       <c r="CL817" s="5"/>
     </row>
     <row r="818" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV818"/>
       <c r="CL818" s="5"/>
     </row>
     <row r="819" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV819"/>
+      <c r="CL819" s="5"/>
     </row>
     <row r="820" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV820"/>
-      <c r="CL820" s="5"/>
     </row>
     <row r="821" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV821"/>
       <c r="CL821" s="5"/>
     </row>
     <row r="822" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV822"/>
       <c r="CL822" s="5"/>
+    </row>
+    <row r="823" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL823" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="15" type="noConversion"/>
@@ -8724,70 +9110,6 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="11.33203125" customWidth="1"/>
-    <col min="2" max="2" width="11.25" customWidth="1"/>
-    <col min="4" max="4" width="27.5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C2" t="s">
-        <v>384</v>
-      </c>
-      <c r="D2" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" t="s">
-        <v>322</v>
-      </c>
-      <c r="D3" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="B4" t="s">
-        <v>464</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>465</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="15" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:Q9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
@@ -8811,37 +9133,37 @@
         <v>4</v>
       </c>
       <c r="E1" t="s">
+        <v>359</v>
+      </c>
+      <c r="F1" t="s">
+        <v>360</v>
+      </c>
+      <c r="G1" t="s">
         <v>361</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>362</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>363</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>364</v>
       </c>
-      <c r="I1" t="s">
+      <c r="L1" t="s">
         <v>365</v>
       </c>
-      <c r="J1" t="s">
+      <c r="M1" t="s">
         <v>366</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>367</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>368</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" s="2" t="s">
         <v>369</v>
-      </c>
-      <c r="O1" t="s">
-        <v>370</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -8855,43 +9177,43 @@
         <v>76</v>
       </c>
       <c r="E2" t="s">
+        <v>370</v>
+      </c>
+      <c r="F2" t="s">
+        <v>371</v>
+      </c>
+      <c r="G2" t="s">
         <v>372</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>373</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>374</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>375</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>376</v>
-      </c>
-      <c r="J2" t="s">
-        <v>377</v>
-      </c>
-      <c r="K2" t="s">
-        <v>378</v>
       </c>
       <c r="L2" t="s">
         <v>52</v>
       </c>
       <c r="M2" t="s">
+        <v>377</v>
+      </c>
+      <c r="N2" t="s">
+        <v>378</v>
+      </c>
+      <c r="O2" t="s">
         <v>379</v>
       </c>
-      <c r="N2" t="s">
+      <c r="P2" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="O2" t="s">
-        <v>381</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>382</v>
-      </c>
       <c r="Q2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
@@ -8920,13 +9242,13 @@
         <v>115</v>
       </c>
       <c r="J3" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="K3" t="s">
         <v>116</v>
       </c>
       <c r="L3" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="M3" t="s">
         <v>115</v>
@@ -8935,7 +9257,7 @@
         <v>115</v>
       </c>
       <c r="O3" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="P3" t="s">
         <v>115</v>
@@ -8944,8 +9266,27 @@
         <v>124</v>
       </c>
     </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>468</v>
+      </c>
+    </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C6" s="3"/>
+      <c r="A6" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>471</v>
+      </c>
     </row>
     <row r="7" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="J7"/>
@@ -8955,6 +9296,70 @@
       <c r="A9" s="2"/>
       <c r="C9" s="2"/>
       <c r="Q9" s="2"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="15" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.33203125" customWidth="1"/>
+    <col min="2" max="2" width="11.25" customWidth="1"/>
+    <col min="4" max="4" width="27.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" t="s">
+        <v>382</v>
+      </c>
+      <c r="D2" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>320</v>
+      </c>
+      <c r="D3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="B4" t="s">
+        <v>459</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>460</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="15" type="noConversion"/>
@@ -8976,7 +9381,7 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="I1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -8990,25 +9395,25 @@
         <v>49</v>
       </c>
       <c r="D2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="E2" t="s">
         <v>71</v>
       </c>
       <c r="F2" t="s">
+        <v>384</v>
+      </c>
+      <c r="G2" t="s">
+        <v>385</v>
+      </c>
+      <c r="H2" t="s">
         <v>386</v>
       </c>
-      <c r="G2" t="s">
-        <v>387</v>
-      </c>
-      <c r="H2" t="s">
-        <v>388</v>
-      </c>
       <c r="I2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="J2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -9037,7 +9442,7 @@
         <v>117</v>
       </c>
       <c r="I3" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>124</v>
@@ -9045,13 +9450,13 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="B4" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="C4" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="E4">
         <v>10</v>
@@ -9060,10 +9465,10 @@
         <v>1</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
     </row>
   </sheetData>
@@ -9090,34 +9495,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>387</v>
+      </c>
+      <c r="C1" t="s">
+        <v>388</v>
+      </c>
+      <c r="D1" t="s">
         <v>389</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>390</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>391</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H1" t="s">
         <v>392</v>
       </c>
-      <c r="F1" t="s">
+      <c r="I1" t="s">
         <v>393</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>394</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>395</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>396</v>
-      </c>
-      <c r="K1" t="s">
-        <v>397</v>
-      </c>
-      <c r="L1" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -9125,34 +9530,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>397</v>
+      </c>
+      <c r="C2" t="s">
+        <v>398</v>
+      </c>
+      <c r="D2" t="s">
         <v>399</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>400</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>401</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>402</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>403</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>404</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>405</v>
       </c>
-      <c r="I2" t="s">
-        <v>406</v>
-      </c>
-      <c r="J2" t="s">
-        <v>407</v>
-      </c>
       <c r="K2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="L2" t="s">
         <v>96</v>
@@ -9169,7 +9574,7 @@
         <v>117</v>
       </c>
       <c r="D3" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E3" t="s">
         <v>2</v>
@@ -9223,28 +9628,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C2" t="s">
         <v>76</v>
       </c>
       <c r="D2" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="E2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="F2" t="s">
         <v>78</v>
       </c>
       <c r="G2" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="H2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="I2" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="J2" t="s">
         <v>53</v>
@@ -9273,7 +9678,7 @@
         <v>117</v>
       </c>
       <c r="H3" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="I3" t="s">
         <v>117</v>
@@ -9310,28 +9715,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>419</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -9339,28 +9744,28 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>427</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>429</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -9394,28 +9799,28 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="C4" s="1">
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>446</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>449</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Diy优胜/萃儿.xlsx
+++ b/Excel/Diy优胜/萃儿.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Diy优胜\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C29B2047-322F-4980-90F9-EC7F060C190B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDFB323C-15AF-4C7C-AB6A-6BCFE59CC60F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -23,6 +23,9 @@
     <sheet name="ContractData" sheetId="11" r:id="rId8"/>
     <sheet name="SpineData" sheetId="12" r:id="rId9"/>
   </sheets>
+  <definedNames>
+    <definedName name="OLE_LINK2" localSheetId="2">SkillData!$E$13</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -299,7 +302,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="553">
   <si>
     <t>Id</t>
   </si>
@@ -1586,38 +1589,38 @@
   </si>
   <si>
     <t>Hip</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>辅助</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>优先Buff</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>OrderBuff</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>string</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>自定义优先级</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>OrderExpression</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>Muzzle</t>
   </si>
   <si>
     <t>MaxPower</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>萃儿</t>
@@ -1627,43 +1630,43 @@
   </si>
   <si>
     <t>萃儿</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>通用地板</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>/Spine/萃儿/front/char_4122_grabds_yun_3.atlas.txt</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>/Spine/萃儿/front/char_4122_grabds_yun_3.png</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>/Spine/萃儿/front/char_4122_grabds_yun_3.skel.bytes</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>/Spine/萃儿/back/char_4122_grabds_yun_3.atlas.txt</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>/Spine/萃儿/back/char_4122_grabds_yun_3.png</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>/Spine/萃儿/back/char_4122_grabds_yun_3.skel.bytes</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>医疗</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>icon_cuier</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>普通技能</t>
@@ -1690,169 +1693,380 @@
     <t>frostl_attack_01_trail</t>
   </si>
   <si>
-    <t>{"MoveHeight":0,"MaxLinkNum":4,"SkillId":"通用干员链式弹道索敌","CanBack":"false"}</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
     <t>萃儿二天赋额外治疗量</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>治疗量提升依溢出</t>
   </si>
   <si>
     <t>{"Rate":0.4,"OrderCode":1000}</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>通用链奶衰减,萃儿二天赋额外治疗量</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>萃儿链奶弹道</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>中立单位</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>萃蔓0</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>萃儿天赋标记,萃蔓伤害分摊</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>萃儿普攻</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>萃儿天赋标记</t>
   </si>
   <si>
     <t>普通Buff</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>萃蔓伤害分摊</t>
   </si>
   <si>
     <t>伤害分摊</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>{"'ShareRate":0.2,"Group":"萃儿天赋","OrderCode":-2000}</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>部署装置</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>被动</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>生成萃蔓0</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>生成萃蔓1</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>ew3类部署装置</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>萃蔓效果</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>普通技能</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>0,0</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>萃儿天赋标记</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>萃蔓伤害分摊</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>自己入场</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>萃蔓1</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>0,-1#-1,0#1,0#0,1</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>{"召唤物ID":"萃蔓0","召唤位置":"使用本技能索敌位置","部署模式":"追加","召唤物方向":"固定方向"}</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>{"召唤物ID":"萃蔓1","召唤位置":"使用自身位置","数量":4}</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>萃儿普攻,生成萃蔓0</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>治疗</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>{"Color":"#96C24E","Alpha":0.25}</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>{"Color":"#96C24E","Alpha":0.5}</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>萃蔓去重</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>自己以外</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>即死</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>萃蔓无敌</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>仅自己</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>无敌2,绝食2</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>萃蔓效果,萃蔓无敌</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>萃蔓去重,生成萃蔓1,萃蔓效果,萃蔓无敌</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>萃儿1</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>在初始状态与当前状态下切换\n弹射治疗量不再衰减，攻击范围缩小，攻击力+100%</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>叶出春芽</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>自动</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>充能释放</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,0#0,-1#-1,0#1,0#0,1</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>萃儿一链奶弹道</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>萃儿1普攻</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>数值变化</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"t":["AttackRate"]}</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>萃儿2</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>手动</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>萃儿2血上限提升</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>数值变化叠加</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"t":["HpRate"],"MaxLevel":99}</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>萃儿3</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>濛濛细雨</t>
+  </si>
+  <si>
+    <t>对所有处于萃蔓地块上的干员进行一次攻击力250%的治疗，并令治疗目标获得8s的生命上限+30%\n可充能3次</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>摇曳萃蔓</t>
+  </si>
+  <si>
+    <t>被动：处于萃蔓地块的友方击倒敌人时或场上友方离场时，为敌人倒下位置或撤退友方位置及其周围四格铺设萃蔓地块。\n主动：萃蔓地块视为自身攻击范围的延伸。攻击间隔缩短（-40%），治疗目标+2。处于萃蔓地块上的生命百分比最低的友方单位受到一天赋效果提升至100%。萃蔓地块上其他友方单位攻击时额外对目标造成萃儿攻击力80%的法术伤害，</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>萃儿3攻击间隔缩短</t>
+  </si>
+  <si>
+    <t>萃儿3攻击间隔缩短</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"t":["AttackGapRate"]}</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>赋予被动</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>入场</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"MoveHeight":0,"MaxLinkNum":3,"SkillId":"通用干员链式弹道索敌","CanBack":"false"}</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>死亡</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>击杀</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>萃儿3击杀生成萃蔓</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>萃儿3被动对干员</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>萃儿3被动对敌</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>萃儿3死亡生成萃蔓</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"技能Id列表":["萃儿3死亡生成萃蔓"]}</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>萃儿3协同索敌标记</t>
+  </si>
+  <si>
+    <t>萃儿3协同索敌标记</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>萃儿3协同标记</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>击中</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>萃儿3启动</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"技能Id列表":["萃儿3击杀生成萃蔓","萃儿3击杀生成萃蔓"]}</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>萃儿3普攻</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>萃儿1,萃儿3攻击间隔缩短</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>萃儿3覆盖伤害分摊</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>萃儿3伤害分摊</t>
+  </si>
+  <si>
+    <t>萃儿3伤害分摊</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"'ShareRate":1,"Group":"萃儿天赋","OrderCode":-2100}</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>萃儿3协同攻击</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>深海色击中</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Magic</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>萃儿1,萃儿2,萃儿3</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>萃儿3延伸攻击范围</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>获取额外攻击范围</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>无敌</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>萃蔓无敌,绝食2</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"技能Id列表":["萃儿3普攻"]}</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>萃儿3附伤启动</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>萃儿3被动对干员,萃儿3被动对敌,萃儿3普攻,萃儿3覆盖伤害分摊,萃儿3协同攻击,萃儿3延伸攻击范围,萃儿3附伤启动</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>萃蔓去重,萃蔓效果,萃蔓无敌</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1919,12 +2133,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10.5"/>
-      <color rgb="FF333639"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF333639"/>
       <name val="宋体"/>
@@ -1975,6 +2183,14 @@
     <font>
       <sz val="10.5"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -2049,9 +2265,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
@@ -2061,16 +2274,19 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -2402,15 +2618,15 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="17" t="s">
         <v>437</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="17" t="s">
         <v>437</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="15" type="noConversion"/>
+  <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3013,13 +3229,13 @@
       </c>
     </row>
     <row r="5" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="17" t="s">
         <v>439</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="E5" s="13"/>
+      <c r="E5" s="12"/>
       <c r="F5" s="2" t="s">
         <v>439</v>
       </c>
@@ -3069,9 +3285,11 @@
         <v>126</v>
       </c>
       <c r="AI5" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="AJ5" s="2"/>
+        <v>486</v>
+      </c>
+      <c r="AJ5" s="2" t="s">
+        <v>544</v>
+      </c>
       <c r="AK5">
         <v>0</v>
       </c>
@@ -3110,7 +3328,7 @@
       </c>
       <c r="BI5" s="2"/>
       <c r="BJ5" s="2"/>
-      <c r="BK5" s="15"/>
+      <c r="BK5" s="14"/>
       <c r="BM5" s="2" t="s">
         <v>130</v>
       </c>
@@ -3131,13 +3349,13 @@
       </c>
     </row>
     <row r="6" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
-        <v>464</v>
+      <c r="A6" s="17" t="s">
+        <v>463</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="E6" s="13"/>
+        <v>462</v>
+      </c>
+      <c r="E6" s="12"/>
       <c r="F6" s="2" t="s">
         <v>440</v>
       </c>
@@ -3183,14 +3401,14 @@
       <c r="AC6">
         <v>0</v>
       </c>
-      <c r="AG6" s="18" t="s">
+      <c r="AG6" s="17" t="s">
         <v>438</v>
       </c>
       <c r="AH6" s="2" t="s">
         <v>428</v>
       </c>
       <c r="AI6" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="AJ6" s="2"/>
       <c r="AK6">
@@ -3208,6 +3426,9 @@
       <c r="AP6">
         <v>0.5</v>
       </c>
+      <c r="AQ6">
+        <v>1</v>
+      </c>
       <c r="AV6" s="2"/>
       <c r="AW6">
         <v>0.25</v>
@@ -3217,7 +3438,7 @@
       </c>
       <c r="BD6" s="2"/>
       <c r="BL6" s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="BM6" s="2"/>
       <c r="BN6" s="2"/>
@@ -3226,13 +3447,13 @@
       <c r="BR6" s="2"/>
     </row>
     <row r="7" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="A7" s="18" t="s">
-        <v>483</v>
+      <c r="A7" s="17" t="s">
+        <v>482</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="E7" s="13"/>
+        <v>462</v>
+      </c>
+      <c r="E7" s="12"/>
       <c r="F7" s="2" t="s">
         <v>440</v>
       </c>
@@ -3278,14 +3499,14 @@
       <c r="AC7">
         <v>0</v>
       </c>
-      <c r="AG7" s="18" t="s">
+      <c r="AG7" s="17" t="s">
         <v>438</v>
       </c>
       <c r="AH7" s="2" t="s">
         <v>428</v>
       </c>
       <c r="AI7" s="2" t="s">
-        <v>497</v>
+        <v>552</v>
       </c>
       <c r="AJ7" s="2"/>
       <c r="AK7">
@@ -3303,6 +3524,9 @@
       <c r="AP7">
         <v>0.5</v>
       </c>
+      <c r="AQ7">
+        <v>1</v>
+      </c>
       <c r="AV7" s="2"/>
       <c r="AW7">
         <v>0.25</v>
@@ -3312,7 +3536,7 @@
       </c>
       <c r="BD7" s="2"/>
       <c r="BL7" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="BM7" s="2"/>
       <c r="BN7" s="2"/>
@@ -3322,7 +3546,7 @@
     </row>
     <row r="8" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
-      <c r="E8" s="13"/>
+      <c r="E8" s="12"/>
       <c r="F8" s="2"/>
       <c r="N8" s="2"/>
       <c r="AG8" s="2"/>
@@ -3330,7 +3554,7 @@
     </row>
     <row r="9" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
-      <c r="E9" s="13"/>
+      <c r="E9" s="12"/>
       <c r="F9" s="2"/>
       <c r="N9" s="2"/>
       <c r="AG9" s="2"/>
@@ -3339,7 +3563,7 @@
     </row>
     <row r="10" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
-      <c r="E10" s="13"/>
+      <c r="E10" s="12"/>
       <c r="F10" s="2"/>
       <c r="N10" s="2"/>
       <c r="AG10" s="2"/>
@@ -3348,7 +3572,7 @@
     </row>
     <row r="11" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
-      <c r="E11" s="13"/>
+      <c r="E11" s="12"/>
       <c r="F11" s="2"/>
       <c r="N11" s="2"/>
       <c r="AG11" s="2"/>
@@ -3356,15 +3580,15 @@
       <c r="BB11" s="2"/>
     </row>
     <row r="13" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="E13" s="13"/>
+      <c r="E13" s="12"/>
     </row>
     <row r="14" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="E14" s="13"/>
+      <c r="E14" s="12"/>
     </row>
     <row r="15" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="E15" s="13"/>
+      <c r="E15" s="12"/>
       <c r="AG15" s="2"/>
-      <c r="BP15" s="16"/>
+      <c r="BP15" s="15"/>
     </row>
     <row r="25" spans="35:63" x14ac:dyDescent="0.25">
       <c r="AI25" s="2"/>
@@ -3384,2759 +3608,2759 @@
       <c r="BK35" s="2"/>
     </row>
     <row r="36" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D36" s="14"/>
-      <c r="E36" s="13"/>
-      <c r="BO36" s="17"/>
-      <c r="BR36" s="17"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="12"/>
+      <c r="BO36" s="16"/>
+      <c r="BR36" s="16"/>
     </row>
     <row r="37" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D37" s="14"/>
-      <c r="E37" s="13"/>
-      <c r="BO37" s="17"/>
-      <c r="BR37" s="17"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="12"/>
+      <c r="BO37" s="16"/>
+      <c r="BR37" s="16"/>
     </row>
     <row r="38" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D38" s="14"/>
-      <c r="E38" s="13"/>
-      <c r="BO38" s="17"/>
-      <c r="BR38" s="17"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="12"/>
+      <c r="BO38" s="16"/>
+      <c r="BR38" s="16"/>
     </row>
     <row r="39" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D39" s="14"/>
-      <c r="E39" s="13"/>
-      <c r="BO39" s="17"/>
-      <c r="BR39" s="17"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="12"/>
+      <c r="BO39" s="16"/>
+      <c r="BR39" s="16"/>
     </row>
     <row r="40" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D40" s="14"/>
-      <c r="E40" s="13"/>
-      <c r="BO40" s="17"/>
-      <c r="BR40" s="17"/>
+      <c r="D40" s="13"/>
+      <c r="E40" s="12"/>
+      <c r="BO40" s="16"/>
+      <c r="BR40" s="16"/>
     </row>
     <row r="41" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D41" s="14"/>
-      <c r="E41" s="13"/>
-      <c r="BO41" s="17"/>
-      <c r="BR41" s="17"/>
+      <c r="D41" s="13"/>
+      <c r="E41" s="12"/>
+      <c r="BO41" s="16"/>
+      <c r="BR41" s="16"/>
     </row>
     <row r="42" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D42" s="14"/>
-      <c r="E42" s="13"/>
-      <c r="BO42" s="17"/>
-      <c r="BR42" s="17"/>
+      <c r="D42" s="13"/>
+      <c r="E42" s="12"/>
+      <c r="BO42" s="16"/>
+      <c r="BR42" s="16"/>
     </row>
     <row r="43" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D43" s="14"/>
-      <c r="E43" s="13"/>
-      <c r="BR43" s="17"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="12"/>
+      <c r="BR43" s="16"/>
     </row>
     <row r="44" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D44" s="14"/>
-      <c r="E44" s="13"/>
-      <c r="BR44" s="17"/>
+      <c r="D44" s="13"/>
+      <c r="E44" s="12"/>
+      <c r="BR44" s="16"/>
     </row>
     <row r="45" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D45" s="14"/>
-      <c r="E45" s="13"/>
-      <c r="BR45" s="17"/>
+      <c r="D45" s="13"/>
+      <c r="E45" s="12"/>
+      <c r="BR45" s="16"/>
     </row>
     <row r="46" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D46" s="14"/>
-      <c r="E46" s="13"/>
-      <c r="BO46" s="17"/>
-      <c r="BR46" s="17"/>
+      <c r="D46" s="13"/>
+      <c r="E46" s="12"/>
+      <c r="BO46" s="16"/>
+      <c r="BR46" s="16"/>
     </row>
     <row r="47" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D47" s="14"/>
-      <c r="E47" s="13"/>
-      <c r="BO47" s="17"/>
-      <c r="BR47" s="17"/>
+      <c r="D47" s="13"/>
+      <c r="E47" s="12"/>
+      <c r="BO47" s="16"/>
+      <c r="BR47" s="16"/>
     </row>
     <row r="48" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D48" s="14"/>
-      <c r="E48" s="13"/>
-      <c r="BO48" s="17"/>
-      <c r="BR48" s="17"/>
+      <c r="D48" s="13"/>
+      <c r="E48" s="12"/>
+      <c r="BO48" s="16"/>
+      <c r="BR48" s="16"/>
     </row>
     <row r="49" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D49" s="14"/>
-      <c r="E49" s="13"/>
-      <c r="BO49" s="17"/>
-      <c r="BR49" s="17"/>
+      <c r="D49" s="13"/>
+      <c r="E49" s="12"/>
+      <c r="BO49" s="16"/>
+      <c r="BR49" s="16"/>
     </row>
     <row r="50" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D50" s="14"/>
-      <c r="E50" s="13"/>
-      <c r="BO50" s="17"/>
-      <c r="BR50" s="17"/>
+      <c r="D50" s="13"/>
+      <c r="E50" s="12"/>
+      <c r="BO50" s="16"/>
+      <c r="BR50" s="16"/>
     </row>
     <row r="51" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D51" s="14"/>
-      <c r="E51" s="13"/>
-      <c r="BO51" s="17"/>
-      <c r="BR51" s="17"/>
+      <c r="D51" s="13"/>
+      <c r="E51" s="12"/>
+      <c r="BO51" s="16"/>
+      <c r="BR51" s="16"/>
     </row>
     <row r="52" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D52" s="14"/>
-      <c r="E52" s="13"/>
-      <c r="BO52" s="17"/>
-      <c r="BR52" s="17"/>
+      <c r="D52" s="13"/>
+      <c r="E52" s="12"/>
+      <c r="BO52" s="16"/>
+      <c r="BR52" s="16"/>
     </row>
     <row r="53" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D53" s="14"/>
-      <c r="E53" s="13"/>
-      <c r="BO53" s="17"/>
-      <c r="BR53" s="17"/>
+      <c r="D53" s="13"/>
+      <c r="E53" s="12"/>
+      <c r="BO53" s="16"/>
+      <c r="BR53" s="16"/>
     </row>
     <row r="54" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D54" s="14"/>
-      <c r="E54" s="13"/>
-      <c r="BO54" s="17"/>
-      <c r="BR54" s="17"/>
+      <c r="D54" s="13"/>
+      <c r="E54" s="12"/>
+      <c r="BO54" s="16"/>
+      <c r="BR54" s="16"/>
     </row>
     <row r="55" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D55" s="14"/>
-      <c r="E55" s="13"/>
-      <c r="BO55" s="17"/>
-      <c r="BR55" s="17"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="12"/>
+      <c r="BO55" s="16"/>
+      <c r="BR55" s="16"/>
     </row>
     <row r="56" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D56" s="14"/>
-      <c r="E56" s="13"/>
-      <c r="BO56" s="17"/>
-      <c r="BR56" s="17"/>
+      <c r="D56" s="13"/>
+      <c r="E56" s="12"/>
+      <c r="BO56" s="16"/>
+      <c r="BR56" s="16"/>
     </row>
     <row r="57" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D57" s="14"/>
-      <c r="E57" s="13"/>
-      <c r="BO57" s="17"/>
-      <c r="BR57" s="17"/>
+      <c r="D57" s="13"/>
+      <c r="E57" s="12"/>
+      <c r="BO57" s="16"/>
+      <c r="BR57" s="16"/>
     </row>
     <row r="58" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D58" s="14"/>
-      <c r="E58" s="13"/>
-      <c r="BO58" s="17"/>
-      <c r="BR58" s="17"/>
+      <c r="D58" s="13"/>
+      <c r="E58" s="12"/>
+      <c r="BO58" s="16"/>
+      <c r="BR58" s="16"/>
     </row>
     <row r="59" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D59" s="14"/>
-      <c r="E59" s="13"/>
-      <c r="BO59" s="17"/>
-      <c r="BR59" s="17"/>
+      <c r="D59" s="13"/>
+      <c r="E59" s="12"/>
+      <c r="BO59" s="16"/>
+      <c r="BR59" s="16"/>
     </row>
     <row r="60" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D60" s="14"/>
-      <c r="E60" s="13"/>
-      <c r="BO60" s="17"/>
-      <c r="BR60" s="17"/>
+      <c r="D60" s="13"/>
+      <c r="E60" s="12"/>
+      <c r="BO60" s="16"/>
+      <c r="BR60" s="16"/>
     </row>
     <row r="61" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D61" s="14"/>
-      <c r="E61" s="13"/>
-      <c r="BO61" s="17"/>
-      <c r="BR61" s="17"/>
+      <c r="D61" s="13"/>
+      <c r="E61" s="12"/>
+      <c r="BO61" s="16"/>
+      <c r="BR61" s="16"/>
     </row>
     <row r="62" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D62" s="14"/>
-      <c r="E62" s="13"/>
-      <c r="BO62" s="17"/>
-      <c r="BR62" s="17"/>
+      <c r="D62" s="13"/>
+      <c r="E62" s="12"/>
+      <c r="BO62" s="16"/>
+      <c r="BR62" s="16"/>
     </row>
     <row r="63" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D63" s="14"/>
-      <c r="E63" s="13"/>
-      <c r="BO63" s="17"/>
-      <c r="BR63" s="17"/>
+      <c r="D63" s="13"/>
+      <c r="E63" s="12"/>
+      <c r="BO63" s="16"/>
+      <c r="BR63" s="16"/>
     </row>
     <row r="64" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D64" s="14"/>
-      <c r="E64" s="13"/>
-      <c r="BO64" s="17"/>
-      <c r="BR64" s="17"/>
+      <c r="D64" s="13"/>
+      <c r="E64" s="12"/>
+      <c r="BO64" s="16"/>
+      <c r="BR64" s="16"/>
     </row>
     <row r="65" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D65" s="14"/>
-      <c r="E65" s="13"/>
-      <c r="BO65" s="17"/>
-      <c r="BR65" s="17"/>
+      <c r="D65" s="13"/>
+      <c r="E65" s="12"/>
+      <c r="BO65" s="16"/>
+      <c r="BR65" s="16"/>
     </row>
     <row r="66" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D66" s="14"/>
-      <c r="E66" s="13"/>
-      <c r="BO66" s="17"/>
-      <c r="BR66" s="17"/>
+      <c r="D66" s="13"/>
+      <c r="E66" s="12"/>
+      <c r="BO66" s="16"/>
+      <c r="BR66" s="16"/>
     </row>
     <row r="67" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D67" s="14"/>
-      <c r="E67" s="13"/>
-      <c r="BO67" s="17"/>
-      <c r="BR67" s="17"/>
+      <c r="D67" s="13"/>
+      <c r="E67" s="12"/>
+      <c r="BO67" s="16"/>
+      <c r="BR67" s="16"/>
     </row>
     <row r="68" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D68" s="14"/>
-      <c r="E68" s="13"/>
-      <c r="BO68" s="17"/>
-      <c r="BR68" s="17"/>
+      <c r="D68" s="13"/>
+      <c r="E68" s="12"/>
+      <c r="BO68" s="16"/>
+      <c r="BR68" s="16"/>
     </row>
     <row r="69" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D69" s="14"/>
-      <c r="E69" s="13"/>
-      <c r="BO69" s="17"/>
-      <c r="BR69" s="17"/>
+      <c r="D69" s="13"/>
+      <c r="E69" s="12"/>
+      <c r="BO69" s="16"/>
+      <c r="BR69" s="16"/>
     </row>
     <row r="70" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D70" s="14"/>
-      <c r="E70" s="13"/>
-      <c r="BO70" s="17"/>
-      <c r="BR70" s="17"/>
+      <c r="D70" s="13"/>
+      <c r="E70" s="12"/>
+      <c r="BO70" s="16"/>
+      <c r="BR70" s="16"/>
     </row>
     <row r="71" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D71" s="14"/>
-      <c r="E71" s="13"/>
-      <c r="BO71" s="17"/>
-      <c r="BR71" s="17"/>
+      <c r="D71" s="13"/>
+      <c r="E71" s="12"/>
+      <c r="BO71" s="16"/>
+      <c r="BR71" s="16"/>
     </row>
     <row r="72" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D72" s="14"/>
-      <c r="E72" s="13"/>
-      <c r="BO72" s="17"/>
-      <c r="BR72" s="17"/>
+      <c r="D72" s="13"/>
+      <c r="E72" s="12"/>
+      <c r="BO72" s="16"/>
+      <c r="BR72" s="16"/>
     </row>
     <row r="73" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D73" s="14"/>
-      <c r="E73" s="13"/>
-      <c r="BO73" s="17"/>
-      <c r="BR73" s="17"/>
+      <c r="D73" s="13"/>
+      <c r="E73" s="12"/>
+      <c r="BO73" s="16"/>
+      <c r="BR73" s="16"/>
     </row>
     <row r="74" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D74" s="14"/>
-      <c r="E74" s="13"/>
-      <c r="BO74" s="17"/>
-      <c r="BR74" s="17"/>
+      <c r="D74" s="13"/>
+      <c r="E74" s="12"/>
+      <c r="BO74" s="16"/>
+      <c r="BR74" s="16"/>
     </row>
     <row r="75" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D75" s="14"/>
-      <c r="E75" s="13"/>
-      <c r="BO75" s="17"/>
-      <c r="BR75" s="17"/>
+      <c r="D75" s="13"/>
+      <c r="E75" s="12"/>
+      <c r="BO75" s="16"/>
+      <c r="BR75" s="16"/>
     </row>
     <row r="76" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D76" s="14"/>
-      <c r="E76" s="13"/>
-      <c r="BO76" s="17"/>
-      <c r="BR76" s="17"/>
+      <c r="D76" s="13"/>
+      <c r="E76" s="12"/>
+      <c r="BO76" s="16"/>
+      <c r="BR76" s="16"/>
     </row>
     <row r="77" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D77" s="14"/>
-      <c r="E77" s="13"/>
-      <c r="BO77" s="17"/>
-      <c r="BR77" s="17"/>
+      <c r="D77" s="13"/>
+      <c r="E77" s="12"/>
+      <c r="BO77" s="16"/>
+      <c r="BR77" s="16"/>
     </row>
     <row r="78" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D78" s="14"/>
-      <c r="E78" s="13"/>
-      <c r="BO78" s="17"/>
-      <c r="BR78" s="17"/>
+      <c r="D78" s="13"/>
+      <c r="E78" s="12"/>
+      <c r="BO78" s="16"/>
+      <c r="BR78" s="16"/>
     </row>
     <row r="79" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D79" s="14"/>
-      <c r="E79" s="13"/>
-      <c r="BO79" s="17"/>
-      <c r="BR79" s="17"/>
+      <c r="D79" s="13"/>
+      <c r="E79" s="12"/>
+      <c r="BO79" s="16"/>
+      <c r="BR79" s="16"/>
     </row>
     <row r="80" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D80" s="14"/>
-      <c r="E80" s="13"/>
-      <c r="BO80" s="17"/>
-      <c r="BR80" s="17"/>
+      <c r="D80" s="13"/>
+      <c r="E80" s="12"/>
+      <c r="BO80" s="16"/>
+      <c r="BR80" s="16"/>
     </row>
     <row r="81" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D81" s="14"/>
-      <c r="E81" s="13"/>
-      <c r="BO81" s="17"/>
-      <c r="BR81" s="17"/>
+      <c r="D81" s="13"/>
+      <c r="E81" s="12"/>
+      <c r="BO81" s="16"/>
+      <c r="BR81" s="16"/>
     </row>
     <row r="82" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D82" s="14"/>
-      <c r="E82" s="13"/>
-      <c r="BO82" s="17"/>
-      <c r="BR82" s="17"/>
+      <c r="D82" s="13"/>
+      <c r="E82" s="12"/>
+      <c r="BO82" s="16"/>
+      <c r="BR82" s="16"/>
     </row>
     <row r="83" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D83" s="14"/>
-      <c r="E83" s="13"/>
-      <c r="BO83" s="17"/>
-      <c r="BR83" s="17"/>
+      <c r="D83" s="13"/>
+      <c r="E83" s="12"/>
+      <c r="BO83" s="16"/>
+      <c r="BR83" s="16"/>
     </row>
     <row r="84" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D84" s="14"/>
-      <c r="E84" s="13"/>
-      <c r="BO84" s="17"/>
-      <c r="BR84" s="17"/>
+      <c r="D84" s="13"/>
+      <c r="E84" s="12"/>
+      <c r="BO84" s="16"/>
+      <c r="BR84" s="16"/>
     </row>
     <row r="85" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D85" s="14"/>
-      <c r="E85" s="13"/>
-      <c r="BO85" s="17"/>
-      <c r="BR85" s="17"/>
+      <c r="D85" s="13"/>
+      <c r="E85" s="12"/>
+      <c r="BO85" s="16"/>
+      <c r="BR85" s="16"/>
     </row>
     <row r="86" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D86" s="14"/>
-      <c r="E86" s="13"/>
-      <c r="BO86" s="17"/>
-      <c r="BR86" s="17"/>
+      <c r="D86" s="13"/>
+      <c r="E86" s="12"/>
+      <c r="BO86" s="16"/>
+      <c r="BR86" s="16"/>
     </row>
     <row r="87" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D87" s="14"/>
-      <c r="E87" s="13"/>
-      <c r="BO87" s="17"/>
-      <c r="BR87" s="17"/>
+      <c r="D87" s="13"/>
+      <c r="E87" s="12"/>
+      <c r="BO87" s="16"/>
+      <c r="BR87" s="16"/>
     </row>
     <row r="88" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D88" s="14"/>
-      <c r="E88" s="13"/>
-      <c r="BO88" s="17"/>
-      <c r="BR88" s="17"/>
+      <c r="D88" s="13"/>
+      <c r="E88" s="12"/>
+      <c r="BO88" s="16"/>
+      <c r="BR88" s="16"/>
     </row>
     <row r="89" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D89" s="14"/>
-      <c r="E89" s="13"/>
-      <c r="BO89" s="17"/>
-      <c r="BR89" s="17"/>
+      <c r="D89" s="13"/>
+      <c r="E89" s="12"/>
+      <c r="BO89" s="16"/>
+      <c r="BR89" s="16"/>
     </row>
     <row r="90" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D90" s="14"/>
-      <c r="E90" s="13"/>
-      <c r="BO90" s="17"/>
-      <c r="BR90" s="17"/>
+      <c r="D90" s="13"/>
+      <c r="E90" s="12"/>
+      <c r="BO90" s="16"/>
+      <c r="BR90" s="16"/>
     </row>
     <row r="91" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D91" s="14"/>
-      <c r="E91" s="13"/>
-      <c r="BO91" s="17"/>
-      <c r="BR91" s="17"/>
+      <c r="D91" s="13"/>
+      <c r="E91" s="12"/>
+      <c r="BO91" s="16"/>
+      <c r="BR91" s="16"/>
     </row>
     <row r="92" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D92" s="14"/>
-      <c r="E92" s="13"/>
-      <c r="BO92" s="17"/>
-      <c r="BR92" s="17"/>
+      <c r="D92" s="13"/>
+      <c r="E92" s="12"/>
+      <c r="BO92" s="16"/>
+      <c r="BR92" s="16"/>
     </row>
     <row r="93" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D93" s="14"/>
-      <c r="E93" s="13"/>
-      <c r="BO93" s="17"/>
-      <c r="BR93" s="17"/>
+      <c r="D93" s="13"/>
+      <c r="E93" s="12"/>
+      <c r="BO93" s="16"/>
+      <c r="BR93" s="16"/>
     </row>
     <row r="94" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D94" s="14"/>
-      <c r="E94" s="13"/>
-      <c r="BO94" s="17"/>
-      <c r="BR94" s="17"/>
+      <c r="D94" s="13"/>
+      <c r="E94" s="12"/>
+      <c r="BO94" s="16"/>
+      <c r="BR94" s="16"/>
     </row>
     <row r="95" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D95" s="14"/>
-      <c r="E95" s="13"/>
-      <c r="BO95" s="17"/>
-      <c r="BR95" s="17"/>
+      <c r="D95" s="13"/>
+      <c r="E95" s="12"/>
+      <c r="BO95" s="16"/>
+      <c r="BR95" s="16"/>
     </row>
     <row r="96" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D96" s="14"/>
-      <c r="E96" s="13"/>
-      <c r="BO96" s="17"/>
-      <c r="BR96" s="17"/>
+      <c r="D96" s="13"/>
+      <c r="E96" s="12"/>
+      <c r="BO96" s="16"/>
+      <c r="BR96" s="16"/>
     </row>
     <row r="97" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D97" s="14"/>
-      <c r="E97" s="13"/>
-      <c r="BO97" s="17"/>
-      <c r="BR97" s="17"/>
+      <c r="D97" s="13"/>
+      <c r="E97" s="12"/>
+      <c r="BO97" s="16"/>
+      <c r="BR97" s="16"/>
     </row>
     <row r="98" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D98" s="14"/>
-      <c r="E98" s="13"/>
-      <c r="BO98" s="17"/>
-      <c r="BR98" s="17"/>
+      <c r="D98" s="13"/>
+      <c r="E98" s="12"/>
+      <c r="BO98" s="16"/>
+      <c r="BR98" s="16"/>
     </row>
     <row r="99" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D99" s="14"/>
-      <c r="E99" s="13"/>
-      <c r="BO99" s="17"/>
-      <c r="BR99" s="17"/>
+      <c r="D99" s="13"/>
+      <c r="E99" s="12"/>
+      <c r="BO99" s="16"/>
+      <c r="BR99" s="16"/>
     </row>
     <row r="100" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D100" s="14"/>
-      <c r="E100" s="13"/>
-      <c r="BO100" s="17"/>
-      <c r="BR100" s="17"/>
+      <c r="D100" s="13"/>
+      <c r="E100" s="12"/>
+      <c r="BO100" s="16"/>
+      <c r="BR100" s="16"/>
     </row>
     <row r="101" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D101" s="14"/>
-      <c r="E101" s="13"/>
-      <c r="BO101" s="17"/>
-      <c r="BR101" s="17"/>
+      <c r="D101" s="13"/>
+      <c r="E101" s="12"/>
+      <c r="BO101" s="16"/>
+      <c r="BR101" s="16"/>
     </row>
     <row r="102" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D102" s="14"/>
-      <c r="E102" s="13"/>
-      <c r="BO102" s="17"/>
-      <c r="BR102" s="17"/>
+      <c r="D102" s="13"/>
+      <c r="E102" s="12"/>
+      <c r="BO102" s="16"/>
+      <c r="BR102" s="16"/>
     </row>
     <row r="103" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D103" s="14"/>
-      <c r="E103" s="13"/>
-      <c r="BO103" s="17"/>
-      <c r="BR103" s="17"/>
+      <c r="D103" s="13"/>
+      <c r="E103" s="12"/>
+      <c r="BO103" s="16"/>
+      <c r="BR103" s="16"/>
     </row>
     <row r="104" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D104" s="14"/>
-      <c r="E104" s="13"/>
-      <c r="BO104" s="17"/>
-      <c r="BR104" s="17"/>
+      <c r="D104" s="13"/>
+      <c r="E104" s="12"/>
+      <c r="BO104" s="16"/>
+      <c r="BR104" s="16"/>
     </row>
     <row r="105" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D105" s="14"/>
-      <c r="E105" s="13"/>
-      <c r="BO105" s="17"/>
-      <c r="BR105" s="17"/>
+      <c r="D105" s="13"/>
+      <c r="E105" s="12"/>
+      <c r="BO105" s="16"/>
+      <c r="BR105" s="16"/>
     </row>
     <row r="106" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D106" s="14"/>
-      <c r="E106" s="13"/>
-      <c r="BO106" s="17"/>
-      <c r="BR106" s="17"/>
+      <c r="D106" s="13"/>
+      <c r="E106" s="12"/>
+      <c r="BO106" s="16"/>
+      <c r="BR106" s="16"/>
     </row>
     <row r="107" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D107" s="14"/>
-      <c r="E107" s="13"/>
-      <c r="BO107" s="17"/>
-      <c r="BR107" s="17"/>
+      <c r="D107" s="13"/>
+      <c r="E107" s="12"/>
+      <c r="BO107" s="16"/>
+      <c r="BR107" s="16"/>
     </row>
     <row r="108" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D108" s="14"/>
-      <c r="E108" s="13"/>
-      <c r="BO108" s="17"/>
-      <c r="BR108" s="17"/>
+      <c r="D108" s="13"/>
+      <c r="E108" s="12"/>
+      <c r="BO108" s="16"/>
+      <c r="BR108" s="16"/>
     </row>
     <row r="109" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D109" s="14"/>
-      <c r="E109" s="13"/>
-      <c r="BO109" s="17"/>
-      <c r="BR109" s="17"/>
+      <c r="D109" s="13"/>
+      <c r="E109" s="12"/>
+      <c r="BO109" s="16"/>
+      <c r="BR109" s="16"/>
     </row>
     <row r="110" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D110" s="14"/>
-      <c r="E110" s="13"/>
-      <c r="BO110" s="17"/>
-      <c r="BR110" s="17"/>
+      <c r="D110" s="13"/>
+      <c r="E110" s="12"/>
+      <c r="BO110" s="16"/>
+      <c r="BR110" s="16"/>
     </row>
     <row r="111" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D111" s="14"/>
-      <c r="E111" s="13"/>
-      <c r="BO111" s="17"/>
-      <c r="BR111" s="17"/>
+      <c r="D111" s="13"/>
+      <c r="E111" s="12"/>
+      <c r="BO111" s="16"/>
+      <c r="BR111" s="16"/>
     </row>
     <row r="112" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D112" s="14"/>
-      <c r="E112" s="13"/>
-      <c r="BO112" s="17"/>
-      <c r="BR112" s="17"/>
+      <c r="D112" s="13"/>
+      <c r="E112" s="12"/>
+      <c r="BO112" s="16"/>
+      <c r="BR112" s="16"/>
     </row>
     <row r="113" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D113" s="14"/>
-      <c r="E113" s="13"/>
-      <c r="BO113" s="17"/>
-      <c r="BR113" s="17"/>
+      <c r="D113" s="13"/>
+      <c r="E113" s="12"/>
+      <c r="BO113" s="16"/>
+      <c r="BR113" s="16"/>
     </row>
     <row r="114" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D114" s="14"/>
-      <c r="E114" s="13"/>
-      <c r="BO114" s="17"/>
-      <c r="BR114" s="17"/>
+      <c r="D114" s="13"/>
+      <c r="E114" s="12"/>
+      <c r="BO114" s="16"/>
+      <c r="BR114" s="16"/>
     </row>
     <row r="115" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D115" s="14"/>
-      <c r="E115" s="13"/>
-      <c r="BO115" s="17"/>
-      <c r="BR115" s="17"/>
+      <c r="D115" s="13"/>
+      <c r="E115" s="12"/>
+      <c r="BO115" s="16"/>
+      <c r="BR115" s="16"/>
     </row>
     <row r="116" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D116" s="14"/>
-      <c r="E116" s="13"/>
-      <c r="BO116" s="17"/>
-      <c r="BR116" s="17"/>
+      <c r="D116" s="13"/>
+      <c r="E116" s="12"/>
+      <c r="BO116" s="16"/>
+      <c r="BR116" s="16"/>
     </row>
     <row r="117" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D117" s="14"/>
-      <c r="E117" s="13"/>
-      <c r="BO117" s="17"/>
-      <c r="BR117" s="17"/>
+      <c r="D117" s="13"/>
+      <c r="E117" s="12"/>
+      <c r="BO117" s="16"/>
+      <c r="BR117" s="16"/>
     </row>
     <row r="118" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D118" s="14"/>
-      <c r="E118" s="13"/>
-      <c r="BO118" s="17"/>
-      <c r="BR118" s="17"/>
+      <c r="D118" s="13"/>
+      <c r="E118" s="12"/>
+      <c r="BO118" s="16"/>
+      <c r="BR118" s="16"/>
     </row>
     <row r="119" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D119" s="14"/>
-      <c r="E119" s="13"/>
-      <c r="BO119" s="17"/>
-      <c r="BR119" s="17"/>
+      <c r="D119" s="13"/>
+      <c r="E119" s="12"/>
+      <c r="BO119" s="16"/>
+      <c r="BR119" s="16"/>
     </row>
     <row r="120" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D120" s="14"/>
-      <c r="E120" s="13"/>
-      <c r="BO120" s="17"/>
-      <c r="BR120" s="17"/>
+      <c r="D120" s="13"/>
+      <c r="E120" s="12"/>
+      <c r="BO120" s="16"/>
+      <c r="BR120" s="16"/>
     </row>
     <row r="121" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D121" s="14"/>
-      <c r="E121" s="13"/>
-      <c r="BO121" s="17"/>
-      <c r="BR121" s="17"/>
+      <c r="D121" s="13"/>
+      <c r="E121" s="12"/>
+      <c r="BO121" s="16"/>
+      <c r="BR121" s="16"/>
     </row>
     <row r="122" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D122" s="14"/>
-      <c r="E122" s="13"/>
-      <c r="BO122" s="17"/>
-      <c r="BR122" s="17"/>
+      <c r="D122" s="13"/>
+      <c r="E122" s="12"/>
+      <c r="BO122" s="16"/>
+      <c r="BR122" s="16"/>
     </row>
     <row r="123" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D123" s="14"/>
-      <c r="E123" s="13"/>
-      <c r="BO123" s="17"/>
-      <c r="BR123" s="17"/>
+      <c r="D123" s="13"/>
+      <c r="E123" s="12"/>
+      <c r="BO123" s="16"/>
+      <c r="BR123" s="16"/>
     </row>
     <row r="124" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D124" s="14"/>
-      <c r="E124" s="13"/>
-      <c r="BO124" s="17"/>
-      <c r="BR124" s="17"/>
+      <c r="D124" s="13"/>
+      <c r="E124" s="12"/>
+      <c r="BO124" s="16"/>
+      <c r="BR124" s="16"/>
     </row>
     <row r="125" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D125" s="14"/>
-      <c r="E125" s="13"/>
-      <c r="BO125" s="17"/>
-      <c r="BR125" s="17"/>
+      <c r="D125" s="13"/>
+      <c r="E125" s="12"/>
+      <c r="BO125" s="16"/>
+      <c r="BR125" s="16"/>
     </row>
     <row r="126" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D126" s="14"/>
-      <c r="E126" s="13"/>
-      <c r="BO126" s="17"/>
-      <c r="BR126" s="17"/>
+      <c r="D126" s="13"/>
+      <c r="E126" s="12"/>
+      <c r="BO126" s="16"/>
+      <c r="BR126" s="16"/>
     </row>
     <row r="127" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D127" s="14"/>
-      <c r="E127" s="13"/>
-      <c r="BO127" s="17"/>
-      <c r="BR127" s="17"/>
+      <c r="D127" s="13"/>
+      <c r="E127" s="12"/>
+      <c r="BO127" s="16"/>
+      <c r="BR127" s="16"/>
     </row>
     <row r="128" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D128" s="14"/>
-      <c r="E128" s="13"/>
-      <c r="BO128" s="17"/>
-      <c r="BR128" s="17"/>
+      <c r="D128" s="13"/>
+      <c r="E128" s="12"/>
+      <c r="BO128" s="16"/>
+      <c r="BR128" s="16"/>
     </row>
     <row r="129" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D129" s="14"/>
-      <c r="E129" s="13"/>
-      <c r="BO129" s="17"/>
-      <c r="BR129" s="17"/>
+      <c r="D129" s="13"/>
+      <c r="E129" s="12"/>
+      <c r="BO129" s="16"/>
+      <c r="BR129" s="16"/>
     </row>
     <row r="130" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D130" s="14"/>
-      <c r="E130" s="13"/>
-      <c r="BO130" s="17"/>
-      <c r="BR130" s="17"/>
+      <c r="D130" s="13"/>
+      <c r="E130" s="12"/>
+      <c r="BO130" s="16"/>
+      <c r="BR130" s="16"/>
     </row>
     <row r="131" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D131" s="14"/>
-      <c r="E131" s="13"/>
-      <c r="BO131" s="17"/>
-      <c r="BR131" s="17"/>
+      <c r="D131" s="13"/>
+      <c r="E131" s="12"/>
+      <c r="BO131" s="16"/>
+      <c r="BR131" s="16"/>
     </row>
     <row r="132" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D132" s="14"/>
-      <c r="E132" s="13"/>
-      <c r="BO132" s="17"/>
-      <c r="BR132" s="17"/>
+      <c r="D132" s="13"/>
+      <c r="E132" s="12"/>
+      <c r="BO132" s="16"/>
+      <c r="BR132" s="16"/>
     </row>
     <row r="133" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D133" s="14"/>
-      <c r="E133" s="13"/>
-      <c r="BO133" s="17"/>
-      <c r="BR133" s="17"/>
+      <c r="D133" s="13"/>
+      <c r="E133" s="12"/>
+      <c r="BO133" s="16"/>
+      <c r="BR133" s="16"/>
     </row>
     <row r="134" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D134" s="14"/>
-      <c r="E134" s="13"/>
-      <c r="BO134" s="17"/>
-      <c r="BR134" s="17"/>
+      <c r="D134" s="13"/>
+      <c r="E134" s="12"/>
+      <c r="BO134" s="16"/>
+      <c r="BR134" s="16"/>
     </row>
     <row r="135" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D135" s="14"/>
-      <c r="E135" s="13"/>
-      <c r="BO135" s="17"/>
-      <c r="BR135" s="17"/>
+      <c r="D135" s="13"/>
+      <c r="E135" s="12"/>
+      <c r="BO135" s="16"/>
+      <c r="BR135" s="16"/>
     </row>
     <row r="136" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D136" s="14"/>
-      <c r="E136" s="13"/>
-      <c r="BO136" s="17"/>
-      <c r="BR136" s="17"/>
+      <c r="D136" s="13"/>
+      <c r="E136" s="12"/>
+      <c r="BO136" s="16"/>
+      <c r="BR136" s="16"/>
     </row>
     <row r="137" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D137" s="14"/>
-      <c r="E137" s="13"/>
-      <c r="BO137" s="17"/>
-      <c r="BR137" s="17"/>
+      <c r="D137" s="13"/>
+      <c r="E137" s="12"/>
+      <c r="BO137" s="16"/>
+      <c r="BR137" s="16"/>
     </row>
     <row r="138" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D138" s="14"/>
-      <c r="E138" s="13"/>
-      <c r="BO138" s="17"/>
-      <c r="BR138" s="17"/>
+      <c r="D138" s="13"/>
+      <c r="E138" s="12"/>
+      <c r="BO138" s="16"/>
+      <c r="BR138" s="16"/>
     </row>
     <row r="139" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D139" s="14"/>
-      <c r="E139" s="13"/>
-      <c r="BO139" s="17"/>
-      <c r="BR139" s="17"/>
+      <c r="D139" s="13"/>
+      <c r="E139" s="12"/>
+      <c r="BO139" s="16"/>
+      <c r="BR139" s="16"/>
     </row>
     <row r="140" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D140" s="14"/>
-      <c r="E140" s="13"/>
-      <c r="BO140" s="17"/>
-      <c r="BR140" s="17"/>
+      <c r="D140" s="13"/>
+      <c r="E140" s="12"/>
+      <c r="BO140" s="16"/>
+      <c r="BR140" s="16"/>
     </row>
     <row r="141" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D141" s="14"/>
-      <c r="E141" s="13"/>
-      <c r="BO141" s="17"/>
-      <c r="BR141" s="17"/>
+      <c r="D141" s="13"/>
+      <c r="E141" s="12"/>
+      <c r="BO141" s="16"/>
+      <c r="BR141" s="16"/>
     </row>
     <row r="142" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D142" s="14"/>
-      <c r="E142" s="13"/>
-      <c r="BO142" s="17"/>
-      <c r="BR142" s="17"/>
+      <c r="D142" s="13"/>
+      <c r="E142" s="12"/>
+      <c r="BO142" s="16"/>
+      <c r="BR142" s="16"/>
     </row>
     <row r="143" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D143" s="14"/>
-      <c r="E143" s="13"/>
-      <c r="BO143" s="17"/>
-      <c r="BR143" s="17"/>
+      <c r="D143" s="13"/>
+      <c r="E143" s="12"/>
+      <c r="BO143" s="16"/>
+      <c r="BR143" s="16"/>
     </row>
     <row r="144" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D144" s="14"/>
-      <c r="E144" s="13"/>
-      <c r="BO144" s="17"/>
-      <c r="BR144" s="17"/>
+      <c r="D144" s="13"/>
+      <c r="E144" s="12"/>
+      <c r="BO144" s="16"/>
+      <c r="BR144" s="16"/>
     </row>
     <row r="145" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D145" s="14"/>
-      <c r="E145" s="13"/>
-      <c r="BO145" s="17"/>
-      <c r="BR145" s="17"/>
+      <c r="D145" s="13"/>
+      <c r="E145" s="12"/>
+      <c r="BO145" s="16"/>
+      <c r="BR145" s="16"/>
     </row>
     <row r="146" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D146" s="14"/>
-      <c r="E146" s="13"/>
-      <c r="BO146" s="17"/>
-      <c r="BR146" s="17"/>
+      <c r="D146" s="13"/>
+      <c r="E146" s="12"/>
+      <c r="BO146" s="16"/>
+      <c r="BR146" s="16"/>
     </row>
     <row r="147" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D147" s="14"/>
-      <c r="E147" s="13"/>
-      <c r="BO147" s="17"/>
-      <c r="BR147" s="17"/>
+      <c r="D147" s="13"/>
+      <c r="E147" s="12"/>
+      <c r="BO147" s="16"/>
+      <c r="BR147" s="16"/>
     </row>
     <row r="148" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D148" s="14"/>
-      <c r="E148" s="13"/>
-      <c r="BO148" s="17"/>
-      <c r="BR148" s="17"/>
+      <c r="D148" s="13"/>
+      <c r="E148" s="12"/>
+      <c r="BO148" s="16"/>
+      <c r="BR148" s="16"/>
     </row>
     <row r="149" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D149" s="14"/>
-      <c r="E149" s="13"/>
-      <c r="BO149" s="17"/>
-      <c r="BR149" s="17"/>
+      <c r="D149" s="13"/>
+      <c r="E149" s="12"/>
+      <c r="BO149" s="16"/>
+      <c r="BR149" s="16"/>
     </row>
     <row r="150" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D150" s="14"/>
-      <c r="E150" s="13"/>
-      <c r="BO150" s="17"/>
-      <c r="BR150" s="17"/>
+      <c r="D150" s="13"/>
+      <c r="E150" s="12"/>
+      <c r="BO150" s="16"/>
+      <c r="BR150" s="16"/>
     </row>
     <row r="151" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D151" s="14"/>
-      <c r="E151" s="13"/>
-      <c r="BO151" s="17"/>
-      <c r="BR151" s="17"/>
+      <c r="D151" s="13"/>
+      <c r="E151" s="12"/>
+      <c r="BO151" s="16"/>
+      <c r="BR151" s="16"/>
     </row>
     <row r="152" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D152" s="14"/>
-      <c r="E152" s="13"/>
-      <c r="BO152" s="17"/>
-      <c r="BR152" s="17"/>
+      <c r="D152" s="13"/>
+      <c r="E152" s="12"/>
+      <c r="BO152" s="16"/>
+      <c r="BR152" s="16"/>
     </row>
     <row r="153" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D153" s="14"/>
-      <c r="E153" s="13"/>
-      <c r="BO153" s="17"/>
-      <c r="BR153" s="17"/>
+      <c r="D153" s="13"/>
+      <c r="E153" s="12"/>
+      <c r="BO153" s="16"/>
+      <c r="BR153" s="16"/>
     </row>
     <row r="154" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D154" s="14"/>
-      <c r="E154" s="13"/>
-      <c r="BO154" s="17"/>
-      <c r="BR154" s="17"/>
+      <c r="D154" s="13"/>
+      <c r="E154" s="12"/>
+      <c r="BO154" s="16"/>
+      <c r="BR154" s="16"/>
     </row>
     <row r="155" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D155" s="14"/>
-      <c r="E155" s="13"/>
-      <c r="BO155" s="17"/>
-      <c r="BR155" s="17"/>
+      <c r="D155" s="13"/>
+      <c r="E155" s="12"/>
+      <c r="BO155" s="16"/>
+      <c r="BR155" s="16"/>
     </row>
     <row r="156" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D156" s="14"/>
-      <c r="E156" s="13"/>
-      <c r="BO156" s="17"/>
-      <c r="BR156" s="17"/>
+      <c r="D156" s="13"/>
+      <c r="E156" s="12"/>
+      <c r="BO156" s="16"/>
+      <c r="BR156" s="16"/>
     </row>
     <row r="157" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D157" s="14"/>
-      <c r="E157" s="13"/>
-      <c r="BO157" s="17"/>
-      <c r="BR157" s="17"/>
+      <c r="D157" s="13"/>
+      <c r="E157" s="12"/>
+      <c r="BO157" s="16"/>
+      <c r="BR157" s="16"/>
     </row>
     <row r="158" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D158" s="14"/>
-      <c r="E158" s="13"/>
-      <c r="BO158" s="17"/>
-      <c r="BR158" s="17"/>
+      <c r="D158" s="13"/>
+      <c r="E158" s="12"/>
+      <c r="BO158" s="16"/>
+      <c r="BR158" s="16"/>
     </row>
     <row r="159" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D159" s="14"/>
-      <c r="E159" s="13"/>
-      <c r="BO159" s="17"/>
-      <c r="BR159" s="17"/>
+      <c r="D159" s="13"/>
+      <c r="E159" s="12"/>
+      <c r="BO159" s="16"/>
+      <c r="BR159" s="16"/>
     </row>
     <row r="160" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D160" s="14"/>
-      <c r="E160" s="13"/>
-      <c r="BO160" s="17"/>
-      <c r="BR160" s="17"/>
+      <c r="D160" s="13"/>
+      <c r="E160" s="12"/>
+      <c r="BO160" s="16"/>
+      <c r="BR160" s="16"/>
     </row>
     <row r="161" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D161" s="14"/>
-      <c r="E161" s="13"/>
-      <c r="BO161" s="17"/>
-      <c r="BR161" s="17"/>
+      <c r="D161" s="13"/>
+      <c r="E161" s="12"/>
+      <c r="BO161" s="16"/>
+      <c r="BR161" s="16"/>
     </row>
     <row r="162" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D162" s="14"/>
-      <c r="E162" s="13"/>
-      <c r="BO162" s="17"/>
-      <c r="BR162" s="17"/>
+      <c r="D162" s="13"/>
+      <c r="E162" s="12"/>
+      <c r="BO162" s="16"/>
+      <c r="BR162" s="16"/>
     </row>
     <row r="163" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D163" s="14"/>
-      <c r="E163" s="13"/>
-      <c r="BO163" s="17"/>
-      <c r="BR163" s="17"/>
+      <c r="D163" s="13"/>
+      <c r="E163" s="12"/>
+      <c r="BO163" s="16"/>
+      <c r="BR163" s="16"/>
     </row>
     <row r="164" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D164" s="14"/>
-      <c r="E164" s="13"/>
-      <c r="BO164" s="17"/>
-      <c r="BR164" s="17"/>
+      <c r="D164" s="13"/>
+      <c r="E164" s="12"/>
+      <c r="BO164" s="16"/>
+      <c r="BR164" s="16"/>
     </row>
     <row r="165" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D165" s="14"/>
-      <c r="E165" s="13"/>
-      <c r="BO165" s="17"/>
-      <c r="BR165" s="17"/>
+      <c r="D165" s="13"/>
+      <c r="E165" s="12"/>
+      <c r="BO165" s="16"/>
+      <c r="BR165" s="16"/>
     </row>
     <row r="166" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D166" s="14"/>
-      <c r="E166" s="13"/>
-      <c r="BO166" s="17"/>
-      <c r="BR166" s="17"/>
+      <c r="D166" s="13"/>
+      <c r="E166" s="12"/>
+      <c r="BO166" s="16"/>
+      <c r="BR166" s="16"/>
     </row>
     <row r="167" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D167" s="14"/>
-      <c r="E167" s="13"/>
-      <c r="BO167" s="17"/>
-      <c r="BR167" s="17"/>
+      <c r="D167" s="13"/>
+      <c r="E167" s="12"/>
+      <c r="BO167" s="16"/>
+      <c r="BR167" s="16"/>
     </row>
     <row r="168" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D168" s="14"/>
-      <c r="E168" s="13"/>
-      <c r="BO168" s="17"/>
-      <c r="BR168" s="17"/>
+      <c r="D168" s="13"/>
+      <c r="E168" s="12"/>
+      <c r="BO168" s="16"/>
+      <c r="BR168" s="16"/>
     </row>
     <row r="169" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D169" s="14"/>
-      <c r="E169" s="13"/>
-      <c r="BO169" s="17"/>
-      <c r="BR169" s="17"/>
+      <c r="D169" s="13"/>
+      <c r="E169" s="12"/>
+      <c r="BO169" s="16"/>
+      <c r="BR169" s="16"/>
     </row>
     <row r="170" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D170" s="14"/>
-      <c r="E170" s="13"/>
-      <c r="BO170" s="17"/>
-      <c r="BR170" s="17"/>
+      <c r="D170" s="13"/>
+      <c r="E170" s="12"/>
+      <c r="BO170" s="16"/>
+      <c r="BR170" s="16"/>
     </row>
     <row r="171" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D171" s="14"/>
-      <c r="E171" s="13"/>
-      <c r="BO171" s="17"/>
-      <c r="BR171" s="17"/>
+      <c r="D171" s="13"/>
+      <c r="E171" s="12"/>
+      <c r="BO171" s="16"/>
+      <c r="BR171" s="16"/>
     </row>
     <row r="172" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D172" s="14"/>
-      <c r="E172" s="13"/>
-      <c r="BO172" s="17"/>
-      <c r="BR172" s="17"/>
+      <c r="D172" s="13"/>
+      <c r="E172" s="12"/>
+      <c r="BO172" s="16"/>
+      <c r="BR172" s="16"/>
     </row>
     <row r="173" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D173" s="14"/>
-      <c r="E173" s="13"/>
-      <c r="BO173" s="17"/>
-      <c r="BR173" s="17"/>
+      <c r="D173" s="13"/>
+      <c r="E173" s="12"/>
+      <c r="BO173" s="16"/>
+      <c r="BR173" s="16"/>
     </row>
     <row r="174" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D174" s="14"/>
-      <c r="E174" s="13"/>
-      <c r="BO174" s="17"/>
-      <c r="BR174" s="17"/>
+      <c r="D174" s="13"/>
+      <c r="E174" s="12"/>
+      <c r="BO174" s="16"/>
+      <c r="BR174" s="16"/>
     </row>
     <row r="175" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D175" s="14"/>
-      <c r="E175" s="13"/>
-      <c r="BO175" s="17"/>
-      <c r="BR175" s="17"/>
+      <c r="D175" s="13"/>
+      <c r="E175" s="12"/>
+      <c r="BO175" s="16"/>
+      <c r="BR175" s="16"/>
     </row>
     <row r="176" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D176" s="14"/>
-      <c r="E176" s="13"/>
-      <c r="BO176" s="17"/>
-      <c r="BR176" s="17"/>
+      <c r="D176" s="13"/>
+      <c r="E176" s="12"/>
+      <c r="BO176" s="16"/>
+      <c r="BR176" s="16"/>
     </row>
     <row r="177" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D177" s="14"/>
-      <c r="E177" s="13"/>
-      <c r="BO177" s="17"/>
-      <c r="BR177" s="17"/>
+      <c r="D177" s="13"/>
+      <c r="E177" s="12"/>
+      <c r="BO177" s="16"/>
+      <c r="BR177" s="16"/>
     </row>
     <row r="178" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D178" s="14"/>
-      <c r="E178" s="13"/>
-      <c r="BO178" s="17"/>
-      <c r="BR178" s="17"/>
+      <c r="D178" s="13"/>
+      <c r="E178" s="12"/>
+      <c r="BO178" s="16"/>
+      <c r="BR178" s="16"/>
     </row>
     <row r="179" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D179" s="14"/>
-      <c r="E179" s="13"/>
-      <c r="BO179" s="17"/>
-      <c r="BR179" s="17"/>
+      <c r="D179" s="13"/>
+      <c r="E179" s="12"/>
+      <c r="BO179" s="16"/>
+      <c r="BR179" s="16"/>
     </row>
     <row r="180" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D180" s="14"/>
-      <c r="E180" s="13"/>
-      <c r="BO180" s="17"/>
-      <c r="BR180" s="17"/>
+      <c r="D180" s="13"/>
+      <c r="E180" s="12"/>
+      <c r="BO180" s="16"/>
+      <c r="BR180" s="16"/>
     </row>
     <row r="181" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D181" s="14"/>
-      <c r="E181" s="13"/>
-      <c r="BO181" s="17"/>
-      <c r="BR181" s="17"/>
+      <c r="D181" s="13"/>
+      <c r="E181" s="12"/>
+      <c r="BO181" s="16"/>
+      <c r="BR181" s="16"/>
     </row>
     <row r="182" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D182" s="14"/>
-      <c r="E182" s="13"/>
-      <c r="BO182" s="17"/>
-      <c r="BR182" s="17"/>
+      <c r="D182" s="13"/>
+      <c r="E182" s="12"/>
+      <c r="BO182" s="16"/>
+      <c r="BR182" s="16"/>
     </row>
     <row r="183" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D183" s="14"/>
-      <c r="E183" s="13"/>
-      <c r="BO183" s="17"/>
-      <c r="BR183" s="17"/>
+      <c r="D183" s="13"/>
+      <c r="E183" s="12"/>
+      <c r="BO183" s="16"/>
+      <c r="BR183" s="16"/>
     </row>
     <row r="184" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D184" s="14"/>
-      <c r="E184" s="13"/>
-      <c r="BO184" s="17"/>
-      <c r="BR184" s="17"/>
+      <c r="D184" s="13"/>
+      <c r="E184" s="12"/>
+      <c r="BO184" s="16"/>
+      <c r="BR184" s="16"/>
     </row>
     <row r="185" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D185" s="14"/>
-      <c r="E185" s="13"/>
-      <c r="BO185" s="17"/>
-      <c r="BR185" s="17"/>
+      <c r="D185" s="13"/>
+      <c r="E185" s="12"/>
+      <c r="BO185" s="16"/>
+      <c r="BR185" s="16"/>
     </row>
     <row r="186" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D186" s="14"/>
-      <c r="E186" s="13"/>
-      <c r="BO186" s="17"/>
-      <c r="BR186" s="17"/>
+      <c r="D186" s="13"/>
+      <c r="E186" s="12"/>
+      <c r="BO186" s="16"/>
+      <c r="BR186" s="16"/>
     </row>
     <row r="187" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D187" s="14"/>
-      <c r="E187" s="13"/>
-      <c r="BO187" s="17"/>
-      <c r="BR187" s="17"/>
+      <c r="D187" s="13"/>
+      <c r="E187" s="12"/>
+      <c r="BO187" s="16"/>
+      <c r="BR187" s="16"/>
     </row>
     <row r="188" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D188" s="14"/>
-      <c r="E188" s="13"/>
-      <c r="BO188" s="17"/>
-      <c r="BR188" s="17"/>
+      <c r="D188" s="13"/>
+      <c r="E188" s="12"/>
+      <c r="BO188" s="16"/>
+      <c r="BR188" s="16"/>
     </row>
     <row r="189" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D189" s="14"/>
-      <c r="E189" s="13"/>
-      <c r="BO189" s="17"/>
-      <c r="BR189" s="17"/>
+      <c r="D189" s="13"/>
+      <c r="E189" s="12"/>
+      <c r="BO189" s="16"/>
+      <c r="BR189" s="16"/>
     </row>
     <row r="190" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D190" s="14"/>
-      <c r="E190" s="13"/>
-      <c r="BO190" s="17"/>
-      <c r="BR190" s="17"/>
+      <c r="D190" s="13"/>
+      <c r="E190" s="12"/>
+      <c r="BO190" s="16"/>
+      <c r="BR190" s="16"/>
     </row>
     <row r="191" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D191" s="14"/>
-      <c r="E191" s="13"/>
-      <c r="BO191" s="17"/>
-      <c r="BR191" s="17"/>
+      <c r="D191" s="13"/>
+      <c r="E191" s="12"/>
+      <c r="BO191" s="16"/>
+      <c r="BR191" s="16"/>
     </row>
     <row r="192" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D192" s="14"/>
-      <c r="E192" s="13"/>
-      <c r="BO192" s="17"/>
-      <c r="BR192" s="17"/>
+      <c r="D192" s="13"/>
+      <c r="E192" s="12"/>
+      <c r="BO192" s="16"/>
+      <c r="BR192" s="16"/>
     </row>
     <row r="193" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D193" s="14"/>
-      <c r="E193" s="13"/>
-      <c r="BO193" s="17"/>
-      <c r="BR193" s="17"/>
+      <c r="D193" s="13"/>
+      <c r="E193" s="12"/>
+      <c r="BO193" s="16"/>
+      <c r="BR193" s="16"/>
     </row>
     <row r="194" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D194" s="14"/>
-      <c r="E194" s="13"/>
-      <c r="BO194" s="17"/>
-      <c r="BR194" s="17"/>
+      <c r="D194" s="13"/>
+      <c r="E194" s="12"/>
+      <c r="BO194" s="16"/>
+      <c r="BR194" s="16"/>
     </row>
     <row r="195" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D195" s="14"/>
-      <c r="E195" s="13"/>
-      <c r="BO195" s="17"/>
-      <c r="BR195" s="17"/>
+      <c r="D195" s="13"/>
+      <c r="E195" s="12"/>
+      <c r="BO195" s="16"/>
+      <c r="BR195" s="16"/>
     </row>
     <row r="196" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D196" s="14"/>
-      <c r="E196" s="13"/>
-      <c r="BO196" s="17"/>
-      <c r="BR196" s="17"/>
+      <c r="D196" s="13"/>
+      <c r="E196" s="12"/>
+      <c r="BO196" s="16"/>
+      <c r="BR196" s="16"/>
     </row>
     <row r="197" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D197" s="14"/>
-      <c r="E197" s="13"/>
-      <c r="BO197" s="17"/>
-      <c r="BR197" s="17"/>
+      <c r="D197" s="13"/>
+      <c r="E197" s="12"/>
+      <c r="BO197" s="16"/>
+      <c r="BR197" s="16"/>
     </row>
     <row r="198" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D198" s="14"/>
-      <c r="E198" s="13"/>
-      <c r="BO198" s="17"/>
-      <c r="BR198" s="17"/>
+      <c r="D198" s="13"/>
+      <c r="E198" s="12"/>
+      <c r="BO198" s="16"/>
+      <c r="BR198" s="16"/>
     </row>
     <row r="199" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D199" s="14"/>
-      <c r="E199" s="13"/>
-      <c r="BO199" s="17"/>
-      <c r="BR199" s="17"/>
+      <c r="D199" s="13"/>
+      <c r="E199" s="12"/>
+      <c r="BO199" s="16"/>
+      <c r="BR199" s="16"/>
     </row>
     <row r="200" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D200" s="14"/>
-      <c r="E200" s="13"/>
-      <c r="BO200" s="17"/>
-      <c r="BR200" s="17"/>
+      <c r="D200" s="13"/>
+      <c r="E200" s="12"/>
+      <c r="BO200" s="16"/>
+      <c r="BR200" s="16"/>
     </row>
     <row r="201" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D201" s="14"/>
-      <c r="E201" s="13"/>
-      <c r="BO201" s="17"/>
-      <c r="BR201" s="17"/>
+      <c r="D201" s="13"/>
+      <c r="E201" s="12"/>
+      <c r="BO201" s="16"/>
+      <c r="BR201" s="16"/>
     </row>
     <row r="202" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D202" s="14"/>
-      <c r="E202" s="13"/>
-      <c r="BO202" s="17"/>
-      <c r="BR202" s="17"/>
+      <c r="D202" s="13"/>
+      <c r="E202" s="12"/>
+      <c r="BO202" s="16"/>
+      <c r="BR202" s="16"/>
     </row>
     <row r="203" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D203" s="14"/>
-      <c r="E203" s="13"/>
-      <c r="BO203" s="17"/>
-      <c r="BR203" s="17"/>
+      <c r="D203" s="13"/>
+      <c r="E203" s="12"/>
+      <c r="BO203" s="16"/>
+      <c r="BR203" s="16"/>
     </row>
     <row r="204" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D204" s="14"/>
-      <c r="E204" s="13"/>
-      <c r="BO204" s="17"/>
-      <c r="BR204" s="17"/>
+      <c r="D204" s="13"/>
+      <c r="E204" s="12"/>
+      <c r="BO204" s="16"/>
+      <c r="BR204" s="16"/>
     </row>
     <row r="205" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D205" s="14"/>
-      <c r="E205" s="13"/>
-      <c r="BO205" s="17"/>
-      <c r="BR205" s="17"/>
+      <c r="D205" s="13"/>
+      <c r="E205" s="12"/>
+      <c r="BO205" s="16"/>
+      <c r="BR205" s="16"/>
     </row>
     <row r="206" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D206" s="14"/>
-      <c r="E206" s="13"/>
-      <c r="BO206" s="17"/>
-      <c r="BR206" s="17"/>
+      <c r="D206" s="13"/>
+      <c r="E206" s="12"/>
+      <c r="BO206" s="16"/>
+      <c r="BR206" s="16"/>
     </row>
     <row r="207" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D207" s="14"/>
-      <c r="E207" s="13"/>
-      <c r="BO207" s="17"/>
-      <c r="BR207" s="17"/>
+      <c r="D207" s="13"/>
+      <c r="E207" s="12"/>
+      <c r="BO207" s="16"/>
+      <c r="BR207" s="16"/>
     </row>
     <row r="208" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D208" s="14"/>
-      <c r="E208" s="13"/>
-      <c r="BO208" s="17"/>
-      <c r="BR208" s="17"/>
+      <c r="D208" s="13"/>
+      <c r="E208" s="12"/>
+      <c r="BO208" s="16"/>
+      <c r="BR208" s="16"/>
     </row>
     <row r="209" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D209" s="14"/>
-      <c r="E209" s="13"/>
-      <c r="BO209" s="17"/>
-      <c r="BR209" s="17"/>
+      <c r="D209" s="13"/>
+      <c r="E209" s="12"/>
+      <c r="BO209" s="16"/>
+      <c r="BR209" s="16"/>
     </row>
     <row r="210" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D210" s="14"/>
-      <c r="E210" s="13"/>
-      <c r="BO210" s="17"/>
-      <c r="BR210" s="17"/>
+      <c r="D210" s="13"/>
+      <c r="E210" s="12"/>
+      <c r="BO210" s="16"/>
+      <c r="BR210" s="16"/>
     </row>
     <row r="211" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D211" s="14"/>
-      <c r="E211" s="13"/>
-      <c r="BO211" s="17"/>
-      <c r="BR211" s="17"/>
+      <c r="D211" s="13"/>
+      <c r="E211" s="12"/>
+      <c r="BO211" s="16"/>
+      <c r="BR211" s="16"/>
     </row>
     <row r="212" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D212" s="14"/>
-      <c r="E212" s="13"/>
-      <c r="BO212" s="17"/>
-      <c r="BR212" s="17"/>
+      <c r="D212" s="13"/>
+      <c r="E212" s="12"/>
+      <c r="BO212" s="16"/>
+      <c r="BR212" s="16"/>
     </row>
     <row r="213" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D213" s="14"/>
-      <c r="E213" s="13"/>
-      <c r="BO213" s="17"/>
-      <c r="BR213" s="17"/>
+      <c r="D213" s="13"/>
+      <c r="E213" s="12"/>
+      <c r="BO213" s="16"/>
+      <c r="BR213" s="16"/>
     </row>
     <row r="214" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D214" s="14"/>
-      <c r="E214" s="13"/>
-      <c r="BO214" s="17"/>
-      <c r="BR214" s="17"/>
+      <c r="D214" s="13"/>
+      <c r="E214" s="12"/>
+      <c r="BO214" s="16"/>
+      <c r="BR214" s="16"/>
     </row>
     <row r="215" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D215" s="14"/>
-      <c r="E215" s="13"/>
-      <c r="BO215" s="17"/>
-      <c r="BR215" s="17"/>
+      <c r="D215" s="13"/>
+      <c r="E215" s="12"/>
+      <c r="BO215" s="16"/>
+      <c r="BR215" s="16"/>
     </row>
     <row r="216" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D216" s="14"/>
-      <c r="E216" s="13"/>
-      <c r="BO216" s="17"/>
-      <c r="BR216" s="17"/>
+      <c r="D216" s="13"/>
+      <c r="E216" s="12"/>
+      <c r="BO216" s="16"/>
+      <c r="BR216" s="16"/>
     </row>
     <row r="217" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D217" s="14"/>
-      <c r="E217" s="13"/>
-      <c r="BO217" s="17"/>
-      <c r="BR217" s="17"/>
+      <c r="D217" s="13"/>
+      <c r="E217" s="12"/>
+      <c r="BO217" s="16"/>
+      <c r="BR217" s="16"/>
     </row>
     <row r="218" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D218" s="14"/>
-      <c r="E218" s="13"/>
-      <c r="BO218" s="17"/>
-      <c r="BR218" s="17"/>
+      <c r="D218" s="13"/>
+      <c r="E218" s="12"/>
+      <c r="BO218" s="16"/>
+      <c r="BR218" s="16"/>
     </row>
     <row r="219" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D219" s="14"/>
-      <c r="E219" s="13"/>
-      <c r="BO219" s="17"/>
-      <c r="BR219" s="17"/>
+      <c r="D219" s="13"/>
+      <c r="E219" s="12"/>
+      <c r="BO219" s="16"/>
+      <c r="BR219" s="16"/>
     </row>
     <row r="220" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D220" s="14"/>
-      <c r="E220" s="13"/>
-      <c r="BO220" s="17"/>
-      <c r="BR220" s="17"/>
+      <c r="D220" s="13"/>
+      <c r="E220" s="12"/>
+      <c r="BO220" s="16"/>
+      <c r="BR220" s="16"/>
     </row>
     <row r="221" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D221" s="14"/>
-      <c r="E221" s="13"/>
-      <c r="BO221" s="17"/>
-      <c r="BR221" s="17"/>
+      <c r="D221" s="13"/>
+      <c r="E221" s="12"/>
+      <c r="BO221" s="16"/>
+      <c r="BR221" s="16"/>
     </row>
     <row r="222" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D222" s="14"/>
-      <c r="E222" s="13"/>
-      <c r="BO222" s="17"/>
-      <c r="BR222" s="17"/>
+      <c r="D222" s="13"/>
+      <c r="E222" s="12"/>
+      <c r="BO222" s="16"/>
+      <c r="BR222" s="16"/>
     </row>
     <row r="223" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D223" s="14"/>
-      <c r="E223" s="13"/>
-      <c r="BO223" s="17"/>
-      <c r="BR223" s="17"/>
+      <c r="D223" s="13"/>
+      <c r="E223" s="12"/>
+      <c r="BO223" s="16"/>
+      <c r="BR223" s="16"/>
     </row>
     <row r="224" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D224" s="14"/>
-      <c r="E224" s="13"/>
-      <c r="BO224" s="17"/>
-      <c r="BR224" s="17"/>
+      <c r="D224" s="13"/>
+      <c r="E224" s="12"/>
+      <c r="BO224" s="16"/>
+      <c r="BR224" s="16"/>
     </row>
     <row r="225" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D225" s="14"/>
-      <c r="E225" s="13"/>
-      <c r="BO225" s="17"/>
-      <c r="BR225" s="17"/>
+      <c r="D225" s="13"/>
+      <c r="E225" s="12"/>
+      <c r="BO225" s="16"/>
+      <c r="BR225" s="16"/>
     </row>
     <row r="226" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D226" s="14"/>
-      <c r="E226" s="13"/>
-      <c r="BO226" s="17"/>
-      <c r="BR226" s="17"/>
+      <c r="D226" s="13"/>
+      <c r="E226" s="12"/>
+      <c r="BO226" s="16"/>
+      <c r="BR226" s="16"/>
     </row>
     <row r="227" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D227" s="14"/>
-      <c r="E227" s="13"/>
-      <c r="BO227" s="17"/>
-      <c r="BR227" s="17"/>
+      <c r="D227" s="13"/>
+      <c r="E227" s="12"/>
+      <c r="BO227" s="16"/>
+      <c r="BR227" s="16"/>
     </row>
     <row r="228" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D228" s="14"/>
-      <c r="E228" s="13"/>
-      <c r="BO228" s="17"/>
-      <c r="BR228" s="17"/>
+      <c r="D228" s="13"/>
+      <c r="E228" s="12"/>
+      <c r="BO228" s="16"/>
+      <c r="BR228" s="16"/>
     </row>
     <row r="229" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D229" s="14"/>
-      <c r="E229" s="13"/>
-      <c r="BO229" s="17"/>
-      <c r="BR229" s="17"/>
+      <c r="D229" s="13"/>
+      <c r="E229" s="12"/>
+      <c r="BO229" s="16"/>
+      <c r="BR229" s="16"/>
     </row>
     <row r="230" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D230" s="14"/>
-      <c r="E230" s="13"/>
-      <c r="BO230" s="17"/>
-      <c r="BR230" s="17"/>
+      <c r="D230" s="13"/>
+      <c r="E230" s="12"/>
+      <c r="BO230" s="16"/>
+      <c r="BR230" s="16"/>
     </row>
     <row r="231" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D231" s="14"/>
-      <c r="E231" s="13"/>
-      <c r="BO231" s="17"/>
-      <c r="BR231" s="17"/>
+      <c r="D231" s="13"/>
+      <c r="E231" s="12"/>
+      <c r="BO231" s="16"/>
+      <c r="BR231" s="16"/>
     </row>
     <row r="232" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D232" s="14"/>
-      <c r="E232" s="13"/>
-      <c r="BO232" s="17"/>
-      <c r="BR232" s="17"/>
+      <c r="D232" s="13"/>
+      <c r="E232" s="12"/>
+      <c r="BO232" s="16"/>
+      <c r="BR232" s="16"/>
     </row>
     <row r="233" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D233" s="14"/>
-      <c r="E233" s="13"/>
-      <c r="BO233" s="17"/>
-      <c r="BR233" s="17"/>
+      <c r="D233" s="13"/>
+      <c r="E233" s="12"/>
+      <c r="BO233" s="16"/>
+      <c r="BR233" s="16"/>
     </row>
     <row r="234" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D234" s="14"/>
-      <c r="E234" s="13"/>
-      <c r="BO234" s="17"/>
-      <c r="BR234" s="17"/>
+      <c r="D234" s="13"/>
+      <c r="E234" s="12"/>
+      <c r="BO234" s="16"/>
+      <c r="BR234" s="16"/>
     </row>
     <row r="235" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D235" s="14"/>
-      <c r="E235" s="13"/>
-      <c r="BO235" s="17"/>
-      <c r="BR235" s="17"/>
+      <c r="D235" s="13"/>
+      <c r="E235" s="12"/>
+      <c r="BO235" s="16"/>
+      <c r="BR235" s="16"/>
     </row>
     <row r="236" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D236" s="14"/>
-      <c r="E236" s="13"/>
-      <c r="BO236" s="17"/>
-      <c r="BR236" s="17"/>
+      <c r="D236" s="13"/>
+      <c r="E236" s="12"/>
+      <c r="BO236" s="16"/>
+      <c r="BR236" s="16"/>
     </row>
     <row r="237" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D237" s="14"/>
-      <c r="E237" s="13"/>
-      <c r="BO237" s="17"/>
-      <c r="BR237" s="17"/>
+      <c r="D237" s="13"/>
+      <c r="E237" s="12"/>
+      <c r="BO237" s="16"/>
+      <c r="BR237" s="16"/>
     </row>
     <row r="238" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D238" s="14"/>
-      <c r="E238" s="13"/>
-      <c r="BO238" s="17"/>
-      <c r="BR238" s="17"/>
+      <c r="D238" s="13"/>
+      <c r="E238" s="12"/>
+      <c r="BO238" s="16"/>
+      <c r="BR238" s="16"/>
     </row>
     <row r="239" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D239" s="14"/>
-      <c r="E239" s="13"/>
-      <c r="BO239" s="17"/>
-      <c r="BR239" s="17"/>
+      <c r="D239" s="13"/>
+      <c r="E239" s="12"/>
+      <c r="BO239" s="16"/>
+      <c r="BR239" s="16"/>
     </row>
     <row r="240" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D240" s="14"/>
-      <c r="E240" s="13"/>
-      <c r="BO240" s="17"/>
-      <c r="BR240" s="17"/>
+      <c r="D240" s="13"/>
+      <c r="E240" s="12"/>
+      <c r="BO240" s="16"/>
+      <c r="BR240" s="16"/>
     </row>
     <row r="241" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D241" s="14"/>
-      <c r="E241" s="13"/>
-      <c r="BO241" s="17"/>
-      <c r="BR241" s="17"/>
+      <c r="D241" s="13"/>
+      <c r="E241" s="12"/>
+      <c r="BO241" s="16"/>
+      <c r="BR241" s="16"/>
     </row>
     <row r="242" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D242" s="14"/>
-      <c r="E242" s="13"/>
-      <c r="BO242" s="17"/>
-      <c r="BR242" s="17"/>
+      <c r="D242" s="13"/>
+      <c r="E242" s="12"/>
+      <c r="BO242" s="16"/>
+      <c r="BR242" s="16"/>
     </row>
     <row r="243" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D243" s="14"/>
-      <c r="E243" s="13"/>
-      <c r="BR243" s="17"/>
+      <c r="D243" s="13"/>
+      <c r="E243" s="12"/>
+      <c r="BR243" s="16"/>
     </row>
     <row r="244" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D244" s="14"/>
-      <c r="E244" s="13"/>
-      <c r="BO244" s="17"/>
-      <c r="BR244" s="17"/>
+      <c r="D244" s="13"/>
+      <c r="E244" s="12"/>
+      <c r="BO244" s="16"/>
+      <c r="BR244" s="16"/>
     </row>
     <row r="245" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D245" s="14"/>
-      <c r="E245" s="13"/>
-      <c r="BO245" s="17"/>
-      <c r="BR245" s="17"/>
+      <c r="D245" s="13"/>
+      <c r="E245" s="12"/>
+      <c r="BO245" s="16"/>
+      <c r="BR245" s="16"/>
     </row>
     <row r="246" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D246" s="14"/>
-      <c r="E246" s="13"/>
-      <c r="BO246" s="17"/>
-      <c r="BR246" s="17"/>
+      <c r="D246" s="13"/>
+      <c r="E246" s="12"/>
+      <c r="BO246" s="16"/>
+      <c r="BR246" s="16"/>
     </row>
     <row r="247" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D247" s="14"/>
-      <c r="E247" s="13"/>
-      <c r="BO247" s="17"/>
-      <c r="BR247" s="17"/>
+      <c r="D247" s="13"/>
+      <c r="E247" s="12"/>
+      <c r="BO247" s="16"/>
+      <c r="BR247" s="16"/>
     </row>
     <row r="248" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D248" s="14"/>
-      <c r="E248" s="13"/>
-      <c r="BO248" s="17"/>
-      <c r="BR248" s="17"/>
+      <c r="D248" s="13"/>
+      <c r="E248" s="12"/>
+      <c r="BO248" s="16"/>
+      <c r="BR248" s="16"/>
     </row>
     <row r="249" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D249" s="14"/>
-      <c r="E249" s="13"/>
-      <c r="BO249" s="17"/>
-      <c r="BR249" s="17"/>
+      <c r="D249" s="13"/>
+      <c r="E249" s="12"/>
+      <c r="BO249" s="16"/>
+      <c r="BR249" s="16"/>
     </row>
     <row r="250" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D250" s="14"/>
-      <c r="E250" s="13"/>
-      <c r="BO250" s="17"/>
-      <c r="BR250" s="17"/>
+      <c r="D250" s="13"/>
+      <c r="E250" s="12"/>
+      <c r="BO250" s="16"/>
+      <c r="BR250" s="16"/>
     </row>
     <row r="251" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D251" s="14"/>
-      <c r="E251" s="13"/>
-      <c r="BO251" s="17"/>
-      <c r="BR251" s="17"/>
+      <c r="D251" s="13"/>
+      <c r="E251" s="12"/>
+      <c r="BO251" s="16"/>
+      <c r="BR251" s="16"/>
     </row>
     <row r="252" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D252" s="14"/>
-      <c r="E252" s="13"/>
-      <c r="BO252" s="17"/>
-      <c r="BR252" s="17"/>
+      <c r="D252" s="13"/>
+      <c r="E252" s="12"/>
+      <c r="BO252" s="16"/>
+      <c r="BR252" s="16"/>
     </row>
     <row r="253" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D253" s="14"/>
-      <c r="E253" s="13"/>
-      <c r="BO253" s="17"/>
-      <c r="BR253" s="17"/>
+      <c r="D253" s="13"/>
+      <c r="E253" s="12"/>
+      <c r="BO253" s="16"/>
+      <c r="BR253" s="16"/>
     </row>
     <row r="254" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D254" s="14"/>
-      <c r="E254" s="13"/>
-      <c r="BO254" s="17"/>
-      <c r="BR254" s="17"/>
+      <c r="D254" s="13"/>
+      <c r="E254" s="12"/>
+      <c r="BO254" s="16"/>
+      <c r="BR254" s="16"/>
     </row>
     <row r="255" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D255" s="14"/>
-      <c r="E255" s="13"/>
-      <c r="BO255" s="17"/>
-      <c r="BR255" s="17"/>
+      <c r="D255" s="13"/>
+      <c r="E255" s="12"/>
+      <c r="BO255" s="16"/>
+      <c r="BR255" s="16"/>
     </row>
     <row r="256" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D256" s="14"/>
-      <c r="E256" s="13"/>
-      <c r="BO256" s="17"/>
-      <c r="BR256" s="17"/>
+      <c r="D256" s="13"/>
+      <c r="E256" s="12"/>
+      <c r="BO256" s="16"/>
+      <c r="BR256" s="16"/>
     </row>
     <row r="257" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D257" s="14"/>
-      <c r="E257" s="13"/>
-      <c r="BO257" s="17"/>
-      <c r="BR257" s="17"/>
+      <c r="D257" s="13"/>
+      <c r="E257" s="12"/>
+      <c r="BO257" s="16"/>
+      <c r="BR257" s="16"/>
     </row>
     <row r="258" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D258" s="14"/>
-      <c r="E258" s="13"/>
-      <c r="BO258" s="17"/>
-      <c r="BR258" s="17"/>
+      <c r="D258" s="13"/>
+      <c r="E258" s="12"/>
+      <c r="BO258" s="16"/>
+      <c r="BR258" s="16"/>
     </row>
     <row r="259" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D259" s="14"/>
-      <c r="E259" s="13"/>
-      <c r="BO259" s="17"/>
-      <c r="BR259" s="17"/>
+      <c r="D259" s="13"/>
+      <c r="E259" s="12"/>
+      <c r="BO259" s="16"/>
+      <c r="BR259" s="16"/>
     </row>
     <row r="260" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D260" s="14"/>
-      <c r="E260" s="13"/>
-      <c r="BO260" s="17"/>
-      <c r="BR260" s="17"/>
+      <c r="D260" s="13"/>
+      <c r="E260" s="12"/>
+      <c r="BO260" s="16"/>
+      <c r="BR260" s="16"/>
     </row>
     <row r="261" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D261" s="14"/>
-      <c r="E261" s="13"/>
-      <c r="BO261" s="17"/>
-      <c r="BR261" s="17"/>
+      <c r="D261" s="13"/>
+      <c r="E261" s="12"/>
+      <c r="BO261" s="16"/>
+      <c r="BR261" s="16"/>
     </row>
     <row r="262" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D262" s="14"/>
-      <c r="E262" s="13"/>
-      <c r="BO262" s="17"/>
-      <c r="BR262" s="17"/>
+      <c r="D262" s="13"/>
+      <c r="E262" s="12"/>
+      <c r="BO262" s="16"/>
+      <c r="BR262" s="16"/>
     </row>
     <row r="263" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D263" s="14"/>
-      <c r="E263" s="13"/>
-      <c r="BO263" s="17"/>
-      <c r="BR263" s="17"/>
+      <c r="D263" s="13"/>
+      <c r="E263" s="12"/>
+      <c r="BO263" s="16"/>
+      <c r="BR263" s="16"/>
     </row>
     <row r="264" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D264" s="14"/>
-      <c r="E264" s="13"/>
-      <c r="BO264" s="17"/>
-      <c r="BR264" s="17"/>
+      <c r="D264" s="13"/>
+      <c r="E264" s="12"/>
+      <c r="BO264" s="16"/>
+      <c r="BR264" s="16"/>
     </row>
     <row r="265" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D265" s="14"/>
-      <c r="E265" s="13"/>
-      <c r="BO265" s="17"/>
-      <c r="BR265" s="17"/>
+      <c r="D265" s="13"/>
+      <c r="E265" s="12"/>
+      <c r="BO265" s="16"/>
+      <c r="BR265" s="16"/>
     </row>
     <row r="266" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D266" s="14"/>
-      <c r="E266" s="13"/>
-      <c r="BO266" s="17"/>
-      <c r="BR266" s="17"/>
+      <c r="D266" s="13"/>
+      <c r="E266" s="12"/>
+      <c r="BO266" s="16"/>
+      <c r="BR266" s="16"/>
     </row>
     <row r="267" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D267" s="14"/>
-      <c r="E267" s="13"/>
-      <c r="BO267" s="17"/>
-      <c r="BR267" s="17"/>
+      <c r="D267" s="13"/>
+      <c r="E267" s="12"/>
+      <c r="BO267" s="16"/>
+      <c r="BR267" s="16"/>
     </row>
     <row r="268" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D268" s="14"/>
-      <c r="E268" s="13"/>
-      <c r="BO268" s="17"/>
-      <c r="BR268" s="17"/>
+      <c r="D268" s="13"/>
+      <c r="E268" s="12"/>
+      <c r="BO268" s="16"/>
+      <c r="BR268" s="16"/>
     </row>
     <row r="269" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D269" s="14"/>
-      <c r="E269" s="13"/>
-      <c r="BO269" s="17"/>
-      <c r="BR269" s="17"/>
+      <c r="D269" s="13"/>
+      <c r="E269" s="12"/>
+      <c r="BO269" s="16"/>
+      <c r="BR269" s="16"/>
     </row>
     <row r="270" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D270" s="14"/>
-      <c r="E270" s="13"/>
-      <c r="BO270" s="17"/>
-      <c r="BR270" s="17"/>
+      <c r="D270" s="13"/>
+      <c r="E270" s="12"/>
+      <c r="BO270" s="16"/>
+      <c r="BR270" s="16"/>
     </row>
     <row r="271" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D271" s="14"/>
-      <c r="E271" s="13"/>
-      <c r="BO271" s="17"/>
-      <c r="BR271" s="17"/>
+      <c r="D271" s="13"/>
+      <c r="E271" s="12"/>
+      <c r="BO271" s="16"/>
+      <c r="BR271" s="16"/>
     </row>
     <row r="272" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D272" s="14"/>
-      <c r="E272" s="13"/>
-      <c r="BO272" s="17"/>
-      <c r="BR272" s="17"/>
+      <c r="D272" s="13"/>
+      <c r="E272" s="12"/>
+      <c r="BO272" s="16"/>
+      <c r="BR272" s="16"/>
     </row>
     <row r="273" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D273" s="14"/>
-      <c r="E273" s="13"/>
-      <c r="BO273" s="17"/>
-      <c r="BR273" s="17"/>
+      <c r="D273" s="13"/>
+      <c r="E273" s="12"/>
+      <c r="BO273" s="16"/>
+      <c r="BR273" s="16"/>
     </row>
     <row r="274" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D274" s="14"/>
-      <c r="E274" s="13"/>
-      <c r="BO274" s="17"/>
-      <c r="BR274" s="17"/>
+      <c r="D274" s="13"/>
+      <c r="E274" s="12"/>
+      <c r="BO274" s="16"/>
+      <c r="BR274" s="16"/>
     </row>
     <row r="275" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D275" s="14"/>
-      <c r="E275" s="13"/>
-      <c r="BO275" s="17"/>
-      <c r="BR275" s="17"/>
+      <c r="D275" s="13"/>
+      <c r="E275" s="12"/>
+      <c r="BO275" s="16"/>
+      <c r="BR275" s="16"/>
     </row>
     <row r="276" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D276" s="14"/>
-      <c r="E276" s="13"/>
-      <c r="BO276" s="17"/>
-      <c r="BR276" s="17"/>
+      <c r="D276" s="13"/>
+      <c r="E276" s="12"/>
+      <c r="BO276" s="16"/>
+      <c r="BR276" s="16"/>
     </row>
     <row r="277" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D277" s="14"/>
-      <c r="E277" s="13"/>
-      <c r="BO277" s="17"/>
-      <c r="BR277" s="17"/>
+      <c r="D277" s="13"/>
+      <c r="E277" s="12"/>
+      <c r="BO277" s="16"/>
+      <c r="BR277" s="16"/>
     </row>
     <row r="278" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D278" s="14"/>
-      <c r="E278" s="13"/>
-      <c r="BO278" s="17"/>
-      <c r="BR278" s="17"/>
+      <c r="D278" s="13"/>
+      <c r="E278" s="12"/>
+      <c r="BO278" s="16"/>
+      <c r="BR278" s="16"/>
     </row>
     <row r="279" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D279" s="14"/>
-      <c r="E279" s="13"/>
-      <c r="BO279" s="17"/>
-      <c r="BR279" s="17"/>
+      <c r="D279" s="13"/>
+      <c r="E279" s="12"/>
+      <c r="BO279" s="16"/>
+      <c r="BR279" s="16"/>
     </row>
     <row r="280" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D280" s="14"/>
-      <c r="E280" s="13"/>
-      <c r="BO280" s="17"/>
-      <c r="BR280" s="17"/>
+      <c r="D280" s="13"/>
+      <c r="E280" s="12"/>
+      <c r="BO280" s="16"/>
+      <c r="BR280" s="16"/>
     </row>
     <row r="281" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D281" s="14"/>
-      <c r="E281" s="13"/>
-      <c r="BO281" s="17"/>
-      <c r="BR281" s="17"/>
+      <c r="D281" s="13"/>
+      <c r="E281" s="12"/>
+      <c r="BO281" s="16"/>
+      <c r="BR281" s="16"/>
     </row>
     <row r="282" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D282" s="14"/>
-      <c r="E282" s="13"/>
-      <c r="BO282" s="17"/>
-      <c r="BR282" s="17"/>
+      <c r="D282" s="13"/>
+      <c r="E282" s="12"/>
+      <c r="BO282" s="16"/>
+      <c r="BR282" s="16"/>
     </row>
     <row r="283" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D283" s="14"/>
-      <c r="E283" s="13"/>
-      <c r="BO283" s="17"/>
-      <c r="BR283" s="17"/>
+      <c r="D283" s="13"/>
+      <c r="E283" s="12"/>
+      <c r="BO283" s="16"/>
+      <c r="BR283" s="16"/>
     </row>
     <row r="284" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D284" s="14"/>
-      <c r="E284" s="13"/>
-      <c r="BO284" s="17"/>
-      <c r="BR284" s="17"/>
+      <c r="D284" s="13"/>
+      <c r="E284" s="12"/>
+      <c r="BO284" s="16"/>
+      <c r="BR284" s="16"/>
     </row>
     <row r="285" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D285" s="14"/>
-      <c r="E285" s="13"/>
-      <c r="BO285" s="17"/>
-      <c r="BR285" s="17"/>
+      <c r="D285" s="13"/>
+      <c r="E285" s="12"/>
+      <c r="BO285" s="16"/>
+      <c r="BR285" s="16"/>
     </row>
     <row r="286" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D286" s="14"/>
-      <c r="E286" s="13"/>
-      <c r="BR286" s="17"/>
+      <c r="D286" s="13"/>
+      <c r="E286" s="12"/>
+      <c r="BR286" s="16"/>
     </row>
     <row r="287" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D287" s="14"/>
-      <c r="E287" s="13"/>
-      <c r="BO287" s="17"/>
-      <c r="BR287" s="17"/>
+      <c r="D287" s="13"/>
+      <c r="E287" s="12"/>
+      <c r="BO287" s="16"/>
+      <c r="BR287" s="16"/>
     </row>
     <row r="288" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D288" s="14"/>
-      <c r="E288" s="13"/>
-      <c r="BO288" s="17"/>
-      <c r="BR288" s="17"/>
+      <c r="D288" s="13"/>
+      <c r="E288" s="12"/>
+      <c r="BO288" s="16"/>
+      <c r="BR288" s="16"/>
     </row>
     <row r="289" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D289" s="14"/>
-      <c r="E289" s="13"/>
-      <c r="BO289" s="17"/>
-      <c r="BR289" s="17"/>
+      <c r="D289" s="13"/>
+      <c r="E289" s="12"/>
+      <c r="BO289" s="16"/>
+      <c r="BR289" s="16"/>
     </row>
     <row r="290" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D290" s="14"/>
-      <c r="E290" s="13"/>
-      <c r="BO290" s="17"/>
-      <c r="BR290" s="17"/>
+      <c r="D290" s="13"/>
+      <c r="E290" s="12"/>
+      <c r="BO290" s="16"/>
+      <c r="BR290" s="16"/>
     </row>
     <row r="291" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D291" s="14"/>
-      <c r="E291" s="13"/>
-      <c r="BO291" s="17"/>
-      <c r="BR291" s="17"/>
+      <c r="D291" s="13"/>
+      <c r="E291" s="12"/>
+      <c r="BO291" s="16"/>
+      <c r="BR291" s="16"/>
     </row>
     <row r="292" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D292" s="14"/>
-      <c r="E292" s="13"/>
-      <c r="BO292" s="17"/>
-      <c r="BR292" s="17"/>
+      <c r="D292" s="13"/>
+      <c r="E292" s="12"/>
+      <c r="BO292" s="16"/>
+      <c r="BR292" s="16"/>
     </row>
     <row r="293" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D293" s="14"/>
-      <c r="E293" s="13"/>
-      <c r="BO293" s="17"/>
-      <c r="BR293" s="17"/>
+      <c r="D293" s="13"/>
+      <c r="E293" s="12"/>
+      <c r="BO293" s="16"/>
+      <c r="BR293" s="16"/>
     </row>
     <row r="294" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D294" s="14"/>
-      <c r="E294" s="13"/>
-      <c r="BO294" s="17"/>
-      <c r="BR294" s="17"/>
+      <c r="D294" s="13"/>
+      <c r="E294" s="12"/>
+      <c r="BO294" s="16"/>
+      <c r="BR294" s="16"/>
     </row>
     <row r="295" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D295" s="14"/>
-      <c r="E295" s="13"/>
-      <c r="BO295" s="17"/>
-      <c r="BR295" s="17"/>
+      <c r="D295" s="13"/>
+      <c r="E295" s="12"/>
+      <c r="BO295" s="16"/>
+      <c r="BR295" s="16"/>
     </row>
     <row r="296" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D296" s="14"/>
-      <c r="E296" s="13"/>
-      <c r="BO296" s="17"/>
-      <c r="BR296" s="17"/>
+      <c r="D296" s="13"/>
+      <c r="E296" s="12"/>
+      <c r="BO296" s="16"/>
+      <c r="BR296" s="16"/>
     </row>
     <row r="297" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D297" s="14"/>
-      <c r="E297" s="13"/>
-      <c r="BO297" s="17"/>
-      <c r="BR297" s="17"/>
+      <c r="D297" s="13"/>
+      <c r="E297" s="12"/>
+      <c r="BO297" s="16"/>
+      <c r="BR297" s="16"/>
     </row>
     <row r="298" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D298" s="14"/>
-      <c r="E298" s="13"/>
-      <c r="BO298" s="17"/>
-      <c r="BR298" s="17"/>
+      <c r="D298" s="13"/>
+      <c r="E298" s="12"/>
+      <c r="BO298" s="16"/>
+      <c r="BR298" s="16"/>
     </row>
     <row r="299" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D299" s="14"/>
-      <c r="E299" s="13"/>
-      <c r="BO299" s="17"/>
-      <c r="BR299" s="17"/>
+      <c r="D299" s="13"/>
+      <c r="E299" s="12"/>
+      <c r="BO299" s="16"/>
+      <c r="BR299" s="16"/>
     </row>
     <row r="300" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D300" s="14"/>
-      <c r="E300" s="13"/>
-      <c r="BO300" s="17"/>
-      <c r="BR300" s="17"/>
+      <c r="D300" s="13"/>
+      <c r="E300" s="12"/>
+      <c r="BO300" s="16"/>
+      <c r="BR300" s="16"/>
     </row>
     <row r="301" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D301" s="14"/>
-      <c r="E301" s="13"/>
-      <c r="BO301" s="17"/>
-      <c r="BR301" s="17"/>
+      <c r="D301" s="13"/>
+      <c r="E301" s="12"/>
+      <c r="BO301" s="16"/>
+      <c r="BR301" s="16"/>
     </row>
     <row r="302" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D302" s="14"/>
-      <c r="E302" s="13"/>
-      <c r="BO302" s="17"/>
-      <c r="BR302" s="17"/>
+      <c r="D302" s="13"/>
+      <c r="E302" s="12"/>
+      <c r="BO302" s="16"/>
+      <c r="BR302" s="16"/>
     </row>
     <row r="303" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D303" s="14"/>
-      <c r="E303" s="13"/>
-      <c r="BO303" s="17"/>
-      <c r="BR303" s="17"/>
+      <c r="D303" s="13"/>
+      <c r="E303" s="12"/>
+      <c r="BO303" s="16"/>
+      <c r="BR303" s="16"/>
     </row>
     <row r="304" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D304" s="14"/>
-      <c r="E304" s="13"/>
-      <c r="BO304" s="17"/>
-      <c r="BR304" s="17"/>
+      <c r="D304" s="13"/>
+      <c r="E304" s="12"/>
+      <c r="BO304" s="16"/>
+      <c r="BR304" s="16"/>
     </row>
     <row r="305" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D305" s="14"/>
-      <c r="E305" s="13"/>
-      <c r="BO305" s="17"/>
-      <c r="BR305" s="17"/>
+      <c r="D305" s="13"/>
+      <c r="E305" s="12"/>
+      <c r="BO305" s="16"/>
+      <c r="BR305" s="16"/>
     </row>
     <row r="306" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D306" s="14"/>
-      <c r="E306" s="13"/>
-      <c r="BO306" s="17"/>
-      <c r="BR306" s="17"/>
+      <c r="D306" s="13"/>
+      <c r="E306" s="12"/>
+      <c r="BO306" s="16"/>
+      <c r="BR306" s="16"/>
     </row>
     <row r="307" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D307" s="14"/>
-      <c r="E307" s="13"/>
-      <c r="BO307" s="17"/>
-      <c r="BR307" s="17"/>
+      <c r="D307" s="13"/>
+      <c r="E307" s="12"/>
+      <c r="BO307" s="16"/>
+      <c r="BR307" s="16"/>
     </row>
     <row r="308" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D308" s="14"/>
-      <c r="E308" s="13"/>
-      <c r="BO308" s="17"/>
-      <c r="BR308" s="17"/>
+      <c r="D308" s="13"/>
+      <c r="E308" s="12"/>
+      <c r="BO308" s="16"/>
+      <c r="BR308" s="16"/>
     </row>
     <row r="309" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D309" s="14"/>
-      <c r="E309" s="13"/>
-      <c r="BO309" s="17"/>
-      <c r="BR309" s="17"/>
+      <c r="D309" s="13"/>
+      <c r="E309" s="12"/>
+      <c r="BO309" s="16"/>
+      <c r="BR309" s="16"/>
     </row>
     <row r="310" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D310" s="14"/>
-      <c r="E310" s="13"/>
-      <c r="BO310" s="17"/>
-      <c r="BR310" s="17"/>
+      <c r="D310" s="13"/>
+      <c r="E310" s="12"/>
+      <c r="BO310" s="16"/>
+      <c r="BR310" s="16"/>
     </row>
     <row r="311" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D311" s="14"/>
-      <c r="E311" s="13"/>
-      <c r="BO311" s="17"/>
-      <c r="BR311" s="17"/>
+      <c r="D311" s="13"/>
+      <c r="E311" s="12"/>
+      <c r="BO311" s="16"/>
+      <c r="BR311" s="16"/>
     </row>
     <row r="312" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D312" s="14"/>
-      <c r="E312" s="13"/>
-      <c r="BO312" s="17"/>
-      <c r="BR312" s="17"/>
+      <c r="D312" s="13"/>
+      <c r="E312" s="12"/>
+      <c r="BO312" s="16"/>
+      <c r="BR312" s="16"/>
     </row>
     <row r="313" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D313" s="14"/>
-      <c r="E313" s="13"/>
-      <c r="BO313" s="17"/>
-      <c r="BR313" s="17"/>
+      <c r="D313" s="13"/>
+      <c r="E313" s="12"/>
+      <c r="BO313" s="16"/>
+      <c r="BR313" s="16"/>
     </row>
     <row r="314" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D314" s="14"/>
-      <c r="E314" s="13"/>
-      <c r="BO314" s="17"/>
-      <c r="BR314" s="17"/>
+      <c r="D314" s="13"/>
+      <c r="E314" s="12"/>
+      <c r="BO314" s="16"/>
+      <c r="BR314" s="16"/>
     </row>
     <row r="315" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D315" s="14"/>
-      <c r="E315" s="13"/>
-      <c r="BO315" s="17"/>
-      <c r="BR315" s="17"/>
+      <c r="D315" s="13"/>
+      <c r="E315" s="12"/>
+      <c r="BO315" s="16"/>
+      <c r="BR315" s="16"/>
     </row>
     <row r="316" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D316" s="14"/>
-      <c r="E316" s="13"/>
-      <c r="BO316" s="17"/>
-      <c r="BR316" s="17"/>
+      <c r="D316" s="13"/>
+      <c r="E316" s="12"/>
+      <c r="BO316" s="16"/>
+      <c r="BR316" s="16"/>
     </row>
     <row r="317" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D317" s="14"/>
-      <c r="E317" s="13"/>
-      <c r="BO317" s="17"/>
-      <c r="BR317" s="17"/>
+      <c r="D317" s="13"/>
+      <c r="E317" s="12"/>
+      <c r="BO317" s="16"/>
+      <c r="BR317" s="16"/>
     </row>
     <row r="318" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D318" s="14"/>
-      <c r="E318" s="13"/>
-      <c r="BO318" s="17"/>
-      <c r="BR318" s="17"/>
+      <c r="D318" s="13"/>
+      <c r="E318" s="12"/>
+      <c r="BO318" s="16"/>
+      <c r="BR318" s="16"/>
     </row>
     <row r="319" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D319" s="14"/>
-      <c r="E319" s="13"/>
-      <c r="BO319" s="17"/>
-      <c r="BR319" s="17"/>
+      <c r="D319" s="13"/>
+      <c r="E319" s="12"/>
+      <c r="BO319" s="16"/>
+      <c r="BR319" s="16"/>
     </row>
     <row r="320" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D320" s="14"/>
-      <c r="E320" s="13"/>
-      <c r="BO320" s="17"/>
-      <c r="BR320" s="17"/>
+      <c r="D320" s="13"/>
+      <c r="E320" s="12"/>
+      <c r="BO320" s="16"/>
+      <c r="BR320" s="16"/>
     </row>
     <row r="321" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D321" s="14"/>
-      <c r="E321" s="13"/>
-      <c r="BO321" s="17"/>
-      <c r="BR321" s="17"/>
+      <c r="D321" s="13"/>
+      <c r="E321" s="12"/>
+      <c r="BO321" s="16"/>
+      <c r="BR321" s="16"/>
     </row>
     <row r="322" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D322" s="14"/>
-      <c r="E322" s="13"/>
-      <c r="BO322" s="17"/>
-      <c r="BR322" s="17"/>
+      <c r="D322" s="13"/>
+      <c r="E322" s="12"/>
+      <c r="BO322" s="16"/>
+      <c r="BR322" s="16"/>
     </row>
     <row r="323" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D323" s="14"/>
-      <c r="E323" s="13"/>
-      <c r="BO323" s="17"/>
-      <c r="BR323" s="17"/>
+      <c r="D323" s="13"/>
+      <c r="E323" s="12"/>
+      <c r="BO323" s="16"/>
+      <c r="BR323" s="16"/>
     </row>
     <row r="324" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D324" s="14"/>
-      <c r="E324" s="13"/>
-      <c r="BO324" s="17"/>
-      <c r="BR324" s="17"/>
+      <c r="D324" s="13"/>
+      <c r="E324" s="12"/>
+      <c r="BO324" s="16"/>
+      <c r="BR324" s="16"/>
     </row>
     <row r="325" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D325" s="14"/>
-      <c r="E325" s="13"/>
-      <c r="BO325" s="17"/>
-      <c r="BR325" s="17"/>
+      <c r="D325" s="13"/>
+      <c r="E325" s="12"/>
+      <c r="BO325" s="16"/>
+      <c r="BR325" s="16"/>
     </row>
     <row r="326" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D326" s="14"/>
-      <c r="E326" s="13"/>
-      <c r="BO326" s="17"/>
-      <c r="BR326" s="17"/>
+      <c r="D326" s="13"/>
+      <c r="E326" s="12"/>
+      <c r="BO326" s="16"/>
+      <c r="BR326" s="16"/>
     </row>
     <row r="327" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D327" s="14"/>
-      <c r="E327" s="13"/>
-      <c r="BO327" s="17"/>
-      <c r="BR327" s="17"/>
+      <c r="D327" s="13"/>
+      <c r="E327" s="12"/>
+      <c r="BO327" s="16"/>
+      <c r="BR327" s="16"/>
     </row>
     <row r="328" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D328" s="14"/>
-      <c r="E328" s="13"/>
-      <c r="BO328" s="17"/>
-      <c r="BR328" s="17"/>
+      <c r="D328" s="13"/>
+      <c r="E328" s="12"/>
+      <c r="BO328" s="16"/>
+      <c r="BR328" s="16"/>
     </row>
     <row r="329" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D329" s="14"/>
-      <c r="E329" s="13"/>
-      <c r="BO329" s="17"/>
-      <c r="BR329" s="17"/>
+      <c r="D329" s="13"/>
+      <c r="E329" s="12"/>
+      <c r="BO329" s="16"/>
+      <c r="BR329" s="16"/>
     </row>
     <row r="330" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D330" s="14"/>
-      <c r="E330" s="13"/>
-      <c r="BO330" s="17"/>
-      <c r="BR330" s="17"/>
+      <c r="D330" s="13"/>
+      <c r="E330" s="12"/>
+      <c r="BO330" s="16"/>
+      <c r="BR330" s="16"/>
     </row>
     <row r="331" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D331" s="14"/>
-      <c r="E331" s="13"/>
-      <c r="BO331" s="17"/>
-      <c r="BR331" s="17"/>
+      <c r="D331" s="13"/>
+      <c r="E331" s="12"/>
+      <c r="BO331" s="16"/>
+      <c r="BR331" s="16"/>
     </row>
     <row r="332" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D332" s="14"/>
-      <c r="E332" s="13"/>
-      <c r="BO332" s="17"/>
-      <c r="BR332" s="17"/>
+      <c r="D332" s="13"/>
+      <c r="E332" s="12"/>
+      <c r="BO332" s="16"/>
+      <c r="BR332" s="16"/>
     </row>
     <row r="333" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D333" s="14"/>
-      <c r="E333" s="13"/>
-      <c r="BO333" s="17"/>
-      <c r="BR333" s="17"/>
+      <c r="D333" s="13"/>
+      <c r="E333" s="12"/>
+      <c r="BO333" s="16"/>
+      <c r="BR333" s="16"/>
     </row>
     <row r="334" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D334" s="14"/>
-      <c r="E334" s="13"/>
-      <c r="BO334" s="17"/>
-      <c r="BR334" s="17"/>
+      <c r="D334" s="13"/>
+      <c r="E334" s="12"/>
+      <c r="BO334" s="16"/>
+      <c r="BR334" s="16"/>
     </row>
     <row r="335" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D335" s="14"/>
-      <c r="E335" s="13"/>
-      <c r="BO335" s="17"/>
-      <c r="BR335" s="17"/>
+      <c r="D335" s="13"/>
+      <c r="E335" s="12"/>
+      <c r="BO335" s="16"/>
+      <c r="BR335" s="16"/>
     </row>
     <row r="336" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D336" s="14"/>
-      <c r="E336" s="13"/>
-      <c r="BO336" s="17"/>
-      <c r="BR336" s="17"/>
+      <c r="D336" s="13"/>
+      <c r="E336" s="12"/>
+      <c r="BO336" s="16"/>
+      <c r="BR336" s="16"/>
     </row>
     <row r="337" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D337" s="14"/>
-      <c r="E337" s="13"/>
-      <c r="BO337" s="17"/>
-      <c r="BR337" s="17"/>
+      <c r="D337" s="13"/>
+      <c r="E337" s="12"/>
+      <c r="BO337" s="16"/>
+      <c r="BR337" s="16"/>
     </row>
     <row r="338" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D338" s="14"/>
-      <c r="E338" s="13"/>
-      <c r="BO338" s="17"/>
-      <c r="BR338" s="17"/>
+      <c r="D338" s="13"/>
+      <c r="E338" s="12"/>
+      <c r="BO338" s="16"/>
+      <c r="BR338" s="16"/>
     </row>
     <row r="339" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D339" s="14"/>
-      <c r="E339" s="13"/>
-      <c r="BO339" s="17"/>
-      <c r="BR339" s="17"/>
+      <c r="D339" s="13"/>
+      <c r="E339" s="12"/>
+      <c r="BO339" s="16"/>
+      <c r="BR339" s="16"/>
     </row>
     <row r="340" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D340" s="14"/>
-      <c r="E340" s="13"/>
-      <c r="BO340" s="17"/>
-      <c r="BR340" s="17"/>
+      <c r="D340" s="13"/>
+      <c r="E340" s="12"/>
+      <c r="BO340" s="16"/>
+      <c r="BR340" s="16"/>
     </row>
     <row r="341" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D341" s="14"/>
-      <c r="E341" s="13"/>
-      <c r="BO341" s="17"/>
-      <c r="BR341" s="17"/>
+      <c r="D341" s="13"/>
+      <c r="E341" s="12"/>
+      <c r="BO341" s="16"/>
+      <c r="BR341" s="16"/>
     </row>
     <row r="342" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D342" s="14"/>
-      <c r="E342" s="13"/>
-      <c r="BR342" s="17"/>
+      <c r="D342" s="13"/>
+      <c r="E342" s="12"/>
+      <c r="BR342" s="16"/>
     </row>
     <row r="343" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D343" s="14"/>
-      <c r="E343" s="13"/>
-      <c r="BR343" s="17"/>
+      <c r="D343" s="13"/>
+      <c r="E343" s="12"/>
+      <c r="BR343" s="16"/>
     </row>
     <row r="344" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D344" s="14"/>
-      <c r="E344" s="13"/>
-      <c r="BR344" s="17"/>
+      <c r="D344" s="13"/>
+      <c r="E344" s="12"/>
+      <c r="BR344" s="16"/>
     </row>
     <row r="345" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D345" s="14"/>
-      <c r="E345" s="13"/>
-      <c r="BO345" s="17"/>
-      <c r="BR345" s="17"/>
+      <c r="D345" s="13"/>
+      <c r="E345" s="12"/>
+      <c r="BO345" s="16"/>
+      <c r="BR345" s="16"/>
     </row>
     <row r="346" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D346" s="14"/>
-      <c r="E346" s="13"/>
-      <c r="BO346" s="17"/>
-      <c r="BR346" s="17"/>
+      <c r="D346" s="13"/>
+      <c r="E346" s="12"/>
+      <c r="BO346" s="16"/>
+      <c r="BR346" s="16"/>
     </row>
     <row r="347" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D347" s="14"/>
-      <c r="E347" s="13"/>
-      <c r="BO347" s="17"/>
-      <c r="BR347" s="17"/>
+      <c r="D347" s="13"/>
+      <c r="E347" s="12"/>
+      <c r="BO347" s="16"/>
+      <c r="BR347" s="16"/>
     </row>
     <row r="348" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D348" s="14"/>
-      <c r="E348" s="13"/>
-      <c r="BO348" s="17"/>
-      <c r="BR348" s="17"/>
+      <c r="D348" s="13"/>
+      <c r="E348" s="12"/>
+      <c r="BO348" s="16"/>
+      <c r="BR348" s="16"/>
     </row>
     <row r="349" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D349" s="14"/>
-      <c r="E349" s="13"/>
-      <c r="BO349" s="17"/>
-      <c r="BR349" s="17"/>
+      <c r="D349" s="13"/>
+      <c r="E349" s="12"/>
+      <c r="BO349" s="16"/>
+      <c r="BR349" s="16"/>
     </row>
     <row r="350" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D350" s="14"/>
-      <c r="E350" s="13"/>
-      <c r="BO350" s="17"/>
-      <c r="BR350" s="17"/>
+      <c r="D350" s="13"/>
+      <c r="E350" s="12"/>
+      <c r="BO350" s="16"/>
+      <c r="BR350" s="16"/>
     </row>
     <row r="351" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D351" s="14"/>
-      <c r="E351" s="13"/>
-      <c r="BO351" s="17"/>
-      <c r="BR351" s="17"/>
+      <c r="D351" s="13"/>
+      <c r="E351" s="12"/>
+      <c r="BO351" s="16"/>
+      <c r="BR351" s="16"/>
     </row>
     <row r="352" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D352" s="14"/>
-      <c r="E352" s="13"/>
-      <c r="BO352" s="17"/>
-      <c r="BR352" s="17"/>
+      <c r="D352" s="13"/>
+      <c r="E352" s="12"/>
+      <c r="BO352" s="16"/>
+      <c r="BR352" s="16"/>
     </row>
     <row r="353" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D353" s="14"/>
-      <c r="E353" s="13"/>
-      <c r="BO353" s="17"/>
-      <c r="BR353" s="17"/>
+      <c r="D353" s="13"/>
+      <c r="E353" s="12"/>
+      <c r="BO353" s="16"/>
+      <c r="BR353" s="16"/>
     </row>
     <row r="354" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D354" s="14"/>
-      <c r="E354" s="13"/>
-      <c r="BO354" s="17"/>
-      <c r="BR354" s="17"/>
+      <c r="D354" s="13"/>
+      <c r="E354" s="12"/>
+      <c r="BO354" s="16"/>
+      <c r="BR354" s="16"/>
     </row>
     <row r="355" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D355" s="14"/>
-      <c r="E355" s="13"/>
-      <c r="BO355" s="17"/>
-      <c r="BR355" s="17"/>
+      <c r="D355" s="13"/>
+      <c r="E355" s="12"/>
+      <c r="BO355" s="16"/>
+      <c r="BR355" s="16"/>
     </row>
     <row r="356" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D356" s="14"/>
-      <c r="E356" s="13"/>
-      <c r="BO356" s="17"/>
-      <c r="BR356" s="17"/>
+      <c r="D356" s="13"/>
+      <c r="E356" s="12"/>
+      <c r="BO356" s="16"/>
+      <c r="BR356" s="16"/>
     </row>
     <row r="357" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D357" s="14"/>
-      <c r="E357" s="13"/>
-      <c r="BO357" s="17"/>
-      <c r="BR357" s="17"/>
+      <c r="D357" s="13"/>
+      <c r="E357" s="12"/>
+      <c r="BO357" s="16"/>
+      <c r="BR357" s="16"/>
     </row>
     <row r="358" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D358" s="14"/>
-      <c r="E358" s="13"/>
-      <c r="BO358" s="17"/>
-      <c r="BR358" s="17"/>
+      <c r="D358" s="13"/>
+      <c r="E358" s="12"/>
+      <c r="BO358" s="16"/>
+      <c r="BR358" s="16"/>
     </row>
     <row r="359" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D359" s="14"/>
-      <c r="E359" s="13"/>
-      <c r="BO359" s="17"/>
-      <c r="BR359" s="17"/>
+      <c r="D359" s="13"/>
+      <c r="E359" s="12"/>
+      <c r="BO359" s="16"/>
+      <c r="BR359" s="16"/>
     </row>
     <row r="360" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D360" s="14"/>
-      <c r="E360" s="13"/>
-      <c r="BO360" s="17"/>
-      <c r="BR360" s="17"/>
+      <c r="D360" s="13"/>
+      <c r="E360" s="12"/>
+      <c r="BO360" s="16"/>
+      <c r="BR360" s="16"/>
     </row>
     <row r="361" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D361" s="14"/>
-      <c r="E361" s="13"/>
-      <c r="BO361" s="17"/>
-      <c r="BR361" s="17"/>
+      <c r="D361" s="13"/>
+      <c r="E361" s="12"/>
+      <c r="BO361" s="16"/>
+      <c r="BR361" s="16"/>
     </row>
     <row r="362" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D362" s="14"/>
-      <c r="E362" s="13"/>
-      <c r="BO362" s="17"/>
-      <c r="BR362" s="17"/>
+      <c r="D362" s="13"/>
+      <c r="E362" s="12"/>
+      <c r="BO362" s="16"/>
+      <c r="BR362" s="16"/>
     </row>
     <row r="363" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D363" s="14"/>
-      <c r="E363" s="13"/>
-      <c r="BO363" s="17"/>
-      <c r="BR363" s="17"/>
+      <c r="D363" s="13"/>
+      <c r="E363" s="12"/>
+      <c r="BO363" s="16"/>
+      <c r="BR363" s="16"/>
     </row>
     <row r="364" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D364" s="14"/>
-      <c r="E364" s="13"/>
-      <c r="BO364" s="17"/>
-      <c r="BR364" s="17"/>
+      <c r="D364" s="13"/>
+      <c r="E364" s="12"/>
+      <c r="BO364" s="16"/>
+      <c r="BR364" s="16"/>
     </row>
     <row r="365" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D365" s="14"/>
-      <c r="E365" s="13"/>
-      <c r="BO365" s="17"/>
-      <c r="BR365" s="17"/>
+      <c r="D365" s="13"/>
+      <c r="E365" s="12"/>
+      <c r="BO365" s="16"/>
+      <c r="BR365" s="16"/>
     </row>
     <row r="366" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D366" s="14"/>
-      <c r="E366" s="13"/>
-      <c r="BO366" s="17"/>
-      <c r="BR366" s="17"/>
+      <c r="D366" s="13"/>
+      <c r="E366" s="12"/>
+      <c r="BO366" s="16"/>
+      <c r="BR366" s="16"/>
     </row>
     <row r="367" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D367" s="14"/>
-      <c r="E367" s="13"/>
-      <c r="BO367" s="17"/>
-      <c r="BR367" s="17"/>
+      <c r="D367" s="13"/>
+      <c r="E367" s="12"/>
+      <c r="BO367" s="16"/>
+      <c r="BR367" s="16"/>
     </row>
     <row r="368" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D368" s="14"/>
-      <c r="E368" s="13"/>
-      <c r="BO368" s="17"/>
-      <c r="BR368" s="17"/>
+      <c r="D368" s="13"/>
+      <c r="E368" s="12"/>
+      <c r="BO368" s="16"/>
+      <c r="BR368" s="16"/>
     </row>
     <row r="369" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D369" s="14"/>
-      <c r="E369" s="13"/>
-      <c r="BO369" s="17"/>
-      <c r="BR369" s="17"/>
+      <c r="D369" s="13"/>
+      <c r="E369" s="12"/>
+      <c r="BO369" s="16"/>
+      <c r="BR369" s="16"/>
     </row>
     <row r="370" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D370" s="14"/>
-      <c r="E370" s="13"/>
-      <c r="BO370" s="17"/>
-      <c r="BR370" s="17"/>
+      <c r="D370" s="13"/>
+      <c r="E370" s="12"/>
+      <c r="BO370" s="16"/>
+      <c r="BR370" s="16"/>
     </row>
     <row r="371" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D371" s="14"/>
-      <c r="E371" s="13"/>
-      <c r="BO371" s="17"/>
-      <c r="BR371" s="17"/>
+      <c r="D371" s="13"/>
+      <c r="E371" s="12"/>
+      <c r="BO371" s="16"/>
+      <c r="BR371" s="16"/>
     </row>
     <row r="372" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D372" s="14"/>
-      <c r="E372" s="13"/>
-      <c r="BO372" s="17"/>
-      <c r="BR372" s="17"/>
+      <c r="D372" s="13"/>
+      <c r="E372" s="12"/>
+      <c r="BO372" s="16"/>
+      <c r="BR372" s="16"/>
     </row>
     <row r="373" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D373" s="14"/>
-      <c r="E373" s="13"/>
-      <c r="BO373" s="17"/>
-      <c r="BR373" s="17"/>
+      <c r="D373" s="13"/>
+      <c r="E373" s="12"/>
+      <c r="BO373" s="16"/>
+      <c r="BR373" s="16"/>
     </row>
     <row r="374" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D374" s="14"/>
-      <c r="E374" s="13"/>
-      <c r="BO374" s="17"/>
-      <c r="BR374" s="17"/>
+      <c r="D374" s="13"/>
+      <c r="E374" s="12"/>
+      <c r="BO374" s="16"/>
+      <c r="BR374" s="16"/>
     </row>
     <row r="375" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D375" s="14"/>
-      <c r="E375" s="13"/>
-      <c r="BO375" s="17"/>
-      <c r="BR375" s="17"/>
+      <c r="D375" s="13"/>
+      <c r="E375" s="12"/>
+      <c r="BO375" s="16"/>
+      <c r="BR375" s="16"/>
     </row>
     <row r="376" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D376" s="14"/>
-      <c r="E376" s="13"/>
-      <c r="BO376" s="17"/>
-      <c r="BR376" s="17"/>
+      <c r="D376" s="13"/>
+      <c r="E376" s="12"/>
+      <c r="BO376" s="16"/>
+      <c r="BR376" s="16"/>
     </row>
     <row r="377" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D377" s="14"/>
-      <c r="E377" s="13"/>
-      <c r="BO377" s="17"/>
-      <c r="BR377" s="17"/>
+      <c r="D377" s="13"/>
+      <c r="E377" s="12"/>
+      <c r="BO377" s="16"/>
+      <c r="BR377" s="16"/>
     </row>
     <row r="378" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D378" s="14"/>
-      <c r="E378" s="13"/>
-      <c r="BO378" s="17"/>
-      <c r="BR378" s="17"/>
+      <c r="D378" s="13"/>
+      <c r="E378" s="12"/>
+      <c r="BO378" s="16"/>
+      <c r="BR378" s="16"/>
     </row>
     <row r="379" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D379" s="14"/>
-      <c r="E379" s="13"/>
-      <c r="BR379" s="17"/>
+      <c r="D379" s="13"/>
+      <c r="E379" s="12"/>
+      <c r="BR379" s="16"/>
     </row>
     <row r="380" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D380" s="14"/>
-      <c r="E380" s="13"/>
-      <c r="BR380" s="17"/>
+      <c r="D380" s="13"/>
+      <c r="E380" s="12"/>
+      <c r="BR380" s="16"/>
     </row>
     <row r="381" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D381" s="14"/>
-      <c r="E381" s="13"/>
-      <c r="BO381" s="17"/>
-      <c r="BR381" s="17"/>
+      <c r="D381" s="13"/>
+      <c r="E381" s="12"/>
+      <c r="BO381" s="16"/>
+      <c r="BR381" s="16"/>
     </row>
     <row r="382" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D382" s="14"/>
-      <c r="E382" s="13"/>
-      <c r="BO382" s="17"/>
-      <c r="BR382" s="17"/>
+      <c r="D382" s="13"/>
+      <c r="E382" s="12"/>
+      <c r="BO382" s="16"/>
+      <c r="BR382" s="16"/>
     </row>
     <row r="383" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D383" s="14"/>
-      <c r="E383" s="13"/>
-      <c r="BO383" s="17"/>
-      <c r="BR383" s="17"/>
+      <c r="D383" s="13"/>
+      <c r="E383" s="12"/>
+      <c r="BO383" s="16"/>
+      <c r="BR383" s="16"/>
     </row>
     <row r="384" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D384" s="14"/>
-      <c r="E384" s="13"/>
-      <c r="BO384" s="17"/>
-      <c r="BR384" s="17"/>
+      <c r="D384" s="13"/>
+      <c r="E384" s="12"/>
+      <c r="BO384" s="16"/>
+      <c r="BR384" s="16"/>
     </row>
     <row r="385" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D385" s="14"/>
-      <c r="E385" s="13"/>
-      <c r="BO385" s="17"/>
-      <c r="BR385" s="17"/>
+      <c r="D385" s="13"/>
+      <c r="E385" s="12"/>
+      <c r="BO385" s="16"/>
+      <c r="BR385" s="16"/>
     </row>
     <row r="386" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D386" s="14"/>
-      <c r="E386" s="13"/>
-      <c r="BO386" s="17"/>
-      <c r="BR386" s="17"/>
+      <c r="D386" s="13"/>
+      <c r="E386" s="12"/>
+      <c r="BO386" s="16"/>
+      <c r="BR386" s="16"/>
     </row>
     <row r="387" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D387" s="14"/>
-      <c r="E387" s="13"/>
-      <c r="BO387" s="17"/>
-      <c r="BR387" s="17"/>
+      <c r="D387" s="13"/>
+      <c r="E387" s="12"/>
+      <c r="BO387" s="16"/>
+      <c r="BR387" s="16"/>
     </row>
     <row r="388" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D388" s="14"/>
-      <c r="E388" s="13"/>
-      <c r="BO388" s="17"/>
-      <c r="BR388" s="17"/>
+      <c r="D388" s="13"/>
+      <c r="E388" s="12"/>
+      <c r="BO388" s="16"/>
+      <c r="BR388" s="16"/>
     </row>
     <row r="389" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D389" s="14"/>
-      <c r="E389" s="13"/>
-      <c r="BO389" s="17"/>
-      <c r="BR389" s="17"/>
+      <c r="D389" s="13"/>
+      <c r="E389" s="12"/>
+      <c r="BO389" s="16"/>
+      <c r="BR389" s="16"/>
     </row>
     <row r="390" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D390" s="14"/>
-      <c r="E390" s="13"/>
-      <c r="BO390" s="17"/>
-      <c r="BR390" s="17"/>
+      <c r="D390" s="13"/>
+      <c r="E390" s="12"/>
+      <c r="BO390" s="16"/>
+      <c r="BR390" s="16"/>
     </row>
     <row r="391" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D391" s="14"/>
-      <c r="E391" s="13"/>
-      <c r="BO391" s="17"/>
-      <c r="BR391" s="17"/>
+      <c r="D391" s="13"/>
+      <c r="E391" s="12"/>
+      <c r="BO391" s="16"/>
+      <c r="BR391" s="16"/>
     </row>
     <row r="392" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D392" s="14"/>
-      <c r="E392" s="13"/>
-      <c r="BO392" s="17"/>
-      <c r="BR392" s="17"/>
+      <c r="D392" s="13"/>
+      <c r="E392" s="12"/>
+      <c r="BO392" s="16"/>
+      <c r="BR392" s="16"/>
     </row>
     <row r="393" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D393" s="14"/>
-      <c r="E393" s="13"/>
-      <c r="BO393" s="17"/>
-      <c r="BR393" s="17"/>
+      <c r="D393" s="13"/>
+      <c r="E393" s="12"/>
+      <c r="BO393" s="16"/>
+      <c r="BR393" s="16"/>
     </row>
     <row r="394" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D394" s="14"/>
-      <c r="E394" s="13"/>
-      <c r="BO394" s="17"/>
-      <c r="BR394" s="17"/>
+      <c r="D394" s="13"/>
+      <c r="E394" s="12"/>
+      <c r="BO394" s="16"/>
+      <c r="BR394" s="16"/>
     </row>
     <row r="395" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D395" s="14"/>
-      <c r="E395" s="13"/>
-      <c r="BO395" s="17"/>
-      <c r="BR395" s="17"/>
+      <c r="D395" s="13"/>
+      <c r="E395" s="12"/>
+      <c r="BO395" s="16"/>
+      <c r="BR395" s="16"/>
     </row>
     <row r="396" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D396" s="14"/>
-      <c r="E396" s="13"/>
-      <c r="BO396" s="17"/>
-      <c r="BR396" s="17"/>
+      <c r="D396" s="13"/>
+      <c r="E396" s="12"/>
+      <c r="BO396" s="16"/>
+      <c r="BR396" s="16"/>
     </row>
     <row r="397" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D397" s="14"/>
-      <c r="E397" s="13"/>
-      <c r="BO397" s="17"/>
-      <c r="BR397" s="17"/>
+      <c r="D397" s="13"/>
+      <c r="E397" s="12"/>
+      <c r="BO397" s="16"/>
+      <c r="BR397" s="16"/>
     </row>
     <row r="398" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D398" s="14"/>
-      <c r="E398" s="13"/>
-      <c r="BO398" s="17"/>
-      <c r="BR398" s="17"/>
+      <c r="D398" s="13"/>
+      <c r="E398" s="12"/>
+      <c r="BO398" s="16"/>
+      <c r="BR398" s="16"/>
     </row>
     <row r="399" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D399" s="14"/>
-      <c r="E399" s="13"/>
-      <c r="BO399" s="17"/>
-      <c r="BR399" s="17"/>
+      <c r="D399" s="13"/>
+      <c r="E399" s="12"/>
+      <c r="BO399" s="16"/>
+      <c r="BR399" s="16"/>
     </row>
     <row r="400" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D400" s="14"/>
-      <c r="E400" s="13"/>
-      <c r="BO400" s="17"/>
-      <c r="BR400" s="17"/>
+      <c r="D400" s="13"/>
+      <c r="E400" s="12"/>
+      <c r="BO400" s="16"/>
+      <c r="BR400" s="16"/>
     </row>
     <row r="401" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D401" s="14"/>
-      <c r="E401" s="13"/>
-      <c r="BO401" s="17"/>
-      <c r="BR401" s="17"/>
+      <c r="D401" s="13"/>
+      <c r="E401" s="12"/>
+      <c r="BO401" s="16"/>
+      <c r="BR401" s="16"/>
     </row>
     <row r="402" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D402" s="14"/>
-      <c r="E402" s="13"/>
-      <c r="BO402" s="17"/>
-      <c r="BR402" s="17"/>
+      <c r="D402" s="13"/>
+      <c r="E402" s="12"/>
+      <c r="BO402" s="16"/>
+      <c r="BR402" s="16"/>
     </row>
     <row r="403" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D403" s="14"/>
-      <c r="E403" s="13"/>
-      <c r="BO403" s="17"/>
-      <c r="BR403" s="17"/>
+      <c r="D403" s="13"/>
+      <c r="E403" s="12"/>
+      <c r="BO403" s="16"/>
+      <c r="BR403" s="16"/>
     </row>
     <row r="404" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D404" s="14"/>
-      <c r="E404" s="13"/>
-      <c r="BR404" s="17"/>
+      <c r="D404" s="13"/>
+      <c r="E404" s="12"/>
+      <c r="BR404" s="16"/>
     </row>
     <row r="405" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D405" s="14"/>
-      <c r="E405" s="13"/>
-      <c r="BR405" s="17"/>
+      <c r="D405" s="13"/>
+      <c r="E405" s="12"/>
+      <c r="BR405" s="16"/>
     </row>
     <row r="406" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D406" s="14"/>
-      <c r="E406" s="13"/>
-      <c r="BO406" s="17"/>
-      <c r="BR406" s="17"/>
+      <c r="D406" s="13"/>
+      <c r="E406" s="12"/>
+      <c r="BO406" s="16"/>
+      <c r="BR406" s="16"/>
     </row>
     <row r="407" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D407" s="14"/>
-      <c r="E407" s="13"/>
-      <c r="BO407" s="17"/>
-      <c r="BR407" s="17"/>
+      <c r="D407" s="13"/>
+      <c r="E407" s="12"/>
+      <c r="BO407" s="16"/>
+      <c r="BR407" s="16"/>
     </row>
     <row r="408" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D408" s="14"/>
-      <c r="E408" s="13"/>
-      <c r="BR408" s="17"/>
+      <c r="D408" s="13"/>
+      <c r="E408" s="12"/>
+      <c r="BR408" s="16"/>
     </row>
     <row r="409" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D409" s="14"/>
-      <c r="E409" s="13"/>
-      <c r="BR409" s="17"/>
+      <c r="D409" s="13"/>
+      <c r="E409" s="12"/>
+      <c r="BR409" s="16"/>
     </row>
     <row r="410" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D410" s="14"/>
-      <c r="E410" s="13"/>
-      <c r="BO410" s="17"/>
-      <c r="BR410" s="17"/>
+      <c r="D410" s="13"/>
+      <c r="E410" s="12"/>
+      <c r="BO410" s="16"/>
+      <c r="BR410" s="16"/>
     </row>
     <row r="411" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D411" s="14"/>
-      <c r="E411" s="13"/>
-      <c r="BO411" s="17"/>
-      <c r="BR411" s="17"/>
+      <c r="D411" s="13"/>
+      <c r="E411" s="12"/>
+      <c r="BO411" s="16"/>
+      <c r="BR411" s="16"/>
     </row>
     <row r="412" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D412" s="14"/>
-      <c r="E412" s="13"/>
-      <c r="BO412" s="17"/>
-      <c r="BR412" s="17"/>
+      <c r="D412" s="13"/>
+      <c r="E412" s="12"/>
+      <c r="BO412" s="16"/>
+      <c r="BR412" s="16"/>
     </row>
     <row r="413" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D413" s="14"/>
-      <c r="E413" s="13"/>
-      <c r="BO413" s="17"/>
-      <c r="BR413" s="17"/>
+      <c r="D413" s="13"/>
+      <c r="E413" s="12"/>
+      <c r="BO413" s="16"/>
+      <c r="BR413" s="16"/>
     </row>
     <row r="414" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D414" s="14"/>
-      <c r="E414" s="13"/>
-      <c r="BO414" s="17"/>
-      <c r="BR414" s="17"/>
+      <c r="D414" s="13"/>
+      <c r="E414" s="12"/>
+      <c r="BO414" s="16"/>
+      <c r="BR414" s="16"/>
     </row>
     <row r="415" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D415" s="14"/>
-      <c r="E415" s="13"/>
-      <c r="BO415" s="17"/>
-      <c r="BR415" s="17"/>
+      <c r="D415" s="13"/>
+      <c r="E415" s="12"/>
+      <c r="BO415" s="16"/>
+      <c r="BR415" s="16"/>
     </row>
     <row r="416" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D416" s="14"/>
-      <c r="E416" s="13"/>
-      <c r="BO416" s="17"/>
-      <c r="BR416" s="17"/>
+      <c r="D416" s="13"/>
+      <c r="E416" s="12"/>
+      <c r="BO416" s="16"/>
+      <c r="BR416" s="16"/>
     </row>
     <row r="417" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D417" s="14"/>
-      <c r="E417" s="13"/>
-      <c r="BO417" s="17"/>
-      <c r="BR417" s="17"/>
+      <c r="D417" s="13"/>
+      <c r="E417" s="12"/>
+      <c r="BO417" s="16"/>
+      <c r="BR417" s="16"/>
     </row>
     <row r="418" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D418" s="14"/>
-      <c r="E418" s="13"/>
-      <c r="BO418" s="17"/>
-      <c r="BR418" s="17"/>
+      <c r="D418" s="13"/>
+      <c r="E418" s="12"/>
+      <c r="BO418" s="16"/>
+      <c r="BR418" s="16"/>
     </row>
     <row r="419" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D419" s="14"/>
-      <c r="E419" s="13"/>
-      <c r="BO419" s="17"/>
-      <c r="BR419" s="17"/>
+      <c r="D419" s="13"/>
+      <c r="E419" s="12"/>
+      <c r="BO419" s="16"/>
+      <c r="BR419" s="16"/>
     </row>
     <row r="420" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D420" s="14"/>
-      <c r="E420" s="13"/>
-      <c r="BO420" s="17"/>
-      <c r="BR420" s="17"/>
+      <c r="D420" s="13"/>
+      <c r="E420" s="12"/>
+      <c r="BO420" s="16"/>
+      <c r="BR420" s="16"/>
     </row>
     <row r="421" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D421" s="14"/>
-      <c r="E421" s="13"/>
-      <c r="BO421" s="17"/>
-      <c r="BR421" s="17"/>
+      <c r="D421" s="13"/>
+      <c r="E421" s="12"/>
+      <c r="BO421" s="16"/>
+      <c r="BR421" s="16"/>
     </row>
     <row r="422" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D422" s="14"/>
-      <c r="E422" s="13"/>
-      <c r="BO422" s="17"/>
-      <c r="BR422" s="17"/>
+      <c r="D422" s="13"/>
+      <c r="E422" s="12"/>
+      <c r="BO422" s="16"/>
+      <c r="BR422" s="16"/>
     </row>
     <row r="423" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D423" s="14"/>
-      <c r="E423" s="13"/>
-      <c r="BO423" s="17"/>
-      <c r="BR423" s="17"/>
+      <c r="D423" s="13"/>
+      <c r="E423" s="12"/>
+      <c r="BO423" s="16"/>
+      <c r="BR423" s="16"/>
     </row>
     <row r="424" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D424" s="14"/>
-      <c r="E424" s="13"/>
-      <c r="BO424" s="17"/>
-      <c r="BR424" s="17"/>
+      <c r="D424" s="13"/>
+      <c r="E424" s="12"/>
+      <c r="BO424" s="16"/>
+      <c r="BR424" s="16"/>
     </row>
     <row r="425" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D425" s="14"/>
-      <c r="E425" s="13"/>
-      <c r="BO425" s="17"/>
-      <c r="BR425" s="17"/>
+      <c r="D425" s="13"/>
+      <c r="E425" s="12"/>
+      <c r="BO425" s="16"/>
+      <c r="BR425" s="16"/>
     </row>
     <row r="426" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D426" s="14"/>
-      <c r="E426" s="13"/>
-      <c r="BO426" s="17"/>
-      <c r="BR426" s="17"/>
+      <c r="D426" s="13"/>
+      <c r="E426" s="12"/>
+      <c r="BO426" s="16"/>
+      <c r="BR426" s="16"/>
     </row>
     <row r="427" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D427" s="14"/>
-      <c r="E427" s="13"/>
+      <c r="D427" s="13"/>
+      <c r="E427" s="12"/>
     </row>
     <row r="428" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D428" s="14"/>
-      <c r="E428" s="13"/>
+      <c r="D428" s="13"/>
+      <c r="E428" s="12"/>
     </row>
     <row r="429" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D429" s="14"/>
-      <c r="E429" s="13"/>
+      <c r="D429" s="13"/>
+      <c r="E429" s="12"/>
     </row>
     <row r="430" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D430" s="14"/>
-      <c r="E430" s="13"/>
+      <c r="D430" s="13"/>
+      <c r="E430" s="12"/>
     </row>
     <row r="431" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D431" s="14"/>
-      <c r="E431" s="13"/>
+      <c r="D431" s="13"/>
+      <c r="E431" s="12"/>
     </row>
     <row r="432" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D432" s="14"/>
-      <c r="E432" s="13"/>
+      <c r="D432" s="13"/>
+      <c r="E432" s="12"/>
     </row>
     <row r="433" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D433" s="14"/>
-      <c r="E433" s="13"/>
+      <c r="D433" s="13"/>
+      <c r="E433" s="12"/>
     </row>
     <row r="434" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D434" s="14"/>
-      <c r="E434" s="13"/>
+      <c r="D434" s="13"/>
+      <c r="E434" s="12"/>
     </row>
     <row r="435" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D435" s="14"/>
-      <c r="E435" s="13"/>
+      <c r="D435" s="13"/>
+      <c r="E435" s="12"/>
     </row>
     <row r="436" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D436" s="14"/>
-      <c r="E436" s="13"/>
+      <c r="D436" s="13"/>
+      <c r="E436" s="12"/>
     </row>
     <row r="437" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D437" s="14"/>
-      <c r="E437" s="13"/>
+      <c r="D437" s="13"/>
+      <c r="E437" s="12"/>
     </row>
     <row r="438" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D438" s="14"/>
-      <c r="E438" s="13"/>
+      <c r="D438" s="13"/>
+      <c r="E438" s="12"/>
     </row>
     <row r="439" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D439" s="14"/>
-      <c r="E439" s="13"/>
+      <c r="D439" s="13"/>
+      <c r="E439" s="12"/>
     </row>
     <row r="440" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D440" s="14"/>
-      <c r="E440" s="13"/>
+      <c r="D440" s="13"/>
+      <c r="E440" s="12"/>
     </row>
     <row r="441" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D441" s="14"/>
-      <c r="E441" s="13"/>
+      <c r="D441" s="13"/>
+      <c r="E441" s="12"/>
     </row>
     <row r="442" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D442" s="14"/>
-      <c r="E442" s="13"/>
+      <c r="D442" s="13"/>
+      <c r="E442" s="12"/>
     </row>
     <row r="443" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D443" s="14"/>
-      <c r="E443" s="13"/>
+      <c r="D443" s="13"/>
+      <c r="E443" s="12"/>
     </row>
     <row r="444" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D444" s="14"/>
-      <c r="E444" s="13"/>
+      <c r="D444" s="13"/>
+      <c r="E444" s="12"/>
     </row>
     <row r="445" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D445" s="14"/>
-      <c r="E445" s="13"/>
+      <c r="D445" s="13"/>
+      <c r="E445" s="12"/>
     </row>
     <row r="446" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D446" s="14"/>
-      <c r="E446" s="13"/>
+      <c r="D446" s="13"/>
+      <c r="E446" s="12"/>
     </row>
     <row r="447" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D447" s="14"/>
-      <c r="E447" s="13"/>
+      <c r="D447" s="13"/>
+      <c r="E447" s="12"/>
     </row>
     <row r="448" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D448" s="14"/>
-      <c r="E448" s="13"/>
+      <c r="D448" s="13"/>
+      <c r="E448" s="12"/>
     </row>
     <row r="449" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D449" s="14"/>
-      <c r="E449" s="13"/>
+      <c r="D449" s="13"/>
+      <c r="E449" s="12"/>
     </row>
     <row r="450" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D450" s="14"/>
-      <c r="E450" s="13"/>
+      <c r="D450" s="13"/>
+      <c r="E450" s="12"/>
     </row>
     <row r="451" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D451" s="14"/>
-      <c r="E451" s="13"/>
+      <c r="D451" s="13"/>
+      <c r="E451" s="12"/>
     </row>
     <row r="452" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D452" s="14"/>
-      <c r="E452" s="13"/>
+      <c r="D452" s="13"/>
+      <c r="E452" s="12"/>
     </row>
     <row r="453" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D453" s="14"/>
-      <c r="E453" s="13"/>
+      <c r="D453" s="13"/>
+      <c r="E453" s="12"/>
     </row>
     <row r="454" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D454" s="14"/>
-      <c r="E454" s="13"/>
+      <c r="D454" s="13"/>
+      <c r="E454" s="12"/>
     </row>
     <row r="455" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D455" s="14"/>
-      <c r="E455" s="13"/>
+      <c r="D455" s="13"/>
+      <c r="E455" s="12"/>
     </row>
     <row r="456" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D456" s="14"/>
-      <c r="E456" s="13"/>
+      <c r="D456" s="13"/>
+      <c r="E456" s="12"/>
     </row>
     <row r="457" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D457" s="14"/>
-      <c r="E457" s="13"/>
+      <c r="D457" s="13"/>
+      <c r="E457" s="12"/>
     </row>
     <row r="458" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D458" s="14"/>
-      <c r="E458" s="13"/>
+      <c r="D458" s="13"/>
+      <c r="E458" s="12"/>
     </row>
     <row r="459" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D459" s="14"/>
-      <c r="E459" s="13"/>
+      <c r="D459" s="13"/>
+      <c r="E459" s="12"/>
     </row>
     <row r="460" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D460" s="14"/>
-      <c r="E460" s="13"/>
+      <c r="D460" s="13"/>
+      <c r="E460" s="12"/>
     </row>
     <row r="461" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D461" s="14"/>
-      <c r="E461" s="13"/>
+      <c r="D461" s="13"/>
+      <c r="E461" s="12"/>
     </row>
     <row r="462" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D462" s="14"/>
-      <c r="E462" s="13"/>
+      <c r="D462" s="13"/>
+      <c r="E462" s="12"/>
     </row>
     <row r="463" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D463" s="14"/>
-      <c r="E463" s="13"/>
+      <c r="D463" s="13"/>
+      <c r="E463" s="12"/>
     </row>
     <row r="464" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D464" s="14"/>
-      <c r="E464" s="13"/>
+      <c r="D464" s="13"/>
+      <c r="E464" s="12"/>
     </row>
     <row r="465" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D465" s="14"/>
-      <c r="E465" s="13"/>
+      <c r="D465" s="13"/>
+      <c r="E465" s="12"/>
     </row>
     <row r="466" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D466" s="14"/>
-      <c r="E466" s="13"/>
+      <c r="D466" s="13"/>
+      <c r="E466" s="12"/>
     </row>
     <row r="467" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D467" s="14"/>
-      <c r="E467" s="13"/>
+      <c r="D467" s="13"/>
+      <c r="E467" s="12"/>
     </row>
     <row r="468" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D468" s="14"/>
-      <c r="E468" s="13"/>
+      <c r="D468" s="13"/>
+      <c r="E468" s="12"/>
     </row>
     <row r="469" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D469" s="14"/>
-      <c r="E469" s="13"/>
+      <c r="D469" s="13"/>
+      <c r="E469" s="12"/>
     </row>
     <row r="470" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D470" s="14"/>
-      <c r="E470" s="13"/>
+      <c r="D470" s="13"/>
+      <c r="E470" s="12"/>
     </row>
     <row r="471" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D471" s="14"/>
-      <c r="E471" s="13"/>
+      <c r="D471" s="13"/>
+      <c r="E471" s="12"/>
     </row>
     <row r="472" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D472" s="14"/>
-      <c r="E472" s="13"/>
+      <c r="D472" s="13"/>
+      <c r="E472" s="12"/>
     </row>
     <row r="473" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D473" s="14"/>
-      <c r="E473" s="13"/>
+      <c r="D473" s="13"/>
+      <c r="E473" s="12"/>
     </row>
     <row r="474" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D474" s="14"/>
-      <c r="E474" s="13"/>
+      <c r="D474" s="13"/>
+      <c r="E474" s="12"/>
     </row>
     <row r="475" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D475" s="14"/>
-      <c r="E475" s="13"/>
+      <c r="D475" s="13"/>
+      <c r="E475" s="12"/>
     </row>
     <row r="476" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D476" s="14"/>
-      <c r="E476" s="13"/>
+      <c r="D476" s="13"/>
+      <c r="E476" s="12"/>
     </row>
     <row r="477" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D477" s="14"/>
-      <c r="E477" s="13"/>
+      <c r="D477" s="13"/>
+      <c r="E477" s="12"/>
     </row>
     <row r="478" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D478" s="14"/>
-      <c r="E478" s="13"/>
+      <c r="D478" s="13"/>
+      <c r="E478" s="12"/>
     </row>
     <row r="479" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D479" s="14"/>
-      <c r="E479" s="13"/>
+      <c r="D479" s="13"/>
+      <c r="E479" s="12"/>
     </row>
     <row r="480" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D480" s="14"/>
-      <c r="E480" s="13"/>
+      <c r="D480" s="13"/>
+      <c r="E480" s="12"/>
     </row>
     <row r="481" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D481" s="14"/>
-      <c r="E481" s="13"/>
+      <c r="D481" s="13"/>
+      <c r="E481" s="12"/>
     </row>
     <row r="482" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D482" s="14"/>
-      <c r="E482" s="13"/>
+      <c r="D482" s="13"/>
+      <c r="E482" s="12"/>
     </row>
     <row r="483" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D483" s="14"/>
-      <c r="E483" s="13"/>
+      <c r="D483" s="13"/>
+      <c r="E483" s="12"/>
     </row>
     <row r="484" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D484" s="14"/>
-      <c r="E484" s="13"/>
+      <c r="D484" s="13"/>
+      <c r="E484" s="12"/>
     </row>
     <row r="485" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D485" s="14"/>
-      <c r="E485" s="13"/>
+      <c r="D485" s="13"/>
+      <c r="E485" s="12"/>
     </row>
     <row r="486" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D486" s="14"/>
-      <c r="E486" s="13"/>
+      <c r="D486" s="13"/>
+      <c r="E486" s="12"/>
     </row>
     <row r="487" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D487" s="14"/>
-      <c r="E487" s="13"/>
+      <c r="D487" s="13"/>
+      <c r="E487" s="12"/>
     </row>
     <row r="488" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D488" s="14"/>
-      <c r="E488" s="13"/>
+      <c r="D488" s="13"/>
+      <c r="E488" s="12"/>
     </row>
     <row r="489" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D489" s="14"/>
-      <c r="E489" s="13"/>
+      <c r="D489" s="13"/>
+      <c r="E489" s="12"/>
     </row>
     <row r="490" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D490" s="14"/>
-      <c r="E490" s="13"/>
+      <c r="D490" s="13"/>
+      <c r="E490" s="12"/>
     </row>
     <row r="491" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D491" s="14"/>
-      <c r="E491" s="13"/>
+      <c r="D491" s="13"/>
+      <c r="E491" s="12"/>
     </row>
     <row r="492" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D492" s="14"/>
-      <c r="E492" s="13"/>
+      <c r="D492" s="13"/>
+      <c r="E492" s="12"/>
     </row>
     <row r="493" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D493" s="14"/>
-      <c r="E493" s="13"/>
+      <c r="D493" s="13"/>
+      <c r="E493" s="12"/>
     </row>
     <row r="494" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D494" s="14"/>
-      <c r="E494" s="13"/>
+      <c r="D494" s="13"/>
+      <c r="E494" s="12"/>
     </row>
     <row r="495" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D495" s="14"/>
-      <c r="E495" s="13"/>
+      <c r="D495" s="13"/>
+      <c r="E495" s="12"/>
     </row>
     <row r="496" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D496" s="14"/>
-      <c r="E496" s="13"/>
+      <c r="D496" s="13"/>
+      <c r="E496" s="12"/>
     </row>
     <row r="497" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D497" s="14"/>
-      <c r="E497" s="13"/>
+      <c r="D497" s="13"/>
+      <c r="E497" s="12"/>
     </row>
     <row r="498" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D498" s="14"/>
-      <c r="E498" s="13"/>
+      <c r="D498" s="13"/>
+      <c r="E498" s="12"/>
     </row>
     <row r="499" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D499" s="14"/>
-      <c r="E499" s="13"/>
+      <c r="D499" s="13"/>
+      <c r="E499" s="12"/>
     </row>
     <row r="500" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D500" s="14"/>
-      <c r="E500" s="13"/>
+      <c r="D500" s="13"/>
+      <c r="E500" s="12"/>
     </row>
     <row r="501" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D501" s="14"/>
-      <c r="E501" s="13"/>
+      <c r="D501" s="13"/>
+      <c r="E501" s="12"/>
     </row>
     <row r="502" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D502" s="14"/>
-      <c r="E502" s="13"/>
+      <c r="D502" s="13"/>
+      <c r="E502" s="12"/>
     </row>
     <row r="503" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D503" s="14"/>
-      <c r="E503" s="13"/>
+      <c r="D503" s="13"/>
+      <c r="E503" s="12"/>
     </row>
     <row r="504" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D504" s="14"/>
-      <c r="E504" s="13"/>
+      <c r="D504" s="13"/>
+      <c r="E504" s="12"/>
     </row>
     <row r="505" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D505" s="14"/>
-      <c r="E505" s="13"/>
+      <c r="D505" s="13"/>
+      <c r="E505" s="12"/>
     </row>
     <row r="506" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D506" s="14"/>
-      <c r="E506" s="13"/>
+      <c r="D506" s="13"/>
+      <c r="E506" s="12"/>
     </row>
     <row r="574" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D574" s="14"/>
-      <c r="E574" s="13"/>
+      <c r="D574" s="13"/>
+      <c r="E574" s="12"/>
     </row>
     <row r="575" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D575" s="14"/>
-      <c r="E575" s="13"/>
+      <c r="D575" s="13"/>
+      <c r="E575" s="12"/>
     </row>
     <row r="576" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D576" s="14"/>
-      <c r="E576" s="13"/>
+      <c r="D576" s="13"/>
+      <c r="E576" s="12"/>
     </row>
     <row r="577" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D577" s="14"/>
-      <c r="E577" s="13"/>
+      <c r="D577" s="13"/>
+      <c r="E577" s="12"/>
     </row>
     <row r="578" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D578" s="14"/>
-      <c r="E578" s="13"/>
+      <c r="D578" s="13"/>
+      <c r="E578" s="12"/>
     </row>
     <row r="579" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D579" s="14"/>
-      <c r="E579" s="13"/>
+      <c r="D579" s="13"/>
+      <c r="E579" s="12"/>
     </row>
     <row r="580" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D580" s="14"/>
-      <c r="E580" s="13"/>
+      <c r="D580" s="13"/>
+      <c r="E580" s="12"/>
     </row>
     <row r="581" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D581" s="14"/>
-      <c r="E581" s="13"/>
+      <c r="D581" s="13"/>
+      <c r="E581" s="12"/>
     </row>
     <row r="582" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D582" s="14"/>
-      <c r="E582" s="13"/>
+      <c r="D582" s="13"/>
+      <c r="E582" s="12"/>
     </row>
     <row r="583" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D583" s="14"/>
-      <c r="E583" s="13"/>
+      <c r="D583" s="13"/>
+      <c r="E583" s="12"/>
     </row>
     <row r="584" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D584" s="14"/>
-      <c r="E584" s="13"/>
+      <c r="D584" s="13"/>
+      <c r="E584" s="12"/>
     </row>
     <row r="585" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D585" s="14"/>
-      <c r="E585" s="13"/>
+      <c r="D585" s="13"/>
+      <c r="E585" s="12"/>
     </row>
     <row r="586" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D586" s="14"/>
-      <c r="E586" s="13"/>
+      <c r="D586" s="13"/>
+      <c r="E586" s="12"/>
     </row>
     <row r="587" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D587" s="14"/>
-      <c r="E587" s="13"/>
+      <c r="D587" s="13"/>
+      <c r="E587" s="12"/>
     </row>
     <row r="588" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D588" s="14"/>
-      <c r="E588" s="13"/>
+      <c r="D588" s="13"/>
+      <c r="E588" s="12"/>
     </row>
     <row r="589" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D589" s="14"/>
-      <c r="E589" s="13"/>
+      <c r="D589" s="13"/>
+      <c r="E589" s="12"/>
     </row>
     <row r="590" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D590" s="14"/>
-      <c r="E590" s="13"/>
+      <c r="D590" s="13"/>
+      <c r="E590" s="12"/>
     </row>
     <row r="591" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D591" s="14"/>
-      <c r="E591" s="13"/>
+      <c r="D591" s="13"/>
+      <c r="E591" s="12"/>
     </row>
     <row r="592" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D592" s="14"/>
-      <c r="E592" s="13"/>
+      <c r="D592" s="13"/>
+      <c r="E592" s="12"/>
     </row>
     <row r="593" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D593" s="14"/>
-      <c r="E593" s="13"/>
+      <c r="D593" s="13"/>
+      <c r="E593" s="12"/>
     </row>
     <row r="594" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D594" s="14"/>
-      <c r="E594" s="13"/>
+      <c r="D594" s="13"/>
+      <c r="E594" s="12"/>
     </row>
     <row r="595" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D595" s="14"/>
-      <c r="E595" s="13"/>
+      <c r="D595" s="13"/>
+      <c r="E595" s="12"/>
     </row>
     <row r="596" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D596" s="14"/>
-      <c r="E596" s="13"/>
+      <c r="D596" s="13"/>
+      <c r="E596" s="12"/>
     </row>
     <row r="597" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D597" s="14"/>
-      <c r="E597" s="13"/>
+      <c r="D597" s="13"/>
+      <c r="E597" s="12"/>
     </row>
     <row r="598" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D598" s="14"/>
-      <c r="E598" s="13"/>
+      <c r="D598" s="13"/>
+      <c r="E598" s="12"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="15" type="noConversion"/>
+  <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <legacyDrawing r:id="rId1"/>
@@ -6145,7 +6369,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:DJ823"/>
+  <dimension ref="A1:DJ825"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.08203125" customWidth="1"/>
@@ -7251,7 +7475,7 @@
     </row>
     <row r="6" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C6" t="s">
         <v>449</v>
@@ -7259,7 +7483,9 @@
       <c r="K6" s="5" t="s">
         <v>450</v>
       </c>
-      <c r="P6" s="3"/>
+      <c r="P6" s="7" t="s">
+        <v>536</v>
+      </c>
       <c r="AC6">
         <v>1</v>
       </c>
@@ -7285,13 +7511,13 @@
         <v>453</v>
       </c>
       <c r="CH6" s="2" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="CI6" t="s">
         <v>435</v>
       </c>
       <c r="CN6" s="2" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="CR6">
         <v>9999</v>
@@ -7302,19 +7528,19 @@
     </row>
     <row r="7" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="K7" s="5" t="s">
         <v>472</v>
       </c>
-      <c r="K7" s="5" t="s">
-        <v>473</v>
-      </c>
       <c r="L7" s="5" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="Q7" s="5" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AC7">
         <v>1</v>
@@ -7332,27 +7558,27 @@
       <c r="BV7"/>
       <c r="CL7" s="5"/>
       <c r="CU7" s="2" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="8" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>476</v>
-      </c>
       <c r="K8" s="5" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="AC8">
         <v>1</v>
       </c>
       <c r="AT8" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="BD8">
         <v>1</v>
@@ -7360,27 +7586,27 @@
       <c r="BV8"/>
       <c r="CL8" s="5"/>
       <c r="CU8" s="2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="9" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>478</v>
-      </c>
       <c r="K9" s="5" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="AC9">
         <v>1</v>
       </c>
       <c r="AT9" s="2" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="BD9">
         <v>99</v>
@@ -7388,10 +7614,10 @@
       <c r="BV9"/>
       <c r="CL9" s="5"/>
       <c r="CM9" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="CN9" s="2" t="s">
         <v>480</v>
-      </c>
-      <c r="CN9" s="2" t="s">
-        <v>481</v>
       </c>
       <c r="CR9">
         <v>9999</v>
@@ -7400,34 +7626,35 @@
     </row>
     <row r="10" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I10">
         <v>1</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
+      </c>
+      <c r="Q10" s="5" t="s">
+        <v>493</v>
       </c>
       <c r="AC10">
         <v>1</v>
       </c>
       <c r="AG10" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="AJ10" s="2" t="s">
-        <v>464</v>
-      </c>
+        <v>491</v>
+      </c>
+      <c r="AJ10" s="2"/>
       <c r="AN10">
         <v>1</v>
       </c>
       <c r="AT10" s="2" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="BD10">
         <v>99</v>
@@ -7436,7 +7663,7 @@
       <c r="CL10" s="5"/>
       <c r="CM10" s="2"/>
       <c r="CN10" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="CR10">
         <v>1</v>
@@ -7454,22 +7681,22 @@
     </row>
     <row r="11" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="AC11">
         <v>1</v>
       </c>
       <c r="AG11" s="2" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="AN11">
         <v>1</v>
@@ -7479,7 +7706,7 @@
       </c>
       <c r="CL11" s="5"/>
       <c r="CN11" s="2" t="s">
-        <v>496</v>
+        <v>548</v>
       </c>
       <c r="CR11">
         <v>9999</v>
@@ -7509,7 +7736,27 @@
       <c r="CA12"/>
     </row>
     <row r="13" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="K13" s="7"/>
+      <c r="A13" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="G13">
+        <v>3</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>507</v>
+      </c>
       <c r="L13" s="7"/>
       <c r="M13"/>
       <c r="N13"/>
@@ -7523,303 +7770,863 @@
       <c r="V13" s="7"/>
       <c r="W13" s="7"/>
       <c r="X13"/>
-      <c r="BU13" s="8"/>
-      <c r="BV13" s="8"/>
-      <c r="BW13" s="8"/>
-      <c r="BX13" s="8"/>
-      <c r="BY13" s="8"/>
+      <c r="AB13">
+        <v>1</v>
+      </c>
+      <c r="AC13">
+        <v>1</v>
+      </c>
+      <c r="AG13" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="AO13" t="s">
+        <v>451</v>
+      </c>
+      <c r="AT13" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="AY13">
+        <v>1</v>
+      </c>
+      <c r="AZ13">
+        <v>1</v>
+      </c>
+      <c r="BD13">
+        <v>1</v>
+      </c>
+      <c r="BO13" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="BT13">
+        <v>0.2</v>
+      </c>
+      <c r="BU13" s="8">
+        <v>1</v>
+      </c>
+      <c r="BV13" s="8">
+        <v>0</v>
+      </c>
+      <c r="BW13" s="8">
+        <v>5</v>
+      </c>
+      <c r="BX13" s="8">
+        <v>1</v>
+      </c>
+      <c r="BY13" s="8" t="s">
+        <v>499</v>
+      </c>
       <c r="BZ13" s="8"/>
       <c r="CA13"/>
-      <c r="CN13" s="3"/>
+      <c r="CH13" s="2"/>
+      <c r="CN13" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="CO13">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="AY14" s="5"/>
-      <c r="BV14"/>
-      <c r="BW14"/>
-      <c r="BX14"/>
-      <c r="BY14"/>
-      <c r="BZ14"/>
+      <c r="A14" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="7" t="s">
+        <v>499</v>
+      </c>
+      <c r="L14" s="7"/>
+      <c r="M14"/>
+      <c r="N14"/>
+      <c r="O14" s="7" t="s">
+        <v>496</v>
+      </c>
+      <c r="P14"/>
+      <c r="Q14"/>
+      <c r="R14" s="7"/>
+      <c r="S14" s="7"/>
+      <c r="T14" s="7"/>
+      <c r="U14" s="7"/>
+      <c r="V14" s="7"/>
+      <c r="W14" s="7"/>
+      <c r="X14"/>
+      <c r="AC14">
+        <v>1</v>
+      </c>
+      <c r="AO14" t="s">
+        <v>451</v>
+      </c>
+      <c r="AT14" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="AY14">
+        <v>1</v>
+      </c>
+      <c r="AZ14">
+        <v>1</v>
+      </c>
+      <c r="BD14">
+        <v>1</v>
+      </c>
+      <c r="BU14" s="8"/>
+      <c r="BV14" s="8"/>
+      <c r="BW14" s="8"/>
+      <c r="BX14" s="8"/>
+      <c r="BY14" s="8"/>
+      <c r="BZ14" s="8"/>
       <c r="CA14"/>
-      <c r="CB14" s="5"/>
-      <c r="CC14" s="5"/>
-      <c r="CD14" s="5"/>
-      <c r="CE14" s="5"/>
-      <c r="CF14" s="5"/>
-      <c r="CH14" s="5"/>
-      <c r="CI14" s="5"/>
-      <c r="CJ14" s="5"/>
-      <c r="CK14" s="5"/>
-      <c r="CL14" s="5"/>
-      <c r="CM14" s="5"/>
+      <c r="CB14" t="s">
+        <v>56</v>
+      </c>
+      <c r="CG14" t="s">
+        <v>453</v>
+      </c>
+      <c r="CH14" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="CI14" t="s">
+        <v>435</v>
+      </c>
+      <c r="CN14" s="3"/>
+      <c r="CY14" t="s">
+        <v>454</v>
+      </c>
     </row>
     <row r="15" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="M15"/>
-      <c r="N15"/>
-      <c r="P15" s="3"/>
-      <c r="R15" s="3"/>
-      <c r="S15"/>
-      <c r="X15"/>
+      <c r="A15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="AG15" s="2"/>
+      <c r="AY15" s="5"/>
       <c r="BV15"/>
-      <c r="CB15" s="6"/>
+      <c r="BW15"/>
+      <c r="BX15"/>
+      <c r="BY15"/>
+      <c r="BZ15"/>
+      <c r="CA15"/>
+      <c r="CB15" s="5"/>
+      <c r="CC15" s="5"/>
+      <c r="CD15" s="5"/>
+      <c r="CE15" s="5"/>
+      <c r="CF15" s="5"/>
+      <c r="CH15" s="5"/>
+      <c r="CI15" s="5"/>
+      <c r="CJ15" s="5"/>
+      <c r="CK15" s="5"/>
+      <c r="CL15" s="5"/>
+      <c r="CM15" s="5"/>
     </row>
     <row r="16" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="BV16"/>
-    </row>
-    <row r="17" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="M17"/>
-      <c r="O17"/>
-      <c r="BO17" s="2"/>
-      <c r="BP17" s="2"/>
-      <c r="CN17" s="3"/>
-    </row>
-    <row r="18" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="J18" s="5"/>
+      <c r="A16" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>512</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="G16">
+        <v>3</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>507</v>
+      </c>
+      <c r="M16"/>
+      <c r="N16"/>
+      <c r="P16" s="3"/>
+      <c r="Q16" s="5" t="s">
+        <v>480</v>
+      </c>
+      <c r="R16" s="3"/>
+      <c r="S16"/>
+      <c r="X16"/>
+      <c r="AC16">
+        <v>1</v>
+      </c>
+      <c r="AO16" t="s">
+        <v>451</v>
+      </c>
+      <c r="AV16">
+        <v>20</v>
+      </c>
+      <c r="AY16">
+        <v>1</v>
+      </c>
+      <c r="AZ16">
+        <v>2.5</v>
+      </c>
+      <c r="BD16">
+        <v>99</v>
+      </c>
+      <c r="BT16">
+        <v>0.2</v>
+      </c>
+      <c r="BV16">
+        <v>30</v>
+      </c>
+      <c r="BW16" s="6">
+        <v>20</v>
+      </c>
+      <c r="BX16" s="6">
+        <v>3</v>
+      </c>
+      <c r="BY16" s="6" t="s">
+        <v>499</v>
+      </c>
+      <c r="CB16" t="s">
+        <v>56</v>
+      </c>
+      <c r="CG16" t="s">
+        <v>453</v>
+      </c>
+      <c r="CH16" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="CI16" t="s">
+        <v>435</v>
+      </c>
+      <c r="CN16" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="CO16">
+        <v>0.3</v>
+      </c>
+      <c r="CR16">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="BV17"/>
+    </row>
+    <row r="18" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>514</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="G18">
+        <v>3</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>507</v>
+      </c>
       <c r="M18"/>
-      <c r="O18" s="3"/>
-      <c r="P18"/>
-      <c r="Q18"/>
-      <c r="CN18" s="2"/>
-    </row>
-    <row r="19" spans="1:92" x14ac:dyDescent="0.25">
+      <c r="O18"/>
+      <c r="AC18">
+        <v>1</v>
+      </c>
+      <c r="AG18" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="BD18">
+        <v>1</v>
+      </c>
+      <c r="BO18" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="BP18" s="2"/>
+      <c r="BT18">
+        <v>30</v>
+      </c>
+      <c r="BV18" s="6">
+        <v>45</v>
+      </c>
+      <c r="BW18" s="6">
+        <v>50</v>
+      </c>
+      <c r="BX18" s="6">
+        <v>1</v>
+      </c>
+      <c r="BY18" s="6" t="s">
+        <v>499</v>
+      </c>
+      <c r="CN18" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="CO18">
+        <v>-0.4</v>
+      </c>
+      <c r="CR18">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="J19" s="5"/>
+      <c r="K19" s="5" t="s">
+        <v>472</v>
+      </c>
+      <c r="L19" s="5" t="s">
+        <v>520</v>
+      </c>
       <c r="M19"/>
-      <c r="CB19" s="9"/>
-    </row>
-    <row r="20" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="M20"/>
-      <c r="O20" s="3"/>
-      <c r="P20"/>
-      <c r="Q20"/>
-    </row>
-    <row r="21" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="A21" s="2"/>
-      <c r="M21"/>
-      <c r="O21" s="3"/>
-      <c r="P21"/>
-      <c r="Q21"/>
-      <c r="CN21" s="3"/>
-    </row>
-    <row r="22" spans="1:92" x14ac:dyDescent="0.25">
+      <c r="O19" s="3"/>
+      <c r="P19"/>
+      <c r="Q19"/>
+      <c r="AC19">
+        <v>1</v>
+      </c>
+      <c r="AV19">
+        <v>20</v>
+      </c>
+      <c r="BD19">
+        <v>99</v>
+      </c>
+      <c r="CN19" s="2"/>
+      <c r="CU19" s="2" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="20" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>472</v>
+      </c>
+      <c r="L20" s="5" t="s">
+        <v>523</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="AC20">
+        <v>2</v>
+      </c>
+      <c r="AF20">
+        <v>1</v>
+      </c>
+      <c r="AT20" s="2"/>
+      <c r="BD20">
+        <v>99</v>
+      </c>
+      <c r="BV20"/>
+      <c r="CL20" s="5"/>
+      <c r="CU20" s="2" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="21" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>472</v>
+      </c>
+      <c r="L21" s="5" t="s">
+        <v>532</v>
+      </c>
+      <c r="O21" s="18" t="s">
+        <v>533</v>
+      </c>
+      <c r="AC21">
+        <v>2</v>
+      </c>
+      <c r="AF21">
+        <v>1</v>
+      </c>
+      <c r="AT21" s="2"/>
+      <c r="BD21">
+        <v>1</v>
+      </c>
+      <c r="BV21"/>
+      <c r="CL21" s="5"/>
+      <c r="CN21" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="CR21">
+        <v>9999</v>
+      </c>
+      <c r="CU21" s="2"/>
+    </row>
+    <row r="22" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="J22" s="5"/>
+      <c r="K22" s="5" t="s">
+        <v>472</v>
+      </c>
+      <c r="L22" s="5" t="s">
+        <v>520</v>
+      </c>
       <c r="M22"/>
-      <c r="AY22" s="5"/>
-      <c r="BV22"/>
-      <c r="BW22"/>
-      <c r="BX22"/>
-      <c r="BY22"/>
-      <c r="BZ22"/>
-      <c r="CA22"/>
-      <c r="CB22" s="5"/>
-      <c r="CC22" s="5"/>
-      <c r="CD22" s="5"/>
-      <c r="CE22" s="5"/>
-      <c r="CF22" s="5"/>
-      <c r="CH22" s="5"/>
-      <c r="CI22" s="5"/>
-      <c r="CJ22" s="5"/>
-      <c r="CK22" s="5"/>
-      <c r="CN22" s="3"/>
-    </row>
-    <row r="23" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="M23"/>
-      <c r="O23" s="3"/>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="1:92" x14ac:dyDescent="0.25">
+      <c r="O22" s="3"/>
+      <c r="P22"/>
+      <c r="Q22"/>
+      <c r="AC22">
+        <v>2</v>
+      </c>
+      <c r="AV22">
+        <v>20</v>
+      </c>
+      <c r="BD22">
+        <v>99</v>
+      </c>
+      <c r="CN22" s="2"/>
+      <c r="CU22" s="2" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="23" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>472</v>
+      </c>
+      <c r="L23" s="5" t="s">
+        <v>522</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="AC23">
+        <v>2</v>
+      </c>
+      <c r="AF23">
+        <v>1</v>
+      </c>
+      <c r="AT23" s="2"/>
+      <c r="BD23">
+        <v>99</v>
+      </c>
+      <c r="BV23"/>
+      <c r="CL23" s="5"/>
+      <c r="CU23" s="2" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="24" spans="1:103" x14ac:dyDescent="0.25">
       <c r="M24"/>
-      <c r="N24"/>
+      <c r="AY24" s="5"/>
       <c r="BV24"/>
+      <c r="BW24"/>
+      <c r="BX24"/>
+      <c r="BY24"/>
+      <c r="BZ24"/>
+      <c r="CA24"/>
+      <c r="CB24" s="5"/>
+      <c r="CC24" s="5"/>
+      <c r="CD24" s="5"/>
+      <c r="CE24" s="5"/>
+      <c r="CF24" s="5"/>
+      <c r="CH24" s="5"/>
       <c r="CI24" s="5"/>
       <c r="CJ24" s="5"/>
-    </row>
-    <row r="25" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="M25"/>
-      <c r="N25"/>
-      <c r="BV25"/>
-      <c r="CJ25" s="5"/>
-    </row>
-    <row r="26" spans="1:92" x14ac:dyDescent="0.25">
+      <c r="CK24" s="5"/>
+      <c r="CN24" s="3"/>
+    </row>
+    <row r="25" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="C25" t="s">
+        <v>449</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="O25" s="18" t="s">
+        <v>516</v>
+      </c>
+      <c r="P25" s="7"/>
+      <c r="AC25">
+        <v>1</v>
+      </c>
+      <c r="AO25" t="s">
+        <v>451</v>
+      </c>
+      <c r="AT25" t="s">
+        <v>452</v>
+      </c>
+      <c r="AY25">
+        <v>1</v>
+      </c>
+      <c r="AZ25">
+        <v>1</v>
+      </c>
+      <c r="BD25">
+        <v>3</v>
+      </c>
+      <c r="CB25" t="s">
+        <v>56</v>
+      </c>
+      <c r="CG25" t="s">
+        <v>453</v>
+      </c>
+      <c r="CH25" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="CI25" t="s">
+        <v>435</v>
+      </c>
+      <c r="CN25" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="CR25">
+        <v>9999</v>
+      </c>
+      <c r="CY25" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="26" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="K26" s="5" t="s">
+        <v>499</v>
+      </c>
       <c r="M26"/>
-      <c r="O26" s="3"/>
-      <c r="AG26" s="2"/>
-      <c r="AO26" s="2"/>
-      <c r="BO26" s="2"/>
-      <c r="BP26" s="2"/>
-      <c r="CG26" s="2"/>
-      <c r="CM26" s="2"/>
-    </row>
-    <row r="27" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="A27" s="2"/>
+      <c r="N26"/>
+      <c r="O26" s="18" t="s">
+        <v>516</v>
+      </c>
+      <c r="Q26" s="5" t="s">
+        <v>480</v>
+      </c>
+      <c r="AC26">
+        <v>1</v>
+      </c>
+      <c r="AO26" t="s">
+        <v>451</v>
+      </c>
+      <c r="AV26">
+        <v>20</v>
+      </c>
+      <c r="BD26">
+        <v>1</v>
+      </c>
+      <c r="BS26">
+        <v>0.01</v>
+      </c>
+      <c r="BV26"/>
+      <c r="CI26" s="5"/>
+      <c r="CJ26" s="5"/>
+      <c r="CN26" t="s">
+        <v>538</v>
+      </c>
+      <c r="CR26">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="27" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>499</v>
+      </c>
       <c r="M27"/>
-      <c r="O27" s="3"/>
-      <c r="AG27" s="2"/>
-      <c r="AO27" s="2"/>
-      <c r="CG27" s="2"/>
-    </row>
-    <row r="28" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="BU28" s="6"/>
-      <c r="CA28"/>
-    </row>
-    <row r="29" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="E29" s="2"/>
-      <c r="O29"/>
-      <c r="W29"/>
-      <c r="X29"/>
-      <c r="BO29" s="2"/>
-      <c r="BP29" s="2"/>
-      <c r="CN29" s="3"/>
-    </row>
-    <row r="30" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="M30"/>
-      <c r="O30" s="3"/>
-      <c r="P30"/>
-      <c r="Q30"/>
-      <c r="CN30" s="3"/>
-    </row>
-    <row r="31" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="A31" s="2"/>
-      <c r="M31"/>
-      <c r="O31" s="3"/>
-      <c r="P31"/>
-      <c r="Q31"/>
+      <c r="N27"/>
+      <c r="O27" s="18" t="s">
+        <v>516</v>
+      </c>
+      <c r="Q27" s="5" t="s">
+        <v>529</v>
+      </c>
+      <c r="AC27">
+        <v>2</v>
+      </c>
+      <c r="AV27">
+        <v>20</v>
+      </c>
+      <c r="AX27" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="AZ27">
+        <v>0.8</v>
+      </c>
+      <c r="BD27">
+        <v>99</v>
+      </c>
+      <c r="BV27"/>
+      <c r="CJ27" s="5"/>
+      <c r="CY27" s="2" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="28" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="K28" s="5" t="s">
+        <v>499</v>
+      </c>
+      <c r="M28"/>
+      <c r="O28" s="18" t="s">
+        <v>516</v>
+      </c>
+      <c r="Q28" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="AC28">
+        <v>1</v>
+      </c>
+      <c r="AG28" s="2"/>
+      <c r="AN28">
+        <v>1</v>
+      </c>
+      <c r="AO28" s="2"/>
+      <c r="AV28">
+        <v>20</v>
+      </c>
+      <c r="BD28">
+        <v>99</v>
+      </c>
+      <c r="BO28" s="2"/>
+      <c r="BP28" s="2"/>
+      <c r="CG28" s="2"/>
+      <c r="CM28" s="2"/>
+      <c r="CU28" s="2" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="29" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="K29" s="5" t="s">
+        <v>499</v>
+      </c>
+      <c r="M29"/>
+      <c r="O29" s="18" t="s">
+        <v>516</v>
+      </c>
+      <c r="Q29" s="5" t="s">
+        <v>480</v>
+      </c>
+      <c r="AC29">
+        <v>1</v>
+      </c>
+      <c r="AG29" s="2"/>
+      <c r="AO29" s="2"/>
+      <c r="AV29">
+        <v>20</v>
+      </c>
+      <c r="BD29">
+        <v>99</v>
+      </c>
+      <c r="BS29">
+        <v>0.01</v>
+      </c>
+      <c r="CG29" s="2"/>
+      <c r="CN29" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="CR29">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="30" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="BU30" s="6"/>
+      <c r="CA30"/>
+    </row>
+    <row r="31" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="E31" s="2"/>
+      <c r="O31"/>
+      <c r="W31"/>
+      <c r="X31"/>
+      <c r="BO31" s="2"/>
+      <c r="BP31" s="2"/>
       <c r="CN31" s="3"/>
     </row>
-    <row r="32" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="A32" s="2"/>
+    <row r="32" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="M32"/>
       <c r="O32" s="3"/>
+      <c r="P32"/>
+      <c r="Q32"/>
+      <c r="CN32" s="3"/>
     </row>
     <row r="33" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
-      <c r="CL33" s="5"/>
+      <c r="M33"/>
+      <c r="O33" s="3"/>
+      <c r="P33"/>
+      <c r="Q33"/>
+      <c r="CN33" s="3"/>
     </row>
     <row r="34" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="CL34" s="5"/>
+      <c r="A34" s="2"/>
+      <c r="O34" s="3"/>
     </row>
     <row r="35" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
-      <c r="C35" s="2"/>
-      <c r="J35" s="2"/>
-      <c r="AJ35" s="2"/>
       <c r="CL35" s="5"/>
-      <c r="CU35" s="2"/>
     </row>
     <row r="36" spans="1:99" x14ac:dyDescent="0.25">
       <c r="CL36" s="5"/>
     </row>
     <row r="37" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="O37"/>
-      <c r="W37"/>
-      <c r="X37"/>
-      <c r="CN37" s="3"/>
+      <c r="A37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="J37" s="2"/>
+      <c r="AJ37" s="2"/>
+      <c r="CL37" s="5"/>
+      <c r="CU37" s="2"/>
     </row>
     <row r="38" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="O38" s="3"/>
-      <c r="X38"/>
+      <c r="CL38" s="5"/>
     </row>
     <row r="39" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="O39" s="3"/>
-      <c r="P39"/>
-      <c r="Q39"/>
+      <c r="O39"/>
+      <c r="W39"/>
       <c r="X39"/>
+      <c r="CN39" s="3"/>
     </row>
     <row r="40" spans="1:99" x14ac:dyDescent="0.25">
       <c r="O40" s="3"/>
       <c r="X40"/>
     </row>
-    <row r="43" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="CM43" s="3"/>
-      <c r="CN43" s="3"/>
+    <row r="41" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="O41" s="3"/>
+      <c r="P41"/>
+      <c r="Q41"/>
+      <c r="X41"/>
+    </row>
+    <row r="42" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="O42" s="3"/>
+      <c r="X42"/>
     </row>
     <row r="45" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="M45"/>
-      <c r="N45"/>
-      <c r="BV45"/>
-      <c r="CB45" s="10"/>
-      <c r="CI45" s="5"/>
-      <c r="CJ45" s="5"/>
-    </row>
-    <row r="46" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="M46"/>
-      <c r="N46"/>
-      <c r="BV46"/>
-      <c r="CB46" s="10"/>
-      <c r="CJ46" s="5"/>
+      <c r="CM45" s="3"/>
+      <c r="CN45" s="3"/>
     </row>
     <row r="47" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="O47"/>
-      <c r="X47"/>
-      <c r="CM47" s="3"/>
-    </row>
-    <row r="50" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL50" s="5"/>
-    </row>
-    <row r="51" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL51" s="5"/>
-    </row>
-    <row r="57" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL57" s="5"/>
-    </row>
-    <row r="58" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL58" s="5"/>
-    </row>
-    <row r="60" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="M47"/>
+      <c r="N47"/>
+      <c r="BV47"/>
+      <c r="CB47" s="9"/>
+      <c r="CI47" s="5"/>
+      <c r="CJ47" s="5"/>
+    </row>
+    <row r="48" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="M48"/>
+      <c r="N48"/>
+      <c r="BV48"/>
+      <c r="CB48" s="9"/>
+      <c r="CJ48" s="5"/>
+    </row>
+    <row r="49" spans="15:91" x14ac:dyDescent="0.25">
+      <c r="O49"/>
+      <c r="X49"/>
+      <c r="CM49" s="3"/>
+    </row>
+    <row r="52" spans="15:91" x14ac:dyDescent="0.25">
+      <c r="CL52" s="5"/>
+    </row>
+    <row r="53" spans="15:91" x14ac:dyDescent="0.25">
+      <c r="CL53" s="5"/>
+    </row>
+    <row r="59" spans="15:91" x14ac:dyDescent="0.25">
+      <c r="CL59" s="5"/>
+    </row>
+    <row r="60" spans="15:91" x14ac:dyDescent="0.25">
       <c r="CL60" s="5"/>
     </row>
-    <row r="61" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL61" s="5"/>
-    </row>
-    <row r="62" spans="74:90" x14ac:dyDescent="0.25">
+    <row r="62" spans="15:91" x14ac:dyDescent="0.25">
       <c r="CL62" s="5"/>
     </row>
-    <row r="63" spans="74:90" x14ac:dyDescent="0.25">
+    <row r="63" spans="15:91" x14ac:dyDescent="0.25">
       <c r="CL63" s="5"/>
     </row>
-    <row r="64" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV64"/>
+    <row r="64" spans="15:91" x14ac:dyDescent="0.25">
+      <c r="CL64" s="5"/>
     </row>
     <row r="65" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV65"/>
+      <c r="CL65" s="5"/>
     </row>
     <row r="66" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV66"/>
-      <c r="CL66" s="5"/>
     </row>
     <row r="67" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL67" s="5"/>
+      <c r="BV67"/>
     </row>
     <row r="68" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV68"/>
       <c r="CL68" s="5"/>
     </row>
     <row r="69" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV69"/>
+      <c r="CL69" s="5"/>
     </row>
     <row r="70" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL70" s="5"/>
     </row>
-    <row r="74" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV74"/>
-    </row>
-    <row r="75" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL75" s="5"/>
-    </row>
-    <row r="83" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL83" s="5"/>
-    </row>
-    <row r="84" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL84" s="5"/>
+    <row r="71" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV71"/>
+    </row>
+    <row r="72" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL72" s="5"/>
+    </row>
+    <row r="76" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV76"/>
+    </row>
+    <row r="77" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL77" s="5"/>
     </row>
     <row r="85" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV85"/>
-    </row>
-    <row r="90" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV90"/>
-    </row>
-    <row r="91" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV91"/>
-      <c r="CL91" s="5"/>
+      <c r="CL85" s="5"/>
+    </row>
+    <row r="86" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL86" s="5"/>
+    </row>
+    <row r="87" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV87"/>
     </row>
     <row r="92" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL92" s="5"/>
+      <c r="BV92"/>
     </row>
     <row r="93" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV93"/>
       <c r="CL93" s="5"/>
     </row>
     <row r="94" spans="74:90" x14ac:dyDescent="0.25">
@@ -7829,13 +8636,13 @@
       <c r="CL95" s="5"/>
     </row>
     <row r="96" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV96"/>
+      <c r="CL96" s="5"/>
     </row>
     <row r="97" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL97" s="5"/>
     </row>
     <row r="98" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL98" s="5"/>
+      <c r="BV98"/>
     </row>
     <row r="99" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL99" s="5"/>
@@ -7844,13 +8651,13 @@
       <c r="CL100" s="5"/>
     </row>
     <row r="101" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV101"/>
+      <c r="CL101" s="5"/>
     </row>
     <row r="102" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL102" s="5"/>
     </row>
     <row r="103" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL103" s="5"/>
+      <c r="BV103"/>
     </row>
     <row r="104" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL104" s="5"/>
@@ -7858,11 +8665,11 @@
     <row r="105" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL105" s="5"/>
     </row>
-    <row r="108" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL108" s="5"/>
-    </row>
-    <row r="109" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL109" s="5"/>
+    <row r="106" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL106" s="5"/>
+    </row>
+    <row r="107" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL107" s="5"/>
     </row>
     <row r="110" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL110" s="5"/>
@@ -7873,14 +8680,14 @@
     <row r="112" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL112" s="5"/>
     </row>
+    <row r="113" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL113" s="5"/>
+    </row>
     <row r="114" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV114"/>
-    </row>
-    <row r="115" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL115" s="5"/>
+      <c r="CL114" s="5"/>
     </row>
     <row r="116" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL116" s="5"/>
+      <c r="BV116"/>
     </row>
     <row r="117" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL117" s="5"/>
@@ -7888,20 +8695,20 @@
     <row r="118" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL118" s="5"/>
     </row>
-    <row r="122" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL122" s="5"/>
+    <row r="119" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL119" s="5"/>
+    </row>
+    <row r="120" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL120" s="5"/>
     </row>
     <row r="124" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV124"/>
-    </row>
-    <row r="125" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV125"/>
-      <c r="CL125" s="5"/>
+      <c r="CL124" s="5"/>
     </row>
     <row r="126" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL126" s="5"/>
+      <c r="BV126"/>
     </row>
     <row r="127" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV127"/>
       <c r="CL127" s="5"/>
     </row>
     <row r="128" spans="74:90" x14ac:dyDescent="0.25">
@@ -7910,195 +8717,195 @@
     <row r="129" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL129" s="5"/>
     </row>
+    <row r="130" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL130" s="5"/>
+    </row>
     <row r="131" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV131"/>
-    </row>
-    <row r="132" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL132" s="5"/>
+      <c r="CL131" s="5"/>
     </row>
     <row r="133" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL133" s="5"/>
+      <c r="BV133"/>
+    </row>
+    <row r="134" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL134" s="5"/>
     </row>
     <row r="135" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL135" s="5"/>
     </row>
-    <row r="136" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL136" s="5"/>
+    <row r="137" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL137" s="5"/>
     </row>
     <row r="138" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV138"/>
-    </row>
-    <row r="139" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL139" s="5"/>
-    </row>
-    <row r="142" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL142" s="5"/>
-    </row>
-    <row r="143" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL143" s="5"/>
-    </row>
-    <row r="146" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL146" s="5"/>
+      <c r="CL138" s="5"/>
+    </row>
+    <row r="140" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV140"/>
+    </row>
+    <row r="141" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL141" s="5"/>
+    </row>
+    <row r="144" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL144" s="5"/>
+    </row>
+    <row r="145" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL145" s="5"/>
     </row>
     <row r="148" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL148" s="5"/>
     </row>
     <row r="150" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV150"/>
-    </row>
-    <row r="151" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL151" s="5"/>
+      <c r="CL150" s="5"/>
     </row>
     <row r="152" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL152" s="5"/>
+      <c r="BV152"/>
+    </row>
+    <row r="153" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL153" s="5"/>
     </row>
     <row r="154" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL154" s="5"/>
     </row>
-    <row r="155" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL155" s="5"/>
-    </row>
     <row r="156" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL156" s="5"/>
     </row>
-    <row r="161" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL161" s="5"/>
-    </row>
-    <row r="162" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL162" s="5"/>
-    </row>
-    <row r="165" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL165" s="5"/>
-    </row>
-    <row r="166" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL166" s="5"/>
-    </row>
-    <row r="170" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL170" s="5"/>
-    </row>
-    <row r="174" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL174" s="5"/>
+    <row r="157" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL157" s="5"/>
+    </row>
+    <row r="158" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL158" s="5"/>
+    </row>
+    <row r="163" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL163" s="5"/>
+    </row>
+    <row r="164" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL164" s="5"/>
+    </row>
+    <row r="167" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL167" s="5"/>
+    </row>
+    <row r="168" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL168" s="5"/>
+    </row>
+    <row r="172" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL172" s="5"/>
     </row>
     <row r="176" spans="90:90" x14ac:dyDescent="0.25">
       <c r="CL176" s="5"/>
     </row>
-    <row r="177" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL177" s="5"/>
+    <row r="178" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL178" s="5"/>
     </row>
     <row r="179" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL179" s="5"/>
     </row>
-    <row r="180" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL180" s="5"/>
+    <row r="181" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL181" s="5"/>
     </row>
     <row r="182" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV182"/>
-    </row>
-    <row r="183" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV183"/>
-      <c r="CL183" s="5"/>
+      <c r="CL182" s="5"/>
     </row>
     <row r="184" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL184" s="5"/>
+      <c r="BV184"/>
+    </row>
+    <row r="185" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV185"/>
+      <c r="CL185" s="5"/>
     </row>
     <row r="186" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL186" s="5"/>
     </row>
-    <row r="195" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV195"/>
-    </row>
-    <row r="196" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV196"/>
-      <c r="CL196" s="5"/>
+    <row r="188" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL188" s="5"/>
     </row>
     <row r="197" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL197" s="5"/>
+      <c r="BV197"/>
     </row>
     <row r="198" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV198"/>
       <c r="CL198" s="5"/>
     </row>
     <row r="199" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV199"/>
+      <c r="CL199" s="5"/>
     </row>
     <row r="200" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV200"/>
       <c r="CL200" s="5"/>
     </row>
     <row r="201" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL201" s="5"/>
+      <c r="BV201"/>
+    </row>
+    <row r="202" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV202"/>
+      <c r="CL202" s="5"/>
     </row>
     <row r="203" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV203"/>
-    </row>
-    <row r="204" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV204"/>
-      <c r="CL204" s="5"/>
+      <c r="CL203" s="5"/>
     </row>
     <row r="205" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL205" s="5"/>
+      <c r="BV205"/>
+    </row>
+    <row r="206" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV206"/>
+      <c r="CL206" s="5"/>
     </row>
     <row r="207" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV207"/>
-    </row>
-    <row r="208" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL208" s="5"/>
-    </row>
-    <row r="211" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL211" s="5"/>
-    </row>
-    <row r="215" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL215" s="5"/>
+      <c r="CL207" s="5"/>
+    </row>
+    <row r="209" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV209"/>
+    </row>
+    <row r="210" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL210" s="5"/>
+    </row>
+    <row r="213" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL213" s="5"/>
     </row>
     <row r="217" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV217"/>
-    </row>
-    <row r="218" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL218" s="5"/>
-    </row>
-    <row r="225" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV225"/>
-    </row>
-    <row r="226" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL226" s="5"/>
+      <c r="CL217" s="5"/>
+    </row>
+    <row r="219" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV219"/>
+    </row>
+    <row r="220" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL220" s="5"/>
     </row>
     <row r="227" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL227" s="5"/>
+      <c r="BV227"/>
+    </row>
+    <row r="228" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL228" s="5"/>
     </row>
     <row r="229" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV229"/>
-    </row>
-    <row r="230" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV230"/>
-      <c r="CL230" s="5"/>
+      <c r="CL229" s="5"/>
     </row>
     <row r="231" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL231" s="5"/>
-    </row>
-    <row r="237" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV237"/>
-    </row>
-    <row r="238" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV238"/>
-      <c r="CL238" s="5"/>
+      <c r="BV231"/>
+    </row>
+    <row r="232" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV232"/>
+      <c r="CL232" s="5"/>
+    </row>
+    <row r="233" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL233" s="5"/>
     </row>
     <row r="239" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV239"/>
-      <c r="CL239" s="5"/>
     </row>
     <row r="240" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV240"/>
       <c r="CL240" s="5"/>
     </row>
-    <row r="245" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV245"/>
-    </row>
-    <row r="246" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV246"/>
-    </row>
-    <row r="250" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV250"/>
-    </row>
-    <row r="251" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL251" s="5"/>
+    <row r="241" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV241"/>
+      <c r="CL241" s="5"/>
+    </row>
+    <row r="242" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL242" s="5"/>
+    </row>
+    <row r="247" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV247"/>
+    </row>
+    <row r="248" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV248"/>
     </row>
     <row r="252" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV252"/>
@@ -8106,46 +8913,44 @@
     <row r="253" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL253" s="5"/>
     </row>
-    <row r="263" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV263"/>
-    </row>
-    <row r="264" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL264" s="5"/>
+    <row r="254" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV254"/>
+    </row>
+    <row r="255" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL255" s="5"/>
+    </row>
+    <row r="265" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV265"/>
     </row>
     <row r="266" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV266"/>
-    </row>
-    <row r="267" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL267" s="5"/>
-    </row>
-    <row r="275" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV275"/>
-    </row>
-    <row r="276" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL276" s="5"/>
-    </row>
-    <row r="280" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV280"/>
-    </row>
-    <row r="281" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL281" s="5"/>
+      <c r="CL266" s="5"/>
+    </row>
+    <row r="268" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV268"/>
+    </row>
+    <row r="269" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL269" s="5"/>
+    </row>
+    <row r="277" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV277"/>
+    </row>
+    <row r="278" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL278" s="5"/>
+    </row>
+    <row r="282" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV282"/>
     </row>
     <row r="283" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV283"/>
-    </row>
-    <row r="284" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL284" s="5"/>
-    </row>
-    <row r="300" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV300"/>
-    </row>
-    <row r="301" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV301"/>
-      <c r="CL301" s="5"/>
+      <c r="CL283" s="5"/>
+    </row>
+    <row r="285" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV285"/>
+    </row>
+    <row r="286" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL286" s="5"/>
     </row>
     <row r="302" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV302"/>
-      <c r="CL302" s="5"/>
     </row>
     <row r="303" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV303"/>
@@ -8153,52 +8958,54 @@
     </row>
     <row r="304" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV304"/>
+      <c r="CL304" s="5"/>
+    </row>
+    <row r="305" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV305"/>
+      <c r="CL305" s="5"/>
     </row>
     <row r="306" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV306"/>
     </row>
-    <row r="307" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV307"/>
-      <c r="CL307" s="5"/>
-    </row>
     <row r="308" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV308"/>
-      <c r="CL308" s="5"/>
     </row>
     <row r="309" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV309"/>
       <c r="CL309" s="5"/>
     </row>
-    <row r="313" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV313"/>
-    </row>
-    <row r="314" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL314" s="5"/>
+    <row r="310" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV310"/>
+      <c r="CL310" s="5"/>
+    </row>
+    <row r="311" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL311" s="5"/>
+    </row>
+    <row r="315" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV315"/>
     </row>
     <row r="316" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV316"/>
-    </row>
-    <row r="317" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV317"/>
-      <c r="CL317" s="5"/>
+      <c r="CL316" s="5"/>
     </row>
     <row r="318" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV318"/>
-      <c r="CL318" s="5"/>
     </row>
     <row r="319" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV319"/>
       <c r="CL319" s="5"/>
     </row>
-    <row r="335" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV335"/>
-    </row>
-    <row r="336" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL336" s="5"/>
-    </row>
-    <row r="344" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL344" s="5"/>
-    </row>
-    <row r="345" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL345" s="5"/>
+    <row r="320" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV320"/>
+      <c r="CL320" s="5"/>
+    </row>
+    <row r="321" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL321" s="5"/>
+    </row>
+    <row r="337" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV337"/>
+    </row>
+    <row r="338" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL338" s="5"/>
     </row>
     <row r="346" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL346" s="5"/>
@@ -8209,35 +9016,38 @@
     <row r="348" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL348" s="5"/>
     </row>
+    <row r="349" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL349" s="5"/>
+    </row>
     <row r="350" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV350"/>
-    </row>
-    <row r="351" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL351" s="5"/>
+      <c r="CL350" s="5"/>
     </row>
     <row r="352" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV352"/>
     </row>
     <row r="353" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV353"/>
       <c r="CL353" s="5"/>
     </row>
     <row r="354" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL354" s="5"/>
+      <c r="BV354"/>
+    </row>
+    <row r="355" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV355"/>
+      <c r="CL355" s="5"/>
     </row>
     <row r="356" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV356"/>
-    </row>
-    <row r="357" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV357"/>
-      <c r="CL357" s="5"/>
+      <c r="CL356" s="5"/>
     </row>
     <row r="358" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV358"/>
-      <c r="CL358" s="5"/>
     </row>
     <row r="359" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV359"/>
       <c r="CL359" s="5"/>
+    </row>
+    <row r="360" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV360"/>
+      <c r="CL360" s="5"/>
     </row>
     <row r="361" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL361" s="5"/>
@@ -8248,11 +9058,8 @@
     <row r="365" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL365" s="5"/>
     </row>
-    <row r="368" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL368" s="5"/>
-    </row>
-    <row r="369" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL369" s="5"/>
+    <row r="367" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL367" s="5"/>
     </row>
     <row r="370" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL370" s="5"/>
@@ -8267,20 +9074,20 @@
       <c r="CL373" s="5"/>
     </row>
     <row r="374" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV374"/>
+      <c r="CL374" s="5"/>
     </row>
     <row r="375" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV375"/>
       <c r="CL375" s="5"/>
     </row>
     <row r="376" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV376"/>
-      <c r="CL376" s="5"/>
     </row>
     <row r="377" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV377"/>
       <c r="CL377" s="5"/>
     </row>
     <row r="378" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV378"/>
       <c r="CL378" s="5"/>
     </row>
     <row r="379" spans="74:90" x14ac:dyDescent="0.25">
@@ -8289,72 +9096,75 @@
     <row r="380" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL380" s="5"/>
     </row>
+    <row r="381" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL381" s="5"/>
+    </row>
     <row r="382" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL382" s="5"/>
     </row>
-    <row r="383" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL383" s="5"/>
-    </row>
     <row r="384" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV384"/>
+      <c r="CL384" s="5"/>
     </row>
     <row r="385" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV385"/>
       <c r="CL385" s="5"/>
     </row>
     <row r="386" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV386"/>
-      <c r="CL386" s="5"/>
     </row>
     <row r="387" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV387"/>
       <c r="CL387" s="5"/>
     </row>
     <row r="388" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV388"/>
       <c r="CL388" s="5"/>
+    </row>
+    <row r="389" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL389" s="5"/>
     </row>
     <row r="390" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL390" s="5"/>
     </row>
-    <row r="391" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL391" s="5"/>
-    </row>
     <row r="392" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV392"/>
       <c r="CL392" s="5"/>
     </row>
     <row r="393" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV393"/>
       <c r="CL393" s="5"/>
     </row>
     <row r="394" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV394"/>
       <c r="CL394" s="5"/>
     </row>
     <row r="395" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV395"/>
       <c r="CL395" s="5"/>
     </row>
     <row r="396" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL396" s="5"/>
     </row>
+    <row r="397" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL397" s="5"/>
+    </row>
     <row r="398" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV398"/>
       <c r="CL398" s="5"/>
     </row>
-    <row r="399" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL399" s="5"/>
-    </row>
     <row r="400" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV400"/>
       <c r="CL400" s="5"/>
     </row>
+    <row r="401" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL401" s="5"/>
+    </row>
     <row r="402" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV402"/>
       <c r="CL402" s="5"/>
     </row>
-    <row r="403" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV403"/>
-      <c r="CL403" s="5"/>
-    </row>
     <row r="404" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV404"/>
       <c r="CL404" s="5"/>
+    </row>
+    <row r="405" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV405"/>
+      <c r="CL405" s="5"/>
     </row>
     <row r="406" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL406" s="5"/>
@@ -8362,47 +9172,44 @@
     <row r="408" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL408" s="5"/>
     </row>
-    <row r="411" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL411" s="5"/>
-    </row>
-    <row r="412" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL412" s="5"/>
-    </row>
-    <row r="416" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV416"/>
-    </row>
-    <row r="417" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV417"/>
-      <c r="CL417" s="5"/>
+    <row r="410" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL410" s="5"/>
+    </row>
+    <row r="413" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL413" s="5"/>
+    </row>
+    <row r="414" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL414" s="5"/>
     </row>
     <row r="418" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV418"/>
-      <c r="CL418" s="5"/>
     </row>
     <row r="419" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV419"/>
       <c r="CL419" s="5"/>
     </row>
     <row r="420" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV420"/>
       <c r="CL420" s="5"/>
     </row>
     <row r="421" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV421"/>
+      <c r="CL421" s="5"/>
     </row>
     <row r="422" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL422" s="5"/>
     </row>
+    <row r="423" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV423"/>
+    </row>
     <row r="424" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL424" s="5"/>
     </row>
-    <row r="425" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL425" s="5"/>
+    <row r="426" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL426" s="5"/>
     </row>
     <row r="427" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL427" s="5"/>
     </row>
-    <row r="428" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL428" s="5"/>
-    </row>
     <row r="429" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL429" s="5"/>
     </row>
@@ -8418,79 +9225,77 @@
     <row r="433" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL433" s="5"/>
     </row>
+    <row r="434" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL434" s="5"/>
+    </row>
     <row r="435" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV435"/>
-    </row>
-    <row r="436" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL436" s="5"/>
+      <c r="CL435" s="5"/>
     </row>
     <row r="437" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL437" s="5"/>
-    </row>
-    <row r="470" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BU470" s="11"/>
-      <c r="BV470" s="12"/>
-    </row>
-    <row r="471" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="H471" s="11"/>
-      <c r="CL471" s="11"/>
-    </row>
-    <row r="477" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BV477"/>
-    </row>
-    <row r="478" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BV478"/>
-      <c r="CL478" s="5"/>
+      <c r="BV437"/>
+    </row>
+    <row r="438" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL438" s="5"/>
+    </row>
+    <row r="439" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL439" s="5"/>
+    </row>
+    <row r="472" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BU472" s="10"/>
+      <c r="BV472" s="11"/>
+    </row>
+    <row r="473" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="H473" s="10"/>
+      <c r="CL473" s="10"/>
     </row>
     <row r="479" spans="8:90" x14ac:dyDescent="0.25">
       <c r="BV479"/>
-      <c r="CL479" s="5"/>
     </row>
     <row r="480" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV480"/>
       <c r="CL480" s="5"/>
     </row>
-    <row r="497" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV497"/>
-    </row>
-    <row r="498" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL498" s="5"/>
-    </row>
-    <row r="530" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV530"/>
-    </row>
-    <row r="531" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV531"/>
-      <c r="CL531" s="5"/>
+    <row r="481" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV481"/>
+      <c r="CL481" s="5"/>
+    </row>
+    <row r="482" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL482" s="5"/>
+    </row>
+    <row r="499" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV499"/>
+    </row>
+    <row r="500" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL500" s="5"/>
     </row>
     <row r="532" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL532" s="5"/>
-    </row>
-    <row r="548" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV548"/>
-    </row>
-    <row r="549" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL549" s="5"/>
-    </row>
-    <row r="555" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV555"/>
-    </row>
-    <row r="556" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV556"/>
-      <c r="CL556" s="5"/>
+      <c r="BV532"/>
+    </row>
+    <row r="533" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV533"/>
+      <c r="CL533" s="5"/>
+    </row>
+    <row r="534" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL534" s="5"/>
+    </row>
+    <row r="550" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV550"/>
+    </row>
+    <row r="551" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL551" s="5"/>
     </row>
     <row r="557" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL557" s="5"/>
-    </row>
-    <row r="562" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV562"/>
-    </row>
-    <row r="563" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV563"/>
-      <c r="CL563" s="5"/>
+      <c r="BV557"/>
+    </row>
+    <row r="558" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV558"/>
+      <c r="CL558" s="5"/>
+    </row>
+    <row r="559" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL559" s="5"/>
     </row>
     <row r="564" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV564"/>
-      <c r="CL564" s="5"/>
     </row>
     <row r="565" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV565"/>
@@ -8545,44 +9350,44 @@
       <c r="CL577" s="5"/>
     </row>
     <row r="578" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV578"/>
       <c r="CL578" s="5"/>
     </row>
-    <row r="582" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV582"/>
-    </row>
-    <row r="583" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV583"/>
-      <c r="CL583" s="5"/>
+    <row r="579" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV579"/>
+      <c r="CL579" s="5"/>
+    </row>
+    <row r="580" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL580" s="5"/>
     </row>
     <row r="584" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL584" s="5"/>
+      <c r="BV584"/>
     </row>
     <row r="585" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV585"/>
+      <c r="CL585" s="5"/>
     </row>
     <row r="586" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL586" s="5"/>
     </row>
-    <row r="589" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV589"/>
-    </row>
-    <row r="590" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV590"/>
-      <c r="CL590" s="5"/>
+    <row r="587" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV587"/>
+    </row>
+    <row r="588" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL588" s="5"/>
     </row>
     <row r="591" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL591" s="5"/>
-    </row>
-    <row r="622" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV622"/>
-    </row>
-    <row r="623" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV623"/>
-      <c r="CL623" s="5"/>
-    </row>
-    <row r="624" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV591"/>
+    </row>
+    <row r="592" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV592"/>
+      <c r="CL592" s="5"/>
+    </row>
+    <row r="593" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL593" s="5"/>
+    </row>
+    <row r="624" spans="74:74" x14ac:dyDescent="0.25">
       <c r="BV624"/>
-      <c r="CL624" s="5"/>
     </row>
     <row r="625" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV625"/>
@@ -8605,132 +9410,132 @@
       <c r="CL629" s="5"/>
     </row>
     <row r="630" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV630"/>
       <c r="CL630" s="5"/>
     </row>
+    <row r="631" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV631"/>
+      <c r="CL631" s="5"/>
+    </row>
     <row r="632" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV632"/>
-    </row>
-    <row r="633" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL633" s="5"/>
-    </row>
-    <row r="637" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV637"/>
-    </row>
-    <row r="638" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL638" s="5"/>
-    </row>
-    <row r="641" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV641"/>
-    </row>
-    <row r="642" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV642"/>
-      <c r="CL642" s="5"/>
+      <c r="CL632" s="5"/>
+    </row>
+    <row r="634" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV634"/>
+    </row>
+    <row r="635" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL635" s="5"/>
+    </row>
+    <row r="639" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV639"/>
+    </row>
+    <row r="640" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL640" s="5"/>
     </row>
     <row r="643" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV643"/>
-      <c r="CL643" s="5"/>
     </row>
     <row r="644" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV644"/>
       <c r="CL644" s="5"/>
     </row>
     <row r="645" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV645"/>
       <c r="CL645" s="5"/>
     </row>
-    <row r="652" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV652"/>
-    </row>
-    <row r="653" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL653" s="5"/>
-    </row>
-    <row r="656" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV656"/>
-    </row>
-    <row r="657" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV657"/>
-      <c r="CL657" s="5"/>
+    <row r="646" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV646"/>
+      <c r="CL646" s="5"/>
+    </row>
+    <row r="647" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL647" s="5"/>
+    </row>
+    <row r="654" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV654"/>
+    </row>
+    <row r="655" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL655" s="5"/>
     </row>
     <row r="658" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV658"/>
-      <c r="CL658" s="5"/>
     </row>
     <row r="659" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV659"/>
       <c r="CL659" s="5"/>
     </row>
     <row r="660" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV660"/>
       <c r="CL660" s="5"/>
     </row>
+    <row r="661" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV661"/>
+      <c r="CL661" s="5"/>
+    </row>
     <row r="662" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV662"/>
-    </row>
-    <row r="663" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV663"/>
-      <c r="CL663" s="5"/>
+      <c r="CL662" s="5"/>
     </row>
     <row r="664" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL664" s="5"/>
+      <c r="BV664"/>
     </row>
     <row r="665" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL665">
-        <v>0.15</v>
-      </c>
+      <c r="BV665"/>
+      <c r="CL665" s="5"/>
+    </row>
+    <row r="666" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL666" s="5"/>
     </row>
     <row r="667" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL667">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="669" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL669">
         <v>0.2</v>
-      </c>
-    </row>
-    <row r="668" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL668">
-        <v>0.1</v>
       </c>
     </row>
     <row r="670" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL670">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="672" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL672">
         <v>0.2</v>
       </c>
     </row>
-    <row r="677" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL677">
+    <row r="679" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL679">
         <v>1</v>
       </c>
     </row>
-    <row r="679" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL679">
+    <row r="681" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL681">
         <v>0.4</v>
       </c>
     </row>
-    <row r="680" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL680">
+    <row r="682" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL682">
         <v>0.6</v>
       </c>
     </row>
-    <row r="683" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL683">
+    <row r="685" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL685">
         <v>0.5</v>
       </c>
     </row>
-    <row r="684" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL684">
+    <row r="686" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL686">
         <v>0.66700000000000004</v>
       </c>
     </row>
-    <row r="685" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL685">
+    <row r="687" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL687">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="688" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV688"/>
-    </row>
-    <row r="689" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV689"/>
-      <c r="CL689" s="5"/>
     </row>
     <row r="690" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV690"/>
-      <c r="CL690" s="5"/>
     </row>
     <row r="691" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV691"/>
@@ -8757,24 +9562,24 @@
       <c r="CL696" s="5"/>
     </row>
     <row r="697" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV697"/>
       <c r="CL697" s="5"/>
     </row>
     <row r="698" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV698"/>
+      <c r="CL698" s="5"/>
     </row>
     <row r="699" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL699" s="5"/>
     </row>
-    <row r="708" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV708"/>
-    </row>
-    <row r="709" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV709"/>
-      <c r="CL709" s="5"/>
+    <row r="700" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV700"/>
+    </row>
+    <row r="701" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL701" s="5"/>
     </row>
     <row r="710" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV710"/>
-      <c r="CL710" s="5"/>
     </row>
     <row r="711" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV711"/>
@@ -8797,124 +9602,124 @@
       <c r="CL715" s="5"/>
     </row>
     <row r="716" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV716"/>
       <c r="CL716" s="5"/>
     </row>
     <row r="717" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV717"/>
+      <c r="CL717" s="5"/>
     </row>
     <row r="718" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL718" s="5"/>
     </row>
-    <row r="723" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV723"/>
-    </row>
-    <row r="724" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV724"/>
-      <c r="CL724" s="5"/>
+    <row r="719" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV719"/>
+    </row>
+    <row r="720" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL720" s="5"/>
     </row>
     <row r="725" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL725" s="5"/>
+      <c r="BV725"/>
     </row>
     <row r="726" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV726"/>
+      <c r="CL726" s="5"/>
     </row>
     <row r="727" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV727"/>
       <c r="CL727" s="5"/>
     </row>
     <row r="728" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL728" s="5"/>
+      <c r="BV728"/>
     </row>
     <row r="729" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV729"/>
+      <c r="CL729" s="5"/>
     </row>
     <row r="730" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV730"/>
       <c r="CL730" s="5"/>
     </row>
     <row r="731" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV731"/>
-      <c r="CL731" s="5"/>
     </row>
     <row r="732" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV732"/>
       <c r="CL732" s="5"/>
     </row>
     <row r="733" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV733"/>
       <c r="CL733" s="5"/>
     </row>
-    <row r="737" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BV737"/>
-    </row>
-    <row r="738" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BV738"/>
-      <c r="CL738" s="5"/>
+    <row r="734" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV734"/>
+      <c r="CL734" s="5"/>
+    </row>
+    <row r="735" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL735" s="5"/>
     </row>
     <row r="739" spans="8:90" x14ac:dyDescent="0.25">
       <c r="BV739"/>
-      <c r="CL739" s="5"/>
     </row>
     <row r="740" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV740"/>
       <c r="CL740" s="5"/>
     </row>
     <row r="741" spans="8:90" x14ac:dyDescent="0.25">
       <c r="BV741"/>
+      <c r="CL741" s="5"/>
     </row>
     <row r="742" spans="8:90" x14ac:dyDescent="0.25">
       <c r="CL742" s="5"/>
     </row>
     <row r="743" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BU743" s="11"/>
-      <c r="BV743" s="12"/>
+      <c r="BV743"/>
     </row>
     <row r="744" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="H744" s="11"/>
-      <c r="CL744" s="11"/>
-    </row>
-    <row r="761" spans="73:90" x14ac:dyDescent="0.25">
-      <c r="BV761"/>
-    </row>
-    <row r="762" spans="73:90" x14ac:dyDescent="0.25">
-      <c r="BV762"/>
-      <c r="CL762" s="5"/>
-    </row>
-    <row r="763" spans="73:90" x14ac:dyDescent="0.25">
+      <c r="CL744" s="5"/>
+    </row>
+    <row r="745" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BU745" s="10"/>
+      <c r="BV745" s="11"/>
+    </row>
+    <row r="746" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="H746" s="10"/>
+      <c r="CL746" s="10"/>
+    </row>
+    <row r="763" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV763"/>
-      <c r="CL763" s="5"/>
-    </row>
-    <row r="764" spans="73:90" x14ac:dyDescent="0.25">
+    </row>
+    <row r="764" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV764"/>
       <c r="CL764" s="5"/>
     </row>
-    <row r="765" spans="73:90" x14ac:dyDescent="0.25">
+    <row r="765" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV765"/>
       <c r="CL765" s="5"/>
     </row>
-    <row r="766" spans="73:90" x14ac:dyDescent="0.25">
+    <row r="766" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV766"/>
-    </row>
-    <row r="767" spans="73:90" x14ac:dyDescent="0.25">
-      <c r="BV767"/>
+      <c r="CL766" s="5"/>
+    </row>
+    <row r="767" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL767" s="5"/>
     </row>
-    <row r="768" spans="73:90" x14ac:dyDescent="0.25">
-      <c r="BU768" s="11"/>
-      <c r="BV768" s="12"/>
-      <c r="CL768" s="5"/>
+    <row r="768" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV768"/>
     </row>
     <row r="769" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="H769" s="11"/>
-      <c r="CL769" s="11"/>
-    </row>
-    <row r="772" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BV772"/>
-    </row>
-    <row r="773" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BV773"/>
-      <c r="CL773" s="5"/>
+      <c r="BV769"/>
+      <c r="CL769" s="5"/>
+    </row>
+    <row r="770" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BU770" s="10"/>
+      <c r="BV770" s="11"/>
+      <c r="CL770" s="5"/>
+    </row>
+    <row r="771" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="H771" s="10"/>
+      <c r="CL771" s="10"/>
     </row>
     <row r="774" spans="8:90" x14ac:dyDescent="0.25">
       <c r="BV774"/>
-      <c r="CL774" s="5"/>
     </row>
     <row r="775" spans="8:90" x14ac:dyDescent="0.25">
       <c r="BV775"/>
@@ -8937,18 +9742,18 @@
       <c r="CL779" s="5"/>
     </row>
     <row r="780" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV780"/>
       <c r="CL780" s="5"/>
     </row>
+    <row r="781" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV781"/>
+      <c r="CL781" s="5"/>
+    </row>
     <row r="782" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BV782"/>
-    </row>
-    <row r="783" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BV783"/>
-      <c r="CL783" s="5"/>
+      <c r="CL782" s="5"/>
     </row>
     <row r="784" spans="8:90" x14ac:dyDescent="0.25">
       <c r="BV784"/>
-      <c r="CL784" s="5"/>
     </row>
     <row r="785" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV785"/>
@@ -8963,18 +9768,18 @@
       <c r="CL787" s="5"/>
     </row>
     <row r="788" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV788"/>
       <c r="CL788" s="5"/>
     </row>
     <row r="789" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV789"/>
+      <c r="CL789" s="5"/>
     </row>
     <row r="790" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV790"/>
       <c r="CL790" s="5"/>
     </row>
     <row r="791" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV791"/>
-      <c r="CL791" s="5"/>
     </row>
     <row r="792" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV792"/>
@@ -9085,24 +9890,32 @@
       <c r="CL818" s="5"/>
     </row>
     <row r="819" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV819"/>
       <c r="CL819" s="5"/>
     </row>
     <row r="820" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV820"/>
+      <c r="CL820" s="5"/>
     </row>
     <row r="821" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV821"/>
       <c r="CL821" s="5"/>
     </row>
     <row r="822" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV822"/>
-      <c r="CL822" s="5"/>
     </row>
     <row r="823" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV823"/>
       <c r="CL823" s="5"/>
     </row>
+    <row r="824" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV824"/>
+      <c r="CL824" s="5"/>
+    </row>
+    <row r="825" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL825" s="5"/>
+    </row>
   </sheetData>
-  <phoneticPr fontId="15" type="noConversion"/>
+  <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <legacyDrawing r:id="rId1"/>
@@ -9111,7 +9924,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.08203125" customWidth="1"/>
@@ -9268,37 +10081,113 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>467</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>469</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>470</v>
       </c>
       <c r="H6">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="J7"/>
-      <c r="P7"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="Q9" s="2"/>
+        <v>470</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8" s="2"/>
+      <c r="C8" s="3"/>
+      <c r="Q8" s="2"/>
+    </row>
+    <row r="9" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="I9" s="3">
+        <v>1</v>
+      </c>
+      <c r="J9"/>
+      <c r="K9" s="3">
+        <v>99999</v>
+      </c>
+      <c r="P9"/>
+      <c r="Q9" s="3" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>467</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="15" type="noConversion"/>
+  <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -9352,17 +10241,17 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="B4" t="s">
         <v>458</v>
       </c>
-      <c r="B4" t="s">
+      <c r="D4" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>460</v>
-      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="15" type="noConversion"/>
+  <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -9370,7 +10259,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.25" customWidth="1"/>
@@ -9450,7 +10339,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B4" t="s">
         <v>455</v>
@@ -9465,14 +10354,37 @@
         <v>1</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="J4" s="2" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="B5" t="s">
+        <v>455</v>
+      </c>
+      <c r="C5" t="s">
+        <v>456</v>
+      </c>
+      <c r="E5">
+        <v>10</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>457</v>
       </c>
+      <c r="J5" s="2" t="s">
+        <v>521</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="15" type="noConversion"/>
+  <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -9602,7 +10514,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="15" type="noConversion"/>
+  <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <legacyDrawing r:id="rId1"/>
@@ -9688,7 +10600,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="15" type="noConversion"/>
+  <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -9824,7 +10736,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="15" type="noConversion"/>
+  <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Excel/Diy优胜/萃儿.xlsx
+++ b/Excel/Diy优胜/萃儿.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Diy优胜\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDFB323C-15AF-4C7C-AB6A-6BCFE59CC60F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AE32AE7-9C06-49BB-B275-36BE5FCD33B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3740" yWindow="3843" windowWidth="17954" windowHeight="10398" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -302,7 +302,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="553">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="554">
   <si>
     <t>Id</t>
   </si>
@@ -1115,9 +1115,6 @@
   </si>
   <si>
     <t>PosLimit</t>
-  </si>
-  <si>
-    <t>CostLimit</t>
   </si>
   <si>
     <t>MidLimit</t>
@@ -1822,10 +1819,6 @@
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>萃蔓去重</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
     <t>自己以外</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
@@ -1842,10 +1835,6 @@
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>萃蔓去重,生成萃蔓1,萃蔓效果,萃蔓无敌</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
     <t>萃儿1</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
@@ -2065,7 +2054,23 @@
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>萃蔓去重,萃蔓效果,萃蔓无敌</t>
+    <t>CostLimit</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>萃蔓</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>#萃蔓去重</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>萃蔓效果,萃蔓无敌</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>生成萃蔓1,萃蔓效果,萃蔓无敌</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
 </sst>
@@ -2619,10 +2624,10 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
   </sheetData>
@@ -3230,14 +3235,14 @@
     </row>
     <row r="5" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>125</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -3279,16 +3284,16 @@
         <v>1</v>
       </c>
       <c r="AG5" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AH5" s="2" t="s">
         <v>126</v>
       </c>
       <c r="AI5" s="2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AJ5" s="2" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="AK5">
         <v>0</v>
@@ -3309,10 +3314,10 @@
         <v>0.25</v>
       </c>
       <c r="BB5" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="BD5" s="2" t="s">
         <v>447</v>
-      </c>
-      <c r="BD5" s="2" t="s">
-        <v>448</v>
       </c>
       <c r="BE5" s="2" t="s">
         <v>127</v>
@@ -3350,14 +3355,14 @@
     </row>
     <row r="6" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A6" s="17" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E6" s="12"/>
       <c r="F6" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -3402,13 +3407,13 @@
         <v>0</v>
       </c>
       <c r="AG6" s="17" t="s">
-        <v>438</v>
+        <v>550</v>
       </c>
       <c r="AH6" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AI6" s="2" t="s">
-        <v>495</v>
+        <v>553</v>
       </c>
       <c r="AJ6" s="2"/>
       <c r="AK6">
@@ -3434,11 +3439,11 @@
         <v>0.25</v>
       </c>
       <c r="BB6" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="BD6" s="2"/>
       <c r="BL6" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="BM6" s="2"/>
       <c r="BN6" s="2"/>
@@ -3448,14 +3453,14 @@
     </row>
     <row r="7" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E7" s="12"/>
       <c r="F7" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -3500,10 +3505,10 @@
         <v>0</v>
       </c>
       <c r="AG7" s="17" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AH7" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AI7" s="2" t="s">
         <v>552</v>
@@ -3532,11 +3537,11 @@
         <v>0.25</v>
       </c>
       <c r="BB7" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="BD7" s="2"/>
       <c r="BL7" s="2" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="BM7" s="2"/>
       <c r="BN7" s="2"/>
@@ -6579,10 +6584,10 @@
         <v>173</v>
       </c>
       <c r="AR1" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AS1" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AT1" t="s">
         <v>174</v>
@@ -6898,230 +6903,230 @@
       <c r="AL2" t="s">
         <v>270</v>
       </c>
-      <c r="AM2" t="s">
+      <c r="AM2" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="AN2" t="s">
         <v>271</v>
       </c>
-      <c r="AN2" t="s">
+      <c r="AO2" t="s">
         <v>272</v>
       </c>
-      <c r="AO2" t="s">
+      <c r="AP2" t="s">
         <v>273</v>
       </c>
-      <c r="AP2" t="s">
+      <c r="AQ2" t="s">
         <v>274</v>
       </c>
-      <c r="AQ2" t="s">
+      <c r="AR2" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="AS2" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="AT2" t="s">
         <v>275</v>
       </c>
-      <c r="AR2" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="AS2" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="AT2" t="s">
+      <c r="AU2" t="s">
         <v>276</v>
       </c>
-      <c r="AU2" t="s">
+      <c r="AV2" t="s">
         <v>277</v>
       </c>
-      <c r="AV2" t="s">
+      <c r="AW2" t="s">
         <v>278</v>
       </c>
-      <c r="AW2" t="s">
+      <c r="AX2" t="s">
         <v>279</v>
       </c>
-      <c r="AX2" t="s">
+      <c r="AY2" t="s">
         <v>280</v>
       </c>
-      <c r="AY2" t="s">
+      <c r="AZ2" t="s">
         <v>281</v>
       </c>
-      <c r="AZ2" t="s">
+      <c r="BA2" t="s">
         <v>282</v>
       </c>
-      <c r="BA2" t="s">
+      <c r="BB2" t="s">
         <v>283</v>
       </c>
-      <c r="BB2" t="s">
+      <c r="BC2" t="s">
         <v>284</v>
       </c>
-      <c r="BC2" t="s">
+      <c r="BD2" t="s">
         <v>285</v>
       </c>
-      <c r="BD2" t="s">
+      <c r="BE2" t="s">
         <v>286</v>
       </c>
-      <c r="BE2" t="s">
+      <c r="BF2" t="s">
         <v>287</v>
       </c>
-      <c r="BF2" t="s">
+      <c r="BG2" t="s">
         <v>288</v>
       </c>
-      <c r="BG2" t="s">
+      <c r="BH2" t="s">
         <v>289</v>
       </c>
-      <c r="BH2" t="s">
+      <c r="BI2" t="s">
         <v>290</v>
       </c>
-      <c r="BI2" t="s">
+      <c r="BJ2" t="s">
         <v>291</v>
       </c>
-      <c r="BJ2" t="s">
+      <c r="BK2" t="s">
         <v>292</v>
       </c>
-      <c r="BK2" t="s">
+      <c r="BL2" t="s">
         <v>293</v>
       </c>
-      <c r="BL2" t="s">
+      <c r="BM2" t="s">
         <v>294</v>
       </c>
-      <c r="BM2" t="s">
+      <c r="BN2" t="s">
         <v>295</v>
-      </c>
-      <c r="BN2" t="s">
-        <v>296</v>
       </c>
       <c r="BO2" t="s">
         <v>78</v>
       </c>
       <c r="BP2" t="s">
+        <v>296</v>
+      </c>
+      <c r="BQ2" t="s">
         <v>297</v>
       </c>
-      <c r="BQ2" t="s">
+      <c r="BR2" t="s">
         <v>298</v>
       </c>
-      <c r="BR2" t="s">
+      <c r="BS2" t="s">
         <v>299</v>
       </c>
-      <c r="BS2" t="s">
+      <c r="BT2" t="s">
         <v>300</v>
-      </c>
-      <c r="BT2" t="s">
-        <v>301</v>
       </c>
       <c r="BU2" s="2" t="s">
         <v>94</v>
       </c>
       <c r="BV2" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="BW2" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="BX2" s="6" t="s">
         <v>302</v>
       </c>
-      <c r="BW2" s="6" t="s">
-        <v>436</v>
-      </c>
-      <c r="BX2" s="6" t="s">
+      <c r="BY2" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="BY2" s="6" t="s">
+      <c r="BZ2" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="BZ2" s="6" t="s">
+      <c r="CA2" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="CA2" s="6" t="s">
+      <c r="CB2" t="s">
         <v>306</v>
       </c>
-      <c r="CB2" t="s">
+      <c r="CC2" t="s">
         <v>307</v>
       </c>
-      <c r="CC2" t="s">
+      <c r="CD2" t="s">
         <v>308</v>
       </c>
-      <c r="CD2" t="s">
+      <c r="CE2" t="s">
         <v>309</v>
       </c>
-      <c r="CE2" t="s">
+      <c r="CF2" t="s">
         <v>310</v>
       </c>
-      <c r="CF2" t="s">
+      <c r="CG2" t="s">
         <v>311</v>
       </c>
-      <c r="CG2" t="s">
+      <c r="CH2" t="s">
         <v>312</v>
       </c>
-      <c r="CH2" t="s">
+      <c r="CI2" t="s">
         <v>313</v>
       </c>
-      <c r="CI2" t="s">
+      <c r="CJ2" t="s">
         <v>314</v>
       </c>
-      <c r="CJ2" t="s">
+      <c r="CK2" t="s">
         <v>315</v>
       </c>
-      <c r="CK2" t="s">
+      <c r="CL2" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="CL2" s="2" t="s">
+      <c r="CM2" t="s">
         <v>317</v>
       </c>
-      <c r="CM2" t="s">
+      <c r="CN2" t="s">
         <v>318</v>
       </c>
-      <c r="CN2" t="s">
+      <c r="CO2" t="s">
         <v>319</v>
       </c>
-      <c r="CO2" t="s">
+      <c r="CP2" t="s">
         <v>320</v>
       </c>
-      <c r="CP2" t="s">
+      <c r="CQ2" t="s">
         <v>321</v>
       </c>
-      <c r="CQ2" t="s">
+      <c r="CR2" t="s">
         <v>322</v>
       </c>
-      <c r="CR2" t="s">
+      <c r="CS2" t="s">
         <v>323</v>
       </c>
-      <c r="CS2" t="s">
+      <c r="CT2" t="s">
         <v>324</v>
       </c>
-      <c r="CT2" t="s">
+      <c r="CU2" t="s">
         <v>325</v>
       </c>
-      <c r="CU2" t="s">
+      <c r="CV2" t="s">
         <v>326</v>
       </c>
-      <c r="CV2" t="s">
+      <c r="CW2" t="s">
         <v>327</v>
       </c>
-      <c r="CW2" t="s">
+      <c r="CX2" t="s">
         <v>328</v>
       </c>
-      <c r="CX2" t="s">
+      <c r="CY2" t="s">
         <v>329</v>
       </c>
-      <c r="CY2" t="s">
+      <c r="CZ2" t="s">
         <v>330</v>
       </c>
-      <c r="CZ2" t="s">
+      <c r="DA2" t="s">
         <v>331</v>
       </c>
-      <c r="DA2" t="s">
+      <c r="DB2" t="s">
         <v>332</v>
       </c>
-      <c r="DB2" t="s">
+      <c r="DC2" t="s">
         <v>333</v>
       </c>
-      <c r="DC2" t="s">
+      <c r="DD2" t="s">
         <v>334</v>
       </c>
-      <c r="DD2" t="s">
+      <c r="DE2" t="s">
         <v>335</v>
       </c>
-      <c r="DE2" t="s">
+      <c r="DF2" t="s">
         <v>336</v>
       </c>
-      <c r="DF2" t="s">
+      <c r="DG2" t="s">
         <v>337</v>
       </c>
-      <c r="DG2" t="s">
+      <c r="DH2" t="s">
         <v>338</v>
       </c>
-      <c r="DH2" t="s">
+      <c r="DI2" t="s">
         <v>339</v>
-      </c>
-      <c r="DI2" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="3" spans="1:113" x14ac:dyDescent="0.25">
@@ -7150,13 +7155,13 @@
         <v>115</v>
       </c>
       <c r="J3" t="s">
+        <v>340</v>
+      </c>
+      <c r="K3" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="L3" s="5" t="s">
         <v>342</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>343</v>
       </c>
       <c r="M3" s="5" t="s">
         <v>117</v>
@@ -7219,7 +7224,7 @@
         <v>115</v>
       </c>
       <c r="AG3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AH3" t="s">
         <v>115</v>
@@ -7243,22 +7248,22 @@
         <v>115</v>
       </c>
       <c r="AO3" t="s">
+        <v>344</v>
+      </c>
+      <c r="AP3" t="s">
         <v>345</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>346</v>
       </c>
       <c r="AQ3" t="s">
         <v>2</v>
       </c>
       <c r="AR3" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AS3" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AT3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AU3" t="s">
         <v>115</v>
@@ -7270,7 +7275,7 @@
         <v>115</v>
       </c>
       <c r="AX3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AY3" t="s">
         <v>115</v>
@@ -7300,7 +7305,7 @@
         <v>115</v>
       </c>
       <c r="BH3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="BI3" t="s">
         <v>115</v>
@@ -7327,10 +7332,10 @@
         <v>118</v>
       </c>
       <c r="BQ3" t="s">
+        <v>348</v>
+      </c>
+      <c r="BR3" t="s">
         <v>349</v>
-      </c>
-      <c r="BR3" t="s">
-        <v>350</v>
       </c>
       <c r="BS3" t="s">
         <v>116</v>
@@ -7351,19 +7356,19 @@
         <v>117</v>
       </c>
       <c r="BY3" s="6" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="BZ3" s="6" t="s">
         <v>115</v>
       </c>
       <c r="CA3" s="6" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="CB3" t="s">
         <v>123</v>
       </c>
       <c r="CC3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="CD3" t="s">
         <v>123</v>
@@ -7375,19 +7380,19 @@
         <v>123</v>
       </c>
       <c r="CG3" t="s">
+        <v>352</v>
+      </c>
+      <c r="CH3" t="s">
         <v>353</v>
-      </c>
-      <c r="CH3" t="s">
-        <v>354</v>
       </c>
       <c r="CI3" t="s">
         <v>2</v>
       </c>
       <c r="CJ3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="CK3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="CL3" s="2" t="s">
         <v>124</v>
@@ -7408,7 +7413,7 @@
         <v>122</v>
       </c>
       <c r="CR3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="CS3" t="s">
         <v>122</v>
@@ -7420,28 +7425,28 @@
         <v>124</v>
       </c>
       <c r="CV3" t="s">
+        <v>355</v>
+      </c>
+      <c r="CW3" t="s">
         <v>356</v>
       </c>
-      <c r="CW3" t="s">
-        <v>357</v>
-      </c>
       <c r="CX3" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="CY3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="CZ3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="DA3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="DB3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="DC3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="DD3" t="s">
         <v>115</v>
@@ -7464,7 +7469,7 @@
     </row>
     <row r="4" spans="1:113" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="5" spans="1:113" x14ac:dyDescent="0.25">
@@ -7475,25 +7480,25 @@
     </row>
     <row r="6" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C6" t="s">
+        <v>448</v>
+      </c>
+      <c r="K6" s="5" t="s">
         <v>449</v>
       </c>
-      <c r="K6" s="5" t="s">
-        <v>450</v>
-      </c>
       <c r="P6" s="7" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="AC6">
         <v>1</v>
       </c>
       <c r="AO6" t="s">
+        <v>450</v>
+      </c>
+      <c r="AT6" t="s">
         <v>451</v>
-      </c>
-      <c r="AT6" t="s">
-        <v>452</v>
       </c>
       <c r="AY6">
         <v>1</v>
@@ -7508,39 +7513,39 @@
         <v>56</v>
       </c>
       <c r="CG6" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="CH6" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="CI6" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="CN6" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="CR6">
         <v>9999</v>
       </c>
       <c r="CY6" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="7" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="K7" s="5" t="s">
         <v>471</v>
       </c>
-      <c r="K7" s="5" t="s">
-        <v>472</v>
-      </c>
       <c r="L7" s="5" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="Q7" s="5" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="AC7">
         <v>1</v>
@@ -7558,27 +7563,27 @@
       <c r="BV7"/>
       <c r="CL7" s="5"/>
       <c r="CU7" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="8" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>475</v>
-      </c>
       <c r="K8" s="5" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AC8">
         <v>1</v>
       </c>
       <c r="AT8" s="2" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="BD8">
         <v>1</v>
@@ -7586,27 +7591,27 @@
       <c r="BV8"/>
       <c r="CL8" s="5"/>
       <c r="CU8" s="2" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>477</v>
-      </c>
       <c r="K9" s="5" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AC9">
         <v>1</v>
       </c>
       <c r="AT9" s="2" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="BD9">
         <v>99</v>
@@ -7614,10 +7619,10 @@
       <c r="BV9"/>
       <c r="CL9" s="5"/>
       <c r="CM9" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="CN9" s="2" t="s">
         <v>479</v>
-      </c>
-      <c r="CN9" s="2" t="s">
-        <v>480</v>
       </c>
       <c r="CR9">
         <v>9999</v>
@@ -7626,35 +7631,35 @@
     </row>
     <row r="10" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>490</v>
+        <v>551</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="I10">
         <v>1</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="Q10" s="5" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="AC10">
         <v>1</v>
       </c>
       <c r="AG10" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="AJ10" s="2"/>
       <c r="AN10">
         <v>1</v>
       </c>
       <c r="AT10" s="2" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="BD10">
         <v>99</v>
@@ -7663,7 +7668,7 @@
       <c r="CL10" s="5"/>
       <c r="CM10" s="2"/>
       <c r="CN10" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="CR10">
         <v>1</v>
@@ -7681,22 +7686,22 @@
     </row>
     <row r="11" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AC11">
         <v>1</v>
       </c>
       <c r="AG11" s="2" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="AN11">
         <v>1</v>
@@ -7706,7 +7711,7 @@
       </c>
       <c r="CL11" s="5"/>
       <c r="CN11" s="2" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="CR11">
         <v>9999</v>
@@ -7737,25 +7742,25 @@
     </row>
     <row r="13" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="G13">
         <v>3</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="L13" s="7"/>
       <c r="M13"/>
@@ -7777,13 +7782,13 @@
         <v>1</v>
       </c>
       <c r="AG13" s="2" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="AO13" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AT13" s="2" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="AY13">
         <v>1</v>
@@ -7795,7 +7800,7 @@
         <v>1</v>
       </c>
       <c r="BO13" s="2" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="BT13">
         <v>0.2</v>
@@ -7813,13 +7818,13 @@
         <v>1</v>
       </c>
       <c r="BY13" s="8" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="BZ13" s="8"/>
       <c r="CA13"/>
       <c r="CH13" s="2"/>
       <c r="CN13" s="3" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="CO13">
         <v>1</v>
@@ -7827,22 +7832,22 @@
     </row>
     <row r="14" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="7" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="L14" s="7"/>
       <c r="M14"/>
       <c r="N14"/>
       <c r="O14" s="7" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="P14"/>
       <c r="Q14"/>
@@ -7857,10 +7862,10 @@
         <v>1</v>
       </c>
       <c r="AO14" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AT14" s="2" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="AY14">
         <v>1</v>
@@ -7882,17 +7887,17 @@
         <v>56</v>
       </c>
       <c r="CG14" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="CH14" s="2" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="CI14" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="CN14" s="3"/>
       <c r="CY14" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="15" spans="1:113" x14ac:dyDescent="0.25">
@@ -7920,31 +7925,31 @@
     </row>
     <row r="16" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="G16">
         <v>3</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="M16"/>
       <c r="N16"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="5" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="R16" s="3"/>
       <c r="S16"/>
@@ -7953,7 +7958,7 @@
         <v>1</v>
       </c>
       <c r="AO16" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AV16">
         <v>20</v>
@@ -7980,22 +7985,22 @@
         <v>3</v>
       </c>
       <c r="BY16" s="6" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="CB16" t="s">
         <v>56</v>
       </c>
       <c r="CG16" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="CH16" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="CI16" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="CN16" s="2" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="CO16">
         <v>0.3</v>
@@ -8009,25 +8014,25 @@
     </row>
     <row r="18" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="D18" s="17" t="s">
         <v>511</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="D18" s="17" t="s">
-        <v>514</v>
-      </c>
       <c r="E18" s="2" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="G18">
         <v>3</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="M18"/>
       <c r="O18"/>
@@ -8035,13 +8040,13 @@
         <v>1</v>
       </c>
       <c r="AG18" s="2" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="BD18">
         <v>1</v>
       </c>
       <c r="BO18" s="2" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="BP18" s="2"/>
       <c r="BT18">
@@ -8057,10 +8062,10 @@
         <v>1</v>
       </c>
       <c r="BY18" s="6" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="CN18" s="2" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="CO18">
         <v>-0.4</v>
@@ -8071,17 +8076,17 @@
     </row>
     <row r="19" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="J19" s="5"/>
       <c r="K19" s="5" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="L19" s="5" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="M19"/>
       <c r="O19" s="3"/>
@@ -8098,24 +8103,24 @@
       </c>
       <c r="CN19" s="2"/>
       <c r="CU19" s="2" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
     </row>
     <row r="20" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="K20" s="5" t="s">
         <v>471</v>
       </c>
-      <c r="K20" s="5" t="s">
-        <v>472</v>
-      </c>
       <c r="L20" s="5" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AC20">
         <v>2</v>
@@ -8130,24 +8135,24 @@
       <c r="BV20"/>
       <c r="CL20" s="5"/>
       <c r="CU20" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="21" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="L21" s="5" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="O21" s="18" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="AC21">
         <v>2</v>
@@ -8162,7 +8167,7 @@
       <c r="BV21"/>
       <c r="CL21" s="5"/>
       <c r="CN21" s="2" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="CR21">
         <v>9999</v>
@@ -8171,17 +8176,17 @@
     </row>
     <row r="22" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="J22" s="5"/>
       <c r="K22" s="5" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="L22" s="5" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="M22"/>
       <c r="O22" s="3"/>
@@ -8198,24 +8203,24 @@
       </c>
       <c r="CN22" s="2"/>
       <c r="CU22" s="2" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
     </row>
     <row r="23" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="K23" s="5" t="s">
         <v>471</v>
       </c>
-      <c r="K23" s="5" t="s">
-        <v>472</v>
-      </c>
       <c r="L23" s="5" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AC23">
         <v>2</v>
@@ -8230,7 +8235,7 @@
       <c r="BV23"/>
       <c r="CL23" s="5"/>
       <c r="CU23" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="24" spans="1:103" x14ac:dyDescent="0.25">
@@ -8255,26 +8260,26 @@
     </row>
     <row r="25" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="C25" t="s">
+        <v>448</v>
+      </c>
+      <c r="K25" s="5" t="s">
         <v>449</v>
       </c>
-      <c r="K25" s="5" t="s">
-        <v>450</v>
-      </c>
       <c r="O25" s="18" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="P25" s="7"/>
       <c r="AC25">
         <v>1</v>
       </c>
       <c r="AO25" t="s">
+        <v>450</v>
+      </c>
+      <c r="AT25" t="s">
         <v>451</v>
-      </c>
-      <c r="AT25" t="s">
-        <v>452</v>
       </c>
       <c r="AY25">
         <v>1</v>
@@ -8289,47 +8294,47 @@
         <v>56</v>
       </c>
       <c r="CG25" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="CH25" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="CI25" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="CN25" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="CR25">
         <v>9999</v>
       </c>
       <c r="CY25" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="26" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="K26" s="5" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="M26"/>
       <c r="N26"/>
       <c r="O26" s="18" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="Q26" s="5" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AC26">
         <v>1</v>
       </c>
       <c r="AO26" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AV26">
         <v>20</v>
@@ -8344,7 +8349,7 @@
       <c r="CI26" s="5"/>
       <c r="CJ26" s="5"/>
       <c r="CN26" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="CR26">
         <v>0.02</v>
@@ -8352,21 +8357,21 @@
     </row>
     <row r="27" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="M27"/>
       <c r="N27"/>
       <c r="O27" s="18" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="Q27" s="5" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="AC27">
         <v>2</v>
@@ -8375,7 +8380,7 @@
         <v>20</v>
       </c>
       <c r="AX27" s="2" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="AZ27">
         <v>0.8</v>
@@ -8386,25 +8391,25 @@
       <c r="BV27"/>
       <c r="CJ27" s="5"/>
       <c r="CY27" s="2" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
     </row>
     <row r="28" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="K28" s="5" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="M28"/>
       <c r="O28" s="18" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="Q28" s="5" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="AC28">
         <v>1</v>
@@ -8425,25 +8430,25 @@
       <c r="CG28" s="2"/>
       <c r="CM28" s="2"/>
       <c r="CU28" s="2" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="29" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="K29" s="5" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="M29"/>
       <c r="O29" s="18" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="Q29" s="5" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AC29">
         <v>1</v>
@@ -8461,7 +8466,7 @@
       </c>
       <c r="CG29" s="2"/>
       <c r="CN29" s="2" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="CR29">
         <v>0.02</v>
@@ -9946,37 +9951,37 @@
         <v>4</v>
       </c>
       <c r="E1" t="s">
+        <v>358</v>
+      </c>
+      <c r="F1" t="s">
         <v>359</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>360</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>361</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>362</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>363</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>364</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>365</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>366</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>367</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" s="2" t="s">
         <v>368</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -9990,43 +9995,43 @@
         <v>76</v>
       </c>
       <c r="E2" t="s">
+        <v>369</v>
+      </c>
+      <c r="F2" t="s">
         <v>370</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>371</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>372</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>373</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>374</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>375</v>
-      </c>
-      <c r="K2" t="s">
-        <v>376</v>
       </c>
       <c r="L2" t="s">
         <v>52</v>
       </c>
       <c r="M2" t="s">
+        <v>376</v>
+      </c>
+      <c r="N2" t="s">
         <v>377</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>378</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="P2" s="2" t="s">
-        <v>380</v>
-      </c>
       <c r="Q2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
@@ -10055,13 +10060,13 @@
         <v>115</v>
       </c>
       <c r="J3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="K3" t="s">
         <v>116</v>
       </c>
       <c r="L3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="M3" t="s">
         <v>115</v>
@@ -10070,7 +10075,7 @@
         <v>115</v>
       </c>
       <c r="O3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="P3" t="s">
         <v>115</v>
@@ -10081,32 +10086,32 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>466</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>468</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>469</v>
       </c>
       <c r="H6">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="Q7" s="2"/>
     </row>
@@ -10117,10 +10122,10 @@
     </row>
     <row r="9" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="I9" s="3">
         <v>1</v>
@@ -10131,59 +10136,59 @@
       </c>
       <c r="P9"/>
       <c r="Q9" s="3" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H14">
         <v>1</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
   </sheetData>
@@ -10208,7 +10213,7 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -10219,10 +10224,10 @@
         <v>47</v>
       </c>
       <c r="C2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -10233,7 +10238,7 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D3" t="s">
         <v>124</v>
@@ -10241,13 +10246,13 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="B4" t="s">
         <v>457</v>
       </c>
-      <c r="B4" t="s">
+      <c r="D4" s="2" t="s">
         <v>458</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>459</v>
       </c>
     </row>
   </sheetData>
@@ -10284,25 +10289,25 @@
         <v>49</v>
       </c>
       <c r="D2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="E2" t="s">
         <v>71</v>
       </c>
       <c r="F2" t="s">
+        <v>383</v>
+      </c>
+      <c r="G2" t="s">
         <v>384</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>385</v>
       </c>
-      <c r="H2" t="s">
-        <v>386</v>
-      </c>
       <c r="I2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="J2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -10331,7 +10336,7 @@
         <v>117</v>
       </c>
       <c r="I3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>124</v>
@@ -10339,13 +10344,13 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B4" t="s">
+        <v>454</v>
+      </c>
+      <c r="C4" t="s">
         <v>455</v>
-      </c>
-      <c r="C4" t="s">
-        <v>456</v>
       </c>
       <c r="E4">
         <v>10</v>
@@ -10354,21 +10359,21 @@
         <v>1</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="B5" t="s">
+        <v>454</v>
+      </c>
+      <c r="C5" t="s">
         <v>455</v>
-      </c>
-      <c r="C5" t="s">
-        <v>456</v>
       </c>
       <c r="E5">
         <v>10</v>
@@ -10377,10 +10382,10 @@
         <v>1</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
     </row>
   </sheetData>
@@ -10407,34 +10412,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>386</v>
+      </c>
+      <c r="C1" t="s">
         <v>387</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>388</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>389</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>390</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>391</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>392</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>393</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>394</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>395</v>
-      </c>
-      <c r="L1" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -10442,34 +10447,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>396</v>
+      </c>
+      <c r="C2" t="s">
         <v>397</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>398</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>399</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>400</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>401</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>402</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>403</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>404</v>
       </c>
-      <c r="J2" t="s">
-        <v>405</v>
-      </c>
       <c r="K2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="L2" t="s">
         <v>96</v>
@@ -10486,7 +10491,7 @@
         <v>117</v>
       </c>
       <c r="D3" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E3" t="s">
         <v>2</v>
@@ -10546,22 +10551,22 @@
         <v>76</v>
       </c>
       <c r="D2" t="s">
+        <v>406</v>
+      </c>
+      <c r="E2" t="s">
         <v>407</v>
-      </c>
-      <c r="E2" t="s">
-        <v>408</v>
       </c>
       <c r="F2" t="s">
         <v>78</v>
       </c>
       <c r="G2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2" t="s">
         <v>267</v>
       </c>
       <c r="I2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="J2" t="s">
         <v>53</v>
@@ -10590,7 +10595,7 @@
         <v>117</v>
       </c>
       <c r="H3" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="I3" t="s">
         <v>117</v>
@@ -10627,28 +10632,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>418</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -10656,28 +10661,28 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>426</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -10711,28 +10716,28 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C4" s="1">
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>445</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>446</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Diy优胜/萃儿.xlsx
+++ b/Excel/Diy优胜/萃儿.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Diy优胜\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AE32AE7-9C06-49BB-B275-36BE5FCD33B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{134BFA38-141D-418D-8841-78EBEEFAF564}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3740" yWindow="3843" windowWidth="17954" windowHeight="10398" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -302,7 +302,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="554">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="927" uniqueCount="558">
   <si>
     <t>Id</t>
   </si>
@@ -1952,18 +1952,6 @@
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>萃儿3被动对敌</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>萃儿3死亡生成萃蔓</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"技能Id列表":["萃儿3死亡生成萃蔓"]}</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
     <t>萃儿3协同索敌标记</t>
   </si>
   <si>
@@ -1983,10 +1971,6 @@
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>{"技能Id列表":["萃儿3击杀生成萃蔓","萃儿3击杀生成萃蔓"]}</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
     <t>萃儿3普攻</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
@@ -2042,18 +2026,10 @@
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>{"技能Id列表":["萃儿3普攻"]}</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
     <t>萃儿3附伤启动</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>萃儿3被动对干员,萃儿3被动对敌,萃儿3普攻,萃儿3覆盖伤害分摊,萃儿3协同攻击,萃儿3延伸攻击范围,萃儿3附伤启动</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
     <t>CostLimit</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
@@ -2071,6 +2047,46 @@
   </si>
   <si>
     <t>生成萃蔓1,萃蔓效果,萃蔓无敌</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>萃儿3撤退生成萃蔓</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>撤退</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>#萃儿3被动对敌</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>萃儿3我方死亡生成萃蔓</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"技能Id列表":["萃儿3对敌死亡生成萃蔓"]}</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>出场</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>#萃儿3敌方死亡生成萃蔓</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>萃儿3被动对干员,萃儿3普攻,萃儿3我方死亡生成萃蔓,萃儿3撤退生成萃蔓,萃儿3覆盖伤害分摊,萃儿3协同攻击,萃儿3延伸攻击范围,萃儿3附伤启动</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"技能Id列表":["萃儿3击杀生成萃蔓","萃儿3我方死亡生成萃蔓","萃儿3撤退生成萃蔓"]}</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"技能Id列表":["萃儿3普攻","萃儿3"]}</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
 </sst>
@@ -3293,7 +3309,7 @@
         <v>485</v>
       </c>
       <c r="AJ5" s="2" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="AK5">
         <v>0</v>
@@ -3407,13 +3423,13 @@
         <v>0</v>
       </c>
       <c r="AG6" s="17" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="AH6" s="2" t="s">
         <v>427</v>
       </c>
       <c r="AI6" s="2" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="AJ6" s="2"/>
       <c r="AK6">
@@ -3511,7 +3527,7 @@
         <v>427</v>
       </c>
       <c r="AI7" s="2" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="AJ7" s="2"/>
       <c r="AK7">
@@ -6374,7 +6390,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:DJ825"/>
+  <dimension ref="A1:DJ827"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.08203125" customWidth="1"/>
@@ -6904,7 +6920,7 @@
         <v>270</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="AN2" t="s">
         <v>271</v>
@@ -7489,7 +7505,7 @@
         <v>449</v>
       </c>
       <c r="P6" s="7" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="AC6">
         <v>1</v>
@@ -7605,7 +7621,7 @@
         <v>471</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>480</v>
+        <v>517</v>
       </c>
       <c r="AC9">
         <v>1</v>
@@ -7631,7 +7647,7 @@
     </row>
     <row r="10" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>476</v>
@@ -7711,7 +7727,7 @@
       </c>
       <c r="CL11" s="5"/>
       <c r="CN11" s="2" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="CR11">
         <v>9999</v>
@@ -8046,7 +8062,7 @@
         <v>1</v>
       </c>
       <c r="BO18" s="2" t="s">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="BP18" s="2"/>
       <c r="BT18">
@@ -8086,7 +8102,7 @@
         <v>471</v>
       </c>
       <c r="L19" s="5" t="s">
-        <v>517</v>
+        <v>553</v>
       </c>
       <c r="M19"/>
       <c r="O19" s="3"/>
@@ -8095,15 +8111,18 @@
       <c r="AC19">
         <v>1</v>
       </c>
-      <c r="AV19">
-        <v>20</v>
+      <c r="AF19">
+        <v>1</v>
+      </c>
+      <c r="AH19">
+        <v>1</v>
       </c>
       <c r="BD19">
         <v>99</v>
       </c>
       <c r="CN19" s="2"/>
       <c r="CU19" s="2" t="s">
-        <v>531</v>
+        <v>556</v>
       </c>
     </row>
     <row r="20" spans="1:103" x14ac:dyDescent="0.25">
@@ -8126,6 +8145,9 @@
         <v>2</v>
       </c>
       <c r="AF20">
+        <v>1</v>
+      </c>
+      <c r="AH20">
         <v>1</v>
       </c>
       <c r="AT20" s="2"/>
@@ -8140,7 +8162,7 @@
     </row>
     <row r="21" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>476</v>
@@ -8149,10 +8171,10 @@
         <v>471</v>
       </c>
       <c r="L21" s="5" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="O21" s="18" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="AC21">
         <v>2</v>
@@ -8167,7 +8189,7 @@
       <c r="BV21"/>
       <c r="CL21" s="5"/>
       <c r="CN21" s="2" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="CR21">
         <v>9999</v>
@@ -8176,7 +8198,7 @@
     </row>
     <row r="22" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>523</v>
+        <v>550</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>516</v>
@@ -8203,12 +8225,12 @@
       </c>
       <c r="CN22" s="2"/>
       <c r="CU22" s="2" t="s">
-        <v>525</v>
+        <v>552</v>
       </c>
     </row>
     <row r="23" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>524</v>
+        <v>554</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>470</v>
@@ -8219,15 +8241,14 @@
       <c r="L23" s="5" t="s">
         <v>519</v>
       </c>
-      <c r="O23" s="2" t="s">
-        <v>479</v>
-      </c>
+      <c r="Q23" s="2"/>
       <c r="AC23">
         <v>2</v>
       </c>
       <c r="AF23">
         <v>1</v>
       </c>
+      <c r="AG23" s="2"/>
       <c r="AT23" s="2"/>
       <c r="BD23">
         <v>99</v>
@@ -8239,203 +8260,195 @@
       </c>
     </row>
     <row r="24" spans="1:103" x14ac:dyDescent="0.25">
-      <c r="M24"/>
-      <c r="AY24" s="5"/>
+      <c r="A24" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="K24" s="5" t="s">
+        <v>471</v>
+      </c>
+      <c r="L24" s="5" t="s">
+        <v>519</v>
+      </c>
+      <c r="Q24" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="AC24">
+        <v>1</v>
+      </c>
+      <c r="AF24">
+        <v>1</v>
+      </c>
+      <c r="AG24" s="2"/>
+      <c r="AT24" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="BD24">
+        <v>99</v>
+      </c>
       <c r="BV24"/>
-      <c r="BW24"/>
-      <c r="BX24"/>
-      <c r="BY24"/>
-      <c r="BZ24"/>
-      <c r="CA24"/>
-      <c r="CB24" s="5"/>
-      <c r="CC24" s="5"/>
-      <c r="CD24" s="5"/>
-      <c r="CE24" s="5"/>
-      <c r="CF24" s="5"/>
-      <c r="CH24" s="5"/>
-      <c r="CI24" s="5"/>
-      <c r="CJ24" s="5"/>
-      <c r="CK24" s="5"/>
-      <c r="CN24" s="3"/>
+      <c r="CL24" s="5"/>
+      <c r="CU24" s="2" t="s">
+        <v>483</v>
+      </c>
     </row>
     <row r="25" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="C25" t="s">
-        <v>448</v>
+        <v>548</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>470</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>449</v>
-      </c>
-      <c r="O25" s="18" t="s">
-        <v>513</v>
-      </c>
-      <c r="P25" s="7"/>
+        <v>471</v>
+      </c>
+      <c r="L25" s="5" t="s">
+        <v>549</v>
+      </c>
+      <c r="Q25" s="2" t="s">
+        <v>479</v>
+      </c>
       <c r="AC25">
         <v>1</v>
       </c>
-      <c r="AO25" t="s">
-        <v>450</v>
-      </c>
-      <c r="AT25" t="s">
-        <v>451</v>
-      </c>
-      <c r="AY25">
+      <c r="AF25">
         <v>1</v>
       </c>
-      <c r="AZ25">
-        <v>1</v>
+      <c r="AG25" s="2"/>
+      <c r="AT25" s="2" t="s">
+        <v>477</v>
       </c>
       <c r="BD25">
-        <v>3</v>
-      </c>
-      <c r="CB25" t="s">
-        <v>56</v>
-      </c>
-      <c r="CG25" t="s">
-        <v>452</v>
-      </c>
-      <c r="CH25" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="CI25" t="s">
-        <v>434</v>
-      </c>
-      <c r="CN25" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="CR25">
-        <v>9999</v>
-      </c>
-      <c r="CY25" t="s">
-        <v>453</v>
+        <v>99</v>
+      </c>
+      <c r="BV25"/>
+      <c r="CL25" s="5"/>
+      <c r="CU25" s="2" t="s">
+        <v>483</v>
       </c>
     </row>
     <row r="26" spans="1:103" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="K26" s="5" t="s">
-        <v>496</v>
-      </c>
       <c r="M26"/>
-      <c r="N26"/>
-      <c r="O26" s="18" t="s">
-        <v>513</v>
-      </c>
-      <c r="Q26" s="5" t="s">
-        <v>479</v>
-      </c>
-      <c r="AC26">
-        <v>1</v>
-      </c>
-      <c r="AO26" t="s">
-        <v>450</v>
-      </c>
-      <c r="AV26">
-        <v>20</v>
-      </c>
-      <c r="BD26">
-        <v>1</v>
-      </c>
-      <c r="BS26">
-        <v>0.01</v>
-      </c>
+      <c r="AY26" s="5"/>
       <c r="BV26"/>
+      <c r="BW26"/>
+      <c r="BX26"/>
+      <c r="BY26"/>
+      <c r="BZ26"/>
+      <c r="CA26"/>
+      <c r="CB26" s="5"/>
+      <c r="CC26" s="5"/>
+      <c r="CD26" s="5"/>
+      <c r="CE26" s="5"/>
+      <c r="CF26" s="5"/>
+      <c r="CH26" s="5"/>
       <c r="CI26" s="5"/>
       <c r="CJ26" s="5"/>
-      <c r="CN26" t="s">
-        <v>535</v>
-      </c>
-      <c r="CR26">
-        <v>0.02</v>
-      </c>
+      <c r="CK26" s="5"/>
+      <c r="CN26" s="3"/>
     </row>
     <row r="27" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>476</v>
+        <v>528</v>
+      </c>
+      <c r="C27" t="s">
+        <v>448</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>496</v>
-      </c>
-      <c r="M27"/>
-      <c r="N27"/>
+        <v>449</v>
+      </c>
       <c r="O27" s="18" t="s">
         <v>513</v>
       </c>
-      <c r="Q27" s="5" t="s">
-        <v>526</v>
-      </c>
+      <c r="P27" s="7"/>
       <c r="AC27">
-        <v>2</v>
-      </c>
-      <c r="AV27">
-        <v>20</v>
-      </c>
-      <c r="AX27" s="2" t="s">
-        <v>540</v>
+        <v>1</v>
+      </c>
+      <c r="AO27" t="s">
+        <v>450</v>
+      </c>
+      <c r="AT27" t="s">
+        <v>451</v>
+      </c>
+      <c r="AY27">
+        <v>1</v>
       </c>
       <c r="AZ27">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="BD27">
-        <v>99</v>
-      </c>
-      <c r="BV27"/>
-      <c r="CJ27" s="5"/>
-      <c r="CY27" s="2" t="s">
-        <v>539</v>
+        <v>3</v>
+      </c>
+      <c r="CB27" t="s">
+        <v>56</v>
+      </c>
+      <c r="CG27" t="s">
+        <v>452</v>
+      </c>
+      <c r="CH27" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="CI27" t="s">
+        <v>434</v>
+      </c>
+      <c r="CN27" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="CR27">
+        <v>9999</v>
+      </c>
+      <c r="CY27" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="28" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>542</v>
+        <v>530</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>543</v>
+        <v>476</v>
       </c>
       <c r="K28" s="5" t="s">
         <v>496</v>
       </c>
       <c r="M28"/>
+      <c r="N28"/>
       <c r="O28" s="18" t="s">
         <v>513</v>
       </c>
       <c r="Q28" s="5" t="s">
-        <v>491</v>
+        <v>479</v>
       </c>
       <c r="AC28">
         <v>1</v>
       </c>
-      <c r="AG28" s="2"/>
-      <c r="AN28">
-        <v>1</v>
-      </c>
-      <c r="AO28" s="2"/>
+      <c r="AO28" t="s">
+        <v>450</v>
+      </c>
       <c r="AV28">
         <v>20</v>
       </c>
       <c r="BD28">
-        <v>99</v>
-      </c>
-      <c r="BO28" s="2"/>
-      <c r="BP28" s="2"/>
-      <c r="CG28" s="2"/>
-      <c r="CM28" s="2"/>
-      <c r="CU28" s="2" t="s">
-        <v>546</v>
+        <v>1</v>
+      </c>
+      <c r="BS28">
+        <v>0.01</v>
+      </c>
+      <c r="BV28"/>
+      <c r="CI28" s="5"/>
+      <c r="CJ28" s="5"/>
+      <c r="CN28" t="s">
+        <v>531</v>
+      </c>
+      <c r="CR28">
+        <v>0.02</v>
       </c>
     </row>
     <row r="29" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>547</v>
+        <v>534</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>476</v>
@@ -8444,200 +8457,272 @@
         <v>496</v>
       </c>
       <c r="M29"/>
+      <c r="N29"/>
       <c r="O29" s="18" t="s">
         <v>513</v>
       </c>
       <c r="Q29" s="5" t="s">
-        <v>479</v>
+        <v>523</v>
       </c>
       <c r="AC29">
-        <v>1</v>
-      </c>
-      <c r="AG29" s="2"/>
-      <c r="AO29" s="2"/>
+        <v>2</v>
+      </c>
       <c r="AV29">
         <v>20</v>
       </c>
+      <c r="AX29" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="AZ29">
+        <v>0.8</v>
+      </c>
       <c r="BD29">
         <v>99</v>
       </c>
-      <c r="BS29">
+      <c r="BV29"/>
+      <c r="CJ29" s="5"/>
+      <c r="CY29" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="30" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="K30" s="5" t="s">
+        <v>496</v>
+      </c>
+      <c r="M30"/>
+      <c r="O30" s="18" t="s">
+        <v>513</v>
+      </c>
+      <c r="Q30" s="5" t="s">
+        <v>491</v>
+      </c>
+      <c r="AC30">
+        <v>1</v>
+      </c>
+      <c r="AG30" s="2"/>
+      <c r="AN30">
+        <v>1</v>
+      </c>
+      <c r="AO30" s="2"/>
+      <c r="AV30">
+        <v>20</v>
+      </c>
+      <c r="BD30">
+        <v>99</v>
+      </c>
+      <c r="BO30" s="2"/>
+      <c r="BP30" s="2"/>
+      <c r="CG30" s="2"/>
+      <c r="CM30" s="2"/>
+      <c r="CU30" s="2" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="31" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="K31" s="5" t="s">
+        <v>496</v>
+      </c>
+      <c r="M31"/>
+      <c r="O31" s="18" t="s">
+        <v>513</v>
+      </c>
+      <c r="Q31" s="5" t="s">
+        <v>479</v>
+      </c>
+      <c r="AC31">
+        <v>1</v>
+      </c>
+      <c r="AG31" s="2"/>
+      <c r="AO31" s="2"/>
+      <c r="AV31">
+        <v>20</v>
+      </c>
+      <c r="BD31">
+        <v>99</v>
+      </c>
+      <c r="BS31">
         <v>0.01</v>
       </c>
-      <c r="CG29" s="2"/>
-      <c r="CN29" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="CR29">
+      <c r="CG31" s="2"/>
+      <c r="CN31" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="CR31">
         <v>0.02</v>
       </c>
     </row>
-    <row r="30" spans="1:103" x14ac:dyDescent="0.25">
-      <c r="BU30" s="6"/>
-      <c r="CA30"/>
-    </row>
-    <row r="31" spans="1:103" x14ac:dyDescent="0.25">
-      <c r="E31" s="2"/>
-      <c r="O31"/>
-      <c r="W31"/>
-      <c r="X31"/>
-      <c r="BO31" s="2"/>
-      <c r="BP31" s="2"/>
-      <c r="CN31" s="3"/>
-    </row>
     <row r="32" spans="1:103" x14ac:dyDescent="0.25">
-      <c r="M32"/>
-      <c r="O32" s="3"/>
-      <c r="P32"/>
-      <c r="Q32"/>
-      <c r="CN32" s="3"/>
+      <c r="BU32" s="6"/>
+      <c r="CA32"/>
     </row>
     <row r="33" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="A33" s="2"/>
-      <c r="M33"/>
-      <c r="O33" s="3"/>
-      <c r="P33"/>
-      <c r="Q33"/>
+      <c r="E33" s="2"/>
+      <c r="O33"/>
+      <c r="W33"/>
+      <c r="X33"/>
+      <c r="BO33" s="2"/>
+      <c r="BP33" s="2"/>
       <c r="CN33" s="3"/>
     </row>
     <row r="34" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="A34" s="2"/>
+      <c r="M34"/>
       <c r="O34" s="3"/>
+      <c r="P34"/>
+      <c r="Q34"/>
+      <c r="CN34" s="3"/>
     </row>
     <row r="35" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
-      <c r="CL35" s="5"/>
+      <c r="M35"/>
+      <c r="O35" s="3"/>
+      <c r="P35"/>
+      <c r="Q35"/>
+      <c r="CN35" s="3"/>
     </row>
     <row r="36" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="CL36" s="5"/>
+      <c r="A36" s="2"/>
+      <c r="O36" s="3"/>
     </row>
     <row r="37" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
-      <c r="C37" s="2"/>
-      <c r="J37" s="2"/>
-      <c r="AJ37" s="2"/>
       <c r="CL37" s="5"/>
-      <c r="CU37" s="2"/>
     </row>
     <row r="38" spans="1:99" x14ac:dyDescent="0.25">
       <c r="CL38" s="5"/>
     </row>
     <row r="39" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="O39"/>
-      <c r="W39"/>
-      <c r="X39"/>
-      <c r="CN39" s="3"/>
+      <c r="A39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="J39" s="2"/>
+      <c r="AJ39" s="2"/>
+      <c r="CL39" s="5"/>
+      <c r="CU39" s="2"/>
     </row>
     <row r="40" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="O40" s="3"/>
-      <c r="X40"/>
+      <c r="CL40" s="5"/>
     </row>
     <row r="41" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="O41" s="3"/>
-      <c r="P41"/>
-      <c r="Q41"/>
+      <c r="O41"/>
+      <c r="W41"/>
       <c r="X41"/>
+      <c r="CN41" s="3"/>
     </row>
     <row r="42" spans="1:99" x14ac:dyDescent="0.25">
       <c r="O42" s="3"/>
       <c r="X42"/>
     </row>
-    <row r="45" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="CM45" s="3"/>
-      <c r="CN45" s="3"/>
+    <row r="43" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="O43" s="3"/>
+      <c r="P43"/>
+      <c r="Q43"/>
+      <c r="X43"/>
+    </row>
+    <row r="44" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="O44" s="3"/>
+      <c r="X44"/>
     </row>
     <row r="47" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="M47"/>
-      <c r="N47"/>
-      <c r="BV47"/>
-      <c r="CB47" s="9"/>
-      <c r="CI47" s="5"/>
-      <c r="CJ47" s="5"/>
-    </row>
-    <row r="48" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="M48"/>
-      <c r="N48"/>
-      <c r="BV48"/>
-      <c r="CB48" s="9"/>
-      <c r="CJ48" s="5"/>
-    </row>
-    <row r="49" spans="15:91" x14ac:dyDescent="0.25">
-      <c r="O49"/>
-      <c r="X49"/>
-      <c r="CM49" s="3"/>
-    </row>
-    <row r="52" spans="15:91" x14ac:dyDescent="0.25">
-      <c r="CL52" s="5"/>
-    </row>
-    <row r="53" spans="15:91" x14ac:dyDescent="0.25">
-      <c r="CL53" s="5"/>
-    </row>
-    <row r="59" spans="15:91" x14ac:dyDescent="0.25">
-      <c r="CL59" s="5"/>
-    </row>
-    <row r="60" spans="15:91" x14ac:dyDescent="0.25">
-      <c r="CL60" s="5"/>
-    </row>
-    <row r="62" spans="15:91" x14ac:dyDescent="0.25">
+      <c r="CM47" s="3"/>
+      <c r="CN47" s="3"/>
+    </row>
+    <row r="49" spans="13:91" x14ac:dyDescent="0.25">
+      <c r="M49"/>
+      <c r="N49"/>
+      <c r="BV49"/>
+      <c r="CB49" s="9"/>
+      <c r="CI49" s="5"/>
+      <c r="CJ49" s="5"/>
+    </row>
+    <row r="50" spans="13:91" x14ac:dyDescent="0.25">
+      <c r="M50"/>
+      <c r="N50"/>
+      <c r="BV50"/>
+      <c r="CB50" s="9"/>
+      <c r="CJ50" s="5"/>
+    </row>
+    <row r="51" spans="13:91" x14ac:dyDescent="0.25">
+      <c r="O51"/>
+      <c r="X51"/>
+      <c r="CM51" s="3"/>
+    </row>
+    <row r="54" spans="13:91" x14ac:dyDescent="0.25">
+      <c r="CL54" s="5"/>
+    </row>
+    <row r="55" spans="13:91" x14ac:dyDescent="0.25">
+      <c r="CL55" s="5"/>
+    </row>
+    <row r="61" spans="13:91" x14ac:dyDescent="0.25">
+      <c r="CL61" s="5"/>
+    </row>
+    <row r="62" spans="13:91" x14ac:dyDescent="0.25">
       <c r="CL62" s="5"/>
     </row>
-    <row r="63" spans="15:91" x14ac:dyDescent="0.25">
-      <c r="CL63" s="5"/>
-    </row>
-    <row r="64" spans="15:91" x14ac:dyDescent="0.25">
+    <row r="64" spans="13:91" x14ac:dyDescent="0.25">
       <c r="CL64" s="5"/>
     </row>
     <row r="65" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL65" s="5"/>
     </row>
     <row r="66" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV66"/>
+      <c r="CL66" s="5"/>
     </row>
     <row r="67" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV67"/>
+      <c r="CL67" s="5"/>
     </row>
     <row r="68" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV68"/>
-      <c r="CL68" s="5"/>
     </row>
     <row r="69" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL69" s="5"/>
+      <c r="BV69"/>
     </row>
     <row r="70" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV70"/>
       <c r="CL70" s="5"/>
     </row>
     <row r="71" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV71"/>
+      <c r="CL71" s="5"/>
     </row>
     <row r="72" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL72" s="5"/>
     </row>
-    <row r="76" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV76"/>
-    </row>
-    <row r="77" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL77" s="5"/>
-    </row>
-    <row r="85" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL85" s="5"/>
-    </row>
-    <row r="86" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL86" s="5"/>
+    <row r="73" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV73"/>
+    </row>
+    <row r="74" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL74" s="5"/>
+    </row>
+    <row r="78" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV78"/>
+    </row>
+    <row r="79" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL79" s="5"/>
     </row>
     <row r="87" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV87"/>
-    </row>
-    <row r="92" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV92"/>
-    </row>
-    <row r="93" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV93"/>
-      <c r="CL93" s="5"/>
+      <c r="CL87" s="5"/>
+    </row>
+    <row r="88" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL88" s="5"/>
+    </row>
+    <row r="89" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV89"/>
     </row>
     <row r="94" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL94" s="5"/>
+      <c r="BV94"/>
     </row>
     <row r="95" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV95"/>
       <c r="CL95" s="5"/>
     </row>
     <row r="96" spans="74:90" x14ac:dyDescent="0.25">
@@ -8647,13 +8732,13 @@
       <c r="CL97" s="5"/>
     </row>
     <row r="98" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV98"/>
+      <c r="CL98" s="5"/>
     </row>
     <row r="99" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL99" s="5"/>
     </row>
     <row r="100" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL100" s="5"/>
+      <c r="BV100"/>
     </row>
     <row r="101" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL101" s="5"/>
@@ -8662,13 +8747,13 @@
       <c r="CL102" s="5"/>
     </row>
     <row r="103" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV103"/>
+      <c r="CL103" s="5"/>
     </row>
     <row r="104" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL104" s="5"/>
     </row>
     <row r="105" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL105" s="5"/>
+      <c r="BV105"/>
     </row>
     <row r="106" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL106" s="5"/>
@@ -8676,11 +8761,11 @@
     <row r="107" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL107" s="5"/>
     </row>
-    <row r="110" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL110" s="5"/>
-    </row>
-    <row r="111" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL111" s="5"/>
+    <row r="108" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL108" s="5"/>
+    </row>
+    <row r="109" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL109" s="5"/>
     </row>
     <row r="112" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL112" s="5"/>
@@ -8691,14 +8776,14 @@
     <row r="114" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL114" s="5"/>
     </row>
+    <row r="115" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL115" s="5"/>
+    </row>
     <row r="116" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV116"/>
-    </row>
-    <row r="117" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL117" s="5"/>
+      <c r="CL116" s="5"/>
     </row>
     <row r="118" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL118" s="5"/>
+      <c r="BV118"/>
     </row>
     <row r="119" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL119" s="5"/>
@@ -8706,20 +8791,20 @@
     <row r="120" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL120" s="5"/>
     </row>
-    <row r="124" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL124" s="5"/>
+    <row r="121" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL121" s="5"/>
+    </row>
+    <row r="122" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL122" s="5"/>
     </row>
     <row r="126" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV126"/>
-    </row>
-    <row r="127" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV127"/>
-      <c r="CL127" s="5"/>
+      <c r="CL126" s="5"/>
     </row>
     <row r="128" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL128" s="5"/>
+      <c r="BV128"/>
     </row>
     <row r="129" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV129"/>
       <c r="CL129" s="5"/>
     </row>
     <row r="130" spans="74:90" x14ac:dyDescent="0.25">
@@ -8728,195 +8813,195 @@
     <row r="131" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL131" s="5"/>
     </row>
+    <row r="132" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL132" s="5"/>
+    </row>
     <row r="133" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV133"/>
-    </row>
-    <row r="134" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL134" s="5"/>
+      <c r="CL133" s="5"/>
     </row>
     <row r="135" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL135" s="5"/>
+      <c r="BV135"/>
+    </row>
+    <row r="136" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL136" s="5"/>
     </row>
     <row r="137" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL137" s="5"/>
     </row>
-    <row r="138" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL138" s="5"/>
+    <row r="139" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL139" s="5"/>
     </row>
     <row r="140" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV140"/>
-    </row>
-    <row r="141" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL141" s="5"/>
-    </row>
-    <row r="144" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL144" s="5"/>
-    </row>
-    <row r="145" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL145" s="5"/>
-    </row>
-    <row r="148" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL148" s="5"/>
+      <c r="CL140" s="5"/>
+    </row>
+    <row r="142" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV142"/>
+    </row>
+    <row r="143" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL143" s="5"/>
+    </row>
+    <row r="146" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL146" s="5"/>
+    </row>
+    <row r="147" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL147" s="5"/>
     </row>
     <row r="150" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL150" s="5"/>
     </row>
     <row r="152" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV152"/>
-    </row>
-    <row r="153" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL153" s="5"/>
+      <c r="CL152" s="5"/>
     </row>
     <row r="154" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL154" s="5"/>
+      <c r="BV154"/>
+    </row>
+    <row r="155" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL155" s="5"/>
     </row>
     <row r="156" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL156" s="5"/>
     </row>
-    <row r="157" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL157" s="5"/>
-    </row>
     <row r="158" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL158" s="5"/>
     </row>
-    <row r="163" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL163" s="5"/>
-    </row>
-    <row r="164" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL164" s="5"/>
-    </row>
-    <row r="167" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL167" s="5"/>
-    </row>
-    <row r="168" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL168" s="5"/>
-    </row>
-    <row r="172" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL172" s="5"/>
-    </row>
-    <row r="176" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL176" s="5"/>
+    <row r="159" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL159" s="5"/>
+    </row>
+    <row r="160" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL160" s="5"/>
+    </row>
+    <row r="165" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL165" s="5"/>
+    </row>
+    <row r="166" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL166" s="5"/>
+    </row>
+    <row r="169" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL169" s="5"/>
+    </row>
+    <row r="170" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL170" s="5"/>
+    </row>
+    <row r="174" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL174" s="5"/>
     </row>
     <row r="178" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL178" s="5"/>
     </row>
-    <row r="179" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL179" s="5"/>
+    <row r="180" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL180" s="5"/>
     </row>
     <row r="181" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL181" s="5"/>
     </row>
-    <row r="182" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL182" s="5"/>
+    <row r="183" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL183" s="5"/>
     </row>
     <row r="184" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV184"/>
-    </row>
-    <row r="185" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV185"/>
-      <c r="CL185" s="5"/>
+      <c r="CL184" s="5"/>
     </row>
     <row r="186" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL186" s="5"/>
+      <c r="BV186"/>
+    </row>
+    <row r="187" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV187"/>
+      <c r="CL187" s="5"/>
     </row>
     <row r="188" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL188" s="5"/>
     </row>
-    <row r="197" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV197"/>
-    </row>
-    <row r="198" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV198"/>
-      <c r="CL198" s="5"/>
+    <row r="190" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL190" s="5"/>
     </row>
     <row r="199" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL199" s="5"/>
+      <c r="BV199"/>
     </row>
     <row r="200" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV200"/>
       <c r="CL200" s="5"/>
     </row>
     <row r="201" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV201"/>
+      <c r="CL201" s="5"/>
     </row>
     <row r="202" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV202"/>
       <c r="CL202" s="5"/>
     </row>
     <row r="203" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL203" s="5"/>
+      <c r="BV203"/>
+    </row>
+    <row r="204" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV204"/>
+      <c r="CL204" s="5"/>
     </row>
     <row r="205" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV205"/>
-    </row>
-    <row r="206" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV206"/>
-      <c r="CL206" s="5"/>
+      <c r="CL205" s="5"/>
     </row>
     <row r="207" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL207" s="5"/>
+      <c r="BV207"/>
+    </row>
+    <row r="208" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV208"/>
+      <c r="CL208" s="5"/>
     </row>
     <row r="209" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV209"/>
-    </row>
-    <row r="210" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL210" s="5"/>
-    </row>
-    <row r="213" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL213" s="5"/>
-    </row>
-    <row r="217" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL217" s="5"/>
+      <c r="CL209" s="5"/>
+    </row>
+    <row r="211" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV211"/>
+    </row>
+    <row r="212" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL212" s="5"/>
+    </row>
+    <row r="215" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL215" s="5"/>
     </row>
     <row r="219" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV219"/>
-    </row>
-    <row r="220" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL220" s="5"/>
-    </row>
-    <row r="227" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV227"/>
-    </row>
-    <row r="228" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL228" s="5"/>
+      <c r="CL219" s="5"/>
+    </row>
+    <row r="221" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV221"/>
+    </row>
+    <row r="222" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL222" s="5"/>
     </row>
     <row r="229" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL229" s="5"/>
+      <c r="BV229"/>
+    </row>
+    <row r="230" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL230" s="5"/>
     </row>
     <row r="231" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV231"/>
-    </row>
-    <row r="232" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV232"/>
-      <c r="CL232" s="5"/>
+      <c r="CL231" s="5"/>
     </row>
     <row r="233" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL233" s="5"/>
-    </row>
-    <row r="239" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV239"/>
-    </row>
-    <row r="240" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV240"/>
-      <c r="CL240" s="5"/>
+      <c r="BV233"/>
+    </row>
+    <row r="234" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV234"/>
+      <c r="CL234" s="5"/>
+    </row>
+    <row r="235" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL235" s="5"/>
     </row>
     <row r="241" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV241"/>
-      <c r="CL241" s="5"/>
     </row>
     <row r="242" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV242"/>
       <c r="CL242" s="5"/>
     </row>
-    <row r="247" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV247"/>
-    </row>
-    <row r="248" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV248"/>
-    </row>
-    <row r="252" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV252"/>
-    </row>
-    <row r="253" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL253" s="5"/>
+    <row r="243" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV243"/>
+      <c r="CL243" s="5"/>
+    </row>
+    <row r="244" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL244" s="5"/>
+    </row>
+    <row r="249" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV249"/>
+    </row>
+    <row r="250" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV250"/>
     </row>
     <row r="254" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV254"/>
@@ -8924,46 +9009,44 @@
     <row r="255" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL255" s="5"/>
     </row>
-    <row r="265" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV265"/>
-    </row>
-    <row r="266" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL266" s="5"/>
+    <row r="256" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV256"/>
+    </row>
+    <row r="257" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL257" s="5"/>
+    </row>
+    <row r="267" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV267"/>
     </row>
     <row r="268" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV268"/>
-    </row>
-    <row r="269" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL269" s="5"/>
-    </row>
-    <row r="277" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV277"/>
-    </row>
-    <row r="278" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL278" s="5"/>
-    </row>
-    <row r="282" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV282"/>
-    </row>
-    <row r="283" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL283" s="5"/>
+      <c r="CL268" s="5"/>
+    </row>
+    <row r="270" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV270"/>
+    </row>
+    <row r="271" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL271" s="5"/>
+    </row>
+    <row r="279" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV279"/>
+    </row>
+    <row r="280" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL280" s="5"/>
+    </row>
+    <row r="284" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV284"/>
     </row>
     <row r="285" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV285"/>
-    </row>
-    <row r="286" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL286" s="5"/>
-    </row>
-    <row r="302" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV302"/>
-    </row>
-    <row r="303" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV303"/>
-      <c r="CL303" s="5"/>
-    </row>
-    <row r="304" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL285" s="5"/>
+    </row>
+    <row r="287" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV287"/>
+    </row>
+    <row r="288" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL288" s="5"/>
+    </row>
+    <row r="304" spans="74:74" x14ac:dyDescent="0.25">
       <c r="BV304"/>
-      <c r="CL304" s="5"/>
     </row>
     <row r="305" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV305"/>
@@ -8971,52 +9054,54 @@
     </row>
     <row r="306" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV306"/>
+      <c r="CL306" s="5"/>
+    </row>
+    <row r="307" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV307"/>
+      <c r="CL307" s="5"/>
     </row>
     <row r="308" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV308"/>
     </row>
-    <row r="309" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV309"/>
-      <c r="CL309" s="5"/>
-    </row>
     <row r="310" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV310"/>
-      <c r="CL310" s="5"/>
     </row>
     <row r="311" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV311"/>
       <c r="CL311" s="5"/>
     </row>
-    <row r="315" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV315"/>
-    </row>
-    <row r="316" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL316" s="5"/>
+    <row r="312" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV312"/>
+      <c r="CL312" s="5"/>
+    </row>
+    <row r="313" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL313" s="5"/>
+    </row>
+    <row r="317" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV317"/>
     </row>
     <row r="318" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV318"/>
-    </row>
-    <row r="319" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV319"/>
-      <c r="CL319" s="5"/>
+      <c r="CL318" s="5"/>
     </row>
     <row r="320" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV320"/>
-      <c r="CL320" s="5"/>
-    </row>
-    <row r="321" spans="90:90" x14ac:dyDescent="0.25">
+    </row>
+    <row r="321" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV321"/>
       <c r="CL321" s="5"/>
     </row>
-    <row r="337" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV337"/>
-    </row>
-    <row r="338" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL338" s="5"/>
-    </row>
-    <row r="346" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL346" s="5"/>
-    </row>
-    <row r="347" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL347" s="5"/>
+    <row r="322" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV322"/>
+      <c r="CL322" s="5"/>
+    </row>
+    <row r="323" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL323" s="5"/>
+    </row>
+    <row r="339" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV339"/>
+    </row>
+    <row r="340" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL340" s="5"/>
     </row>
     <row r="348" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL348" s="5"/>
@@ -9027,35 +9112,38 @@
     <row r="350" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL350" s="5"/>
     </row>
+    <row r="351" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL351" s="5"/>
+    </row>
     <row r="352" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV352"/>
-    </row>
-    <row r="353" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL353" s="5"/>
+      <c r="CL352" s="5"/>
     </row>
     <row r="354" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV354"/>
     </row>
     <row r="355" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV355"/>
       <c r="CL355" s="5"/>
     </row>
     <row r="356" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL356" s="5"/>
+      <c r="BV356"/>
+    </row>
+    <row r="357" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV357"/>
+      <c r="CL357" s="5"/>
     </row>
     <row r="358" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV358"/>
-    </row>
-    <row r="359" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV359"/>
-      <c r="CL359" s="5"/>
+      <c r="CL358" s="5"/>
     </row>
     <row r="360" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV360"/>
-      <c r="CL360" s="5"/>
     </row>
     <row r="361" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV361"/>
       <c r="CL361" s="5"/>
+    </row>
+    <row r="362" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV362"/>
+      <c r="CL362" s="5"/>
     </row>
     <row r="363" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL363" s="5"/>
@@ -9066,11 +9154,8 @@
     <row r="367" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL367" s="5"/>
     </row>
-    <row r="370" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL370" s="5"/>
-    </row>
-    <row r="371" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL371" s="5"/>
+    <row r="369" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL369" s="5"/>
     </row>
     <row r="372" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL372" s="5"/>
@@ -9085,20 +9170,20 @@
       <c r="CL375" s="5"/>
     </row>
     <row r="376" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV376"/>
+      <c r="CL376" s="5"/>
     </row>
     <row r="377" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV377"/>
       <c r="CL377" s="5"/>
     </row>
     <row r="378" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV378"/>
-      <c r="CL378" s="5"/>
     </row>
     <row r="379" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV379"/>
       <c r="CL379" s="5"/>
     </row>
     <row r="380" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV380"/>
       <c r="CL380" s="5"/>
     </row>
     <row r="381" spans="74:90" x14ac:dyDescent="0.25">
@@ -9107,72 +9192,75 @@
     <row r="382" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL382" s="5"/>
     </row>
+    <row r="383" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL383" s="5"/>
+    </row>
     <row r="384" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL384" s="5"/>
     </row>
-    <row r="385" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL385" s="5"/>
-    </row>
     <row r="386" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV386"/>
+      <c r="CL386" s="5"/>
     </row>
     <row r="387" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV387"/>
       <c r="CL387" s="5"/>
     </row>
     <row r="388" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV388"/>
-      <c r="CL388" s="5"/>
     </row>
     <row r="389" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV389"/>
       <c r="CL389" s="5"/>
     </row>
     <row r="390" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV390"/>
       <c r="CL390" s="5"/>
+    </row>
+    <row r="391" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL391" s="5"/>
     </row>
     <row r="392" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL392" s="5"/>
     </row>
-    <row r="393" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL393" s="5"/>
-    </row>
     <row r="394" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV394"/>
       <c r="CL394" s="5"/>
     </row>
     <row r="395" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV395"/>
       <c r="CL395" s="5"/>
     </row>
     <row r="396" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV396"/>
       <c r="CL396" s="5"/>
     </row>
     <row r="397" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV397"/>
       <c r="CL397" s="5"/>
     </row>
     <row r="398" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL398" s="5"/>
     </row>
+    <row r="399" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL399" s="5"/>
+    </row>
     <row r="400" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV400"/>
       <c r="CL400" s="5"/>
     </row>
-    <row r="401" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL401" s="5"/>
-    </row>
     <row r="402" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV402"/>
       <c r="CL402" s="5"/>
     </row>
+    <row r="403" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL403" s="5"/>
+    </row>
     <row r="404" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV404"/>
       <c r="CL404" s="5"/>
     </row>
-    <row r="405" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV405"/>
-      <c r="CL405" s="5"/>
-    </row>
     <row r="406" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV406"/>
       <c r="CL406" s="5"/>
+    </row>
+    <row r="407" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV407"/>
+      <c r="CL407" s="5"/>
     </row>
     <row r="408" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL408" s="5"/>
@@ -9180,47 +9268,44 @@
     <row r="410" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL410" s="5"/>
     </row>
-    <row r="413" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL413" s="5"/>
-    </row>
-    <row r="414" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL414" s="5"/>
-    </row>
-    <row r="418" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV418"/>
-    </row>
-    <row r="419" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV419"/>
-      <c r="CL419" s="5"/>
+    <row r="412" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL412" s="5"/>
+    </row>
+    <row r="415" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL415" s="5"/>
+    </row>
+    <row r="416" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL416" s="5"/>
     </row>
     <row r="420" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV420"/>
-      <c r="CL420" s="5"/>
     </row>
     <row r="421" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV421"/>
       <c r="CL421" s="5"/>
     </row>
     <row r="422" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV422"/>
       <c r="CL422" s="5"/>
     </row>
     <row r="423" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV423"/>
+      <c r="CL423" s="5"/>
     </row>
     <row r="424" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL424" s="5"/>
     </row>
+    <row r="425" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV425"/>
+    </row>
     <row r="426" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL426" s="5"/>
     </row>
-    <row r="427" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL427" s="5"/>
+    <row r="428" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL428" s="5"/>
     </row>
     <row r="429" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL429" s="5"/>
     </row>
-    <row r="430" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL430" s="5"/>
-    </row>
     <row r="431" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL431" s="5"/>
     </row>
@@ -9236,79 +9321,77 @@
     <row r="435" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL435" s="5"/>
     </row>
+    <row r="436" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL436" s="5"/>
+    </row>
     <row r="437" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV437"/>
-    </row>
-    <row r="438" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL438" s="5"/>
+      <c r="CL437" s="5"/>
     </row>
     <row r="439" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL439" s="5"/>
-    </row>
-    <row r="472" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BU472" s="10"/>
-      <c r="BV472" s="11"/>
-    </row>
-    <row r="473" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="H473" s="10"/>
-      <c r="CL473" s="10"/>
-    </row>
-    <row r="479" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BV479"/>
-    </row>
-    <row r="480" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BV480"/>
-      <c r="CL480" s="5"/>
+      <c r="BV439"/>
+    </row>
+    <row r="440" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL440" s="5"/>
+    </row>
+    <row r="441" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL441" s="5"/>
+    </row>
+    <row r="474" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BU474" s="10"/>
+      <c r="BV474" s="11"/>
+    </row>
+    <row r="475" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="H475" s="10"/>
+      <c r="CL475" s="10"/>
     </row>
     <row r="481" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV481"/>
-      <c r="CL481" s="5"/>
     </row>
     <row r="482" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV482"/>
       <c r="CL482" s="5"/>
     </row>
-    <row r="499" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV499"/>
-    </row>
-    <row r="500" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL500" s="5"/>
-    </row>
-    <row r="532" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV532"/>
-    </row>
-    <row r="533" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV533"/>
-      <c r="CL533" s="5"/>
+    <row r="483" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV483"/>
+      <c r="CL483" s="5"/>
+    </row>
+    <row r="484" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL484" s="5"/>
+    </row>
+    <row r="501" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV501"/>
+    </row>
+    <row r="502" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL502" s="5"/>
     </row>
     <row r="534" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL534" s="5"/>
-    </row>
-    <row r="550" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV550"/>
-    </row>
-    <row r="551" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL551" s="5"/>
-    </row>
-    <row r="557" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV557"/>
-    </row>
-    <row r="558" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV558"/>
-      <c r="CL558" s="5"/>
+      <c r="BV534"/>
+    </row>
+    <row r="535" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV535"/>
+      <c r="CL535" s="5"/>
+    </row>
+    <row r="536" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL536" s="5"/>
+    </row>
+    <row r="552" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV552"/>
+    </row>
+    <row r="553" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL553" s="5"/>
     </row>
     <row r="559" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL559" s="5"/>
-    </row>
-    <row r="564" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV564"/>
-    </row>
-    <row r="565" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV565"/>
-      <c r="CL565" s="5"/>
+      <c r="BV559"/>
+    </row>
+    <row r="560" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV560"/>
+      <c r="CL560" s="5"/>
+    </row>
+    <row r="561" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL561" s="5"/>
     </row>
     <row r="566" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV566"/>
-      <c r="CL566" s="5"/>
     </row>
     <row r="567" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV567"/>
@@ -9363,44 +9446,44 @@
       <c r="CL579" s="5"/>
     </row>
     <row r="580" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV580"/>
       <c r="CL580" s="5"/>
     </row>
-    <row r="584" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV584"/>
-    </row>
-    <row r="585" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV585"/>
-      <c r="CL585" s="5"/>
+    <row r="581" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV581"/>
+      <c r="CL581" s="5"/>
+    </row>
+    <row r="582" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL582" s="5"/>
     </row>
     <row r="586" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL586" s="5"/>
+      <c r="BV586"/>
     </row>
     <row r="587" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV587"/>
+      <c r="CL587" s="5"/>
     </row>
     <row r="588" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL588" s="5"/>
     </row>
-    <row r="591" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV591"/>
-    </row>
-    <row r="592" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV592"/>
-      <c r="CL592" s="5"/>
-    </row>
-    <row r="593" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL593" s="5"/>
-    </row>
-    <row r="624" spans="74:74" x14ac:dyDescent="0.25">
-      <c r="BV624"/>
-    </row>
-    <row r="625" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV625"/>
-      <c r="CL625" s="5"/>
+    <row r="589" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV589"/>
+    </row>
+    <row r="590" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL590" s="5"/>
+    </row>
+    <row r="593" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV593"/>
+    </row>
+    <row r="594" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV594"/>
+      <c r="CL594" s="5"/>
+    </row>
+    <row r="595" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL595" s="5"/>
     </row>
     <row r="626" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV626"/>
-      <c r="CL626" s="5"/>
     </row>
     <row r="627" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV627"/>
@@ -9423,132 +9506,132 @@
       <c r="CL631" s="5"/>
     </row>
     <row r="632" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV632"/>
       <c r="CL632" s="5"/>
     </row>
+    <row r="633" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV633"/>
+      <c r="CL633" s="5"/>
+    </row>
     <row r="634" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV634"/>
-    </row>
-    <row r="635" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL635" s="5"/>
-    </row>
-    <row r="639" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV639"/>
-    </row>
-    <row r="640" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL640" s="5"/>
-    </row>
-    <row r="643" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV643"/>
-    </row>
-    <row r="644" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV644"/>
-      <c r="CL644" s="5"/>
+      <c r="CL634" s="5"/>
+    </row>
+    <row r="636" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV636"/>
+    </row>
+    <row r="637" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL637" s="5"/>
+    </row>
+    <row r="641" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV641"/>
+    </row>
+    <row r="642" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL642" s="5"/>
     </row>
     <row r="645" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV645"/>
-      <c r="CL645" s="5"/>
     </row>
     <row r="646" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV646"/>
       <c r="CL646" s="5"/>
     </row>
     <row r="647" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV647"/>
       <c r="CL647" s="5"/>
     </row>
-    <row r="654" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV654"/>
-    </row>
-    <row r="655" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL655" s="5"/>
-    </row>
-    <row r="658" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV658"/>
-    </row>
-    <row r="659" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV659"/>
-      <c r="CL659" s="5"/>
+    <row r="648" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV648"/>
+      <c r="CL648" s="5"/>
+    </row>
+    <row r="649" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL649" s="5"/>
+    </row>
+    <row r="656" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV656"/>
+    </row>
+    <row r="657" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL657" s="5"/>
     </row>
     <row r="660" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV660"/>
-      <c r="CL660" s="5"/>
     </row>
     <row r="661" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV661"/>
       <c r="CL661" s="5"/>
     </row>
     <row r="662" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV662"/>
       <c r="CL662" s="5"/>
     </row>
+    <row r="663" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV663"/>
+      <c r="CL663" s="5"/>
+    </row>
     <row r="664" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV664"/>
-    </row>
-    <row r="665" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV665"/>
-      <c r="CL665" s="5"/>
+      <c r="CL664" s="5"/>
     </row>
     <row r="666" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL666" s="5"/>
+      <c r="BV666"/>
     </row>
     <row r="667" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL667">
-        <v>0.15</v>
-      </c>
+      <c r="BV667"/>
+      <c r="CL667" s="5"/>
+    </row>
+    <row r="668" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL668" s="5"/>
     </row>
     <row r="669" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL669">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="671" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL671">
         <v>0.2</v>
-      </c>
-    </row>
-    <row r="670" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL670">
-        <v>0.1</v>
       </c>
     </row>
     <row r="672" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL672">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="674" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL674">
         <v>0.2</v>
-      </c>
-    </row>
-    <row r="679" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL679">
-        <v>1</v>
       </c>
     </row>
     <row r="681" spans="90:90" x14ac:dyDescent="0.25">
       <c r="CL681">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="683" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL683">
         <v>0.4</v>
       </c>
     </row>
-    <row r="682" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL682">
+    <row r="684" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL684">
         <v>0.6</v>
-      </c>
-    </row>
-    <row r="685" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL685">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="686" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL686">
-        <v>0.66700000000000004</v>
       </c>
     </row>
     <row r="687" spans="90:90" x14ac:dyDescent="0.25">
       <c r="CL687">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="688" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL688">
+        <v>0.66700000000000004</v>
+      </c>
+    </row>
+    <row r="689" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL689">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="690" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV690"/>
-    </row>
-    <row r="691" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV691"/>
-      <c r="CL691" s="5"/>
     </row>
     <row r="692" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV692"/>
-      <c r="CL692" s="5"/>
     </row>
     <row r="693" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV693"/>
@@ -9575,24 +9658,24 @@
       <c r="CL698" s="5"/>
     </row>
     <row r="699" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV699"/>
       <c r="CL699" s="5"/>
     </row>
     <row r="700" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV700"/>
+      <c r="CL700" s="5"/>
     </row>
     <row r="701" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL701" s="5"/>
     </row>
-    <row r="710" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV710"/>
-    </row>
-    <row r="711" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV711"/>
-      <c r="CL711" s="5"/>
+    <row r="702" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV702"/>
+    </row>
+    <row r="703" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL703" s="5"/>
     </row>
     <row r="712" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV712"/>
-      <c r="CL712" s="5"/>
     </row>
     <row r="713" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV713"/>
@@ -9615,124 +9698,124 @@
       <c r="CL717" s="5"/>
     </row>
     <row r="718" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV718"/>
       <c r="CL718" s="5"/>
     </row>
     <row r="719" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV719"/>
+      <c r="CL719" s="5"/>
     </row>
     <row r="720" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL720" s="5"/>
     </row>
-    <row r="725" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV725"/>
-    </row>
-    <row r="726" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV726"/>
-      <c r="CL726" s="5"/>
+    <row r="721" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV721"/>
+    </row>
+    <row r="722" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL722" s="5"/>
     </row>
     <row r="727" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL727" s="5"/>
+      <c r="BV727"/>
     </row>
     <row r="728" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV728"/>
+      <c r="CL728" s="5"/>
     </row>
     <row r="729" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV729"/>
       <c r="CL729" s="5"/>
     </row>
     <row r="730" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL730" s="5"/>
+      <c r="BV730"/>
     </row>
     <row r="731" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV731"/>
+      <c r="CL731" s="5"/>
     </row>
     <row r="732" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV732"/>
       <c r="CL732" s="5"/>
     </row>
     <row r="733" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV733"/>
-      <c r="CL733" s="5"/>
     </row>
     <row r="734" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV734"/>
       <c r="CL734" s="5"/>
     </row>
     <row r="735" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV735"/>
       <c r="CL735" s="5"/>
     </row>
-    <row r="739" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BV739"/>
-    </row>
-    <row r="740" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BV740"/>
-      <c r="CL740" s="5"/>
+    <row r="736" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV736"/>
+      <c r="CL736" s="5"/>
+    </row>
+    <row r="737" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="CL737" s="5"/>
     </row>
     <row r="741" spans="8:90" x14ac:dyDescent="0.25">
       <c r="BV741"/>
-      <c r="CL741" s="5"/>
     </row>
     <row r="742" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV742"/>
       <c r="CL742" s="5"/>
     </row>
     <row r="743" spans="8:90" x14ac:dyDescent="0.25">
       <c r="BV743"/>
+      <c r="CL743" s="5"/>
     </row>
     <row r="744" spans="8:90" x14ac:dyDescent="0.25">
       <c r="CL744" s="5"/>
     </row>
     <row r="745" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BU745" s="10"/>
-      <c r="BV745" s="11"/>
+      <c r="BV745"/>
     </row>
     <row r="746" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="H746" s="10"/>
-      <c r="CL746" s="10"/>
-    </row>
-    <row r="763" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV763"/>
-    </row>
-    <row r="764" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV764"/>
-      <c r="CL764" s="5"/>
+      <c r="CL746" s="5"/>
+    </row>
+    <row r="747" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BU747" s="10"/>
+      <c r="BV747" s="11"/>
+    </row>
+    <row r="748" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="H748" s="10"/>
+      <c r="CL748" s="10"/>
     </row>
     <row r="765" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV765"/>
-      <c r="CL765" s="5"/>
     </row>
     <row r="766" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV766"/>
       <c r="CL766" s="5"/>
     </row>
     <row r="767" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV767"/>
       <c r="CL767" s="5"/>
     </row>
     <row r="768" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV768"/>
+      <c r="CL768" s="5"/>
     </row>
     <row r="769" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BV769"/>
       <c r="CL769" s="5"/>
     </row>
     <row r="770" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BU770" s="10"/>
-      <c r="BV770" s="11"/>
-      <c r="CL770" s="5"/>
+      <c r="BV770"/>
     </row>
     <row r="771" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="H771" s="10"/>
-      <c r="CL771" s="10"/>
-    </row>
-    <row r="774" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BV774"/>
-    </row>
-    <row r="775" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BV775"/>
-      <c r="CL775" s="5"/>
+      <c r="BV771"/>
+      <c r="CL771" s="5"/>
+    </row>
+    <row r="772" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BU772" s="10"/>
+      <c r="BV772" s="11"/>
+      <c r="CL772" s="5"/>
+    </row>
+    <row r="773" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="H773" s="10"/>
+      <c r="CL773" s="10"/>
     </row>
     <row r="776" spans="8:90" x14ac:dyDescent="0.25">
       <c r="BV776"/>
-      <c r="CL776" s="5"/>
     </row>
     <row r="777" spans="8:90" x14ac:dyDescent="0.25">
       <c r="BV777"/>
@@ -9755,18 +9838,18 @@
       <c r="CL781" s="5"/>
     </row>
     <row r="782" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV782"/>
       <c r="CL782" s="5"/>
     </row>
+    <row r="783" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV783"/>
+      <c r="CL783" s="5"/>
+    </row>
     <row r="784" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BV784"/>
-    </row>
-    <row r="785" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV785"/>
-      <c r="CL785" s="5"/>
+      <c r="CL784" s="5"/>
     </row>
     <row r="786" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV786"/>
-      <c r="CL786" s="5"/>
     </row>
     <row r="787" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV787"/>
@@ -9781,18 +9864,18 @@
       <c r="CL789" s="5"/>
     </row>
     <row r="790" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV790"/>
       <c r="CL790" s="5"/>
     </row>
     <row r="791" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV791"/>
+      <c r="CL791" s="5"/>
     </row>
     <row r="792" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV792"/>
       <c r="CL792" s="5"/>
     </row>
     <row r="793" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV793"/>
-      <c r="CL793" s="5"/>
     </row>
     <row r="794" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV794"/>
@@ -9903,21 +9986,29 @@
       <c r="CL820" s="5"/>
     </row>
     <row r="821" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV821"/>
       <c r="CL821" s="5"/>
     </row>
     <row r="822" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV822"/>
+      <c r="CL822" s="5"/>
     </row>
     <row r="823" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV823"/>
       <c r="CL823" s="5"/>
     </row>
     <row r="824" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV824"/>
-      <c r="CL824" s="5"/>
     </row>
     <row r="825" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV825"/>
       <c r="CL825" s="5"/>
+    </row>
+    <row r="826" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV826"/>
+      <c r="CL826" s="5"/>
+    </row>
+    <row r="827" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL827" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="14" type="noConversion"/>
@@ -10111,7 +10202,7 @@
         <v>491</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="Q7" s="2"/>
     </row>
@@ -10163,7 +10254,7 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>466</v>
@@ -10171,7 +10262,7 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>468</v>
@@ -10180,12 +10271,12 @@
         <v>1</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>466</v>

--- a/Excel/Diy优胜/萃儿.xlsx
+++ b/Excel/Diy优胜/萃儿.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Diy优胜\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{134BFA38-141D-418D-8841-78EBEEFAF564}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12286A33-FCC6-4879-BA34-7CBC153F54C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -302,7 +302,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="927" uniqueCount="558">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="560">
   <si>
     <t>Id</t>
   </si>
@@ -1914,9 +1914,6 @@
   </si>
   <si>
     <t>萃儿3攻击间隔缩短</t>
-  </si>
-  <si>
-    <t>萃儿3攻击间隔缩短</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
@@ -2082,11 +2079,22 @@
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>{"技能Id列表":["萃儿3击杀生成萃蔓","萃儿3我方死亡生成萃蔓","萃儿3撤退生成萃蔓"]}</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
     <t>{"技能Id列表":["萃儿3普攻","萃儿3"]}</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>特技激活</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"技能Id列表":["萃儿3击杀生成萃蔓","萃儿3我方死亡生成萃蔓","萃儿3撤退生成萃蔓","萃儿3协同标记"]}</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>嘉维尔buff</t>
+  </si>
+  <si>
+    <t>范围治疗</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
 </sst>
@@ -3269,26 +3277,26 @@
       <c r="J5">
         <v>90</v>
       </c>
-      <c r="K5">
-        <v>1920</v>
+      <c r="K5" s="2">
+        <v>1949</v>
       </c>
       <c r="M5">
-        <v>750</v>
+        <v>520</v>
       </c>
       <c r="O5">
-        <v>130</v>
+        <v>180</v>
       </c>
       <c r="Q5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="U5">
         <v>0.5</v>
       </c>
       <c r="V5">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="Y5">
         <v>0.05</v>
@@ -3309,7 +3317,7 @@
         <v>485</v>
       </c>
       <c r="AJ5" s="2" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="AK5">
         <v>0</v>
@@ -3423,13 +3431,13 @@
         <v>0</v>
       </c>
       <c r="AG6" s="17" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="AH6" s="2" t="s">
         <v>427</v>
       </c>
       <c r="AI6" s="2" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="AJ6" s="2"/>
       <c r="AK6">
@@ -3527,7 +3535,7 @@
         <v>427</v>
       </c>
       <c r="AI7" s="2" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="AJ7" s="2"/>
       <c r="AK7">
@@ -6920,7 +6928,7 @@
         <v>270</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="AN2" t="s">
         <v>271</v>
@@ -7505,7 +7513,7 @@
         <v>449</v>
       </c>
       <c r="P6" s="7" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="AC6">
         <v>1</v>
@@ -7621,7 +7629,7 @@
         <v>471</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AC9">
         <v>1</v>
@@ -7647,7 +7655,7 @@
     </row>
     <row r="10" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>476</v>
@@ -7707,6 +7715,9 @@
       <c r="C11" s="2" t="s">
         <v>476</v>
       </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
       <c r="K11" s="5" t="s">
         <v>471</v>
       </c>
@@ -7716,6 +7727,9 @@
       <c r="AC11">
         <v>1</v>
       </c>
+      <c r="AF11">
+        <v>1</v>
+      </c>
       <c r="AG11" s="2" t="s">
         <v>492</v>
       </c>
@@ -7727,10 +7741,19 @@
       </c>
       <c r="CL11" s="5"/>
       <c r="CN11" s="2" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="CR11">
         <v>9999</v>
+      </c>
+      <c r="DD11">
+        <v>1</v>
+      </c>
+      <c r="DG11">
+        <v>1</v>
+      </c>
+      <c r="DH11">
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:113" x14ac:dyDescent="0.25">
@@ -7911,7 +7934,12 @@
       <c r="CI14" t="s">
         <v>434</v>
       </c>
-      <c r="CN14" s="3"/>
+      <c r="CN14" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="CR14">
+        <v>9999</v>
+      </c>
       <c r="CY14" t="s">
         <v>453</v>
       </c>
@@ -8025,10 +8053,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:103" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:112" x14ac:dyDescent="0.25">
       <c r="BV17"/>
     </row>
-    <row r="18" spans="1:103" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>508</v>
       </c>
@@ -8062,7 +8090,7 @@
         <v>1</v>
       </c>
       <c r="BO18" s="2" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="BP18" s="2"/>
       <c r="BT18">
@@ -8081,7 +8109,7 @@
         <v>496</v>
       </c>
       <c r="CN18" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="CO18">
         <v>-0.4</v>
@@ -8090,19 +8118,19 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:103" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="J19" s="5"/>
       <c r="K19" s="5" t="s">
         <v>471</v>
       </c>
       <c r="L19" s="5" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="M19"/>
       <c r="O19" s="3"/>
@@ -8122,12 +8150,12 @@
       </c>
       <c r="CN19" s="2"/>
       <c r="CU19" s="2" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="20" spans="1:103" x14ac:dyDescent="0.25">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="20" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>470</v>
@@ -8136,7 +8164,7 @@
         <v>471</v>
       </c>
       <c r="L20" s="5" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="O20" s="2" t="s">
         <v>479</v>
@@ -8160,9 +8188,9 @@
         <v>483</v>
       </c>
     </row>
-    <row r="21" spans="1:103" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>476</v>
@@ -8171,10 +8199,10 @@
         <v>471</v>
       </c>
       <c r="L21" s="5" t="s">
+        <v>525</v>
+      </c>
+      <c r="O21" s="18" t="s">
         <v>526</v>
-      </c>
-      <c r="O21" s="18" t="s">
-        <v>527</v>
       </c>
       <c r="AC21">
         <v>2</v>
@@ -8189,26 +8217,26 @@
       <c r="BV21"/>
       <c r="CL21" s="5"/>
       <c r="CN21" s="2" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="CR21">
         <v>9999</v>
       </c>
       <c r="CU21" s="2"/>
     </row>
-    <row r="22" spans="1:103" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="J22" s="5"/>
       <c r="K22" s="5" t="s">
         <v>471</v>
       </c>
       <c r="L22" s="5" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="M22"/>
       <c r="O22" s="3"/>
@@ -8225,12 +8253,12 @@
       </c>
       <c r="CN22" s="2"/>
       <c r="CU22" s="2" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="23" spans="1:103" x14ac:dyDescent="0.25">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="23" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>470</v>
@@ -8239,7 +8267,7 @@
         <v>471</v>
       </c>
       <c r="L23" s="5" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="AC23">
@@ -8259,9 +8287,9 @@
         <v>483</v>
       </c>
     </row>
-    <row r="24" spans="1:103" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>470</v>
@@ -8270,7 +8298,7 @@
         <v>471</v>
       </c>
       <c r="L24" s="5" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="Q24" s="2" t="s">
         <v>479</v>
@@ -8294,9 +8322,9 @@
         <v>483</v>
       </c>
     </row>
-    <row r="25" spans="1:103" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>470</v>
@@ -8305,7 +8333,7 @@
         <v>471</v>
       </c>
       <c r="L25" s="5" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="Q25" s="2" t="s">
         <v>479</v>
@@ -8329,7 +8357,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="26" spans="1:103" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:112" x14ac:dyDescent="0.25">
       <c r="M26"/>
       <c r="AY26" s="5"/>
       <c r="BV26"/>
@@ -8349,19 +8377,20 @@
       <c r="CK26" s="5"/>
       <c r="CN26" s="3"/>
     </row>
-    <row r="27" spans="1:103" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C27" t="s">
         <v>448</v>
       </c>
+      <c r="J27" s="2" t="s">
+        <v>556</v>
+      </c>
       <c r="K27" s="5" t="s">
         <v>449</v>
       </c>
-      <c r="O27" s="18" t="s">
-        <v>513</v>
-      </c>
+      <c r="O27" s="18"/>
       <c r="P27" s="7"/>
       <c r="AC27">
         <v>1</v>
@@ -8403,21 +8432,22 @@
         <v>453</v>
       </c>
     </row>
-    <row r="28" spans="1:103" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>476</v>
       </c>
+      <c r="J28" s="2" t="s">
+        <v>556</v>
+      </c>
       <c r="K28" s="5" t="s">
         <v>496</v>
       </c>
       <c r="M28"/>
       <c r="N28"/>
-      <c r="O28" s="18" t="s">
-        <v>513</v>
-      </c>
+      <c r="O28" s="18"/>
       <c r="Q28" s="5" t="s">
         <v>479</v>
       </c>
@@ -8440,29 +8470,30 @@
       <c r="CI28" s="5"/>
       <c r="CJ28" s="5"/>
       <c r="CN28" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="CR28">
         <v>0.02</v>
       </c>
     </row>
-    <row r="29" spans="1:103" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>476</v>
       </c>
+      <c r="J29" s="2" t="s">
+        <v>556</v>
+      </c>
       <c r="K29" s="5" t="s">
         <v>496</v>
       </c>
       <c r="M29"/>
       <c r="N29"/>
-      <c r="O29" s="18" t="s">
-        <v>513</v>
-      </c>
+      <c r="O29" s="18"/>
       <c r="Q29" s="5" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="AC29">
         <v>2</v>
@@ -8471,7 +8502,7 @@
         <v>20</v>
       </c>
       <c r="AX29" s="2" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="AZ29">
         <v>0.8</v>
@@ -8481,24 +8512,28 @@
       </c>
       <c r="BV29"/>
       <c r="CJ29" s="5"/>
+      <c r="CM29" s="2" t="s">
+        <v>522</v>
+      </c>
       <c r="CY29" s="2" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="30" spans="1:103" x14ac:dyDescent="0.25">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="30" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="C30" s="2" t="s">
-        <v>539</v>
+      <c r="J30" s="2" t="s">
+        <v>556</v>
       </c>
       <c r="K30" s="5" t="s">
         <v>496</v>
       </c>
       <c r="M30"/>
-      <c r="O30" s="18" t="s">
-        <v>513</v>
-      </c>
+      <c r="O30" s="18"/>
       <c r="Q30" s="5" t="s">
         <v>491</v>
       </c>
@@ -8518,26 +8553,39 @@
       </c>
       <c r="BO30" s="2"/>
       <c r="BP30" s="2"/>
+      <c r="BT30">
+        <v>30</v>
+      </c>
       <c r="CG30" s="2"/>
       <c r="CM30" s="2"/>
       <c r="CU30" s="2" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="31" spans="1:103" x14ac:dyDescent="0.25">
+        <v>555</v>
+      </c>
+      <c r="DD30">
+        <v>1</v>
+      </c>
+      <c r="DG30">
+        <v>1</v>
+      </c>
+      <c r="DH30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>476</v>
       </c>
+      <c r="J31" s="2" t="s">
+        <v>556</v>
+      </c>
       <c r="K31" s="5" t="s">
         <v>496</v>
       </c>
       <c r="M31"/>
-      <c r="O31" s="18" t="s">
-        <v>513</v>
-      </c>
+      <c r="O31" s="18"/>
       <c r="Q31" s="5" t="s">
         <v>479</v>
       </c>
@@ -8557,13 +8605,13 @@
       </c>
       <c r="CG31" s="2"/>
       <c r="CN31" s="2" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="CR31">
         <v>0.02</v>
       </c>
     </row>
-    <row r="32" spans="1:103" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:112" x14ac:dyDescent="0.25">
       <c r="BU32" s="6"/>
       <c r="CA32"/>
     </row>
@@ -10193,6 +10241,9 @@
       <c r="H6">
         <v>1</v>
       </c>
+      <c r="J6" s="2" t="s">
+        <v>559</v>
+      </c>
       <c r="Q6" s="2" t="s">
         <v>469</v>
       </c>
@@ -10202,7 +10253,7 @@
         <v>491</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="Q7" s="2"/>
     </row>
@@ -10243,18 +10294,18 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>501</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>466</v>
@@ -10262,7 +10313,7 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>468</v>
@@ -10270,13 +10321,16 @@
       <c r="H14">
         <v>1</v>
       </c>
+      <c r="J14" t="s">
+        <v>558</v>
+      </c>
       <c r="Q14" s="2" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>466</v>
@@ -10453,7 +10507,7 @@
         <v>459</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -10476,7 +10530,7 @@
         <v>456</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Diy优胜/萃儿.xlsx
+++ b/Excel/Diy优胜/萃儿.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Diy优胜\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12286A33-FCC6-4879-BA34-7CBC153F54C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2203A1F7-1A84-4097-A289-8C02F76A3CD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -302,7 +302,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="560">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="561">
   <si>
     <t>Id</t>
   </si>
@@ -388,12 +388,6 @@
     <t>高度</t>
   </si>
   <si>
-    <t>高台单位？</t>
-  </si>
-  <si>
-    <t>地面</t>
-  </si>
-  <si>
     <t>阻挡个数</t>
   </si>
   <si>
@@ -550,12 +544,6 @@
     <t>Height</t>
   </si>
   <si>
-    <t>CanSetHigh</t>
-  </si>
-  <si>
-    <t>CanSetGround</t>
-  </si>
-  <si>
     <t>StopCount</t>
   </si>
   <si>
@@ -2095,6 +2083,26 @@
   </si>
   <si>
     <t>范围治疗</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>可部署位</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>CanSetPos</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>string[]</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>高台位</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>全地形</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
 </sst>
@@ -2648,10 +2656,10 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
     </row>
   </sheetData>
@@ -2662,7 +2670,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:BS598"/>
+  <dimension ref="A1:BR598"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.58203125" customWidth="1"/>
@@ -2693,22 +2701,22 @@
     <col min="35" max="35" width="63.75" customWidth="1"/>
     <col min="36" max="36" width="20.1640625" customWidth="1"/>
     <col min="37" max="37" width="9.83203125" customWidth="1"/>
-    <col min="43" max="43" width="12.5" customWidth="1"/>
-    <col min="50" max="50" width="24.33203125" customWidth="1"/>
-    <col min="52" max="52" width="17.75" customWidth="1"/>
-    <col min="53" max="53" width="7.83203125" customWidth="1"/>
-    <col min="56" max="56" width="24.25" customWidth="1"/>
-    <col min="57" max="57" width="13.25" customWidth="1"/>
-    <col min="58" max="58" width="16.08203125" customWidth="1"/>
-    <col min="59" max="59" width="8" customWidth="1"/>
-    <col min="64" max="64" width="39.58203125" customWidth="1"/>
-    <col min="65" max="65" width="14" customWidth="1"/>
-    <col min="66" max="66" width="14.83203125" customWidth="1"/>
-    <col min="67" max="70" width="14" customWidth="1"/>
-    <col min="71" max="71" width="19.1640625" customWidth="1"/>
+    <col min="42" max="42" width="12.5" customWidth="1"/>
+    <col min="49" max="49" width="24.33203125" customWidth="1"/>
+    <col min="51" max="51" width="17.75" customWidth="1"/>
+    <col min="52" max="52" width="7.83203125" customWidth="1"/>
+    <col min="55" max="55" width="24.25" customWidth="1"/>
+    <col min="56" max="56" width="13.25" customWidth="1"/>
+    <col min="57" max="57" width="16.08203125" customWidth="1"/>
+    <col min="58" max="58" width="8" customWidth="1"/>
+    <col min="63" max="63" width="39.58203125" customWidth="1"/>
+    <col min="64" max="64" width="14" customWidth="1"/>
+    <col min="65" max="65" width="14.83203125" customWidth="1"/>
+    <col min="66" max="69" width="14" customWidth="1"/>
+    <col min="70" max="70" width="19.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="D1" t="s">
         <v>4</v>
       </c>
@@ -2784,274 +2792,268 @@
       <c r="AL1" t="s">
         <v>27</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AM1" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="AN1" t="s">
         <v>28</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>29</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>30</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AR1" t="s">
         <v>31</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AS1" t="s">
         <v>32</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AT1" t="s">
         <v>33</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AU1" t="s">
         <v>34</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AV1" t="s">
         <v>35</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AW1" t="s">
         <v>36</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AX1" t="s">
         <v>37</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AY1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AZ1" t="s">
         <v>39</v>
       </c>
-      <c r="AZ1" s="2" t="s">
+      <c r="BC1" t="s">
         <v>40</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BD1" t="s">
         <v>41</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BE1" t="s">
         <v>42</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BF1" t="s">
         <v>43</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BG1" t="s">
         <v>44</v>
       </c>
-      <c r="BG1" t="s">
-        <v>45</v>
-      </c>
-      <c r="BH1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="1:71" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" t="s">
         <v>47</v>
       </c>
-      <c r="C2" t="s">
+      <c r="G2" t="s">
         <v>48</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>49</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>50</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>51</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>52</v>
       </c>
-      <c r="J2" t="s">
+      <c r="L2" t="s">
         <v>53</v>
       </c>
-      <c r="K2" t="s">
+      <c r="M2" t="s">
         <v>54</v>
       </c>
-      <c r="L2" t="s">
+      <c r="N2" t="s">
         <v>55</v>
       </c>
-      <c r="M2" t="s">
+      <c r="O2" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="N2" t="s">
+      <c r="P2" t="s">
         <v>57</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="Q2" t="s">
         <v>58</v>
       </c>
-      <c r="P2" t="s">
+      <c r="R2" t="s">
         <v>59</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="S2" t="s">
         <v>60</v>
       </c>
-      <c r="R2" t="s">
+      <c r="T2" t="s">
         <v>61</v>
       </c>
-      <c r="S2" t="s">
+      <c r="U2" t="s">
         <v>62</v>
       </c>
-      <c r="T2" t="s">
+      <c r="V2" t="s">
         <v>63</v>
       </c>
-      <c r="U2" t="s">
+      <c r="W2" t="s">
         <v>64</v>
       </c>
-      <c r="V2" t="s">
+      <c r="X2" t="s">
         <v>65</v>
       </c>
-      <c r="W2" t="s">
+      <c r="Y2" t="s">
         <v>66</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Z2" t="s">
         <v>67</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="AA2" t="s">
         <v>68</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AB2" t="s">
         <v>69</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AC2" t="s">
         <v>70</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AD2" t="s">
         <v>71</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AE2" t="s">
         <v>72</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AF2" t="s">
         <v>73</v>
       </c>
-      <c r="AE2" t="s">
+      <c r="AG2" t="s">
         <v>74</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AH2" t="s">
         <v>75</v>
       </c>
-      <c r="AG2" t="s">
+      <c r="AI2" t="s">
         <v>76</v>
       </c>
-      <c r="AH2" t="s">
+      <c r="AJ2" t="s">
         <v>77</v>
       </c>
-      <c r="AI2" t="s">
+      <c r="AK2" t="s">
         <v>78</v>
       </c>
-      <c r="AJ2" t="s">
+      <c r="AL2" t="s">
         <v>79</v>
       </c>
-      <c r="AK2" t="s">
+      <c r="AM2" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="AN2" t="s">
         <v>80</v>
       </c>
-      <c r="AL2" t="s">
+      <c r="AO2" t="s">
         <v>81</v>
       </c>
-      <c r="AM2" t="s">
+      <c r="AP2" t="s">
         <v>82</v>
       </c>
-      <c r="AN2" t="s">
+      <c r="AQ2" t="s">
         <v>83</v>
       </c>
-      <c r="AO2" t="s">
+      <c r="AR2" t="s">
         <v>84</v>
       </c>
-      <c r="AP2" t="s">
+      <c r="AS2" t="s">
         <v>85</v>
       </c>
-      <c r="AQ2" t="s">
+      <c r="AT2" t="s">
         <v>86</v>
       </c>
-      <c r="AR2" t="s">
+      <c r="AU2" t="s">
         <v>87</v>
       </c>
-      <c r="AS2" t="s">
+      <c r="AV2" t="s">
         <v>88</v>
       </c>
-      <c r="AT2" t="s">
+      <c r="AW2" t="s">
         <v>89</v>
       </c>
-      <c r="AU2" t="s">
+      <c r="AX2" t="s">
         <v>90</v>
       </c>
-      <c r="AV2" t="s">
+      <c r="AY2" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="AW2" t="s">
+      <c r="AZ2" t="s">
         <v>92</v>
       </c>
-      <c r="AX2" t="s">
+      <c r="BA2" t="s">
         <v>93</v>
       </c>
-      <c r="AY2" t="s">
+      <c r="BB2" t="s">
         <v>94</v>
       </c>
-      <c r="AZ2" s="2" t="s">
+      <c r="BC2" t="s">
         <v>95</v>
       </c>
-      <c r="BA2" t="s">
+      <c r="BD2" t="s">
         <v>96</v>
       </c>
-      <c r="BB2" t="s">
+      <c r="BE2" t="s">
         <v>97</v>
       </c>
-      <c r="BC2" t="s">
+      <c r="BF2" t="s">
         <v>98</v>
       </c>
-      <c r="BD2" t="s">
+      <c r="BG2" t="s">
         <v>99</v>
       </c>
-      <c r="BE2" t="s">
+      <c r="BH2" t="s">
         <v>100</v>
       </c>
-      <c r="BF2" t="s">
+      <c r="BI2" t="s">
         <v>101</v>
       </c>
-      <c r="BG2" t="s">
+      <c r="BJ2" t="s">
         <v>102</v>
       </c>
-      <c r="BH2" t="s">
+      <c r="BK2" t="s">
         <v>103</v>
       </c>
-      <c r="BI2" t="s">
+      <c r="BL2" t="s">
         <v>104</v>
       </c>
-      <c r="BJ2" t="s">
+      <c r="BM2" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="BK2" t="s">
+      <c r="BN2" t="s">
         <v>106</v>
       </c>
-      <c r="BL2" t="s">
+      <c r="BO2" t="s">
         <v>107</v>
       </c>
-      <c r="BM2" t="s">
+      <c r="BP2" t="s">
         <v>108</v>
       </c>
-      <c r="BN2" s="2" t="s">
+      <c r="BQ2" t="s">
         <v>109</v>
       </c>
-      <c r="BO2" t="s">
+      <c r="BR2" t="s">
         <v>110</v>
       </c>
-      <c r="BP2" t="s">
-        <v>111</v>
-      </c>
-      <c r="BQ2" t="s">
-        <v>112</v>
-      </c>
-      <c r="BR2" t="s">
-        <v>113</v>
-      </c>
-      <c r="BS2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="3" spans="1:71" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -3059,88 +3061,88 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="F3" t="s">
         <v>2</v>
       </c>
       <c r="G3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H3" t="s">
         <v>2</v>
       </c>
       <c r="I3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="J3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="K3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="L3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="M3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="N3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="O3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="P3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="Q3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="R3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="S3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="T3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="U3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="V3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="W3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="X3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="Y3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="Z3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="AA3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="AB3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="AC3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="AD3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="AE3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="AF3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="AG3" t="s">
         <v>2</v>
@@ -3149,61 +3151,61 @@
         <v>2</v>
       </c>
       <c r="AI3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AJ3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AK3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="AL3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AM3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AM3" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AP3" t="s">
+        <v>111</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>111</v>
+      </c>
+      <c r="AT3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AU3" t="s">
         <v>115</v>
       </c>
-      <c r="AN3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AO3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AQ3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AS3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AT3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AU3" t="s">
-        <v>117</v>
-      </c>
       <c r="AV3" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="AW3" t="s">
         <v>116</v>
       </c>
       <c r="AX3" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="AY3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="AZ3" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="BA3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="BB3" t="s">
-        <v>121</v>
+        <v>2</v>
       </c>
       <c r="BC3" t="s">
         <v>2</v>
@@ -3215,58 +3217,55 @@
         <v>2</v>
       </c>
       <c r="BF3" t="s">
+        <v>118</v>
+      </c>
+      <c r="BG3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BH3" t="s">
         <v>2</v>
       </c>
-      <c r="BG3" t="s">
-        <v>122</v>
-      </c>
-      <c r="BH3" t="s">
-        <v>117</v>
-      </c>
       <c r="BI3" t="s">
+        <v>119</v>
+      </c>
+      <c r="BJ3" t="s">
         <v>2</v>
       </c>
-      <c r="BJ3" t="s">
-        <v>123</v>
-      </c>
       <c r="BK3" t="s">
-        <v>2</v>
+        <v>120</v>
       </c>
       <c r="BL3" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="BM3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="BN3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="BO3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="BP3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="BQ3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="BR3" t="s">
-        <v>123</v>
-      </c>
-      <c r="BS3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="5" spans="1:71" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="5" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="2" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -3308,85 +3307,82 @@
         <v>1</v>
       </c>
       <c r="AG5" s="2" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="AH5" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="AI5" s="2" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="AJ5" s="2" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="AK5">
         <v>0</v>
       </c>
-      <c r="AM5">
+      <c r="AM5" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="AN5">
         <v>1</v>
       </c>
-      <c r="AN5">
-        <v>0</v>
-      </c>
       <c r="AO5">
+        <v>0.5</v>
+      </c>
+      <c r="AV5">
+        <v>0.25</v>
+      </c>
+      <c r="BA5" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="BC5" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="BD5" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="BE5" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="BF5" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="BG5">
+        <v>6</v>
+      </c>
+      <c r="BH5" s="2"/>
+      <c r="BI5" s="2"/>
+      <c r="BJ5" s="14"/>
+      <c r="BL5" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="BM5" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="BO5" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="BP5" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="BQ5" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="BR5">
         <v>1</v>
       </c>
-      <c r="AP5">
-        <v>0.5</v>
-      </c>
-      <c r="AW5">
-        <v>0.25</v>
-      </c>
-      <c r="BB5" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="BD5" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="BE5" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="BF5" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="BG5" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="BH5">
-        <v>6</v>
-      </c>
-      <c r="BI5" s="2"/>
-      <c r="BJ5" s="2"/>
-      <c r="BK5" s="14"/>
-      <c r="BM5" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="BN5" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="BP5" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="BQ5" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="BR5" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="BS5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:71" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A6" s="17" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="E6" s="12"/>
       <c r="F6" s="2" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -3431,60 +3427,57 @@
         <v>0</v>
       </c>
       <c r="AG6" s="17" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="AH6" s="2" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="AI6" s="2" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="AJ6" s="2"/>
       <c r="AK6">
         <v>3</v>
       </c>
-      <c r="AM6">
+      <c r="AM6" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>0.5</v>
+      </c>
+      <c r="AP6">
         <v>1</v>
       </c>
-      <c r="AN6">
-        <v>1</v>
-      </c>
-      <c r="AO6">
-        <v>0</v>
-      </c>
-      <c r="AP6">
-        <v>0.5</v>
-      </c>
-      <c r="AQ6">
-        <v>1</v>
-      </c>
-      <c r="AV6" s="2"/>
-      <c r="AW6">
+      <c r="AU6" s="2"/>
+      <c r="AV6">
         <v>0.25</v>
       </c>
-      <c r="BB6" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="BD6" s="2"/>
-      <c r="BL6" s="2" t="s">
-        <v>488</v>
-      </c>
+      <c r="BA6" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="BC6" s="2"/>
+      <c r="BK6" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="BL6" s="2"/>
       <c r="BM6" s="2"/>
-      <c r="BN6" s="2"/>
+      <c r="BO6" s="2"/>
       <c r="BP6" s="2"/>
       <c r="BQ6" s="2"/>
-      <c r="BR6" s="2"/>
-    </row>
-    <row r="7" spans="1:71" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="E7" s="12"/>
       <c r="F7" s="2" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -3529,2466 +3522,2463 @@
         <v>0</v>
       </c>
       <c r="AG7" s="17" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="AH7" s="2" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="AI7" s="2" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="AJ7" s="2"/>
       <c r="AK7">
         <v>3</v>
       </c>
-      <c r="AM7">
+      <c r="AM7" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0.5</v>
+      </c>
+      <c r="AP7">
         <v>1</v>
       </c>
-      <c r="AN7">
-        <v>1</v>
-      </c>
-      <c r="AO7">
-        <v>0</v>
-      </c>
-      <c r="AP7">
-        <v>0.5</v>
-      </c>
-      <c r="AQ7">
-        <v>1</v>
-      </c>
-      <c r="AV7" s="2"/>
-      <c r="AW7">
+      <c r="AU7" s="2"/>
+      <c r="AV7">
         <v>0.25</v>
       </c>
-      <c r="BB7" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="BD7" s="2"/>
-      <c r="BL7" s="2" t="s">
-        <v>487</v>
-      </c>
+      <c r="BA7" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="BC7" s="2"/>
+      <c r="BK7" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="BL7" s="2"/>
       <c r="BM7" s="2"/>
-      <c r="BN7" s="2"/>
+      <c r="BO7" s="2"/>
       <c r="BP7" s="2"/>
       <c r="BQ7" s="2"/>
-      <c r="BR7" s="2"/>
-    </row>
-    <row r="8" spans="1:71" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="E8" s="12"/>
       <c r="F8" s="2"/>
       <c r="N8" s="2"/>
       <c r="AG8" s="2"/>
-      <c r="BB8" s="2"/>
-    </row>
-    <row r="9" spans="1:71" x14ac:dyDescent="0.25">
+      <c r="BA8" s="2"/>
+    </row>
+    <row r="9" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="E9" s="12"/>
       <c r="F9" s="2"/>
       <c r="N9" s="2"/>
       <c r="AG9" s="2"/>
       <c r="AI9" s="2"/>
-      <c r="BB9" s="2"/>
-    </row>
-    <row r="10" spans="1:71" x14ac:dyDescent="0.25">
+      <c r="BA9" s="2"/>
+    </row>
+    <row r="10" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="E10" s="12"/>
       <c r="F10" s="2"/>
       <c r="N10" s="2"/>
       <c r="AG10" s="2"/>
       <c r="AI10" s="2"/>
-      <c r="BB10" s="2"/>
-    </row>
-    <row r="11" spans="1:71" x14ac:dyDescent="0.25">
+      <c r="BA10" s="2"/>
+    </row>
+    <row r="11" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="E11" s="12"/>
       <c r="F11" s="2"/>
       <c r="N11" s="2"/>
       <c r="AG11" s="2"/>
       <c r="AI11" s="2"/>
-      <c r="BB11" s="2"/>
-    </row>
-    <row r="13" spans="1:71" x14ac:dyDescent="0.25">
+      <c r="BA11" s="2"/>
+    </row>
+    <row r="13" spans="1:70" x14ac:dyDescent="0.25">
       <c r="E13" s="12"/>
     </row>
-    <row r="14" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:70" x14ac:dyDescent="0.25">
       <c r="E14" s="12"/>
     </row>
-    <row r="15" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:70" x14ac:dyDescent="0.25">
       <c r="E15" s="12"/>
       <c r="AG15" s="2"/>
-      <c r="BP15" s="15"/>
-    </row>
-    <row r="25" spans="35:63" x14ac:dyDescent="0.25">
+      <c r="BO15" s="15"/>
+    </row>
+    <row r="25" spans="35:62" x14ac:dyDescent="0.25">
       <c r="AI25" s="2"/>
     </row>
-    <row r="31" spans="35:63" x14ac:dyDescent="0.25">
+    <row r="31" spans="35:62" x14ac:dyDescent="0.25">
       <c r="AI31" s="2"/>
-      <c r="BK31" s="2"/>
-    </row>
-    <row r="33" spans="4:70" x14ac:dyDescent="0.25">
+      <c r="BJ31" s="2"/>
+    </row>
+    <row r="33" spans="4:69" x14ac:dyDescent="0.25">
       <c r="AI33" s="2"/>
     </row>
-    <row r="34" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="34" spans="4:69" x14ac:dyDescent="0.25">
       <c r="AI34" s="2"/>
     </row>
-    <row r="35" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="35" spans="4:69" x14ac:dyDescent="0.25">
       <c r="AI35" s="2"/>
-      <c r="BK35" s="2"/>
-    </row>
-    <row r="36" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BJ35" s="2"/>
+    </row>
+    <row r="36" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D36" s="13"/>
       <c r="E36" s="12"/>
-      <c r="BO36" s="16"/>
-      <c r="BR36" s="16"/>
-    </row>
-    <row r="37" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN36" s="16"/>
+      <c r="BQ36" s="16"/>
+    </row>
+    <row r="37" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D37" s="13"/>
       <c r="E37" s="12"/>
-      <c r="BO37" s="16"/>
-      <c r="BR37" s="16"/>
-    </row>
-    <row r="38" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN37" s="16"/>
+      <c r="BQ37" s="16"/>
+    </row>
+    <row r="38" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D38" s="13"/>
       <c r="E38" s="12"/>
-      <c r="BO38" s="16"/>
-      <c r="BR38" s="16"/>
-    </row>
-    <row r="39" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN38" s="16"/>
+      <c r="BQ38" s="16"/>
+    </row>
+    <row r="39" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D39" s="13"/>
       <c r="E39" s="12"/>
-      <c r="BO39" s="16"/>
-      <c r="BR39" s="16"/>
-    </row>
-    <row r="40" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN39" s="16"/>
+      <c r="BQ39" s="16"/>
+    </row>
+    <row r="40" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D40" s="13"/>
       <c r="E40" s="12"/>
-      <c r="BO40" s="16"/>
-      <c r="BR40" s="16"/>
-    </row>
-    <row r="41" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN40" s="16"/>
+      <c r="BQ40" s="16"/>
+    </row>
+    <row r="41" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D41" s="13"/>
       <c r="E41" s="12"/>
-      <c r="BO41" s="16"/>
-      <c r="BR41" s="16"/>
-    </row>
-    <row r="42" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN41" s="16"/>
+      <c r="BQ41" s="16"/>
+    </row>
+    <row r="42" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D42" s="13"/>
       <c r="E42" s="12"/>
-      <c r="BO42" s="16"/>
-      <c r="BR42" s="16"/>
-    </row>
-    <row r="43" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN42" s="16"/>
+      <c r="BQ42" s="16"/>
+    </row>
+    <row r="43" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D43" s="13"/>
       <c r="E43" s="12"/>
-      <c r="BR43" s="16"/>
-    </row>
-    <row r="44" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ43" s="16"/>
+    </row>
+    <row r="44" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D44" s="13"/>
       <c r="E44" s="12"/>
-      <c r="BR44" s="16"/>
-    </row>
-    <row r="45" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ44" s="16"/>
+    </row>
+    <row r="45" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D45" s="13"/>
       <c r="E45" s="12"/>
-      <c r="BR45" s="16"/>
-    </row>
-    <row r="46" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ45" s="16"/>
+    </row>
+    <row r="46" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D46" s="13"/>
       <c r="E46" s="12"/>
-      <c r="BO46" s="16"/>
-      <c r="BR46" s="16"/>
-    </row>
-    <row r="47" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN46" s="16"/>
+      <c r="BQ46" s="16"/>
+    </row>
+    <row r="47" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D47" s="13"/>
       <c r="E47" s="12"/>
-      <c r="BO47" s="16"/>
-      <c r="BR47" s="16"/>
-    </row>
-    <row r="48" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN47" s="16"/>
+      <c r="BQ47" s="16"/>
+    </row>
+    <row r="48" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D48" s="13"/>
       <c r="E48" s="12"/>
-      <c r="BO48" s="16"/>
-      <c r="BR48" s="16"/>
-    </row>
-    <row r="49" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN48" s="16"/>
+      <c r="BQ48" s="16"/>
+    </row>
+    <row r="49" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D49" s="13"/>
       <c r="E49" s="12"/>
-      <c r="BO49" s="16"/>
-      <c r="BR49" s="16"/>
-    </row>
-    <row r="50" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN49" s="16"/>
+      <c r="BQ49" s="16"/>
+    </row>
+    <row r="50" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D50" s="13"/>
       <c r="E50" s="12"/>
-      <c r="BO50" s="16"/>
-      <c r="BR50" s="16"/>
-    </row>
-    <row r="51" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN50" s="16"/>
+      <c r="BQ50" s="16"/>
+    </row>
+    <row r="51" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D51" s="13"/>
       <c r="E51" s="12"/>
-      <c r="BO51" s="16"/>
-      <c r="BR51" s="16"/>
-    </row>
-    <row r="52" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN51" s="16"/>
+      <c r="BQ51" s="16"/>
+    </row>
+    <row r="52" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D52" s="13"/>
       <c r="E52" s="12"/>
-      <c r="BO52" s="16"/>
-      <c r="BR52" s="16"/>
-    </row>
-    <row r="53" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN52" s="16"/>
+      <c r="BQ52" s="16"/>
+    </row>
+    <row r="53" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D53" s="13"/>
       <c r="E53" s="12"/>
-      <c r="BO53" s="16"/>
-      <c r="BR53" s="16"/>
-    </row>
-    <row r="54" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN53" s="16"/>
+      <c r="BQ53" s="16"/>
+    </row>
+    <row r="54" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D54" s="13"/>
       <c r="E54" s="12"/>
-      <c r="BO54" s="16"/>
-      <c r="BR54" s="16"/>
-    </row>
-    <row r="55" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN54" s="16"/>
+      <c r="BQ54" s="16"/>
+    </row>
+    <row r="55" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D55" s="13"/>
       <c r="E55" s="12"/>
-      <c r="BO55" s="16"/>
-      <c r="BR55" s="16"/>
-    </row>
-    <row r="56" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN55" s="16"/>
+      <c r="BQ55" s="16"/>
+    </row>
+    <row r="56" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D56" s="13"/>
       <c r="E56" s="12"/>
-      <c r="BO56" s="16"/>
-      <c r="BR56" s="16"/>
-    </row>
-    <row r="57" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN56" s="16"/>
+      <c r="BQ56" s="16"/>
+    </row>
+    <row r="57" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D57" s="13"/>
       <c r="E57" s="12"/>
-      <c r="BO57" s="16"/>
-      <c r="BR57" s="16"/>
-    </row>
-    <row r="58" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN57" s="16"/>
+      <c r="BQ57" s="16"/>
+    </row>
+    <row r="58" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D58" s="13"/>
       <c r="E58" s="12"/>
-      <c r="BO58" s="16"/>
-      <c r="BR58" s="16"/>
-    </row>
-    <row r="59" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN58" s="16"/>
+      <c r="BQ58" s="16"/>
+    </row>
+    <row r="59" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D59" s="13"/>
       <c r="E59" s="12"/>
-      <c r="BO59" s="16"/>
-      <c r="BR59" s="16"/>
-    </row>
-    <row r="60" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN59" s="16"/>
+      <c r="BQ59" s="16"/>
+    </row>
+    <row r="60" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D60" s="13"/>
       <c r="E60" s="12"/>
-      <c r="BO60" s="16"/>
-      <c r="BR60" s="16"/>
-    </row>
-    <row r="61" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN60" s="16"/>
+      <c r="BQ60" s="16"/>
+    </row>
+    <row r="61" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D61" s="13"/>
       <c r="E61" s="12"/>
-      <c r="BO61" s="16"/>
-      <c r="BR61" s="16"/>
-    </row>
-    <row r="62" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN61" s="16"/>
+      <c r="BQ61" s="16"/>
+    </row>
+    <row r="62" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D62" s="13"/>
       <c r="E62" s="12"/>
-      <c r="BO62" s="16"/>
-      <c r="BR62" s="16"/>
-    </row>
-    <row r="63" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN62" s="16"/>
+      <c r="BQ62" s="16"/>
+    </row>
+    <row r="63" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D63" s="13"/>
       <c r="E63" s="12"/>
-      <c r="BO63" s="16"/>
-      <c r="BR63" s="16"/>
-    </row>
-    <row r="64" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN63" s="16"/>
+      <c r="BQ63" s="16"/>
+    </row>
+    <row r="64" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D64" s="13"/>
       <c r="E64" s="12"/>
-      <c r="BO64" s="16"/>
-      <c r="BR64" s="16"/>
-    </row>
-    <row r="65" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN64" s="16"/>
+      <c r="BQ64" s="16"/>
+    </row>
+    <row r="65" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D65" s="13"/>
       <c r="E65" s="12"/>
-      <c r="BO65" s="16"/>
-      <c r="BR65" s="16"/>
-    </row>
-    <row r="66" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN65" s="16"/>
+      <c r="BQ65" s="16"/>
+    </row>
+    <row r="66" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D66" s="13"/>
       <c r="E66" s="12"/>
-      <c r="BO66" s="16"/>
-      <c r="BR66" s="16"/>
-    </row>
-    <row r="67" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN66" s="16"/>
+      <c r="BQ66" s="16"/>
+    </row>
+    <row r="67" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D67" s="13"/>
       <c r="E67" s="12"/>
-      <c r="BO67" s="16"/>
-      <c r="BR67" s="16"/>
-    </row>
-    <row r="68" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN67" s="16"/>
+      <c r="BQ67" s="16"/>
+    </row>
+    <row r="68" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D68" s="13"/>
       <c r="E68" s="12"/>
-      <c r="BO68" s="16"/>
-      <c r="BR68" s="16"/>
-    </row>
-    <row r="69" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN68" s="16"/>
+      <c r="BQ68" s="16"/>
+    </row>
+    <row r="69" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D69" s="13"/>
       <c r="E69" s="12"/>
-      <c r="BO69" s="16"/>
-      <c r="BR69" s="16"/>
-    </row>
-    <row r="70" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN69" s="16"/>
+      <c r="BQ69" s="16"/>
+    </row>
+    <row r="70" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D70" s="13"/>
       <c r="E70" s="12"/>
-      <c r="BO70" s="16"/>
-      <c r="BR70" s="16"/>
-    </row>
-    <row r="71" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN70" s="16"/>
+      <c r="BQ70" s="16"/>
+    </row>
+    <row r="71" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D71" s="13"/>
       <c r="E71" s="12"/>
-      <c r="BO71" s="16"/>
-      <c r="BR71" s="16"/>
-    </row>
-    <row r="72" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN71" s="16"/>
+      <c r="BQ71" s="16"/>
+    </row>
+    <row r="72" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D72" s="13"/>
       <c r="E72" s="12"/>
-      <c r="BO72" s="16"/>
-      <c r="BR72" s="16"/>
-    </row>
-    <row r="73" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN72" s="16"/>
+      <c r="BQ72" s="16"/>
+    </row>
+    <row r="73" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D73" s="13"/>
       <c r="E73" s="12"/>
-      <c r="BO73" s="16"/>
-      <c r="BR73" s="16"/>
-    </row>
-    <row r="74" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN73" s="16"/>
+      <c r="BQ73" s="16"/>
+    </row>
+    <row r="74" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D74" s="13"/>
       <c r="E74" s="12"/>
-      <c r="BO74" s="16"/>
-      <c r="BR74" s="16"/>
-    </row>
-    <row r="75" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN74" s="16"/>
+      <c r="BQ74" s="16"/>
+    </row>
+    <row r="75" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D75" s="13"/>
       <c r="E75" s="12"/>
-      <c r="BO75" s="16"/>
-      <c r="BR75" s="16"/>
-    </row>
-    <row r="76" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN75" s="16"/>
+      <c r="BQ75" s="16"/>
+    </row>
+    <row r="76" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D76" s="13"/>
       <c r="E76" s="12"/>
-      <c r="BO76" s="16"/>
-      <c r="BR76" s="16"/>
-    </row>
-    <row r="77" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN76" s="16"/>
+      <c r="BQ76" s="16"/>
+    </row>
+    <row r="77" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D77" s="13"/>
       <c r="E77" s="12"/>
-      <c r="BO77" s="16"/>
-      <c r="BR77" s="16"/>
-    </row>
-    <row r="78" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN77" s="16"/>
+      <c r="BQ77" s="16"/>
+    </row>
+    <row r="78" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D78" s="13"/>
       <c r="E78" s="12"/>
-      <c r="BO78" s="16"/>
-      <c r="BR78" s="16"/>
-    </row>
-    <row r="79" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN78" s="16"/>
+      <c r="BQ78" s="16"/>
+    </row>
+    <row r="79" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D79" s="13"/>
       <c r="E79" s="12"/>
-      <c r="BO79" s="16"/>
-      <c r="BR79" s="16"/>
-    </row>
-    <row r="80" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN79" s="16"/>
+      <c r="BQ79" s="16"/>
+    </row>
+    <row r="80" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D80" s="13"/>
       <c r="E80" s="12"/>
-      <c r="BO80" s="16"/>
-      <c r="BR80" s="16"/>
-    </row>
-    <row r="81" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN80" s="16"/>
+      <c r="BQ80" s="16"/>
+    </row>
+    <row r="81" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D81" s="13"/>
       <c r="E81" s="12"/>
-      <c r="BO81" s="16"/>
-      <c r="BR81" s="16"/>
-    </row>
-    <row r="82" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN81" s="16"/>
+      <c r="BQ81" s="16"/>
+    </row>
+    <row r="82" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D82" s="13"/>
       <c r="E82" s="12"/>
-      <c r="BO82" s="16"/>
-      <c r="BR82" s="16"/>
-    </row>
-    <row r="83" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN82" s="16"/>
+      <c r="BQ82" s="16"/>
+    </row>
+    <row r="83" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D83" s="13"/>
       <c r="E83" s="12"/>
-      <c r="BO83" s="16"/>
-      <c r="BR83" s="16"/>
-    </row>
-    <row r="84" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN83" s="16"/>
+      <c r="BQ83" s="16"/>
+    </row>
+    <row r="84" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D84" s="13"/>
       <c r="E84" s="12"/>
-      <c r="BO84" s="16"/>
-      <c r="BR84" s="16"/>
-    </row>
-    <row r="85" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN84" s="16"/>
+      <c r="BQ84" s="16"/>
+    </row>
+    <row r="85" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D85" s="13"/>
       <c r="E85" s="12"/>
-      <c r="BO85" s="16"/>
-      <c r="BR85" s="16"/>
-    </row>
-    <row r="86" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN85" s="16"/>
+      <c r="BQ85" s="16"/>
+    </row>
+    <row r="86" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D86" s="13"/>
       <c r="E86" s="12"/>
-      <c r="BO86" s="16"/>
-      <c r="BR86" s="16"/>
-    </row>
-    <row r="87" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN86" s="16"/>
+      <c r="BQ86" s="16"/>
+    </row>
+    <row r="87" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D87" s="13"/>
       <c r="E87" s="12"/>
-      <c r="BO87" s="16"/>
-      <c r="BR87" s="16"/>
-    </row>
-    <row r="88" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN87" s="16"/>
+      <c r="BQ87" s="16"/>
+    </row>
+    <row r="88" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D88" s="13"/>
       <c r="E88" s="12"/>
-      <c r="BO88" s="16"/>
-      <c r="BR88" s="16"/>
-    </row>
-    <row r="89" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN88" s="16"/>
+      <c r="BQ88" s="16"/>
+    </row>
+    <row r="89" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D89" s="13"/>
       <c r="E89" s="12"/>
-      <c r="BO89" s="16"/>
-      <c r="BR89" s="16"/>
-    </row>
-    <row r="90" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN89" s="16"/>
+      <c r="BQ89" s="16"/>
+    </row>
+    <row r="90" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D90" s="13"/>
       <c r="E90" s="12"/>
-      <c r="BO90" s="16"/>
-      <c r="BR90" s="16"/>
-    </row>
-    <row r="91" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN90" s="16"/>
+      <c r="BQ90" s="16"/>
+    </row>
+    <row r="91" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D91" s="13"/>
       <c r="E91" s="12"/>
-      <c r="BO91" s="16"/>
-      <c r="BR91" s="16"/>
-    </row>
-    <row r="92" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN91" s="16"/>
+      <c r="BQ91" s="16"/>
+    </row>
+    <row r="92" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D92" s="13"/>
       <c r="E92" s="12"/>
-      <c r="BO92" s="16"/>
-      <c r="BR92" s="16"/>
-    </row>
-    <row r="93" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN92" s="16"/>
+      <c r="BQ92" s="16"/>
+    </row>
+    <row r="93" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D93" s="13"/>
       <c r="E93" s="12"/>
-      <c r="BO93" s="16"/>
-      <c r="BR93" s="16"/>
-    </row>
-    <row r="94" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN93" s="16"/>
+      <c r="BQ93" s="16"/>
+    </row>
+    <row r="94" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D94" s="13"/>
       <c r="E94" s="12"/>
-      <c r="BO94" s="16"/>
-      <c r="BR94" s="16"/>
-    </row>
-    <row r="95" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN94" s="16"/>
+      <c r="BQ94" s="16"/>
+    </row>
+    <row r="95" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D95" s="13"/>
       <c r="E95" s="12"/>
-      <c r="BO95" s="16"/>
-      <c r="BR95" s="16"/>
-    </row>
-    <row r="96" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN95" s="16"/>
+      <c r="BQ95" s="16"/>
+    </row>
+    <row r="96" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D96" s="13"/>
       <c r="E96" s="12"/>
-      <c r="BO96" s="16"/>
-      <c r="BR96" s="16"/>
-    </row>
-    <row r="97" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN96" s="16"/>
+      <c r="BQ96" s="16"/>
+    </row>
+    <row r="97" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D97" s="13"/>
       <c r="E97" s="12"/>
-      <c r="BO97" s="16"/>
-      <c r="BR97" s="16"/>
-    </row>
-    <row r="98" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN97" s="16"/>
+      <c r="BQ97" s="16"/>
+    </row>
+    <row r="98" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D98" s="13"/>
       <c r="E98" s="12"/>
-      <c r="BO98" s="16"/>
-      <c r="BR98" s="16"/>
-    </row>
-    <row r="99" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN98" s="16"/>
+      <c r="BQ98" s="16"/>
+    </row>
+    <row r="99" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D99" s="13"/>
       <c r="E99" s="12"/>
-      <c r="BO99" s="16"/>
-      <c r="BR99" s="16"/>
-    </row>
-    <row r="100" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN99" s="16"/>
+      <c r="BQ99" s="16"/>
+    </row>
+    <row r="100" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D100" s="13"/>
       <c r="E100" s="12"/>
-      <c r="BO100" s="16"/>
-      <c r="BR100" s="16"/>
-    </row>
-    <row r="101" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN100" s="16"/>
+      <c r="BQ100" s="16"/>
+    </row>
+    <row r="101" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D101" s="13"/>
       <c r="E101" s="12"/>
-      <c r="BO101" s="16"/>
-      <c r="BR101" s="16"/>
-    </row>
-    <row r="102" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN101" s="16"/>
+      <c r="BQ101" s="16"/>
+    </row>
+    <row r="102" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D102" s="13"/>
       <c r="E102" s="12"/>
-      <c r="BO102" s="16"/>
-      <c r="BR102" s="16"/>
-    </row>
-    <row r="103" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN102" s="16"/>
+      <c r="BQ102" s="16"/>
+    </row>
+    <row r="103" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D103" s="13"/>
       <c r="E103" s="12"/>
-      <c r="BO103" s="16"/>
-      <c r="BR103" s="16"/>
-    </row>
-    <row r="104" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN103" s="16"/>
+      <c r="BQ103" s="16"/>
+    </row>
+    <row r="104" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D104" s="13"/>
       <c r="E104" s="12"/>
-      <c r="BO104" s="16"/>
-      <c r="BR104" s="16"/>
-    </row>
-    <row r="105" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN104" s="16"/>
+      <c r="BQ104" s="16"/>
+    </row>
+    <row r="105" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D105" s="13"/>
       <c r="E105" s="12"/>
-      <c r="BO105" s="16"/>
-      <c r="BR105" s="16"/>
-    </row>
-    <row r="106" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN105" s="16"/>
+      <c r="BQ105" s="16"/>
+    </row>
+    <row r="106" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D106" s="13"/>
       <c r="E106" s="12"/>
-      <c r="BO106" s="16"/>
-      <c r="BR106" s="16"/>
-    </row>
-    <row r="107" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN106" s="16"/>
+      <c r="BQ106" s="16"/>
+    </row>
+    <row r="107" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D107" s="13"/>
       <c r="E107" s="12"/>
-      <c r="BO107" s="16"/>
-      <c r="BR107" s="16"/>
-    </row>
-    <row r="108" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN107" s="16"/>
+      <c r="BQ107" s="16"/>
+    </row>
+    <row r="108" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D108" s="13"/>
       <c r="E108" s="12"/>
-      <c r="BO108" s="16"/>
-      <c r="BR108" s="16"/>
-    </row>
-    <row r="109" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN108" s="16"/>
+      <c r="BQ108" s="16"/>
+    </row>
+    <row r="109" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D109" s="13"/>
       <c r="E109" s="12"/>
-      <c r="BO109" s="16"/>
-      <c r="BR109" s="16"/>
-    </row>
-    <row r="110" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN109" s="16"/>
+      <c r="BQ109" s="16"/>
+    </row>
+    <row r="110" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D110" s="13"/>
       <c r="E110" s="12"/>
-      <c r="BO110" s="16"/>
-      <c r="BR110" s="16"/>
-    </row>
-    <row r="111" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN110" s="16"/>
+      <c r="BQ110" s="16"/>
+    </row>
+    <row r="111" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D111" s="13"/>
       <c r="E111" s="12"/>
-      <c r="BO111" s="16"/>
-      <c r="BR111" s="16"/>
-    </row>
-    <row r="112" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN111" s="16"/>
+      <c r="BQ111" s="16"/>
+    </row>
+    <row r="112" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D112" s="13"/>
       <c r="E112" s="12"/>
-      <c r="BO112" s="16"/>
-      <c r="BR112" s="16"/>
-    </row>
-    <row r="113" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN112" s="16"/>
+      <c r="BQ112" s="16"/>
+    </row>
+    <row r="113" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D113" s="13"/>
       <c r="E113" s="12"/>
-      <c r="BO113" s="16"/>
-      <c r="BR113" s="16"/>
-    </row>
-    <row r="114" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN113" s="16"/>
+      <c r="BQ113" s="16"/>
+    </row>
+    <row r="114" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D114" s="13"/>
       <c r="E114" s="12"/>
-      <c r="BO114" s="16"/>
-      <c r="BR114" s="16"/>
-    </row>
-    <row r="115" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN114" s="16"/>
+      <c r="BQ114" s="16"/>
+    </row>
+    <row r="115" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D115" s="13"/>
       <c r="E115" s="12"/>
-      <c r="BO115" s="16"/>
-      <c r="BR115" s="16"/>
-    </row>
-    <row r="116" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN115" s="16"/>
+      <c r="BQ115" s="16"/>
+    </row>
+    <row r="116" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D116" s="13"/>
       <c r="E116" s="12"/>
-      <c r="BO116" s="16"/>
-      <c r="BR116" s="16"/>
-    </row>
-    <row r="117" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN116" s="16"/>
+      <c r="BQ116" s="16"/>
+    </row>
+    <row r="117" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D117" s="13"/>
       <c r="E117" s="12"/>
-      <c r="BO117" s="16"/>
-      <c r="BR117" s="16"/>
-    </row>
-    <row r="118" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN117" s="16"/>
+      <c r="BQ117" s="16"/>
+    </row>
+    <row r="118" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D118" s="13"/>
       <c r="E118" s="12"/>
-      <c r="BO118" s="16"/>
-      <c r="BR118" s="16"/>
-    </row>
-    <row r="119" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN118" s="16"/>
+      <c r="BQ118" s="16"/>
+    </row>
+    <row r="119" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D119" s="13"/>
       <c r="E119" s="12"/>
-      <c r="BO119" s="16"/>
-      <c r="BR119" s="16"/>
-    </row>
-    <row r="120" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN119" s="16"/>
+      <c r="BQ119" s="16"/>
+    </row>
+    <row r="120" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D120" s="13"/>
       <c r="E120" s="12"/>
-      <c r="BO120" s="16"/>
-      <c r="BR120" s="16"/>
-    </row>
-    <row r="121" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN120" s="16"/>
+      <c r="BQ120" s="16"/>
+    </row>
+    <row r="121" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D121" s="13"/>
       <c r="E121" s="12"/>
-      <c r="BO121" s="16"/>
-      <c r="BR121" s="16"/>
-    </row>
-    <row r="122" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN121" s="16"/>
+      <c r="BQ121" s="16"/>
+    </row>
+    <row r="122" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D122" s="13"/>
       <c r="E122" s="12"/>
-      <c r="BO122" s="16"/>
-      <c r="BR122" s="16"/>
-    </row>
-    <row r="123" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN122" s="16"/>
+      <c r="BQ122" s="16"/>
+    </row>
+    <row r="123" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D123" s="13"/>
       <c r="E123" s="12"/>
-      <c r="BO123" s="16"/>
-      <c r="BR123" s="16"/>
-    </row>
-    <row r="124" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN123" s="16"/>
+      <c r="BQ123" s="16"/>
+    </row>
+    <row r="124" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D124" s="13"/>
       <c r="E124" s="12"/>
-      <c r="BO124" s="16"/>
-      <c r="BR124" s="16"/>
-    </row>
-    <row r="125" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN124" s="16"/>
+      <c r="BQ124" s="16"/>
+    </row>
+    <row r="125" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D125" s="13"/>
       <c r="E125" s="12"/>
-      <c r="BO125" s="16"/>
-      <c r="BR125" s="16"/>
-    </row>
-    <row r="126" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN125" s="16"/>
+      <c r="BQ125" s="16"/>
+    </row>
+    <row r="126" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D126" s="13"/>
       <c r="E126" s="12"/>
-      <c r="BO126" s="16"/>
-      <c r="BR126" s="16"/>
-    </row>
-    <row r="127" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN126" s="16"/>
+      <c r="BQ126" s="16"/>
+    </row>
+    <row r="127" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D127" s="13"/>
       <c r="E127" s="12"/>
-      <c r="BO127" s="16"/>
-      <c r="BR127" s="16"/>
-    </row>
-    <row r="128" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN127" s="16"/>
+      <c r="BQ127" s="16"/>
+    </row>
+    <row r="128" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D128" s="13"/>
       <c r="E128" s="12"/>
-      <c r="BO128" s="16"/>
-      <c r="BR128" s="16"/>
-    </row>
-    <row r="129" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN128" s="16"/>
+      <c r="BQ128" s="16"/>
+    </row>
+    <row r="129" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D129" s="13"/>
       <c r="E129" s="12"/>
-      <c r="BO129" s="16"/>
-      <c r="BR129" s="16"/>
-    </row>
-    <row r="130" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN129" s="16"/>
+      <c r="BQ129" s="16"/>
+    </row>
+    <row r="130" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D130" s="13"/>
       <c r="E130" s="12"/>
-      <c r="BO130" s="16"/>
-      <c r="BR130" s="16"/>
-    </row>
-    <row r="131" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN130" s="16"/>
+      <c r="BQ130" s="16"/>
+    </row>
+    <row r="131" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D131" s="13"/>
       <c r="E131" s="12"/>
-      <c r="BO131" s="16"/>
-      <c r="BR131" s="16"/>
-    </row>
-    <row r="132" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN131" s="16"/>
+      <c r="BQ131" s="16"/>
+    </row>
+    <row r="132" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D132" s="13"/>
       <c r="E132" s="12"/>
-      <c r="BO132" s="16"/>
-      <c r="BR132" s="16"/>
-    </row>
-    <row r="133" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN132" s="16"/>
+      <c r="BQ132" s="16"/>
+    </row>
+    <row r="133" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D133" s="13"/>
       <c r="E133" s="12"/>
-      <c r="BO133" s="16"/>
-      <c r="BR133" s="16"/>
-    </row>
-    <row r="134" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN133" s="16"/>
+      <c r="BQ133" s="16"/>
+    </row>
+    <row r="134" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D134" s="13"/>
       <c r="E134" s="12"/>
-      <c r="BO134" s="16"/>
-      <c r="BR134" s="16"/>
-    </row>
-    <row r="135" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN134" s="16"/>
+      <c r="BQ134" s="16"/>
+    </row>
+    <row r="135" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D135" s="13"/>
       <c r="E135" s="12"/>
-      <c r="BO135" s="16"/>
-      <c r="BR135" s="16"/>
-    </row>
-    <row r="136" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN135" s="16"/>
+      <c r="BQ135" s="16"/>
+    </row>
+    <row r="136" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D136" s="13"/>
       <c r="E136" s="12"/>
-      <c r="BO136" s="16"/>
-      <c r="BR136" s="16"/>
-    </row>
-    <row r="137" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN136" s="16"/>
+      <c r="BQ136" s="16"/>
+    </row>
+    <row r="137" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D137" s="13"/>
       <c r="E137" s="12"/>
-      <c r="BO137" s="16"/>
-      <c r="BR137" s="16"/>
-    </row>
-    <row r="138" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN137" s="16"/>
+      <c r="BQ137" s="16"/>
+    </row>
+    <row r="138" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D138" s="13"/>
       <c r="E138" s="12"/>
-      <c r="BO138" s="16"/>
-      <c r="BR138" s="16"/>
-    </row>
-    <row r="139" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN138" s="16"/>
+      <c r="BQ138" s="16"/>
+    </row>
+    <row r="139" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D139" s="13"/>
       <c r="E139" s="12"/>
-      <c r="BO139" s="16"/>
-      <c r="BR139" s="16"/>
-    </row>
-    <row r="140" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN139" s="16"/>
+      <c r="BQ139" s="16"/>
+    </row>
+    <row r="140" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D140" s="13"/>
       <c r="E140" s="12"/>
-      <c r="BO140" s="16"/>
-      <c r="BR140" s="16"/>
-    </row>
-    <row r="141" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN140" s="16"/>
+      <c r="BQ140" s="16"/>
+    </row>
+    <row r="141" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D141" s="13"/>
       <c r="E141" s="12"/>
-      <c r="BO141" s="16"/>
-      <c r="BR141" s="16"/>
-    </row>
-    <row r="142" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN141" s="16"/>
+      <c r="BQ141" s="16"/>
+    </row>
+    <row r="142" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D142" s="13"/>
       <c r="E142" s="12"/>
-      <c r="BO142" s="16"/>
-      <c r="BR142" s="16"/>
-    </row>
-    <row r="143" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN142" s="16"/>
+      <c r="BQ142" s="16"/>
+    </row>
+    <row r="143" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D143" s="13"/>
       <c r="E143" s="12"/>
-      <c r="BO143" s="16"/>
-      <c r="BR143" s="16"/>
-    </row>
-    <row r="144" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN143" s="16"/>
+      <c r="BQ143" s="16"/>
+    </row>
+    <row r="144" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D144" s="13"/>
       <c r="E144" s="12"/>
-      <c r="BO144" s="16"/>
-      <c r="BR144" s="16"/>
-    </row>
-    <row r="145" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN144" s="16"/>
+      <c r="BQ144" s="16"/>
+    </row>
+    <row r="145" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D145" s="13"/>
       <c r="E145" s="12"/>
-      <c r="BO145" s="16"/>
-      <c r="BR145" s="16"/>
-    </row>
-    <row r="146" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN145" s="16"/>
+      <c r="BQ145" s="16"/>
+    </row>
+    <row r="146" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D146" s="13"/>
       <c r="E146" s="12"/>
-      <c r="BO146" s="16"/>
-      <c r="BR146" s="16"/>
-    </row>
-    <row r="147" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN146" s="16"/>
+      <c r="BQ146" s="16"/>
+    </row>
+    <row r="147" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D147" s="13"/>
       <c r="E147" s="12"/>
-      <c r="BO147" s="16"/>
-      <c r="BR147" s="16"/>
-    </row>
-    <row r="148" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN147" s="16"/>
+      <c r="BQ147" s="16"/>
+    </row>
+    <row r="148" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D148" s="13"/>
       <c r="E148" s="12"/>
-      <c r="BO148" s="16"/>
-      <c r="BR148" s="16"/>
-    </row>
-    <row r="149" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN148" s="16"/>
+      <c r="BQ148" s="16"/>
+    </row>
+    <row r="149" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D149" s="13"/>
       <c r="E149" s="12"/>
-      <c r="BO149" s="16"/>
-      <c r="BR149" s="16"/>
-    </row>
-    <row r="150" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN149" s="16"/>
+      <c r="BQ149" s="16"/>
+    </row>
+    <row r="150" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D150" s="13"/>
       <c r="E150" s="12"/>
-      <c r="BO150" s="16"/>
-      <c r="BR150" s="16"/>
-    </row>
-    <row r="151" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN150" s="16"/>
+      <c r="BQ150" s="16"/>
+    </row>
+    <row r="151" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D151" s="13"/>
       <c r="E151" s="12"/>
-      <c r="BO151" s="16"/>
-      <c r="BR151" s="16"/>
-    </row>
-    <row r="152" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN151" s="16"/>
+      <c r="BQ151" s="16"/>
+    </row>
+    <row r="152" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D152" s="13"/>
       <c r="E152" s="12"/>
-      <c r="BO152" s="16"/>
-      <c r="BR152" s="16"/>
-    </row>
-    <row r="153" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN152" s="16"/>
+      <c r="BQ152" s="16"/>
+    </row>
+    <row r="153" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D153" s="13"/>
       <c r="E153" s="12"/>
-      <c r="BO153" s="16"/>
-      <c r="BR153" s="16"/>
-    </row>
-    <row r="154" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN153" s="16"/>
+      <c r="BQ153" s="16"/>
+    </row>
+    <row r="154" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D154" s="13"/>
       <c r="E154" s="12"/>
-      <c r="BO154" s="16"/>
-      <c r="BR154" s="16"/>
-    </row>
-    <row r="155" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN154" s="16"/>
+      <c r="BQ154" s="16"/>
+    </row>
+    <row r="155" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D155" s="13"/>
       <c r="E155" s="12"/>
-      <c r="BO155" s="16"/>
-      <c r="BR155" s="16"/>
-    </row>
-    <row r="156" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN155" s="16"/>
+      <c r="BQ155" s="16"/>
+    </row>
+    <row r="156" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D156" s="13"/>
       <c r="E156" s="12"/>
-      <c r="BO156" s="16"/>
-      <c r="BR156" s="16"/>
-    </row>
-    <row r="157" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN156" s="16"/>
+      <c r="BQ156" s="16"/>
+    </row>
+    <row r="157" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D157" s="13"/>
       <c r="E157" s="12"/>
-      <c r="BO157" s="16"/>
-      <c r="BR157" s="16"/>
-    </row>
-    <row r="158" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN157" s="16"/>
+      <c r="BQ157" s="16"/>
+    </row>
+    <row r="158" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D158" s="13"/>
       <c r="E158" s="12"/>
-      <c r="BO158" s="16"/>
-      <c r="BR158" s="16"/>
-    </row>
-    <row r="159" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN158" s="16"/>
+      <c r="BQ158" s="16"/>
+    </row>
+    <row r="159" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D159" s="13"/>
       <c r="E159" s="12"/>
-      <c r="BO159" s="16"/>
-      <c r="BR159" s="16"/>
-    </row>
-    <row r="160" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN159" s="16"/>
+      <c r="BQ159" s="16"/>
+    </row>
+    <row r="160" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D160" s="13"/>
       <c r="E160" s="12"/>
-      <c r="BO160" s="16"/>
-      <c r="BR160" s="16"/>
-    </row>
-    <row r="161" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN160" s="16"/>
+      <c r="BQ160" s="16"/>
+    </row>
+    <row r="161" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D161" s="13"/>
       <c r="E161" s="12"/>
-      <c r="BO161" s="16"/>
-      <c r="BR161" s="16"/>
-    </row>
-    <row r="162" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN161" s="16"/>
+      <c r="BQ161" s="16"/>
+    </row>
+    <row r="162" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D162" s="13"/>
       <c r="E162" s="12"/>
-      <c r="BO162" s="16"/>
-      <c r="BR162" s="16"/>
-    </row>
-    <row r="163" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN162" s="16"/>
+      <c r="BQ162" s="16"/>
+    </row>
+    <row r="163" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D163" s="13"/>
       <c r="E163" s="12"/>
-      <c r="BO163" s="16"/>
-      <c r="BR163" s="16"/>
-    </row>
-    <row r="164" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN163" s="16"/>
+      <c r="BQ163" s="16"/>
+    </row>
+    <row r="164" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D164" s="13"/>
       <c r="E164" s="12"/>
-      <c r="BO164" s="16"/>
-      <c r="BR164" s="16"/>
-    </row>
-    <row r="165" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN164" s="16"/>
+      <c r="BQ164" s="16"/>
+    </row>
+    <row r="165" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D165" s="13"/>
       <c r="E165" s="12"/>
-      <c r="BO165" s="16"/>
-      <c r="BR165" s="16"/>
-    </row>
-    <row r="166" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN165" s="16"/>
+      <c r="BQ165" s="16"/>
+    </row>
+    <row r="166" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D166" s="13"/>
       <c r="E166" s="12"/>
-      <c r="BO166" s="16"/>
-      <c r="BR166" s="16"/>
-    </row>
-    <row r="167" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN166" s="16"/>
+      <c r="BQ166" s="16"/>
+    </row>
+    <row r="167" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D167" s="13"/>
       <c r="E167" s="12"/>
-      <c r="BO167" s="16"/>
-      <c r="BR167" s="16"/>
-    </row>
-    <row r="168" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN167" s="16"/>
+      <c r="BQ167" s="16"/>
+    </row>
+    <row r="168" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D168" s="13"/>
       <c r="E168" s="12"/>
-      <c r="BO168" s="16"/>
-      <c r="BR168" s="16"/>
-    </row>
-    <row r="169" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN168" s="16"/>
+      <c r="BQ168" s="16"/>
+    </row>
+    <row r="169" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D169" s="13"/>
       <c r="E169" s="12"/>
-      <c r="BO169" s="16"/>
-      <c r="BR169" s="16"/>
-    </row>
-    <row r="170" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN169" s="16"/>
+      <c r="BQ169" s="16"/>
+    </row>
+    <row r="170" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D170" s="13"/>
       <c r="E170" s="12"/>
-      <c r="BO170" s="16"/>
-      <c r="BR170" s="16"/>
-    </row>
-    <row r="171" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN170" s="16"/>
+      <c r="BQ170" s="16"/>
+    </row>
+    <row r="171" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D171" s="13"/>
       <c r="E171" s="12"/>
-      <c r="BO171" s="16"/>
-      <c r="BR171" s="16"/>
-    </row>
-    <row r="172" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN171" s="16"/>
+      <c r="BQ171" s="16"/>
+    </row>
+    <row r="172" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D172" s="13"/>
       <c r="E172" s="12"/>
-      <c r="BO172" s="16"/>
-      <c r="BR172" s="16"/>
-    </row>
-    <row r="173" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN172" s="16"/>
+      <c r="BQ172" s="16"/>
+    </row>
+    <row r="173" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D173" s="13"/>
       <c r="E173" s="12"/>
-      <c r="BO173" s="16"/>
-      <c r="BR173" s="16"/>
-    </row>
-    <row r="174" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN173" s="16"/>
+      <c r="BQ173" s="16"/>
+    </row>
+    <row r="174" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D174" s="13"/>
       <c r="E174" s="12"/>
-      <c r="BO174" s="16"/>
-      <c r="BR174" s="16"/>
-    </row>
-    <row r="175" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN174" s="16"/>
+      <c r="BQ174" s="16"/>
+    </row>
+    <row r="175" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D175" s="13"/>
       <c r="E175" s="12"/>
-      <c r="BO175" s="16"/>
-      <c r="BR175" s="16"/>
-    </row>
-    <row r="176" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN175" s="16"/>
+      <c r="BQ175" s="16"/>
+    </row>
+    <row r="176" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D176" s="13"/>
       <c r="E176" s="12"/>
-      <c r="BO176" s="16"/>
-      <c r="BR176" s="16"/>
-    </row>
-    <row r="177" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN176" s="16"/>
+      <c r="BQ176" s="16"/>
+    </row>
+    <row r="177" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D177" s="13"/>
       <c r="E177" s="12"/>
-      <c r="BO177" s="16"/>
-      <c r="BR177" s="16"/>
-    </row>
-    <row r="178" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN177" s="16"/>
+      <c r="BQ177" s="16"/>
+    </row>
+    <row r="178" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D178" s="13"/>
       <c r="E178" s="12"/>
-      <c r="BO178" s="16"/>
-      <c r="BR178" s="16"/>
-    </row>
-    <row r="179" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN178" s="16"/>
+      <c r="BQ178" s="16"/>
+    </row>
+    <row r="179" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D179" s="13"/>
       <c r="E179" s="12"/>
-      <c r="BO179" s="16"/>
-      <c r="BR179" s="16"/>
-    </row>
-    <row r="180" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN179" s="16"/>
+      <c r="BQ179" s="16"/>
+    </row>
+    <row r="180" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D180" s="13"/>
       <c r="E180" s="12"/>
-      <c r="BO180" s="16"/>
-      <c r="BR180" s="16"/>
-    </row>
-    <row r="181" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN180" s="16"/>
+      <c r="BQ180" s="16"/>
+    </row>
+    <row r="181" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D181" s="13"/>
       <c r="E181" s="12"/>
-      <c r="BO181" s="16"/>
-      <c r="BR181" s="16"/>
-    </row>
-    <row r="182" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN181" s="16"/>
+      <c r="BQ181" s="16"/>
+    </row>
+    <row r="182" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D182" s="13"/>
       <c r="E182" s="12"/>
-      <c r="BO182" s="16"/>
-      <c r="BR182" s="16"/>
-    </row>
-    <row r="183" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN182" s="16"/>
+      <c r="BQ182" s="16"/>
+    </row>
+    <row r="183" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D183" s="13"/>
       <c r="E183" s="12"/>
-      <c r="BO183" s="16"/>
-      <c r="BR183" s="16"/>
-    </row>
-    <row r="184" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN183" s="16"/>
+      <c r="BQ183" s="16"/>
+    </row>
+    <row r="184" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D184" s="13"/>
       <c r="E184" s="12"/>
-      <c r="BO184" s="16"/>
-      <c r="BR184" s="16"/>
-    </row>
-    <row r="185" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN184" s="16"/>
+      <c r="BQ184" s="16"/>
+    </row>
+    <row r="185" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D185" s="13"/>
       <c r="E185" s="12"/>
-      <c r="BO185" s="16"/>
-      <c r="BR185" s="16"/>
-    </row>
-    <row r="186" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN185" s="16"/>
+      <c r="BQ185" s="16"/>
+    </row>
+    <row r="186" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D186" s="13"/>
       <c r="E186" s="12"/>
-      <c r="BO186" s="16"/>
-      <c r="BR186" s="16"/>
-    </row>
-    <row r="187" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN186" s="16"/>
+      <c r="BQ186" s="16"/>
+    </row>
+    <row r="187" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D187" s="13"/>
       <c r="E187" s="12"/>
-      <c r="BO187" s="16"/>
-      <c r="BR187" s="16"/>
-    </row>
-    <row r="188" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN187" s="16"/>
+      <c r="BQ187" s="16"/>
+    </row>
+    <row r="188" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D188" s="13"/>
       <c r="E188" s="12"/>
-      <c r="BO188" s="16"/>
-      <c r="BR188" s="16"/>
-    </row>
-    <row r="189" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN188" s="16"/>
+      <c r="BQ188" s="16"/>
+    </row>
+    <row r="189" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D189" s="13"/>
       <c r="E189" s="12"/>
-      <c r="BO189" s="16"/>
-      <c r="BR189" s="16"/>
-    </row>
-    <row r="190" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN189" s="16"/>
+      <c r="BQ189" s="16"/>
+    </row>
+    <row r="190" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D190" s="13"/>
       <c r="E190" s="12"/>
-      <c r="BO190" s="16"/>
-      <c r="BR190" s="16"/>
-    </row>
-    <row r="191" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN190" s="16"/>
+      <c r="BQ190" s="16"/>
+    </row>
+    <row r="191" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D191" s="13"/>
       <c r="E191" s="12"/>
-      <c r="BO191" s="16"/>
-      <c r="BR191" s="16"/>
-    </row>
-    <row r="192" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN191" s="16"/>
+      <c r="BQ191" s="16"/>
+    </row>
+    <row r="192" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D192" s="13"/>
       <c r="E192" s="12"/>
-      <c r="BO192" s="16"/>
-      <c r="BR192" s="16"/>
-    </row>
-    <row r="193" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN192" s="16"/>
+      <c r="BQ192" s="16"/>
+    </row>
+    <row r="193" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D193" s="13"/>
       <c r="E193" s="12"/>
-      <c r="BO193" s="16"/>
-      <c r="BR193" s="16"/>
-    </row>
-    <row r="194" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN193" s="16"/>
+      <c r="BQ193" s="16"/>
+    </row>
+    <row r="194" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D194" s="13"/>
       <c r="E194" s="12"/>
-      <c r="BO194" s="16"/>
-      <c r="BR194" s="16"/>
-    </row>
-    <row r="195" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN194" s="16"/>
+      <c r="BQ194" s="16"/>
+    </row>
+    <row r="195" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D195" s="13"/>
       <c r="E195" s="12"/>
-      <c r="BO195" s="16"/>
-      <c r="BR195" s="16"/>
-    </row>
-    <row r="196" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN195" s="16"/>
+      <c r="BQ195" s="16"/>
+    </row>
+    <row r="196" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D196" s="13"/>
       <c r="E196" s="12"/>
-      <c r="BO196" s="16"/>
-      <c r="BR196" s="16"/>
-    </row>
-    <row r="197" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN196" s="16"/>
+      <c r="BQ196" s="16"/>
+    </row>
+    <row r="197" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D197" s="13"/>
       <c r="E197" s="12"/>
-      <c r="BO197" s="16"/>
-      <c r="BR197" s="16"/>
-    </row>
-    <row r="198" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN197" s="16"/>
+      <c r="BQ197" s="16"/>
+    </row>
+    <row r="198" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D198" s="13"/>
       <c r="E198" s="12"/>
-      <c r="BO198" s="16"/>
-      <c r="BR198" s="16"/>
-    </row>
-    <row r="199" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN198" s="16"/>
+      <c r="BQ198" s="16"/>
+    </row>
+    <row r="199" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D199" s="13"/>
       <c r="E199" s="12"/>
-      <c r="BO199" s="16"/>
-      <c r="BR199" s="16"/>
-    </row>
-    <row r="200" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN199" s="16"/>
+      <c r="BQ199" s="16"/>
+    </row>
+    <row r="200" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D200" s="13"/>
       <c r="E200" s="12"/>
-      <c r="BO200" s="16"/>
-      <c r="BR200" s="16"/>
-    </row>
-    <row r="201" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN200" s="16"/>
+      <c r="BQ200" s="16"/>
+    </row>
+    <row r="201" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D201" s="13"/>
       <c r="E201" s="12"/>
-      <c r="BO201" s="16"/>
-      <c r="BR201" s="16"/>
-    </row>
-    <row r="202" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN201" s="16"/>
+      <c r="BQ201" s="16"/>
+    </row>
+    <row r="202" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D202" s="13"/>
       <c r="E202" s="12"/>
-      <c r="BO202" s="16"/>
-      <c r="BR202" s="16"/>
-    </row>
-    <row r="203" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN202" s="16"/>
+      <c r="BQ202" s="16"/>
+    </row>
+    <row r="203" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D203" s="13"/>
       <c r="E203" s="12"/>
-      <c r="BO203" s="16"/>
-      <c r="BR203" s="16"/>
-    </row>
-    <row r="204" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN203" s="16"/>
+      <c r="BQ203" s="16"/>
+    </row>
+    <row r="204" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D204" s="13"/>
       <c r="E204" s="12"/>
-      <c r="BO204" s="16"/>
-      <c r="BR204" s="16"/>
-    </row>
-    <row r="205" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN204" s="16"/>
+      <c r="BQ204" s="16"/>
+    </row>
+    <row r="205" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D205" s="13"/>
       <c r="E205" s="12"/>
-      <c r="BO205" s="16"/>
-      <c r="BR205" s="16"/>
-    </row>
-    <row r="206" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN205" s="16"/>
+      <c r="BQ205" s="16"/>
+    </row>
+    <row r="206" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D206" s="13"/>
       <c r="E206" s="12"/>
-      <c r="BO206" s="16"/>
-      <c r="BR206" s="16"/>
-    </row>
-    <row r="207" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN206" s="16"/>
+      <c r="BQ206" s="16"/>
+    </row>
+    <row r="207" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D207" s="13"/>
       <c r="E207" s="12"/>
-      <c r="BO207" s="16"/>
-      <c r="BR207" s="16"/>
-    </row>
-    <row r="208" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN207" s="16"/>
+      <c r="BQ207" s="16"/>
+    </row>
+    <row r="208" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D208" s="13"/>
       <c r="E208" s="12"/>
-      <c r="BO208" s="16"/>
-      <c r="BR208" s="16"/>
-    </row>
-    <row r="209" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN208" s="16"/>
+      <c r="BQ208" s="16"/>
+    </row>
+    <row r="209" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D209" s="13"/>
       <c r="E209" s="12"/>
-      <c r="BO209" s="16"/>
-      <c r="BR209" s="16"/>
-    </row>
-    <row r="210" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN209" s="16"/>
+      <c r="BQ209" s="16"/>
+    </row>
+    <row r="210" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D210" s="13"/>
       <c r="E210" s="12"/>
-      <c r="BO210" s="16"/>
-      <c r="BR210" s="16"/>
-    </row>
-    <row r="211" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN210" s="16"/>
+      <c r="BQ210" s="16"/>
+    </row>
+    <row r="211" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D211" s="13"/>
       <c r="E211" s="12"/>
-      <c r="BO211" s="16"/>
-      <c r="BR211" s="16"/>
-    </row>
-    <row r="212" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN211" s="16"/>
+      <c r="BQ211" s="16"/>
+    </row>
+    <row r="212" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D212" s="13"/>
       <c r="E212" s="12"/>
-      <c r="BO212" s="16"/>
-      <c r="BR212" s="16"/>
-    </row>
-    <row r="213" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN212" s="16"/>
+      <c r="BQ212" s="16"/>
+    </row>
+    <row r="213" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D213" s="13"/>
       <c r="E213" s="12"/>
-      <c r="BO213" s="16"/>
-      <c r="BR213" s="16"/>
-    </row>
-    <row r="214" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN213" s="16"/>
+      <c r="BQ213" s="16"/>
+    </row>
+    <row r="214" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D214" s="13"/>
       <c r="E214" s="12"/>
-      <c r="BO214" s="16"/>
-      <c r="BR214" s="16"/>
-    </row>
-    <row r="215" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN214" s="16"/>
+      <c r="BQ214" s="16"/>
+    </row>
+    <row r="215" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D215" s="13"/>
       <c r="E215" s="12"/>
-      <c r="BO215" s="16"/>
-      <c r="BR215" s="16"/>
-    </row>
-    <row r="216" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN215" s="16"/>
+      <c r="BQ215" s="16"/>
+    </row>
+    <row r="216" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D216" s="13"/>
       <c r="E216" s="12"/>
-      <c r="BO216" s="16"/>
-      <c r="BR216" s="16"/>
-    </row>
-    <row r="217" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN216" s="16"/>
+      <c r="BQ216" s="16"/>
+    </row>
+    <row r="217" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D217" s="13"/>
       <c r="E217" s="12"/>
-      <c r="BO217" s="16"/>
-      <c r="BR217" s="16"/>
-    </row>
-    <row r="218" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN217" s="16"/>
+      <c r="BQ217" s="16"/>
+    </row>
+    <row r="218" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D218" s="13"/>
       <c r="E218" s="12"/>
-      <c r="BO218" s="16"/>
-      <c r="BR218" s="16"/>
-    </row>
-    <row r="219" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN218" s="16"/>
+      <c r="BQ218" s="16"/>
+    </row>
+    <row r="219" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D219" s="13"/>
       <c r="E219" s="12"/>
-      <c r="BO219" s="16"/>
-      <c r="BR219" s="16"/>
-    </row>
-    <row r="220" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN219" s="16"/>
+      <c r="BQ219" s="16"/>
+    </row>
+    <row r="220" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D220" s="13"/>
       <c r="E220" s="12"/>
-      <c r="BO220" s="16"/>
-      <c r="BR220" s="16"/>
-    </row>
-    <row r="221" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN220" s="16"/>
+      <c r="BQ220" s="16"/>
+    </row>
+    <row r="221" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D221" s="13"/>
       <c r="E221" s="12"/>
-      <c r="BO221" s="16"/>
-      <c r="BR221" s="16"/>
-    </row>
-    <row r="222" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN221" s="16"/>
+      <c r="BQ221" s="16"/>
+    </row>
+    <row r="222" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D222" s="13"/>
       <c r="E222" s="12"/>
-      <c r="BO222" s="16"/>
-      <c r="BR222" s="16"/>
-    </row>
-    <row r="223" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN222" s="16"/>
+      <c r="BQ222" s="16"/>
+    </row>
+    <row r="223" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D223" s="13"/>
       <c r="E223" s="12"/>
-      <c r="BO223" s="16"/>
-      <c r="BR223" s="16"/>
-    </row>
-    <row r="224" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN223" s="16"/>
+      <c r="BQ223" s="16"/>
+    </row>
+    <row r="224" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D224" s="13"/>
       <c r="E224" s="12"/>
-      <c r="BO224" s="16"/>
-      <c r="BR224" s="16"/>
-    </row>
-    <row r="225" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN224" s="16"/>
+      <c r="BQ224" s="16"/>
+    </row>
+    <row r="225" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D225" s="13"/>
       <c r="E225" s="12"/>
-      <c r="BO225" s="16"/>
-      <c r="BR225" s="16"/>
-    </row>
-    <row r="226" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN225" s="16"/>
+      <c r="BQ225" s="16"/>
+    </row>
+    <row r="226" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D226" s="13"/>
       <c r="E226" s="12"/>
-      <c r="BO226" s="16"/>
-      <c r="BR226" s="16"/>
-    </row>
-    <row r="227" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN226" s="16"/>
+      <c r="BQ226" s="16"/>
+    </row>
+    <row r="227" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D227" s="13"/>
       <c r="E227" s="12"/>
-      <c r="BO227" s="16"/>
-      <c r="BR227" s="16"/>
-    </row>
-    <row r="228" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN227" s="16"/>
+      <c r="BQ227" s="16"/>
+    </row>
+    <row r="228" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D228" s="13"/>
       <c r="E228" s="12"/>
-      <c r="BO228" s="16"/>
-      <c r="BR228" s="16"/>
-    </row>
-    <row r="229" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN228" s="16"/>
+      <c r="BQ228" s="16"/>
+    </row>
+    <row r="229" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D229" s="13"/>
       <c r="E229" s="12"/>
-      <c r="BO229" s="16"/>
-      <c r="BR229" s="16"/>
-    </row>
-    <row r="230" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN229" s="16"/>
+      <c r="BQ229" s="16"/>
+    </row>
+    <row r="230" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D230" s="13"/>
       <c r="E230" s="12"/>
-      <c r="BO230" s="16"/>
-      <c r="BR230" s="16"/>
-    </row>
-    <row r="231" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN230" s="16"/>
+      <c r="BQ230" s="16"/>
+    </row>
+    <row r="231" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D231" s="13"/>
       <c r="E231" s="12"/>
-      <c r="BO231" s="16"/>
-      <c r="BR231" s="16"/>
-    </row>
-    <row r="232" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN231" s="16"/>
+      <c r="BQ231" s="16"/>
+    </row>
+    <row r="232" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D232" s="13"/>
       <c r="E232" s="12"/>
-      <c r="BO232" s="16"/>
-      <c r="BR232" s="16"/>
-    </row>
-    <row r="233" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN232" s="16"/>
+      <c r="BQ232" s="16"/>
+    </row>
+    <row r="233" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D233" s="13"/>
       <c r="E233" s="12"/>
-      <c r="BO233" s="16"/>
-      <c r="BR233" s="16"/>
-    </row>
-    <row r="234" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN233" s="16"/>
+      <c r="BQ233" s="16"/>
+    </row>
+    <row r="234" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D234" s="13"/>
       <c r="E234" s="12"/>
-      <c r="BO234" s="16"/>
-      <c r="BR234" s="16"/>
-    </row>
-    <row r="235" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN234" s="16"/>
+      <c r="BQ234" s="16"/>
+    </row>
+    <row r="235" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D235" s="13"/>
       <c r="E235" s="12"/>
-      <c r="BO235" s="16"/>
-      <c r="BR235" s="16"/>
-    </row>
-    <row r="236" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN235" s="16"/>
+      <c r="BQ235" s="16"/>
+    </row>
+    <row r="236" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D236" s="13"/>
       <c r="E236" s="12"/>
-      <c r="BO236" s="16"/>
-      <c r="BR236" s="16"/>
-    </row>
-    <row r="237" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN236" s="16"/>
+      <c r="BQ236" s="16"/>
+    </row>
+    <row r="237" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D237" s="13"/>
       <c r="E237" s="12"/>
-      <c r="BO237" s="16"/>
-      <c r="BR237" s="16"/>
-    </row>
-    <row r="238" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN237" s="16"/>
+      <c r="BQ237" s="16"/>
+    </row>
+    <row r="238" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D238" s="13"/>
       <c r="E238" s="12"/>
-      <c r="BO238" s="16"/>
-      <c r="BR238" s="16"/>
-    </row>
-    <row r="239" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN238" s="16"/>
+      <c r="BQ238" s="16"/>
+    </row>
+    <row r="239" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D239" s="13"/>
       <c r="E239" s="12"/>
-      <c r="BO239" s="16"/>
-      <c r="BR239" s="16"/>
-    </row>
-    <row r="240" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN239" s="16"/>
+      <c r="BQ239" s="16"/>
+    </row>
+    <row r="240" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D240" s="13"/>
       <c r="E240" s="12"/>
-      <c r="BO240" s="16"/>
-      <c r="BR240" s="16"/>
-    </row>
-    <row r="241" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN240" s="16"/>
+      <c r="BQ240" s="16"/>
+    </row>
+    <row r="241" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D241" s="13"/>
       <c r="E241" s="12"/>
-      <c r="BO241" s="16"/>
-      <c r="BR241" s="16"/>
-    </row>
-    <row r="242" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN241" s="16"/>
+      <c r="BQ241" s="16"/>
+    </row>
+    <row r="242" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D242" s="13"/>
       <c r="E242" s="12"/>
-      <c r="BO242" s="16"/>
-      <c r="BR242" s="16"/>
-    </row>
-    <row r="243" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN242" s="16"/>
+      <c r="BQ242" s="16"/>
+    </row>
+    <row r="243" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D243" s="13"/>
       <c r="E243" s="12"/>
-      <c r="BR243" s="16"/>
-    </row>
-    <row r="244" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ243" s="16"/>
+    </row>
+    <row r="244" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D244" s="13"/>
       <c r="E244" s="12"/>
-      <c r="BO244" s="16"/>
-      <c r="BR244" s="16"/>
-    </row>
-    <row r="245" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN244" s="16"/>
+      <c r="BQ244" s="16"/>
+    </row>
+    <row r="245" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D245" s="13"/>
       <c r="E245" s="12"/>
-      <c r="BO245" s="16"/>
-      <c r="BR245" s="16"/>
-    </row>
-    <row r="246" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN245" s="16"/>
+      <c r="BQ245" s="16"/>
+    </row>
+    <row r="246" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D246" s="13"/>
       <c r="E246" s="12"/>
-      <c r="BO246" s="16"/>
-      <c r="BR246" s="16"/>
-    </row>
-    <row r="247" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN246" s="16"/>
+      <c r="BQ246" s="16"/>
+    </row>
+    <row r="247" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D247" s="13"/>
       <c r="E247" s="12"/>
-      <c r="BO247" s="16"/>
-      <c r="BR247" s="16"/>
-    </row>
-    <row r="248" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN247" s="16"/>
+      <c r="BQ247" s="16"/>
+    </row>
+    <row r="248" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D248" s="13"/>
       <c r="E248" s="12"/>
-      <c r="BO248" s="16"/>
-      <c r="BR248" s="16"/>
-    </row>
-    <row r="249" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN248" s="16"/>
+      <c r="BQ248" s="16"/>
+    </row>
+    <row r="249" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D249" s="13"/>
       <c r="E249" s="12"/>
-      <c r="BO249" s="16"/>
-      <c r="BR249" s="16"/>
-    </row>
-    <row r="250" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN249" s="16"/>
+      <c r="BQ249" s="16"/>
+    </row>
+    <row r="250" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D250" s="13"/>
       <c r="E250" s="12"/>
-      <c r="BO250" s="16"/>
-      <c r="BR250" s="16"/>
-    </row>
-    <row r="251" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN250" s="16"/>
+      <c r="BQ250" s="16"/>
+    </row>
+    <row r="251" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D251" s="13"/>
       <c r="E251" s="12"/>
-      <c r="BO251" s="16"/>
-      <c r="BR251" s="16"/>
-    </row>
-    <row r="252" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN251" s="16"/>
+      <c r="BQ251" s="16"/>
+    </row>
+    <row r="252" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D252" s="13"/>
       <c r="E252" s="12"/>
-      <c r="BO252" s="16"/>
-      <c r="BR252" s="16"/>
-    </row>
-    <row r="253" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN252" s="16"/>
+      <c r="BQ252" s="16"/>
+    </row>
+    <row r="253" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D253" s="13"/>
       <c r="E253" s="12"/>
-      <c r="BO253" s="16"/>
-      <c r="BR253" s="16"/>
-    </row>
-    <row r="254" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN253" s="16"/>
+      <c r="BQ253" s="16"/>
+    </row>
+    <row r="254" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D254" s="13"/>
       <c r="E254" s="12"/>
-      <c r="BO254" s="16"/>
-      <c r="BR254" s="16"/>
-    </row>
-    <row r="255" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN254" s="16"/>
+      <c r="BQ254" s="16"/>
+    </row>
+    <row r="255" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D255" s="13"/>
       <c r="E255" s="12"/>
-      <c r="BO255" s="16"/>
-      <c r="BR255" s="16"/>
-    </row>
-    <row r="256" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN255" s="16"/>
+      <c r="BQ255" s="16"/>
+    </row>
+    <row r="256" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D256" s="13"/>
       <c r="E256" s="12"/>
-      <c r="BO256" s="16"/>
-      <c r="BR256" s="16"/>
-    </row>
-    <row r="257" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN256" s="16"/>
+      <c r="BQ256" s="16"/>
+    </row>
+    <row r="257" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D257" s="13"/>
       <c r="E257" s="12"/>
-      <c r="BO257" s="16"/>
-      <c r="BR257" s="16"/>
-    </row>
-    <row r="258" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN257" s="16"/>
+      <c r="BQ257" s="16"/>
+    </row>
+    <row r="258" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D258" s="13"/>
       <c r="E258" s="12"/>
-      <c r="BO258" s="16"/>
-      <c r="BR258" s="16"/>
-    </row>
-    <row r="259" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN258" s="16"/>
+      <c r="BQ258" s="16"/>
+    </row>
+    <row r="259" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D259" s="13"/>
       <c r="E259" s="12"/>
-      <c r="BO259" s="16"/>
-      <c r="BR259" s="16"/>
-    </row>
-    <row r="260" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN259" s="16"/>
+      <c r="BQ259" s="16"/>
+    </row>
+    <row r="260" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D260" s="13"/>
       <c r="E260" s="12"/>
-      <c r="BO260" s="16"/>
-      <c r="BR260" s="16"/>
-    </row>
-    <row r="261" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN260" s="16"/>
+      <c r="BQ260" s="16"/>
+    </row>
+    <row r="261" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D261" s="13"/>
       <c r="E261" s="12"/>
-      <c r="BO261" s="16"/>
-      <c r="BR261" s="16"/>
-    </row>
-    <row r="262" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN261" s="16"/>
+      <c r="BQ261" s="16"/>
+    </row>
+    <row r="262" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D262" s="13"/>
       <c r="E262" s="12"/>
-      <c r="BO262" s="16"/>
-      <c r="BR262" s="16"/>
-    </row>
-    <row r="263" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN262" s="16"/>
+      <c r="BQ262" s="16"/>
+    </row>
+    <row r="263" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D263" s="13"/>
       <c r="E263" s="12"/>
-      <c r="BO263" s="16"/>
-      <c r="BR263" s="16"/>
-    </row>
-    <row r="264" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN263" s="16"/>
+      <c r="BQ263" s="16"/>
+    </row>
+    <row r="264" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D264" s="13"/>
       <c r="E264" s="12"/>
-      <c r="BO264" s="16"/>
-      <c r="BR264" s="16"/>
-    </row>
-    <row r="265" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN264" s="16"/>
+      <c r="BQ264" s="16"/>
+    </row>
+    <row r="265" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D265" s="13"/>
       <c r="E265" s="12"/>
-      <c r="BO265" s="16"/>
-      <c r="BR265" s="16"/>
-    </row>
-    <row r="266" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN265" s="16"/>
+      <c r="BQ265" s="16"/>
+    </row>
+    <row r="266" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D266" s="13"/>
       <c r="E266" s="12"/>
-      <c r="BO266" s="16"/>
-      <c r="BR266" s="16"/>
-    </row>
-    <row r="267" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN266" s="16"/>
+      <c r="BQ266" s="16"/>
+    </row>
+    <row r="267" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D267" s="13"/>
       <c r="E267" s="12"/>
-      <c r="BO267" s="16"/>
-      <c r="BR267" s="16"/>
-    </row>
-    <row r="268" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN267" s="16"/>
+      <c r="BQ267" s="16"/>
+    </row>
+    <row r="268" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D268" s="13"/>
       <c r="E268" s="12"/>
-      <c r="BO268" s="16"/>
-      <c r="BR268" s="16"/>
-    </row>
-    <row r="269" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN268" s="16"/>
+      <c r="BQ268" s="16"/>
+    </row>
+    <row r="269" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D269" s="13"/>
       <c r="E269" s="12"/>
-      <c r="BO269" s="16"/>
-      <c r="BR269" s="16"/>
-    </row>
-    <row r="270" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN269" s="16"/>
+      <c r="BQ269" s="16"/>
+    </row>
+    <row r="270" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D270" s="13"/>
       <c r="E270" s="12"/>
-      <c r="BO270" s="16"/>
-      <c r="BR270" s="16"/>
-    </row>
-    <row r="271" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN270" s="16"/>
+      <c r="BQ270" s="16"/>
+    </row>
+    <row r="271" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D271" s="13"/>
       <c r="E271" s="12"/>
-      <c r="BO271" s="16"/>
-      <c r="BR271" s="16"/>
-    </row>
-    <row r="272" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN271" s="16"/>
+      <c r="BQ271" s="16"/>
+    </row>
+    <row r="272" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D272" s="13"/>
       <c r="E272" s="12"/>
-      <c r="BO272" s="16"/>
-      <c r="BR272" s="16"/>
-    </row>
-    <row r="273" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN272" s="16"/>
+      <c r="BQ272" s="16"/>
+    </row>
+    <row r="273" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D273" s="13"/>
       <c r="E273" s="12"/>
-      <c r="BO273" s="16"/>
-      <c r="BR273" s="16"/>
-    </row>
-    <row r="274" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN273" s="16"/>
+      <c r="BQ273" s="16"/>
+    </row>
+    <row r="274" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D274" s="13"/>
       <c r="E274" s="12"/>
-      <c r="BO274" s="16"/>
-      <c r="BR274" s="16"/>
-    </row>
-    <row r="275" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN274" s="16"/>
+      <c r="BQ274" s="16"/>
+    </row>
+    <row r="275" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D275" s="13"/>
       <c r="E275" s="12"/>
-      <c r="BO275" s="16"/>
-      <c r="BR275" s="16"/>
-    </row>
-    <row r="276" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN275" s="16"/>
+      <c r="BQ275" s="16"/>
+    </row>
+    <row r="276" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D276" s="13"/>
       <c r="E276" s="12"/>
-      <c r="BO276" s="16"/>
-      <c r="BR276" s="16"/>
-    </row>
-    <row r="277" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN276" s="16"/>
+      <c r="BQ276" s="16"/>
+    </row>
+    <row r="277" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D277" s="13"/>
       <c r="E277" s="12"/>
-      <c r="BO277" s="16"/>
-      <c r="BR277" s="16"/>
-    </row>
-    <row r="278" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN277" s="16"/>
+      <c r="BQ277" s="16"/>
+    </row>
+    <row r="278" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D278" s="13"/>
       <c r="E278" s="12"/>
-      <c r="BO278" s="16"/>
-      <c r="BR278" s="16"/>
-    </row>
-    <row r="279" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN278" s="16"/>
+      <c r="BQ278" s="16"/>
+    </row>
+    <row r="279" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D279" s="13"/>
       <c r="E279" s="12"/>
-      <c r="BO279" s="16"/>
-      <c r="BR279" s="16"/>
-    </row>
-    <row r="280" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN279" s="16"/>
+      <c r="BQ279" s="16"/>
+    </row>
+    <row r="280" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D280" s="13"/>
       <c r="E280" s="12"/>
-      <c r="BO280" s="16"/>
-      <c r="BR280" s="16"/>
-    </row>
-    <row r="281" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN280" s="16"/>
+      <c r="BQ280" s="16"/>
+    </row>
+    <row r="281" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D281" s="13"/>
       <c r="E281" s="12"/>
-      <c r="BO281" s="16"/>
-      <c r="BR281" s="16"/>
-    </row>
-    <row r="282" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN281" s="16"/>
+      <c r="BQ281" s="16"/>
+    </row>
+    <row r="282" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D282" s="13"/>
       <c r="E282" s="12"/>
-      <c r="BO282" s="16"/>
-      <c r="BR282" s="16"/>
-    </row>
-    <row r="283" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN282" s="16"/>
+      <c r="BQ282" s="16"/>
+    </row>
+    <row r="283" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D283" s="13"/>
       <c r="E283" s="12"/>
-      <c r="BO283" s="16"/>
-      <c r="BR283" s="16"/>
-    </row>
-    <row r="284" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN283" s="16"/>
+      <c r="BQ283" s="16"/>
+    </row>
+    <row r="284" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D284" s="13"/>
       <c r="E284" s="12"/>
-      <c r="BO284" s="16"/>
-      <c r="BR284" s="16"/>
-    </row>
-    <row r="285" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN284" s="16"/>
+      <c r="BQ284" s="16"/>
+    </row>
+    <row r="285" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D285" s="13"/>
       <c r="E285" s="12"/>
-      <c r="BO285" s="16"/>
-      <c r="BR285" s="16"/>
-    </row>
-    <row r="286" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN285" s="16"/>
+      <c r="BQ285" s="16"/>
+    </row>
+    <row r="286" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D286" s="13"/>
       <c r="E286" s="12"/>
-      <c r="BR286" s="16"/>
-    </row>
-    <row r="287" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ286" s="16"/>
+    </row>
+    <row r="287" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D287" s="13"/>
       <c r="E287" s="12"/>
-      <c r="BO287" s="16"/>
-      <c r="BR287" s="16"/>
-    </row>
-    <row r="288" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN287" s="16"/>
+      <c r="BQ287" s="16"/>
+    </row>
+    <row r="288" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D288" s="13"/>
       <c r="E288" s="12"/>
-      <c r="BO288" s="16"/>
-      <c r="BR288" s="16"/>
-    </row>
-    <row r="289" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN288" s="16"/>
+      <c r="BQ288" s="16"/>
+    </row>
+    <row r="289" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D289" s="13"/>
       <c r="E289" s="12"/>
-      <c r="BO289" s="16"/>
-      <c r="BR289" s="16"/>
-    </row>
-    <row r="290" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN289" s="16"/>
+      <c r="BQ289" s="16"/>
+    </row>
+    <row r="290" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D290" s="13"/>
       <c r="E290" s="12"/>
-      <c r="BO290" s="16"/>
-      <c r="BR290" s="16"/>
-    </row>
-    <row r="291" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN290" s="16"/>
+      <c r="BQ290" s="16"/>
+    </row>
+    <row r="291" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D291" s="13"/>
       <c r="E291" s="12"/>
-      <c r="BO291" s="16"/>
-      <c r="BR291" s="16"/>
-    </row>
-    <row r="292" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN291" s="16"/>
+      <c r="BQ291" s="16"/>
+    </row>
+    <row r="292" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D292" s="13"/>
       <c r="E292" s="12"/>
-      <c r="BO292" s="16"/>
-      <c r="BR292" s="16"/>
-    </row>
-    <row r="293" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN292" s="16"/>
+      <c r="BQ292" s="16"/>
+    </row>
+    <row r="293" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D293" s="13"/>
       <c r="E293" s="12"/>
-      <c r="BO293" s="16"/>
-      <c r="BR293" s="16"/>
-    </row>
-    <row r="294" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN293" s="16"/>
+      <c r="BQ293" s="16"/>
+    </row>
+    <row r="294" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D294" s="13"/>
       <c r="E294" s="12"/>
-      <c r="BO294" s="16"/>
-      <c r="BR294" s="16"/>
-    </row>
-    <row r="295" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN294" s="16"/>
+      <c r="BQ294" s="16"/>
+    </row>
+    <row r="295" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D295" s="13"/>
       <c r="E295" s="12"/>
-      <c r="BO295" s="16"/>
-      <c r="BR295" s="16"/>
-    </row>
-    <row r="296" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN295" s="16"/>
+      <c r="BQ295" s="16"/>
+    </row>
+    <row r="296" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D296" s="13"/>
       <c r="E296" s="12"/>
-      <c r="BO296" s="16"/>
-      <c r="BR296" s="16"/>
-    </row>
-    <row r="297" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN296" s="16"/>
+      <c r="BQ296" s="16"/>
+    </row>
+    <row r="297" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D297" s="13"/>
       <c r="E297" s="12"/>
-      <c r="BO297" s="16"/>
-      <c r="BR297" s="16"/>
-    </row>
-    <row r="298" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN297" s="16"/>
+      <c r="BQ297" s="16"/>
+    </row>
+    <row r="298" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D298" s="13"/>
       <c r="E298" s="12"/>
-      <c r="BO298" s="16"/>
-      <c r="BR298" s="16"/>
-    </row>
-    <row r="299" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN298" s="16"/>
+      <c r="BQ298" s="16"/>
+    </row>
+    <row r="299" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D299" s="13"/>
       <c r="E299" s="12"/>
-      <c r="BO299" s="16"/>
-      <c r="BR299" s="16"/>
-    </row>
-    <row r="300" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN299" s="16"/>
+      <c r="BQ299" s="16"/>
+    </row>
+    <row r="300" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D300" s="13"/>
       <c r="E300" s="12"/>
-      <c r="BO300" s="16"/>
-      <c r="BR300" s="16"/>
-    </row>
-    <row r="301" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN300" s="16"/>
+      <c r="BQ300" s="16"/>
+    </row>
+    <row r="301" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D301" s="13"/>
       <c r="E301" s="12"/>
-      <c r="BO301" s="16"/>
-      <c r="BR301" s="16"/>
-    </row>
-    <row r="302" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN301" s="16"/>
+      <c r="BQ301" s="16"/>
+    </row>
+    <row r="302" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D302" s="13"/>
       <c r="E302" s="12"/>
-      <c r="BO302" s="16"/>
-      <c r="BR302" s="16"/>
-    </row>
-    <row r="303" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN302" s="16"/>
+      <c r="BQ302" s="16"/>
+    </row>
+    <row r="303" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D303" s="13"/>
       <c r="E303" s="12"/>
-      <c r="BO303" s="16"/>
-      <c r="BR303" s="16"/>
-    </row>
-    <row r="304" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN303" s="16"/>
+      <c r="BQ303" s="16"/>
+    </row>
+    <row r="304" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D304" s="13"/>
       <c r="E304" s="12"/>
-      <c r="BO304" s="16"/>
-      <c r="BR304" s="16"/>
-    </row>
-    <row r="305" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN304" s="16"/>
+      <c r="BQ304" s="16"/>
+    </row>
+    <row r="305" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D305" s="13"/>
       <c r="E305" s="12"/>
-      <c r="BO305" s="16"/>
-      <c r="BR305" s="16"/>
-    </row>
-    <row r="306" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN305" s="16"/>
+      <c r="BQ305" s="16"/>
+    </row>
+    <row r="306" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D306" s="13"/>
       <c r="E306" s="12"/>
-      <c r="BO306" s="16"/>
-      <c r="BR306" s="16"/>
-    </row>
-    <row r="307" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN306" s="16"/>
+      <c r="BQ306" s="16"/>
+    </row>
+    <row r="307" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D307" s="13"/>
       <c r="E307" s="12"/>
-      <c r="BO307" s="16"/>
-      <c r="BR307" s="16"/>
-    </row>
-    <row r="308" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN307" s="16"/>
+      <c r="BQ307" s="16"/>
+    </row>
+    <row r="308" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D308" s="13"/>
       <c r="E308" s="12"/>
-      <c r="BO308" s="16"/>
-      <c r="BR308" s="16"/>
-    </row>
-    <row r="309" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN308" s="16"/>
+      <c r="BQ308" s="16"/>
+    </row>
+    <row r="309" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D309" s="13"/>
       <c r="E309" s="12"/>
-      <c r="BO309" s="16"/>
-      <c r="BR309" s="16"/>
-    </row>
-    <row r="310" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN309" s="16"/>
+      <c r="BQ309" s="16"/>
+    </row>
+    <row r="310" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D310" s="13"/>
       <c r="E310" s="12"/>
-      <c r="BO310" s="16"/>
-      <c r="BR310" s="16"/>
-    </row>
-    <row r="311" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN310" s="16"/>
+      <c r="BQ310" s="16"/>
+    </row>
+    <row r="311" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D311" s="13"/>
       <c r="E311" s="12"/>
-      <c r="BO311" s="16"/>
-      <c r="BR311" s="16"/>
-    </row>
-    <row r="312" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN311" s="16"/>
+      <c r="BQ311" s="16"/>
+    </row>
+    <row r="312" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D312" s="13"/>
       <c r="E312" s="12"/>
-      <c r="BO312" s="16"/>
-      <c r="BR312" s="16"/>
-    </row>
-    <row r="313" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN312" s="16"/>
+      <c r="BQ312" s="16"/>
+    </row>
+    <row r="313" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D313" s="13"/>
       <c r="E313" s="12"/>
-      <c r="BO313" s="16"/>
-      <c r="BR313" s="16"/>
-    </row>
-    <row r="314" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN313" s="16"/>
+      <c r="BQ313" s="16"/>
+    </row>
+    <row r="314" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D314" s="13"/>
       <c r="E314" s="12"/>
-      <c r="BO314" s="16"/>
-      <c r="BR314" s="16"/>
-    </row>
-    <row r="315" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN314" s="16"/>
+      <c r="BQ314" s="16"/>
+    </row>
+    <row r="315" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D315" s="13"/>
       <c r="E315" s="12"/>
-      <c r="BO315" s="16"/>
-      <c r="BR315" s="16"/>
-    </row>
-    <row r="316" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN315" s="16"/>
+      <c r="BQ315" s="16"/>
+    </row>
+    <row r="316" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D316" s="13"/>
       <c r="E316" s="12"/>
-      <c r="BO316" s="16"/>
-      <c r="BR316" s="16"/>
-    </row>
-    <row r="317" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN316" s="16"/>
+      <c r="BQ316" s="16"/>
+    </row>
+    <row r="317" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D317" s="13"/>
       <c r="E317" s="12"/>
-      <c r="BO317" s="16"/>
-      <c r="BR317" s="16"/>
-    </row>
-    <row r="318" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN317" s="16"/>
+      <c r="BQ317" s="16"/>
+    </row>
+    <row r="318" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D318" s="13"/>
       <c r="E318" s="12"/>
-      <c r="BO318" s="16"/>
-      <c r="BR318" s="16"/>
-    </row>
-    <row r="319" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN318" s="16"/>
+      <c r="BQ318" s="16"/>
+    </row>
+    <row r="319" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D319" s="13"/>
       <c r="E319" s="12"/>
-      <c r="BO319" s="16"/>
-      <c r="BR319" s="16"/>
-    </row>
-    <row r="320" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN319" s="16"/>
+      <c r="BQ319" s="16"/>
+    </row>
+    <row r="320" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D320" s="13"/>
       <c r="E320" s="12"/>
-      <c r="BO320" s="16"/>
-      <c r="BR320" s="16"/>
-    </row>
-    <row r="321" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN320" s="16"/>
+      <c r="BQ320" s="16"/>
+    </row>
+    <row r="321" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D321" s="13"/>
       <c r="E321" s="12"/>
-      <c r="BO321" s="16"/>
-      <c r="BR321" s="16"/>
-    </row>
-    <row r="322" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN321" s="16"/>
+      <c r="BQ321" s="16"/>
+    </row>
+    <row r="322" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D322" s="13"/>
       <c r="E322" s="12"/>
-      <c r="BO322" s="16"/>
-      <c r="BR322" s="16"/>
-    </row>
-    <row r="323" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN322" s="16"/>
+      <c r="BQ322" s="16"/>
+    </row>
+    <row r="323" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D323" s="13"/>
       <c r="E323" s="12"/>
-      <c r="BO323" s="16"/>
-      <c r="BR323" s="16"/>
-    </row>
-    <row r="324" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN323" s="16"/>
+      <c r="BQ323" s="16"/>
+    </row>
+    <row r="324" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D324" s="13"/>
       <c r="E324" s="12"/>
-      <c r="BO324" s="16"/>
-      <c r="BR324" s="16"/>
-    </row>
-    <row r="325" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN324" s="16"/>
+      <c r="BQ324" s="16"/>
+    </row>
+    <row r="325" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D325" s="13"/>
       <c r="E325" s="12"/>
-      <c r="BO325" s="16"/>
-      <c r="BR325" s="16"/>
-    </row>
-    <row r="326" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN325" s="16"/>
+      <c r="BQ325" s="16"/>
+    </row>
+    <row r="326" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D326" s="13"/>
       <c r="E326" s="12"/>
-      <c r="BO326" s="16"/>
-      <c r="BR326" s="16"/>
-    </row>
-    <row r="327" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN326" s="16"/>
+      <c r="BQ326" s="16"/>
+    </row>
+    <row r="327" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D327" s="13"/>
       <c r="E327" s="12"/>
-      <c r="BO327" s="16"/>
-      <c r="BR327" s="16"/>
-    </row>
-    <row r="328" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN327" s="16"/>
+      <c r="BQ327" s="16"/>
+    </row>
+    <row r="328" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D328" s="13"/>
       <c r="E328" s="12"/>
-      <c r="BO328" s="16"/>
-      <c r="BR328" s="16"/>
-    </row>
-    <row r="329" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN328" s="16"/>
+      <c r="BQ328" s="16"/>
+    </row>
+    <row r="329" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D329" s="13"/>
       <c r="E329" s="12"/>
-      <c r="BO329" s="16"/>
-      <c r="BR329" s="16"/>
-    </row>
-    <row r="330" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN329" s="16"/>
+      <c r="BQ329" s="16"/>
+    </row>
+    <row r="330" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D330" s="13"/>
       <c r="E330" s="12"/>
-      <c r="BO330" s="16"/>
-      <c r="BR330" s="16"/>
-    </row>
-    <row r="331" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN330" s="16"/>
+      <c r="BQ330" s="16"/>
+    </row>
+    <row r="331" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D331" s="13"/>
       <c r="E331" s="12"/>
-      <c r="BO331" s="16"/>
-      <c r="BR331" s="16"/>
-    </row>
-    <row r="332" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN331" s="16"/>
+      <c r="BQ331" s="16"/>
+    </row>
+    <row r="332" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D332" s="13"/>
       <c r="E332" s="12"/>
-      <c r="BO332" s="16"/>
-      <c r="BR332" s="16"/>
-    </row>
-    <row r="333" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN332" s="16"/>
+      <c r="BQ332" s="16"/>
+    </row>
+    <row r="333" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D333" s="13"/>
       <c r="E333" s="12"/>
-      <c r="BO333" s="16"/>
-      <c r="BR333" s="16"/>
-    </row>
-    <row r="334" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN333" s="16"/>
+      <c r="BQ333" s="16"/>
+    </row>
+    <row r="334" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D334" s="13"/>
       <c r="E334" s="12"/>
-      <c r="BO334" s="16"/>
-      <c r="BR334" s="16"/>
-    </row>
-    <row r="335" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN334" s="16"/>
+      <c r="BQ334" s="16"/>
+    </row>
+    <row r="335" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D335" s="13"/>
       <c r="E335" s="12"/>
-      <c r="BO335" s="16"/>
-      <c r="BR335" s="16"/>
-    </row>
-    <row r="336" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN335" s="16"/>
+      <c r="BQ335" s="16"/>
+    </row>
+    <row r="336" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D336" s="13"/>
       <c r="E336" s="12"/>
-      <c r="BO336" s="16"/>
-      <c r="BR336" s="16"/>
-    </row>
-    <row r="337" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN336" s="16"/>
+      <c r="BQ336" s="16"/>
+    </row>
+    <row r="337" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D337" s="13"/>
       <c r="E337" s="12"/>
-      <c r="BO337" s="16"/>
-      <c r="BR337" s="16"/>
-    </row>
-    <row r="338" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN337" s="16"/>
+      <c r="BQ337" s="16"/>
+    </row>
+    <row r="338" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D338" s="13"/>
       <c r="E338" s="12"/>
-      <c r="BO338" s="16"/>
-      <c r="BR338" s="16"/>
-    </row>
-    <row r="339" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN338" s="16"/>
+      <c r="BQ338" s="16"/>
+    </row>
+    <row r="339" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D339" s="13"/>
       <c r="E339" s="12"/>
-      <c r="BO339" s="16"/>
-      <c r="BR339" s="16"/>
-    </row>
-    <row r="340" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN339" s="16"/>
+      <c r="BQ339" s="16"/>
+    </row>
+    <row r="340" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D340" s="13"/>
       <c r="E340" s="12"/>
-      <c r="BO340" s="16"/>
-      <c r="BR340" s="16"/>
-    </row>
-    <row r="341" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN340" s="16"/>
+      <c r="BQ340" s="16"/>
+    </row>
+    <row r="341" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D341" s="13"/>
       <c r="E341" s="12"/>
-      <c r="BO341" s="16"/>
-      <c r="BR341" s="16"/>
-    </row>
-    <row r="342" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN341" s="16"/>
+      <c r="BQ341" s="16"/>
+    </row>
+    <row r="342" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D342" s="13"/>
       <c r="E342" s="12"/>
-      <c r="BR342" s="16"/>
-    </row>
-    <row r="343" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ342" s="16"/>
+    </row>
+    <row r="343" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D343" s="13"/>
       <c r="E343" s="12"/>
-      <c r="BR343" s="16"/>
-    </row>
-    <row r="344" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ343" s="16"/>
+    </row>
+    <row r="344" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D344" s="13"/>
       <c r="E344" s="12"/>
-      <c r="BR344" s="16"/>
-    </row>
-    <row r="345" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ344" s="16"/>
+    </row>
+    <row r="345" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D345" s="13"/>
       <c r="E345" s="12"/>
-      <c r="BO345" s="16"/>
-      <c r="BR345" s="16"/>
-    </row>
-    <row r="346" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN345" s="16"/>
+      <c r="BQ345" s="16"/>
+    </row>
+    <row r="346" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D346" s="13"/>
       <c r="E346" s="12"/>
-      <c r="BO346" s="16"/>
-      <c r="BR346" s="16"/>
-    </row>
-    <row r="347" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN346" s="16"/>
+      <c r="BQ346" s="16"/>
+    </row>
+    <row r="347" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D347" s="13"/>
       <c r="E347" s="12"/>
-      <c r="BO347" s="16"/>
-      <c r="BR347" s="16"/>
-    </row>
-    <row r="348" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN347" s="16"/>
+      <c r="BQ347" s="16"/>
+    </row>
+    <row r="348" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D348" s="13"/>
       <c r="E348" s="12"/>
-      <c r="BO348" s="16"/>
-      <c r="BR348" s="16"/>
-    </row>
-    <row r="349" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN348" s="16"/>
+      <c r="BQ348" s="16"/>
+    </row>
+    <row r="349" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D349" s="13"/>
       <c r="E349" s="12"/>
-      <c r="BO349" s="16"/>
-      <c r="BR349" s="16"/>
-    </row>
-    <row r="350" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN349" s="16"/>
+      <c r="BQ349" s="16"/>
+    </row>
+    <row r="350" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D350" s="13"/>
       <c r="E350" s="12"/>
-      <c r="BO350" s="16"/>
-      <c r="BR350" s="16"/>
-    </row>
-    <row r="351" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN350" s="16"/>
+      <c r="BQ350" s="16"/>
+    </row>
+    <row r="351" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D351" s="13"/>
       <c r="E351" s="12"/>
-      <c r="BO351" s="16"/>
-      <c r="BR351" s="16"/>
-    </row>
-    <row r="352" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN351" s="16"/>
+      <c r="BQ351" s="16"/>
+    </row>
+    <row r="352" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D352" s="13"/>
       <c r="E352" s="12"/>
-      <c r="BO352" s="16"/>
-      <c r="BR352" s="16"/>
-    </row>
-    <row r="353" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN352" s="16"/>
+      <c r="BQ352" s="16"/>
+    </row>
+    <row r="353" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D353" s="13"/>
       <c r="E353" s="12"/>
-      <c r="BO353" s="16"/>
-      <c r="BR353" s="16"/>
-    </row>
-    <row r="354" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN353" s="16"/>
+      <c r="BQ353" s="16"/>
+    </row>
+    <row r="354" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D354" s="13"/>
       <c r="E354" s="12"/>
-      <c r="BO354" s="16"/>
-      <c r="BR354" s="16"/>
-    </row>
-    <row r="355" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN354" s="16"/>
+      <c r="BQ354" s="16"/>
+    </row>
+    <row r="355" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D355" s="13"/>
       <c r="E355" s="12"/>
-      <c r="BO355" s="16"/>
-      <c r="BR355" s="16"/>
-    </row>
-    <row r="356" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN355" s="16"/>
+      <c r="BQ355" s="16"/>
+    </row>
+    <row r="356" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D356" s="13"/>
       <c r="E356" s="12"/>
-      <c r="BO356" s="16"/>
-      <c r="BR356" s="16"/>
-    </row>
-    <row r="357" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN356" s="16"/>
+      <c r="BQ356" s="16"/>
+    </row>
+    <row r="357" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D357" s="13"/>
       <c r="E357" s="12"/>
-      <c r="BO357" s="16"/>
-      <c r="BR357" s="16"/>
-    </row>
-    <row r="358" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN357" s="16"/>
+      <c r="BQ357" s="16"/>
+    </row>
+    <row r="358" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D358" s="13"/>
       <c r="E358" s="12"/>
-      <c r="BO358" s="16"/>
-      <c r="BR358" s="16"/>
-    </row>
-    <row r="359" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN358" s="16"/>
+      <c r="BQ358" s="16"/>
+    </row>
+    <row r="359" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D359" s="13"/>
       <c r="E359" s="12"/>
-      <c r="BO359" s="16"/>
-      <c r="BR359" s="16"/>
-    </row>
-    <row r="360" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN359" s="16"/>
+      <c r="BQ359" s="16"/>
+    </row>
+    <row r="360" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D360" s="13"/>
       <c r="E360" s="12"/>
-      <c r="BO360" s="16"/>
-      <c r="BR360" s="16"/>
-    </row>
-    <row r="361" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN360" s="16"/>
+      <c r="BQ360" s="16"/>
+    </row>
+    <row r="361" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D361" s="13"/>
       <c r="E361" s="12"/>
-      <c r="BO361" s="16"/>
-      <c r="BR361" s="16"/>
-    </row>
-    <row r="362" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN361" s="16"/>
+      <c r="BQ361" s="16"/>
+    </row>
+    <row r="362" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D362" s="13"/>
       <c r="E362" s="12"/>
-      <c r="BO362" s="16"/>
-      <c r="BR362" s="16"/>
-    </row>
-    <row r="363" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN362" s="16"/>
+      <c r="BQ362" s="16"/>
+    </row>
+    <row r="363" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D363" s="13"/>
       <c r="E363" s="12"/>
-      <c r="BO363" s="16"/>
-      <c r="BR363" s="16"/>
-    </row>
-    <row r="364" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN363" s="16"/>
+      <c r="BQ363" s="16"/>
+    </row>
+    <row r="364" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D364" s="13"/>
       <c r="E364" s="12"/>
-      <c r="BO364" s="16"/>
-      <c r="BR364" s="16"/>
-    </row>
-    <row r="365" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN364" s="16"/>
+      <c r="BQ364" s="16"/>
+    </row>
+    <row r="365" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D365" s="13"/>
       <c r="E365" s="12"/>
-      <c r="BO365" s="16"/>
-      <c r="BR365" s="16"/>
-    </row>
-    <row r="366" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN365" s="16"/>
+      <c r="BQ365" s="16"/>
+    </row>
+    <row r="366" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D366" s="13"/>
       <c r="E366" s="12"/>
-      <c r="BO366" s="16"/>
-      <c r="BR366" s="16"/>
-    </row>
-    <row r="367" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN366" s="16"/>
+      <c r="BQ366" s="16"/>
+    </row>
+    <row r="367" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D367" s="13"/>
       <c r="E367" s="12"/>
-      <c r="BO367" s="16"/>
-      <c r="BR367" s="16"/>
-    </row>
-    <row r="368" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN367" s="16"/>
+      <c r="BQ367" s="16"/>
+    </row>
+    <row r="368" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D368" s="13"/>
       <c r="E368" s="12"/>
-      <c r="BO368" s="16"/>
-      <c r="BR368" s="16"/>
-    </row>
-    <row r="369" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN368" s="16"/>
+      <c r="BQ368" s="16"/>
+    </row>
+    <row r="369" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D369" s="13"/>
       <c r="E369" s="12"/>
-      <c r="BO369" s="16"/>
-      <c r="BR369" s="16"/>
-    </row>
-    <row r="370" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN369" s="16"/>
+      <c r="BQ369" s="16"/>
+    </row>
+    <row r="370" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D370" s="13"/>
       <c r="E370" s="12"/>
-      <c r="BO370" s="16"/>
-      <c r="BR370" s="16"/>
-    </row>
-    <row r="371" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN370" s="16"/>
+      <c r="BQ370" s="16"/>
+    </row>
+    <row r="371" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D371" s="13"/>
       <c r="E371" s="12"/>
-      <c r="BO371" s="16"/>
-      <c r="BR371" s="16"/>
-    </row>
-    <row r="372" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN371" s="16"/>
+      <c r="BQ371" s="16"/>
+    </row>
+    <row r="372" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D372" s="13"/>
       <c r="E372" s="12"/>
-      <c r="BO372" s="16"/>
-      <c r="BR372" s="16"/>
-    </row>
-    <row r="373" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN372" s="16"/>
+      <c r="BQ372" s="16"/>
+    </row>
+    <row r="373" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D373" s="13"/>
       <c r="E373" s="12"/>
-      <c r="BO373" s="16"/>
-      <c r="BR373" s="16"/>
-    </row>
-    <row r="374" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN373" s="16"/>
+      <c r="BQ373" s="16"/>
+    </row>
+    <row r="374" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D374" s="13"/>
       <c r="E374" s="12"/>
-      <c r="BO374" s="16"/>
-      <c r="BR374" s="16"/>
-    </row>
-    <row r="375" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN374" s="16"/>
+      <c r="BQ374" s="16"/>
+    </row>
+    <row r="375" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D375" s="13"/>
       <c r="E375" s="12"/>
-      <c r="BO375" s="16"/>
-      <c r="BR375" s="16"/>
-    </row>
-    <row r="376" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN375" s="16"/>
+      <c r="BQ375" s="16"/>
+    </row>
+    <row r="376" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D376" s="13"/>
       <c r="E376" s="12"/>
-      <c r="BO376" s="16"/>
-      <c r="BR376" s="16"/>
-    </row>
-    <row r="377" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN376" s="16"/>
+      <c r="BQ376" s="16"/>
+    </row>
+    <row r="377" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D377" s="13"/>
       <c r="E377" s="12"/>
-      <c r="BO377" s="16"/>
-      <c r="BR377" s="16"/>
-    </row>
-    <row r="378" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN377" s="16"/>
+      <c r="BQ377" s="16"/>
+    </row>
+    <row r="378" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D378" s="13"/>
       <c r="E378" s="12"/>
-      <c r="BO378" s="16"/>
-      <c r="BR378" s="16"/>
-    </row>
-    <row r="379" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN378" s="16"/>
+      <c r="BQ378" s="16"/>
+    </row>
+    <row r="379" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D379" s="13"/>
       <c r="E379" s="12"/>
-      <c r="BR379" s="16"/>
-    </row>
-    <row r="380" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ379" s="16"/>
+    </row>
+    <row r="380" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D380" s="13"/>
       <c r="E380" s="12"/>
-      <c r="BR380" s="16"/>
-    </row>
-    <row r="381" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ380" s="16"/>
+    </row>
+    <row r="381" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D381" s="13"/>
       <c r="E381" s="12"/>
-      <c r="BO381" s="16"/>
-      <c r="BR381" s="16"/>
-    </row>
-    <row r="382" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN381" s="16"/>
+      <c r="BQ381" s="16"/>
+    </row>
+    <row r="382" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D382" s="13"/>
       <c r="E382" s="12"/>
-      <c r="BO382" s="16"/>
-      <c r="BR382" s="16"/>
-    </row>
-    <row r="383" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN382" s="16"/>
+      <c r="BQ382" s="16"/>
+    </row>
+    <row r="383" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D383" s="13"/>
       <c r="E383" s="12"/>
-      <c r="BO383" s="16"/>
-      <c r="BR383" s="16"/>
-    </row>
-    <row r="384" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN383" s="16"/>
+      <c r="BQ383" s="16"/>
+    </row>
+    <row r="384" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D384" s="13"/>
       <c r="E384" s="12"/>
-      <c r="BO384" s="16"/>
-      <c r="BR384" s="16"/>
-    </row>
-    <row r="385" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN384" s="16"/>
+      <c r="BQ384" s="16"/>
+    </row>
+    <row r="385" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D385" s="13"/>
       <c r="E385" s="12"/>
-      <c r="BO385" s="16"/>
-      <c r="BR385" s="16"/>
-    </row>
-    <row r="386" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN385" s="16"/>
+      <c r="BQ385" s="16"/>
+    </row>
+    <row r="386" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D386" s="13"/>
       <c r="E386" s="12"/>
-      <c r="BO386" s="16"/>
-      <c r="BR386" s="16"/>
-    </row>
-    <row r="387" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN386" s="16"/>
+      <c r="BQ386" s="16"/>
+    </row>
+    <row r="387" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D387" s="13"/>
       <c r="E387" s="12"/>
-      <c r="BO387" s="16"/>
-      <c r="BR387" s="16"/>
-    </row>
-    <row r="388" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN387" s="16"/>
+      <c r="BQ387" s="16"/>
+    </row>
+    <row r="388" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D388" s="13"/>
       <c r="E388" s="12"/>
-      <c r="BO388" s="16"/>
-      <c r="BR388" s="16"/>
-    </row>
-    <row r="389" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN388" s="16"/>
+      <c r="BQ388" s="16"/>
+    </row>
+    <row r="389" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D389" s="13"/>
       <c r="E389" s="12"/>
-      <c r="BO389" s="16"/>
-      <c r="BR389" s="16"/>
-    </row>
-    <row r="390" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN389" s="16"/>
+      <c r="BQ389" s="16"/>
+    </row>
+    <row r="390" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D390" s="13"/>
       <c r="E390" s="12"/>
-      <c r="BO390" s="16"/>
-      <c r="BR390" s="16"/>
-    </row>
-    <row r="391" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN390" s="16"/>
+      <c r="BQ390" s="16"/>
+    </row>
+    <row r="391" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D391" s="13"/>
       <c r="E391" s="12"/>
-      <c r="BO391" s="16"/>
-      <c r="BR391" s="16"/>
-    </row>
-    <row r="392" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN391" s="16"/>
+      <c r="BQ391" s="16"/>
+    </row>
+    <row r="392" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D392" s="13"/>
       <c r="E392" s="12"/>
-      <c r="BO392" s="16"/>
-      <c r="BR392" s="16"/>
-    </row>
-    <row r="393" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN392" s="16"/>
+      <c r="BQ392" s="16"/>
+    </row>
+    <row r="393" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D393" s="13"/>
       <c r="E393" s="12"/>
-      <c r="BO393" s="16"/>
-      <c r="BR393" s="16"/>
-    </row>
-    <row r="394" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN393" s="16"/>
+      <c r="BQ393" s="16"/>
+    </row>
+    <row r="394" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D394" s="13"/>
       <c r="E394" s="12"/>
-      <c r="BO394" s="16"/>
-      <c r="BR394" s="16"/>
-    </row>
-    <row r="395" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN394" s="16"/>
+      <c r="BQ394" s="16"/>
+    </row>
+    <row r="395" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D395" s="13"/>
       <c r="E395" s="12"/>
-      <c r="BO395" s="16"/>
-      <c r="BR395" s="16"/>
-    </row>
-    <row r="396" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN395" s="16"/>
+      <c r="BQ395" s="16"/>
+    </row>
+    <row r="396" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D396" s="13"/>
       <c r="E396" s="12"/>
-      <c r="BO396" s="16"/>
-      <c r="BR396" s="16"/>
-    </row>
-    <row r="397" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN396" s="16"/>
+      <c r="BQ396" s="16"/>
+    </row>
+    <row r="397" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D397" s="13"/>
       <c r="E397" s="12"/>
-      <c r="BO397" s="16"/>
-      <c r="BR397" s="16"/>
-    </row>
-    <row r="398" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN397" s="16"/>
+      <c r="BQ397" s="16"/>
+    </row>
+    <row r="398" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D398" s="13"/>
       <c r="E398" s="12"/>
-      <c r="BO398" s="16"/>
-      <c r="BR398" s="16"/>
-    </row>
-    <row r="399" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN398" s="16"/>
+      <c r="BQ398" s="16"/>
+    </row>
+    <row r="399" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D399" s="13"/>
       <c r="E399" s="12"/>
-      <c r="BO399" s="16"/>
-      <c r="BR399" s="16"/>
-    </row>
-    <row r="400" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN399" s="16"/>
+      <c r="BQ399" s="16"/>
+    </row>
+    <row r="400" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D400" s="13"/>
       <c r="E400" s="12"/>
-      <c r="BO400" s="16"/>
-      <c r="BR400" s="16"/>
-    </row>
-    <row r="401" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN400" s="16"/>
+      <c r="BQ400" s="16"/>
+    </row>
+    <row r="401" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D401" s="13"/>
       <c r="E401" s="12"/>
-      <c r="BO401" s="16"/>
-      <c r="BR401" s="16"/>
-    </row>
-    <row r="402" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN401" s="16"/>
+      <c r="BQ401" s="16"/>
+    </row>
+    <row r="402" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D402" s="13"/>
       <c r="E402" s="12"/>
-      <c r="BO402" s="16"/>
-      <c r="BR402" s="16"/>
-    </row>
-    <row r="403" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN402" s="16"/>
+      <c r="BQ402" s="16"/>
+    </row>
+    <row r="403" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D403" s="13"/>
       <c r="E403" s="12"/>
-      <c r="BO403" s="16"/>
-      <c r="BR403" s="16"/>
-    </row>
-    <row r="404" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN403" s="16"/>
+      <c r="BQ403" s="16"/>
+    </row>
+    <row r="404" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D404" s="13"/>
       <c r="E404" s="12"/>
-      <c r="BR404" s="16"/>
-    </row>
-    <row r="405" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ404" s="16"/>
+    </row>
+    <row r="405" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D405" s="13"/>
       <c r="E405" s="12"/>
-      <c r="BR405" s="16"/>
-    </row>
-    <row r="406" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ405" s="16"/>
+    </row>
+    <row r="406" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D406" s="13"/>
       <c r="E406" s="12"/>
-      <c r="BO406" s="16"/>
-      <c r="BR406" s="16"/>
-    </row>
-    <row r="407" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN406" s="16"/>
+      <c r="BQ406" s="16"/>
+    </row>
+    <row r="407" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D407" s="13"/>
       <c r="E407" s="12"/>
-      <c r="BO407" s="16"/>
-      <c r="BR407" s="16"/>
-    </row>
-    <row r="408" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN407" s="16"/>
+      <c r="BQ407" s="16"/>
+    </row>
+    <row r="408" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D408" s="13"/>
       <c r="E408" s="12"/>
-      <c r="BR408" s="16"/>
-    </row>
-    <row r="409" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ408" s="16"/>
+    </row>
+    <row r="409" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D409" s="13"/>
       <c r="E409" s="12"/>
-      <c r="BR409" s="16"/>
-    </row>
-    <row r="410" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ409" s="16"/>
+    </row>
+    <row r="410" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D410" s="13"/>
       <c r="E410" s="12"/>
-      <c r="BO410" s="16"/>
-      <c r="BR410" s="16"/>
-    </row>
-    <row r="411" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN410" s="16"/>
+      <c r="BQ410" s="16"/>
+    </row>
+    <row r="411" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D411" s="13"/>
       <c r="E411" s="12"/>
-      <c r="BO411" s="16"/>
-      <c r="BR411" s="16"/>
-    </row>
-    <row r="412" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN411" s="16"/>
+      <c r="BQ411" s="16"/>
+    </row>
+    <row r="412" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D412" s="13"/>
       <c r="E412" s="12"/>
-      <c r="BO412" s="16"/>
-      <c r="BR412" s="16"/>
-    </row>
-    <row r="413" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN412" s="16"/>
+      <c r="BQ412" s="16"/>
+    </row>
+    <row r="413" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D413" s="13"/>
       <c r="E413" s="12"/>
-      <c r="BO413" s="16"/>
-      <c r="BR413" s="16"/>
-    </row>
-    <row r="414" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN413" s="16"/>
+      <c r="BQ413" s="16"/>
+    </row>
+    <row r="414" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D414" s="13"/>
       <c r="E414" s="12"/>
-      <c r="BO414" s="16"/>
-      <c r="BR414" s="16"/>
-    </row>
-    <row r="415" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN414" s="16"/>
+      <c r="BQ414" s="16"/>
+    </row>
+    <row r="415" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D415" s="13"/>
       <c r="E415" s="12"/>
-      <c r="BO415" s="16"/>
-      <c r="BR415" s="16"/>
-    </row>
-    <row r="416" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN415" s="16"/>
+      <c r="BQ415" s="16"/>
+    </row>
+    <row r="416" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D416" s="13"/>
       <c r="E416" s="12"/>
-      <c r="BO416" s="16"/>
-      <c r="BR416" s="16"/>
-    </row>
-    <row r="417" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN416" s="16"/>
+      <c r="BQ416" s="16"/>
+    </row>
+    <row r="417" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D417" s="13"/>
       <c r="E417" s="12"/>
-      <c r="BO417" s="16"/>
-      <c r="BR417" s="16"/>
-    </row>
-    <row r="418" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN417" s="16"/>
+      <c r="BQ417" s="16"/>
+    </row>
+    <row r="418" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D418" s="13"/>
       <c r="E418" s="12"/>
-      <c r="BO418" s="16"/>
-      <c r="BR418" s="16"/>
-    </row>
-    <row r="419" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN418" s="16"/>
+      <c r="BQ418" s="16"/>
+    </row>
+    <row r="419" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D419" s="13"/>
       <c r="E419" s="12"/>
-      <c r="BO419" s="16"/>
-      <c r="BR419" s="16"/>
-    </row>
-    <row r="420" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN419" s="16"/>
+      <c r="BQ419" s="16"/>
+    </row>
+    <row r="420" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D420" s="13"/>
       <c r="E420" s="12"/>
-      <c r="BO420" s="16"/>
-      <c r="BR420" s="16"/>
-    </row>
-    <row r="421" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN420" s="16"/>
+      <c r="BQ420" s="16"/>
+    </row>
+    <row r="421" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D421" s="13"/>
       <c r="E421" s="12"/>
-      <c r="BO421" s="16"/>
-      <c r="BR421" s="16"/>
-    </row>
-    <row r="422" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN421" s="16"/>
+      <c r="BQ421" s="16"/>
+    </row>
+    <row r="422" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D422" s="13"/>
       <c r="E422" s="12"/>
-      <c r="BO422" s="16"/>
-      <c r="BR422" s="16"/>
-    </row>
-    <row r="423" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN422" s="16"/>
+      <c r="BQ422" s="16"/>
+    </row>
+    <row r="423" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D423" s="13"/>
       <c r="E423" s="12"/>
-      <c r="BO423" s="16"/>
-      <c r="BR423" s="16"/>
-    </row>
-    <row r="424" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN423" s="16"/>
+      <c r="BQ423" s="16"/>
+    </row>
+    <row r="424" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D424" s="13"/>
       <c r="E424" s="12"/>
-      <c r="BO424" s="16"/>
-      <c r="BR424" s="16"/>
-    </row>
-    <row r="425" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN424" s="16"/>
+      <c r="BQ424" s="16"/>
+    </row>
+    <row r="425" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D425" s="13"/>
       <c r="E425" s="12"/>
-      <c r="BO425" s="16"/>
-      <c r="BR425" s="16"/>
-    </row>
-    <row r="426" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN425" s="16"/>
+      <c r="BQ425" s="16"/>
+    </row>
+    <row r="426" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D426" s="13"/>
       <c r="E426" s="12"/>
-      <c r="BO426" s="16"/>
-      <c r="BR426" s="16"/>
-    </row>
-    <row r="427" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN426" s="16"/>
+      <c r="BQ426" s="16"/>
+    </row>
+    <row r="427" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D427" s="13"/>
       <c r="E427" s="12"/>
     </row>
-    <row r="428" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="428" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D428" s="13"/>
       <c r="E428" s="12"/>
     </row>
-    <row r="429" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="429" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D429" s="13"/>
       <c r="E429" s="12"/>
     </row>
-    <row r="430" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="430" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D430" s="13"/>
       <c r="E430" s="12"/>
     </row>
-    <row r="431" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="431" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D431" s="13"/>
       <c r="E431" s="12"/>
     </row>
-    <row r="432" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="432" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D432" s="13"/>
       <c r="E432" s="12"/>
     </row>
@@ -6485,334 +6475,334 @@
   <sheetData>
     <row r="1" spans="1:113" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F1" t="s">
+        <v>133</v>
+      </c>
+      <c r="G1" t="s">
         <v>134</v>
       </c>
-      <c r="D1" t="s">
+      <c r="H1" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="E1" t="s">
+      <c r="I1" t="s">
         <v>136</v>
       </c>
-      <c r="F1" t="s">
+      <c r="J1" t="s">
         <v>137</v>
       </c>
-      <c r="G1" t="s">
+      <c r="K1" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="L1" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="I1" t="s">
+      <c r="M1" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="J1" t="s">
+      <c r="N1" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="O1" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="P1" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="Q1" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="R1" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="S1" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="T1" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="U1" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="V1" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="W1" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="X1" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="Y1" t="s">
         <v>151</v>
       </c>
-      <c r="U1" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="V1" s="5" t="s">
+      <c r="Z1" t="s">
         <v>152</v>
       </c>
-      <c r="W1" s="5" t="s">
+      <c r="AA1" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="X1" s="5" t="s">
+      <c r="AB1" t="s">
         <v>154</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AC1" t="s">
         <v>155</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AD1" t="s">
         <v>156</v>
       </c>
-      <c r="AA1" s="5" t="s">
+      <c r="AE1" t="s">
         <v>157</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AF1" t="s">
         <v>158</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AG1" t="s">
         <v>159</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AH1" t="s">
         <v>160</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AI1" t="s">
         <v>161</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AJ1" t="s">
         <v>162</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AK1" t="s">
         <v>163</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AL1" t="s">
         <v>164</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AM1" t="s">
         <v>165</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AN1" t="s">
         <v>166</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AO1" t="s">
         <v>167</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AP1" t="s">
         <v>168</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AQ1" t="s">
         <v>169</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AR1" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="AS1" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="AT1" t="s">
         <v>170</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AU1" t="s">
         <v>171</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AV1" t="s">
         <v>172</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AW1" t="s">
         <v>173</v>
       </c>
-      <c r="AR1" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="AS1" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="AT1" t="s">
+      <c r="AX1" t="s">
         <v>174</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AY1" t="s">
         <v>175</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AZ1" t="s">
         <v>176</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="BA1" t="s">
         <v>177</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="BB1" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="BC1" t="s">
         <v>179</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BD1" t="s">
         <v>180</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BE1" t="s">
         <v>181</v>
       </c>
-      <c r="BB1" s="2" t="s">
+      <c r="BF1" t="s">
         <v>182</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BG1" t="s">
         <v>183</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BH1" t="s">
         <v>184</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BJ1" t="s">
+        <v>184</v>
+      </c>
+      <c r="BK1" t="s">
         <v>185</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BL1" t="s">
         <v>186</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BM1" t="s">
         <v>187</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BN1" t="s">
         <v>188</v>
       </c>
-      <c r="BJ1" t="s">
-        <v>188</v>
-      </c>
-      <c r="BK1" t="s">
+      <c r="BO1" t="s">
         <v>189</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BP1" t="s">
         <v>190</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BQ1" t="s">
         <v>191</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BR1" t="s">
         <v>192</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BS1" t="s">
         <v>193</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BT1" t="s">
         <v>194</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BU1" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BV1" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="BS1" t="s">
+      <c r="BW1" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="BT1" t="s">
+      <c r="BX1" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="BU1" s="2" t="s">
+      <c r="BY1" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="BV1" s="6" t="s">
+      <c r="BZ1" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="BW1" s="6" t="s">
+      <c r="CA1" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="BX1" s="6" t="s">
+      <c r="CB1" t="s">
         <v>202</v>
       </c>
-      <c r="BY1" s="6" t="s">
+      <c r="CC1" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="BZ1" s="6" t="s">
+      <c r="CD1" t="s">
         <v>204</v>
       </c>
-      <c r="CA1" s="6" t="s">
+      <c r="CE1" t="s">
         <v>205</v>
       </c>
-      <c r="CB1" t="s">
+      <c r="CF1" t="s">
         <v>206</v>
       </c>
-      <c r="CC1" s="6" t="s">
+      <c r="CG1" t="s">
         <v>207</v>
       </c>
-      <c r="CD1" t="s">
+      <c r="CH1" t="s">
         <v>208</v>
       </c>
-      <c r="CE1" t="s">
+      <c r="CI1" t="s">
         <v>209</v>
       </c>
-      <c r="CF1" t="s">
+      <c r="CJ1" t="s">
         <v>210</v>
       </c>
-      <c r="CG1" t="s">
+      <c r="CK1" t="s">
         <v>211</v>
       </c>
-      <c r="CH1" t="s">
+      <c r="CL1" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="CI1" t="s">
+      <c r="CM1" t="s">
         <v>213</v>
       </c>
-      <c r="CJ1" t="s">
+      <c r="CN1" t="s">
         <v>214</v>
       </c>
-      <c r="CK1" t="s">
+      <c r="CO1" t="s">
         <v>215</v>
       </c>
-      <c r="CL1" s="2" t="s">
+      <c r="CP1" t="s">
         <v>216</v>
       </c>
-      <c r="CM1" t="s">
+      <c r="CQ1" t="s">
         <v>217</v>
       </c>
-      <c r="CN1" t="s">
+      <c r="CR1" t="s">
+        <v>194</v>
+      </c>
+      <c r="CS1" t="s">
         <v>218</v>
       </c>
-      <c r="CO1" t="s">
+      <c r="CT1" t="s">
         <v>219</v>
       </c>
-      <c r="CP1" t="s">
+      <c r="CU1" t="s">
         <v>220</v>
       </c>
-      <c r="CQ1" t="s">
+      <c r="CV1" t="s">
         <v>221</v>
       </c>
-      <c r="CR1" t="s">
-        <v>198</v>
-      </c>
-      <c r="CS1" t="s">
+      <c r="CW1" t="s">
         <v>222</v>
       </c>
-      <c r="CT1" t="s">
+      <c r="CX1" t="s">
         <v>223</v>
       </c>
-      <c r="CU1" t="s">
+      <c r="CY1" t="s">
         <v>224</v>
       </c>
-      <c r="CV1" t="s">
+      <c r="CZ1" t="s">
+        <v>223</v>
+      </c>
+      <c r="DA1" t="s">
         <v>225</v>
       </c>
-      <c r="CW1" t="s">
+      <c r="DB1" t="s">
         <v>226</v>
       </c>
-      <c r="CX1" t="s">
+      <c r="DC1" t="s">
         <v>227</v>
       </c>
-      <c r="CY1" t="s">
+      <c r="DD1" t="s">
         <v>228</v>
       </c>
-      <c r="CZ1" t="s">
-        <v>227</v>
-      </c>
-      <c r="DA1" t="s">
+      <c r="DE1" t="s">
         <v>229</v>
       </c>
-      <c r="DB1" t="s">
+      <c r="DF1" t="s">
         <v>230</v>
       </c>
-      <c r="DC1" t="s">
+      <c r="DG1" t="s">
         <v>231</v>
       </c>
-      <c r="DD1" t="s">
+      <c r="DH1" t="s">
         <v>232</v>
       </c>
-      <c r="DE1" t="s">
+      <c r="DI1" t="s">
         <v>233</v>
-      </c>
-      <c r="DF1" t="s">
-        <v>234</v>
-      </c>
-      <c r="DG1" t="s">
-        <v>235</v>
-      </c>
-      <c r="DH1" t="s">
-        <v>236</v>
-      </c>
-      <c r="DI1" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="2" spans="1:113" x14ac:dyDescent="0.25">
@@ -6820,337 +6810,337 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2" t="s">
+        <v>234</v>
+      </c>
+      <c r="F2" t="s">
+        <v>235</v>
+      </c>
+      <c r="G2" t="s">
+        <v>50</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="I2" t="s">
+        <v>237</v>
+      </c>
+      <c r="J2" t="s">
+        <v>238</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="P2" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="Q2" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="R2" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="S2" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="T2" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="U2" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="V2" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="W2" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="X2" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>253</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>254</v>
+      </c>
+      <c r="AA2" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>256</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>257</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>258</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>259</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>260</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>261</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>262</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>263</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>264</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>265</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>266</v>
+      </c>
+      <c r="AM2" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>267</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>268</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>269</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>270</v>
+      </c>
+      <c r="AR2" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="AS2" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>271</v>
+      </c>
+      <c r="AU2" t="s">
+        <v>272</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>273</v>
+      </c>
+      <c r="AW2" t="s">
+        <v>274</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>275</v>
+      </c>
+      <c r="AY2" t="s">
+        <v>276</v>
+      </c>
+      <c r="AZ2" t="s">
+        <v>277</v>
+      </c>
+      <c r="BA2" t="s">
+        <v>278</v>
+      </c>
+      <c r="BB2" t="s">
+        <v>279</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>280</v>
+      </c>
+      <c r="BD2" t="s">
+        <v>281</v>
+      </c>
+      <c r="BE2" t="s">
+        <v>282</v>
+      </c>
+      <c r="BF2" t="s">
+        <v>283</v>
+      </c>
+      <c r="BG2" t="s">
+        <v>284</v>
+      </c>
+      <c r="BH2" t="s">
+        <v>285</v>
+      </c>
+      <c r="BI2" t="s">
+        <v>286</v>
+      </c>
+      <c r="BJ2" t="s">
+        <v>287</v>
+      </c>
+      <c r="BK2" t="s">
+        <v>288</v>
+      </c>
+      <c r="BL2" t="s">
+        <v>289</v>
+      </c>
+      <c r="BM2" t="s">
+        <v>290</v>
+      </c>
+      <c r="BN2" t="s">
+        <v>291</v>
+      </c>
+      <c r="BO2" t="s">
         <v>76</v>
       </c>
-      <c r="E2" t="s">
-        <v>238</v>
-      </c>
-      <c r="F2" t="s">
-        <v>239</v>
-      </c>
-      <c r="G2" t="s">
-        <v>52</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="I2" t="s">
-        <v>241</v>
-      </c>
-      <c r="J2" t="s">
-        <v>242</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="O2" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="P2" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="Q2" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="R2" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="S2" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="T2" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="U2" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="V2" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="W2" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="X2" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>257</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>258</v>
-      </c>
-      <c r="AA2" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>260</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>261</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>262</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>263</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>264</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>265</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>266</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>267</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>268</v>
-      </c>
-      <c r="AK2" t="s">
-        <v>269</v>
-      </c>
-      <c r="AL2" t="s">
-        <v>270</v>
-      </c>
-      <c r="AM2" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="AN2" t="s">
-        <v>271</v>
-      </c>
-      <c r="AO2" t="s">
-        <v>272</v>
-      </c>
-      <c r="AP2" t="s">
-        <v>273</v>
-      </c>
-      <c r="AQ2" t="s">
-        <v>274</v>
-      </c>
-      <c r="AR2" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="AS2" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="AT2" t="s">
-        <v>275</v>
-      </c>
-      <c r="AU2" t="s">
-        <v>276</v>
-      </c>
-      <c r="AV2" t="s">
-        <v>277</v>
-      </c>
-      <c r="AW2" t="s">
-        <v>278</v>
-      </c>
-      <c r="AX2" t="s">
-        <v>279</v>
-      </c>
-      <c r="AY2" t="s">
-        <v>280</v>
-      </c>
-      <c r="AZ2" t="s">
-        <v>281</v>
-      </c>
-      <c r="BA2" t="s">
-        <v>282</v>
-      </c>
-      <c r="BB2" t="s">
-        <v>283</v>
-      </c>
-      <c r="BC2" t="s">
-        <v>284</v>
-      </c>
-      <c r="BD2" t="s">
-        <v>285</v>
-      </c>
-      <c r="BE2" t="s">
-        <v>286</v>
-      </c>
-      <c r="BF2" t="s">
-        <v>287</v>
-      </c>
-      <c r="BG2" t="s">
-        <v>288</v>
-      </c>
-      <c r="BH2" t="s">
-        <v>289</v>
-      </c>
-      <c r="BI2" t="s">
-        <v>290</v>
-      </c>
-      <c r="BJ2" t="s">
-        <v>291</v>
-      </c>
-      <c r="BK2" t="s">
+      <c r="BP2" t="s">
         <v>292</v>
       </c>
-      <c r="BL2" t="s">
+      <c r="BQ2" t="s">
         <v>293</v>
       </c>
-      <c r="BM2" t="s">
+      <c r="BR2" t="s">
         <v>294</v>
       </c>
-      <c r="BN2" t="s">
+      <c r="BS2" t="s">
         <v>295</v>
       </c>
-      <c r="BO2" t="s">
-        <v>78</v>
-      </c>
-      <c r="BP2" t="s">
+      <c r="BT2" t="s">
         <v>296</v>
       </c>
-      <c r="BQ2" t="s">
+      <c r="BU2" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV2" s="6" t="s">
         <v>297</v>
       </c>
-      <c r="BR2" t="s">
+      <c r="BW2" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="BX2" s="6" t="s">
         <v>298</v>
       </c>
-      <c r="BS2" t="s">
+      <c r="BY2" s="6" t="s">
         <v>299</v>
       </c>
-      <c r="BT2" t="s">
+      <c r="BZ2" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="BU2" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="BV2" s="6" t="s">
+      <c r="CA2" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="BW2" s="6" t="s">
-        <v>435</v>
-      </c>
-      <c r="BX2" s="6" t="s">
+      <c r="CB2" t="s">
         <v>302</v>
       </c>
-      <c r="BY2" s="6" t="s">
+      <c r="CC2" t="s">
         <v>303</v>
       </c>
-      <c r="BZ2" s="6" t="s">
+      <c r="CD2" t="s">
         <v>304</v>
       </c>
-      <c r="CA2" s="6" t="s">
+      <c r="CE2" t="s">
         <v>305</v>
       </c>
-      <c r="CB2" t="s">
+      <c r="CF2" t="s">
         <v>306</v>
       </c>
-      <c r="CC2" t="s">
+      <c r="CG2" t="s">
         <v>307</v>
       </c>
-      <c r="CD2" t="s">
+      <c r="CH2" t="s">
         <v>308</v>
       </c>
-      <c r="CE2" t="s">
+      <c r="CI2" t="s">
         <v>309</v>
       </c>
-      <c r="CF2" t="s">
+      <c r="CJ2" t="s">
         <v>310</v>
       </c>
-      <c r="CG2" t="s">
+      <c r="CK2" t="s">
         <v>311</v>
       </c>
-      <c r="CH2" t="s">
+      <c r="CL2" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="CI2" t="s">
+      <c r="CM2" t="s">
         <v>313</v>
       </c>
-      <c r="CJ2" t="s">
+      <c r="CN2" t="s">
         <v>314</v>
       </c>
-      <c r="CK2" t="s">
+      <c r="CO2" t="s">
         <v>315</v>
       </c>
-      <c r="CL2" s="2" t="s">
+      <c r="CP2" t="s">
         <v>316</v>
       </c>
-      <c r="CM2" t="s">
+      <c r="CQ2" t="s">
         <v>317</v>
       </c>
-      <c r="CN2" t="s">
+      <c r="CR2" t="s">
         <v>318</v>
       </c>
-      <c r="CO2" t="s">
+      <c r="CS2" t="s">
         <v>319</v>
       </c>
-      <c r="CP2" t="s">
+      <c r="CT2" t="s">
         <v>320</v>
       </c>
-      <c r="CQ2" t="s">
+      <c r="CU2" t="s">
         <v>321</v>
       </c>
-      <c r="CR2" t="s">
+      <c r="CV2" t="s">
         <v>322</v>
       </c>
-      <c r="CS2" t="s">
+      <c r="CW2" t="s">
         <v>323</v>
       </c>
-      <c r="CT2" t="s">
+      <c r="CX2" t="s">
         <v>324</v>
       </c>
-      <c r="CU2" t="s">
+      <c r="CY2" t="s">
         <v>325</v>
       </c>
-      <c r="CV2" t="s">
+      <c r="CZ2" t="s">
         <v>326</v>
       </c>
-      <c r="CW2" t="s">
+      <c r="DA2" t="s">
         <v>327</v>
       </c>
-      <c r="CX2" t="s">
+      <c r="DB2" t="s">
         <v>328</v>
       </c>
-      <c r="CY2" t="s">
+      <c r="DC2" t="s">
         <v>329</v>
       </c>
-      <c r="CZ2" t="s">
+      <c r="DD2" t="s">
         <v>330</v>
       </c>
-      <c r="DA2" t="s">
+      <c r="DE2" t="s">
         <v>331</v>
       </c>
-      <c r="DB2" t="s">
+      <c r="DF2" t="s">
         <v>332</v>
       </c>
-      <c r="DC2" t="s">
+      <c r="DG2" t="s">
         <v>333</v>
       </c>
-      <c r="DD2" t="s">
+      <c r="DH2" t="s">
         <v>334</v>
       </c>
-      <c r="DE2" t="s">
+      <c r="DI2" t="s">
         <v>335</v>
-      </c>
-      <c r="DF2" t="s">
-        <v>336</v>
-      </c>
-      <c r="DG2" t="s">
-        <v>337</v>
-      </c>
-      <c r="DH2" t="s">
-        <v>338</v>
-      </c>
-      <c r="DI2" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="3" spans="1:113" x14ac:dyDescent="0.25">
@@ -7170,330 +7160,330 @@
         <v>2</v>
       </c>
       <c r="G3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="I3" t="s">
+        <v>111</v>
+      </c>
+      <c r="J3" t="s">
+        <v>336</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="O3" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="J3" t="s">
-        <v>340</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>341</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>342</v>
-      </c>
-      <c r="M3" s="5" t="s">
+      <c r="P3" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q3" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="R3" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="S3" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="T3" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="U3" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="V3" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="W3" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="X3" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>111</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>111</v>
+      </c>
+      <c r="AA3" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>111</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>111</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>111</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>111</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>339</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>111</v>
+      </c>
+      <c r="AI3" t="s">
         <v>117</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="O3" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="P3" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q3" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="R3" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="S3" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="T3" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="U3" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="V3" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="W3" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="X3" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>115</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AA3" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>343</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>121</v>
       </c>
       <c r="AJ3" t="s">
         <v>3</v>
       </c>
       <c r="AK3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="AL3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="AM3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="AN3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="AO3" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="AP3" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="AQ3" t="s">
         <v>2</v>
       </c>
       <c r="AR3" s="2" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="AS3" s="2" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="AT3" t="s">
+        <v>342</v>
+      </c>
+      <c r="AU3" t="s">
+        <v>111</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AW3" t="s">
+        <v>111</v>
+      </c>
+      <c r="AX3" t="s">
+        <v>343</v>
+      </c>
+      <c r="AY3" t="s">
+        <v>111</v>
+      </c>
+      <c r="AZ3" t="s">
+        <v>112</v>
+      </c>
+      <c r="BA3" t="s">
+        <v>111</v>
+      </c>
+      <c r="BB3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>112</v>
+      </c>
+      <c r="BD3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BE3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BF3" t="s">
+        <v>112</v>
+      </c>
+      <c r="BG3" t="s">
+        <v>111</v>
+      </c>
+      <c r="BH3" t="s">
+        <v>342</v>
+      </c>
+      <c r="BI3" t="s">
+        <v>111</v>
+      </c>
+      <c r="BJ3" t="s">
+        <v>112</v>
+      </c>
+      <c r="BK3" t="s">
+        <v>112</v>
+      </c>
+      <c r="BL3" t="s">
+        <v>112</v>
+      </c>
+      <c r="BM3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BN3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BO3" t="s">
+        <v>114</v>
+      </c>
+      <c r="BP3" t="s">
+        <v>114</v>
+      </c>
+      <c r="BQ3" t="s">
+        <v>344</v>
+      </c>
+      <c r="BR3" t="s">
+        <v>345</v>
+      </c>
+      <c r="BS3" t="s">
+        <v>112</v>
+      </c>
+      <c r="BT3" t="s">
+        <v>112</v>
+      </c>
+      <c r="BU3" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="BV3" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="BW3" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="BX3" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="BY3" s="6" t="s">
         <v>346</v>
       </c>
-      <c r="AU3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AV3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AW3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AX3" t="s">
+      <c r="BZ3" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="CA3" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>119</v>
+      </c>
+      <c r="CC3" t="s">
         <v>347</v>
       </c>
-      <c r="AY3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AZ3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BA3" t="s">
-        <v>115</v>
-      </c>
-      <c r="BB3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BC3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BD3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BE3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BF3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BG3" t="s">
-        <v>115</v>
-      </c>
-      <c r="BH3" t="s">
-        <v>346</v>
-      </c>
-      <c r="BI3" t="s">
-        <v>115</v>
-      </c>
-      <c r="BJ3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BK3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BL3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BM3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BN3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BO3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BP3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BQ3" t="s">
+      <c r="CD3" t="s">
+        <v>119</v>
+      </c>
+      <c r="CE3" t="s">
+        <v>119</v>
+      </c>
+      <c r="CF3" t="s">
+        <v>119</v>
+      </c>
+      <c r="CG3" t="s">
         <v>348</v>
       </c>
-      <c r="BR3" t="s">
+      <c r="CH3" t="s">
         <v>349</v>
-      </c>
-      <c r="BS3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BT3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BU3" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="BV3" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="BW3" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="BX3" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="BY3" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="BZ3" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="CA3" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="CB3" t="s">
-        <v>123</v>
-      </c>
-      <c r="CC3" t="s">
-        <v>351</v>
-      </c>
-      <c r="CD3" t="s">
-        <v>123</v>
-      </c>
-      <c r="CE3" t="s">
-        <v>123</v>
-      </c>
-      <c r="CF3" t="s">
-        <v>123</v>
-      </c>
-      <c r="CG3" t="s">
-        <v>352</v>
-      </c>
-      <c r="CH3" t="s">
-        <v>353</v>
       </c>
       <c r="CI3" t="s">
         <v>2</v>
       </c>
       <c r="CJ3" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="CK3" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="CL3" s="2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="CM3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="CN3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="CO3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="CP3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="CQ3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="CR3" t="s">
+        <v>347</v>
+      </c>
+      <c r="CS3" t="s">
+        <v>118</v>
+      </c>
+      <c r="CT3" t="s">
+        <v>111</v>
+      </c>
+      <c r="CU3" t="s">
+        <v>120</v>
+      </c>
+      <c r="CV3" t="s">
         <v>351</v>
       </c>
-      <c r="CS3" t="s">
-        <v>122</v>
-      </c>
-      <c r="CT3" t="s">
-        <v>115</v>
-      </c>
-      <c r="CU3" t="s">
-        <v>124</v>
-      </c>
-      <c r="CV3" t="s">
-        <v>355</v>
-      </c>
       <c r="CW3" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="CX3" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="CY3" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="CZ3" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="DA3" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="DB3" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="DC3" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="DD3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="DE3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="DF3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="DG3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="DH3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="DI3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:113" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
     </row>
     <row r="5" spans="1:113" x14ac:dyDescent="0.25">
@@ -7504,25 +7494,25 @@
     </row>
     <row r="6" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="C6" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="P6" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="AC6">
         <v>1</v>
       </c>
       <c r="AO6" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="AT6" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="AY6">
         <v>1</v>
@@ -7534,42 +7524,42 @@
         <v>1</v>
       </c>
       <c r="CB6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="CG6" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="CH6" s="2" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="CI6" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="CN6" s="2" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="CR6">
         <v>9999</v>
       </c>
       <c r="CY6" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
     </row>
     <row r="7" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="Q7" s="5" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="AC7">
         <v>1</v>
@@ -7587,27 +7577,27 @@
       <c r="BV7"/>
       <c r="CL7" s="5"/>
       <c r="CU7" s="2" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
     </row>
     <row r="8" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="AC8">
         <v>1</v>
       </c>
       <c r="AT8" s="2" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="BD8">
         <v>1</v>
@@ -7615,27 +7605,27 @@
       <c r="BV8"/>
       <c r="CL8" s="5"/>
       <c r="CU8" s="2" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
     </row>
     <row r="9" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="AC9">
         <v>1</v>
       </c>
       <c r="AT9" s="2" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="BD9">
         <v>99</v>
@@ -7643,10 +7633,10 @@
       <c r="BV9"/>
       <c r="CL9" s="5"/>
       <c r="CM9" s="2" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="CN9" s="2" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="CR9">
         <v>9999</v>
@@ -7655,35 +7645,35 @@
     </row>
     <row r="10" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="I10">
         <v>1</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="Q10" s="5" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="AC10">
         <v>1</v>
       </c>
       <c r="AG10" s="2" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="AJ10" s="2"/>
       <c r="AN10">
         <v>1</v>
       </c>
       <c r="AT10" s="2" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="BD10">
         <v>99</v>
@@ -7692,7 +7682,7 @@
       <c r="CL10" s="5"/>
       <c r="CM10" s="2"/>
       <c r="CN10" s="2" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="CR10">
         <v>1</v>
@@ -7710,19 +7700,19 @@
     </row>
     <row r="11" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="I11">
         <v>1</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="AC11">
         <v>1</v>
@@ -7731,7 +7721,7 @@
         <v>1</v>
       </c>
       <c r="AG11" s="2" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="AN11">
         <v>1</v>
@@ -7741,7 +7731,7 @@
       </c>
       <c r="CL11" s="5"/>
       <c r="CN11" s="2" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="CR11">
         <v>9999</v>
@@ -7781,25 +7771,25 @@
     </row>
     <row r="13" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="G13">
         <v>3</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="L13" s="7"/>
       <c r="M13"/>
@@ -7821,13 +7811,13 @@
         <v>1</v>
       </c>
       <c r="AG13" s="2" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="AO13" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="AT13" s="2" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="AY13">
         <v>1</v>
@@ -7839,7 +7829,7 @@
         <v>1</v>
       </c>
       <c r="BO13" s="2" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="BT13">
         <v>0.2</v>
@@ -7857,13 +7847,13 @@
         <v>1</v>
       </c>
       <c r="BY13" s="8" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="BZ13" s="8"/>
       <c r="CA13"/>
       <c r="CH13" s="2"/>
       <c r="CN13" s="3" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="CO13">
         <v>1</v>
@@ -7871,22 +7861,22 @@
     </row>
     <row r="14" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="7" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="L14" s="7"/>
       <c r="M14"/>
       <c r="N14"/>
       <c r="O14" s="7" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="P14"/>
       <c r="Q14"/>
@@ -7901,10 +7891,10 @@
         <v>1</v>
       </c>
       <c r="AO14" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="AT14" s="2" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="AY14">
         <v>1</v>
@@ -7923,25 +7913,25 @@
       <c r="BZ14" s="8"/>
       <c r="CA14"/>
       <c r="CB14" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="CG14" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="CH14" s="2" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="CI14" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="CN14" s="2" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="CR14">
         <v>9999</v>
       </c>
       <c r="CY14" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
     </row>
     <row r="15" spans="1:113" x14ac:dyDescent="0.25">
@@ -7969,31 +7959,31 @@
     </row>
     <row r="16" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="G16">
         <v>3</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="M16"/>
       <c r="N16"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="5" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="R16" s="3"/>
       <c r="S16"/>
@@ -8002,7 +7992,7 @@
         <v>1</v>
       </c>
       <c r="AO16" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="AV16">
         <v>20</v>
@@ -8029,22 +8019,22 @@
         <v>3</v>
       </c>
       <c r="BY16" s="6" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="CB16" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="CG16" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="CH16" s="2" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="CI16" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="CN16" s="2" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="CO16">
         <v>0.3</v>
@@ -8058,25 +8048,25 @@
     </row>
     <row r="18" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>507</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>508</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="D18" s="17" t="s">
-        <v>511</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>512</v>
       </c>
       <c r="G18">
         <v>3</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="M18"/>
       <c r="O18"/>
@@ -8084,13 +8074,13 @@
         <v>1</v>
       </c>
       <c r="AG18" s="2" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="BD18">
         <v>1</v>
       </c>
       <c r="BO18" s="2" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="BP18" s="2"/>
       <c r="BT18">
@@ -8106,10 +8096,10 @@
         <v>1</v>
       </c>
       <c r="BY18" s="6" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="CN18" s="2" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="CO18">
         <v>-0.4</v>
@@ -8120,17 +8110,17 @@
     </row>
     <row r="19" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="J19" s="5"/>
       <c r="K19" s="5" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="L19" s="5" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="M19"/>
       <c r="O19" s="3"/>
@@ -8150,24 +8140,24 @@
       </c>
       <c r="CN19" s="2"/>
       <c r="CU19" s="2" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
     </row>
     <row r="20" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="L20" s="5" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="AC20">
         <v>2</v>
@@ -8185,24 +8175,24 @@
       <c r="BV20"/>
       <c r="CL20" s="5"/>
       <c r="CU20" s="2" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
     </row>
     <row r="21" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="L21" s="5" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="O21" s="18" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="AC21">
         <v>2</v>
@@ -8217,7 +8207,7 @@
       <c r="BV21"/>
       <c r="CL21" s="5"/>
       <c r="CN21" s="2" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="CR21">
         <v>9999</v>
@@ -8226,17 +8216,17 @@
     </row>
     <row r="22" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="J22" s="5"/>
       <c r="K22" s="5" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="L22" s="5" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="M22"/>
       <c r="O22" s="3"/>
@@ -8253,21 +8243,21 @@
       </c>
       <c r="CN22" s="2"/>
       <c r="CU22" s="2" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
     </row>
     <row r="23" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="L23" s="5" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="AC23">
@@ -8284,24 +8274,24 @@
       <c r="BV23"/>
       <c r="CL23" s="5"/>
       <c r="CU23" s="2" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
     </row>
     <row r="24" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="K24" s="5" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="L24" s="5" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="AC24">
         <v>1</v>
@@ -8311,7 +8301,7 @@
       </c>
       <c r="AG24" s="2"/>
       <c r="AT24" s="2" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="BD24">
         <v>99</v>
@@ -8319,24 +8309,24 @@
       <c r="BV24"/>
       <c r="CL24" s="5"/>
       <c r="CU24" s="2" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
     </row>
     <row r="25" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="L25" s="5" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="AC25">
         <v>1</v>
@@ -8346,7 +8336,7 @@
       </c>
       <c r="AG25" s="2"/>
       <c r="AT25" s="2" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="BD25">
         <v>99</v>
@@ -8354,7 +8344,7 @@
       <c r="BV25"/>
       <c r="CL25" s="5"/>
       <c r="CU25" s="2" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
     </row>
     <row r="26" spans="1:112" x14ac:dyDescent="0.25">
@@ -8379,16 +8369,16 @@
     </row>
     <row r="27" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="C27" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="O27" s="18"/>
       <c r="P27" s="7"/>
@@ -8396,10 +8386,10 @@
         <v>1</v>
       </c>
       <c r="AO27" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="AT27" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="AY27">
         <v>1</v>
@@ -8411,51 +8401,51 @@
         <v>3</v>
       </c>
       <c r="CB27" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="CG27" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="CH27" s="2" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="CI27" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="CN27" s="2" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="CR27">
         <v>9999</v>
       </c>
       <c r="CY27" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
     </row>
     <row r="28" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="K28" s="5" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="M28"/>
       <c r="N28"/>
       <c r="O28" s="18"/>
       <c r="Q28" s="5" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="AC28">
         <v>1</v>
       </c>
       <c r="AO28" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="AV28">
         <v>20</v>
@@ -8470,7 +8460,7 @@
       <c r="CI28" s="5"/>
       <c r="CJ28" s="5"/>
       <c r="CN28" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="CR28">
         <v>0.02</v>
@@ -8478,22 +8468,22 @@
     </row>
     <row r="29" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="K29" s="5" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="M29"/>
       <c r="N29"/>
       <c r="O29" s="18"/>
       <c r="Q29" s="5" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="AC29">
         <v>2</v>
@@ -8502,7 +8492,7 @@
         <v>20</v>
       </c>
       <c r="AX29" s="2" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="AZ29">
         <v>0.8</v>
@@ -8513,29 +8503,29 @@
       <c r="BV29"/>
       <c r="CJ29" s="5"/>
       <c r="CM29" s="2" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="CY29" s="2" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
     </row>
     <row r="30" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="K30" s="5" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="M30"/>
       <c r="O30" s="18"/>
       <c r="Q30" s="5" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="AC30">
         <v>1</v>
@@ -8559,7 +8549,7 @@
       <c r="CG30" s="2"/>
       <c r="CM30" s="2"/>
       <c r="CU30" s="2" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="DD30">
         <v>1</v>
@@ -8573,21 +8563,21 @@
     </row>
     <row r="31" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="K31" s="5" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="M31"/>
       <c r="O31" s="18"/>
       <c r="Q31" s="5" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="AC31">
         <v>1</v>
@@ -8605,7 +8595,7 @@
       </c>
       <c r="CG31" s="2"/>
       <c r="CN31" s="2" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="CR31">
         <v>0.02</v>
@@ -10090,37 +10080,37 @@
         <v>4</v>
       </c>
       <c r="E1" t="s">
+        <v>354</v>
+      </c>
+      <c r="F1" t="s">
+        <v>355</v>
+      </c>
+      <c r="G1" t="s">
+        <v>356</v>
+      </c>
+      <c r="H1" t="s">
+        <v>357</v>
+      </c>
+      <c r="I1" t="s">
         <v>358</v>
       </c>
-      <c r="F1" t="s">
+      <c r="J1" t="s">
         <v>359</v>
       </c>
-      <c r="G1" t="s">
+      <c r="L1" t="s">
         <v>360</v>
       </c>
-      <c r="H1" t="s">
+      <c r="M1" t="s">
         <v>361</v>
       </c>
-      <c r="I1" t="s">
+      <c r="N1" t="s">
         <v>362</v>
       </c>
-      <c r="J1" t="s">
+      <c r="O1" t="s">
         <v>363</v>
       </c>
-      <c r="L1" t="s">
+      <c r="P1" s="2" t="s">
         <v>364</v>
-      </c>
-      <c r="M1" t="s">
-        <v>365</v>
-      </c>
-      <c r="N1" t="s">
-        <v>366</v>
-      </c>
-      <c r="O1" t="s">
-        <v>367</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -10128,49 +10118,49 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E2" t="s">
+        <v>365</v>
+      </c>
+      <c r="F2" t="s">
+        <v>366</v>
+      </c>
+      <c r="G2" t="s">
+        <v>367</v>
+      </c>
+      <c r="H2" t="s">
+        <v>368</v>
+      </c>
+      <c r="I2" t="s">
         <v>369</v>
       </c>
-      <c r="F2" t="s">
+      <c r="J2" t="s">
         <v>370</v>
       </c>
-      <c r="G2" t="s">
+      <c r="K2" t="s">
         <v>371</v>
       </c>
-      <c r="H2" t="s">
+      <c r="L2" t="s">
+        <v>50</v>
+      </c>
+      <c r="M2" t="s">
         <v>372</v>
       </c>
-      <c r="I2" t="s">
+      <c r="N2" t="s">
         <v>373</v>
       </c>
-      <c r="J2" t="s">
+      <c r="O2" t="s">
         <v>374</v>
       </c>
-      <c r="K2" t="s">
+      <c r="P2" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="L2" t="s">
-        <v>52</v>
-      </c>
-      <c r="M2" t="s">
-        <v>376</v>
-      </c>
-      <c r="N2" t="s">
-        <v>377</v>
-      </c>
-      <c r="O2" t="s">
-        <v>378</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>379</v>
-      </c>
       <c r="Q2" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
@@ -10184,76 +10174,76 @@
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="F3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="G3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="H3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="I3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="J3" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="K3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="L3" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="M3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="N3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="O3" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="P3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="Q3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="H6">
         <v>1</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="Q7" s="2"/>
     </row>
@@ -10264,10 +10254,10 @@
     </row>
     <row r="9" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="I9" s="3">
         <v>1</v>
@@ -10278,62 +10268,62 @@
       </c>
       <c r="P9"/>
       <c r="Q9" s="3" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="H14">
         <v>1</v>
       </c>
       <c r="J14" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
     </row>
   </sheetData>
@@ -10358,7 +10348,7 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -10366,13 +10356,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C2" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="D2" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -10383,21 +10373,21 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="D3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="B4" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
     </row>
   </sheetData>
@@ -10420,7 +10410,7 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="I1" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -10428,31 +10418,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" t="s">
         <v>47</v>
       </c>
-      <c r="C2" t="s">
-        <v>49</v>
-      </c>
       <c r="D2" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F2" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="G2" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="H2" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="I2" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J2" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -10469,33 +10459,33 @@
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="G3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="H3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I3" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="B4" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="C4" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="E4">
         <v>10</v>
@@ -10504,21 +10494,21 @@
         <v>1</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="B5" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="C5" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="E5">
         <v>10</v>
@@ -10527,10 +10517,10 @@
         <v>1</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
     </row>
   </sheetData>
@@ -10557,34 +10547,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>382</v>
+      </c>
+      <c r="C1" t="s">
+        <v>383</v>
+      </c>
+      <c r="D1" t="s">
+        <v>384</v>
+      </c>
+      <c r="E1" t="s">
+        <v>385</v>
+      </c>
+      <c r="F1" t="s">
         <v>386</v>
       </c>
-      <c r="C1" t="s">
+      <c r="H1" t="s">
         <v>387</v>
       </c>
-      <c r="D1" t="s">
+      <c r="I1" t="s">
         <v>388</v>
       </c>
-      <c r="E1" t="s">
+      <c r="J1" t="s">
         <v>389</v>
       </c>
-      <c r="F1" t="s">
+      <c r="K1" t="s">
         <v>390</v>
       </c>
-      <c r="H1" t="s">
+      <c r="L1" t="s">
         <v>391</v>
-      </c>
-      <c r="I1" t="s">
-        <v>392</v>
-      </c>
-      <c r="J1" t="s">
-        <v>393</v>
-      </c>
-      <c r="K1" t="s">
-        <v>394</v>
-      </c>
-      <c r="L1" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -10592,37 +10582,37 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C2" t="s">
+        <v>393</v>
+      </c>
+      <c r="D2" t="s">
+        <v>394</v>
+      </c>
+      <c r="E2" t="s">
+        <v>395</v>
+      </c>
+      <c r="F2" t="s">
         <v>396</v>
       </c>
-      <c r="C2" t="s">
+      <c r="G2" t="s">
         <v>397</v>
       </c>
-      <c r="D2" t="s">
+      <c r="H2" t="s">
         <v>398</v>
       </c>
-      <c r="E2" t="s">
+      <c r="I2" t="s">
         <v>399</v>
       </c>
-      <c r="F2" t="s">
+      <c r="J2" t="s">
         <v>400</v>
       </c>
-      <c r="G2" t="s">
-        <v>401</v>
-      </c>
-      <c r="H2" t="s">
-        <v>402</v>
-      </c>
-      <c r="I2" t="s">
-        <v>403</v>
-      </c>
-      <c r="J2" t="s">
-        <v>404</v>
-      </c>
       <c r="K2" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="L2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -10633,34 +10623,34 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D3" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="E3" t="s">
         <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="H3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="J3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="K3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="L3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -10690,31 +10680,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2" t="s">
+        <v>402</v>
+      </c>
+      <c r="E2" t="s">
+        <v>403</v>
+      </c>
+      <c r="F2" t="s">
         <v>76</v>
       </c>
-      <c r="D2" t="s">
-        <v>406</v>
-      </c>
-      <c r="E2" t="s">
-        <v>407</v>
-      </c>
-      <c r="F2" t="s">
-        <v>78</v>
-      </c>
       <c r="G2" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="H2" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="I2" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="J2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -10731,22 +10721,22 @@
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="F3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="G3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="H3" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="I3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="J3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -10777,28 +10767,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>414</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -10806,28 +10796,28 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>422</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -10835,10 +10825,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>2</v>
@@ -10861,28 +10851,28 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="C4" s="1">
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>441</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>445</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Diy优胜/萃儿.xlsx
+++ b/Excel/Diy优胜/萃儿.xlsx
@@ -24,9 +24,9 @@
     <sheet name="SpineData" sheetId="12" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="OLE_LINK2" localSheetId="2">SkillData!$E$13</definedName>
+    <definedName name="OLE_LINK2" localSheetId="2">'SkillData'!$E$13</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -326,7 +326,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="942" uniqueCount="559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="560">
   <si>
     <t>Id</t>
   </si>
@@ -349,6 +349,9 @@
     <t>模型大小倍率</t>
   </si>
   <si>
+    <t>模型偏移</t>
+  </si>
+  <si>
     <t>精英化</t>
   </si>
   <si>
@@ -415,6 +418,12 @@
     <t>可选技能</t>
   </si>
   <si>
+    <t>血条</t>
+  </si>
+  <si>
+    <t>技力条</t>
+  </si>
+  <si>
     <t>高度</t>
   </si>
   <si>
@@ -484,6 +493,9 @@
     <t>ModelScale</t>
   </si>
   <si>
+    <t>ModelOffset</t>
+  </si>
+  <si>
     <t>engName</t>
   </si>
   <si>
@@ -580,6 +592,9 @@
     <t>HpBarType</t>
   </si>
   <si>
+    <t>SpBarType</t>
+  </si>
+  <si>
     <t>Height</t>
   </si>
   <si>
@@ -685,6 +700,9 @@
     <t>float</t>
   </si>
   <si>
+    <t>UnityEngine.Vector3</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -721,6 +739,12 @@
     <t>萃儿1,萃儿2,萃儿3</t>
   </si>
   <si>
+    <t>小型:蓝</t>
+  </si>
+  <si>
+    <t>小型:绿</t>
+  </si>
+  <si>
     <t>高台位</t>
   </si>
   <si>
@@ -772,12 +796,18 @@
     <t>辅助</t>
   </si>
   <si>
+    <t>{"Color":"#96C24E","Alpha":0.5,"Size":0.8}</t>
+  </si>
+  <si>
     <t>萃蔓1</t>
   </si>
   <si>
     <t>萃蔓效果,萃蔓无敌</t>
   </si>
   <si>
+    <t>{"Color":"#96C24E","Alpha":0.25,"Size":0.8}</t>
+  </si>
+  <si>
     <t>#备注</t>
   </si>
   <si>
@@ -1897,9 +1927,6 @@
     <t>ForwordDirection</t>
   </si>
   <si>
-    <t>UnityEngine.Vector3</t>
-  </si>
-  <si>
     <t>Description</t>
   </si>
   <si>
@@ -1979,45 +2006,14 @@
   </si>
   <si>
     <t>/Spine/萃儿/back/char_4122_grabds_yun_3.skel.bytes</t>
-  </si>
-  <si>
-    <t>血条</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>技力条</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SpBarType</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>小型:蓝</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>小型:绿</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"Color":"#96C24E","Alpha":0.5,"Size":0.8}</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"Color":"#96C24E","Alpha":0.25,"Size":0.8}</t>
-    <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2029,34 +2025,6 @@
       <color theme="1"/>
       <name val="宋体"/>
       <family val="3"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -2085,23 +2053,20 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+  <cellXfs count="3">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1" applyProtection="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="常规 2" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2406,948 +2371,1222 @@
   <dimension ref="A2:B4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="9" customWidth="1"/>
+    <col min="1" max="2" width="9" customWidth="1" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="4">
+      <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>4</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:BU7"/>
+  <dimension ref="A1:BV7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.58203125" customWidth="1"/>
-    <col min="2" max="3" width="9" customWidth="1"/>
-    <col min="4" max="5" width="8.58203125" customWidth="1"/>
-    <col min="6" max="6" width="19.58203125" customWidth="1"/>
-    <col min="7" max="7" width="8.25" customWidth="1"/>
-    <col min="8" max="10" width="9" customWidth="1"/>
-    <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="4.08203125" customWidth="1"/>
-    <col min="13" max="13" width="5.58203125" customWidth="1"/>
-    <col min="14" max="14" width="4" customWidth="1"/>
-    <col min="15" max="15" width="7.75" customWidth="1"/>
-    <col min="16" max="16" width="10.83203125" customWidth="1"/>
-    <col min="17" max="18" width="3.83203125" customWidth="1"/>
-    <col min="19" max="20" width="3.58203125" customWidth="1"/>
-    <col min="21" max="21" width="10.25" customWidth="1"/>
-    <col min="22" max="22" width="9.58203125" customWidth="1"/>
-    <col min="23" max="23" width="10.75" customWidth="1"/>
-    <col min="24" max="24" width="12.83203125" customWidth="1"/>
-    <col min="25" max="25" width="13.08203125" customWidth="1"/>
-    <col min="26" max="26" width="10.75" customWidth="1"/>
-    <col min="27" max="28" width="9" customWidth="1"/>
-    <col min="29" max="29" width="8" customWidth="1"/>
-    <col min="30" max="30" width="17.08203125" customWidth="1"/>
-    <col min="31" max="32" width="9" customWidth="1"/>
-    <col min="33" max="33" width="9.75" customWidth="1"/>
-    <col min="34" max="34" width="7.83203125" customWidth="1"/>
-    <col min="35" max="35" width="15.83203125" customWidth="1"/>
-    <col min="36" max="36" width="13.83203125" customWidth="1"/>
-    <col min="37" max="37" width="63.75" customWidth="1"/>
-    <col min="38" max="38" width="20.1640625" customWidth="1"/>
-    <col min="39" max="40" width="9.83203125" customWidth="1"/>
-    <col min="41" max="44" width="9" customWidth="1"/>
-    <col min="45" max="45" width="12.5" customWidth="1"/>
-    <col min="46" max="51" width="9" customWidth="1"/>
-    <col min="52" max="52" width="24.33203125" customWidth="1"/>
-    <col min="53" max="53" width="9" customWidth="1"/>
-    <col min="54" max="54" width="17.75" customWidth="1"/>
-    <col min="55" max="55" width="7.83203125" customWidth="1"/>
-    <col min="56" max="57" width="9" customWidth="1"/>
-    <col min="58" max="58" width="24.25" customWidth="1"/>
-    <col min="59" max="59" width="13.25" customWidth="1"/>
-    <col min="60" max="60" width="16.08203125" customWidth="1"/>
-    <col min="61" max="61" width="8" customWidth="1"/>
-    <col min="62" max="65" width="9" customWidth="1"/>
-    <col min="66" max="66" width="39.58203125" customWidth="1"/>
-    <col min="67" max="67" width="14" customWidth="1"/>
-    <col min="68" max="68" width="14.83203125" customWidth="1"/>
-    <col min="69" max="72" width="14" customWidth="1"/>
-    <col min="73" max="73" width="19.1640625" customWidth="1"/>
+    <col min="1" max="1" width="22.58203125" customWidth="1" style="2"/>
+    <col min="2" max="2" width="9" customWidth="1" style="2"/>
+    <col min="3" max="3" width="9" customWidth="1" style="2"/>
+    <col min="4" max="4" width="8.58203125" customWidth="1" style="2"/>
+    <col min="5" max="5" width="8.58203125" customWidth="1" style="2"/>
+    <col min="6" max="6" width="19.58203125" customWidth="1" style="2"/>
+    <col min="7" max="7" width="8.25" customWidth="1" style="2"/>
+    <col min="8" max="8" width="9" customWidth="1" style="2"/>
+    <col min="9" max="9" width="9" customWidth="1" style="2"/>
+    <col min="10" max="10" width="9" customWidth="1" style="2"/>
+    <col min="11" max="11" width="9" customWidth="1" style="2"/>
+    <col min="12" max="12" width="6" customWidth="1" style="2"/>
+    <col min="13" max="13" width="4.08203125" customWidth="1" style="2"/>
+    <col min="14" max="14" width="5.58203125" customWidth="1" style="2"/>
+    <col min="15" max="15" width="4" customWidth="1" style="2"/>
+    <col min="16" max="16" width="7.75" customWidth="1" style="2"/>
+    <col min="17" max="17" width="10.83203125" customWidth="1" style="2"/>
+    <col min="18" max="18" width="3.83203125" customWidth="1" style="2"/>
+    <col min="19" max="19" width="3.83203125" customWidth="1" style="2"/>
+    <col min="20" max="20" width="3.58203125" customWidth="1" style="2"/>
+    <col min="21" max="21" width="3.58203125" customWidth="1" style="2"/>
+    <col min="22" max="22" width="10.25" customWidth="1" style="2"/>
+    <col min="23" max="23" width="9.58203125" customWidth="1" style="2"/>
+    <col min="24" max="24" width="10.75" customWidth="1" style="2"/>
+    <col min="25" max="25" width="12.83203125" customWidth="1" style="2"/>
+    <col min="26" max="26" width="13.08203125" customWidth="1" style="2"/>
+    <col min="27" max="27" width="10.75" customWidth="1" style="2"/>
+    <col min="28" max="28" width="9" customWidth="1" style="2"/>
+    <col min="29" max="29" width="9" customWidth="1" style="2"/>
+    <col min="30" max="30" width="8" customWidth="1" style="2"/>
+    <col min="31" max="31" width="17.08203125" customWidth="1" style="2"/>
+    <col min="32" max="32" width="9" customWidth="1" style="2"/>
+    <col min="33" max="33" width="9" customWidth="1" style="2"/>
+    <col min="34" max="34" width="9.75" customWidth="1" style="2"/>
+    <col min="35" max="35" width="7.83203125" customWidth="1" style="2"/>
+    <col min="36" max="36" width="15.83203125" customWidth="1" style="2"/>
+    <col min="37" max="37" width="13.83203125" customWidth="1" style="2"/>
+    <col min="38" max="38" width="63.75" customWidth="1" style="2"/>
+    <col min="39" max="39" width="20.1640625" customWidth="1" style="2"/>
+    <col min="40" max="40" width="9.83203125" customWidth="1" style="2"/>
+    <col min="41" max="41" width="9.83203125" customWidth="1" style="2"/>
+    <col min="42" max="42" width="9" customWidth="1" style="2"/>
+    <col min="43" max="43" width="9" customWidth="1" style="2"/>
+    <col min="44" max="44" width="9" customWidth="1" style="2"/>
+    <col min="45" max="45" width="9" customWidth="1" style="2"/>
+    <col min="46" max="46" width="12.5" customWidth="1" style="2"/>
+    <col min="47" max="47" width="9" customWidth="1" style="2"/>
+    <col min="48" max="48" width="9" customWidth="1" style="2"/>
+    <col min="49" max="49" width="9" customWidth="1" style="2"/>
+    <col min="50" max="50" width="9" customWidth="1" style="2"/>
+    <col min="51" max="51" width="9" customWidth="1" style="2"/>
+    <col min="52" max="52" width="9" customWidth="1" style="2"/>
+    <col min="53" max="53" width="24.33203125" customWidth="1" style="2"/>
+    <col min="54" max="54" width="9" customWidth="1" style="2"/>
+    <col min="55" max="55" width="17.75" customWidth="1" style="2"/>
+    <col min="56" max="56" width="7.83203125" customWidth="1" style="2"/>
+    <col min="57" max="57" width="9" customWidth="1" style="2"/>
+    <col min="58" max="58" width="9" customWidth="1" style="2"/>
+    <col min="59" max="59" width="24.25" customWidth="1" style="2"/>
+    <col min="60" max="60" width="13.25" customWidth="1" style="2"/>
+    <col min="61" max="61" width="16.08203125" customWidth="1" style="2"/>
+    <col min="62" max="62" width="8" customWidth="1" style="2"/>
+    <col min="63" max="63" width="9" customWidth="1" style="2"/>
+    <col min="64" max="64" width="9" customWidth="1" style="2"/>
+    <col min="65" max="65" width="9" customWidth="1" style="2"/>
+    <col min="66" max="66" width="9" customWidth="1" style="2"/>
+    <col min="67" max="67" width="39.58203125" customWidth="1" style="2"/>
+    <col min="68" max="68" width="14" customWidth="1" style="2"/>
+    <col min="69" max="69" width="14.83203125" customWidth="1" style="2"/>
+    <col min="70" max="70" width="14" customWidth="1" style="2"/>
+    <col min="71" max="71" width="14" customWidth="1" style="2"/>
+    <col min="72" max="72" width="14" customWidth="1" style="2"/>
+    <col min="73" max="73" width="14" customWidth="1" style="2"/>
+    <col min="74" max="74" width="19.1640625" customWidth="1" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="D1" t="s">
+    <row r="1">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="F1" s="2"/>
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J1" t="s">
+      <c r="I1" s="2"/>
+      <c r="J1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="M1" t="s">
+      <c r="L1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="O1" t="s">
+      <c r="M1" s="2"/>
+      <c r="N1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="O1" s="2"/>
+      <c r="P1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="S1" t="s">
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="U1" t="s">
+      <c r="S1" s="2"/>
+      <c r="T1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="V1" t="s">
+      <c r="U1" s="2"/>
+      <c r="V1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="X1" t="s">
+      <c r="W1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="X1" s="2"/>
+      <c r="Y1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="Z1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AA1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AB1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AC1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AD1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AE1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AF1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AG1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AH1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AI1" s="2"/>
+      <c r="AJ1" s="2"/>
+      <c r="AK1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AL1" s="2" t="s">
         <v>28</v>
       </c>
       <c r="AM1" s="2" t="s">
-        <v>551</v>
+        <v>29</v>
       </c>
       <c r="AN1" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="AO1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AP1" t="s">
         <v>30</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AO1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AP1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AQ1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AR1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AS1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AT1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AU1" s="2"/>
+      <c r="AV1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AW1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="AX1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="AY1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="AZ1" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BA1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BB1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BC1" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BD1" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BE1" s="2"/>
+      <c r="BF1" s="2"/>
+      <c r="BG1" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BH1" s="2" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="2" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="BI1" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="BJ1" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="BK1" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="BL1" s="2"/>
+      <c r="BM1" s="2"/>
+      <c r="BN1" s="2"/>
+      <c r="BO1" s="2"/>
+      <c r="BP1" s="2"/>
+      <c r="BQ1" s="2"/>
+      <c r="BR1" s="2"/>
+      <c r="BS1" s="2"/>
+      <c r="BT1" s="2"/>
+      <c r="BU1" s="2"/>
+      <c r="BV1" s="2"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="B2" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="H2" t="s">
+      <c r="C2" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="I2" t="s">
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="J2" t="s">
+      <c r="G2" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="K2" t="s">
+      <c r="H2" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="L2" t="s">
+      <c r="I2" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="M2" t="s">
+      <c r="J2" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="N2" t="s">
+      <c r="K2" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="O2" t="s">
+      <c r="L2" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="P2" t="s">
+      <c r="M2" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="N2" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="R2" t="s">
+      <c r="O2" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="S2" t="s">
+      <c r="P2" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="T2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="U2" t="s">
+      <c r="R2" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="V2" t="s">
+      <c r="S2" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="W2" t="s">
+      <c r="T2" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="X2" t="s">
+      <c r="U2" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="V2" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="W2" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="X2" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="Y2" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="Z2" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AA2" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AE2" t="s">
+      <c r="AB2" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AC2" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="AG2" t="s">
+      <c r="AD2" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="AH2" t="s">
+      <c r="AE2" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="AI2" t="s">
+      <c r="AF2" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="AJ2" t="s">
+      <c r="AG2" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="AK2" t="s">
+      <c r="AH2" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="AL2" t="s">
+      <c r="AI2" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="AM2" s="1" t="s">
+      <c r="AJ2" s="2" t="s">
         <v>83</v>
       </c>
+      <c r="AK2" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AL2" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="AM2" s="2" t="s">
+        <v>86</v>
+      </c>
       <c r="AN2" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="AO2" t="s">
-        <v>84</v>
-      </c>
-      <c r="AP2" t="s">
-        <v>85</v>
-      </c>
-      <c r="AQ2" t="s">
-        <v>86</v>
-      </c>
-      <c r="AR2" t="s">
         <v>87</v>
       </c>
-      <c r="AS2" t="s">
+      <c r="AO2" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="AT2" t="s">
+      <c r="AP2" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="AU2" t="s">
+      <c r="AQ2" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="AV2" t="s">
+      <c r="AR2" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="AW2" t="s">
+      <c r="AS2" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="AX2" t="s">
+      <c r="AT2" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="AY2" t="s">
+      <c r="AU2" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="AZ2" t="s">
+      <c r="AV2" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="BA2" t="s">
+      <c r="AW2" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="BB2" t="s">
+      <c r="AX2" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="BC2" t="s">
+      <c r="AY2" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="BD2" t="s">
+      <c r="AZ2" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="BE2" t="s">
+      <c r="BA2" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="BF2" t="s">
+      <c r="BB2" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="BG2" t="s">
+      <c r="BC2" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="BH2" t="s">
+      <c r="BD2" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="BI2" t="s">
+      <c r="BE2" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="BJ2" t="s">
+      <c r="BF2" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="BK2" t="s">
+      <c r="BG2" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="BL2" t="s">
+      <c r="BH2" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="BM2" t="s">
+      <c r="BI2" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="BN2" t="s">
+      <c r="BJ2" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="BO2" t="s">
+      <c r="BK2" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="BP2" t="s">
+      <c r="BL2" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="BQ2" t="s">
+      <c r="BM2" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="BR2" t="s">
+      <c r="BN2" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="BS2" t="s">
+      <c r="BO2" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="BT2" t="s">
+      <c r="BP2" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="BU2" t="s">
+      <c r="BQ2" s="2" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="3" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="BR2" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="BS2" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="BT2" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="BU2" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="BV2" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" t="s">
-        <v>117</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="C3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G3" t="s">
-        <v>118</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="G3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="I3" t="s">
-        <v>119</v>
-      </c>
-      <c r="J3" t="s">
-        <v>119</v>
-      </c>
-      <c r="K3" t="s">
-        <v>119</v>
-      </c>
-      <c r="L3" t="s">
-        <v>119</v>
-      </c>
-      <c r="M3" t="s">
-        <v>119</v>
-      </c>
-      <c r="N3" t="s">
-        <v>119</v>
-      </c>
-      <c r="O3" t="s">
-        <v>119</v>
-      </c>
-      <c r="P3" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>119</v>
-      </c>
-      <c r="R3" t="s">
-        <v>119</v>
-      </c>
-      <c r="S3" t="s">
-        <v>119</v>
-      </c>
-      <c r="T3" t="s">
-        <v>119</v>
-      </c>
-      <c r="U3" t="s">
-        <v>118</v>
-      </c>
-      <c r="V3" t="s">
-        <v>119</v>
-      </c>
-      <c r="W3" t="s">
-        <v>119</v>
-      </c>
-      <c r="X3" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>118</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>118</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>119</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>118</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>119</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AE3" t="s">
+      <c r="J3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AA3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AB3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AD3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AF3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="AF3" t="s">
-        <v>119</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>119</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>119</v>
-      </c>
-      <c r="AI3" t="s">
+      <c r="AG3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="AH3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="AJ3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="AJ3" t="s">
+      <c r="AK3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="AK3" t="s">
-        <v>120</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>120</v>
+      <c r="AL3" s="2" t="s">
+        <v>126</v>
       </c>
       <c r="AM3" s="2" t="s">
-        <v>554</v>
+        <v>126</v>
       </c>
       <c r="AN3" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="AO3" t="s">
-        <v>118</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>121</v>
-      </c>
-      <c r="AQ3" t="s">
-        <v>119</v>
-      </c>
-      <c r="AR3" t="s">
-        <v>118</v>
-      </c>
-      <c r="AS3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AU3" t="s">
-        <v>118</v>
-      </c>
-      <c r="AV3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AW3" t="s">
-        <v>119</v>
-      </c>
-      <c r="AX3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AO3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AP3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AQ3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="AR3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="AS3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AT3" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="AY3" t="s">
-        <v>118</v>
-      </c>
-      <c r="AZ3" t="s">
+      <c r="AU3" s="2"/>
+      <c r="AV3" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="BA3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BB3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BC3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BD3" t="s">
-        <v>124</v>
-      </c>
-      <c r="BE3" t="s">
+      <c r="AW3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AX3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="AY3" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="AZ3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="BA3" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="BB3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BC3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BD3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="BE3" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="BF3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="BF3" t="s">
+      <c r="BG3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="BG3" t="s">
+      <c r="BH3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="BH3" t="s">
+      <c r="BI3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="BI3" t="s">
+      <c r="BJ3" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="BK3" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="BJ3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BK3" t="s">
+      <c r="BL3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="BL3" t="s">
-        <v>121</v>
-      </c>
-      <c r="BM3" t="s">
+      <c r="BM3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="BN3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="BN3" t="s">
-        <v>126</v>
-      </c>
-      <c r="BO3" t="s">
-        <v>121</v>
-      </c>
-      <c r="BP3" t="s">
-        <v>121</v>
-      </c>
-      <c r="BQ3" t="s">
-        <v>121</v>
-      </c>
-      <c r="BR3" t="s">
-        <v>121</v>
-      </c>
-      <c r="BS3" t="s">
-        <v>121</v>
-      </c>
-      <c r="BT3" t="s">
-        <v>121</v>
-      </c>
-      <c r="BU3" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="5" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="BO3" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="BP3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="BQ3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="BR3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="BS3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="BT3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="BU3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="BV3" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+      <c r="T4" s="2"/>
+      <c r="U4" s="2"/>
+      <c r="V4" s="2"/>
+      <c r="W4" s="2"/>
+      <c r="X4" s="2"/>
+      <c r="Y4" s="2"/>
+      <c r="Z4" s="2"/>
+      <c r="AA4" s="2"/>
+      <c r="AB4" s="2"/>
+      <c r="AC4" s="2"/>
+      <c r="AD4" s="2"/>
+      <c r="AE4" s="2"/>
+      <c r="AF4" s="2"/>
+      <c r="AG4" s="2"/>
+      <c r="AH4" s="2"/>
+      <c r="AI4" s="2"/>
+      <c r="AJ4" s="2"/>
+      <c r="AK4" s="2"/>
+      <c r="AL4" s="2"/>
+      <c r="AM4" s="2"/>
+      <c r="AN4" s="2"/>
+      <c r="AO4" s="2"/>
+      <c r="AP4" s="2"/>
+      <c r="AQ4" s="2"/>
+      <c r="AR4" s="2"/>
+      <c r="AS4" s="2"/>
+      <c r="AT4" s="2"/>
+      <c r="AU4" s="2"/>
+      <c r="AV4" s="2"/>
+      <c r="AW4" s="2"/>
+      <c r="AX4" s="2"/>
+      <c r="AY4" s="2"/>
+      <c r="AZ4" s="2"/>
+      <c r="BA4" s="2"/>
+      <c r="BB4" s="2"/>
+      <c r="BC4" s="2"/>
+      <c r="BD4" s="2"/>
+      <c r="BE4" s="2"/>
+      <c r="BF4" s="2"/>
+      <c r="BG4" s="2"/>
+      <c r="BH4" s="2"/>
+      <c r="BI4" s="2"/>
+      <c r="BJ4" s="2"/>
+      <c r="BK4" s="2"/>
+      <c r="BL4" s="2"/>
+      <c r="BM4" s="2"/>
+      <c r="BN4" s="2"/>
+      <c r="BO4" s="2"/>
+      <c r="BP4" s="2"/>
+      <c r="BQ4" s="2"/>
+      <c r="BR4" s="2"/>
+      <c r="BS4" s="2"/>
+      <c r="BT4" s="2"/>
+      <c r="BU4" s="2"/>
+      <c r="BV4" s="2"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
-        <v>127</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="B5" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="I5">
+      <c r="G5" s="2">
+        <v>1</v>
+      </c>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2">
         <v>2</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="2">
         <v>90</v>
       </c>
-      <c r="K5">
+      <c r="L5" s="2">
         <v>1949</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="2"/>
+      <c r="N5" s="2">
         <v>520</v>
       </c>
-      <c r="O5">
+      <c r="O5" s="2"/>
+      <c r="P5" s="2">
         <v>180</v>
       </c>
-      <c r="Q5">
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2">
         <v>0</v>
       </c>
-      <c r="S5">
+      <c r="S5" s="2"/>
+      <c r="T5" s="2">
         <v>18</v>
       </c>
-      <c r="U5">
+      <c r="U5" s="2"/>
+      <c r="V5" s="2">
         <v>0.5</v>
       </c>
-      <c r="V5">
+      <c r="W5" s="2">
         <v>70</v>
       </c>
-      <c r="Y5">
+      <c r="X5" s="2"/>
+      <c r="Y5" s="2"/>
+      <c r="Z5" s="2">
         <v>0.05</v>
       </c>
-      <c r="Z5">
+      <c r="AA5" s="2">
         <v>1.6</v>
       </c>
-      <c r="AC5">
-        <v>1</v>
-      </c>
-      <c r="AI5" t="s">
+      <c r="AB5" s="2"/>
+      <c r="AC5" s="2"/>
+      <c r="AD5" s="2">
+        <v>1</v>
+      </c>
+      <c r="AE5" s="2"/>
+      <c r="AF5" s="2"/>
+      <c r="AG5" s="2"/>
+      <c r="AH5" s="2"/>
+      <c r="AI5" s="2"/>
+      <c r="AJ5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="AJ5" t="s">
-        <v>128</v>
-      </c>
-      <c r="AK5" t="s">
-        <v>129</v>
-      </c>
-      <c r="AL5" t="s">
-        <v>130</v>
+      <c r="AK5" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="AL5" s="2" t="s">
+        <v>135</v>
       </c>
       <c r="AM5" s="2" t="s">
-        <v>555</v>
+        <v>136</v>
       </c>
       <c r="AN5" s="2" t="s">
-        <v>556</v>
-      </c>
-      <c r="AP5" t="s">
-        <v>131</v>
-      </c>
-      <c r="AQ5">
-        <v>1</v>
-      </c>
-      <c r="AR5">
+        <v>137</v>
+      </c>
+      <c r="AO5" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="AP5" s="2"/>
+      <c r="AQ5" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="AR5" s="2">
+        <v>1</v>
+      </c>
+      <c r="AS5" s="2">
         <v>0.5</v>
       </c>
-      <c r="AY5">
+      <c r="AT5" s="2"/>
+      <c r="AU5" s="2"/>
+      <c r="AV5" s="2"/>
+      <c r="AW5" s="2"/>
+      <c r="AX5" s="2"/>
+      <c r="AY5" s="2"/>
+      <c r="AZ5" s="2">
         <v>0.25</v>
       </c>
-      <c r="BD5" t="s">
-        <v>132</v>
-      </c>
-      <c r="BF5" t="s">
-        <v>133</v>
-      </c>
-      <c r="BG5" t="s">
+      <c r="BA5" s="2"/>
+      <c r="BB5" s="2"/>
+      <c r="BC5" s="2"/>
+      <c r="BD5" s="2"/>
+      <c r="BE5" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="BF5" s="2"/>
+      <c r="BG5" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="BH5" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="BI5" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="BJ5" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="BK5" s="2">
+        <v>6</v>
+      </c>
+      <c r="BL5" s="2"/>
+      <c r="BM5" s="2"/>
+      <c r="BN5" s="2"/>
+      <c r="BO5" s="2"/>
+      <c r="BP5" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="BQ5" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="BR5" s="2"/>
+      <c r="BS5" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="BT5" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="BU5" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="BV5" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="G6" s="2">
+        <v>1</v>
+      </c>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2">
+        <v>2</v>
+      </c>
+      <c r="K6" s="2">
+        <v>90</v>
+      </c>
+      <c r="L6" s="2">
+        <v>100</v>
+      </c>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2">
+        <v>0</v>
+      </c>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2">
+        <v>0</v>
+      </c>
+      <c r="S6" s="2"/>
+      <c r="T6" s="2">
+        <v>0</v>
+      </c>
+      <c r="U6" s="2"/>
+      <c r="V6" s="2">
+        <v>0</v>
+      </c>
+      <c r="W6" s="2">
+        <v>0</v>
+      </c>
+      <c r="X6" s="2"/>
+      <c r="Y6" s="2"/>
+      <c r="Z6" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="AA6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="2"/>
+      <c r="AD6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="2"/>
+      <c r="AF6" s="2"/>
+      <c r="AG6" s="2"/>
+      <c r="AH6" s="2"/>
+      <c r="AI6" s="2"/>
+      <c r="AJ6" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="AK6" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="BH5" t="s">
-        <v>135</v>
-      </c>
-      <c r="BI5" t="s">
-        <v>136</v>
-      </c>
-      <c r="BJ5">
-        <v>6</v>
-      </c>
-      <c r="BO5" t="s">
-        <v>137</v>
-      </c>
-      <c r="BP5" t="s">
-        <v>138</v>
-      </c>
-      <c r="BR5" t="s">
-        <v>139</v>
-      </c>
-      <c r="BS5" t="s">
-        <v>139</v>
-      </c>
-      <c r="BT5" t="s">
-        <v>140</v>
-      </c>
-      <c r="BU5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>141</v>
-      </c>
-      <c r="B6" t="s">
-        <v>142</v>
-      </c>
-      <c r="F6" t="s">
-        <v>143</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="I6">
+      <c r="AL6" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="AM6" s="2"/>
+      <c r="AN6" s="2"/>
+      <c r="AO6" s="2"/>
+      <c r="AP6" s="2"/>
+      <c r="AQ6" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="AR6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AS6" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="AT6" s="2">
+        <v>1</v>
+      </c>
+      <c r="AU6" s="2"/>
+      <c r="AV6" s="2"/>
+      <c r="AW6" s="2"/>
+      <c r="AX6" s="2"/>
+      <c r="AY6" s="2"/>
+      <c r="AZ6" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="BA6" s="2"/>
+      <c r="BB6" s="2"/>
+      <c r="BC6" s="2"/>
+      <c r="BD6" s="2"/>
+      <c r="BE6" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="BF6" s="2"/>
+      <c r="BG6" s="2"/>
+      <c r="BH6" s="2"/>
+      <c r="BI6" s="2"/>
+      <c r="BJ6" s="2"/>
+      <c r="BK6" s="2"/>
+      <c r="BL6" s="2"/>
+      <c r="BM6" s="2"/>
+      <c r="BN6" s="2"/>
+      <c r="BO6" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="BP6" s="2"/>
+      <c r="BQ6" s="2"/>
+      <c r="BR6" s="2"/>
+      <c r="BS6" s="2"/>
+      <c r="BT6" s="2"/>
+      <c r="BU6" s="2"/>
+      <c r="BV6" s="2"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="G7" s="2">
+        <v>1</v>
+      </c>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2">
         <v>2</v>
       </c>
-      <c r="J6">
+      <c r="K7" s="2">
         <v>90</v>
       </c>
-      <c r="K6">
+      <c r="L7" s="2">
         <v>100</v>
       </c>
-      <c r="M6">
+      <c r="M7" s="2"/>
+      <c r="N7" s="2">
         <v>0</v>
       </c>
-      <c r="O6">
+      <c r="O7" s="2"/>
+      <c r="P7" s="2">
         <v>0</v>
       </c>
-      <c r="Q6">
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2">
         <v>0</v>
       </c>
-      <c r="S6">
+      <c r="S7" s="2"/>
+      <c r="T7" s="2">
         <v>0</v>
       </c>
-      <c r="U6">
+      <c r="U7" s="2"/>
+      <c r="V7" s="2">
         <v>0</v>
       </c>
-      <c r="V6">
+      <c r="W7" s="2">
         <v>0</v>
       </c>
-      <c r="Y6">
+      <c r="X7" s="2"/>
+      <c r="Y7" s="2"/>
+      <c r="Z7" s="2">
         <v>0.05</v>
       </c>
-      <c r="Z6">
+      <c r="AA7" s="2">
         <v>0</v>
       </c>
-      <c r="AA6">
+      <c r="AB7" s="2">
         <v>0</v>
       </c>
-      <c r="AC6">
+      <c r="AC7" s="2"/>
+      <c r="AD7" s="2">
         <v>0</v>
       </c>
-      <c r="AI6" t="s">
-        <v>144</v>
-      </c>
-      <c r="AJ6" t="s">
-        <v>128</v>
-      </c>
-      <c r="AK6" t="s">
-        <v>145</v>
-      </c>
-      <c r="AP6" t="s">
-        <v>146</v>
-      </c>
-      <c r="AQ6">
+      <c r="AE7" s="2"/>
+      <c r="AF7" s="2"/>
+      <c r="AG7" s="2"/>
+      <c r="AH7" s="2"/>
+      <c r="AI7" s="2"/>
+      <c r="AJ7" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="AK7" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="AL7" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="AM7" s="2"/>
+      <c r="AN7" s="2"/>
+      <c r="AO7" s="2"/>
+      <c r="AP7" s="2"/>
+      <c r="AQ7" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="AR7" s="2">
         <v>0</v>
       </c>
-      <c r="AR6">
+      <c r="AS7" s="2">
         <v>0.5</v>
       </c>
-      <c r="AS6">
-        <v>1</v>
-      </c>
-      <c r="AY6">
+      <c r="AT7" s="2">
+        <v>1</v>
+      </c>
+      <c r="AU7" s="2"/>
+      <c r="AV7" s="2"/>
+      <c r="AW7" s="2"/>
+      <c r="AX7" s="2"/>
+      <c r="AY7" s="2"/>
+      <c r="AZ7" s="2">
         <v>0.25</v>
       </c>
-      <c r="BD6" t="s">
-        <v>147</v>
-      </c>
-      <c r="BN6" s="3" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="7" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>148</v>
-      </c>
-      <c r="B7" t="s">
-        <v>142</v>
-      </c>
-      <c r="F7" t="s">
-        <v>143</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>2</v>
-      </c>
-      <c r="J7">
-        <v>90</v>
-      </c>
-      <c r="K7">
-        <v>100</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>0</v>
-      </c>
-      <c r="V7">
-        <v>0</v>
-      </c>
-      <c r="Y7">
-        <v>0.05</v>
-      </c>
-      <c r="Z7">
-        <v>0</v>
-      </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AC7">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="s">
-        <v>144</v>
-      </c>
-      <c r="AJ7" t="s">
-        <v>128</v>
-      </c>
-      <c r="AK7" t="s">
-        <v>149</v>
-      </c>
-      <c r="AP7" t="s">
-        <v>146</v>
-      </c>
-      <c r="AQ7">
-        <v>0</v>
-      </c>
-      <c r="AR7">
-        <v>0.5</v>
-      </c>
-      <c r="AS7">
-        <v>1</v>
-      </c>
-      <c r="AY7">
-        <v>0.25</v>
-      </c>
-      <c r="BD7" t="s">
-        <v>147</v>
-      </c>
-      <c r="BN7" s="3" t="s">
-        <v>558</v>
-      </c>
+      <c r="BA7" s="2"/>
+      <c r="BB7" s="2"/>
+      <c r="BC7" s="2"/>
+      <c r="BD7" s="2"/>
+      <c r="BE7" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="BF7" s="2"/>
+      <c r="BG7" s="2"/>
+      <c r="BH7" s="2"/>
+      <c r="BI7" s="2"/>
+      <c r="BJ7" s="2"/>
+      <c r="BK7" s="2"/>
+      <c r="BL7" s="2"/>
+      <c r="BM7" s="2"/>
+      <c r="BN7" s="2"/>
+      <c r="BO7" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="BP7" s="2"/>
+      <c r="BQ7" s="2"/>
+      <c r="BR7" s="2"/>
+      <c r="BS7" s="2"/>
+      <c r="BT7" s="2"/>
+      <c r="BU7" s="2"/>
+      <c r="BV7" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -3357,2076 +3596,2076 @@
   <dimension ref="A1:DI689"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.08203125" customWidth="1"/>
-    <col min="2" max="2" width="15.58203125" customWidth="1"/>
-    <col min="3" max="3" width="7.75" customWidth="1"/>
-    <col min="4" max="4" width="16.58203125" customWidth="1"/>
-    <col min="5" max="5" width="16.83203125" customWidth="1"/>
-    <col min="6" max="6" width="31.33203125" customWidth="1"/>
-    <col min="7" max="7" width="7.33203125" customWidth="1"/>
-    <col min="8" max="8" width="20.58203125" customWidth="1"/>
-    <col min="9" max="9" width="10.75" customWidth="1"/>
-    <col min="10" max="10" width="15.75" customWidth="1"/>
-    <col min="11" max="13" width="8.33203125" customWidth="1"/>
-    <col min="14" max="14" width="11.75" customWidth="1"/>
-    <col min="15" max="15" width="13.08203125" customWidth="1"/>
-    <col min="16" max="16" width="11.58203125" customWidth="1"/>
-    <col min="17" max="17" width="21.5" customWidth="1"/>
-    <col min="18" max="18" width="19.83203125" customWidth="1"/>
-    <col min="19" max="19" width="16.58203125" customWidth="1"/>
-    <col min="20" max="20" width="19.08203125" customWidth="1"/>
-    <col min="21" max="21" width="18.33203125" customWidth="1"/>
-    <col min="22" max="22" width="17.75" customWidth="1"/>
-    <col min="23" max="23" width="8.33203125" customWidth="1"/>
-    <col min="24" max="24" width="18.5" customWidth="1"/>
-    <col min="25" max="25" width="16.58203125" customWidth="1"/>
-    <col min="26" max="26" width="10.6640625" customWidth="1"/>
-    <col min="27" max="27" width="8.33203125" customWidth="1"/>
-    <col min="28" max="28" width="15.1640625" customWidth="1"/>
-    <col min="29" max="30" width="8.58203125" customWidth="1"/>
-    <col min="31" max="31" width="13.4140625" customWidth="1"/>
-    <col min="32" max="32" width="13.75" customWidth="1"/>
-    <col min="33" max="33" width="14.58203125" customWidth="1"/>
-    <col min="34" max="34" width="17.4140625" customWidth="1"/>
-    <col min="35" max="35" width="8.58203125" customWidth="1"/>
-    <col min="36" max="36" width="12.5" customWidth="1"/>
-    <col min="37" max="37" width="8.58203125" customWidth="1"/>
-    <col min="38" max="39" width="8.33203125" customWidth="1"/>
-    <col min="40" max="40" width="15" customWidth="1"/>
-    <col min="41" max="41" width="18" customWidth="1"/>
-    <col min="42" max="42" width="20.58203125" customWidth="1"/>
-    <col min="43" max="45" width="11.83203125" customWidth="1"/>
-    <col min="46" max="46" width="18.4140625" customWidth="1"/>
-    <col min="47" max="47" width="12.25" customWidth="1"/>
-    <col min="48" max="48" width="11.9140625" customWidth="1"/>
-    <col min="49" max="49" width="19.58203125" customWidth="1"/>
-    <col min="50" max="50" width="12.6640625" customWidth="1"/>
-    <col min="51" max="51" width="9" customWidth="1"/>
-    <col min="52" max="52" width="7" customWidth="1"/>
-    <col min="53" max="53" width="11.75" customWidth="1"/>
-    <col min="54" max="54" width="19.75" customWidth="1"/>
-    <col min="55" max="55" width="5.08203125" customWidth="1"/>
-    <col min="56" max="56" width="8.5" customWidth="1"/>
-    <col min="57" max="57" width="13.5" customWidth="1"/>
-    <col min="58" max="58" width="14.6640625" customWidth="1"/>
-    <col min="59" max="59" width="10.1640625" customWidth="1"/>
-    <col min="60" max="60" width="8.25" customWidth="1"/>
-    <col min="61" max="61" width="8.33203125" customWidth="1"/>
-    <col min="62" max="62" width="10.1640625" customWidth="1"/>
-    <col min="63" max="67" width="8.33203125" customWidth="1"/>
-    <col min="68" max="70" width="11.25" customWidth="1"/>
-    <col min="71" max="71" width="6.58203125" customWidth="1"/>
-    <col min="72" max="73" width="8" customWidth="1"/>
-    <col min="74" max="74" width="7.33203125" customWidth="1"/>
-    <col min="75" max="76" width="8.5" customWidth="1"/>
-    <col min="77" max="78" width="7.83203125" customWidth="1"/>
-    <col min="79" max="79" width="22.1640625" customWidth="1"/>
-    <col min="80" max="80" width="13.5" customWidth="1"/>
-    <col min="81" max="81" width="21.1640625" customWidth="1"/>
-    <col min="82" max="82" width="15.75" customWidth="1"/>
-    <col min="83" max="83" width="15.58203125" customWidth="1"/>
-    <col min="84" max="84" width="12.83203125" customWidth="1"/>
-    <col min="85" max="85" width="16.1640625" customWidth="1"/>
-    <col min="86" max="86" width="9" customWidth="1"/>
-    <col min="87" max="87" width="16" customWidth="1"/>
-    <col min="88" max="89" width="12.83203125" customWidth="1"/>
-    <col min="90" max="90" width="23.58203125" customWidth="1"/>
-    <col min="91" max="91" width="12.83203125" customWidth="1"/>
-    <col min="92" max="92" width="17.08203125" customWidth="1"/>
-    <col min="93" max="98" width="9" customWidth="1"/>
-    <col min="99" max="99" width="14" customWidth="1"/>
-    <col min="100" max="100" width="8" customWidth="1"/>
-    <col min="101" max="101" width="9" customWidth="1"/>
-    <col min="102" max="102" width="11.08203125" customWidth="1"/>
-    <col min="103" max="103" width="13.75" customWidth="1"/>
-    <col min="104" max="109" width="9" customWidth="1"/>
-    <col min="110" max="110" width="15.5" customWidth="1"/>
-    <col min="111" max="113" width="9" customWidth="1"/>
+    <col min="1" max="1" width="21.08203125" customWidth="1" style="2"/>
+    <col min="2" max="2" width="15.58203125" customWidth="1" style="2"/>
+    <col min="3" max="3" width="7.75" customWidth="1" style="2"/>
+    <col min="4" max="4" width="16.58203125" customWidth="1" style="2"/>
+    <col min="5" max="5" width="16.83203125" customWidth="1" style="2"/>
+    <col min="6" max="6" width="31.33203125" customWidth="1" style="2"/>
+    <col min="7" max="7" width="7.33203125" customWidth="1" style="2"/>
+    <col min="8" max="8" width="20.58203125" customWidth="1" style="2"/>
+    <col min="9" max="9" width="10.75" customWidth="1" style="2"/>
+    <col min="10" max="10" width="15.75" customWidth="1" style="2"/>
+    <col min="11" max="13" width="8.33203125" customWidth="1" style="2"/>
+    <col min="14" max="14" width="11.75" customWidth="1" style="2"/>
+    <col min="15" max="15" width="13.08203125" customWidth="1" style="2"/>
+    <col min="16" max="16" width="11.58203125" customWidth="1" style="2"/>
+    <col min="17" max="17" width="21.5" customWidth="1" style="2"/>
+    <col min="18" max="18" width="19.83203125" customWidth="1" style="2"/>
+    <col min="19" max="19" width="16.58203125" customWidth="1" style="2"/>
+    <col min="20" max="20" width="19.08203125" customWidth="1" style="2"/>
+    <col min="21" max="21" width="18.33203125" customWidth="1" style="2"/>
+    <col min="22" max="22" width="17.75" customWidth="1" style="2"/>
+    <col min="23" max="23" width="8.33203125" customWidth="1" style="2"/>
+    <col min="24" max="24" width="18.5" customWidth="1" style="2"/>
+    <col min="25" max="25" width="16.58203125" customWidth="1" style="2"/>
+    <col min="26" max="26" width="10.6640625" customWidth="1" style="2"/>
+    <col min="27" max="27" width="8.33203125" customWidth="1" style="2"/>
+    <col min="28" max="28" width="15.1640625" customWidth="1" style="2"/>
+    <col min="29" max="30" width="8.58203125" customWidth="1" style="2"/>
+    <col min="31" max="31" width="13.4140625" customWidth="1" style="2"/>
+    <col min="32" max="32" width="13.75" customWidth="1" style="2"/>
+    <col min="33" max="33" width="14.58203125" customWidth="1" style="2"/>
+    <col min="34" max="34" width="17.4140625" customWidth="1" style="2"/>
+    <col min="35" max="35" width="8.58203125" customWidth="1" style="2"/>
+    <col min="36" max="36" width="12.5" customWidth="1" style="2"/>
+    <col min="37" max="37" width="8.58203125" customWidth="1" style="2"/>
+    <col min="38" max="39" width="8.33203125" customWidth="1" style="2"/>
+    <col min="40" max="40" width="15" customWidth="1" style="2"/>
+    <col min="41" max="41" width="18" customWidth="1" style="2"/>
+    <col min="42" max="42" width="20.58203125" customWidth="1" style="2"/>
+    <col min="43" max="45" width="11.83203125" customWidth="1" style="2"/>
+    <col min="46" max="46" width="18.4140625" customWidth="1" style="2"/>
+    <col min="47" max="47" width="12.25" customWidth="1" style="2"/>
+    <col min="48" max="48" width="11.9140625" customWidth="1" style="2"/>
+    <col min="49" max="49" width="19.58203125" customWidth="1" style="2"/>
+    <col min="50" max="50" width="12.6640625" customWidth="1" style="2"/>
+    <col min="51" max="51" width="9" customWidth="1" style="2"/>
+    <col min="52" max="52" width="7" customWidth="1" style="2"/>
+    <col min="53" max="53" width="11.75" customWidth="1" style="2"/>
+    <col min="54" max="54" width="19.75" customWidth="1" style="2"/>
+    <col min="55" max="55" width="5.08203125" customWidth="1" style="2"/>
+    <col min="56" max="56" width="8.5" customWidth="1" style="2"/>
+    <col min="57" max="57" width="13.5" customWidth="1" style="2"/>
+    <col min="58" max="58" width="14.6640625" customWidth="1" style="2"/>
+    <col min="59" max="59" width="10.1640625" customWidth="1" style="2"/>
+    <col min="60" max="60" width="8.25" customWidth="1" style="2"/>
+    <col min="61" max="61" width="8.33203125" customWidth="1" style="2"/>
+    <col min="62" max="62" width="10.1640625" customWidth="1" style="2"/>
+    <col min="63" max="67" width="8.33203125" customWidth="1" style="2"/>
+    <col min="68" max="70" width="11.25" customWidth="1" style="2"/>
+    <col min="71" max="71" width="6.58203125" customWidth="1" style="2"/>
+    <col min="72" max="73" width="8" customWidth="1" style="2"/>
+    <col min="74" max="74" width="7.33203125" customWidth="1" style="2"/>
+    <col min="75" max="76" width="8.5" customWidth="1" style="2"/>
+    <col min="77" max="78" width="7.83203125" customWidth="1" style="2"/>
+    <col min="79" max="79" width="22.1640625" customWidth="1" style="2"/>
+    <col min="80" max="80" width="13.5" customWidth="1" style="2"/>
+    <col min="81" max="81" width="21.1640625" customWidth="1" style="2"/>
+    <col min="82" max="82" width="15.75" customWidth="1" style="2"/>
+    <col min="83" max="83" width="15.58203125" customWidth="1" style="2"/>
+    <col min="84" max="84" width="12.83203125" customWidth="1" style="2"/>
+    <col min="85" max="85" width="16.1640625" customWidth="1" style="2"/>
+    <col min="86" max="86" width="9" customWidth="1" style="2"/>
+    <col min="87" max="87" width="16" customWidth="1" style="2"/>
+    <col min="88" max="89" width="12.83203125" customWidth="1" style="2"/>
+    <col min="90" max="90" width="23.58203125" customWidth="1" style="2"/>
+    <col min="91" max="91" width="12.83203125" customWidth="1" style="2"/>
+    <col min="92" max="92" width="17.08203125" customWidth="1" style="2"/>
+    <col min="93" max="98" width="9" customWidth="1" style="2"/>
+    <col min="99" max="99" width="14" customWidth="1" style="2"/>
+    <col min="100" max="100" width="8" customWidth="1" style="2"/>
+    <col min="101" max="101" width="9" customWidth="1" style="2"/>
+    <col min="102" max="102" width="11.08203125" customWidth="1" style="2"/>
+    <col min="103" max="103" width="13.75" customWidth="1" style="2"/>
+    <col min="104" max="109" width="9" customWidth="1" style="2"/>
+    <col min="110" max="110" width="15.5" customWidth="1" style="2"/>
+    <col min="111" max="113" width="9" customWidth="1" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="B1" t="s">
-        <v>150</v>
-      </c>
-      <c r="D1" t="s">
-        <v>151</v>
-      </c>
-      <c r="E1" t="s">
-        <v>152</v>
-      </c>
-      <c r="F1" t="s">
-        <v>153</v>
-      </c>
-      <c r="G1" t="s">
-        <v>154</v>
-      </c>
-      <c r="H1" t="s">
-        <v>155</v>
-      </c>
-      <c r="I1" t="s">
-        <v>156</v>
-      </c>
-      <c r="J1" t="s">
-        <v>157</v>
-      </c>
-      <c r="K1" t="s">
-        <v>158</v>
-      </c>
-      <c r="L1" t="s">
-        <v>159</v>
-      </c>
-      <c r="M1" t="s">
+    <row r="1">
+      <c r="B1" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="N1" t="s">
+      <c r="D1" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="O1" t="s">
+      <c r="E1" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="P1" t="s">
+      <c r="F1" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="G1" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="R1" t="s">
+      <c r="H1" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="S1" t="s">
+      <c r="I1" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="T1" t="s">
+      <c r="J1" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="U1" t="s">
-        <v>167</v>
-      </c>
-      <c r="V1" t="s">
+      <c r="K1" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="W1" t="s">
+      <c r="L1" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="X1" t="s">
+      <c r="M1" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="N1" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="O1" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="P1" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="R1" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="S1" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="T1" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="U1" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="V1" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="W1" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="X1" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="Y1" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="Z1" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AA1" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AB1" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AC1" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AD1" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AE1" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AF1" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AG1" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AH1" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AI1" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AJ1" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AK1" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AL1" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AM1" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AN1" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AO1" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="AP1" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="AQ1" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="AR1" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="AS1" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="AT1" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="AU1" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="AV1" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="AW1" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="AX1" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="BJ1" t="s">
-        <v>206</v>
-      </c>
-      <c r="BK1" t="s">
+      <c r="AY1" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="AZ1" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BA1" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BB1" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BC1" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BD1" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BE1" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BF1" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="BS1" t="s">
+      <c r="BG1" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="BT1" t="s">
+      <c r="BH1" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="BU1" t="s">
+      <c r="BJ1" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="BK1" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="BV1" t="s">
+      <c r="BL1" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="BW1" t="s">
+      <c r="BM1" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="BX1" t="s">
+      <c r="BN1" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="BY1" t="s">
+      <c r="BO1" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="BZ1" t="s">
+      <c r="BP1" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="CA1" t="s">
+      <c r="BQ1" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="CB1" t="s">
+      <c r="BR1" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="CC1" t="s">
+      <c r="BS1" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="CD1" t="s">
+      <c r="BT1" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="CE1" t="s">
+      <c r="BU1" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="CF1" t="s">
+      <c r="BV1" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="CG1" t="s">
+      <c r="BW1" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="CH1" t="s">
+      <c r="BX1" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="CI1" t="s">
+      <c r="BY1" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="CJ1" t="s">
+      <c r="BZ1" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="CK1" t="s">
+      <c r="CA1" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="CL1" t="s">
+      <c r="CB1" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="CM1" t="s">
+      <c r="CC1" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="CN1" t="s">
+      <c r="CD1" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="CO1" t="s">
+      <c r="CE1" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="CP1" t="s">
+      <c r="CF1" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="CQ1" t="s">
+      <c r="CG1" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="CR1" t="s">
-        <v>216</v>
-      </c>
-      <c r="CS1" t="s">
+      <c r="CH1" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="CT1" t="s">
+      <c r="CI1" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="CU1" t="s">
+      <c r="CJ1" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="CV1" t="s">
+      <c r="CK1" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="CW1" t="s">
+      <c r="CL1" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="CX1" t="s">
+      <c r="CM1" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="CY1" t="s">
+      <c r="CN1" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="CZ1" t="s">
-        <v>245</v>
-      </c>
-      <c r="DA1" t="s">
+      <c r="CO1" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="DB1" t="s">
+      <c r="CP1" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="DC1" t="s">
+      <c r="CQ1" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="DD1" t="s">
+      <c r="CR1" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="CS1" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="DE1" t="s">
+      <c r="CT1" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="DF1" t="s">
+      <c r="CU1" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="DG1" t="s">
+      <c r="CV1" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="DH1" t="s">
+      <c r="CW1" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="DI1" t="s">
+      <c r="CX1" s="2" t="s">
         <v>255</v>
       </c>
-    </row>
-    <row r="2" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="CY1" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="CZ1" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="DA1" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="DB1" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="DC1" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="DD1" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="DE1" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="DF1" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="DG1" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="DH1" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="DI1" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E2" t="s">
-        <v>256</v>
-      </c>
-      <c r="F2" t="s">
-        <v>257</v>
-      </c>
-      <c r="G2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H2" t="s">
-        <v>258</v>
-      </c>
-      <c r="I2" t="s">
-        <v>259</v>
-      </c>
-      <c r="J2" t="s">
-        <v>260</v>
-      </c>
-      <c r="K2" t="s">
-        <v>261</v>
-      </c>
-      <c r="L2" t="s">
-        <v>262</v>
-      </c>
-      <c r="M2" t="s">
-        <v>263</v>
-      </c>
-      <c r="N2" t="s">
-        <v>264</v>
-      </c>
-      <c r="O2" t="s">
-        <v>265</v>
-      </c>
-      <c r="P2" t="s">
+      <c r="C2" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="F2" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="R2" t="s">
+      <c r="G2" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="S2" t="s">
+      <c r="I2" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="T2" t="s">
+      <c r="J2" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="U2" t="s">
+      <c r="K2" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="V2" t="s">
+      <c r="L2" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="W2" t="s">
+      <c r="M2" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="X2" t="s">
+      <c r="N2" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="O2" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="P2" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="R2" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="S2" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="T2" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="AE2" t="s">
+      <c r="U2" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="V2" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="AG2" t="s">
+      <c r="W2" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="AH2" t="s">
+      <c r="X2" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="AI2" t="s">
+      <c r="Y2" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="AJ2" t="s">
+      <c r="Z2" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="AK2" t="s">
+      <c r="AA2" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="AL2" t="s">
+      <c r="AB2" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="AM2" t="s">
+      <c r="AC2" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="AN2" t="s">
+      <c r="AD2" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="AO2" t="s">
+      <c r="AE2" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="AP2" t="s">
+      <c r="AF2" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="AQ2" t="s">
+      <c r="AG2" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="AR2" t="s">
+      <c r="AH2" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="AS2" t="s">
+      <c r="AI2" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="AT2" t="s">
+      <c r="AJ2" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="AU2" t="s">
+      <c r="AK2" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="AV2" t="s">
+      <c r="AL2" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="AW2" t="s">
+      <c r="AM2" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="AX2" t="s">
+      <c r="AN2" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="AY2" t="s">
+      <c r="AO2" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="AZ2" t="s">
+      <c r="AP2" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="BA2" t="s">
+      <c r="AQ2" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="BB2" t="s">
+      <c r="AR2" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="BC2" t="s">
+      <c r="AS2" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="BD2" t="s">
+      <c r="AT2" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="BE2" t="s">
+      <c r="AU2" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="BF2" t="s">
+      <c r="AV2" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="BG2" t="s">
+      <c r="AW2" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="BH2" t="s">
+      <c r="AX2" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="BI2" t="s">
+      <c r="AY2" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="BJ2" t="s">
+      <c r="AZ2" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="BK2" t="s">
+      <c r="BA2" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="BL2" t="s">
+      <c r="BB2" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="BM2" t="s">
+      <c r="BC2" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="BN2" t="s">
+      <c r="BD2" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="BO2" t="s">
-        <v>81</v>
-      </c>
-      <c r="BP2" t="s">
+      <c r="BE2" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="BQ2" t="s">
+      <c r="BF2" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="BR2" t="s">
+      <c r="BG2" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="BS2" t="s">
+      <c r="BH2" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="BT2" t="s">
+      <c r="BI2" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="BU2" t="s">
-        <v>96</v>
-      </c>
-      <c r="BV2" t="s">
+      <c r="BJ2" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="BW2" t="s">
+      <c r="BK2" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="BX2" t="s">
+      <c r="BL2" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="BY2" t="s">
+      <c r="BM2" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="BZ2" t="s">
+      <c r="BN2" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="CA2" t="s">
+      <c r="BO2" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="BP2" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="CB2" t="s">
+      <c r="BQ2" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="CC2" t="s">
+      <c r="BR2" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="CD2" t="s">
+      <c r="BS2" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="CE2" t="s">
+      <c r="BT2" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="CF2" t="s">
+      <c r="BU2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BV2" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="CG2" t="s">
+      <c r="BW2" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="CH2" t="s">
+      <c r="BX2" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="CI2" t="s">
+      <c r="BY2" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="CJ2" t="s">
+      <c r="BZ2" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="CK2" t="s">
+      <c r="CA2" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="CL2" t="s">
+      <c r="CB2" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="CM2" t="s">
+      <c r="CC2" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="CN2" t="s">
+      <c r="CD2" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="CO2" t="s">
+      <c r="CE2" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="CP2" t="s">
+      <c r="CF2" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="CQ2" t="s">
+      <c r="CG2" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="CR2" t="s">
+      <c r="CH2" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="CS2" t="s">
+      <c r="CI2" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="CT2" t="s">
+      <c r="CJ2" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="CU2" t="s">
+      <c r="CK2" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="CV2" t="s">
+      <c r="CL2" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="CW2" t="s">
+      <c r="CM2" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="CX2" t="s">
+      <c r="CN2" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="CY2" t="s">
+      <c r="CO2" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="CZ2" t="s">
+      <c r="CP2" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="DA2" t="s">
+      <c r="CQ2" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="DB2" t="s">
+      <c r="CR2" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="DC2" t="s">
+      <c r="CS2" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="DD2" t="s">
+      <c r="CT2" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="DE2" t="s">
+      <c r="CU2" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="DF2" t="s">
+      <c r="CV2" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="DG2" t="s">
+      <c r="CW2" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="DH2" t="s">
+      <c r="CX2" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="DI2" t="s">
+      <c r="CY2" s="2" t="s">
         <v>361</v>
       </c>
-    </row>
-    <row r="3" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="CZ2" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="DA2" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="DB2" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="DC2" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="DD2" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="DE2" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="DF2" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="DG2" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="DH2" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="DI2" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G3" t="s">
-        <v>119</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="G3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="I3" t="s">
-        <v>117</v>
-      </c>
-      <c r="J3" t="s">
-        <v>362</v>
-      </c>
-      <c r="K3" t="s">
-        <v>363</v>
-      </c>
-      <c r="L3" t="s">
-        <v>364</v>
-      </c>
-      <c r="M3" t="s">
-        <v>119</v>
-      </c>
-      <c r="N3" t="s">
-        <v>119</v>
-      </c>
-      <c r="O3" t="s">
+      <c r="I3" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="P3" t="s">
+      <c r="J3" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="S3" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="T3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="W3" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="R3" t="s">
+      <c r="X3" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="S3" t="s">
-        <v>117</v>
-      </c>
-      <c r="T3" t="s">
-        <v>118</v>
-      </c>
-      <c r="U3" t="s">
-        <v>118</v>
-      </c>
-      <c r="V3" t="s">
-        <v>118</v>
-      </c>
-      <c r="W3" t="s">
-        <v>117</v>
-      </c>
-      <c r="X3" t="s">
-        <v>117</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>117</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>118</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>119</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>365</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>124</v>
-      </c>
-      <c r="AJ3" t="s">
+      <c r="Y3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="Z3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AA3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AB3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AC3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="AD3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AE3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AF3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AG3" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="AH3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AI3" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="AJ3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="AK3" t="s">
-        <v>119</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>119</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>119</v>
-      </c>
-      <c r="AN3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AO3" t="s">
-        <v>366</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>367</v>
-      </c>
-      <c r="AQ3" t="s">
+      <c r="AK3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="AL3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="AM3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="AN3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AO3" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="AP3" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="AQ3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="AR3" t="s">
+      <c r="AR3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="AS3" t="s">
+      <c r="AS3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="AT3" t="s">
-        <v>368</v>
-      </c>
-      <c r="AU3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AV3" t="s">
-        <v>118</v>
-      </c>
-      <c r="AW3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AX3" t="s">
-        <v>369</v>
-      </c>
-      <c r="AY3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AZ3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BA3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BB3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BC3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BD3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BE3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BF3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BG3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BH3" t="s">
-        <v>368</v>
-      </c>
-      <c r="BI3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BJ3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BK3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BL3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BM3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BN3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BO3" t="s">
-        <v>120</v>
-      </c>
-      <c r="BP3" t="s">
-        <v>120</v>
-      </c>
-      <c r="BQ3" t="s">
-        <v>370</v>
-      </c>
-      <c r="BR3" t="s">
-        <v>371</v>
-      </c>
-      <c r="BS3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BT3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BU3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BV3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BW3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BX3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BY3" t="s">
-        <v>372</v>
-      </c>
-      <c r="BZ3" t="s">
-        <v>117</v>
-      </c>
-      <c r="CA3" t="s">
-        <v>372</v>
-      </c>
-      <c r="CB3" t="s">
-        <v>121</v>
-      </c>
-      <c r="CC3" t="s">
-        <v>373</v>
-      </c>
-      <c r="CD3" t="s">
-        <v>121</v>
-      </c>
-      <c r="CE3" t="s">
-        <v>121</v>
-      </c>
-      <c r="CF3" t="s">
-        <v>121</v>
-      </c>
-      <c r="CG3" t="s">
-        <v>374</v>
-      </c>
-      <c r="CH3" t="s">
-        <v>375</v>
-      </c>
-      <c r="CI3" t="s">
+      <c r="AT3" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="AU3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AV3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AW3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AX3" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="AY3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AZ3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="BA3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BB3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="BC3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="BD3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="BE3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="BF3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="BG3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BH3" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="BI3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BJ3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="BK3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="BL3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="BM3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="BN3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="BO3" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="BP3" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="BQ3" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="BR3" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="BS3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="BT3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="BU3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BV3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="BW3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="BX3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="BY3" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="BZ3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="CA3" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="CB3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="CC3" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="CD3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="CE3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="CF3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="CG3" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="CH3" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="CI3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="CJ3" t="s">
-        <v>376</v>
-      </c>
-      <c r="CK3" t="s">
-        <v>376</v>
-      </c>
-      <c r="CL3" t="s">
-        <v>126</v>
-      </c>
-      <c r="CM3" t="s">
+      <c r="CJ3" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="CK3" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="CL3" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="CM3" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN3" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="CO3" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="CP3" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="CQ3" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="CR3" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="CS3" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="CT3" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="CN3" t="s">
+      <c r="CU3" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="CV3" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="CW3" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="CX3" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="CY3" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="CZ3" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="DA3" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="DB3" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="DC3" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="DD3" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="CO3" t="s">
-        <v>125</v>
-      </c>
-      <c r="CP3" t="s">
-        <v>125</v>
-      </c>
-      <c r="CQ3" t="s">
-        <v>125</v>
-      </c>
-      <c r="CR3" t="s">
-        <v>373</v>
-      </c>
-      <c r="CS3" t="s">
-        <v>125</v>
-      </c>
-      <c r="CT3" t="s">
-        <v>117</v>
-      </c>
-      <c r="CU3" t="s">
-        <v>126</v>
-      </c>
-      <c r="CV3" t="s">
-        <v>377</v>
-      </c>
-      <c r="CW3" t="s">
-        <v>378</v>
-      </c>
-      <c r="CX3" t="s">
-        <v>378</v>
-      </c>
-      <c r="CY3" t="s">
-        <v>377</v>
-      </c>
-      <c r="CZ3" t="s">
-        <v>377</v>
-      </c>
-      <c r="DA3" t="s">
-        <v>377</v>
-      </c>
-      <c r="DB3" t="s">
-        <v>377</v>
-      </c>
-      <c r="DC3" t="s">
-        <v>377</v>
-      </c>
-      <c r="DD3" t="s">
-        <v>117</v>
-      </c>
-      <c r="DE3" t="s">
-        <v>117</v>
-      </c>
-      <c r="DF3" t="s">
-        <v>117</v>
-      </c>
-      <c r="DG3" t="s">
-        <v>117</v>
-      </c>
-      <c r="DH3" t="s">
-        <v>117</v>
-      </c>
-      <c r="DI3" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="4" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="6" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>380</v>
-      </c>
-      <c r="C6" t="s">
-        <v>381</v>
-      </c>
-      <c r="K6" t="s">
-        <v>382</v>
-      </c>
-      <c r="P6" t="s">
-        <v>383</v>
-      </c>
-      <c r="AC6">
-        <v>1</v>
-      </c>
-      <c r="AO6" t="s">
-        <v>384</v>
-      </c>
-      <c r="AT6" t="s">
-        <v>385</v>
-      </c>
-      <c r="AY6">
-        <v>1</v>
-      </c>
-      <c r="AZ6">
-        <v>1</v>
-      </c>
-      <c r="BD6">
-        <v>1</v>
-      </c>
-      <c r="CB6" t="s">
-        <v>57</v>
-      </c>
-      <c r="CG6" t="s">
-        <v>386</v>
-      </c>
-      <c r="CH6" t="s">
-        <v>387</v>
-      </c>
-      <c r="CI6" t="s">
-        <v>388</v>
-      </c>
-      <c r="CN6" t="s">
+      <c r="DE3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="DF3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="DG3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="DH3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="DI3" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="CR6">
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="AC6" s="2">
+        <v>1</v>
+      </c>
+      <c r="AO6" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="AT6" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="AY6" s="2">
+        <v>1</v>
+      </c>
+      <c r="AZ6" s="2">
+        <v>1</v>
+      </c>
+      <c r="BD6" s="2">
+        <v>1</v>
+      </c>
+      <c r="CB6" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="CG6" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="CH6" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="CI6" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="CN6" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="CR6" s="2">
         <v>9999</v>
       </c>
-      <c r="CY6" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="7" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="CY6" s="2" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="AC7" s="2">
+        <v>1</v>
+      </c>
+      <c r="AF7" s="2">
+        <v>1</v>
+      </c>
+      <c r="AV7" s="2">
+        <v>20</v>
+      </c>
+      <c r="BD7" s="2">
+        <v>1</v>
+      </c>
+      <c r="CU7" s="2" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="AC8" s="2">
+        <v>1</v>
+      </c>
+      <c r="AT8" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="BD8" s="2">
+        <v>1</v>
+      </c>
+      <c r="CU8" s="2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="C7" t="s">
+      <c r="K9" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="AC9" s="2">
+        <v>1</v>
+      </c>
+      <c r="AT9" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="BD9" s="2">
+        <v>99</v>
+      </c>
+      <c r="CM9" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="CN9" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="CR9" s="2">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="I10" s="2">
+        <v>1</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="AC10" s="2">
+        <v>1</v>
+      </c>
+      <c r="AG10" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="AN10" s="2">
+        <v>1</v>
+      </c>
+      <c r="AT10" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="BD10" s="2">
+        <v>99</v>
+      </c>
+      <c r="CN10" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="CR10" s="2">
+        <v>1</v>
+      </c>
+      <c r="DD10" s="2">
+        <v>1</v>
+      </c>
+      <c r="DG10" s="2">
+        <v>1</v>
+      </c>
+      <c r="DH10" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="I11" s="2">
+        <v>1</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="AC11" s="2">
+        <v>1</v>
+      </c>
+      <c r="AF11" s="2">
+        <v>1</v>
+      </c>
+      <c r="AG11" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="AN11" s="2">
+        <v>1</v>
+      </c>
+      <c r="BD11" s="2">
+        <v>1</v>
+      </c>
+      <c r="CN11" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="CR11" s="2">
+        <v>9999</v>
+      </c>
+      <c r="DD11" s="2">
+        <v>1</v>
+      </c>
+      <c r="DG11" s="2">
+        <v>1</v>
+      </c>
+      <c r="DH11" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="G13" s="2">
+        <v>3</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="AB13" s="2">
+        <v>1</v>
+      </c>
+      <c r="AC13" s="2">
+        <v>1</v>
+      </c>
+      <c r="AG13" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="AO13" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="AT13" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="AY13" s="2">
+        <v>1</v>
+      </c>
+      <c r="AZ13" s="2">
+        <v>1</v>
+      </c>
+      <c r="BD13" s="2">
+        <v>1</v>
+      </c>
+      <c r="BO13" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="BT13" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="BU13" s="2">
+        <v>1</v>
+      </c>
+      <c r="BV13" s="2">
+        <v>0</v>
+      </c>
+      <c r="BW13" s="2">
+        <v>5</v>
+      </c>
+      <c r="BX13" s="2">
+        <v>1</v>
+      </c>
+      <c r="BY13" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="K7" t="s">
-        <v>393</v>
-      </c>
-      <c r="L7" t="s">
+      <c r="CN13" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="CO13" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="AC14" s="2">
+        <v>1</v>
+      </c>
+      <c r="AO14" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="Q7" t="s">
+      <c r="AT14" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="AY14" s="2">
+        <v>1</v>
+      </c>
+      <c r="AZ14" s="2">
+        <v>1</v>
+      </c>
+      <c r="BD14" s="2">
+        <v>1</v>
+      </c>
+      <c r="CB14" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="CG14" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="CH14" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="CI14" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="CN14" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="CR14" s="2">
+        <v>9999</v>
+      </c>
+      <c r="CY14" s="2" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="G16" s="2">
+        <v>3</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="AC16" s="2">
+        <v>1</v>
+      </c>
+      <c r="AO16" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="AV16" s="2">
+        <v>20</v>
+      </c>
+      <c r="AY16" s="2">
+        <v>1</v>
+      </c>
+      <c r="AZ16" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="BD16" s="2">
+        <v>99</v>
+      </c>
+      <c r="BT16" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="BV16" s="2">
+        <v>30</v>
+      </c>
+      <c r="BW16" s="2">
+        <v>20</v>
+      </c>
+      <c r="BX16" s="2">
+        <v>3</v>
+      </c>
+      <c r="BY16" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="CB16" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="CG16" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="CH16" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="CI16" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="CN16" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="CO16" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="CR16" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="G18" s="2">
+        <v>3</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="AC18" s="2">
+        <v>1</v>
+      </c>
+      <c r="AG18" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="BD18" s="2">
+        <v>1</v>
+      </c>
+      <c r="BO18" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="BT18" s="2">
+        <v>30</v>
+      </c>
+      <c r="BV18" s="2">
+        <v>45</v>
+      </c>
+      <c r="BW18" s="2">
+        <v>50</v>
+      </c>
+      <c r="BX18" s="2">
+        <v>1</v>
+      </c>
+      <c r="BY18" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="CN18" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="CO18" s="2">
+        <v>-0.4</v>
+      </c>
+      <c r="CR18" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="AC19" s="2">
+        <v>1</v>
+      </c>
+      <c r="AF19" s="2">
+        <v>1</v>
+      </c>
+      <c r="AH19" s="2">
+        <v>1</v>
+      </c>
+      <c r="BD19" s="2">
+        <v>99</v>
+      </c>
+      <c r="CU19" s="2" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="AC20" s="2">
+        <v>2</v>
+      </c>
+      <c r="AF20" s="2">
+        <v>1</v>
+      </c>
+      <c r="AH20" s="2">
+        <v>1</v>
+      </c>
+      <c r="BD20" s="2">
+        <v>99</v>
+      </c>
+      <c r="CU20" s="2" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="AC21" s="2">
+        <v>2</v>
+      </c>
+      <c r="AF21" s="2">
+        <v>1</v>
+      </c>
+      <c r="BD21" s="2">
+        <v>1</v>
+      </c>
+      <c r="CN21" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="CR21" s="2">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="AC22" s="2">
+        <v>2</v>
+      </c>
+      <c r="AV22" s="2">
+        <v>20</v>
+      </c>
+      <c r="BD22" s="2">
+        <v>99</v>
+      </c>
+      <c r="CU22" s="2" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="AC23" s="2">
+        <v>2</v>
+      </c>
+      <c r="AF23" s="2">
+        <v>1</v>
+      </c>
+      <c r="BD23" s="2">
+        <v>99</v>
+      </c>
+      <c r="CU23" s="2" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="Q24" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="AC24" s="2">
+        <v>1</v>
+      </c>
+      <c r="AF24" s="2">
+        <v>1</v>
+      </c>
+      <c r="AT24" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="BD24" s="2">
+        <v>99</v>
+      </c>
+      <c r="CU24" s="2" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="Q25" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="AC25" s="2">
+        <v>1</v>
+      </c>
+      <c r="AF25" s="2">
+        <v>1</v>
+      </c>
+      <c r="AT25" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="BD25" s="2">
+        <v>99</v>
+      </c>
+      <c r="CU25" s="2" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="AC27" s="2">
+        <v>1</v>
+      </c>
+      <c r="AO27" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="AT27" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="AC7">
-        <v>1</v>
-      </c>
-      <c r="AF7">
-        <v>1</v>
-      </c>
-      <c r="AV7">
+      <c r="AY27" s="2">
+        <v>1</v>
+      </c>
+      <c r="AZ27" s="2">
+        <v>1</v>
+      </c>
+      <c r="BD27" s="2">
+        <v>3</v>
+      </c>
+      <c r="CB27" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="CG27" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="CH27" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="CI27" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="CN27" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="CR27" s="2">
+        <v>9999</v>
+      </c>
+      <c r="CY27" s="2" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="Q28" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="AC28" s="2">
+        <v>1</v>
+      </c>
+      <c r="AO28" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="AV28" s="2">
         <v>20</v>
       </c>
-      <c r="BD7">
-        <v>1</v>
-      </c>
-      <c r="CU7" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="8" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>397</v>
-      </c>
-      <c r="C8" t="s">
-        <v>398</v>
-      </c>
-      <c r="K8" t="s">
-        <v>393</v>
-      </c>
-      <c r="L8" t="s">
-        <v>399</v>
-      </c>
-      <c r="AC8">
-        <v>1</v>
-      </c>
-      <c r="AT8" t="s">
-        <v>400</v>
-      </c>
-      <c r="BD8">
-        <v>1</v>
-      </c>
-      <c r="CU8" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="9" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>402</v>
-      </c>
-      <c r="C9" t="s">
-        <v>381</v>
-      </c>
-      <c r="K9" t="s">
-        <v>393</v>
-      </c>
-      <c r="L9" t="s">
-        <v>403</v>
-      </c>
-      <c r="AC9">
-        <v>1</v>
-      </c>
-      <c r="AT9" t="s">
-        <v>404</v>
-      </c>
-      <c r="BD9">
+      <c r="BD28" s="2">
+        <v>1</v>
+      </c>
+      <c r="BS28" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="CN28" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="CR28" s="2">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="Q29" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="AC29" s="2">
+        <v>2</v>
+      </c>
+      <c r="AV29" s="2">
+        <v>20</v>
+      </c>
+      <c r="AX29" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="AZ29" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="BD29" s="2">
         <v>99</v>
       </c>
-      <c r="CM9" t="s">
-        <v>395</v>
-      </c>
-      <c r="CN9" t="s">
-        <v>405</v>
-      </c>
-      <c r="CR9">
-        <v>9999</v>
-      </c>
-    </row>
-    <row r="10" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>406</v>
-      </c>
-      <c r="C10" t="s">
-        <v>381</v>
-      </c>
-      <c r="I10">
-        <v>1</v>
-      </c>
-      <c r="K10" t="s">
-        <v>393</v>
-      </c>
-      <c r="L10" t="s">
-        <v>399</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>407</v>
-      </c>
-      <c r="AC10">
-        <v>1</v>
-      </c>
-      <c r="AG10" t="s">
-        <v>408</v>
-      </c>
-      <c r="AN10">
-        <v>1</v>
-      </c>
-      <c r="AT10" t="s">
-        <v>404</v>
-      </c>
-      <c r="BD10">
+      <c r="CM29" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="CY29" s="2" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="Q30" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="AC30" s="2">
+        <v>1</v>
+      </c>
+      <c r="AN30" s="2">
+        <v>1</v>
+      </c>
+      <c r="AV30" s="2">
+        <v>20</v>
+      </c>
+      <c r="BD30" s="2">
         <v>99</v>
       </c>
-      <c r="CN10" t="s">
-        <v>409</v>
-      </c>
-      <c r="CR10">
-        <v>1</v>
-      </c>
-      <c r="DD10">
-        <v>1</v>
-      </c>
-      <c r="DG10">
-        <v>1</v>
-      </c>
-      <c r="DH10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>407</v>
-      </c>
-      <c r="C11" t="s">
-        <v>381</v>
-      </c>
-      <c r="I11">
-        <v>1</v>
-      </c>
-      <c r="K11" t="s">
-        <v>393</v>
-      </c>
-      <c r="L11" t="s">
-        <v>399</v>
-      </c>
-      <c r="AC11">
-        <v>1</v>
-      </c>
-      <c r="AF11">
-        <v>1</v>
-      </c>
-      <c r="AG11" t="s">
-        <v>410</v>
-      </c>
-      <c r="AN11">
-        <v>1</v>
-      </c>
-      <c r="BD11">
-        <v>1</v>
-      </c>
-      <c r="CN11" t="s">
-        <v>411</v>
-      </c>
-      <c r="CR11">
-        <v>9999</v>
-      </c>
-      <c r="DD11">
-        <v>1</v>
-      </c>
-      <c r="DG11">
-        <v>1</v>
-      </c>
-      <c r="DH11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>412</v>
-      </c>
-      <c r="C13" t="s">
-        <v>381</v>
-      </c>
-      <c r="D13" t="s">
-        <v>413</v>
-      </c>
-      <c r="E13" t="s">
-        <v>414</v>
-      </c>
-      <c r="G13">
-        <v>3</v>
-      </c>
-      <c r="J13" t="s">
+      <c r="BT30" s="2">
+        <v>30</v>
+      </c>
+      <c r="CU30" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="DD30" s="2">
+        <v>1</v>
+      </c>
+      <c r="DG30" s="2">
+        <v>1</v>
+      </c>
+      <c r="DH30" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="Q31" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="K13" t="s">
-        <v>416</v>
-      </c>
-      <c r="AB13">
-        <v>1</v>
-      </c>
-      <c r="AC13">
-        <v>1</v>
-      </c>
-      <c r="AG13" t="s">
-        <v>410</v>
-      </c>
-      <c r="AO13" t="s">
-        <v>384</v>
-      </c>
-      <c r="AT13" t="s">
-        <v>417</v>
-      </c>
-      <c r="AY13">
-        <v>1</v>
-      </c>
-      <c r="AZ13">
-        <v>1</v>
-      </c>
-      <c r="BD13">
-        <v>1</v>
-      </c>
-      <c r="BO13" t="s">
-        <v>418</v>
-      </c>
-      <c r="BT13">
+      <c r="AC31" s="2">
+        <v>1</v>
+      </c>
+      <c r="AV31" s="2">
+        <v>20</v>
+      </c>
+      <c r="BD31" s="2">
+        <v>99</v>
+      </c>
+      <c r="BS31" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="CN31" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="CR31" s="2">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="CL669" s="2">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="CL671" s="2">
         <v>0.2</v>
       </c>
-      <c r="BU13">
-        <v>1</v>
-      </c>
-      <c r="BV13">
-        <v>0</v>
-      </c>
-      <c r="BW13">
-        <v>5</v>
-      </c>
-      <c r="BX13">
-        <v>1</v>
-      </c>
-      <c r="BY13" t="s">
-        <v>382</v>
-      </c>
-      <c r="CN13" t="s">
-        <v>412</v>
-      </c>
-      <c r="CO13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>418</v>
-      </c>
-      <c r="C14" t="s">
-        <v>381</v>
-      </c>
-      <c r="K14" t="s">
-        <v>382</v>
-      </c>
-      <c r="O14" t="s">
-        <v>412</v>
-      </c>
-      <c r="AC14">
-        <v>1</v>
-      </c>
-      <c r="AO14" t="s">
-        <v>384</v>
-      </c>
-      <c r="AT14" t="s">
-        <v>417</v>
-      </c>
-      <c r="AY14">
-        <v>1</v>
-      </c>
-      <c r="AZ14">
-        <v>1</v>
-      </c>
-      <c r="BD14">
-        <v>1</v>
-      </c>
-      <c r="CB14" t="s">
-        <v>57</v>
-      </c>
-      <c r="CG14" t="s">
-        <v>386</v>
-      </c>
-      <c r="CH14" t="s">
-        <v>419</v>
-      </c>
-      <c r="CI14" t="s">
-        <v>388</v>
-      </c>
-      <c r="CN14" t="s">
-        <v>389</v>
-      </c>
-      <c r="CR14">
-        <v>9999</v>
-      </c>
-      <c r="CY14" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="16" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>420</v>
-      </c>
-      <c r="C16" t="s">
-        <v>381</v>
-      </c>
-      <c r="D16" t="s">
-        <v>421</v>
-      </c>
-      <c r="E16" t="s">
-        <v>422</v>
-      </c>
-      <c r="G16">
-        <v>3</v>
-      </c>
-      <c r="J16" t="s">
-        <v>415</v>
-      </c>
-      <c r="K16" t="s">
-        <v>416</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>405</v>
-      </c>
-      <c r="AC16">
-        <v>1</v>
-      </c>
-      <c r="AO16" t="s">
-        <v>384</v>
-      </c>
-      <c r="AV16">
-        <v>20</v>
-      </c>
-      <c r="AY16">
-        <v>1</v>
-      </c>
-      <c r="AZ16">
-        <v>2.5</v>
-      </c>
-      <c r="BD16">
-        <v>99</v>
-      </c>
-      <c r="BT16">
+    </row>
+    <row r="672">
+      <c r="CL672" s="2">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="CL674" s="2">
         <v>0.2</v>
       </c>
-      <c r="BV16">
-        <v>30</v>
-      </c>
-      <c r="BW16">
-        <v>20</v>
-      </c>
-      <c r="BX16">
-        <v>3</v>
-      </c>
-      <c r="BY16" t="s">
-        <v>382</v>
-      </c>
-      <c r="CB16" t="s">
-        <v>57</v>
-      </c>
-      <c r="CG16" t="s">
-        <v>386</v>
-      </c>
-      <c r="CH16" t="s">
-        <v>387</v>
-      </c>
-      <c r="CI16" t="s">
-        <v>388</v>
-      </c>
-      <c r="CN16" t="s">
-        <v>423</v>
-      </c>
-      <c r="CO16">
-        <v>0.3</v>
-      </c>
-      <c r="CR16">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:112" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>424</v>
-      </c>
-      <c r="C18" t="s">
-        <v>381</v>
-      </c>
-      <c r="D18" t="s">
-        <v>425</v>
-      </c>
-      <c r="E18" t="s">
-        <v>426</v>
-      </c>
-      <c r="G18">
-        <v>3</v>
-      </c>
-      <c r="J18" t="s">
-        <v>415</v>
-      </c>
-      <c r="K18" t="s">
-        <v>416</v>
-      </c>
-      <c r="AC18">
-        <v>1</v>
-      </c>
-      <c r="AG18" t="s">
-        <v>410</v>
-      </c>
-      <c r="BD18">
-        <v>1</v>
-      </c>
-      <c r="BO18" t="s">
-        <v>427</v>
-      </c>
-      <c r="BT18">
-        <v>30</v>
-      </c>
-      <c r="BV18">
-        <v>45</v>
-      </c>
-      <c r="BW18">
-        <v>50</v>
-      </c>
-      <c r="BX18">
-        <v>1</v>
-      </c>
-      <c r="BY18" t="s">
-        <v>382</v>
-      </c>
-      <c r="CN18" t="s">
-        <v>428</v>
-      </c>
-      <c r="CO18">
-        <v>-0.4</v>
-      </c>
-      <c r="CR18">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" spans="1:112" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>429</v>
-      </c>
-      <c r="C19" t="s">
-        <v>430</v>
-      </c>
-      <c r="K19" t="s">
-        <v>393</v>
-      </c>
-      <c r="L19" t="s">
-        <v>431</v>
-      </c>
-      <c r="AC19">
-        <v>1</v>
-      </c>
-      <c r="AF19">
-        <v>1</v>
-      </c>
-      <c r="AH19">
-        <v>1</v>
-      </c>
-      <c r="BD19">
-        <v>99</v>
-      </c>
-      <c r="CU19" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="20" spans="1:112" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>433</v>
-      </c>
-      <c r="C20" t="s">
-        <v>392</v>
-      </c>
-      <c r="K20" t="s">
-        <v>393</v>
-      </c>
-      <c r="L20" t="s">
-        <v>434</v>
-      </c>
-      <c r="O20" t="s">
-        <v>405</v>
-      </c>
-      <c r="AC20">
-        <v>2</v>
-      </c>
-      <c r="AF20">
-        <v>1</v>
-      </c>
-      <c r="AH20">
-        <v>1</v>
-      </c>
-      <c r="BD20">
-        <v>99</v>
-      </c>
-      <c r="CU20" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="21" spans="1:112" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>435</v>
-      </c>
-      <c r="C21" t="s">
-        <v>381</v>
-      </c>
-      <c r="K21" t="s">
-        <v>393</v>
-      </c>
-      <c r="L21" t="s">
-        <v>436</v>
-      </c>
-      <c r="O21" t="s">
-        <v>437</v>
-      </c>
-      <c r="AC21">
-        <v>2</v>
-      </c>
-      <c r="AF21">
-        <v>1</v>
-      </c>
-      <c r="BD21">
-        <v>1</v>
-      </c>
-      <c r="CN21" t="s">
-        <v>438</v>
-      </c>
-      <c r="CR21">
-        <v>9999</v>
-      </c>
-    </row>
-    <row r="22" spans="1:112" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>439</v>
-      </c>
-      <c r="C22" t="s">
-        <v>430</v>
-      </c>
-      <c r="K22" t="s">
-        <v>393</v>
-      </c>
-      <c r="L22" t="s">
-        <v>403</v>
-      </c>
-      <c r="AC22">
-        <v>2</v>
-      </c>
-      <c r="AV22">
-        <v>20</v>
-      </c>
-      <c r="BD22">
-        <v>99</v>
-      </c>
-      <c r="CU22" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="23" spans="1:112" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>441</v>
-      </c>
-      <c r="C23" t="s">
-        <v>392</v>
-      </c>
-      <c r="K23" t="s">
-        <v>393</v>
-      </c>
-      <c r="L23" t="s">
-        <v>442</v>
-      </c>
-      <c r="AC23">
-        <v>2</v>
-      </c>
-      <c r="AF23">
-        <v>1</v>
-      </c>
-      <c r="BD23">
-        <v>99</v>
-      </c>
-      <c r="CU23" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="24" spans="1:112" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>443</v>
-      </c>
-      <c r="C24" t="s">
-        <v>392</v>
-      </c>
-      <c r="K24" t="s">
-        <v>393</v>
-      </c>
-      <c r="L24" t="s">
-        <v>442</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>405</v>
-      </c>
-      <c r="AC24">
-        <v>1</v>
-      </c>
-      <c r="AF24">
-        <v>1</v>
-      </c>
-      <c r="AT24" t="s">
-        <v>404</v>
-      </c>
-      <c r="BD24">
-        <v>99</v>
-      </c>
-      <c r="CU24" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="25" spans="1:112" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>444</v>
-      </c>
-      <c r="C25" t="s">
-        <v>392</v>
-      </c>
-      <c r="K25" t="s">
-        <v>393</v>
-      </c>
-      <c r="L25" t="s">
-        <v>445</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>405</v>
-      </c>
-      <c r="AC25">
-        <v>1</v>
-      </c>
-      <c r="AF25">
-        <v>1</v>
-      </c>
-      <c r="AT25" t="s">
-        <v>404</v>
-      </c>
-      <c r="BD25">
-        <v>99</v>
-      </c>
-      <c r="CU25" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="27" spans="1:112" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>446</v>
-      </c>
-      <c r="C27" t="s">
-        <v>381</v>
-      </c>
-      <c r="J27" t="s">
-        <v>447</v>
-      </c>
-      <c r="K27" t="s">
-        <v>382</v>
-      </c>
-      <c r="AC27">
-        <v>1</v>
-      </c>
-      <c r="AO27" t="s">
-        <v>384</v>
-      </c>
-      <c r="AT27" t="s">
-        <v>385</v>
-      </c>
-      <c r="AY27">
-        <v>1</v>
-      </c>
-      <c r="AZ27">
-        <v>1</v>
-      </c>
-      <c r="BD27">
-        <v>3</v>
-      </c>
-      <c r="CB27" t="s">
-        <v>57</v>
-      </c>
-      <c r="CG27" t="s">
-        <v>386</v>
-      </c>
-      <c r="CH27" t="s">
-        <v>387</v>
-      </c>
-      <c r="CI27" t="s">
-        <v>388</v>
-      </c>
-      <c r="CN27" t="s">
-        <v>389</v>
-      </c>
-      <c r="CR27">
-        <v>9999</v>
-      </c>
-      <c r="CY27" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="28" spans="1:112" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>448</v>
-      </c>
-      <c r="C28" t="s">
-        <v>381</v>
-      </c>
-      <c r="J28" t="s">
-        <v>447</v>
-      </c>
-      <c r="K28" t="s">
-        <v>382</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>405</v>
-      </c>
-      <c r="AC28">
-        <v>1</v>
-      </c>
-      <c r="AO28" t="s">
-        <v>384</v>
-      </c>
-      <c r="AV28">
-        <v>20</v>
-      </c>
-      <c r="BD28">
-        <v>1</v>
-      </c>
-      <c r="BS28">
-        <v>0.01</v>
-      </c>
-      <c r="CN28" t="s">
-        <v>449</v>
-      </c>
-      <c r="CR28">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="29" spans="1:112" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>450</v>
-      </c>
-      <c r="C29" t="s">
-        <v>381</v>
-      </c>
-      <c r="J29" t="s">
-        <v>447</v>
-      </c>
-      <c r="K29" t="s">
-        <v>382</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>438</v>
-      </c>
-      <c r="AC29">
-        <v>2</v>
-      </c>
-      <c r="AV29">
-        <v>20</v>
-      </c>
-      <c r="AX29" t="s">
-        <v>451</v>
-      </c>
-      <c r="AZ29">
-        <v>0.8</v>
-      </c>
-      <c r="BD29">
-        <v>99</v>
-      </c>
-      <c r="CM29" t="s">
-        <v>438</v>
-      </c>
-      <c r="CY29" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="30" spans="1:112" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>453</v>
-      </c>
-      <c r="C30" t="s">
-        <v>454</v>
-      </c>
-      <c r="J30" t="s">
-        <v>447</v>
-      </c>
-      <c r="K30" t="s">
-        <v>382</v>
-      </c>
-      <c r="Q30" t="s">
-        <v>407</v>
-      </c>
-      <c r="AC30">
-        <v>1</v>
-      </c>
-      <c r="AN30">
-        <v>1</v>
-      </c>
-      <c r="AV30">
-        <v>20</v>
-      </c>
-      <c r="BD30">
-        <v>99</v>
-      </c>
-      <c r="BT30">
-        <v>30</v>
-      </c>
-      <c r="CU30" t="s">
-        <v>455</v>
-      </c>
-      <c r="DD30">
-        <v>1</v>
-      </c>
-      <c r="DG30">
-        <v>1</v>
-      </c>
-      <c r="DH30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:112" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>456</v>
-      </c>
-      <c r="C31" t="s">
-        <v>381</v>
-      </c>
-      <c r="J31" t="s">
-        <v>447</v>
-      </c>
-      <c r="K31" t="s">
-        <v>382</v>
-      </c>
-      <c r="Q31" t="s">
-        <v>405</v>
-      </c>
-      <c r="AC31">
-        <v>1</v>
-      </c>
-      <c r="AV31">
-        <v>20</v>
-      </c>
-      <c r="BD31">
-        <v>99</v>
-      </c>
-      <c r="BS31">
-        <v>0.01</v>
-      </c>
-      <c r="CN31" t="s">
-        <v>437</v>
-      </c>
-      <c r="CR31">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="669" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL669">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="671" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL671">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="672" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL672">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="674" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL674">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="681" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL681">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="683" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL683">
+    </row>
+    <row r="681">
+      <c r="CL681" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="CL683" s="2">
         <v>0.4</v>
       </c>
     </row>
-    <row r="684" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL684">
+    <row r="684">
+      <c r="CL684" s="2">
         <v>0.6</v>
       </c>
     </row>
-    <row r="687" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL687">
+    <row r="687">
+      <c r="CL687" s="2">
         <v>0.5</v>
       </c>
     </row>
-    <row r="688" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL688">
-        <v>0.66700000000000004</v>
-      </c>
-    </row>
-    <row r="689" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL689">
+    <row r="688">
+      <c r="CL688" s="2">
+        <v>0.667</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="CL689" s="2">
         <v>0.2</v>
       </c>
     </row>
@@ -5434,6 +5673,7 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -5443,268 +5683,269 @@
   <dimension ref="A1:Q15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.08203125" customWidth="1"/>
-    <col min="2" max="2" width="31.25" customWidth="1"/>
-    <col min="3" max="6" width="9" customWidth="1"/>
-    <col min="7" max="7" width="18.75" customWidth="1"/>
-    <col min="8" max="8" width="15" customWidth="1"/>
-    <col min="9" max="13" width="9" customWidth="1"/>
-    <col min="14" max="14" width="16.08203125" customWidth="1"/>
-    <col min="15" max="15" width="9.5" customWidth="1"/>
-    <col min="16" max="16" width="22.1640625" customWidth="1"/>
-    <col min="17" max="17" width="12.83203125" customWidth="1"/>
+    <col min="1" max="1" width="18.08203125" customWidth="1" style="2"/>
+    <col min="2" max="2" width="31.25" customWidth="1" style="2"/>
+    <col min="3" max="6" width="9" customWidth="1" style="2"/>
+    <col min="7" max="7" width="18.75" customWidth="1" style="2"/>
+    <col min="8" max="8" width="15" customWidth="1" style="2"/>
+    <col min="9" max="13" width="9" customWidth="1" style="2"/>
+    <col min="14" max="14" width="16.08203125" customWidth="1" style="2"/>
+    <col min="15" max="15" width="9.5" customWidth="1" style="2"/>
+    <col min="16" max="16" width="22.1640625" customWidth="1" style="2"/>
+    <col min="17" max="17" width="12.83203125" customWidth="1" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E1" t="s">
-        <v>457</v>
-      </c>
-      <c r="F1" t="s">
-        <v>458</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="E1" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="H6" s="2">
+        <v>1</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="I9" s="2">
+        <v>1</v>
+      </c>
+      <c r="K9" s="2">
+        <v>99999</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="H1" t="s">
-        <v>460</v>
-      </c>
-      <c r="I1" t="s">
-        <v>461</v>
-      </c>
-      <c r="J1" t="s">
-        <v>462</v>
-      </c>
-      <c r="L1" t="s">
-        <v>463</v>
-      </c>
-      <c r="M1" t="s">
-        <v>464</v>
-      </c>
-      <c r="N1" t="s">
-        <v>465</v>
-      </c>
-      <c r="O1" t="s">
-        <v>466</v>
-      </c>
-      <c r="P1" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E2" t="s">
-        <v>468</v>
-      </c>
-      <c r="F2" t="s">
-        <v>469</v>
-      </c>
-      <c r="G2" t="s">
-        <v>470</v>
-      </c>
-      <c r="H2" t="s">
-        <v>471</v>
-      </c>
-      <c r="I2" t="s">
-        <v>472</v>
-      </c>
-      <c r="J2" t="s">
-        <v>473</v>
-      </c>
-      <c r="K2" t="s">
-        <v>474</v>
-      </c>
-      <c r="L2" t="s">
-        <v>53</v>
-      </c>
-      <c r="M2" t="s">
-        <v>475</v>
-      </c>
-      <c r="N2" t="s">
-        <v>476</v>
-      </c>
-      <c r="O2" t="s">
-        <v>477</v>
-      </c>
-      <c r="P2" t="s">
-        <v>478</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" t="s">
-        <v>119</v>
-      </c>
-      <c r="F3" t="s">
-        <v>119</v>
-      </c>
-      <c r="G3" t="s">
-        <v>119</v>
-      </c>
-      <c r="H3" t="s">
-        <v>117</v>
-      </c>
-      <c r="I3" t="s">
-        <v>117</v>
-      </c>
-      <c r="J3" t="s">
-        <v>377</v>
-      </c>
-      <c r="K3" t="s">
-        <v>118</v>
-      </c>
-      <c r="L3" t="s">
-        <v>341</v>
-      </c>
-      <c r="M3" t="s">
-        <v>117</v>
-      </c>
-      <c r="N3" t="s">
-        <v>117</v>
-      </c>
-      <c r="O3" t="s">
-        <v>341</v>
-      </c>
-      <c r="P3" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>395</v>
-      </c>
-      <c r="C5" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>405</v>
-      </c>
-      <c r="C6" t="s">
-        <v>480</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="J6" t="s">
-        <v>481</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>407</v>
-      </c>
-      <c r="C7" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>412</v>
-      </c>
-      <c r="C9" t="s">
-        <v>484</v>
-      </c>
-      <c r="I9">
-        <v>1</v>
-      </c>
-      <c r="K9">
-        <v>99999</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>423</v>
-      </c>
-      <c r="C10" t="s">
-        <v>486</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>428</v>
-      </c>
-      <c r="C12" t="s">
-        <v>484</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>438</v>
-      </c>
-      <c r="C13" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>449</v>
-      </c>
-      <c r="C14" t="s">
-        <v>480</v>
-      </c>
-      <c r="H14">
-        <v>1</v>
-      </c>
-      <c r="J14" t="s">
+      <c r="C14" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="H14" s="2">
+        <v>1</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>489</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>437</v>
-      </c>
-      <c r="C15" t="s">
-        <v>479</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -5713,63 +5954,64 @@
   <dimension ref="A1:D4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" customWidth="1"/>
-    <col min="2" max="2" width="11.25" customWidth="1"/>
-    <col min="3" max="3" width="9" customWidth="1"/>
-    <col min="4" max="4" width="27.5" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" customWidth="1" style="2"/>
+    <col min="2" max="2" width="11.25" customWidth="1" style="2"/>
+    <col min="3" max="3" width="9" customWidth="1" style="2"/>
+    <col min="4" max="4" width="27.5" customWidth="1" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="C1" s="2" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C2" t="s">
-        <v>492</v>
-      </c>
-      <c r="D2" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B2" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" t="s">
-        <v>341</v>
-      </c>
-      <c r="D3" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>493</v>
-      </c>
-      <c r="B4" t="s">
-        <v>494</v>
-      </c>
-      <c r="D4" t="s">
-        <v>495</v>
+      <c r="C3" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>505</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -5778,132 +6020,133 @@
   <dimension ref="A1:J5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.25" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
-    <col min="3" max="3" width="27.25" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" customWidth="1"/>
-    <col min="5" max="10" width="9" customWidth="1"/>
+    <col min="1" max="1" width="15.25" customWidth="1" style="2"/>
+    <col min="2" max="2" width="9" customWidth="1" style="2"/>
+    <col min="3" max="3" width="27.25" customWidth="1" style="2"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1" style="2"/>
+    <col min="5" max="10" width="9" customWidth="1" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="I1" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="1">
+      <c r="I1" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D2" t="s">
-        <v>496</v>
-      </c>
-      <c r="E2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F2" t="s">
-        <v>497</v>
-      </c>
-      <c r="G2" t="s">
-        <v>498</v>
-      </c>
-      <c r="H2" t="s">
-        <v>499</v>
-      </c>
-      <c r="I2" t="s">
-        <v>336</v>
-      </c>
-      <c r="J2" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B2" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F3" t="s">
-        <v>119</v>
-      </c>
-      <c r="G3" t="s">
-        <v>119</v>
-      </c>
-      <c r="H3" t="s">
-        <v>119</v>
-      </c>
-      <c r="I3" t="s">
-        <v>376</v>
-      </c>
-      <c r="J3" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>387</v>
-      </c>
-      <c r="B4" t="s">
-        <v>500</v>
-      </c>
-      <c r="C4" t="s">
-        <v>501</v>
-      </c>
-      <c r="E4">
+      <c r="E3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="E4" s="2">
         <v>10</v>
       </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4" t="s">
-        <v>502</v>
-      </c>
-      <c r="J4" t="s">
+      <c r="H4" s="2">
+        <v>1</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="E5" s="2">
+        <v>10</v>
+      </c>
+      <c r="H5" s="2">
+        <v>1</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>503</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>419</v>
-      </c>
-      <c r="B5" t="s">
-        <v>500</v>
-      </c>
-      <c r="C5" t="s">
-        <v>501</v>
-      </c>
-      <c r="E5">
-        <v>10</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5" t="s">
-        <v>493</v>
-      </c>
-      <c r="J5" t="s">
-        <v>503</v>
+      <c r="J5" s="2" t="s">
+        <v>513</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -5912,129 +6155,130 @@
   <dimension ref="A1:L3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.25" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="4" width="10.08203125" customWidth="1"/>
-    <col min="5" max="10" width="11.25" customWidth="1"/>
-    <col min="11" max="11" width="6.33203125" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="1" max="1" width="15.25" customWidth="1" style="2"/>
+    <col min="2" max="2" width="28" customWidth="1" style="2"/>
+    <col min="3" max="4" width="10.08203125" customWidth="1" style="2"/>
+    <col min="5" max="10" width="11.25" customWidth="1" style="2"/>
+    <col min="11" max="11" width="6.33203125" customWidth="1" style="2"/>
+    <col min="12" max="12" width="9" customWidth="1" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>504</v>
-      </c>
-      <c r="C1" t="s">
-        <v>505</v>
-      </c>
-      <c r="D1" t="s">
-        <v>506</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="B1" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>507</v>
       </c>
-      <c r="F1" t="s">
-        <v>508</v>
-      </c>
-      <c r="H1" t="s">
-        <v>509</v>
-      </c>
-      <c r="I1" t="s">
-        <v>510</v>
-      </c>
-      <c r="J1" t="s">
-        <v>511</v>
-      </c>
-      <c r="K1" t="s">
-        <v>512</v>
-      </c>
-      <c r="L1" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>514</v>
-      </c>
-      <c r="C2" t="s">
-        <v>515</v>
-      </c>
-      <c r="D2" t="s">
-        <v>516</v>
-      </c>
-      <c r="E2" t="s">
-        <v>517</v>
-      </c>
-      <c r="F2" t="s">
-        <v>518</v>
-      </c>
-      <c r="G2" t="s">
-        <v>519</v>
-      </c>
-      <c r="H2" t="s">
-        <v>520</v>
-      </c>
-      <c r="I2" t="s">
-        <v>521</v>
-      </c>
-      <c r="J2" t="s">
-        <v>522</v>
-      </c>
-      <c r="K2" t="s">
-        <v>497</v>
-      </c>
-      <c r="L2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="L2" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D3" t="s">
-        <v>523</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="C3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F3" t="s">
-        <v>117</v>
-      </c>
-      <c r="G3" t="s">
-        <v>117</v>
-      </c>
-      <c r="H3" t="s">
-        <v>119</v>
-      </c>
-      <c r="I3" t="s">
-        <v>119</v>
-      </c>
-      <c r="J3" t="s">
-        <v>119</v>
-      </c>
-      <c r="K3" t="s">
-        <v>118</v>
-      </c>
-      <c r="L3" t="s">
-        <v>118</v>
+      <c r="F3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>123</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -6044,49 +6288,49 @@
   <dimension ref="A2:J3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.08203125" customWidth="1"/>
-    <col min="2" max="2" width="16.25" customWidth="1"/>
-    <col min="3" max="3" width="16.33203125" customWidth="1"/>
-    <col min="4" max="4" width="47.83203125" customWidth="1"/>
-    <col min="5" max="5" width="10.25" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1"/>
-    <col min="7" max="9" width="9" customWidth="1"/>
-    <col min="10" max="10" width="11.83203125" customWidth="1"/>
+    <col min="1" max="1" width="19.08203125" customWidth="1" style="2"/>
+    <col min="2" max="2" width="16.25" customWidth="1" style="2"/>
+    <col min="3" max="3" width="16.33203125" customWidth="1" style="2"/>
+    <col min="4" max="4" width="47.83203125" customWidth="1" style="2"/>
+    <col min="5" max="5" width="10.25" customWidth="1" style="2"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1" style="2"/>
+    <col min="7" max="9" width="9" customWidth="1" style="2"/>
+    <col min="10" max="10" width="11.83203125" customWidth="1" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
-        <v>257</v>
-      </c>
-      <c r="C2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D2" t="s">
-        <v>524</v>
-      </c>
-      <c r="E2" t="s">
-        <v>525</v>
-      </c>
-      <c r="F2" t="s">
-        <v>81</v>
-      </c>
-      <c r="G2" t="s">
-        <v>526</v>
-      </c>
-      <c r="H2" t="s">
-        <v>285</v>
-      </c>
-      <c r="I2" t="s">
-        <v>527</v>
-      </c>
-      <c r="J2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -6100,27 +6344,28 @@
         <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>528</v>
+        <v>537</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -6129,133 +6374,134 @@
   <dimension ref="A1:I4"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" customWidth="1"/>
-    <col min="2" max="2" width="13.83203125" customWidth="1"/>
-    <col min="3" max="3" width="20.58203125" customWidth="1"/>
-    <col min="4" max="4" width="39.6640625" customWidth="1"/>
-    <col min="5" max="5" width="37.58203125" customWidth="1"/>
-    <col min="6" max="6" width="39.5" customWidth="1"/>
-    <col min="7" max="7" width="38.58203125" customWidth="1"/>
-    <col min="8" max="8" width="32.25" customWidth="1"/>
-    <col min="9" max="9" width="39.9140625" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" customWidth="1" style="2"/>
+    <col min="2" max="2" width="13.83203125" customWidth="1" style="2"/>
+    <col min="3" max="3" width="20.58203125" customWidth="1" style="2"/>
+    <col min="4" max="4" width="39.6640625" customWidth="1" style="2"/>
+    <col min="5" max="5" width="37.58203125" customWidth="1" style="2"/>
+    <col min="6" max="6" width="39.5" customWidth="1" style="2"/>
+    <col min="7" max="7" width="38.58203125" customWidth="1" style="2"/>
+    <col min="8" max="8" width="32.25" customWidth="1" style="2"/>
+    <col min="9" max="9" width="39.9140625" customWidth="1" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>529</v>
-      </c>
-      <c r="C1" t="s">
-        <v>530</v>
-      </c>
-      <c r="D1" t="s">
-        <v>531</v>
-      </c>
-      <c r="E1" t="s">
-        <v>532</v>
-      </c>
-      <c r="F1" t="s">
-        <v>533</v>
-      </c>
-      <c r="G1" t="s">
-        <v>534</v>
-      </c>
-      <c r="H1" t="s">
-        <v>535</v>
-      </c>
-      <c r="I1" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="B1" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
-        <v>537</v>
-      </c>
-      <c r="C2" t="s">
-        <v>538</v>
-      </c>
-      <c r="D2" t="s">
-        <v>539</v>
-      </c>
-      <c r="E2" t="s">
-        <v>540</v>
-      </c>
-      <c r="F2" t="s">
-        <v>541</v>
-      </c>
-      <c r="G2" t="s">
-        <v>542</v>
-      </c>
-      <c r="H2" t="s">
-        <v>543</v>
-      </c>
-      <c r="I2" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B2" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C3" t="s">
-        <v>117</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="B3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="4">
+      <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4" t="s">
-        <v>545</v>
-      </c>
-      <c r="E4" t="s">
-        <v>546</v>
-      </c>
-      <c r="F4" t="s">
-        <v>547</v>
-      </c>
-      <c r="G4" t="s">
-        <v>548</v>
-      </c>
-      <c r="H4" t="s">
-        <v>549</v>
-      </c>
-      <c r="I4" t="s">
-        <v>550</v>
+      <c r="C4" s="2">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>559</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 

--- a/Excel/Diy优胜/萃儿.xlsx
+++ b/Excel/Diy优胜/萃儿.xlsx
@@ -326,7 +326,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="560">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="562">
   <si>
     <t>Id</t>
   </si>
@@ -673,6 +673,9 @@
     <t>Ablititys</t>
   </si>
   <si>
+    <t>StartAnimation</t>
+  </si>
+  <si>
     <t>DefaultAnimation</t>
   </si>
   <si>
@@ -689,6 +692,9 @@
   </si>
   <si>
     <t>ForwardAnimation</t>
+  </si>
+  <si>
+    <t>DieAnimation</t>
   </si>
   <si>
     <t>MaxAnimationScale</t>
@@ -2053,11 +2059,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
@@ -2371,30 +2380,30 @@
   <dimension ref="A2:B4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="9" customWidth="1" style="2"/>
+    <col min="1" max="2" width="9" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2407,7 +2416,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:BV7"/>
+  <dimension ref="A1:BX7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.58203125" customWidth="1" style="2"/>
@@ -2477,13 +2486,15 @@
     <col min="65" max="65" width="9" customWidth="1" style="2"/>
     <col min="66" max="66" width="9" customWidth="1" style="2"/>
     <col min="67" max="67" width="39.58203125" customWidth="1" style="2"/>
-    <col min="68" max="68" width="14" customWidth="1" style="2"/>
-    <col min="69" max="69" width="14.83203125" customWidth="1" style="2"/>
-    <col min="70" max="70" width="14" customWidth="1" style="2"/>
+    <col min="68" max="68" width="9" customWidth="1" style="2"/>
+    <col min="69" max="69" width="14" customWidth="1" style="2"/>
+    <col min="70" max="70" width="14.83203125" customWidth="1" style="2"/>
     <col min="71" max="71" width="14" customWidth="1" style="2"/>
     <col min="72" max="72" width="14" customWidth="1" style="2"/>
     <col min="73" max="73" width="14" customWidth="1" style="2"/>
-    <col min="74" max="74" width="19.1640625" customWidth="1" style="2"/>
+    <col min="74" max="74" width="14" customWidth="1" style="2"/>
+    <col min="75" max="75" width="9" customWidth="1" style="2"/>
+    <col min="76" max="76" width="19.1640625" customWidth="1" style="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2655,6 +2666,8 @@
       <c r="BT1" s="2"/>
       <c r="BU1" s="2"/>
       <c r="BV1" s="2"/>
+      <c r="BW1" s="2"/>
+      <c r="BX1" s="2"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
@@ -2875,6 +2888,12 @@
       <c r="BV2" s="2" t="s">
         <v>121</v>
       </c>
+      <c r="BW2" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BX2" s="2" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
@@ -2884,7 +2903,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -2892,91 +2911,91 @@
         <v>2</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="J3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="V3" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="W3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="Y3" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="Z3" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="AA3" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="AB3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="AC3" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="O3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="X3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="Y3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="Z3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AB3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="AC3" s="2" t="s">
-        <v>123</v>
-      </c>
       <c r="AD3" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AE3" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AF3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="AG3" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AH3" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AI3" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AJ3" s="2" t="s">
         <v>2</v>
@@ -2985,10 +3004,10 @@
         <v>2</v>
       </c>
       <c r="AL3" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AM3" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AN3" s="2" t="s">
         <v>2</v>
@@ -2997,50 +3016,50 @@
         <v>2</v>
       </c>
       <c r="AP3" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AQ3" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="AR3" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="AR3" s="2" t="s">
+      <c r="AS3" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="AS3" s="2" t="s">
-        <v>123</v>
-      </c>
       <c r="AT3" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AU3" s="2"/>
       <c r="AV3" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AW3" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AX3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="AY3" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="AZ3" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="AY3" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="AZ3" s="2" t="s">
-        <v>123</v>
-      </c>
       <c r="BA3" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="BB3" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="BC3" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="BD3" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="BE3" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="BF3" s="2" t="s">
         <v>2</v>
@@ -3055,43 +3074,49 @@
         <v>2</v>
       </c>
       <c r="BJ3" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="BK3" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="BL3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="BM3" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="BN3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="BO3" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="BP3" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="BQ3" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="BR3" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="BS3" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="BT3" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="BU3" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="BV3" s="2" t="s">
-        <v>123</v>
+        <v>129</v>
+      </c>
+      <c r="BW3" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="BX3" s="2" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="4">
@@ -3169,13 +3194,15 @@
       <c r="BT4" s="2"/>
       <c r="BU4" s="2"/>
       <c r="BV4" s="2"/>
+      <c r="BW4" s="2"/>
+      <c r="BX4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
@@ -3242,23 +3269,23 @@
         <v>4</v>
       </c>
       <c r="AK5" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AL5" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AM5" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AN5" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AO5" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AP5" s="2"/>
       <c r="AQ5" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AR5" s="2">
         <v>1</v>
@@ -3280,20 +3307,20 @@
       <c r="BC5" s="2"/>
       <c r="BD5" s="2"/>
       <c r="BE5" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="BF5" s="2"/>
       <c r="BG5" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="BH5" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="BI5" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="BJ5" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="BK5" s="2">
         <v>6</v>
@@ -3302,38 +3329,40 @@
       <c r="BM5" s="2"/>
       <c r="BN5" s="2"/>
       <c r="BO5" s="2"/>
-      <c r="BP5" s="2" t="s">
-        <v>145</v>
-      </c>
+      <c r="BP5" s="2"/>
       <c r="BQ5" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="BR5" s="2"/>
-      <c r="BS5" s="2" t="s">
         <v>147</v>
       </c>
+      <c r="BR5" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="BS5" s="2"/>
       <c r="BT5" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="BU5" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="BV5" s="2">
+        <v>149</v>
+      </c>
+      <c r="BV5" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="BW5" s="2"/>
+      <c r="BX5" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
       <c r="F6" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -3393,20 +3422,20 @@
       <c r="AH6" s="2"/>
       <c r="AI6" s="2"/>
       <c r="AJ6" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AK6" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AL6" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM6" s="2"/>
       <c r="AN6" s="2"/>
       <c r="AO6" s="2"/>
       <c r="AP6" s="2"/>
       <c r="AQ6" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AR6" s="2">
         <v>0</v>
@@ -3430,7 +3459,7 @@
       <c r="BC6" s="2"/>
       <c r="BD6" s="2"/>
       <c r="BE6" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="BF6" s="2"/>
       <c r="BG6" s="2"/>
@@ -3442,7 +3471,7 @@
       <c r="BM6" s="2"/>
       <c r="BN6" s="2"/>
       <c r="BO6" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="BP6" s="2"/>
       <c r="BQ6" s="2"/>
@@ -3451,19 +3480,21 @@
       <c r="BT6" s="2"/>
       <c r="BU6" s="2"/>
       <c r="BV6" s="2"/>
+      <c r="BW6" s="2"/>
+      <c r="BX6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -3523,20 +3554,20 @@
       <c r="AH7" s="2"/>
       <c r="AI7" s="2"/>
       <c r="AJ7" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AK7" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AL7" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="AM7" s="2"/>
       <c r="AN7" s="2"/>
       <c r="AO7" s="2"/>
       <c r="AP7" s="2"/>
       <c r="AQ7" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AR7" s="2">
         <v>0</v>
@@ -3560,7 +3591,7 @@
       <c r="BC7" s="2"/>
       <c r="BD7" s="2"/>
       <c r="BE7" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="BF7" s="2"/>
       <c r="BG7" s="2"/>
@@ -3572,7 +3603,7 @@
       <c r="BM7" s="2"/>
       <c r="BN7" s="2"/>
       <c r="BO7" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="BP7" s="2"/>
       <c r="BQ7" s="2"/>
@@ -3581,6 +3612,8 @@
       <c r="BT7" s="2"/>
       <c r="BU7" s="2"/>
       <c r="BV7" s="2"/>
+      <c r="BW7" s="2"/>
+      <c r="BX7" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
@@ -3596,2076 +3629,2076 @@
   <dimension ref="A1:DI689"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.08203125" customWidth="1" style="2"/>
-    <col min="2" max="2" width="15.58203125" customWidth="1" style="2"/>
-    <col min="3" max="3" width="7.75" customWidth="1" style="2"/>
-    <col min="4" max="4" width="16.58203125" customWidth="1" style="2"/>
-    <col min="5" max="5" width="16.83203125" customWidth="1" style="2"/>
-    <col min="6" max="6" width="31.33203125" customWidth="1" style="2"/>
-    <col min="7" max="7" width="7.33203125" customWidth="1" style="2"/>
-    <col min="8" max="8" width="20.58203125" customWidth="1" style="2"/>
-    <col min="9" max="9" width="10.75" customWidth="1" style="2"/>
-    <col min="10" max="10" width="15.75" customWidth="1" style="2"/>
-    <col min="11" max="13" width="8.33203125" customWidth="1" style="2"/>
-    <col min="14" max="14" width="11.75" customWidth="1" style="2"/>
-    <col min="15" max="15" width="13.08203125" customWidth="1" style="2"/>
-    <col min="16" max="16" width="11.58203125" customWidth="1" style="2"/>
-    <col min="17" max="17" width="21.5" customWidth="1" style="2"/>
-    <col min="18" max="18" width="19.83203125" customWidth="1" style="2"/>
-    <col min="19" max="19" width="16.58203125" customWidth="1" style="2"/>
-    <col min="20" max="20" width="19.08203125" customWidth="1" style="2"/>
-    <col min="21" max="21" width="18.33203125" customWidth="1" style="2"/>
-    <col min="22" max="22" width="17.75" customWidth="1" style="2"/>
-    <col min="23" max="23" width="8.33203125" customWidth="1" style="2"/>
-    <col min="24" max="24" width="18.5" customWidth="1" style="2"/>
-    <col min="25" max="25" width="16.58203125" customWidth="1" style="2"/>
-    <col min="26" max="26" width="10.6640625" customWidth="1" style="2"/>
-    <col min="27" max="27" width="8.33203125" customWidth="1" style="2"/>
-    <col min="28" max="28" width="15.1640625" customWidth="1" style="2"/>
-    <col min="29" max="30" width="8.58203125" customWidth="1" style="2"/>
-    <col min="31" max="31" width="13.4140625" customWidth="1" style="2"/>
-    <col min="32" max="32" width="13.75" customWidth="1" style="2"/>
-    <col min="33" max="33" width="14.58203125" customWidth="1" style="2"/>
-    <col min="34" max="34" width="17.4140625" customWidth="1" style="2"/>
-    <col min="35" max="35" width="8.58203125" customWidth="1" style="2"/>
-    <col min="36" max="36" width="12.5" customWidth="1" style="2"/>
-    <col min="37" max="37" width="8.58203125" customWidth="1" style="2"/>
-    <col min="38" max="39" width="8.33203125" customWidth="1" style="2"/>
-    <col min="40" max="40" width="15" customWidth="1" style="2"/>
-    <col min="41" max="41" width="18" customWidth="1" style="2"/>
-    <col min="42" max="42" width="20.58203125" customWidth="1" style="2"/>
-    <col min="43" max="45" width="11.83203125" customWidth="1" style="2"/>
-    <col min="46" max="46" width="18.4140625" customWidth="1" style="2"/>
-    <col min="47" max="47" width="12.25" customWidth="1" style="2"/>
-    <col min="48" max="48" width="11.9140625" customWidth="1" style="2"/>
-    <col min="49" max="49" width="19.58203125" customWidth="1" style="2"/>
-    <col min="50" max="50" width="12.6640625" customWidth="1" style="2"/>
-    <col min="51" max="51" width="9" customWidth="1" style="2"/>
-    <col min="52" max="52" width="7" customWidth="1" style="2"/>
-    <col min="53" max="53" width="11.75" customWidth="1" style="2"/>
-    <col min="54" max="54" width="19.75" customWidth="1" style="2"/>
-    <col min="55" max="55" width="5.08203125" customWidth="1" style="2"/>
-    <col min="56" max="56" width="8.5" customWidth="1" style="2"/>
-    <col min="57" max="57" width="13.5" customWidth="1" style="2"/>
-    <col min="58" max="58" width="14.6640625" customWidth="1" style="2"/>
-    <col min="59" max="59" width="10.1640625" customWidth="1" style="2"/>
-    <col min="60" max="60" width="8.25" customWidth="1" style="2"/>
-    <col min="61" max="61" width="8.33203125" customWidth="1" style="2"/>
-    <col min="62" max="62" width="10.1640625" customWidth="1" style="2"/>
-    <col min="63" max="67" width="8.33203125" customWidth="1" style="2"/>
-    <col min="68" max="70" width="11.25" customWidth="1" style="2"/>
-    <col min="71" max="71" width="6.58203125" customWidth="1" style="2"/>
-    <col min="72" max="73" width="8" customWidth="1" style="2"/>
-    <col min="74" max="74" width="7.33203125" customWidth="1" style="2"/>
-    <col min="75" max="76" width="8.5" customWidth="1" style="2"/>
-    <col min="77" max="78" width="7.83203125" customWidth="1" style="2"/>
-    <col min="79" max="79" width="22.1640625" customWidth="1" style="2"/>
-    <col min="80" max="80" width="13.5" customWidth="1" style="2"/>
-    <col min="81" max="81" width="21.1640625" customWidth="1" style="2"/>
-    <col min="82" max="82" width="15.75" customWidth="1" style="2"/>
-    <col min="83" max="83" width="15.58203125" customWidth="1" style="2"/>
-    <col min="84" max="84" width="12.83203125" customWidth="1" style="2"/>
-    <col min="85" max="85" width="16.1640625" customWidth="1" style="2"/>
-    <col min="86" max="86" width="9" customWidth="1" style="2"/>
-    <col min="87" max="87" width="16" customWidth="1" style="2"/>
-    <col min="88" max="89" width="12.83203125" customWidth="1" style="2"/>
-    <col min="90" max="90" width="23.58203125" customWidth="1" style="2"/>
-    <col min="91" max="91" width="12.83203125" customWidth="1" style="2"/>
-    <col min="92" max="92" width="17.08203125" customWidth="1" style="2"/>
-    <col min="93" max="98" width="9" customWidth="1" style="2"/>
-    <col min="99" max="99" width="14" customWidth="1" style="2"/>
-    <col min="100" max="100" width="8" customWidth="1" style="2"/>
-    <col min="101" max="101" width="9" customWidth="1" style="2"/>
-    <col min="102" max="102" width="11.08203125" customWidth="1" style="2"/>
-    <col min="103" max="103" width="13.75" customWidth="1" style="2"/>
-    <col min="104" max="109" width="9" customWidth="1" style="2"/>
-    <col min="110" max="110" width="15.5" customWidth="1" style="2"/>
-    <col min="111" max="113" width="9" customWidth="1" style="2"/>
+    <col min="1" max="1" width="21.08203125" customWidth="1" style="3"/>
+    <col min="2" max="2" width="15.58203125" customWidth="1" style="3"/>
+    <col min="3" max="3" width="7.75" customWidth="1" style="3"/>
+    <col min="4" max="4" width="16.58203125" customWidth="1" style="3"/>
+    <col min="5" max="5" width="16.83203125" customWidth="1" style="3"/>
+    <col min="6" max="6" width="31.33203125" customWidth="1" style="3"/>
+    <col min="7" max="7" width="7.33203125" customWidth="1" style="3"/>
+    <col min="8" max="8" width="20.58203125" customWidth="1" style="3"/>
+    <col min="9" max="9" width="10.75" customWidth="1" style="3"/>
+    <col min="10" max="10" width="15.75" customWidth="1" style="3"/>
+    <col min="11" max="13" width="8.33203125" customWidth="1" style="3"/>
+    <col min="14" max="14" width="11.75" customWidth="1" style="3"/>
+    <col min="15" max="15" width="13.08203125" customWidth="1" style="3"/>
+    <col min="16" max="16" width="11.58203125" customWidth="1" style="3"/>
+    <col min="17" max="17" width="21.5" customWidth="1" style="3"/>
+    <col min="18" max="18" width="19.83203125" customWidth="1" style="3"/>
+    <col min="19" max="19" width="16.58203125" customWidth="1" style="3"/>
+    <col min="20" max="20" width="19.08203125" customWidth="1" style="3"/>
+    <col min="21" max="21" width="18.33203125" customWidth="1" style="3"/>
+    <col min="22" max="22" width="17.75" customWidth="1" style="3"/>
+    <col min="23" max="23" width="8.33203125" customWidth="1" style="3"/>
+    <col min="24" max="24" width="18.5" customWidth="1" style="3"/>
+    <col min="25" max="25" width="16.58203125" customWidth="1" style="3"/>
+    <col min="26" max="26" width="10.6640625" customWidth="1" style="3"/>
+    <col min="27" max="27" width="8.33203125" customWidth="1" style="3"/>
+    <col min="28" max="28" width="15.1640625" customWidth="1" style="3"/>
+    <col min="29" max="30" width="8.58203125" customWidth="1" style="3"/>
+    <col min="31" max="31" width="13.4140625" customWidth="1" style="3"/>
+    <col min="32" max="32" width="13.75" customWidth="1" style="3"/>
+    <col min="33" max="33" width="14.58203125" customWidth="1" style="3"/>
+    <col min="34" max="34" width="17.4140625" customWidth="1" style="3"/>
+    <col min="35" max="35" width="8.58203125" customWidth="1" style="3"/>
+    <col min="36" max="36" width="12.5" customWidth="1" style="3"/>
+    <col min="37" max="37" width="8.58203125" customWidth="1" style="3"/>
+    <col min="38" max="39" width="8.33203125" customWidth="1" style="3"/>
+    <col min="40" max="40" width="15" customWidth="1" style="3"/>
+    <col min="41" max="41" width="18" customWidth="1" style="3"/>
+    <col min="42" max="42" width="20.58203125" customWidth="1" style="3"/>
+    <col min="43" max="45" width="11.83203125" customWidth="1" style="3"/>
+    <col min="46" max="46" width="18.4140625" customWidth="1" style="3"/>
+    <col min="47" max="47" width="12.25" customWidth="1" style="3"/>
+    <col min="48" max="48" width="11.9140625" customWidth="1" style="3"/>
+    <col min="49" max="49" width="19.58203125" customWidth="1" style="3"/>
+    <col min="50" max="50" width="12.6640625" customWidth="1" style="3"/>
+    <col min="51" max="51" width="9" customWidth="1" style="3"/>
+    <col min="52" max="52" width="7" customWidth="1" style="3"/>
+    <col min="53" max="53" width="11.75" customWidth="1" style="3"/>
+    <col min="54" max="54" width="19.75" customWidth="1" style="3"/>
+    <col min="55" max="55" width="5.08203125" customWidth="1" style="3"/>
+    <col min="56" max="56" width="8.5" customWidth="1" style="3"/>
+    <col min="57" max="57" width="13.5" customWidth="1" style="3"/>
+    <col min="58" max="58" width="14.6640625" customWidth="1" style="3"/>
+    <col min="59" max="59" width="10.1640625" customWidth="1" style="3"/>
+    <col min="60" max="60" width="8.25" customWidth="1" style="3"/>
+    <col min="61" max="61" width="8.33203125" customWidth="1" style="3"/>
+    <col min="62" max="62" width="10.1640625" customWidth="1" style="3"/>
+    <col min="63" max="67" width="8.33203125" customWidth="1" style="3"/>
+    <col min="68" max="70" width="11.25" customWidth="1" style="3"/>
+    <col min="71" max="71" width="6.58203125" customWidth="1" style="3"/>
+    <col min="72" max="73" width="8" customWidth="1" style="3"/>
+    <col min="74" max="74" width="7.33203125" customWidth="1" style="3"/>
+    <col min="75" max="76" width="8.5" customWidth="1" style="3"/>
+    <col min="77" max="78" width="7.83203125" customWidth="1" style="3"/>
+    <col min="79" max="79" width="22.1640625" customWidth="1" style="3"/>
+    <col min="80" max="80" width="13.5" customWidth="1" style="3"/>
+    <col min="81" max="81" width="21.1640625" customWidth="1" style="3"/>
+    <col min="82" max="82" width="15.75" customWidth="1" style="3"/>
+    <col min="83" max="83" width="15.58203125" customWidth="1" style="3"/>
+    <col min="84" max="84" width="12.83203125" customWidth="1" style="3"/>
+    <col min="85" max="85" width="16.1640625" customWidth="1" style="3"/>
+    <col min="86" max="86" width="9" customWidth="1" style="3"/>
+    <col min="87" max="87" width="16" customWidth="1" style="3"/>
+    <col min="88" max="89" width="12.83203125" customWidth="1" style="3"/>
+    <col min="90" max="90" width="23.58203125" customWidth="1" style="3"/>
+    <col min="91" max="91" width="12.83203125" customWidth="1" style="3"/>
+    <col min="92" max="92" width="17.08203125" customWidth="1" style="3"/>
+    <col min="93" max="98" width="9" customWidth="1" style="3"/>
+    <col min="99" max="99" width="14" customWidth="1" style="3"/>
+    <col min="100" max="100" width="8" customWidth="1" style="3"/>
+    <col min="101" max="101" width="9" customWidth="1" style="3"/>
+    <col min="102" max="102" width="11.08203125" customWidth="1" style="3"/>
+    <col min="103" max="103" width="13.75" customWidth="1" style="3"/>
+    <col min="104" max="109" width="9" customWidth="1" style="3"/>
+    <col min="110" max="110" width="15.5" customWidth="1" style="3"/>
+    <col min="111" max="113" width="9" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="M1" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="O1" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="P1" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="Q1" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="R1" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="U1" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="V1" s="2" t="s">
+      <c r="S1" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="T1" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="U1" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="V1" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="W1" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="X1" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="Y1" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="Z1" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AA1" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AB1" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AC1" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AD1" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AE1" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="AH1" s="2" t="s">
+      <c r="AF1" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AG1" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="AH1" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="AK1" s="2" t="s">
+      <c r="AI1" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="AL1" s="2" t="s">
+      <c r="AJ1" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="AM1" s="2" t="s">
+      <c r="AK1" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="AN1" s="2" t="s">
+      <c r="AL1" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="AO1" s="2" t="s">
+      <c r="AM1" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="AP1" s="2" t="s">
+      <c r="AN1" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="AQ1" s="2" t="s">
+      <c r="AO1" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="AR1" s="2" t="s">
+      <c r="AP1" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="AS1" s="2" t="s">
+      <c r="AQ1" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="AT1" s="2" t="s">
+      <c r="AR1" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="AU1" s="2" t="s">
+      <c r="AS1" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="AV1" s="2" t="s">
+      <c r="AT1" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="AW1" s="2" t="s">
+      <c r="AU1" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="AX1" s="2" t="s">
+      <c r="AV1" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="AY1" s="2" t="s">
+      <c r="AW1" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="AZ1" s="2" t="s">
+      <c r="AX1" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="BA1" s="2" t="s">
+      <c r="AY1" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="BB1" s="2" t="s">
+      <c r="AZ1" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="BC1" s="2" t="s">
+      <c r="BA1" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="BD1" s="2" t="s">
+      <c r="BB1" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="BE1" s="2" t="s">
+      <c r="BC1" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="BF1" s="2" t="s">
+      <c r="BD1" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="BG1" s="2" t="s">
+      <c r="BE1" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="BH1" s="2" t="s">
+      <c r="BF1" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="BJ1" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="BK1" s="2" t="s">
+      <c r="BG1" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="BL1" s="2" t="s">
+      <c r="BH1" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="BM1" s="2" t="s">
+      <c r="BJ1" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="BK1" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="BN1" s="2" t="s">
+      <c r="BL1" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="BO1" s="2" t="s">
+      <c r="BM1" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="BP1" s="2" t="s">
+      <c r="BN1" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="BQ1" s="2" t="s">
+      <c r="BO1" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="BR1" s="2" t="s">
+      <c r="BP1" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="BS1" s="2" t="s">
+      <c r="BQ1" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="BT1" s="2" t="s">
+      <c r="BR1" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="BU1" s="2" t="s">
+      <c r="BS1" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="BV1" s="2" t="s">
+      <c r="BT1" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="BW1" s="2" t="s">
+      <c r="BU1" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="BX1" s="2" t="s">
+      <c r="BV1" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="BY1" s="2" t="s">
+      <c r="BW1" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="BZ1" s="2" t="s">
+      <c r="BX1" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="CA1" s="2" t="s">
+      <c r="BY1" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="CB1" s="2" t="s">
+      <c r="BZ1" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="CC1" s="2" t="s">
+      <c r="CA1" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="CD1" s="2" t="s">
+      <c r="CB1" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="CE1" s="2" t="s">
+      <c r="CC1" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="CF1" s="2" t="s">
+      <c r="CD1" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="CG1" s="2" t="s">
+      <c r="CE1" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="CH1" s="2" t="s">
+      <c r="CF1" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="CI1" s="2" t="s">
+      <c r="CG1" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="CJ1" s="2" t="s">
+      <c r="CH1" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="CK1" s="2" t="s">
+      <c r="CI1" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="CL1" s="2" t="s">
+      <c r="CJ1" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="CM1" s="2" t="s">
+      <c r="CK1" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="CN1" s="2" t="s">
+      <c r="CL1" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="CO1" s="2" t="s">
+      <c r="CM1" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="CP1" s="2" t="s">
+      <c r="CN1" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="CQ1" s="2" t="s">
+      <c r="CO1" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="CR1" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="CS1" s="2" t="s">
+      <c r="CP1" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="CT1" s="2" t="s">
+      <c r="CQ1" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="CU1" s="2" t="s">
+      <c r="CR1" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="CS1" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="CV1" s="2" t="s">
+      <c r="CT1" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="CW1" s="2" t="s">
+      <c r="CU1" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="CX1" s="2" t="s">
+      <c r="CV1" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="CY1" s="2" t="s">
+      <c r="CW1" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="CZ1" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="DA1" s="2" t="s">
+      <c r="CX1" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="DB1" s="2" t="s">
+      <c r="CY1" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="DC1" s="2" t="s">
+      <c r="CZ1" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="DA1" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="DD1" s="2" t="s">
+      <c r="DB1" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="DE1" s="2" t="s">
+      <c r="DC1" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="DF1" s="2" t="s">
+      <c r="DD1" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="DG1" s="2" t="s">
+      <c r="DE1" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="DH1" s="2" t="s">
+      <c r="DF1" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="DI1" s="2" t="s">
+      <c r="DG1" s="3" t="s">
         <v>265</v>
       </c>
+      <c r="DH1" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="DI1" s="3" t="s">
+        <v>267</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="G2" s="2" t="s">
+      <c r="E2" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="J2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="J2" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="K2" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="L2" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="M2" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="N2" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="O2" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="P2" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="Q2" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="T2" s="2" t="s">
+      <c r="R2" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="U2" s="2" t="s">
+      <c r="S2" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="V2" s="2" t="s">
+      <c r="T2" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="U2" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="X2" s="2" t="s">
+      <c r="V2" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="Y2" s="2" t="s">
+      <c r="W2" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="Z2" s="2" t="s">
+      <c r="X2" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="AA2" s="2" t="s">
+      <c r="Y2" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="AB2" s="2" t="s">
+      <c r="Z2" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="AC2" s="2" t="s">
+      <c r="AA2" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="AD2" s="2" t="s">
+      <c r="AB2" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="AE2" s="2" t="s">
+      <c r="AC2" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="AF2" s="2" t="s">
+      <c r="AD2" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="AG2" s="2" t="s">
+      <c r="AE2" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="AH2" s="2" t="s">
+      <c r="AF2" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="AI2" s="2" t="s">
+      <c r="AG2" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="AJ2" s="2" t="s">
+      <c r="AH2" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="AK2" s="2" t="s">
+      <c r="AI2" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="AL2" s="2" t="s">
+      <c r="AJ2" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="AM2" s="2" t="s">
+      <c r="AK2" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="AN2" s="2" t="s">
+      <c r="AL2" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="AO2" s="2" t="s">
+      <c r="AM2" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="AP2" s="2" t="s">
+      <c r="AN2" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="AQ2" s="2" t="s">
+      <c r="AO2" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="AR2" s="2" t="s">
+      <c r="AP2" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="AS2" s="2" t="s">
+      <c r="AQ2" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="AT2" s="2" t="s">
+      <c r="AR2" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="AU2" s="2" t="s">
+      <c r="AS2" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="AV2" s="2" t="s">
+      <c r="AT2" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="AW2" s="2" t="s">
+      <c r="AU2" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="AX2" s="2" t="s">
+      <c r="AV2" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="AY2" s="2" t="s">
+      <c r="AW2" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="AZ2" s="2" t="s">
+      <c r="AX2" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="BA2" s="2" t="s">
+      <c r="AY2" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="BB2" s="2" t="s">
+      <c r="AZ2" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="BC2" s="2" t="s">
+      <c r="BA2" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="BD2" s="2" t="s">
+      <c r="BB2" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="BE2" s="2" t="s">
+      <c r="BC2" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="BF2" s="2" t="s">
+      <c r="BD2" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="BG2" s="2" t="s">
+      <c r="BE2" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="BH2" s="2" t="s">
+      <c r="BF2" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="BI2" s="2" t="s">
+      <c r="BG2" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="BJ2" s="2" t="s">
+      <c r="BH2" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="BK2" s="2" t="s">
+      <c r="BI2" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="BL2" s="2" t="s">
+      <c r="BJ2" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="BM2" s="2" t="s">
+      <c r="BK2" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="BN2" s="2" t="s">
+      <c r="BL2" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="BO2" s="2" t="s">
+      <c r="BM2" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="BN2" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="BO2" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="BP2" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="BQ2" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="BR2" s="2" t="s">
+      <c r="BP2" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="BS2" s="2" t="s">
+      <c r="BQ2" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="BT2" s="2" t="s">
+      <c r="BR2" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="BU2" s="2" t="s">
+      <c r="BS2" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="BT2" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="BU2" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="BV2" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="BW2" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="BX2" s="2" t="s">
+      <c r="BV2" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="BY2" s="2" t="s">
+      <c r="BW2" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="BZ2" s="2" t="s">
+      <c r="BX2" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="CA2" s="2" t="s">
+      <c r="BY2" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="CB2" s="2" t="s">
+      <c r="BZ2" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="CC2" s="2" t="s">
+      <c r="CA2" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="CD2" s="2" t="s">
+      <c r="CB2" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="CE2" s="2" t="s">
+      <c r="CC2" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="CF2" s="2" t="s">
+      <c r="CD2" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="CG2" s="2" t="s">
+      <c r="CE2" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="CH2" s="2" t="s">
+      <c r="CF2" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="CI2" s="2" t="s">
+      <c r="CG2" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="CJ2" s="2" t="s">
+      <c r="CH2" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="CK2" s="2" t="s">
+      <c r="CI2" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="CL2" s="2" t="s">
+      <c r="CJ2" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="CM2" s="2" t="s">
+      <c r="CK2" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="CN2" s="2" t="s">
+      <c r="CL2" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="CO2" s="2" t="s">
+      <c r="CM2" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="CP2" s="2" t="s">
+      <c r="CN2" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="CQ2" s="2" t="s">
+      <c r="CO2" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="CR2" s="2" t="s">
+      <c r="CP2" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="CS2" s="2" t="s">
+      <c r="CQ2" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="CT2" s="2" t="s">
+      <c r="CR2" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="CU2" s="2" t="s">
+      <c r="CS2" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="CV2" s="2" t="s">
+      <c r="CT2" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="CW2" s="2" t="s">
+      <c r="CU2" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="CX2" s="2" t="s">
+      <c r="CV2" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="CY2" s="2" t="s">
+      <c r="CW2" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="CZ2" s="2" t="s">
+      <c r="CX2" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="DA2" s="2" t="s">
+      <c r="CY2" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="DB2" s="2" t="s">
+      <c r="CZ2" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="DC2" s="2" t="s">
+      <c r="DA2" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="DD2" s="2" t="s">
+      <c r="DB2" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="DE2" s="2" t="s">
+      <c r="DC2" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="DF2" s="2" t="s">
+      <c r="DD2" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="DG2" s="2" t="s">
+      <c r="DE2" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="DH2" s="2" t="s">
+      <c r="DF2" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="DI2" s="2" t="s">
+      <c r="DG2" s="3" t="s">
         <v>371</v>
       </c>
+      <c r="DH2" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="DI2" s="3" t="s">
+        <v>373</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="T3" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="U3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="V3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="W3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="X3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="Y3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="Z3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AA3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AC3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="AD3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AE3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AF3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AG3" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="AH3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AI3" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="AJ3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="AL3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="AM3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="AN3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AO3" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="AP3" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="AQ3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="M3" s="2" t="s">
+      <c r="AR3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AS3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AT3" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="AU3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AV3" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="AW3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AX3" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="AY3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AZ3" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="BA3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="BB3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="BC3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BD3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="BE3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="BF3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BG3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="BH3" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="BI3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="BJ3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BK3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BL3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BM3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="BN3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="BO3" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="BP3" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="Q3" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="X3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="Y3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="Z3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AB3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AC3" s="2" t="s">
+      <c r="BQ3" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="BR3" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="BS3" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="AD3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AE3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AF3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AG3" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="AH3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AI3" s="2" t="s">
+      <c r="BT3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BU3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="BV3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BW3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BX3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="BY3" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="BZ3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="CA3" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="CB3" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="CC3" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="CD3" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="CE3" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="CF3" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="CG3" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="CH3" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="CI3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="CJ3" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="CK3" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="CL3" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="CM3" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="AJ3" s="2" t="s">
+      <c r="CN3" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="CO3" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="CP3" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="CQ3" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="CR3" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="CS3" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="CT3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="CU3" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="CV3" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="CW3" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="CX3" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="CY3" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="CZ3" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="DA3" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="DB3" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="DC3" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="DD3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="DE3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="DF3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="DG3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="DH3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="DI3" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="AC6" s="3">
+        <v>1</v>
+      </c>
+      <c r="AO6" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="AT6" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="AY6" s="3">
+        <v>1</v>
+      </c>
+      <c r="AZ6" s="3">
+        <v>1</v>
+      </c>
+      <c r="BD6" s="3">
+        <v>1</v>
+      </c>
+      <c r="CB6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="CG6" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="CH6" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="CI6" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="CN6" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="CR6" s="3">
+        <v>9999</v>
+      </c>
+      <c r="CY6" s="3" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="Q7" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="AC7" s="3">
+        <v>1</v>
+      </c>
+      <c r="AF7" s="3">
+        <v>1</v>
+      </c>
+      <c r="AV7" s="3">
+        <v>20</v>
+      </c>
+      <c r="BD7" s="3">
+        <v>1</v>
+      </c>
+      <c r="CU7" s="3" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="AC8" s="3">
+        <v>1</v>
+      </c>
+      <c r="AT8" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="BD8" s="3">
+        <v>1</v>
+      </c>
+      <c r="CU8" s="3" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="AC9" s="3">
+        <v>1</v>
+      </c>
+      <c r="AT9" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="BD9" s="3">
+        <v>99</v>
+      </c>
+      <c r="CM9" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="CN9" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="CR9" s="3">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="I10" s="3">
+        <v>1</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="AC10" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG10" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="AN10" s="3">
+        <v>1</v>
+      </c>
+      <c r="AT10" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="BD10" s="3">
+        <v>99</v>
+      </c>
+      <c r="CN10" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="CR10" s="3">
+        <v>1</v>
+      </c>
+      <c r="DD10" s="3">
+        <v>1</v>
+      </c>
+      <c r="DG10" s="3">
+        <v>1</v>
+      </c>
+      <c r="DH10" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="I11" s="3">
+        <v>1</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="AC11" s="3">
+        <v>1</v>
+      </c>
+      <c r="AF11" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG11" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="AN11" s="3">
+        <v>1</v>
+      </c>
+      <c r="BD11" s="3">
+        <v>1</v>
+      </c>
+      <c r="CN11" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="CR11" s="3">
+        <v>9999</v>
+      </c>
+      <c r="DD11" s="3">
+        <v>1</v>
+      </c>
+      <c r="DG11" s="3">
+        <v>1</v>
+      </c>
+      <c r="DH11" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="G13" s="3">
         <v>3</v>
       </c>
-      <c r="AK3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="AL3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="AM3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="AN3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AO3" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="AP3" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="AQ3" s="2" t="s">
+      <c r="J13" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="AB13" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC13" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG13" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="AO13" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="AT13" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="AY13" s="3">
+        <v>1</v>
+      </c>
+      <c r="AZ13" s="3">
+        <v>1</v>
+      </c>
+      <c r="BD13" s="3">
+        <v>1</v>
+      </c>
+      <c r="BO13" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="BT13" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="BU13" s="3">
+        <v>1</v>
+      </c>
+      <c r="BV13" s="3">
+        <v>0</v>
+      </c>
+      <c r="BW13" s="3">
+        <v>5</v>
+      </c>
+      <c r="BX13" s="3">
+        <v>1</v>
+      </c>
+      <c r="BY13" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="CN13" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="CO13" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="AC14" s="3">
+        <v>1</v>
+      </c>
+      <c r="AO14" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="AT14" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="AY14" s="3">
+        <v>1</v>
+      </c>
+      <c r="AZ14" s="3">
+        <v>1</v>
+      </c>
+      <c r="BD14" s="3">
+        <v>1</v>
+      </c>
+      <c r="CB14" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="CG14" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="CH14" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="CI14" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="CN14" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="CR14" s="3">
+        <v>9999</v>
+      </c>
+      <c r="CY14" s="3" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="G16" s="3">
+        <v>3</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="Q16" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="AC16" s="3">
+        <v>1</v>
+      </c>
+      <c r="AO16" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="AV16" s="3">
+        <v>20</v>
+      </c>
+      <c r="AY16" s="3">
+        <v>1</v>
+      </c>
+      <c r="AZ16" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="BD16" s="3">
+        <v>99</v>
+      </c>
+      <c r="BT16" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="BV16" s="3">
+        <v>30</v>
+      </c>
+      <c r="BW16" s="3">
+        <v>20</v>
+      </c>
+      <c r="BX16" s="3">
+        <v>3</v>
+      </c>
+      <c r="BY16" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="CB16" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="CG16" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="CH16" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="CI16" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="CN16" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="CO16" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="CR16" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="G18" s="3">
+        <v>3</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="AC18" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG18" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="BD18" s="3">
+        <v>1</v>
+      </c>
+      <c r="BO18" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="BT18" s="3">
+        <v>30</v>
+      </c>
+      <c r="BV18" s="3">
+        <v>45</v>
+      </c>
+      <c r="BW18" s="3">
+        <v>50</v>
+      </c>
+      <c r="BX18" s="3">
+        <v>1</v>
+      </c>
+      <c r="BY18" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="CN18" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="CO18" s="3">
+        <v>-0.4</v>
+      </c>
+      <c r="CR18" s="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="AC19" s="3">
+        <v>1</v>
+      </c>
+      <c r="AF19" s="3">
+        <v>1</v>
+      </c>
+      <c r="AH19" s="3">
+        <v>1</v>
+      </c>
+      <c r="BD19" s="3">
+        <v>99</v>
+      </c>
+      <c r="CU19" s="3" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="AC20" s="3">
         <v>2</v>
       </c>
-      <c r="AR3" s="2" t="s">
+      <c r="AF20" s="3">
+        <v>1</v>
+      </c>
+      <c r="AH20" s="3">
+        <v>1</v>
+      </c>
+      <c r="BD20" s="3">
+        <v>99</v>
+      </c>
+      <c r="CU20" s="3" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="AC21" s="3">
         <v>2</v>
       </c>
-      <c r="AS3" s="2" t="s">
+      <c r="AF21" s="3">
+        <v>1</v>
+      </c>
+      <c r="BD21" s="3">
+        <v>1</v>
+      </c>
+      <c r="CN21" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="CR21" s="3">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="AC22" s="3">
         <v>2</v>
       </c>
-      <c r="AT3" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="AU3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AV3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AW3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AX3" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="AY3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AZ3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BA3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="BB3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="BC3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BD3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="BE3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="BF3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BG3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="BH3" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="BI3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="BJ3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BK3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BL3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BM3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="BN3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="BO3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="BP3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="BQ3" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="BR3" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="BS3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BT3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BU3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="BV3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BW3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BX3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="BY3" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="BZ3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="CA3" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="CB3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="CC3" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="CD3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="CE3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="CF3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="CG3" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="CH3" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="CI3" s="2" t="s">
+      <c r="AV22" s="3">
+        <v>20</v>
+      </c>
+      <c r="BD22" s="3">
+        <v>99</v>
+      </c>
+      <c r="CU22" s="3" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="AC23" s="3">
         <v>2</v>
       </c>
-      <c r="CJ3" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="CK3" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="CL3" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="CM3" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="CN3" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="CO3" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="CP3" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="CQ3" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="CR3" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="CS3" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="CT3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="CU3" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="CV3" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="CW3" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="CX3" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="CY3" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="CZ3" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="DA3" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="DB3" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="DC3" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="DD3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="DE3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="DF3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="DG3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="DH3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="DI3" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="P6" s="2" t="s">
+      <c r="AF23" s="3">
+        <v>1</v>
+      </c>
+      <c r="BD23" s="3">
+        <v>99</v>
+      </c>
+      <c r="CU23" s="3" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="AC24" s="3">
+        <v>1</v>
+      </c>
+      <c r="AF24" s="3">
+        <v>1</v>
+      </c>
+      <c r="AT24" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="BD24" s="3">
+        <v>99</v>
+      </c>
+      <c r="CU24" s="3" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="Q25" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="AC25" s="3">
+        <v>1</v>
+      </c>
+      <c r="AF25" s="3">
+        <v>1</v>
+      </c>
+      <c r="AT25" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="BD25" s="3">
+        <v>99</v>
+      </c>
+      <c r="CU25" s="3" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="AC6" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO6" s="2" t="s">
+      <c r="J27" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="K27" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="AT6" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="AY6" s="2">
-        <v>1</v>
-      </c>
-      <c r="AZ6" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD6" s="2">
-        <v>1</v>
-      </c>
-      <c r="CB6" s="2" t="s">
+      <c r="AC27" s="3">
+        <v>1</v>
+      </c>
+      <c r="AO27" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="AT27" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="AY27" s="3">
+        <v>1</v>
+      </c>
+      <c r="AZ27" s="3">
+        <v>1</v>
+      </c>
+      <c r="BD27" s="3">
+        <v>3</v>
+      </c>
+      <c r="CB27" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="CG6" s="2" t="s">
+      <c r="CG27" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="CH27" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="CI27" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="CN27" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="CR27" s="3">
+        <v>9999</v>
+      </c>
+      <c r="CY27" s="3" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="Q28" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="AC28" s="3">
+        <v>1</v>
+      </c>
+      <c r="AO28" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="CH6" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="CI6" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="CN6" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="CR6" s="2">
-        <v>9999</v>
-      </c>
-      <c r="CY6" s="2" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="AC7" s="2">
-        <v>1</v>
-      </c>
-      <c r="AF7" s="2">
-        <v>1</v>
-      </c>
-      <c r="AV7" s="2">
+      <c r="AV28" s="3">
         <v>20</v>
       </c>
-      <c r="BD7" s="2">
-        <v>1</v>
-      </c>
-      <c r="CU7" s="2" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="AC8" s="2">
-        <v>1</v>
-      </c>
-      <c r="AT8" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="BD8" s="2">
-        <v>1</v>
-      </c>
-      <c r="CU8" s="2" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="AC9" s="2">
-        <v>1</v>
-      </c>
-      <c r="AT9" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="BD9" s="2">
+      <c r="BD28" s="3">
+        <v>1</v>
+      </c>
+      <c r="BS28" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="CN28" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="CR28" s="3">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="AC29" s="3">
+        <v>2</v>
+      </c>
+      <c r="AV29" s="3">
+        <v>20</v>
+      </c>
+      <c r="AX29" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="AZ29" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="BD29" s="3">
         <v>99</v>
       </c>
-      <c r="CM9" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="CN9" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="CR9" s="2">
-        <v>9999</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="I10" s="2">
-        <v>1</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="Q10" s="2" t="s">
+      <c r="CM29" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="CY29" s="3" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="Q30" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="AC30" s="3">
+        <v>1</v>
+      </c>
+      <c r="AN30" s="3">
+        <v>1</v>
+      </c>
+      <c r="AV30" s="3">
+        <v>20</v>
+      </c>
+      <c r="BD30" s="3">
+        <v>99</v>
+      </c>
+      <c r="BT30" s="3">
+        <v>30</v>
+      </c>
+      <c r="CU30" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="DD30" s="3">
+        <v>1</v>
+      </c>
+      <c r="DG30" s="3">
+        <v>1</v>
+      </c>
+      <c r="DH30" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="Q31" s="3" t="s">
         <v>417</v>
       </c>
-      <c r="AC10" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG10" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="AN10" s="2">
-        <v>1</v>
-      </c>
-      <c r="AT10" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="BD10" s="2">
+      <c r="AC31" s="3">
+        <v>1</v>
+      </c>
+      <c r="AV31" s="3">
+        <v>20</v>
+      </c>
+      <c r="BD31" s="3">
         <v>99</v>
       </c>
-      <c r="CN10" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="CR10" s="2">
-        <v>1</v>
-      </c>
-      <c r="DD10" s="2">
-        <v>1</v>
-      </c>
-      <c r="DG10" s="2">
-        <v>1</v>
-      </c>
-      <c r="DH10" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="I11" s="2">
-        <v>1</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="AC11" s="2">
-        <v>1</v>
-      </c>
-      <c r="AF11" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG11" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="AN11" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD11" s="2">
-        <v>1</v>
-      </c>
-      <c r="CN11" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="CR11" s="2">
-        <v>9999</v>
-      </c>
-      <c r="DD11" s="2">
-        <v>1</v>
-      </c>
-      <c r="DG11" s="2">
-        <v>1</v>
-      </c>
-      <c r="DH11" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="G13" s="2">
-        <v>3</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="AB13" s="2">
-        <v>1</v>
-      </c>
-      <c r="AC13" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG13" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="AO13" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="AT13" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="AY13" s="2">
-        <v>1</v>
-      </c>
-      <c r="AZ13" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD13" s="2">
-        <v>1</v>
-      </c>
-      <c r="BO13" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="BT13" s="2">
+      <c r="BS31" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="CN31" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="CR31" s="3">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="CL669" s="3">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="CL671" s="3">
         <v>0.2</v>
       </c>
-      <c r="BU13" s="2">
-        <v>1</v>
-      </c>
-      <c r="BV13" s="2">
-        <v>0</v>
-      </c>
-      <c r="BW13" s="2">
-        <v>5</v>
-      </c>
-      <c r="BX13" s="2">
-        <v>1</v>
-      </c>
-      <c r="BY13" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="CN13" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="CO13" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="O14" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="AC14" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO14" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="AT14" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="AY14" s="2">
-        <v>1</v>
-      </c>
-      <c r="AZ14" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD14" s="2">
-        <v>1</v>
-      </c>
-      <c r="CB14" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="CG14" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="CH14" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="CI14" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="CN14" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="CR14" s="2">
-        <v>9999</v>
-      </c>
-      <c r="CY14" s="2" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="G16" s="2">
-        <v>3</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="Q16" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="AC16" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO16" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="AV16" s="2">
-        <v>20</v>
-      </c>
-      <c r="AY16" s="2">
-        <v>1</v>
-      </c>
-      <c r="AZ16" s="2">
-        <v>2.5</v>
-      </c>
-      <c r="BD16" s="2">
-        <v>99</v>
-      </c>
-      <c r="BT16" s="2">
+    </row>
+    <row r="672">
+      <c r="CL672" s="3">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="CL674" s="3">
         <v>0.2</v>
       </c>
-      <c r="BV16" s="2">
-        <v>30</v>
-      </c>
-      <c r="BW16" s="2">
-        <v>20</v>
-      </c>
-      <c r="BX16" s="2">
-        <v>3</v>
-      </c>
-      <c r="BY16" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="CB16" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="CG16" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="CH16" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="CI16" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="CN16" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="CO16" s="2">
-        <v>0.3</v>
-      </c>
-      <c r="CR16" s="2">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="G18" s="2">
-        <v>3</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="AC18" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG18" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="BD18" s="2">
-        <v>1</v>
-      </c>
-      <c r="BO18" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="BT18" s="2">
-        <v>30</v>
-      </c>
-      <c r="BV18" s="2">
-        <v>45</v>
-      </c>
-      <c r="BW18" s="2">
-        <v>50</v>
-      </c>
-      <c r="BX18" s="2">
-        <v>1</v>
-      </c>
-      <c r="BY18" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="CN18" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="CO18" s="2">
-        <v>-0.4</v>
-      </c>
-      <c r="CR18" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="AC19" s="2">
-        <v>1</v>
-      </c>
-      <c r="AF19" s="2">
-        <v>1</v>
-      </c>
-      <c r="AH19" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD19" s="2">
-        <v>99</v>
-      </c>
-      <c r="CU19" s="2" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="L20" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="O20" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="AC20" s="2">
-        <v>2</v>
-      </c>
-      <c r="AF20" s="2">
-        <v>1</v>
-      </c>
-      <c r="AH20" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD20" s="2">
-        <v>99</v>
-      </c>
-      <c r="CU20" s="2" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="L21" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="O21" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="AC21" s="2">
-        <v>2</v>
-      </c>
-      <c r="AF21" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD21" s="2">
-        <v>1</v>
-      </c>
-      <c r="CN21" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="CR21" s="2">
-        <v>9999</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="L22" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="AC22" s="2">
-        <v>2</v>
-      </c>
-      <c r="AV22" s="2">
-        <v>20</v>
-      </c>
-      <c r="BD22" s="2">
-        <v>99</v>
-      </c>
-      <c r="CU22" s="2" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="L23" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="AC23" s="2">
-        <v>2</v>
-      </c>
-      <c r="AF23" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD23" s="2">
-        <v>99</v>
-      </c>
-      <c r="CU23" s="2" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="L24" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="Q24" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="AC24" s="2">
-        <v>1</v>
-      </c>
-      <c r="AF24" s="2">
-        <v>1</v>
-      </c>
-      <c r="AT24" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="BD24" s="2">
-        <v>99</v>
-      </c>
-      <c r="CU24" s="2" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="L25" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="Q25" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="AC25" s="2">
-        <v>1</v>
-      </c>
-      <c r="AF25" s="2">
-        <v>1</v>
-      </c>
-      <c r="AT25" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="BD25" s="2">
-        <v>99</v>
-      </c>
-      <c r="CU25" s="2" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="AC27" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO27" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="AT27" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="AY27" s="2">
-        <v>1</v>
-      </c>
-      <c r="AZ27" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD27" s="2">
-        <v>3</v>
-      </c>
-      <c r="CB27" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="CG27" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="CH27" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="CI27" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="CN27" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="CR27" s="2">
-        <v>9999</v>
-      </c>
-      <c r="CY27" s="2" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="Q28" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="AC28" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO28" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="AV28" s="2">
-        <v>20</v>
-      </c>
-      <c r="BD28" s="2">
-        <v>1</v>
-      </c>
-      <c r="BS28" s="2">
-        <v>0.01</v>
-      </c>
-      <c r="CN28" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="CR28" s="2">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="Q29" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="AC29" s="2">
-        <v>2</v>
-      </c>
-      <c r="AV29" s="2">
-        <v>20</v>
-      </c>
-      <c r="AX29" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="AZ29" s="2">
-        <v>0.8</v>
-      </c>
-      <c r="BD29" s="2">
-        <v>99</v>
-      </c>
-      <c r="CM29" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="CY29" s="2" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="K30" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="Q30" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="AC30" s="2">
-        <v>1</v>
-      </c>
-      <c r="AN30" s="2">
-        <v>1</v>
-      </c>
-      <c r="AV30" s="2">
-        <v>20</v>
-      </c>
-      <c r="BD30" s="2">
-        <v>99</v>
-      </c>
-      <c r="BT30" s="2">
-        <v>30</v>
-      </c>
-      <c r="CU30" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="DD30" s="2">
-        <v>1</v>
-      </c>
-      <c r="DG30" s="2">
-        <v>1</v>
-      </c>
-      <c r="DH30" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="K31" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="Q31" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="AC31" s="2">
-        <v>1</v>
-      </c>
-      <c r="AV31" s="2">
-        <v>20</v>
-      </c>
-      <c r="BD31" s="2">
-        <v>99</v>
-      </c>
-      <c r="BS31" s="2">
-        <v>0.01</v>
-      </c>
-      <c r="CN31" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="CR31" s="2">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="669">
-      <c r="CL669" s="2">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="671">
-      <c r="CL671" s="2">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="672">
-      <c r="CL672" s="2">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="674">
-      <c r="CL674" s="2">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="681">
-      <c r="CL681" s="2">
+      <c r="CL681" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="683">
-      <c r="CL683" s="2">
+      <c r="CL683" s="3">
         <v>0.4</v>
       </c>
     </row>
     <row r="684">
-      <c r="CL684" s="2">
+      <c r="CL684" s="3">
         <v>0.6</v>
       </c>
     </row>
     <row r="687">
-      <c r="CL687" s="2">
+      <c r="CL687" s="3">
         <v>0.5</v>
       </c>
     </row>
     <row r="688">
-      <c r="CL688" s="2">
+      <c r="CL688" s="3">
         <v>0.667</v>
       </c>
     </row>
     <row r="689">
-      <c r="CL689" s="2">
+      <c r="CL689" s="3">
         <v>0.2</v>
       </c>
     </row>
@@ -5683,262 +5716,262 @@
   <dimension ref="A1:Q15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.08203125" customWidth="1" style="2"/>
-    <col min="2" max="2" width="31.25" customWidth="1" style="2"/>
-    <col min="3" max="6" width="9" customWidth="1" style="2"/>
-    <col min="7" max="7" width="18.75" customWidth="1" style="2"/>
-    <col min="8" max="8" width="15" customWidth="1" style="2"/>
-    <col min="9" max="13" width="9" customWidth="1" style="2"/>
-    <col min="14" max="14" width="16.08203125" customWidth="1" style="2"/>
-    <col min="15" max="15" width="9.5" customWidth="1" style="2"/>
-    <col min="16" max="16" width="22.1640625" customWidth="1" style="2"/>
-    <col min="17" max="17" width="12.83203125" customWidth="1" style="2"/>
+    <col min="1" max="1" width="18.08203125" customWidth="1" style="3"/>
+    <col min="2" max="2" width="31.25" customWidth="1" style="3"/>
+    <col min="3" max="6" width="9" customWidth="1" style="3"/>
+    <col min="7" max="7" width="18.75" customWidth="1" style="3"/>
+    <col min="8" max="8" width="15" customWidth="1" style="3"/>
+    <col min="9" max="13" width="9" customWidth="1" style="3"/>
+    <col min="14" max="14" width="16.08203125" customWidth="1" style="3"/>
+    <col min="15" max="15" width="9.5" customWidth="1" style="3"/>
+    <col min="16" max="16" width="22.1640625" customWidth="1" style="3"/>
+    <col min="17" max="17" width="12.83203125" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="G1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>470</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>471</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>472</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="M1" s="3" t="s">
         <v>476</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>477</v>
       </c>
+      <c r="O1" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>479</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="G2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>480</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>483</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="J2" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="L2" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="M2" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="O2" s="2" t="s">
+      <c r="M2" s="3" t="s">
         <v>487</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="N2" s="3" t="s">
         <v>488</v>
       </c>
-      <c r="Q2" s="2" t="s">
-        <v>357</v>
+      <c r="O2" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>132</v>
+      <c r="L3" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>489</v>
+      <c r="A5" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>491</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="H6" s="2">
-        <v>1</v>
-      </c>
-      <c r="J6" s="2" t="s">
+      <c r="A6" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="H6" s="3">
+        <v>1</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="Q6" s="3" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="I9" s="3">
+        <v>1</v>
+      </c>
+      <c r="K9" s="3">
+        <v>99999</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>491</v>
       </c>
-      <c r="Q6" s="2" t="s">
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>492</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="I9" s="2">
-        <v>1</v>
-      </c>
-      <c r="K9" s="2">
-        <v>99999</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="Q12" s="2" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="H14" s="2">
-        <v>1</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="Q14" s="2" t="s">
-        <v>500</v>
+      <c r="H14" s="3">
+        <v>1</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>502</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>489</v>
+      <c r="A15" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>491</v>
       </c>
     </row>
   </sheetData>
@@ -5954,57 +5987,57 @@
   <dimension ref="A1:D4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" customWidth="1" style="2"/>
-    <col min="2" max="2" width="11.25" customWidth="1" style="2"/>
-    <col min="3" max="3" width="9" customWidth="1" style="2"/>
-    <col min="4" max="4" width="27.5" customWidth="1" style="2"/>
+    <col min="1" max="1" width="11.33203125" customWidth="1" style="3"/>
+    <col min="2" max="2" width="11.25" customWidth="1" style="3"/>
+    <col min="3" max="3" width="9" customWidth="1" style="3"/>
+    <col min="4" max="4" width="27.5" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>501</v>
+      <c r="C1" s="3" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>357</v>
+      <c r="C2" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>132</v>
+      <c r="C3" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>505</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>507</v>
       </c>
     </row>
   </sheetData>
@@ -6020,126 +6053,126 @@
   <dimension ref="A1:J5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.25" customWidth="1" style="2"/>
-    <col min="2" max="2" width="9" customWidth="1" style="2"/>
-    <col min="3" max="3" width="27.25" customWidth="1" style="2"/>
-    <col min="4" max="4" width="10.83203125" customWidth="1" style="2"/>
-    <col min="5" max="10" width="9" customWidth="1" style="2"/>
+    <col min="1" max="1" width="15.25" customWidth="1" style="3"/>
+    <col min="2" max="2" width="9" customWidth="1" style="3"/>
+    <col min="3" max="3" width="27.25" customWidth="1" style="3"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1" style="3"/>
+    <col min="5" max="10" width="9" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="I1" s="2" t="s">
-        <v>242</v>
+      <c r="I1" s="3" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="D2" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="H2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>509</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>357</v>
+      <c r="G2" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="F3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>132</v>
+      <c r="F3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="E4" s="2">
+      <c r="A4" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="E4" s="3">
         <v>10</v>
       </c>
-      <c r="H4" s="2">
-        <v>1</v>
-      </c>
-      <c r="I4" s="2" t="s">
+      <c r="H4" s="3">
+        <v>1</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>512</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>513</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="E5" s="2">
+      <c r="E5" s="3">
         <v>10</v>
       </c>
-      <c r="H5" s="2">
-        <v>1</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>513</v>
+      <c r="H5" s="3">
+        <v>1</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>515</v>
       </c>
     </row>
   </sheetData>
@@ -6155,123 +6188,123 @@
   <dimension ref="A1:L3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.25" customWidth="1" style="2"/>
-    <col min="2" max="2" width="28" customWidth="1" style="2"/>
-    <col min="3" max="4" width="10.08203125" customWidth="1" style="2"/>
-    <col min="5" max="10" width="11.25" customWidth="1" style="2"/>
-    <col min="11" max="11" width="6.33203125" customWidth="1" style="2"/>
-    <col min="12" max="12" width="9" customWidth="1" style="2"/>
+    <col min="1" max="1" width="15.25" customWidth="1" style="3"/>
+    <col min="2" max="2" width="28" customWidth="1" style="3"/>
+    <col min="3" max="4" width="10.08203125" customWidth="1" style="3"/>
+    <col min="5" max="10" width="11.25" customWidth="1" style="3"/>
+    <col min="11" max="11" width="6.33203125" customWidth="1" style="3"/>
+    <col min="12" max="12" width="9" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>516</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>517</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>518</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>519</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>520</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>521</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>522</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>523</v>
       </c>
+      <c r="K1" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>525</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>526</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>527</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>528</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>529</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>530</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>531</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>532</v>
       </c>
-      <c r="K2" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="L2" s="2" t="s">
+      <c r="I2" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="L2" s="3" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H3" s="2" t="s">
+      <c r="L3" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -6288,45 +6321,45 @@
   <dimension ref="A2:J3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.08203125" customWidth="1" style="2"/>
-    <col min="2" max="2" width="16.25" customWidth="1" style="2"/>
-    <col min="3" max="3" width="16.33203125" customWidth="1" style="2"/>
-    <col min="4" max="4" width="47.83203125" customWidth="1" style="2"/>
-    <col min="5" max="5" width="10.25" customWidth="1" style="2"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1" style="2"/>
-    <col min="7" max="9" width="9" customWidth="1" style="2"/>
-    <col min="10" max="10" width="11.83203125" customWidth="1" style="2"/>
+    <col min="1" max="1" width="19.08203125" customWidth="1" style="3"/>
+    <col min="2" max="2" width="16.25" customWidth="1" style="3"/>
+    <col min="3" max="3" width="16.33203125" customWidth="1" style="3"/>
+    <col min="4" max="4" width="47.83203125" customWidth="1" style="3"/>
+    <col min="5" max="5" width="10.25" customWidth="1" style="3"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1" style="3"/>
+    <col min="7" max="9" width="9" customWidth="1" style="3"/>
+    <col min="10" max="10" width="11.83203125" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="B2" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="D2" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="J2" s="2" t="s">
+      <c r="G2" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>58</v>
       </c>
     </row>
@@ -6344,22 +6377,22 @@
         <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -6374,128 +6407,128 @@
   <dimension ref="A1:I4"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" customWidth="1" style="2"/>
-    <col min="2" max="2" width="13.83203125" customWidth="1" style="2"/>
-    <col min="3" max="3" width="20.58203125" customWidth="1" style="2"/>
-    <col min="4" max="4" width="39.6640625" customWidth="1" style="2"/>
-    <col min="5" max="5" width="37.58203125" customWidth="1" style="2"/>
-    <col min="6" max="6" width="39.5" customWidth="1" style="2"/>
-    <col min="7" max="7" width="38.58203125" customWidth="1" style="2"/>
-    <col min="8" max="8" width="32.25" customWidth="1" style="2"/>
-    <col min="9" max="9" width="39.9140625" customWidth="1" style="2"/>
+    <col min="1" max="1" width="8.6640625" customWidth="1" style="3"/>
+    <col min="2" max="2" width="13.83203125" customWidth="1" style="3"/>
+    <col min="3" max="3" width="20.58203125" customWidth="1" style="3"/>
+    <col min="4" max="4" width="39.6640625" customWidth="1" style="3"/>
+    <col min="5" max="5" width="37.58203125" customWidth="1" style="3"/>
+    <col min="6" max="6" width="39.5" customWidth="1" style="3"/>
+    <col min="7" max="7" width="38.58203125" customWidth="1" style="3"/>
+    <col min="8" max="8" width="32.25" customWidth="1" style="3"/>
+    <col min="9" max="9" width="39.9140625" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>540</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>541</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>542</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>543</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>544</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>545</v>
       </c>
+      <c r="H1" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>547</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>548</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>550</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>551</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>552</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>553</v>
       </c>
+      <c r="H2" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>555</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="B3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="2">
-        <v>1</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="F4" s="2" t="s">
+      <c r="C4" s="3">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>556</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>557</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>558</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="G4" s="3" t="s">
         <v>559</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>561</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Diy优胜/萃儿.xlsx
+++ b/Excel/Diy优胜/萃儿.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Diy优胜\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{866C0311-E00B-46F3-A8DB-DDDBAA396B30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0176D519-F4D8-4088-8F5D-24CA0E561379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -24,9 +24,9 @@
     <sheet name="SpineData" sheetId="12" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="OLE_LINK2" localSheetId="2">'SkillData'!$E$13</definedName>
+    <definedName name="OLE_LINK2" localSheetId="2">SkillData!$E$13</definedName>
   </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -326,7 +326,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="562">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="949" uniqueCount="562">
   <si>
     <t>Id</t>
   </si>
@@ -2018,8 +2018,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2032,6 +2031,19 @@
       <name val="宋体"/>
       <family val="3"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2059,23 +2071,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2380,37 +2386,36 @@
   <dimension ref="A2:B4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="9" customWidth="1" style="3"/>
+    <col min="1" max="2" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="s">
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" t="s">
         <v>4</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -2419,1207 +2424,933 @@
   <dimension ref="A1:BX7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.58203125" customWidth="1" style="2"/>
-    <col min="2" max="2" width="9" customWidth="1" style="2"/>
-    <col min="3" max="3" width="9" customWidth="1" style="2"/>
-    <col min="4" max="4" width="8.58203125" customWidth="1" style="2"/>
-    <col min="5" max="5" width="8.58203125" customWidth="1" style="2"/>
-    <col min="6" max="6" width="19.58203125" customWidth="1" style="2"/>
-    <col min="7" max="7" width="8.25" customWidth="1" style="2"/>
-    <col min="8" max="8" width="9" customWidth="1" style="2"/>
-    <col min="9" max="9" width="9" customWidth="1" style="2"/>
-    <col min="10" max="10" width="9" customWidth="1" style="2"/>
-    <col min="11" max="11" width="9" customWidth="1" style="2"/>
-    <col min="12" max="12" width="6" customWidth="1" style="2"/>
-    <col min="13" max="13" width="4.08203125" customWidth="1" style="2"/>
-    <col min="14" max="14" width="5.58203125" customWidth="1" style="2"/>
-    <col min="15" max="15" width="4" customWidth="1" style="2"/>
-    <col min="16" max="16" width="7.75" customWidth="1" style="2"/>
-    <col min="17" max="17" width="10.83203125" customWidth="1" style="2"/>
-    <col min="18" max="18" width="3.83203125" customWidth="1" style="2"/>
-    <col min="19" max="19" width="3.83203125" customWidth="1" style="2"/>
-    <col min="20" max="20" width="3.58203125" customWidth="1" style="2"/>
-    <col min="21" max="21" width="3.58203125" customWidth="1" style="2"/>
-    <col min="22" max="22" width="10.25" customWidth="1" style="2"/>
-    <col min="23" max="23" width="9.58203125" customWidth="1" style="2"/>
-    <col min="24" max="24" width="10.75" customWidth="1" style="2"/>
-    <col min="25" max="25" width="12.83203125" customWidth="1" style="2"/>
-    <col min="26" max="26" width="13.08203125" customWidth="1" style="2"/>
-    <col min="27" max="27" width="10.75" customWidth="1" style="2"/>
-    <col min="28" max="28" width="9" customWidth="1" style="2"/>
-    <col min="29" max="29" width="9" customWidth="1" style="2"/>
-    <col min="30" max="30" width="8" customWidth="1" style="2"/>
-    <col min="31" max="31" width="17.08203125" customWidth="1" style="2"/>
-    <col min="32" max="32" width="9" customWidth="1" style="2"/>
-    <col min="33" max="33" width="9" customWidth="1" style="2"/>
-    <col min="34" max="34" width="9.75" customWidth="1" style="2"/>
-    <col min="35" max="35" width="7.83203125" customWidth="1" style="2"/>
-    <col min="36" max="36" width="15.83203125" customWidth="1" style="2"/>
-    <col min="37" max="37" width="13.83203125" customWidth="1" style="2"/>
-    <col min="38" max="38" width="63.75" customWidth="1" style="2"/>
-    <col min="39" max="39" width="20.1640625" customWidth="1" style="2"/>
-    <col min="40" max="40" width="9.83203125" customWidth="1" style="2"/>
-    <col min="41" max="41" width="9.83203125" customWidth="1" style="2"/>
-    <col min="42" max="42" width="9" customWidth="1" style="2"/>
-    <col min="43" max="43" width="9" customWidth="1" style="2"/>
-    <col min="44" max="44" width="9" customWidth="1" style="2"/>
-    <col min="45" max="45" width="9" customWidth="1" style="2"/>
-    <col min="46" max="46" width="12.5" customWidth="1" style="2"/>
-    <col min="47" max="47" width="9" customWidth="1" style="2"/>
-    <col min="48" max="48" width="9" customWidth="1" style="2"/>
-    <col min="49" max="49" width="9" customWidth="1" style="2"/>
-    <col min="50" max="50" width="9" customWidth="1" style="2"/>
-    <col min="51" max="51" width="9" customWidth="1" style="2"/>
-    <col min="52" max="52" width="9" customWidth="1" style="2"/>
-    <col min="53" max="53" width="24.33203125" customWidth="1" style="2"/>
-    <col min="54" max="54" width="9" customWidth="1" style="2"/>
-    <col min="55" max="55" width="17.75" customWidth="1" style="2"/>
-    <col min="56" max="56" width="7.83203125" customWidth="1" style="2"/>
-    <col min="57" max="57" width="9" customWidth="1" style="2"/>
-    <col min="58" max="58" width="9" customWidth="1" style="2"/>
-    <col min="59" max="59" width="24.25" customWidth="1" style="2"/>
-    <col min="60" max="60" width="13.25" customWidth="1" style="2"/>
-    <col min="61" max="61" width="16.08203125" customWidth="1" style="2"/>
-    <col min="62" max="62" width="8" customWidth="1" style="2"/>
-    <col min="63" max="63" width="9" customWidth="1" style="2"/>
-    <col min="64" max="64" width="9" customWidth="1" style="2"/>
-    <col min="65" max="65" width="9" customWidth="1" style="2"/>
-    <col min="66" max="66" width="9" customWidth="1" style="2"/>
-    <col min="67" max="67" width="39.58203125" customWidth="1" style="2"/>
-    <col min="68" max="68" width="9" customWidth="1" style="2"/>
-    <col min="69" max="69" width="14" customWidth="1" style="2"/>
-    <col min="70" max="70" width="14.83203125" customWidth="1" style="2"/>
-    <col min="71" max="71" width="14" customWidth="1" style="2"/>
-    <col min="72" max="72" width="14" customWidth="1" style="2"/>
-    <col min="73" max="73" width="14" customWidth="1" style="2"/>
-    <col min="74" max="74" width="14" customWidth="1" style="2"/>
-    <col min="75" max="75" width="9" customWidth="1" style="2"/>
-    <col min="76" max="76" width="19.1640625" customWidth="1" style="2"/>
+    <col min="1" max="1" width="22.58203125" customWidth="1"/>
+    <col min="2" max="3" width="9" customWidth="1"/>
+    <col min="4" max="5" width="8.58203125" customWidth="1"/>
+    <col min="6" max="6" width="19.58203125" customWidth="1"/>
+    <col min="7" max="7" width="8.25" customWidth="1"/>
+    <col min="8" max="11" width="9" customWidth="1"/>
+    <col min="12" max="12" width="6" customWidth="1"/>
+    <col min="13" max="13" width="4.08203125" customWidth="1"/>
+    <col min="14" max="14" width="5.58203125" customWidth="1"/>
+    <col min="15" max="15" width="4" customWidth="1"/>
+    <col min="16" max="16" width="7.75" customWidth="1"/>
+    <col min="17" max="17" width="10.83203125" customWidth="1"/>
+    <col min="18" max="19" width="3.83203125" customWidth="1"/>
+    <col min="20" max="21" width="3.58203125" customWidth="1"/>
+    <col min="22" max="22" width="10.25" customWidth="1"/>
+    <col min="23" max="23" width="9.58203125" customWidth="1"/>
+    <col min="24" max="24" width="10.75" customWidth="1"/>
+    <col min="25" max="25" width="12.83203125" customWidth="1"/>
+    <col min="26" max="26" width="13.08203125" customWidth="1"/>
+    <col min="27" max="27" width="10.75" customWidth="1"/>
+    <col min="28" max="29" width="9" customWidth="1"/>
+    <col min="30" max="30" width="8" customWidth="1"/>
+    <col min="31" max="31" width="17.08203125" customWidth="1"/>
+    <col min="32" max="33" width="9" customWidth="1"/>
+    <col min="34" max="34" width="9.75" customWidth="1"/>
+    <col min="35" max="35" width="7.83203125" customWidth="1"/>
+    <col min="36" max="36" width="15.83203125" customWidth="1"/>
+    <col min="37" max="37" width="13.83203125" customWidth="1"/>
+    <col min="38" max="38" width="63.75" customWidth="1"/>
+    <col min="39" max="39" width="20.1640625" customWidth="1"/>
+    <col min="40" max="41" width="9.83203125" customWidth="1"/>
+    <col min="42" max="45" width="9" customWidth="1"/>
+    <col min="46" max="46" width="12.5" customWidth="1"/>
+    <col min="47" max="52" width="9" customWidth="1"/>
+    <col min="53" max="53" width="24.33203125" customWidth="1"/>
+    <col min="54" max="54" width="9" customWidth="1"/>
+    <col min="55" max="55" width="17.75" customWidth="1"/>
+    <col min="56" max="56" width="7.83203125" customWidth="1"/>
+    <col min="57" max="58" width="9" customWidth="1"/>
+    <col min="59" max="59" width="24.25" customWidth="1"/>
+    <col min="60" max="60" width="13.25" customWidth="1"/>
+    <col min="61" max="61" width="16.08203125" customWidth="1"/>
+    <col min="62" max="62" width="8" customWidth="1"/>
+    <col min="63" max="66" width="9" customWidth="1"/>
+    <col min="67" max="67" width="39.58203125" customWidth="1"/>
+    <col min="68" max="68" width="9" customWidth="1"/>
+    <col min="69" max="69" width="14" customWidth="1"/>
+    <col min="70" max="70" width="14.83203125" customWidth="1"/>
+    <col min="71" max="74" width="14" customWidth="1"/>
+    <col min="75" max="75" width="9" customWidth="1"/>
+    <col min="76" max="76" width="19.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2" t="s">
+    <row r="1" spans="1:76" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2" t="s">
+      <c r="N1" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2" t="s">
+      <c r="P1" t="s">
         <v>12</v>
       </c>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2" t="s">
+      <c r="R1" t="s">
         <v>13</v>
       </c>
-      <c r="S1" s="2"/>
-      <c r="T1" s="2" t="s">
+      <c r="T1" t="s">
         <v>14</v>
       </c>
-      <c r="U1" s="2"/>
-      <c r="V1" s="2" t="s">
+      <c r="V1" t="s">
         <v>15</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="W1" t="s">
         <v>16</v>
       </c>
-      <c r="X1" s="2"/>
-      <c r="Y1" s="2" t="s">
+      <c r="Y1" t="s">
         <v>17</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="Z1" t="s">
         <v>18</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AA1" t="s">
         <v>19</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AB1" t="s">
         <v>20</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AC1" t="s">
         <v>21</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AD1" t="s">
         <v>22</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AE1" t="s">
         <v>23</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AF1" t="s">
         <v>24</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AG1" t="s">
         <v>25</v>
       </c>
-      <c r="AH1" s="2" t="s">
+      <c r="AH1" t="s">
         <v>26</v>
       </c>
-      <c r="AI1" s="2"/>
-      <c r="AJ1" s="2"/>
-      <c r="AK1" s="2" t="s">
+      <c r="AK1" t="s">
         <v>27</v>
       </c>
-      <c r="AL1" s="2" t="s">
+      <c r="AL1" t="s">
         <v>28</v>
       </c>
-      <c r="AM1" s="2" t="s">
+      <c r="AM1" t="s">
         <v>29</v>
       </c>
-      <c r="AN1" s="2" t="s">
+      <c r="AN1" t="s">
         <v>30</v>
       </c>
-      <c r="AO1" s="2" t="s">
+      <c r="AO1" t="s">
         <v>31</v>
       </c>
-      <c r="AP1" s="2" t="s">
+      <c r="AP1" t="s">
         <v>32</v>
       </c>
-      <c r="AQ1" s="2" t="s">
+      <c r="AQ1" t="s">
         <v>33</v>
       </c>
-      <c r="AR1" s="2" t="s">
+      <c r="AR1" t="s">
         <v>34</v>
       </c>
-      <c r="AS1" s="2" t="s">
+      <c r="AS1" t="s">
         <v>35</v>
       </c>
-      <c r="AT1" s="2" t="s">
+      <c r="AT1" t="s">
         <v>36</v>
       </c>
-      <c r="AU1" s="2"/>
-      <c r="AV1" s="2" t="s">
+      <c r="AV1" t="s">
         <v>37</v>
       </c>
-      <c r="AW1" s="2" t="s">
+      <c r="AW1" t="s">
         <v>38</v>
       </c>
-      <c r="AX1" s="2" t="s">
+      <c r="AX1" t="s">
         <v>39</v>
       </c>
-      <c r="AY1" s="2" t="s">
+      <c r="AY1" t="s">
         <v>40</v>
       </c>
-      <c r="AZ1" s="2" t="s">
+      <c r="AZ1" t="s">
         <v>41</v>
       </c>
-      <c r="BA1" s="2" t="s">
+      <c r="BA1" t="s">
         <v>42</v>
       </c>
-      <c r="BB1" s="2" t="s">
+      <c r="BB1" t="s">
         <v>43</v>
       </c>
-      <c r="BC1" s="2" t="s">
+      <c r="BC1" t="s">
         <v>44</v>
       </c>
-      <c r="BD1" s="2" t="s">
+      <c r="BD1" t="s">
         <v>45</v>
       </c>
-      <c r="BE1" s="2"/>
-      <c r="BF1" s="2"/>
-      <c r="BG1" s="2" t="s">
+      <c r="BG1" t="s">
         <v>46</v>
       </c>
-      <c r="BH1" s="2" t="s">
+      <c r="BH1" t="s">
         <v>47</v>
       </c>
-      <c r="BI1" s="2" t="s">
+      <c r="BI1" t="s">
         <v>48</v>
       </c>
-      <c r="BJ1" s="2" t="s">
+      <c r="BJ1" t="s">
         <v>49</v>
       </c>
-      <c r="BK1" s="2" t="s">
+      <c r="BK1" t="s">
         <v>50</v>
       </c>
-      <c r="BL1" s="2"/>
-      <c r="BM1" s="2"/>
-      <c r="BN1" s="2"/>
-      <c r="BO1" s="2"/>
-      <c r="BP1" s="2"/>
-      <c r="BQ1" s="2"/>
-      <c r="BR1" s="2"/>
-      <c r="BS1" s="2"/>
-      <c r="BT1" s="2"/>
-      <c r="BU1" s="2"/>
-      <c r="BV1" s="2"/>
-      <c r="BW1" s="2"/>
-      <c r="BX1" s="2"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
+    </row>
+    <row r="2" spans="1:76" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" t="s">
         <v>52</v>
       </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2" t="s">
+      <c r="F2" t="s">
         <v>53</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" t="s">
         <v>54</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" t="s">
         <v>55</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" t="s">
         <v>56</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" t="s">
         <v>57</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" t="s">
         <v>58</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" t="s">
         <v>59</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="M2" t="s">
         <v>60</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="N2" t="s">
         <v>61</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="O2" t="s">
         <v>62</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="P2" t="s">
         <v>63</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="Q2" t="s">
         <v>64</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="R2" t="s">
         <v>65</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="S2" t="s">
         <v>66</v>
       </c>
-      <c r="T2" s="2" t="s">
+      <c r="T2" t="s">
         <v>67</v>
       </c>
-      <c r="U2" s="2" t="s">
+      <c r="U2" t="s">
         <v>68</v>
       </c>
-      <c r="V2" s="2" t="s">
+      <c r="V2" t="s">
         <v>69</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="W2" t="s">
         <v>70</v>
       </c>
-      <c r="X2" s="2" t="s">
+      <c r="X2" t="s">
         <v>71</v>
       </c>
-      <c r="Y2" s="2" t="s">
+      <c r="Y2" t="s">
         <v>72</v>
       </c>
-      <c r="Z2" s="2" t="s">
+      <c r="Z2" t="s">
         <v>73</v>
       </c>
-      <c r="AA2" s="2" t="s">
+      <c r="AA2" t="s">
         <v>74</v>
       </c>
-      <c r="AB2" s="2" t="s">
+      <c r="AB2" t="s">
         <v>75</v>
       </c>
-      <c r="AC2" s="2" t="s">
+      <c r="AC2" t="s">
         <v>76</v>
       </c>
-      <c r="AD2" s="2" t="s">
+      <c r="AD2" t="s">
         <v>77</v>
       </c>
-      <c r="AE2" s="2" t="s">
+      <c r="AE2" t="s">
         <v>78</v>
       </c>
-      <c r="AF2" s="2" t="s">
+      <c r="AF2" t="s">
         <v>79</v>
       </c>
-      <c r="AG2" s="2" t="s">
+      <c r="AG2" t="s">
         <v>80</v>
       </c>
-      <c r="AH2" s="2" t="s">
+      <c r="AH2" t="s">
         <v>81</v>
       </c>
-      <c r="AI2" s="2" t="s">
+      <c r="AI2" t="s">
         <v>82</v>
       </c>
-      <c r="AJ2" s="2" t="s">
+      <c r="AJ2" t="s">
         <v>83</v>
       </c>
-      <c r="AK2" s="2" t="s">
+      <c r="AK2" t="s">
         <v>84</v>
       </c>
-      <c r="AL2" s="2" t="s">
+      <c r="AL2" t="s">
         <v>85</v>
       </c>
-      <c r="AM2" s="2" t="s">
+      <c r="AM2" t="s">
         <v>86</v>
       </c>
-      <c r="AN2" s="2" t="s">
+      <c r="AN2" t="s">
         <v>87</v>
       </c>
-      <c r="AO2" s="2" t="s">
+      <c r="AO2" t="s">
         <v>88</v>
       </c>
-      <c r="AP2" s="2" t="s">
+      <c r="AP2" t="s">
         <v>89</v>
       </c>
-      <c r="AQ2" s="2" t="s">
+      <c r="AQ2" t="s">
         <v>90</v>
       </c>
-      <c r="AR2" s="2" t="s">
+      <c r="AR2" t="s">
         <v>91</v>
       </c>
-      <c r="AS2" s="2" t="s">
+      <c r="AS2" t="s">
         <v>92</v>
       </c>
-      <c r="AT2" s="2" t="s">
+      <c r="AT2" t="s">
         <v>93</v>
       </c>
-      <c r="AU2" s="2" t="s">
+      <c r="AU2" t="s">
         <v>94</v>
       </c>
-      <c r="AV2" s="2" t="s">
+      <c r="AV2" t="s">
         <v>95</v>
       </c>
-      <c r="AW2" s="2" t="s">
+      <c r="AW2" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="2" t="s">
+      <c r="AX2" t="s">
         <v>97</v>
       </c>
-      <c r="AY2" s="2" t="s">
+      <c r="AY2" t="s">
         <v>98</v>
       </c>
-      <c r="AZ2" s="2" t="s">
+      <c r="AZ2" t="s">
         <v>99</v>
       </c>
-      <c r="BA2" s="2" t="s">
+      <c r="BA2" t="s">
         <v>100</v>
       </c>
-      <c r="BB2" s="2" t="s">
+      <c r="BB2" t="s">
         <v>101</v>
       </c>
-      <c r="BC2" s="2" t="s">
+      <c r="BC2" t="s">
         <v>102</v>
       </c>
-      <c r="BD2" s="2" t="s">
+      <c r="BD2" t="s">
         <v>103</v>
       </c>
-      <c r="BE2" s="2" t="s">
+      <c r="BE2" t="s">
         <v>104</v>
       </c>
-      <c r="BF2" s="2" t="s">
+      <c r="BF2" t="s">
         <v>105</v>
       </c>
-      <c r="BG2" s="2" t="s">
+      <c r="BG2" t="s">
         <v>106</v>
       </c>
-      <c r="BH2" s="2" t="s">
+      <c r="BH2" t="s">
         <v>107</v>
       </c>
-      <c r="BI2" s="2" t="s">
+      <c r="BI2" t="s">
         <v>108</v>
       </c>
-      <c r="BJ2" s="2" t="s">
+      <c r="BJ2" t="s">
         <v>109</v>
       </c>
-      <c r="BK2" s="2" t="s">
+      <c r="BK2" t="s">
         <v>110</v>
       </c>
-      <c r="BL2" s="2" t="s">
+      <c r="BL2" t="s">
         <v>111</v>
       </c>
-      <c r="BM2" s="2" t="s">
+      <c r="BM2" t="s">
         <v>112</v>
       </c>
-      <c r="BN2" s="2" t="s">
+      <c r="BN2" t="s">
         <v>113</v>
       </c>
-      <c r="BO2" s="2" t="s">
+      <c r="BO2" t="s">
         <v>114</v>
       </c>
-      <c r="BP2" s="2" t="s">
+      <c r="BP2" t="s">
         <v>115</v>
       </c>
-      <c r="BQ2" s="2" t="s">
+      <c r="BQ2" t="s">
         <v>116</v>
       </c>
-      <c r="BR2" s="2" t="s">
+      <c r="BR2" t="s">
         <v>117</v>
       </c>
-      <c r="BS2" s="2" t="s">
+      <c r="BS2" t="s">
         <v>118</v>
       </c>
-      <c r="BT2" s="2" t="s">
+      <c r="BT2" t="s">
         <v>119</v>
       </c>
-      <c r="BU2" s="2" t="s">
+      <c r="BU2" t="s">
         <v>120</v>
       </c>
-      <c r="BV2" s="2" t="s">
+      <c r="BV2" t="s">
         <v>121</v>
       </c>
-      <c r="BW2" s="2" t="s">
+      <c r="BW2" t="s">
         <v>122</v>
       </c>
-      <c r="BX2" s="2" t="s">
+      <c r="BX2" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:76" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" t="s">
         <v>124</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2" t="s">
+      <c r="F3" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" t="s">
         <v>125</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" t="s">
         <v>126</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" t="s">
         <v>2</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" t="s">
         <v>127</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" t="s">
         <v>127</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L3" t="s">
         <v>127</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="M3" t="s">
         <v>127</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="N3" t="s">
         <v>127</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="O3" t="s">
         <v>127</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="P3" t="s">
         <v>127</v>
       </c>
-      <c r="Q3" s="2" t="s">
+      <c r="Q3" t="s">
         <v>127</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="R3" t="s">
         <v>127</v>
       </c>
-      <c r="S3" s="2" t="s">
+      <c r="S3" t="s">
         <v>127</v>
       </c>
-      <c r="T3" s="2" t="s">
+      <c r="T3" t="s">
         <v>127</v>
       </c>
-      <c r="U3" s="2" t="s">
+      <c r="U3" t="s">
         <v>127</v>
       </c>
-      <c r="V3" s="2" t="s">
+      <c r="V3" t="s">
         <v>125</v>
       </c>
-      <c r="W3" s="2" t="s">
+      <c r="W3" t="s">
         <v>127</v>
       </c>
-      <c r="X3" s="2" t="s">
+      <c r="X3" t="s">
         <v>127</v>
       </c>
-      <c r="Y3" s="2" t="s">
+      <c r="Y3" t="s">
         <v>125</v>
       </c>
-      <c r="Z3" s="2" t="s">
+      <c r="Z3" t="s">
         <v>125</v>
       </c>
-      <c r="AA3" s="2" t="s">
+      <c r="AA3" t="s">
         <v>125</v>
       </c>
-      <c r="AB3" s="2" t="s">
+      <c r="AB3" t="s">
         <v>127</v>
       </c>
-      <c r="AC3" s="2" t="s">
+      <c r="AC3" t="s">
         <v>125</v>
       </c>
-      <c r="AD3" s="2" t="s">
+      <c r="AD3" t="s">
         <v>127</v>
       </c>
-      <c r="AE3" s="2" t="s">
+      <c r="AE3" t="s">
         <v>124</v>
       </c>
-      <c r="AF3" s="2" t="s">
+      <c r="AF3" t="s">
         <v>2</v>
       </c>
-      <c r="AG3" s="2" t="s">
+      <c r="AG3" t="s">
         <v>127</v>
       </c>
-      <c r="AH3" s="2" t="s">
+      <c r="AH3" t="s">
         <v>127</v>
       </c>
-      <c r="AI3" s="2" t="s">
+      <c r="AI3" t="s">
         <v>127</v>
       </c>
-      <c r="AJ3" s="2" t="s">
+      <c r="AJ3" t="s">
         <v>2</v>
       </c>
-      <c r="AK3" s="2" t="s">
+      <c r="AK3" t="s">
         <v>2</v>
       </c>
-      <c r="AL3" s="2" t="s">
+      <c r="AL3" t="s">
         <v>128</v>
       </c>
-      <c r="AM3" s="2" t="s">
+      <c r="AM3" t="s">
         <v>128</v>
       </c>
-      <c r="AN3" s="2" t="s">
+      <c r="AN3" t="s">
         <v>2</v>
       </c>
-      <c r="AO3" s="2" t="s">
+      <c r="AO3" t="s">
         <v>2</v>
       </c>
-      <c r="AP3" s="2" t="s">
+      <c r="AP3" t="s">
         <v>125</v>
       </c>
-      <c r="AQ3" s="2" t="s">
+      <c r="AQ3" t="s">
         <v>129</v>
       </c>
-      <c r="AR3" s="2" t="s">
+      <c r="AR3" t="s">
         <v>127</v>
       </c>
-      <c r="AS3" s="2" t="s">
+      <c r="AS3" t="s">
         <v>125</v>
       </c>
-      <c r="AT3" s="2" t="s">
+      <c r="AT3" t="s">
         <v>124</v>
       </c>
-      <c r="AU3" s="2"/>
-      <c r="AV3" s="2" t="s">
+      <c r="AV3" t="s">
         <v>125</v>
       </c>
-      <c r="AW3" s="2" t="s">
+      <c r="AW3" t="s">
         <v>124</v>
       </c>
-      <c r="AX3" s="2" t="s">
+      <c r="AX3" t="s">
         <v>127</v>
       </c>
-      <c r="AY3" s="2" t="s">
+      <c r="AY3" t="s">
         <v>130</v>
       </c>
-      <c r="AZ3" s="2" t="s">
+      <c r="AZ3" t="s">
         <v>125</v>
       </c>
-      <c r="BA3" s="2" t="s">
+      <c r="BA3" t="s">
         <v>131</v>
       </c>
-      <c r="BB3" s="2" t="s">
+      <c r="BB3" t="s">
         <v>124</v>
       </c>
-      <c r="BC3" s="2" t="s">
+      <c r="BC3" t="s">
         <v>124</v>
       </c>
-      <c r="BD3" s="2" t="s">
+      <c r="BD3" t="s">
         <v>125</v>
       </c>
-      <c r="BE3" s="2" t="s">
+      <c r="BE3" t="s">
         <v>132</v>
       </c>
-      <c r="BF3" s="2" t="s">
+      <c r="BF3" t="s">
         <v>2</v>
       </c>
-      <c r="BG3" s="2" t="s">
+      <c r="BG3" t="s">
         <v>2</v>
       </c>
-      <c r="BH3" s="2" t="s">
+      <c r="BH3" t="s">
         <v>2</v>
       </c>
-      <c r="BI3" s="2" t="s">
+      <c r="BI3" t="s">
         <v>2</v>
       </c>
-      <c r="BJ3" s="2" t="s">
+      <c r="BJ3" t="s">
         <v>133</v>
       </c>
-      <c r="BK3" s="2" t="s">
+      <c r="BK3" t="s">
         <v>127</v>
       </c>
-      <c r="BL3" s="2" t="s">
+      <c r="BL3" t="s">
         <v>2</v>
       </c>
-      <c r="BM3" s="2" t="s">
+      <c r="BM3" t="s">
         <v>129</v>
       </c>
-      <c r="BN3" s="2" t="s">
+      <c r="BN3" t="s">
         <v>2</v>
       </c>
-      <c r="BO3" s="2" t="s">
+      <c r="BO3" t="s">
         <v>134</v>
       </c>
-      <c r="BP3" s="2" t="s">
+      <c r="BP3" t="s">
         <v>129</v>
       </c>
-      <c r="BQ3" s="2" t="s">
+      <c r="BQ3" t="s">
         <v>129</v>
       </c>
-      <c r="BR3" s="2" t="s">
+      <c r="BR3" t="s">
         <v>129</v>
       </c>
-      <c r="BS3" s="2" t="s">
+      <c r="BS3" t="s">
         <v>129</v>
       </c>
-      <c r="BT3" s="2" t="s">
+      <c r="BT3" t="s">
         <v>129</v>
       </c>
-      <c r="BU3" s="2" t="s">
+      <c r="BU3" t="s">
         <v>129</v>
       </c>
-      <c r="BV3" s="2" t="s">
+      <c r="BV3" t="s">
         <v>129</v>
       </c>
-      <c r="BW3" s="2" t="s">
+      <c r="BW3" t="s">
         <v>129</v>
       </c>
-      <c r="BX3" s="2" t="s">
+      <c r="BX3" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="2"/>
-      <c r="S4" s="2"/>
-      <c r="T4" s="2"/>
-      <c r="U4" s="2"/>
-      <c r="V4" s="2"/>
-      <c r="W4" s="2"/>
-      <c r="X4" s="2"/>
-      <c r="Y4" s="2"/>
-      <c r="Z4" s="2"/>
-      <c r="AA4" s="2"/>
-      <c r="AB4" s="2"/>
-      <c r="AC4" s="2"/>
-      <c r="AD4" s="2"/>
-      <c r="AE4" s="2"/>
-      <c r="AF4" s="2"/>
-      <c r="AG4" s="2"/>
-      <c r="AH4" s="2"/>
-      <c r="AI4" s="2"/>
-      <c r="AJ4" s="2"/>
-      <c r="AK4" s="2"/>
-      <c r="AL4" s="2"/>
-      <c r="AM4" s="2"/>
-      <c r="AN4" s="2"/>
-      <c r="AO4" s="2"/>
-      <c r="AP4" s="2"/>
-      <c r="AQ4" s="2"/>
-      <c r="AR4" s="2"/>
-      <c r="AS4" s="2"/>
-      <c r="AT4" s="2"/>
-      <c r="AU4" s="2"/>
-      <c r="AV4" s="2"/>
-      <c r="AW4" s="2"/>
-      <c r="AX4" s="2"/>
-      <c r="AY4" s="2"/>
-      <c r="AZ4" s="2"/>
-      <c r="BA4" s="2"/>
-      <c r="BB4" s="2"/>
-      <c r="BC4" s="2"/>
-      <c r="BD4" s="2"/>
-      <c r="BE4" s="2"/>
-      <c r="BF4" s="2"/>
-      <c r="BG4" s="2"/>
-      <c r="BH4" s="2"/>
-      <c r="BI4" s="2"/>
-      <c r="BJ4" s="2"/>
-      <c r="BK4" s="2"/>
-      <c r="BL4" s="2"/>
-      <c r="BM4" s="2"/>
-      <c r="BN4" s="2"/>
-      <c r="BO4" s="2"/>
-      <c r="BP4" s="2"/>
-      <c r="BQ4" s="2"/>
-      <c r="BR4" s="2"/>
-      <c r="BS4" s="2"/>
-      <c r="BT4" s="2"/>
-      <c r="BU4" s="2"/>
-      <c r="BV4" s="2"/>
-      <c r="BW4" s="2"/>
-      <c r="BX4" s="2"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:76" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" t="s">
         <v>135</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2" t="s">
+      <c r="F5" t="s">
         <v>4</v>
       </c>
-      <c r="G5" s="2">
-        <v>1</v>
-      </c>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2">
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="J5">
         <v>2</v>
       </c>
-      <c r="K5" s="2">
+      <c r="K5">
         <v>90</v>
       </c>
-      <c r="L5" s="2">
+      <c r="L5">
         <v>1949</v>
       </c>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2">
+      <c r="N5">
         <v>520</v>
       </c>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2">
+      <c r="P5">
         <v>180</v>
       </c>
-      <c r="Q5" s="2"/>
-      <c r="R5" s="2">
+      <c r="R5">
         <v>0</v>
       </c>
-      <c r="S5" s="2"/>
-      <c r="T5" s="2">
+      <c r="T5">
         <v>18</v>
       </c>
-      <c r="U5" s="2"/>
-      <c r="V5" s="2">
+      <c r="V5">
         <v>0.5</v>
       </c>
-      <c r="W5" s="2">
+      <c r="W5">
         <v>70</v>
       </c>
-      <c r="X5" s="2"/>
-      <c r="Y5" s="2"/>
-      <c r="Z5" s="2">
+      <c r="Z5">
         <v>0.05</v>
       </c>
-      <c r="AA5" s="2">
+      <c r="AA5">
         <v>1.6</v>
       </c>
-      <c r="AB5" s="2"/>
-      <c r="AC5" s="2"/>
-      <c r="AD5" s="2">
-        <v>1</v>
-      </c>
-      <c r="AE5" s="2"/>
-      <c r="AF5" s="2"/>
-      <c r="AG5" s="2"/>
-      <c r="AH5" s="2"/>
-      <c r="AI5" s="2"/>
-      <c r="AJ5" s="2" t="s">
+      <c r="AD5">
+        <v>1</v>
+      </c>
+      <c r="AJ5" t="s">
         <v>4</v>
       </c>
-      <c r="AK5" s="2" t="s">
+      <c r="AK5" t="s">
         <v>136</v>
       </c>
-      <c r="AL5" s="2" t="s">
+      <c r="AL5" t="s">
         <v>137</v>
       </c>
-      <c r="AM5" s="2" t="s">
+      <c r="AM5" t="s">
         <v>138</v>
       </c>
-      <c r="AN5" s="2" t="s">
+      <c r="AN5" t="s">
         <v>139</v>
       </c>
-      <c r="AO5" s="2" t="s">
+      <c r="AO5" t="s">
         <v>140</v>
       </c>
-      <c r="AP5" s="2"/>
-      <c r="AQ5" s="2" t="s">
+      <c r="AQ5" t="s">
         <v>141</v>
       </c>
-      <c r="AR5" s="2">
-        <v>1</v>
-      </c>
-      <c r="AS5" s="2">
+      <c r="AR5">
+        <v>1</v>
+      </c>
+      <c r="AS5">
         <v>0.5</v>
       </c>
-      <c r="AT5" s="2"/>
-      <c r="AU5" s="2"/>
-      <c r="AV5" s="2"/>
-      <c r="AW5" s="2"/>
-      <c r="AX5" s="2"/>
-      <c r="AY5" s="2"/>
-      <c r="AZ5" s="2">
+      <c r="AZ5">
         <v>0.25</v>
       </c>
-      <c r="BA5" s="2"/>
-      <c r="BB5" s="2"/>
-      <c r="BC5" s="2"/>
-      <c r="BD5" s="2"/>
-      <c r="BE5" s="2" t="s">
+      <c r="BE5" t="s">
         <v>142</v>
       </c>
-      <c r="BF5" s="2"/>
-      <c r="BG5" s="2" t="s">
+      <c r="BG5" t="s">
         <v>143</v>
       </c>
-      <c r="BH5" s="2" t="s">
+      <c r="BH5" t="s">
         <v>144</v>
       </c>
-      <c r="BI5" s="2" t="s">
+      <c r="BI5" t="s">
         <v>145</v>
       </c>
-      <c r="BJ5" s="2" t="s">
+      <c r="BJ5" t="s">
         <v>146</v>
       </c>
-      <c r="BK5" s="2">
+      <c r="BK5">
         <v>6</v>
       </c>
-      <c r="BL5" s="2"/>
-      <c r="BM5" s="2"/>
-      <c r="BN5" s="2"/>
-      <c r="BO5" s="2"/>
-      <c r="BP5" s="2"/>
-      <c r="BQ5" s="2" t="s">
+      <c r="BQ5" t="s">
         <v>147</v>
       </c>
-      <c r="BR5" s="2" t="s">
+      <c r="BR5" t="s">
         <v>148</v>
       </c>
-      <c r="BS5" s="2"/>
-      <c r="BT5" s="2" t="s">
+      <c r="BT5" t="s">
         <v>149</v>
       </c>
-      <c r="BU5" s="2" t="s">
+      <c r="BU5" t="s">
         <v>149</v>
       </c>
-      <c r="BV5" s="2" t="s">
+      <c r="BV5" t="s">
         <v>150</v>
       </c>
-      <c r="BW5" s="2"/>
-      <c r="BX5" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="s">
+      <c r="BX5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:76" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>151</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" t="s">
         <v>152</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2" t="s">
+      <c r="F6" t="s">
         <v>153</v>
       </c>
-      <c r="G6" s="2">
-        <v>1</v>
-      </c>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2">
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="J6">
         <v>2</v>
       </c>
-      <c r="K6" s="2">
+      <c r="K6">
         <v>90</v>
       </c>
-      <c r="L6" s="2">
+      <c r="L6">
         <v>100</v>
       </c>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2">
+      <c r="N6">
         <v>0</v>
       </c>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2">
+      <c r="P6">
         <v>0</v>
       </c>
-      <c r="Q6" s="2"/>
-      <c r="R6" s="2">
+      <c r="R6">
         <v>0</v>
       </c>
-      <c r="S6" s="2"/>
-      <c r="T6" s="2">
+      <c r="T6">
         <v>0</v>
       </c>
-      <c r="U6" s="2"/>
-      <c r="V6" s="2">
+      <c r="V6">
         <v>0</v>
       </c>
-      <c r="W6" s="2">
+      <c r="W6">
         <v>0</v>
       </c>
-      <c r="X6" s="2"/>
-      <c r="Y6" s="2"/>
-      <c r="Z6" s="2">
+      <c r="Z6">
         <v>0.05</v>
       </c>
-      <c r="AA6" s="2">
+      <c r="AA6">
         <v>0</v>
       </c>
-      <c r="AB6" s="2">
+      <c r="AB6">
         <v>0</v>
       </c>
-      <c r="AC6" s="2"/>
-      <c r="AD6" s="2">
+      <c r="AD6">
         <v>0</v>
       </c>
-      <c r="AE6" s="2"/>
-      <c r="AF6" s="2"/>
-      <c r="AG6" s="2"/>
-      <c r="AH6" s="2"/>
-      <c r="AI6" s="2"/>
-      <c r="AJ6" s="2" t="s">
+      <c r="AJ6" t="s">
         <v>154</v>
       </c>
-      <c r="AK6" s="2" t="s">
+      <c r="AK6" t="s">
         <v>136</v>
       </c>
-      <c r="AL6" s="2" t="s">
+      <c r="AL6" t="s">
         <v>155</v>
       </c>
-      <c r="AM6" s="2"/>
-      <c r="AN6" s="2"/>
-      <c r="AO6" s="2"/>
-      <c r="AP6" s="2"/>
-      <c r="AQ6" s="2" t="s">
+      <c r="AQ6" t="s">
         <v>156</v>
       </c>
-      <c r="AR6" s="2">
+      <c r="AR6">
         <v>0</v>
       </c>
-      <c r="AS6" s="2">
+      <c r="AS6">
         <v>0.5</v>
       </c>
-      <c r="AT6" s="2">
-        <v>1</v>
-      </c>
-      <c r="AU6" s="2"/>
-      <c r="AV6" s="2"/>
-      <c r="AW6" s="2"/>
-      <c r="AX6" s="2"/>
-      <c r="AY6" s="2"/>
-      <c r="AZ6" s="2">
+      <c r="AT6">
+        <v>1</v>
+      </c>
+      <c r="AZ6">
         <v>0.25</v>
       </c>
-      <c r="BA6" s="2"/>
-      <c r="BB6" s="2"/>
-      <c r="BC6" s="2"/>
-      <c r="BD6" s="2"/>
-      <c r="BE6" s="2" t="s">
+      <c r="BE6" t="s">
         <v>157</v>
       </c>
-      <c r="BF6" s="2"/>
-      <c r="BG6" s="2"/>
-      <c r="BH6" s="2"/>
-      <c r="BI6" s="2"/>
-      <c r="BJ6" s="2"/>
-      <c r="BK6" s="2"/>
-      <c r="BL6" s="2"/>
-      <c r="BM6" s="2"/>
-      <c r="BN6" s="2"/>
-      <c r="BO6" s="2" t="s">
+      <c r="BO6" t="s">
         <v>158</v>
       </c>
-      <c r="BP6" s="2"/>
-      <c r="BQ6" s="2"/>
-      <c r="BR6" s="2"/>
-      <c r="BS6" s="2"/>
-      <c r="BT6" s="2"/>
-      <c r="BU6" s="2"/>
-      <c r="BV6" s="2"/>
-      <c r="BW6" s="2"/>
-      <c r="BX6" s="2"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="s">
+    </row>
+    <row r="7" spans="1:76" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>159</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" t="s">
         <v>152</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2" t="s">
+      <c r="F7" t="s">
         <v>153</v>
       </c>
-      <c r="G7" s="2">
-        <v>1</v>
-      </c>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2">
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="J7">
         <v>2</v>
       </c>
-      <c r="K7" s="2">
+      <c r="K7">
         <v>90</v>
       </c>
-      <c r="L7" s="2">
+      <c r="L7">
         <v>100</v>
       </c>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2">
+      <c r="N7">
         <v>0</v>
       </c>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2">
+      <c r="P7">
         <v>0</v>
       </c>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="2">
+      <c r="R7">
         <v>0</v>
       </c>
-      <c r="S7" s="2"/>
-      <c r="T7" s="2">
+      <c r="T7">
         <v>0</v>
       </c>
-      <c r="U7" s="2"/>
-      <c r="V7" s="2">
+      <c r="V7">
         <v>0</v>
       </c>
-      <c r="W7" s="2">
+      <c r="W7">
         <v>0</v>
       </c>
-      <c r="X7" s="2"/>
-      <c r="Y7" s="2"/>
-      <c r="Z7" s="2">
+      <c r="Z7">
         <v>0.05</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AA7">
         <v>0</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AB7">
         <v>0</v>
       </c>
-      <c r="AC7" s="2"/>
-      <c r="AD7" s="2">
+      <c r="AD7">
         <v>0</v>
       </c>
-      <c r="AE7" s="2"/>
-      <c r="AF7" s="2"/>
-      <c r="AG7" s="2"/>
-      <c r="AH7" s="2"/>
-      <c r="AI7" s="2"/>
-      <c r="AJ7" s="2" t="s">
+      <c r="AJ7" t="s">
         <v>154</v>
       </c>
-      <c r="AK7" s="2" t="s">
+      <c r="AK7" t="s">
         <v>136</v>
       </c>
-      <c r="AL7" s="2" t="s">
+      <c r="AL7" t="s">
         <v>160</v>
       </c>
-      <c r="AM7" s="2"/>
-      <c r="AN7" s="2"/>
-      <c r="AO7" s="2"/>
-      <c r="AP7" s="2"/>
-      <c r="AQ7" s="2" t="s">
+      <c r="AQ7" t="s">
         <v>156</v>
       </c>
-      <c r="AR7" s="2">
+      <c r="AR7">
         <v>0</v>
       </c>
-      <c r="AS7" s="2">
+      <c r="AS7">
         <v>0.5</v>
       </c>
-      <c r="AT7" s="2">
-        <v>1</v>
-      </c>
-      <c r="AU7" s="2"/>
-      <c r="AV7" s="2"/>
-      <c r="AW7" s="2"/>
-      <c r="AX7" s="2"/>
-      <c r="AY7" s="2"/>
-      <c r="AZ7" s="2">
+      <c r="AT7">
+        <v>1</v>
+      </c>
+      <c r="AZ7">
         <v>0.25</v>
       </c>
-      <c r="BA7" s="2"/>
-      <c r="BB7" s="2"/>
-      <c r="BC7" s="2"/>
-      <c r="BD7" s="2"/>
-      <c r="BE7" s="2" t="s">
+      <c r="BE7" t="s">
         <v>157</v>
       </c>
-      <c r="BF7" s="2"/>
-      <c r="BG7" s="2"/>
-      <c r="BH7" s="2"/>
-      <c r="BI7" s="2"/>
-      <c r="BJ7" s="2"/>
-      <c r="BK7" s="2"/>
-      <c r="BL7" s="2"/>
-      <c r="BM7" s="2"/>
-      <c r="BN7" s="2"/>
-      <c r="BO7" s="2" t="s">
+      <c r="BO7" t="s">
         <v>161</v>
       </c>
-      <c r="BP7" s="2"/>
-      <c r="BQ7" s="2"/>
-      <c r="BR7" s="2"/>
-      <c r="BS7" s="2"/>
-      <c r="BT7" s="2"/>
-      <c r="BU7" s="2"/>
-      <c r="BV7" s="2"/>
-      <c r="BW7" s="2"/>
-      <c r="BX7" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -3629,2076 +3360,2091 @@
   <dimension ref="A1:DI689"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.08203125" customWidth="1" style="3"/>
-    <col min="2" max="2" width="15.58203125" customWidth="1" style="3"/>
-    <col min="3" max="3" width="7.75" customWidth="1" style="3"/>
-    <col min="4" max="4" width="16.58203125" customWidth="1" style="3"/>
-    <col min="5" max="5" width="16.83203125" customWidth="1" style="3"/>
-    <col min="6" max="6" width="31.33203125" customWidth="1" style="3"/>
-    <col min="7" max="7" width="7.33203125" customWidth="1" style="3"/>
-    <col min="8" max="8" width="20.58203125" customWidth="1" style="3"/>
-    <col min="9" max="9" width="10.75" customWidth="1" style="3"/>
-    <col min="10" max="10" width="15.75" customWidth="1" style="3"/>
-    <col min="11" max="13" width="8.33203125" customWidth="1" style="3"/>
-    <col min="14" max="14" width="11.75" customWidth="1" style="3"/>
-    <col min="15" max="15" width="13.08203125" customWidth="1" style="3"/>
-    <col min="16" max="16" width="11.58203125" customWidth="1" style="3"/>
-    <col min="17" max="17" width="21.5" customWidth="1" style="3"/>
-    <col min="18" max="18" width="19.83203125" customWidth="1" style="3"/>
-    <col min="19" max="19" width="16.58203125" customWidth="1" style="3"/>
-    <col min="20" max="20" width="19.08203125" customWidth="1" style="3"/>
-    <col min="21" max="21" width="18.33203125" customWidth="1" style="3"/>
-    <col min="22" max="22" width="17.75" customWidth="1" style="3"/>
-    <col min="23" max="23" width="8.33203125" customWidth="1" style="3"/>
-    <col min="24" max="24" width="18.5" customWidth="1" style="3"/>
-    <col min="25" max="25" width="16.58203125" customWidth="1" style="3"/>
-    <col min="26" max="26" width="10.6640625" customWidth="1" style="3"/>
-    <col min="27" max="27" width="8.33203125" customWidth="1" style="3"/>
-    <col min="28" max="28" width="15.1640625" customWidth="1" style="3"/>
-    <col min="29" max="30" width="8.58203125" customWidth="1" style="3"/>
-    <col min="31" max="31" width="13.4140625" customWidth="1" style="3"/>
-    <col min="32" max="32" width="13.75" customWidth="1" style="3"/>
-    <col min="33" max="33" width="14.58203125" customWidth="1" style="3"/>
-    <col min="34" max="34" width="17.4140625" customWidth="1" style="3"/>
-    <col min="35" max="35" width="8.58203125" customWidth="1" style="3"/>
-    <col min="36" max="36" width="12.5" customWidth="1" style="3"/>
-    <col min="37" max="37" width="8.58203125" customWidth="1" style="3"/>
-    <col min="38" max="39" width="8.33203125" customWidth="1" style="3"/>
-    <col min="40" max="40" width="15" customWidth="1" style="3"/>
-    <col min="41" max="41" width="18" customWidth="1" style="3"/>
-    <col min="42" max="42" width="20.58203125" customWidth="1" style="3"/>
-    <col min="43" max="45" width="11.83203125" customWidth="1" style="3"/>
-    <col min="46" max="46" width="18.4140625" customWidth="1" style="3"/>
-    <col min="47" max="47" width="12.25" customWidth="1" style="3"/>
-    <col min="48" max="48" width="11.9140625" customWidth="1" style="3"/>
-    <col min="49" max="49" width="19.58203125" customWidth="1" style="3"/>
-    <col min="50" max="50" width="12.6640625" customWidth="1" style="3"/>
-    <col min="51" max="51" width="9" customWidth="1" style="3"/>
-    <col min="52" max="52" width="7" customWidth="1" style="3"/>
-    <col min="53" max="53" width="11.75" customWidth="1" style="3"/>
-    <col min="54" max="54" width="19.75" customWidth="1" style="3"/>
-    <col min="55" max="55" width="5.08203125" customWidth="1" style="3"/>
-    <col min="56" max="56" width="8.5" customWidth="1" style="3"/>
-    <col min="57" max="57" width="13.5" customWidth="1" style="3"/>
-    <col min="58" max="58" width="14.6640625" customWidth="1" style="3"/>
-    <col min="59" max="59" width="10.1640625" customWidth="1" style="3"/>
-    <col min="60" max="60" width="8.25" customWidth="1" style="3"/>
-    <col min="61" max="61" width="8.33203125" customWidth="1" style="3"/>
-    <col min="62" max="62" width="10.1640625" customWidth="1" style="3"/>
-    <col min="63" max="67" width="8.33203125" customWidth="1" style="3"/>
-    <col min="68" max="70" width="11.25" customWidth="1" style="3"/>
-    <col min="71" max="71" width="6.58203125" customWidth="1" style="3"/>
-    <col min="72" max="73" width="8" customWidth="1" style="3"/>
-    <col min="74" max="74" width="7.33203125" customWidth="1" style="3"/>
-    <col min="75" max="76" width="8.5" customWidth="1" style="3"/>
-    <col min="77" max="78" width="7.83203125" customWidth="1" style="3"/>
-    <col min="79" max="79" width="22.1640625" customWidth="1" style="3"/>
-    <col min="80" max="80" width="13.5" customWidth="1" style="3"/>
-    <col min="81" max="81" width="21.1640625" customWidth="1" style="3"/>
-    <col min="82" max="82" width="15.75" customWidth="1" style="3"/>
-    <col min="83" max="83" width="15.58203125" customWidth="1" style="3"/>
-    <col min="84" max="84" width="12.83203125" customWidth="1" style="3"/>
-    <col min="85" max="85" width="16.1640625" customWidth="1" style="3"/>
-    <col min="86" max="86" width="9" customWidth="1" style="3"/>
-    <col min="87" max="87" width="16" customWidth="1" style="3"/>
-    <col min="88" max="89" width="12.83203125" customWidth="1" style="3"/>
-    <col min="90" max="90" width="23.58203125" customWidth="1" style="3"/>
-    <col min="91" max="91" width="12.83203125" customWidth="1" style="3"/>
-    <col min="92" max="92" width="17.08203125" customWidth="1" style="3"/>
-    <col min="93" max="98" width="9" customWidth="1" style="3"/>
-    <col min="99" max="99" width="14" customWidth="1" style="3"/>
-    <col min="100" max="100" width="8" customWidth="1" style="3"/>
-    <col min="101" max="101" width="9" customWidth="1" style="3"/>
-    <col min="102" max="102" width="11.08203125" customWidth="1" style="3"/>
-    <col min="103" max="103" width="13.75" customWidth="1" style="3"/>
-    <col min="104" max="109" width="9" customWidth="1" style="3"/>
-    <col min="110" max="110" width="15.5" customWidth="1" style="3"/>
-    <col min="111" max="113" width="9" customWidth="1" style="3"/>
+    <col min="1" max="1" width="21.08203125" customWidth="1"/>
+    <col min="2" max="2" width="15.58203125" customWidth="1"/>
+    <col min="3" max="3" width="7.75" customWidth="1"/>
+    <col min="4" max="4" width="16.58203125" customWidth="1"/>
+    <col min="5" max="5" width="16.83203125" customWidth="1"/>
+    <col min="6" max="6" width="31.33203125" customWidth="1"/>
+    <col min="7" max="7" width="7.33203125" customWidth="1"/>
+    <col min="8" max="8" width="20.58203125" customWidth="1"/>
+    <col min="9" max="9" width="10.75" customWidth="1"/>
+    <col min="10" max="10" width="15.75" customWidth="1"/>
+    <col min="11" max="13" width="8.33203125" customWidth="1"/>
+    <col min="14" max="14" width="11.75" customWidth="1"/>
+    <col min="15" max="15" width="13.08203125" customWidth="1"/>
+    <col min="16" max="16" width="11.58203125" customWidth="1"/>
+    <col min="17" max="17" width="21.5" customWidth="1"/>
+    <col min="18" max="18" width="19.83203125" customWidth="1"/>
+    <col min="19" max="19" width="16.58203125" customWidth="1"/>
+    <col min="20" max="20" width="19.08203125" customWidth="1"/>
+    <col min="21" max="21" width="18.33203125" customWidth="1"/>
+    <col min="22" max="22" width="17.75" customWidth="1"/>
+    <col min="23" max="23" width="8.33203125" customWidth="1"/>
+    <col min="24" max="24" width="18.5" customWidth="1"/>
+    <col min="25" max="25" width="16.58203125" customWidth="1"/>
+    <col min="26" max="26" width="10.6640625" customWidth="1"/>
+    <col min="27" max="27" width="8.33203125" customWidth="1"/>
+    <col min="28" max="28" width="15.1640625" customWidth="1"/>
+    <col min="29" max="30" width="8.58203125" customWidth="1"/>
+    <col min="31" max="31" width="13.4140625" customWidth="1"/>
+    <col min="32" max="32" width="13.75" customWidth="1"/>
+    <col min="33" max="33" width="14.58203125" customWidth="1"/>
+    <col min="34" max="34" width="17.4140625" customWidth="1"/>
+    <col min="35" max="35" width="8.58203125" customWidth="1"/>
+    <col min="36" max="36" width="12.5" customWidth="1"/>
+    <col min="37" max="37" width="8.58203125" customWidth="1"/>
+    <col min="38" max="39" width="8.33203125" customWidth="1"/>
+    <col min="40" max="40" width="15" customWidth="1"/>
+    <col min="41" max="41" width="18" customWidth="1"/>
+    <col min="42" max="42" width="20.58203125" customWidth="1"/>
+    <col min="43" max="45" width="11.83203125" customWidth="1"/>
+    <col min="46" max="46" width="18.4140625" customWidth="1"/>
+    <col min="47" max="47" width="12.25" customWidth="1"/>
+    <col min="48" max="48" width="11.9140625" customWidth="1"/>
+    <col min="49" max="49" width="19.58203125" customWidth="1"/>
+    <col min="50" max="50" width="12.6640625" customWidth="1"/>
+    <col min="51" max="51" width="9" customWidth="1"/>
+    <col min="52" max="52" width="7" customWidth="1"/>
+    <col min="53" max="53" width="11.75" customWidth="1"/>
+    <col min="54" max="54" width="19.75" customWidth="1"/>
+    <col min="55" max="55" width="5.08203125" customWidth="1"/>
+    <col min="56" max="56" width="8.5" customWidth="1"/>
+    <col min="57" max="57" width="13.5" customWidth="1"/>
+    <col min="58" max="58" width="14.6640625" customWidth="1"/>
+    <col min="59" max="59" width="10.1640625" customWidth="1"/>
+    <col min="60" max="60" width="8.25" customWidth="1"/>
+    <col min="61" max="61" width="8.33203125" customWidth="1"/>
+    <col min="62" max="62" width="10.1640625" customWidth="1"/>
+    <col min="63" max="67" width="8.33203125" customWidth="1"/>
+    <col min="68" max="70" width="11.25" customWidth="1"/>
+    <col min="71" max="71" width="6.58203125" customWidth="1"/>
+    <col min="72" max="73" width="8" customWidth="1"/>
+    <col min="74" max="74" width="7.33203125" customWidth="1"/>
+    <col min="75" max="76" width="8.5" customWidth="1"/>
+    <col min="77" max="78" width="7.83203125" customWidth="1"/>
+    <col min="79" max="79" width="22.1640625" customWidth="1"/>
+    <col min="80" max="80" width="13.5" customWidth="1"/>
+    <col min="81" max="81" width="21.1640625" customWidth="1"/>
+    <col min="82" max="82" width="15.75" customWidth="1"/>
+    <col min="83" max="83" width="15.58203125" customWidth="1"/>
+    <col min="84" max="84" width="12.83203125" customWidth="1"/>
+    <col min="85" max="85" width="16.1640625" customWidth="1"/>
+    <col min="86" max="86" width="9" customWidth="1"/>
+    <col min="87" max="87" width="16" customWidth="1"/>
+    <col min="88" max="89" width="12.83203125" customWidth="1"/>
+    <col min="90" max="90" width="23.58203125" customWidth="1"/>
+    <col min="91" max="91" width="12.83203125" customWidth="1"/>
+    <col min="92" max="92" width="17.08203125" customWidth="1"/>
+    <col min="93" max="98" width="9" customWidth="1"/>
+    <col min="99" max="99" width="14" customWidth="1"/>
+    <col min="100" max="100" width="8" customWidth="1"/>
+    <col min="101" max="101" width="9" customWidth="1"/>
+    <col min="102" max="102" width="11.08203125" customWidth="1"/>
+    <col min="103" max="103" width="13.75" customWidth="1"/>
+    <col min="104" max="109" width="9" customWidth="1"/>
+    <col min="110" max="110" width="15.5" customWidth="1"/>
+    <col min="111" max="113" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="3" t="s">
+    <row r="1" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
         <v>162</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" t="s">
         <v>163</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" t="s">
         <v>164</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" t="s">
         <v>165</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" t="s">
         <v>166</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" t="s">
         <v>167</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" t="s">
         <v>168</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" t="s">
         <v>169</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" t="s">
         <v>170</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" t="s">
         <v>171</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" t="s">
         <v>172</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" t="s">
         <v>173</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" t="s">
         <v>174</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" t="s">
         <v>175</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" t="s">
         <v>176</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="R1" t="s">
         <v>177</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="S1" t="s">
         <v>178</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="T1" t="s">
         <v>179</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="U1" t="s">
         <v>179</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="V1" t="s">
         <v>180</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="W1" t="s">
         <v>181</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="X1" t="s">
         <v>182</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="Y1" t="s">
         <v>183</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="Z1" t="s">
         <v>184</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AA1" t="s">
         <v>185</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AB1" t="s">
         <v>186</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AC1" t="s">
         <v>187</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AD1" t="s">
         <v>188</v>
       </c>
-      <c r="AE1" s="3" t="s">
+      <c r="AE1" t="s">
         <v>189</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AF1" t="s">
         <v>190</v>
       </c>
-      <c r="AG1" s="3" t="s">
+      <c r="AG1" t="s">
         <v>191</v>
       </c>
-      <c r="AH1" s="3" t="s">
+      <c r="AH1" t="s">
         <v>192</v>
       </c>
-      <c r="AI1" s="3" t="s">
+      <c r="AI1" t="s">
         <v>193</v>
       </c>
-      <c r="AJ1" s="3" t="s">
+      <c r="AJ1" t="s">
         <v>194</v>
       </c>
-      <c r="AK1" s="3" t="s">
+      <c r="AK1" t="s">
         <v>195</v>
       </c>
-      <c r="AL1" s="3" t="s">
+      <c r="AL1" t="s">
         <v>196</v>
       </c>
-      <c r="AM1" s="3" t="s">
+      <c r="AM1" t="s">
         <v>197</v>
       </c>
-      <c r="AN1" s="3" t="s">
+      <c r="AN1" t="s">
         <v>198</v>
       </c>
-      <c r="AO1" s="3" t="s">
+      <c r="AO1" t="s">
         <v>199</v>
       </c>
-      <c r="AP1" s="3" t="s">
+      <c r="AP1" t="s">
         <v>200</v>
       </c>
-      <c r="AQ1" s="3" t="s">
+      <c r="AQ1" t="s">
         <v>201</v>
       </c>
-      <c r="AR1" s="3" t="s">
+      <c r="AR1" t="s">
         <v>202</v>
       </c>
-      <c r="AS1" s="3" t="s">
+      <c r="AS1" t="s">
         <v>203</v>
       </c>
-      <c r="AT1" s="3" t="s">
+      <c r="AT1" t="s">
         <v>204</v>
       </c>
-      <c r="AU1" s="3" t="s">
+      <c r="AU1" t="s">
         <v>205</v>
       </c>
-      <c r="AV1" s="3" t="s">
+      <c r="AV1" t="s">
         <v>206</v>
       </c>
-      <c r="AW1" s="3" t="s">
+      <c r="AW1" t="s">
         <v>207</v>
       </c>
-      <c r="AX1" s="3" t="s">
+      <c r="AX1" t="s">
         <v>208</v>
       </c>
-      <c r="AY1" s="3" t="s">
+      <c r="AY1" t="s">
         <v>209</v>
       </c>
-      <c r="AZ1" s="3" t="s">
+      <c r="AZ1" t="s">
         <v>210</v>
       </c>
-      <c r="BA1" s="3" t="s">
+      <c r="BA1" t="s">
         <v>211</v>
       </c>
-      <c r="BB1" s="3" t="s">
+      <c r="BB1" t="s">
         <v>212</v>
       </c>
-      <c r="BC1" s="3" t="s">
+      <c r="BC1" t="s">
         <v>213</v>
       </c>
-      <c r="BD1" s="3" t="s">
+      <c r="BD1" t="s">
         <v>214</v>
       </c>
-      <c r="BE1" s="3" t="s">
+      <c r="BE1" t="s">
         <v>215</v>
       </c>
-      <c r="BF1" s="3" t="s">
+      <c r="BF1" t="s">
         <v>216</v>
       </c>
-      <c r="BG1" s="3" t="s">
+      <c r="BG1" t="s">
         <v>217</v>
       </c>
-      <c r="BH1" s="3" t="s">
+      <c r="BH1" t="s">
         <v>218</v>
       </c>
-      <c r="BJ1" s="3" t="s">
+      <c r="BJ1" t="s">
         <v>218</v>
       </c>
-      <c r="BK1" s="3" t="s">
+      <c r="BK1" t="s">
         <v>219</v>
       </c>
-      <c r="BL1" s="3" t="s">
+      <c r="BL1" t="s">
         <v>220</v>
       </c>
-      <c r="BM1" s="3" t="s">
+      <c r="BM1" t="s">
         <v>221</v>
       </c>
-      <c r="BN1" s="3" t="s">
+      <c r="BN1" t="s">
         <v>222</v>
       </c>
-      <c r="BO1" s="3" t="s">
+      <c r="BO1" t="s">
         <v>223</v>
       </c>
-      <c r="BP1" s="3" t="s">
+      <c r="BP1" t="s">
         <v>224</v>
       </c>
-      <c r="BQ1" s="3" t="s">
+      <c r="BQ1" t="s">
         <v>225</v>
       </c>
-      <c r="BR1" s="3" t="s">
+      <c r="BR1" t="s">
         <v>226</v>
       </c>
-      <c r="BS1" s="3" t="s">
+      <c r="BS1" t="s">
         <v>227</v>
       </c>
-      <c r="BT1" s="3" t="s">
+      <c r="BT1" t="s">
         <v>228</v>
       </c>
-      <c r="BU1" s="3" t="s">
+      <c r="BU1" t="s">
         <v>229</v>
       </c>
-      <c r="BV1" s="3" t="s">
+      <c r="BV1" t="s">
         <v>230</v>
       </c>
-      <c r="BW1" s="3" t="s">
+      <c r="BW1" t="s">
         <v>231</v>
       </c>
-      <c r="BX1" s="3" t="s">
+      <c r="BX1" t="s">
         <v>232</v>
       </c>
-      <c r="BY1" s="3" t="s">
+      <c r="BY1" t="s">
         <v>233</v>
       </c>
-      <c r="BZ1" s="3" t="s">
+      <c r="BZ1" t="s">
         <v>234</v>
       </c>
-      <c r="CA1" s="3" t="s">
+      <c r="CA1" t="s">
         <v>235</v>
       </c>
-      <c r="CB1" s="3" t="s">
+      <c r="CB1" t="s">
         <v>236</v>
       </c>
-      <c r="CC1" s="3" t="s">
+      <c r="CC1" t="s">
         <v>237</v>
       </c>
-      <c r="CD1" s="3" t="s">
+      <c r="CD1" t="s">
         <v>238</v>
       </c>
-      <c r="CE1" s="3" t="s">
+      <c r="CE1" t="s">
         <v>239</v>
       </c>
-      <c r="CF1" s="3" t="s">
+      <c r="CF1" t="s">
         <v>240</v>
       </c>
-      <c r="CG1" s="3" t="s">
+      <c r="CG1" t="s">
         <v>241</v>
       </c>
-      <c r="CH1" s="3" t="s">
+      <c r="CH1" t="s">
         <v>242</v>
       </c>
-      <c r="CI1" s="3" t="s">
+      <c r="CI1" t="s">
         <v>243</v>
       </c>
-      <c r="CJ1" s="3" t="s">
+      <c r="CJ1" t="s">
         <v>244</v>
       </c>
-      <c r="CK1" s="3" t="s">
+      <c r="CK1" t="s">
         <v>245</v>
       </c>
-      <c r="CL1" s="3" t="s">
+      <c r="CL1" t="s">
         <v>246</v>
       </c>
-      <c r="CM1" s="3" t="s">
+      <c r="CM1" t="s">
         <v>247</v>
       </c>
-      <c r="CN1" s="3" t="s">
+      <c r="CN1" t="s">
         <v>248</v>
       </c>
-      <c r="CO1" s="3" t="s">
+      <c r="CO1" t="s">
         <v>249</v>
       </c>
-      <c r="CP1" s="3" t="s">
+      <c r="CP1" t="s">
         <v>250</v>
       </c>
-      <c r="CQ1" s="3" t="s">
+      <c r="CQ1" t="s">
         <v>251</v>
       </c>
-      <c r="CR1" s="3" t="s">
+      <c r="CR1" t="s">
         <v>228</v>
       </c>
-      <c r="CS1" s="3" t="s">
+      <c r="CS1" t="s">
         <v>252</v>
       </c>
-      <c r="CT1" s="3" t="s">
+      <c r="CT1" t="s">
         <v>253</v>
       </c>
-      <c r="CU1" s="3" t="s">
+      <c r="CU1" t="s">
         <v>254</v>
       </c>
-      <c r="CV1" s="3" t="s">
+      <c r="CV1" t="s">
         <v>255</v>
       </c>
-      <c r="CW1" s="3" t="s">
+      <c r="CW1" t="s">
         <v>256</v>
       </c>
-      <c r="CX1" s="3" t="s">
+      <c r="CX1" t="s">
         <v>257</v>
       </c>
-      <c r="CY1" s="3" t="s">
+      <c r="CY1" t="s">
         <v>258</v>
       </c>
-      <c r="CZ1" s="3" t="s">
+      <c r="CZ1" t="s">
         <v>257</v>
       </c>
-      <c r="DA1" s="3" t="s">
+      <c r="DA1" t="s">
         <v>259</v>
       </c>
-      <c r="DB1" s="3" t="s">
+      <c r="DB1" t="s">
         <v>260</v>
       </c>
-      <c r="DC1" s="3" t="s">
+      <c r="DC1" t="s">
         <v>261</v>
       </c>
-      <c r="DD1" s="3" t="s">
+      <c r="DD1" t="s">
         <v>262</v>
       </c>
-      <c r="DE1" s="3" t="s">
+      <c r="DE1" t="s">
         <v>263</v>
       </c>
-      <c r="DF1" s="3" t="s">
+      <c r="DF1" t="s">
         <v>264</v>
       </c>
-      <c r="DG1" s="3" t="s">
+      <c r="DG1" t="s">
         <v>265</v>
       </c>
-      <c r="DH1" s="3" t="s">
+      <c r="DH1" t="s">
         <v>266</v>
       </c>
-      <c r="DI1" s="3" t="s">
+      <c r="DI1" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" t="s">
         <v>83</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" t="s">
         <v>268</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" t="s">
         <v>269</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" t="s">
         <v>57</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" t="s">
         <v>270</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" t="s">
         <v>271</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" t="s">
         <v>272</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" t="s">
         <v>273</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="L2" t="s">
         <v>274</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="M2" t="s">
         <v>275</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="N2" t="s">
         <v>276</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="O2" t="s">
         <v>277</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="P2" t="s">
         <v>278</v>
       </c>
-      <c r="Q2" s="3" t="s">
+      <c r="Q2" t="s">
         <v>279</v>
       </c>
-      <c r="R2" s="3" t="s">
+      <c r="R2" t="s">
         <v>280</v>
       </c>
-      <c r="S2" s="3" t="s">
+      <c r="S2" t="s">
         <v>281</v>
       </c>
-      <c r="T2" s="3" t="s">
+      <c r="T2" t="s">
         <v>282</v>
       </c>
-      <c r="U2" s="3" t="s">
+      <c r="U2" t="s">
         <v>283</v>
       </c>
-      <c r="V2" s="3" t="s">
+      <c r="V2" t="s">
         <v>284</v>
       </c>
-      <c r="W2" s="3" t="s">
+      <c r="W2" t="s">
         <v>285</v>
       </c>
-      <c r="X2" s="3" t="s">
+      <c r="X2" t="s">
         <v>286</v>
       </c>
-      <c r="Y2" s="3" t="s">
+      <c r="Y2" t="s">
         <v>287</v>
       </c>
-      <c r="Z2" s="3" t="s">
+      <c r="Z2" t="s">
         <v>288</v>
       </c>
-      <c r="AA2" s="3" t="s">
+      <c r="AA2" t="s">
         <v>289</v>
       </c>
-      <c r="AB2" s="3" t="s">
+      <c r="AB2" t="s">
         <v>290</v>
       </c>
-      <c r="AC2" s="3" t="s">
+      <c r="AC2" t="s">
         <v>291</v>
       </c>
-      <c r="AD2" s="3" t="s">
+      <c r="AD2" t="s">
         <v>292</v>
       </c>
-      <c r="AE2" s="3" t="s">
+      <c r="AE2" t="s">
         <v>293</v>
       </c>
-      <c r="AF2" s="3" t="s">
+      <c r="AF2" t="s">
         <v>294</v>
       </c>
-      <c r="AG2" s="3" t="s">
+      <c r="AG2" t="s">
         <v>295</v>
       </c>
-      <c r="AH2" s="3" t="s">
+      <c r="AH2" t="s">
         <v>296</v>
       </c>
-      <c r="AI2" s="3" t="s">
+      <c r="AI2" t="s">
         <v>297</v>
       </c>
-      <c r="AJ2" s="3" t="s">
+      <c r="AJ2" t="s">
         <v>298</v>
       </c>
-      <c r="AK2" s="3" t="s">
+      <c r="AK2" t="s">
         <v>299</v>
       </c>
-      <c r="AL2" s="3" t="s">
+      <c r="AL2" t="s">
         <v>300</v>
       </c>
-      <c r="AM2" s="3" t="s">
+      <c r="AM2" t="s">
         <v>301</v>
       </c>
-      <c r="AN2" s="3" t="s">
+      <c r="AN2" t="s">
         <v>302</v>
       </c>
-      <c r="AO2" s="3" t="s">
+      <c r="AO2" t="s">
         <v>303</v>
       </c>
-      <c r="AP2" s="3" t="s">
+      <c r="AP2" t="s">
         <v>304</v>
       </c>
-      <c r="AQ2" s="3" t="s">
+      <c r="AQ2" t="s">
         <v>305</v>
       </c>
-      <c r="AR2" s="3" t="s">
+      <c r="AR2" t="s">
         <v>306</v>
       </c>
-      <c r="AS2" s="3" t="s">
+      <c r="AS2" t="s">
         <v>307</v>
       </c>
-      <c r="AT2" s="3" t="s">
+      <c r="AT2" t="s">
         <v>308</v>
       </c>
-      <c r="AU2" s="3" t="s">
+      <c r="AU2" t="s">
         <v>309</v>
       </c>
-      <c r="AV2" s="3" t="s">
+      <c r="AV2" t="s">
         <v>310</v>
       </c>
-      <c r="AW2" s="3" t="s">
+      <c r="AW2" t="s">
         <v>311</v>
       </c>
-      <c r="AX2" s="3" t="s">
+      <c r="AX2" t="s">
         <v>312</v>
       </c>
-      <c r="AY2" s="3" t="s">
+      <c r="AY2" t="s">
         <v>313</v>
       </c>
-      <c r="AZ2" s="3" t="s">
+      <c r="AZ2" t="s">
         <v>314</v>
       </c>
-      <c r="BA2" s="3" t="s">
+      <c r="BA2" t="s">
         <v>315</v>
       </c>
-      <c r="BB2" s="3" t="s">
+      <c r="BB2" t="s">
         <v>316</v>
       </c>
-      <c r="BC2" s="3" t="s">
+      <c r="BC2" t="s">
         <v>317</v>
       </c>
-      <c r="BD2" s="3" t="s">
+      <c r="BD2" t="s">
         <v>318</v>
       </c>
-      <c r="BE2" s="3" t="s">
+      <c r="BE2" t="s">
         <v>319</v>
       </c>
-      <c r="BF2" s="3" t="s">
+      <c r="BF2" t="s">
         <v>320</v>
       </c>
-      <c r="BG2" s="3" t="s">
+      <c r="BG2" t="s">
         <v>321</v>
       </c>
-      <c r="BH2" s="3" t="s">
+      <c r="BH2" t="s">
         <v>322</v>
       </c>
-      <c r="BI2" s="3" t="s">
+      <c r="BI2" t="s">
         <v>323</v>
       </c>
-      <c r="BJ2" s="3" t="s">
+      <c r="BJ2" t="s">
         <v>324</v>
       </c>
-      <c r="BK2" s="3" t="s">
+      <c r="BK2" t="s">
         <v>325</v>
       </c>
-      <c r="BL2" s="3" t="s">
+      <c r="BL2" t="s">
         <v>326</v>
       </c>
-      <c r="BM2" s="3" t="s">
+      <c r="BM2" t="s">
         <v>327</v>
       </c>
-      <c r="BN2" s="3" t="s">
+      <c r="BN2" t="s">
         <v>328</v>
       </c>
-      <c r="BO2" s="3" t="s">
+      <c r="BO2" t="s">
         <v>85</v>
       </c>
-      <c r="BP2" s="3" t="s">
+      <c r="BP2" t="s">
         <v>329</v>
       </c>
-      <c r="BQ2" s="3" t="s">
+      <c r="BQ2" t="s">
         <v>330</v>
       </c>
-      <c r="BR2" s="3" t="s">
+      <c r="BR2" t="s">
         <v>331</v>
       </c>
-      <c r="BS2" s="3" t="s">
+      <c r="BS2" t="s">
         <v>332</v>
       </c>
-      <c r="BT2" s="3" t="s">
+      <c r="BT2" t="s">
         <v>333</v>
       </c>
-      <c r="BU2" s="3" t="s">
+      <c r="BU2" t="s">
         <v>101</v>
       </c>
-      <c r="BV2" s="3" t="s">
+      <c r="BV2" t="s">
         <v>334</v>
       </c>
-      <c r="BW2" s="3" t="s">
+      <c r="BW2" t="s">
         <v>335</v>
       </c>
-      <c r="BX2" s="3" t="s">
+      <c r="BX2" t="s">
         <v>336</v>
       </c>
-      <c r="BY2" s="3" t="s">
+      <c r="BY2" t="s">
         <v>337</v>
       </c>
-      <c r="BZ2" s="3" t="s">
+      <c r="BZ2" t="s">
         <v>338</v>
       </c>
-      <c r="CA2" s="3" t="s">
+      <c r="CA2" t="s">
         <v>339</v>
       </c>
-      <c r="CB2" s="3" t="s">
+      <c r="CB2" t="s">
         <v>340</v>
       </c>
-      <c r="CC2" s="3" t="s">
+      <c r="CC2" t="s">
         <v>341</v>
       </c>
-      <c r="CD2" s="3" t="s">
+      <c r="CD2" t="s">
         <v>342</v>
       </c>
-      <c r="CE2" s="3" t="s">
+      <c r="CE2" t="s">
         <v>343</v>
       </c>
-      <c r="CF2" s="3" t="s">
+      <c r="CF2" t="s">
         <v>344</v>
       </c>
-      <c r="CG2" s="3" t="s">
+      <c r="CG2" t="s">
         <v>345</v>
       </c>
-      <c r="CH2" s="3" t="s">
+      <c r="CH2" t="s">
         <v>346</v>
       </c>
-      <c r="CI2" s="3" t="s">
+      <c r="CI2" t="s">
         <v>347</v>
       </c>
-      <c r="CJ2" s="3" t="s">
+      <c r="CJ2" t="s">
         <v>348</v>
       </c>
-      <c r="CK2" s="3" t="s">
+      <c r="CK2" t="s">
         <v>349</v>
       </c>
-      <c r="CL2" s="3" t="s">
+      <c r="CL2" t="s">
         <v>350</v>
       </c>
-      <c r="CM2" s="3" t="s">
+      <c r="CM2" t="s">
         <v>351</v>
       </c>
-      <c r="CN2" s="3" t="s">
+      <c r="CN2" t="s">
         <v>352</v>
       </c>
-      <c r="CO2" s="3" t="s">
+      <c r="CO2" t="s">
         <v>353</v>
       </c>
-      <c r="CP2" s="3" t="s">
+      <c r="CP2" t="s">
         <v>354</v>
       </c>
-      <c r="CQ2" s="3" t="s">
+      <c r="CQ2" t="s">
         <v>355</v>
       </c>
-      <c r="CR2" s="3" t="s">
+      <c r="CR2" t="s">
         <v>356</v>
       </c>
-      <c r="CS2" s="3" t="s">
+      <c r="CS2" t="s">
         <v>357</v>
       </c>
-      <c r="CT2" s="3" t="s">
+      <c r="CT2" t="s">
         <v>358</v>
       </c>
-      <c r="CU2" s="3" t="s">
+      <c r="CU2" t="s">
         <v>359</v>
       </c>
-      <c r="CV2" s="3" t="s">
+      <c r="CV2" t="s">
         <v>360</v>
       </c>
-      <c r="CW2" s="3" t="s">
+      <c r="CW2" t="s">
         <v>361</v>
       </c>
-      <c r="CX2" s="3" t="s">
+      <c r="CX2" t="s">
         <v>362</v>
       </c>
-      <c r="CY2" s="3" t="s">
+      <c r="CY2" t="s">
         <v>363</v>
       </c>
-      <c r="CZ2" s="3" t="s">
+      <c r="CZ2" t="s">
         <v>364</v>
       </c>
-      <c r="DA2" s="3" t="s">
+      <c r="DA2" t="s">
         <v>365</v>
       </c>
-      <c r="DB2" s="3" t="s">
+      <c r="DB2" t="s">
         <v>366</v>
       </c>
-      <c r="DC2" s="3" t="s">
+      <c r="DC2" t="s">
         <v>367</v>
       </c>
-      <c r="DD2" s="3" t="s">
+      <c r="DD2" t="s">
         <v>368</v>
       </c>
-      <c r="DE2" s="3" t="s">
+      <c r="DE2" t="s">
         <v>369</v>
       </c>
-      <c r="DF2" s="3" t="s">
+      <c r="DF2" t="s">
         <v>370</v>
       </c>
-      <c r="DG2" s="3" t="s">
+      <c r="DG2" t="s">
         <v>371</v>
       </c>
-      <c r="DH2" s="3" t="s">
+      <c r="DH2" t="s">
         <v>372</v>
       </c>
-      <c r="DI2" s="3" t="s">
+      <c r="DI2" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" t="s">
         <v>127</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" t="s">
         <v>124</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" t="s">
         <v>374</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" t="s">
         <v>375</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="L3" t="s">
         <v>376</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="M3" t="s">
         <v>127</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="N3" t="s">
         <v>127</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="O3" t="s">
         <v>130</v>
       </c>
-      <c r="P3" s="3" t="s">
+      <c r="P3" t="s">
         <v>130</v>
       </c>
-      <c r="Q3" s="3" t="s">
+      <c r="Q3" t="s">
         <v>130</v>
       </c>
-      <c r="R3" s="3" t="s">
+      <c r="R3" t="s">
         <v>130</v>
       </c>
-      <c r="S3" s="3" t="s">
+      <c r="S3" t="s">
         <v>124</v>
       </c>
-      <c r="T3" s="3" t="s">
+      <c r="T3" t="s">
         <v>125</v>
       </c>
-      <c r="U3" s="3" t="s">
+      <c r="U3" t="s">
         <v>125</v>
       </c>
-      <c r="V3" s="3" t="s">
+      <c r="V3" t="s">
         <v>125</v>
       </c>
-      <c r="W3" s="3" t="s">
+      <c r="W3" t="s">
         <v>124</v>
       </c>
-      <c r="X3" s="3" t="s">
+      <c r="X3" t="s">
         <v>124</v>
       </c>
-      <c r="Y3" s="3" t="s">
+      <c r="Y3" t="s">
         <v>124</v>
       </c>
-      <c r="Z3" s="3" t="s">
+      <c r="Z3" t="s">
         <v>124</v>
       </c>
-      <c r="AA3" s="3" t="s">
+      <c r="AA3" t="s">
         <v>125</v>
       </c>
-      <c r="AB3" s="3" t="s">
+      <c r="AB3" t="s">
         <v>124</v>
       </c>
-      <c r="AC3" s="3" t="s">
+      <c r="AC3" t="s">
         <v>127</v>
       </c>
-      <c r="AD3" s="3" t="s">
+      <c r="AD3" t="s">
         <v>124</v>
       </c>
-      <c r="AE3" s="3" t="s">
+      <c r="AE3" t="s">
         <v>124</v>
       </c>
-      <c r="AF3" s="3" t="s">
+      <c r="AF3" t="s">
         <v>124</v>
       </c>
-      <c r="AG3" s="3" t="s">
+      <c r="AG3" t="s">
         <v>377</v>
       </c>
-      <c r="AH3" s="3" t="s">
+      <c r="AH3" t="s">
         <v>124</v>
       </c>
-      <c r="AI3" s="3" t="s">
+      <c r="AI3" t="s">
         <v>132</v>
       </c>
-      <c r="AJ3" s="3" t="s">
+      <c r="AJ3" t="s">
         <v>3</v>
       </c>
-      <c r="AK3" s="3" t="s">
+      <c r="AK3" t="s">
         <v>127</v>
       </c>
-      <c r="AL3" s="3" t="s">
+      <c r="AL3" t="s">
         <v>127</v>
       </c>
-      <c r="AM3" s="3" t="s">
+      <c r="AM3" t="s">
         <v>127</v>
       </c>
-      <c r="AN3" s="3" t="s">
+      <c r="AN3" t="s">
         <v>124</v>
       </c>
-      <c r="AO3" s="3" t="s">
+      <c r="AO3" t="s">
         <v>378</v>
       </c>
-      <c r="AP3" s="3" t="s">
+      <c r="AP3" t="s">
         <v>379</v>
       </c>
-      <c r="AQ3" s="3" t="s">
+      <c r="AQ3" t="s">
         <v>2</v>
       </c>
-      <c r="AR3" s="3" t="s">
+      <c r="AR3" t="s">
         <v>2</v>
       </c>
-      <c r="AS3" s="3" t="s">
+      <c r="AS3" t="s">
         <v>2</v>
       </c>
-      <c r="AT3" s="3" t="s">
+      <c r="AT3" t="s">
         <v>380</v>
       </c>
-      <c r="AU3" s="3" t="s">
+      <c r="AU3" t="s">
         <v>124</v>
       </c>
-      <c r="AV3" s="3" t="s">
+      <c r="AV3" t="s">
         <v>125</v>
       </c>
-      <c r="AW3" s="3" t="s">
+      <c r="AW3" t="s">
         <v>124</v>
       </c>
-      <c r="AX3" s="3" t="s">
+      <c r="AX3" t="s">
         <v>381</v>
       </c>
-      <c r="AY3" s="3" t="s">
+      <c r="AY3" t="s">
         <v>124</v>
       </c>
-      <c r="AZ3" s="3" t="s">
+      <c r="AZ3" t="s">
         <v>125</v>
       </c>
-      <c r="BA3" s="3" t="s">
+      <c r="BA3" t="s">
         <v>124</v>
       </c>
-      <c r="BB3" s="3" t="s">
+      <c r="BB3" t="s">
         <v>127</v>
       </c>
-      <c r="BC3" s="3" t="s">
+      <c r="BC3" t="s">
         <v>125</v>
       </c>
-      <c r="BD3" s="3" t="s">
+      <c r="BD3" t="s">
         <v>127</v>
       </c>
-      <c r="BE3" s="3" t="s">
+      <c r="BE3" t="s">
         <v>127</v>
       </c>
-      <c r="BF3" s="3" t="s">
+      <c r="BF3" t="s">
         <v>125</v>
       </c>
-      <c r="BG3" s="3" t="s">
+      <c r="BG3" t="s">
         <v>124</v>
       </c>
-      <c r="BH3" s="3" t="s">
+      <c r="BH3" t="s">
         <v>380</v>
       </c>
-      <c r="BI3" s="3" t="s">
+      <c r="BI3" t="s">
         <v>124</v>
       </c>
-      <c r="BJ3" s="3" t="s">
+      <c r="BJ3" t="s">
         <v>125</v>
       </c>
-      <c r="BK3" s="3" t="s">
+      <c r="BK3" t="s">
         <v>125</v>
       </c>
-      <c r="BL3" s="3" t="s">
+      <c r="BL3" t="s">
         <v>125</v>
       </c>
-      <c r="BM3" s="3" t="s">
+      <c r="BM3" t="s">
         <v>127</v>
       </c>
-      <c r="BN3" s="3" t="s">
+      <c r="BN3" t="s">
         <v>127</v>
       </c>
-      <c r="BO3" s="3" t="s">
+      <c r="BO3" t="s">
         <v>128</v>
       </c>
-      <c r="BP3" s="3" t="s">
+      <c r="BP3" t="s">
         <v>128</v>
       </c>
-      <c r="BQ3" s="3" t="s">
+      <c r="BQ3" t="s">
         <v>382</v>
       </c>
-      <c r="BR3" s="3" t="s">
+      <c r="BR3" t="s">
         <v>383</v>
       </c>
-      <c r="BS3" s="3" t="s">
+      <c r="BS3" t="s">
         <v>125</v>
       </c>
-      <c r="BT3" s="3" t="s">
+      <c r="BT3" t="s">
         <v>125</v>
       </c>
-      <c r="BU3" s="3" t="s">
+      <c r="BU3" t="s">
         <v>124</v>
       </c>
-      <c r="BV3" s="3" t="s">
+      <c r="BV3" t="s">
         <v>125</v>
       </c>
-      <c r="BW3" s="3" t="s">
+      <c r="BW3" t="s">
         <v>125</v>
       </c>
-      <c r="BX3" s="3" t="s">
+      <c r="BX3" t="s">
         <v>127</v>
       </c>
-      <c r="BY3" s="3" t="s">
+      <c r="BY3" t="s">
         <v>384</v>
       </c>
-      <c r="BZ3" s="3" t="s">
+      <c r="BZ3" t="s">
         <v>124</v>
       </c>
-      <c r="CA3" s="3" t="s">
+      <c r="CA3" t="s">
         <v>384</v>
       </c>
-      <c r="CB3" s="3" t="s">
+      <c r="CB3" t="s">
         <v>129</v>
       </c>
-      <c r="CC3" s="3" t="s">
+      <c r="CC3" t="s">
         <v>385</v>
       </c>
-      <c r="CD3" s="3" t="s">
+      <c r="CD3" t="s">
         <v>129</v>
       </c>
-      <c r="CE3" s="3" t="s">
+      <c r="CE3" t="s">
         <v>129</v>
       </c>
-      <c r="CF3" s="3" t="s">
+      <c r="CF3" t="s">
         <v>129</v>
       </c>
-      <c r="CG3" s="3" t="s">
+      <c r="CG3" t="s">
         <v>386</v>
       </c>
-      <c r="CH3" s="3" t="s">
+      <c r="CH3" t="s">
         <v>387</v>
       </c>
-      <c r="CI3" s="3" t="s">
+      <c r="CI3" t="s">
         <v>2</v>
       </c>
-      <c r="CJ3" s="3" t="s">
+      <c r="CJ3" t="s">
         <v>388</v>
       </c>
-      <c r="CK3" s="3" t="s">
+      <c r="CK3" t="s">
         <v>388</v>
       </c>
-      <c r="CL3" s="3" t="s">
+      <c r="CL3" t="s">
         <v>134</v>
       </c>
-      <c r="CM3" s="3" t="s">
+      <c r="CM3" t="s">
         <v>130</v>
       </c>
-      <c r="CN3" s="3" t="s">
+      <c r="CN3" t="s">
         <v>130</v>
       </c>
-      <c r="CO3" s="3" t="s">
+      <c r="CO3" t="s">
         <v>133</v>
       </c>
-      <c r="CP3" s="3" t="s">
+      <c r="CP3" t="s">
         <v>133</v>
       </c>
-      <c r="CQ3" s="3" t="s">
+      <c r="CQ3" t="s">
         <v>133</v>
       </c>
-      <c r="CR3" s="3" t="s">
+      <c r="CR3" t="s">
         <v>385</v>
       </c>
-      <c r="CS3" s="3" t="s">
+      <c r="CS3" t="s">
         <v>133</v>
       </c>
-      <c r="CT3" s="3" t="s">
+      <c r="CT3" t="s">
         <v>124</v>
       </c>
-      <c r="CU3" s="3" t="s">
+      <c r="CU3" t="s">
         <v>134</v>
       </c>
-      <c r="CV3" s="3" t="s">
+      <c r="CV3" t="s">
         <v>389</v>
       </c>
-      <c r="CW3" s="3" t="s">
+      <c r="CW3" t="s">
         <v>390</v>
       </c>
-      <c r="CX3" s="3" t="s">
+      <c r="CX3" t="s">
         <v>390</v>
       </c>
-      <c r="CY3" s="3" t="s">
+      <c r="CY3" t="s">
         <v>389</v>
       </c>
-      <c r="CZ3" s="3" t="s">
+      <c r="CZ3" t="s">
         <v>389</v>
       </c>
-      <c r="DA3" s="3" t="s">
+      <c r="DA3" t="s">
         <v>389</v>
       </c>
-      <c r="DB3" s="3" t="s">
+      <c r="DB3" t="s">
         <v>389</v>
       </c>
-      <c r="DC3" s="3" t="s">
+      <c r="DC3" t="s">
         <v>389</v>
       </c>
-      <c r="DD3" s="3" t="s">
+      <c r="DD3" t="s">
         <v>124</v>
       </c>
-      <c r="DE3" s="3" t="s">
+      <c r="DE3" t="s">
         <v>124</v>
       </c>
-      <c r="DF3" s="3" t="s">
+      <c r="DF3" t="s">
         <v>124</v>
       </c>
-      <c r="DG3" s="3" t="s">
+      <c r="DG3" t="s">
         <v>124</v>
       </c>
-      <c r="DH3" s="3" t="s">
+      <c r="DH3" t="s">
         <v>124</v>
       </c>
-      <c r="DI3" s="3" t="s">
+      <c r="DI3" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>392</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" t="s">
         <v>393</v>
       </c>
-      <c r="K6" s="3" t="s">
+      <c r="K6" t="s">
         <v>394</v>
       </c>
-      <c r="P6" s="3" t="s">
+      <c r="P6" t="s">
         <v>395</v>
       </c>
-      <c r="AC6" s="3">
-        <v>1</v>
-      </c>
-      <c r="AO6" s="3" t="s">
+      <c r="AC6">
+        <v>1</v>
+      </c>
+      <c r="AO6" t="s">
         <v>396</v>
       </c>
-      <c r="AT6" s="3" t="s">
+      <c r="AT6" t="s">
         <v>397</v>
       </c>
-      <c r="AY6" s="3">
-        <v>1</v>
-      </c>
-      <c r="AZ6" s="3">
-        <v>1</v>
-      </c>
-      <c r="BD6" s="3">
-        <v>1</v>
-      </c>
-      <c r="CB6" s="3" t="s">
+      <c r="AY6">
+        <v>1</v>
+      </c>
+      <c r="AZ6">
+        <v>1</v>
+      </c>
+      <c r="BD6">
+        <v>1</v>
+      </c>
+      <c r="CB6" t="s">
         <v>61</v>
       </c>
-      <c r="CG6" s="3" t="s">
+      <c r="CG6" t="s">
         <v>398</v>
       </c>
-      <c r="CH6" s="3" t="s">
+      <c r="CH6" t="s">
         <v>399</v>
       </c>
-      <c r="CI6" s="3" t="s">
+      <c r="CI6" t="s">
         <v>400</v>
       </c>
-      <c r="CN6" s="3" t="s">
+      <c r="CN6" t="s">
         <v>401</v>
       </c>
-      <c r="CR6" s="3">
+      <c r="CR6">
         <v>9999</v>
       </c>
-      <c r="CY6" s="3" t="s">
+      <c r="CY6" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>403</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" t="s">
         <v>404</v>
       </c>
-      <c r="K7" s="3" t="s">
+      <c r="K7" t="s">
         <v>405</v>
       </c>
-      <c r="L7" s="3" t="s">
+      <c r="L7" t="s">
         <v>406</v>
       </c>
-      <c r="Q7" s="3" t="s">
+      <c r="Q7" t="s">
         <v>407</v>
       </c>
-      <c r="AC7" s="3">
-        <v>1</v>
-      </c>
-      <c r="AF7" s="3">
-        <v>1</v>
-      </c>
-      <c r="AV7" s="3">
+      <c r="X7">
+        <v>1</v>
+      </c>
+      <c r="AC7">
+        <v>1</v>
+      </c>
+      <c r="AF7">
+        <v>1</v>
+      </c>
+      <c r="AV7">
         <v>20</v>
       </c>
-      <c r="BD7" s="3">
-        <v>1</v>
-      </c>
-      <c r="CU7" s="3" t="s">
+      <c r="BD7">
+        <v>1</v>
+      </c>
+      <c r="CU7" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="3" t="s">
+    <row r="8" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>409</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" t="s">
         <v>410</v>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="K8" t="s">
         <v>405</v>
       </c>
-      <c r="L8" s="3" t="s">
+      <c r="L8" t="s">
         <v>411</v>
       </c>
-      <c r="AC8" s="3">
-        <v>1</v>
-      </c>
-      <c r="AT8" s="3" t="s">
+      <c r="X8">
+        <v>1</v>
+      </c>
+      <c r="AC8">
+        <v>1</v>
+      </c>
+      <c r="AT8" t="s">
         <v>412</v>
       </c>
-      <c r="BD8" s="3">
-        <v>1</v>
-      </c>
-      <c r="CU8" s="3" t="s">
+      <c r="BD8">
+        <v>1</v>
+      </c>
+      <c r="CU8" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
+    <row r="9" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>414</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" t="s">
         <v>393</v>
       </c>
-      <c r="K9" s="3" t="s">
+      <c r="K9" t="s">
         <v>405</v>
       </c>
-      <c r="L9" s="3" t="s">
+      <c r="L9" t="s">
         <v>415</v>
       </c>
-      <c r="AC9" s="3">
-        <v>1</v>
-      </c>
-      <c r="AT9" s="3" t="s">
+      <c r="AC9">
+        <v>1</v>
+      </c>
+      <c r="AT9" t="s">
         <v>416</v>
       </c>
-      <c r="BD9" s="3">
+      <c r="BD9">
         <v>99</v>
       </c>
-      <c r="CM9" s="3" t="s">
+      <c r="CM9" t="s">
         <v>407</v>
       </c>
-      <c r="CN9" s="3" t="s">
+      <c r="CN9" t="s">
         <v>417</v>
       </c>
-      <c r="CR9" s="3">
+      <c r="CR9">
         <v>9999</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="3" t="s">
+    <row r="10" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>418</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" t="s">
         <v>393</v>
       </c>
-      <c r="I10" s="3">
-        <v>1</v>
-      </c>
-      <c r="K10" s="3" t="s">
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="K10" t="s">
         <v>405</v>
       </c>
-      <c r="L10" s="3" t="s">
+      <c r="L10" t="s">
         <v>411</v>
       </c>
-      <c r="Q10" s="3" t="s">
+      <c r="Q10" t="s">
         <v>419</v>
       </c>
-      <c r="AC10" s="3">
-        <v>1</v>
-      </c>
-      <c r="AG10" s="3" t="s">
+      <c r="AC10">
+        <v>1</v>
+      </c>
+      <c r="AG10" t="s">
         <v>420</v>
       </c>
-      <c r="AN10" s="3">
-        <v>1</v>
-      </c>
-      <c r="AT10" s="3" t="s">
+      <c r="AN10">
+        <v>1</v>
+      </c>
+      <c r="AT10" t="s">
         <v>416</v>
       </c>
-      <c r="BD10" s="3">
+      <c r="BD10">
         <v>99</v>
       </c>
-      <c r="CN10" s="3" t="s">
+      <c r="CN10" t="s">
         <v>421</v>
       </c>
-      <c r="CR10" s="3">
-        <v>1</v>
-      </c>
-      <c r="DD10" s="3">
-        <v>1</v>
-      </c>
-      <c r="DG10" s="3">
-        <v>1</v>
-      </c>
-      <c r="DH10" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
+      <c r="CR10">
+        <v>1</v>
+      </c>
+      <c r="DD10">
+        <v>1</v>
+      </c>
+      <c r="DG10">
+        <v>1</v>
+      </c>
+      <c r="DH10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>419</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" t="s">
         <v>393</v>
       </c>
-      <c r="I11" s="3">
-        <v>1</v>
-      </c>
-      <c r="K11" s="3" t="s">
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="K11" t="s">
         <v>405</v>
       </c>
-      <c r="L11" s="3" t="s">
+      <c r="L11" t="s">
         <v>411</v>
       </c>
-      <c r="AC11" s="3">
-        <v>1</v>
-      </c>
-      <c r="AF11" s="3">
-        <v>1</v>
-      </c>
-      <c r="AG11" s="3" t="s">
+      <c r="AC11">
+        <v>1</v>
+      </c>
+      <c r="AF11">
+        <v>1</v>
+      </c>
+      <c r="AG11" t="s">
         <v>422</v>
       </c>
-      <c r="AN11" s="3">
-        <v>1</v>
-      </c>
-      <c r="BD11" s="3">
-        <v>1</v>
-      </c>
-      <c r="CN11" s="3" t="s">
+      <c r="AN11">
+        <v>1</v>
+      </c>
+      <c r="BD11">
+        <v>1</v>
+      </c>
+      <c r="CN11" t="s">
         <v>423</v>
       </c>
-      <c r="CR11" s="3">
+      <c r="CR11">
         <v>9999</v>
       </c>
-      <c r="DD11" s="3">
-        <v>1</v>
-      </c>
-      <c r="DG11" s="3">
-        <v>1</v>
-      </c>
-      <c r="DH11" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
+      <c r="DD11">
+        <v>1</v>
+      </c>
+      <c r="DG11">
+        <v>1</v>
+      </c>
+      <c r="DH11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>424</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" t="s">
         <v>393</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" t="s">
         <v>425</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" t="s">
         <v>426</v>
       </c>
-      <c r="G13" s="3">
+      <c r="G13">
         <v>3</v>
       </c>
-      <c r="J13" s="3" t="s">
+      <c r="J13" t="s">
         <v>427</v>
       </c>
-      <c r="K13" s="3" t="s">
+      <c r="K13" t="s">
         <v>428</v>
       </c>
-      <c r="AB13" s="3">
-        <v>1</v>
-      </c>
-      <c r="AC13" s="3">
-        <v>1</v>
-      </c>
-      <c r="AG13" s="3" t="s">
+      <c r="AB13">
+        <v>1</v>
+      </c>
+      <c r="AC13">
+        <v>1</v>
+      </c>
+      <c r="AG13" t="s">
         <v>422</v>
       </c>
-      <c r="AO13" s="3" t="s">
+      <c r="AO13" t="s">
         <v>396</v>
       </c>
-      <c r="AT13" s="3" t="s">
+      <c r="AT13" t="s">
         <v>429</v>
       </c>
-      <c r="AY13" s="3">
-        <v>1</v>
-      </c>
-      <c r="AZ13" s="3">
-        <v>1</v>
-      </c>
-      <c r="BD13" s="3">
-        <v>1</v>
-      </c>
-      <c r="BO13" s="3" t="s">
+      <c r="AY13">
+        <v>1</v>
+      </c>
+      <c r="AZ13">
+        <v>1</v>
+      </c>
+      <c r="BD13">
+        <v>1</v>
+      </c>
+      <c r="BO13" t="s">
         <v>430</v>
       </c>
-      <c r="BT13" s="3">
+      <c r="BT13">
         <v>0.2</v>
       </c>
-      <c r="BU13" s="3">
-        <v>1</v>
-      </c>
-      <c r="BV13" s="3">
+      <c r="BU13">
+        <v>1</v>
+      </c>
+      <c r="BV13">
         <v>0</v>
       </c>
-      <c r="BW13" s="3">
+      <c r="BW13">
         <v>5</v>
       </c>
-      <c r="BX13" s="3">
-        <v>1</v>
-      </c>
-      <c r="BY13" s="3" t="s">
+      <c r="BX13">
+        <v>1</v>
+      </c>
+      <c r="BY13" t="s">
         <v>394</v>
       </c>
-      <c r="CN13" s="3" t="s">
+      <c r="CN13" t="s">
         <v>424</v>
       </c>
-      <c r="CO13" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
+      <c r="CO13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>430</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" t="s">
         <v>393</v>
       </c>
-      <c r="K14" s="3" t="s">
+      <c r="K14" t="s">
         <v>394</v>
       </c>
-      <c r="O14" s="3" t="s">
+      <c r="O14" t="s">
         <v>424</v>
       </c>
-      <c r="AC14" s="3">
-        <v>1</v>
-      </c>
-      <c r="AO14" s="3" t="s">
+      <c r="AC14">
+        <v>1</v>
+      </c>
+      <c r="AO14" t="s">
         <v>396</v>
       </c>
-      <c r="AT14" s="3" t="s">
+      <c r="AT14" t="s">
         <v>429</v>
       </c>
-      <c r="AY14" s="3">
-        <v>1</v>
-      </c>
-      <c r="AZ14" s="3">
-        <v>1</v>
-      </c>
-      <c r="BD14" s="3">
-        <v>1</v>
-      </c>
-      <c r="CB14" s="3" t="s">
+      <c r="AY14">
+        <v>1</v>
+      </c>
+      <c r="AZ14">
+        <v>1</v>
+      </c>
+      <c r="BD14">
+        <v>1</v>
+      </c>
+      <c r="CB14" t="s">
         <v>61</v>
       </c>
-      <c r="CG14" s="3" t="s">
+      <c r="CG14" t="s">
         <v>398</v>
       </c>
-      <c r="CH14" s="3" t="s">
+      <c r="CH14" t="s">
         <v>431</v>
       </c>
-      <c r="CI14" s="3" t="s">
+      <c r="CI14" t="s">
         <v>400</v>
       </c>
-      <c r="CN14" s="3" t="s">
+      <c r="CN14" t="s">
         <v>401</v>
       </c>
-      <c r="CR14" s="3">
+      <c r="CR14">
         <v>9999</v>
       </c>
-      <c r="CY14" s="3" t="s">
+      <c r="CY14" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="3" t="s">
+    <row r="16" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>432</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" t="s">
         <v>393</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" t="s">
         <v>433</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="E16" t="s">
         <v>434</v>
       </c>
-      <c r="G16" s="3">
+      <c r="G16">
         <v>3</v>
       </c>
-      <c r="J16" s="3" t="s">
+      <c r="J16" t="s">
         <v>427</v>
       </c>
-      <c r="K16" s="3" t="s">
+      <c r="K16" t="s">
         <v>428</v>
       </c>
-      <c r="Q16" s="3" t="s">
+      <c r="Q16" t="s">
         <v>417</v>
       </c>
-      <c r="AC16" s="3">
-        <v>1</v>
-      </c>
-      <c r="AO16" s="3" t="s">
+      <c r="AC16">
+        <v>1</v>
+      </c>
+      <c r="AO16" t="s">
         <v>396</v>
       </c>
-      <c r="AV16" s="3">
+      <c r="AV16">
         <v>20</v>
       </c>
-      <c r="AY16" s="3">
-        <v>1</v>
-      </c>
-      <c r="AZ16" s="3">
+      <c r="AY16">
+        <v>1</v>
+      </c>
+      <c r="AZ16">
         <v>2.5</v>
       </c>
-      <c r="BD16" s="3">
+      <c r="BD16">
         <v>99</v>
       </c>
-      <c r="BT16" s="3">
+      <c r="BT16">
         <v>0.2</v>
       </c>
-      <c r="BV16" s="3">
+      <c r="BV16">
         <v>30</v>
       </c>
-      <c r="BW16" s="3">
+      <c r="BW16">
         <v>20</v>
       </c>
-      <c r="BX16" s="3">
+      <c r="BX16">
         <v>3</v>
       </c>
-      <c r="BY16" s="3" t="s">
+      <c r="BY16" t="s">
         <v>394</v>
       </c>
-      <c r="CB16" s="3" t="s">
+      <c r="CB16" t="s">
         <v>61</v>
       </c>
-      <c r="CG16" s="3" t="s">
+      <c r="CG16" t="s">
         <v>398</v>
       </c>
-      <c r="CH16" s="3" t="s">
+      <c r="CH16" t="s">
         <v>399</v>
       </c>
-      <c r="CI16" s="3" t="s">
+      <c r="CI16" t="s">
         <v>400</v>
       </c>
-      <c r="CN16" s="3" t="s">
+      <c r="CN16" t="s">
         <v>435</v>
       </c>
-      <c r="CO16" s="3">
+      <c r="CO16">
         <v>0.3</v>
       </c>
-      <c r="CR16" s="3">
+      <c r="CR16">
         <v>8</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="3" t="s">
+    <row r="18" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>436</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" t="s">
         <v>393</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" t="s">
         <v>437</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="E18" t="s">
         <v>438</v>
       </c>
-      <c r="G18" s="3">
+      <c r="G18">
         <v>3</v>
       </c>
-      <c r="J18" s="3" t="s">
+      <c r="J18" t="s">
         <v>427</v>
       </c>
-      <c r="K18" s="3" t="s">
+      <c r="K18" t="s">
         <v>428</v>
       </c>
-      <c r="AC18" s="3">
-        <v>1</v>
-      </c>
-      <c r="AG18" s="3" t="s">
+      <c r="AC18">
+        <v>1</v>
+      </c>
+      <c r="AG18" t="s">
         <v>422</v>
       </c>
-      <c r="BD18" s="3">
-        <v>1</v>
-      </c>
-      <c r="BO18" s="3" t="s">
+      <c r="BD18">
+        <v>1</v>
+      </c>
+      <c r="BO18" t="s">
         <v>439</v>
       </c>
-      <c r="BT18" s="3">
+      <c r="BT18">
         <v>30</v>
       </c>
-      <c r="BV18" s="3">
+      <c r="BV18">
         <v>45</v>
       </c>
-      <c r="BW18" s="3">
+      <c r="BW18">
         <v>50</v>
       </c>
-      <c r="BX18" s="3">
-        <v>1</v>
-      </c>
-      <c r="BY18" s="3" t="s">
+      <c r="BX18">
+        <v>1</v>
+      </c>
+      <c r="BY18" t="s">
         <v>394</v>
       </c>
-      <c r="CN18" s="3" t="s">
+      <c r="CN18" t="s">
         <v>440</v>
       </c>
-      <c r="CO18" s="3">
+      <c r="CO18">
         <v>-0.4</v>
       </c>
-      <c r="CR18" s="3">
+      <c r="CR18">
         <v>30</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="3" t="s">
+    <row r="19" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>441</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" t="s">
         <v>442</v>
       </c>
-      <c r="K19" s="3" t="s">
+      <c r="K19" t="s">
         <v>405</v>
       </c>
-      <c r="L19" s="3" t="s">
+      <c r="L19" t="s">
         <v>443</v>
       </c>
-      <c r="AC19" s="3">
-        <v>1</v>
-      </c>
-      <c r="AF19" s="3">
-        <v>1</v>
-      </c>
-      <c r="AH19" s="3">
-        <v>1</v>
-      </c>
-      <c r="BD19" s="3">
+      <c r="AC19">
+        <v>1</v>
+      </c>
+      <c r="AF19">
+        <v>1</v>
+      </c>
+      <c r="AH19">
+        <v>1</v>
+      </c>
+      <c r="BD19">
         <v>99</v>
       </c>
-      <c r="CU19" s="3" t="s">
+      <c r="CU19" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="3" t="s">
+    <row r="20" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>445</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" t="s">
         <v>404</v>
       </c>
-      <c r="K20" s="3" t="s">
+      <c r="K20" t="s">
         <v>405</v>
       </c>
-      <c r="L20" s="3" t="s">
+      <c r="L20" t="s">
         <v>446</v>
       </c>
-      <c r="O20" s="3" t="s">
+      <c r="O20" t="s">
         <v>417</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="X20">
+        <v>1</v>
+      </c>
+      <c r="AC20">
         <v>2</v>
       </c>
-      <c r="AF20" s="3">
-        <v>1</v>
-      </c>
-      <c r="AH20" s="3">
-        <v>1</v>
-      </c>
-      <c r="BD20" s="3">
+      <c r="AF20">
+        <v>1</v>
+      </c>
+      <c r="AH20">
+        <v>1</v>
+      </c>
+      <c r="BD20">
         <v>99</v>
       </c>
-      <c r="CU20" s="3" t="s">
+      <c r="CU20" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="3" t="s">
+    <row r="21" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>447</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" t="s">
         <v>393</v>
       </c>
-      <c r="K21" s="3" t="s">
+      <c r="K21" t="s">
         <v>405</v>
       </c>
-      <c r="L21" s="3" t="s">
+      <c r="L21" t="s">
         <v>448</v>
       </c>
-      <c r="O21" s="3" t="s">
+      <c r="O21" t="s">
         <v>449</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AC21">
         <v>2</v>
       </c>
-      <c r="AF21" s="3">
-        <v>1</v>
-      </c>
-      <c r="BD21" s="3">
-        <v>1</v>
-      </c>
-      <c r="CN21" s="3" t="s">
+      <c r="AF21">
+        <v>1</v>
+      </c>
+      <c r="BD21">
+        <v>1</v>
+      </c>
+      <c r="CN21" t="s">
         <v>450</v>
       </c>
-      <c r="CR21" s="3">
+      <c r="CR21">
         <v>9999</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="3" t="s">
+    <row r="22" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>451</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" t="s">
         <v>442</v>
       </c>
-      <c r="K22" s="3" t="s">
+      <c r="K22" t="s">
         <v>405</v>
       </c>
-      <c r="L22" s="3" t="s">
+      <c r="L22" t="s">
         <v>415</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AC22">
         <v>2</v>
       </c>
-      <c r="AV22" s="3">
+      <c r="AV22">
         <v>20</v>
       </c>
-      <c r="BD22" s="3">
+      <c r="BD22">
         <v>99</v>
       </c>
-      <c r="CU22" s="3" t="s">
+      <c r="CU22" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="3" t="s">
+    <row r="23" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>453</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" t="s">
         <v>404</v>
       </c>
-      <c r="K23" s="3" t="s">
+      <c r="K23" t="s">
         <v>405</v>
       </c>
-      <c r="L23" s="3" t="s">
+      <c r="L23" t="s">
         <v>454</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AC23">
         <v>2</v>
       </c>
-      <c r="AF23" s="3">
-        <v>1</v>
-      </c>
-      <c r="BD23" s="3">
+      <c r="AF23">
+        <v>1</v>
+      </c>
+      <c r="BD23">
         <v>99</v>
       </c>
-      <c r="CU23" s="3" t="s">
+      <c r="CU23" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="3" t="s">
+    <row r="24" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>455</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" t="s">
         <v>404</v>
       </c>
-      <c r="K24" s="3" t="s">
+      <c r="K24" t="s">
         <v>405</v>
       </c>
-      <c r="L24" s="3" t="s">
+      <c r="L24" t="s">
         <v>454</v>
       </c>
-      <c r="Q24" s="3" t="s">
+      <c r="Q24" t="s">
         <v>417</v>
       </c>
-      <c r="AC24" s="3">
-        <v>1</v>
-      </c>
-      <c r="AF24" s="3">
-        <v>1</v>
-      </c>
-      <c r="AT24" s="3" t="s">
+      <c r="X24">
+        <v>1</v>
+      </c>
+      <c r="AC24">
+        <v>1</v>
+      </c>
+      <c r="AF24">
+        <v>1</v>
+      </c>
+      <c r="AT24" t="s">
         <v>416</v>
       </c>
-      <c r="BD24" s="3">
+      <c r="BD24">
         <v>99</v>
       </c>
-      <c r="CU24" s="3" t="s">
+      <c r="CU24" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="3" t="s">
+    <row r="25" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>456</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" t="s">
         <v>404</v>
       </c>
-      <c r="K25" s="3" t="s">
+      <c r="K25" t="s">
         <v>405</v>
       </c>
-      <c r="L25" s="3" t="s">
+      <c r="L25" t="s">
         <v>457</v>
       </c>
-      <c r="Q25" s="3" t="s">
+      <c r="Q25" t="s">
         <v>417</v>
       </c>
-      <c r="AC25" s="3">
-        <v>1</v>
-      </c>
-      <c r="AF25" s="3">
-        <v>1</v>
-      </c>
-      <c r="AT25" s="3" t="s">
+      <c r="X25">
+        <v>1</v>
+      </c>
+      <c r="AC25">
+        <v>1</v>
+      </c>
+      <c r="AF25">
+        <v>1</v>
+      </c>
+      <c r="AT25" t="s">
         <v>416</v>
       </c>
-      <c r="BD25" s="3">
+      <c r="BD25">
         <v>99</v>
       </c>
-      <c r="CU25" s="3" t="s">
+      <c r="CU25" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="3" t="s">
+    <row r="27" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>458</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" t="s">
         <v>393</v>
       </c>
-      <c r="J27" s="3" t="s">
+      <c r="J27" t="s">
         <v>459</v>
       </c>
-      <c r="K27" s="3" t="s">
+      <c r="K27" t="s">
         <v>394</v>
       </c>
-      <c r="AC27" s="3">
-        <v>1</v>
-      </c>
-      <c r="AO27" s="3" t="s">
+      <c r="AC27">
+        <v>1</v>
+      </c>
+      <c r="AO27" t="s">
         <v>396</v>
       </c>
-      <c r="AT27" s="3" t="s">
+      <c r="AT27" t="s">
         <v>397</v>
       </c>
-      <c r="AY27" s="3">
-        <v>1</v>
-      </c>
-      <c r="AZ27" s="3">
-        <v>1</v>
-      </c>
-      <c r="BD27" s="3">
+      <c r="AY27">
+        <v>1</v>
+      </c>
+      <c r="AZ27">
+        <v>1</v>
+      </c>
+      <c r="BD27">
         <v>3</v>
       </c>
-      <c r="CB27" s="3" t="s">
+      <c r="CB27" t="s">
         <v>61</v>
       </c>
-      <c r="CG27" s="3" t="s">
+      <c r="CG27" t="s">
         <v>398</v>
       </c>
-      <c r="CH27" s="3" t="s">
+      <c r="CH27" t="s">
         <v>399</v>
       </c>
-      <c r="CI27" s="3" t="s">
+      <c r="CI27" t="s">
         <v>400</v>
       </c>
-      <c r="CN27" s="3" t="s">
+      <c r="CN27" t="s">
         <v>401</v>
       </c>
-      <c r="CR27" s="3">
+      <c r="CR27">
         <v>9999</v>
       </c>
-      <c r="CY27" s="3" t="s">
+      <c r="CY27" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="3" t="s">
+    <row r="28" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>460</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" t="s">
         <v>393</v>
       </c>
-      <c r="J28" s="3" t="s">
+      <c r="J28" t="s">
         <v>459</v>
       </c>
-      <c r="K28" s="3" t="s">
+      <c r="K28" t="s">
         <v>394</v>
       </c>
-      <c r="Q28" s="3" t="s">
+      <c r="Q28" t="s">
         <v>417</v>
       </c>
-      <c r="AC28" s="3">
-        <v>1</v>
-      </c>
-      <c r="AO28" s="3" t="s">
+      <c r="AC28">
+        <v>1</v>
+      </c>
+      <c r="AO28" t="s">
         <v>396</v>
       </c>
-      <c r="AV28" s="3">
+      <c r="AV28">
         <v>20</v>
       </c>
-      <c r="BD28" s="3">
-        <v>1</v>
-      </c>
-      <c r="BS28" s="3">
+      <c r="BD28">
+        <v>1</v>
+      </c>
+      <c r="BS28">
         <v>0.01</v>
       </c>
-      <c r="CN28" s="3" t="s">
+      <c r="CN28" t="s">
         <v>461</v>
       </c>
-      <c r="CR28" s="3">
+      <c r="CR28">
         <v>0.02</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="3" t="s">
+    <row r="29" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>462</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C29" t="s">
         <v>393</v>
       </c>
-      <c r="J29" s="3" t="s">
+      <c r="J29" t="s">
         <v>459</v>
       </c>
-      <c r="K29" s="3" t="s">
+      <c r="K29" t="s">
         <v>394</v>
       </c>
-      <c r="Q29" s="3" t="s">
+      <c r="Q29" t="s">
         <v>450</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29">
         <v>2</v>
       </c>
-      <c r="AV29" s="3">
+      <c r="AV29">
         <v>20</v>
       </c>
-      <c r="AX29" s="3" t="s">
+      <c r="AX29" t="s">
         <v>463</v>
       </c>
-      <c r="AZ29" s="3">
+      <c r="AZ29">
         <v>0.8</v>
       </c>
-      <c r="BD29" s="3">
+      <c r="BD29">
         <v>99</v>
       </c>
-      <c r="CM29" s="3" t="s">
+      <c r="CM29" t="s">
         <v>450</v>
       </c>
-      <c r="CY29" s="3" t="s">
+      <c r="CY29" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="3" t="s">
+    <row r="30" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>465</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" t="s">
         <v>466</v>
       </c>
-      <c r="J30" s="3" t="s">
+      <c r="J30" t="s">
         <v>459</v>
       </c>
-      <c r="K30" s="3" t="s">
+      <c r="K30" t="s">
         <v>394</v>
       </c>
-      <c r="Q30" s="3" t="s">
+      <c r="Q30" t="s">
         <v>419</v>
       </c>
-      <c r="AC30" s="3">
-        <v>1</v>
-      </c>
-      <c r="AN30" s="3">
-        <v>1</v>
-      </c>
-      <c r="AV30" s="3">
+      <c r="AC30">
+        <v>1</v>
+      </c>
+      <c r="AN30">
+        <v>1</v>
+      </c>
+      <c r="AV30">
         <v>20</v>
       </c>
-      <c r="BD30" s="3">
+      <c r="BD30">
         <v>99</v>
       </c>
-      <c r="BT30" s="3">
+      <c r="BT30">
         <v>30</v>
       </c>
-      <c r="CU30" s="3" t="s">
+      <c r="CU30" t="s">
         <v>467</v>
       </c>
-      <c r="DD30" s="3">
-        <v>1</v>
-      </c>
-      <c r="DG30" s="3">
-        <v>1</v>
-      </c>
-      <c r="DH30" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="s">
+      <c r="DD30">
+        <v>1</v>
+      </c>
+      <c r="DG30">
+        <v>1</v>
+      </c>
+      <c r="DH30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>468</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" t="s">
         <v>393</v>
       </c>
-      <c r="J31" s="3" t="s">
+      <c r="J31" t="s">
         <v>459</v>
       </c>
-      <c r="K31" s="3" t="s">
+      <c r="K31" t="s">
         <v>394</v>
       </c>
-      <c r="Q31" s="3" t="s">
+      <c r="Q31" t="s">
         <v>417</v>
       </c>
-      <c r="AC31" s="3">
-        <v>1</v>
-      </c>
-      <c r="AV31" s="3">
+      <c r="AC31">
+        <v>1</v>
+      </c>
+      <c r="AV31">
         <v>20</v>
       </c>
-      <c r="BD31" s="3">
+      <c r="BD31">
         <v>99</v>
       </c>
-      <c r="BS31" s="3">
+      <c r="BS31">
         <v>0.01</v>
       </c>
-      <c r="CN31" s="3" t="s">
+      <c r="CN31" t="s">
         <v>449</v>
       </c>
-      <c r="CR31" s="3">
+      <c r="CR31">
         <v>0.02</v>
       </c>
     </row>
-    <row r="669">
-      <c r="CL669" s="3">
+    <row r="669" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL669">
         <v>0.15</v>
       </c>
     </row>
-    <row r="671">
-      <c r="CL671" s="3">
+    <row r="671" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL671">
         <v>0.2</v>
       </c>
     </row>
-    <row r="672">
-      <c r="CL672" s="3">
+    <row r="672" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL672">
         <v>0.1</v>
       </c>
     </row>
-    <row r="674">
-      <c r="CL674" s="3">
+    <row r="674" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL674">
         <v>0.2</v>
       </c>
     </row>
-    <row r="681">
-      <c r="CL681" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="683">
-      <c r="CL683" s="3">
+    <row r="681" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL681">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="683" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL683">
         <v>0.4</v>
       </c>
     </row>
-    <row r="684">
-      <c r="CL684" s="3">
+    <row r="684" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL684">
         <v>0.6</v>
       </c>
     </row>
-    <row r="687">
-      <c r="CL687" s="3">
+    <row r="687" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL687">
         <v>0.5</v>
       </c>
     </row>
-    <row r="688">
-      <c r="CL688" s="3">
-        <v>0.667</v>
-      </c>
-    </row>
-    <row r="689">
-      <c r="CL689" s="3">
+    <row r="688" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL688">
+        <v>0.66700000000000004</v>
+      </c>
+    </row>
+    <row r="689" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL689">
         <v>0.2</v>
       </c>
     </row>
@@ -5706,7 +5452,6 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -5716,261 +5461,261 @@
   <dimension ref="A1:Q15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.08203125" customWidth="1" style="3"/>
-    <col min="2" max="2" width="31.25" customWidth="1" style="3"/>
-    <col min="3" max="6" width="9" customWidth="1" style="3"/>
-    <col min="7" max="7" width="18.75" customWidth="1" style="3"/>
-    <col min="8" max="8" width="15" customWidth="1" style="3"/>
-    <col min="9" max="13" width="9" customWidth="1" style="3"/>
-    <col min="14" max="14" width="16.08203125" customWidth="1" style="3"/>
-    <col min="15" max="15" width="9.5" customWidth="1" style="3"/>
-    <col min="16" max="16" width="22.1640625" customWidth="1" style="3"/>
-    <col min="17" max="17" width="12.83203125" customWidth="1" style="3"/>
+    <col min="1" max="1" width="18.08203125" customWidth="1"/>
+    <col min="2" max="2" width="31.25" customWidth="1"/>
+    <col min="3" max="6" width="9" customWidth="1"/>
+    <col min="7" max="7" width="18.75" customWidth="1"/>
+    <col min="8" max="8" width="15" customWidth="1"/>
+    <col min="9" max="13" width="9" customWidth="1"/>
+    <col min="14" max="14" width="16.08203125" customWidth="1"/>
+    <col min="15" max="15" width="9.5" customWidth="1"/>
+    <col min="16" max="16" width="22.1640625" customWidth="1"/>
+    <col min="17" max="17" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" t="s">
         <v>469</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" t="s">
         <v>470</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" t="s">
         <v>471</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" t="s">
         <v>472</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" t="s">
         <v>473</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" t="s">
         <v>474</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" t="s">
         <v>475</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" t="s">
         <v>476</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" t="s">
         <v>477</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" t="s">
         <v>478</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" t="s">
         <v>83</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" t="s">
         <v>480</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" t="s">
         <v>481</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" t="s">
         <v>482</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" t="s">
         <v>483</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" t="s">
         <v>484</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" t="s">
         <v>485</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" t="s">
         <v>486</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="L2" t="s">
         <v>57</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="M2" t="s">
         <v>487</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="N2" t="s">
         <v>488</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="O2" t="s">
         <v>489</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="P2" t="s">
         <v>490</v>
       </c>
-      <c r="Q2" s="3" t="s">
+      <c r="Q2" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" t="s">
         <v>127</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" t="s">
         <v>127</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" t="s">
         <v>127</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" t="s">
         <v>124</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" t="s">
         <v>124</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" t="s">
         <v>389</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" t="s">
         <v>125</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="L3" t="s">
         <v>353</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="M3" t="s">
         <v>124</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="N3" t="s">
         <v>124</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="O3" t="s">
         <v>353</v>
       </c>
-      <c r="P3" s="3" t="s">
+      <c r="P3" t="s">
         <v>124</v>
       </c>
-      <c r="Q3" s="3" t="s">
+      <c r="Q3" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>407</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>417</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" t="s">
         <v>492</v>
       </c>
-      <c r="H6" s="3">
-        <v>1</v>
-      </c>
-      <c r="J6" s="3" t="s">
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="J6" t="s">
         <v>493</v>
       </c>
-      <c r="Q6" s="3" t="s">
+      <c r="Q6" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>419</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>424</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" t="s">
         <v>496</v>
       </c>
-      <c r="I9" s="3">
-        <v>1</v>
-      </c>
-      <c r="K9" s="3">
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="K9">
         <v>99999</v>
       </c>
-      <c r="Q9" s="3" t="s">
+      <c r="Q9" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="3" t="s">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>435</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" t="s">
         <v>498</v>
       </c>
-      <c r="Q10" s="3" t="s">
+      <c r="Q10" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>440</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" t="s">
         <v>496</v>
       </c>
-      <c r="Q12" s="3" t="s">
+      <c r="Q12" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>450</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>461</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" t="s">
         <v>492</v>
       </c>
-      <c r="H14" s="3">
-        <v>1</v>
-      </c>
-      <c r="J14" s="3" t="s">
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="J14" t="s">
         <v>501</v>
       </c>
-      <c r="Q14" s="3" t="s">
+      <c r="Q14" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="3" t="s">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>449</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" t="s">
         <v>491</v>
       </c>
     </row>
@@ -5978,7 +5723,6 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -5987,56 +5731,56 @@
   <dimension ref="A1:D4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" customWidth="1" style="3"/>
-    <col min="2" max="2" width="11.25" customWidth="1" style="3"/>
-    <col min="3" max="3" width="9" customWidth="1" style="3"/>
-    <col min="4" max="4" width="27.5" customWidth="1" style="3"/>
+    <col min="1" max="1" width="11.33203125" customWidth="1"/>
+    <col min="2" max="2" width="11.25" customWidth="1"/>
+    <col min="3" max="3" width="9" customWidth="1"/>
+    <col min="4" max="4" width="27.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" t="s">
         <v>504</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" t="s">
         <v>353</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>505</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" t="s">
         <v>506</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" t="s">
         <v>507</v>
       </c>
     </row>
@@ -6044,7 +5788,6 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -6053,125 +5796,125 @@
   <dimension ref="A1:J5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.25" customWidth="1" style="3"/>
-    <col min="2" max="2" width="9" customWidth="1" style="3"/>
-    <col min="3" max="3" width="27.25" customWidth="1" style="3"/>
-    <col min="4" max="4" width="10.83203125" customWidth="1" style="3"/>
-    <col min="5" max="10" width="9" customWidth="1" style="3"/>
+    <col min="1" max="1" width="15.25" customWidth="1"/>
+    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="3" max="3" width="27.25" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1"/>
+    <col min="5" max="10" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="I1" s="3" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I1" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" t="s">
         <v>53</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" t="s">
         <v>508</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" t="s">
         <v>76</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" t="s">
         <v>509</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" t="s">
         <v>510</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" t="s">
         <v>511</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" t="s">
         <v>348</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" t="s">
         <v>125</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" t="s">
         <v>127</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" t="s">
         <v>127</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" t="s">
         <v>127</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" t="s">
         <v>388</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>399</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" t="s">
         <v>512</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" t="s">
         <v>513</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4">
         <v>10</v>
       </c>
-      <c r="H4" s="3">
-        <v>1</v>
-      </c>
-      <c r="I4" s="3" t="s">
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4" t="s">
         <v>514</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>431</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" t="s">
         <v>512</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" t="s">
         <v>513</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5">
         <v>10</v>
       </c>
-      <c r="H5" s="3">
-        <v>1</v>
-      </c>
-      <c r="I5" s="3" t="s">
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5" t="s">
         <v>505</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="J5" t="s">
         <v>515</v>
       </c>
     </row>
@@ -6179,7 +5922,6 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -6188,122 +5930,122 @@
   <dimension ref="A1:L3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.25" customWidth="1" style="3"/>
-    <col min="2" max="2" width="28" customWidth="1" style="3"/>
-    <col min="3" max="4" width="10.08203125" customWidth="1" style="3"/>
-    <col min="5" max="10" width="11.25" customWidth="1" style="3"/>
-    <col min="11" max="11" width="6.33203125" customWidth="1" style="3"/>
-    <col min="12" max="12" width="9" customWidth="1" style="3"/>
+    <col min="1" max="1" width="15.25" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="4" width="10.08203125" customWidth="1"/>
+    <col min="5" max="10" width="11.25" customWidth="1"/>
+    <col min="11" max="11" width="6.33203125" customWidth="1"/>
+    <col min="12" max="12" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" t="s">
         <v>516</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" t="s">
         <v>517</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" t="s">
         <v>518</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" t="s">
         <v>519</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" t="s">
         <v>520</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" t="s">
         <v>521</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" t="s">
         <v>522</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" t="s">
         <v>523</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" t="s">
         <v>524</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" t="s">
         <v>526</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" t="s">
         <v>527</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" t="s">
         <v>528</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" t="s">
         <v>529</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" t="s">
         <v>530</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" t="s">
         <v>531</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" t="s">
         <v>532</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" t="s">
         <v>533</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" t="s">
         <v>534</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" t="s">
         <v>509</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="L2" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" t="s">
         <v>127</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" t="s">
         <v>126</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" t="s">
         <v>124</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" t="s">
         <v>124</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" t="s">
         <v>127</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" t="s">
         <v>127</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" t="s">
         <v>127</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" t="s">
         <v>125</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="L3" t="s">
         <v>125</v>
       </c>
     </row>
@@ -6311,7 +6053,6 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -6321,49 +6062,49 @@
   <dimension ref="A2:J3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.08203125" customWidth="1" style="3"/>
-    <col min="2" max="2" width="16.25" customWidth="1" style="3"/>
-    <col min="3" max="3" width="16.33203125" customWidth="1" style="3"/>
-    <col min="4" max="4" width="47.83203125" customWidth="1" style="3"/>
-    <col min="5" max="5" width="10.25" customWidth="1" style="3"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1" style="3"/>
-    <col min="7" max="9" width="9" customWidth="1" style="3"/>
-    <col min="10" max="10" width="11.83203125" customWidth="1" style="3"/>
+    <col min="1" max="1" width="19.08203125" customWidth="1"/>
+    <col min="2" max="2" width="16.25" customWidth="1"/>
+    <col min="3" max="3" width="16.33203125" customWidth="1"/>
+    <col min="4" max="4" width="47.83203125" customWidth="1"/>
+    <col min="5" max="5" width="10.25" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+    <col min="7" max="9" width="9" customWidth="1"/>
+    <col min="10" max="10" width="11.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" t="s">
         <v>269</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" t="s">
         <v>83</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" t="s">
         <v>535</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" t="s">
         <v>536</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" t="s">
         <v>85</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" t="s">
         <v>537</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" t="s">
         <v>297</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" t="s">
         <v>538</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1">
+    <row r="3" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -6398,7 +6139,6 @@
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -6407,134 +6147,133 @@
   <dimension ref="A1:I4"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" customWidth="1" style="3"/>
-    <col min="2" max="2" width="13.83203125" customWidth="1" style="3"/>
-    <col min="3" max="3" width="20.58203125" customWidth="1" style="3"/>
-    <col min="4" max="4" width="39.6640625" customWidth="1" style="3"/>
-    <col min="5" max="5" width="37.58203125" customWidth="1" style="3"/>
-    <col min="6" max="6" width="39.5" customWidth="1" style="3"/>
-    <col min="7" max="7" width="38.58203125" customWidth="1" style="3"/>
-    <col min="8" max="8" width="32.25" customWidth="1" style="3"/>
-    <col min="9" max="9" width="39.9140625" customWidth="1" style="3"/>
+    <col min="1" max="1" width="8.6640625" customWidth="1"/>
+    <col min="2" max="2" width="13.83203125" customWidth="1"/>
+    <col min="3" max="3" width="20.58203125" customWidth="1"/>
+    <col min="4" max="4" width="39.6640625" customWidth="1"/>
+    <col min="5" max="5" width="37.58203125" customWidth="1"/>
+    <col min="6" max="6" width="39.5" customWidth="1"/>
+    <col min="7" max="7" width="38.58203125" customWidth="1"/>
+    <col min="8" max="8" width="32.25" customWidth="1"/>
+    <col min="9" max="9" width="39.9140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" t="s">
         <v>540</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" t="s">
         <v>541</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" t="s">
         <v>542</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" t="s">
         <v>543</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" t="s">
         <v>544</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" t="s">
         <v>545</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" t="s">
         <v>546</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" t="s">
         <v>547</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" t="s">
         <v>548</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" t="s">
         <v>549</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" t="s">
         <v>550</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" t="s">
         <v>551</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" t="s">
         <v>552</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" t="s">
         <v>553</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" t="s">
         <v>554</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" t="s">
         <v>555</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" t="s">
         <v>124</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" t="s">
         <v>124</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="3">
-        <v>1</v>
-      </c>
-      <c r="D4" s="3" t="s">
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
         <v>556</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" t="s">
         <v>557</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" t="s">
         <v>558</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" t="s">
         <v>559</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" t="s">
         <v>560</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" t="s">
         <v>561</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 

--- a/Excel/Diy优胜/萃儿.xlsx
+++ b/Excel/Diy优胜/萃儿.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Diy优胜\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0176D519-F4D8-4088-8F5D-24CA0E561379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B902A7C8-D959-4363-AFD8-2DD120290FBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -326,7 +326,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="949" uniqueCount="562">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="952" uniqueCount="564">
   <si>
     <t>Id</t>
   </si>
@@ -2012,13 +2012,20 @@
   </si>
   <si>
     <t>/Spine/萃儿/back/char_4122_grabds_yun_3.skel.bytes</t>
+  </si>
+  <si>
+    <t>Extexture:token_10030_mlyss_wtrman.png</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>skill_icon_skchr_cgbird_3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2044,6 +2051,21 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2071,11 +2093,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -4719,6 +4744,9 @@
       <c r="E13" t="s">
         <v>426</v>
       </c>
+      <c r="F13" s="2" t="s">
+        <v>562</v>
+      </c>
       <c r="G13">
         <v>3</v>
       </c>
@@ -4846,6 +4874,9 @@
       <c r="E16" t="s">
         <v>434</v>
       </c>
+      <c r="F16" s="2" t="s">
+        <v>562</v>
+      </c>
       <c r="G16">
         <v>3</v>
       </c>
@@ -4925,6 +4956,9 @@
       </c>
       <c r="E18" t="s">
         <v>438</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>563</v>
       </c>
       <c r="G18">
         <v>3</v>
